--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -28,27 +28,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -61,27 +61,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -91,12 +91,12 @@
     <t>Educational buildings, equipment, materials; subsidiary services to education (boarding facilities, staff housing); language training; colloquia, seminars, lectures, etc.</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Research and studies on education effectiveness, relevance and quality; systematic evaluation and monitoring.</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
@@ -130,6 +130,9 @@
     <t>Formal and non-formal primary education for children; all elementary and first cycle systematic instruction; provision of learning materials.</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
@@ -139,9 +142,6 @@
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07 - Health</t>
   </si>
   <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>Second cycle systematic instruction at junior level.</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Elementary vocational training and secondary level technical education; on-the job training; apprenticeships; including informal vocational training.</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
@@ -256,6 +256,9 @@
     <t>Degree and diploma programmes at universities, colleges and polytechnics; scholarships.</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
@@ -265,9 +268,6 @@
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -277,12 +277,12 @@
     <t>Professional-level vocational training programmes and in-service training.</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
@@ -292,9 +292,15 @@
     <t>Health sector policy, planning and programmes; aid to health ministries, public health administration; institution capacity building and advice; medical insurance programmes; including health system strengthening and health governance; unspecified health activities.</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
@@ -304,12 +310,6 @@
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -328,12 +328,12 @@
     <t>General medical research (excluding basic health research and research for prevention and control of NCDs (12382)).</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>Laboratories, specialised clinics and hospitals (including equipment and supplies); ambulances; dental services; medical rehabilitation. Excludes noncommunicable diseases (123xx).</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -382,12 +382,12 @@
     <t>District-level hospitals, clinics and dispensaries and related medical equipment; excluding specialised hospitals and clinics (12191).</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -520,12 +520,12 @@
     <t>Population/development policies; demographic research/analysis; reproductive health research; unspecified population activities. (Use purpose code 15190 for data on migration and refugees. Use code 13096 for census work, vital registration and migration data collection.)</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -580,21 +580,21 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -604,15 +604,15 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>Large scale sewerage including trunk sewers and sewage pumping stations; domestic and industrial waste water treatment plants.</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>Municipal and industrial solid waste management, including hazardous and toxic waste; collection, disposal and treatment; landfill areas; composting and reuse.</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -715,27 +715,27 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Fiscal policy and planning; support to ministries of finance; strengthening financial and managerial accountability; public expenditure management; improving financial management systems; budget drafting; inter-governmental fiscal relations, public audit, public debt. (Use code 15114 for domestic revenue mobilisation and code 33120 for customs).</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
@@ -760,12 +760,12 @@
     <t>Decentralisation processes (including political, administrative and fiscal dimensions); intergovernmental relations and federalism; strengthening departments of regional and local government, regional and local authorities and their national associations. (Use specific sector codes for decentralisation of sector management and services.)</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
@@ -775,15 +775,15 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -859,12 +859,12 @@
     <t>Support to administration of developing countries' foreign aid (including triangular and south-south cooperation).</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -943,12 +943,12 @@
     <t>Judicial law and order sectors; policy development within ministries of justice or equivalents.</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
@@ -958,12 +958,12 @@
     <t>Police affairs and services.</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Fire-prevention and fire-fighting affairs and services.</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>Prisons</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
@@ -1027,15 +1027,15 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -1072,12 +1072,12 @@
     <t>Electoral management bodies and processes, election observation, voters' education. (Use code 15230 when in the context of an international peacekeeping operation.)</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -1099,12 +1099,12 @@
     <t>Activities that support free and uncensored flow of information on public issues; activities that increase the editorial and technical skills and the integrity of the print and broadcast media, e.g. training of journalists. (Use codes 22010-22040 for provision of equipment and capital assistance to media.)</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -1147,15 +1147,15 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -1192,12 +1192,12 @@
     <t>Collection, production, management and dissemination of statistics and data related to Government &amp; Civil Society. Includes macroeconomic statistics, government finance, fiscal and public sector statistics, support to development of administrative data infrastructure, civil society surveys.</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -1231,15 +1231,15 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02 - Defence</t>
   </si>
   <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -1276,18 +1276,18 @@
     <t>Social protection or social security strategies, legislation and administration; institution capacity building and advice; social security and other social schemes; support programmes, cash benefits, pensions and special programmes for older persons, orphans, persons with disabilities, children, mothers with newborns, those living in poverty, without jobs and other vulnerable groups; social dimensions of structural adjustment.</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Social protection schemes in the form of cash or in-kind benefits, including pensions, against the risks linked to old age.</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -1348,12 +1348,12 @@
     <t>Employment policy and planning; institution capacity building and advice; employment creation and income generation programmes; including activities specifically designed for the needs of vulnerable groups.</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
@@ -1363,12 +1363,12 @@
     <t>Housing sector policy, planning and programmes; excluding low-cost housing and slum clearance (16040).</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
@@ -1378,12 +1378,12 @@
     <t>Including slum clearance.</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -1402,15 +1402,15 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -1444,12 +1444,12 @@
     <t>Recreation and sport</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -1486,12 +1486,12 @@
     <t>Transport sector policy, planning and programmes; aid to transport ministries; institution capacity building and advice; unspecified transport; activities that combine road, rail, water and/or air transport. Includes prevention of road accidents. Whenever possible, report transport of goods under the sector of the good being transported.</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21011</t>
   </si>
   <si>
@@ -1528,12 +1528,12 @@
     <t>Road infrastructure, road vehicles; passenger road transport, motor passenger cars.</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -1615,12 +1615,12 @@
     <t>Whether or not related to transportation. Whenever possible, report storage projects under the sector of the resource being stored.</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>Communications sector policy, planning and programmes; institution capacity building and advice; including postal services development; unspecified communications activities.</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22011</t>
   </si>
   <si>
@@ -1684,12 +1684,12 @@
     <t>Radio and TV links, equipment; newspapers; printing and publishing.</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -1708,9 +1708,15 @@
     <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
@@ -1720,12 +1726,6 @@
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -1741,12 +1741,12 @@
     <t>Regulation of the energy sector, including wholesale and retail electricity provision.</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -2032,12 +2032,12 @@
     <t>Finance sector policy, planning and programmes; institution capacity building and advice; financial markets and systems.</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -2089,12 +2089,12 @@
     <t>Public sector policies and institution support to the business environment and investment climate, including business regulations, property rights, non-discrimination, investment promotion, competition policy, enterprises law, private-public partnerships.</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -2131,9 +2131,15 @@
     <t>Agricultural sector policy, planning and programmes; aid to agricultural ministries; institution capacity building and advice; unspecified agriculture.</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
@@ -2143,12 +2149,6 @@
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2419,9 +2419,15 @@
     <t>Industrial sector policy, planning and programmes; institution capacity building and advice; unspecified industrial activities; manufacturing of goods not specified below.</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
@@ -2431,12 +2437,6 @@
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2713,12 +2713,12 @@
     <t>331</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -2788,12 +2788,12 @@
     <t>Environmental policy, laws, regulations and economic instruments; administrational institutions and practices; environmental and land use planning and decision-making procedures; seminars, meetings; miscellaneous conservation and protection measures not specified below.</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -2812,12 +2812,12 @@
     <t>Including natural reserves and actions in the surrounding areas; other measures to protect endangered or vulnerable species and their habitats (e.g. wetlands preservation).</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -2848,18 +2848,18 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -2878,12 +2878,12 @@
     <t>Urban development and planning; urban management, land information systems.</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -2935,12 +2935,12 @@
     <t>Disaster risk reduction activities if not sector specific. Comprises risk assessments, structural prevention measures (e.g. flood prevention infrastructure), preparedness measures (e.g. early warning systems) normative prevention measures (e.g. building codes, land-use planning), and risk transfer systems (e.g. insurance schemes, risk funds). Also includes building local and national capacities and supporting the establishment of efficient and sustainable national structures able to promote disaster risk reduction.</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
@@ -2959,12 +2959,12 @@
     <t>Short or longer term household food security programmes and activities that improve the access of households to nutritionally adequate diets (excluding any cash transfers within broader social welfare programmes that do not have a specific food security, food acquisition or nutrition focus which should be reported under code 16010).</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -2992,12 +2992,12 @@
     <t>When sector cannot be identified.</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -3007,12 +3007,12 @@
     <t>Unearmarked contributions to the government budget; support for the implementation of macroeconomic reforms (structural adjustment programmes, poverty reduction strategies); general programme assistance (when not allocable by sector).</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
@@ -3022,12 +3022,12 @@
     <t>Supply of edible human food under national or international programmes including transport costs, cash payments made for food supplies; project food assistance aid and food assistance aid for market sales when benefiting sector not specified. Excludes food security policy and administrative management (43071), household food security programmes (43072) and emergency food assistance aid (72040). Report as multilateral: i) food assistance aid by EU financed out of its budget and allocated pro rata to EU member countries; and ii) core contributions to the World Food Programme.</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
@@ -3037,12 +3037,12 @@
     <t>Capital goods and services; lines of credit.</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -3061,18 +3061,18 @@
     <t>Actions falling outside the code headings below.</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -3130,12 +3130,12 @@
     <t>Shelter, water, sanitation, education, health services including supply of medicines and malnutrition management, including medical nutrition management; supply of other nonfood relief items (including cash and voucher delivery modalities) for the benefit of crisisaffected people, including refugees and internally displaced people in developing countries, Includes assistance delivered by or coordinated by international civil protection units in the immediate aftermath of a disaster (in-kind assistance, deployment of specially-equipped teams, logistics and transportation, or assessment and coordination by experts sent to the field). Also includes measures to promote and protect the safety, well-being, dignity and integrity of crisis-affected people including refugees and internally displaced persons in developing countries. (Activities designed to protect the security of persons or properties through the use or display of force are not reportable as ODA.)</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72011</t>
   </si>
   <si>
@@ -3181,12 +3181,12 @@
     <t>Social and economic rehabilitation in the aftermath of emergencies to facilitate recovery and resilience building and enable populations to restore their livelihoods in the wake of an emergency situation (e.g. trauma counselling and treatment, employment programmes). Includes infrastructure necessary for the delivery of humanitarian aid; restoring pre-existing essential infrastructure and facilities (e.g. water and sanitation, shelter, health care services, education); rehabilitation of basic agricultural inputs and livestock. Excludes longer-term reconstruction ('build back better') which is reportable against relevant sectors.</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
@@ -3196,24 +3196,24 @@
     <t>Building the responsiveness, capability and capacity of international, regional and national humanitarian actors to disasters. Support to the institutional capacities of national and local government, specialised humanitarian bodies, and civil society organisations to anticipate, respond and recover from the impact of potential, imminent and current hazardous events and emergency situations that pose humanitarian threats and could call for a humanitarian response. This includes risk analysis and assessment, mitigation, preparedness, such as stockpiling of emergency items and training and capacity building aimed to increase the speed and effectiveness of lifesaving assistance delivered in the occurrence of crisis.</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
@@ -3223,12 +3223,12 @@
     <t>Costs incurred in donor countries for basic assistance to asylum seekers and refugees from developing countries, up to 12 months, when costs cannot be disaggregated. See section II.6 and Annex 17.</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>93011</t>
   </si>
   <si>
@@ -3310,10 +3310,10 @@
     <t>Contributions to general development of the recipient should be included under programme assistance (51010).</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -3741,7 +3741,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -3753,7 +3753,7 @@
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
         <v>20</v>
@@ -3811,7 +3811,7 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -3823,7 +3823,7 @@
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
@@ -3846,22 +3846,22 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s">
         <v>40</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
       </c>
       <c r="K6" t="s">
         <v>41</v>
@@ -3884,19 +3884,19 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
         <v>19</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -3916,22 +3916,22 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s">
         <v>40</v>
-      </c>
-      <c r="J8" t="s">
-        <v>20</v>
       </c>
       <c r="K8" t="s">
         <v>41</v>
@@ -3951,22 +3951,22 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" t="s">
         <v>40</v>
-      </c>
-      <c r="J9" t="s">
-        <v>20</v>
       </c>
       <c r="K9" t="s">
         <v>41</v>
@@ -3986,25 +3986,25 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" t="s">
         <v>54</v>
-      </c>
-      <c r="J10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4024,19 +4024,19 @@
         <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
         <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
         <v>59</v>
       </c>
       <c r="J11" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K11" t="s">
         <v>60</v>
@@ -4056,22 +4056,22 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
         <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K12" t="s">
         <v>65</v>
@@ -4091,7 +4091,7 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
         <v>69</v>
@@ -4100,16 +4100,16 @@
         <v>17</v>
       </c>
       <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" t="s">
         <v>70</v>
       </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>71</v>
-      </c>
-      <c r="J13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4126,7 +4126,7 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F14" t="s">
         <v>69</v>
@@ -4135,13 +4135,13 @@
         <v>17</v>
       </c>
       <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" t="s">
         <v>70</v>
-      </c>
-      <c r="I14" t="s">
-        <v>75</v>
-      </c>
-      <c r="J14" t="s">
-        <v>20</v>
       </c>
       <c r="K14" t="s">
         <v>76</v>
@@ -4161,22 +4161,22 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s">
         <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" t="s">
         <v>82</v>
-      </c>
-      <c r="J15" t="s">
-        <v>20</v>
       </c>
       <c r="K15" t="s">
         <v>83</v>
@@ -4196,22 +4196,22 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s">
         <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s">
         <v>88</v>
@@ -4231,19 +4231,19 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J17" t="s">
         <v>96</v>
@@ -4266,19 +4266,19 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J18" t="s">
         <v>96</v>
@@ -4301,19 +4301,19 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="J19" t="s">
         <v>96</v>
@@ -4336,19 +4336,19 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="F20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="J20" t="s">
         <v>96</v>
@@ -4371,19 +4371,19 @@
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J21" t="s">
         <v>96</v>
@@ -4412,16 +4412,16 @@
         <v>117</v>
       </c>
       <c r="G22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I22" t="s">
         <v>59</v>
       </c>
       <c r="J22" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="K22" t="s">
         <v>60</v>
@@ -4441,22 +4441,22 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
         <v>117</v>
       </c>
       <c r="G23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s">
+        <v>95</v>
+      </c>
+      <c r="I23" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" t="s">
         <v>118</v>
-      </c>
-      <c r="I23" t="s">
-        <v>122</v>
-      </c>
-      <c r="J23" t="s">
-        <v>96</v>
       </c>
       <c r="K23" t="s">
         <v>123</v>
@@ -4482,16 +4482,16 @@
         <v>117</v>
       </c>
       <c r="G24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s">
         <v>59</v>
       </c>
       <c r="J24" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="K24" t="s">
         <v>60</v>
@@ -4517,16 +4517,16 @@
         <v>117</v>
       </c>
       <c r="G25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s">
         <v>59</v>
       </c>
       <c r="J25" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="K25" t="s">
         <v>60</v>
@@ -4552,16 +4552,16 @@
         <v>117</v>
       </c>
       <c r="G26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I26" t="s">
         <v>59</v>
       </c>
       <c r="J26" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="K26" t="s">
         <v>60</v>
@@ -4587,16 +4587,16 @@
         <v>117</v>
       </c>
       <c r="G27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I27" t="s">
         <v>59</v>
       </c>
       <c r="J27" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="K27" t="s">
         <v>60</v>
@@ -4622,16 +4622,16 @@
         <v>117</v>
       </c>
       <c r="G28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s">
         <v>59</v>
       </c>
       <c r="J28" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="K28" t="s">
         <v>60</v>
@@ -4657,16 +4657,16 @@
         <v>117</v>
       </c>
       <c r="G29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I29" t="s">
         <v>59</v>
       </c>
       <c r="J29" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="K29" t="s">
         <v>60</v>
@@ -4686,22 +4686,22 @@
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s">
         <v>117</v>
       </c>
       <c r="G30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s">
+        <v>95</v>
+      </c>
+      <c r="I30" t="s">
+        <v>59</v>
+      </c>
+      <c r="J30" t="s">
         <v>118</v>
-      </c>
-      <c r="I30" t="s">
-        <v>95</v>
-      </c>
-      <c r="J30" t="s">
-        <v>96</v>
       </c>
       <c r="K30" t="s">
         <v>97</v>
@@ -4727,16 +4727,16 @@
         <v>148</v>
       </c>
       <c r="G31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s">
         <v>59</v>
       </c>
       <c r="J31" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="K31" t="s">
         <v>60</v>
@@ -4762,16 +4762,16 @@
         <v>148</v>
       </c>
       <c r="G32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="I32" t="s">
         <v>59</v>
       </c>
       <c r="J32" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="K32" t="s">
         <v>60</v>
@@ -4797,16 +4797,16 @@
         <v>148</v>
       </c>
       <c r="G33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="I33" t="s">
         <v>59</v>
       </c>
       <c r="J33" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="K33" t="s">
         <v>60</v>
@@ -4832,16 +4832,16 @@
         <v>148</v>
       </c>
       <c r="G34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="I34" t="s">
         <v>59</v>
       </c>
       <c r="J34" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="K34" t="s">
         <v>60</v>
@@ -4867,16 +4867,16 @@
         <v>148</v>
       </c>
       <c r="G35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="I35" t="s">
         <v>59</v>
       </c>
       <c r="J35" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="K35" t="s">
         <v>60</v>
@@ -4896,22 +4896,22 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="F36" t="s">
         <v>148</v>
       </c>
       <c r="G36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s">
+        <v>95</v>
+      </c>
+      <c r="I36" t="s">
+        <v>59</v>
+      </c>
+      <c r="J36" t="s">
         <v>149</v>
-      </c>
-      <c r="I36" t="s">
-        <v>104</v>
-      </c>
-      <c r="J36" t="s">
-        <v>96</v>
       </c>
       <c r="K36" t="s">
         <v>105</v>
@@ -4936,11 +4936,11 @@
       <c r="G37" t="s">
         <v>168</v>
       </c>
+      <c r="H37" t="s">
+        <v>169</v>
+      </c>
       <c r="I37" t="s">
         <v>59</v>
-      </c>
-      <c r="J37" t="s">
-        <v>169</v>
       </c>
       <c r="K37" t="s">
         <v>60</v>
@@ -4965,11 +4965,11 @@
       <c r="G38" t="s">
         <v>168</v>
       </c>
+      <c r="H38" t="s">
+        <v>169</v>
+      </c>
       <c r="I38" t="s">
         <v>59</v>
-      </c>
-      <c r="J38" t="s">
-        <v>169</v>
       </c>
       <c r="K38" t="s">
         <v>60</v>
@@ -4994,11 +4994,11 @@
       <c r="G39" t="s">
         <v>168</v>
       </c>
+      <c r="H39" t="s">
+        <v>169</v>
+      </c>
       <c r="I39" t="s">
         <v>59</v>
-      </c>
-      <c r="J39" t="s">
-        <v>169</v>
       </c>
       <c r="K39" t="s">
         <v>60</v>
@@ -5023,11 +5023,11 @@
       <c r="G40" t="s">
         <v>168</v>
       </c>
+      <c r="H40" t="s">
+        <v>169</v>
+      </c>
       <c r="I40" t="s">
         <v>59</v>
-      </c>
-      <c r="J40" t="s">
-        <v>169</v>
       </c>
       <c r="K40" t="s">
         <v>60</v>
@@ -5047,16 +5047,16 @@
         <v>14</v>
       </c>
       <c r="E41" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G41" t="s">
         <v>168</v>
       </c>
+      <c r="H41" t="s">
+        <v>169</v>
+      </c>
       <c r="I41" t="s">
-        <v>95</v>
-      </c>
-      <c r="J41" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="K41" t="s">
         <v>97</v>
@@ -5076,16 +5076,16 @@
         <v>14</v>
       </c>
       <c r="E42" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="G42" t="s">
         <v>168</v>
       </c>
+      <c r="H42" t="s">
+        <v>169</v>
+      </c>
       <c r="I42" t="s">
-        <v>104</v>
-      </c>
-      <c r="J42" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="K42" t="s">
         <v>105</v>
@@ -5110,10 +5110,10 @@
       <c r="G43" t="s">
         <v>189</v>
       </c>
+      <c r="H43" t="s">
+        <v>190</v>
+      </c>
       <c r="I43" t="s">
-        <v>190</v>
-      </c>
-      <c r="J43" t="s">
         <v>191</v>
       </c>
       <c r="K43" t="s">
@@ -5139,11 +5139,11 @@
       <c r="G44" t="s">
         <v>189</v>
       </c>
+      <c r="H44" t="s">
+        <v>190</v>
+      </c>
       <c r="I44" t="s">
         <v>197</v>
-      </c>
-      <c r="J44" t="s">
-        <v>191</v>
       </c>
       <c r="K44" t="s">
         <v>198</v>
@@ -5168,10 +5168,10 @@
       <c r="G45" t="s">
         <v>189</v>
       </c>
+      <c r="H45" t="s">
+        <v>190</v>
+      </c>
       <c r="I45" t="s">
-        <v>190</v>
-      </c>
-      <c r="J45" t="s">
         <v>191</v>
       </c>
       <c r="K45" t="s">
@@ -5197,10 +5197,10 @@
       <c r="G46" t="s">
         <v>189</v>
       </c>
+      <c r="H46" t="s">
+        <v>190</v>
+      </c>
       <c r="I46" t="s">
-        <v>190</v>
-      </c>
-      <c r="J46" t="s">
         <v>191</v>
       </c>
       <c r="K46" t="s">
@@ -5221,16 +5221,16 @@
         <v>14</v>
       </c>
       <c r="E47" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="G47" t="s">
         <v>189</v>
       </c>
+      <c r="H47" t="s">
+        <v>190</v>
+      </c>
       <c r="I47" t="s">
-        <v>208</v>
-      </c>
-      <c r="J47" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="K47" t="s">
         <v>209</v>
@@ -5255,10 +5255,10 @@
       <c r="G48" t="s">
         <v>189</v>
       </c>
+      <c r="H48" t="s">
+        <v>190</v>
+      </c>
       <c r="I48" t="s">
-        <v>190</v>
-      </c>
-      <c r="J48" t="s">
         <v>191</v>
       </c>
       <c r="K48" t="s">
@@ -5284,10 +5284,10 @@
       <c r="G49" t="s">
         <v>189</v>
       </c>
+      <c r="H49" t="s">
+        <v>190</v>
+      </c>
       <c r="I49" t="s">
-        <v>190</v>
-      </c>
-      <c r="J49" t="s">
         <v>191</v>
       </c>
       <c r="K49" t="s">
@@ -5308,16 +5308,16 @@
         <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="G50" t="s">
         <v>189</v>
       </c>
+      <c r="H50" t="s">
+        <v>190</v>
+      </c>
       <c r="I50" t="s">
-        <v>208</v>
-      </c>
-      <c r="J50" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="K50" t="s">
         <v>209</v>
@@ -5342,10 +5342,10 @@
       <c r="G51" t="s">
         <v>189</v>
       </c>
+      <c r="H51" t="s">
+        <v>190</v>
+      </c>
       <c r="I51" t="s">
-        <v>190</v>
-      </c>
-      <c r="J51" t="s">
         <v>191</v>
       </c>
       <c r="K51" t="s">
@@ -5366,16 +5366,16 @@
         <v>14</v>
       </c>
       <c r="E52" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="G52" t="s">
         <v>189</v>
       </c>
+      <c r="H52" t="s">
+        <v>190</v>
+      </c>
       <c r="I52" t="s">
-        <v>225</v>
-      </c>
-      <c r="J52" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="K52" t="s">
         <v>226</v>
@@ -5400,11 +5400,11 @@
       <c r="G53" t="s">
         <v>189</v>
       </c>
+      <c r="H53" t="s">
+        <v>190</v>
+      </c>
       <c r="I53" t="s">
         <v>19</v>
-      </c>
-      <c r="J53" t="s">
-        <v>191</v>
       </c>
       <c r="K53" t="s">
         <v>21</v>
@@ -5459,7 +5459,7 @@
         <v>14</v>
       </c>
       <c r="E55" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F55" t="s">
         <v>234</v>
@@ -5471,7 +5471,7 @@
         <v>236</v>
       </c>
       <c r="I55" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J55" t="s">
         <v>238</v>
@@ -5494,7 +5494,7 @@
         <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F56" t="s">
         <v>234</v>
@@ -5506,7 +5506,7 @@
         <v>236</v>
       </c>
       <c r="I56" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="J56" t="s">
         <v>238</v>
@@ -5564,7 +5564,7 @@
         <v>14</v>
       </c>
       <c r="E58" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F58" t="s">
         <v>234</v>
@@ -5576,7 +5576,7 @@
         <v>236</v>
       </c>
       <c r="I58" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J58" t="s">
         <v>238</v>
@@ -5599,7 +5599,7 @@
         <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F59" t="s">
         <v>234</v>
@@ -5611,7 +5611,7 @@
         <v>236</v>
       </c>
       <c r="I59" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J59" t="s">
         <v>238</v>
@@ -5634,7 +5634,7 @@
         <v>14</v>
       </c>
       <c r="E60" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F60" t="s">
         <v>234</v>
@@ -5646,7 +5646,7 @@
         <v>236</v>
       </c>
       <c r="I60" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J60" t="s">
         <v>238</v>
@@ -5669,7 +5669,7 @@
         <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F61" t="s">
         <v>234</v>
@@ -5681,7 +5681,7 @@
         <v>236</v>
       </c>
       <c r="I61" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J61" t="s">
         <v>238</v>
@@ -5704,7 +5704,7 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F62" t="s">
         <v>234</v>
@@ -5716,7 +5716,7 @@
         <v>236</v>
       </c>
       <c r="I62" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J62" t="s">
         <v>238</v>
@@ -5739,7 +5739,7 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F63" t="s">
         <v>234</v>
@@ -5751,13 +5751,13 @@
         <v>236</v>
       </c>
       <c r="I63" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="J63" t="s">
         <v>238</v>
       </c>
       <c r="K63" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -5774,7 +5774,7 @@
         <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F64" t="s">
         <v>234</v>
@@ -5786,13 +5786,13 @@
         <v>236</v>
       </c>
       <c r="I64" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="J64" t="s">
         <v>238</v>
       </c>
       <c r="K64" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -5809,7 +5809,7 @@
         <v>14</v>
       </c>
       <c r="E65" t="s">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="F65" t="s">
         <v>234</v>
@@ -5821,7 +5821,7 @@
         <v>236</v>
       </c>
       <c r="I65" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="J65" t="s">
         <v>238</v>
@@ -5879,7 +5879,7 @@
         <v>14</v>
       </c>
       <c r="E67" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F67" t="s">
         <v>234</v>
@@ -5891,7 +5891,7 @@
         <v>236</v>
       </c>
       <c r="I67" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J67" t="s">
         <v>238</v>
@@ -5926,13 +5926,13 @@
         <v>236</v>
       </c>
       <c r="I68" t="s">
-        <v>292</v>
+        <v>237</v>
       </c>
       <c r="J68" t="s">
         <v>238</v>
       </c>
       <c r="K68" t="s">
-        <v>239</v>
+        <v>292</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -5961,13 +5961,13 @@
         <v>236</v>
       </c>
       <c r="I69" t="s">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="J69" t="s">
         <v>238</v>
       </c>
       <c r="K69" t="s">
-        <v>239</v>
+        <v>296</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -5984,7 +5984,7 @@
         <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F70" t="s">
         <v>234</v>
@@ -5996,7 +5996,7 @@
         <v>236</v>
       </c>
       <c r="I70" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="J70" t="s">
         <v>238</v>
@@ -6019,7 +6019,7 @@
         <v>14</v>
       </c>
       <c r="E71" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F71" t="s">
         <v>234</v>
@@ -6031,7 +6031,7 @@
         <v>236</v>
       </c>
       <c r="I71" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="J71" t="s">
         <v>238</v>
@@ -6089,7 +6089,7 @@
         <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="F73" t="s">
         <v>234</v>
@@ -6101,7 +6101,7 @@
         <v>236</v>
       </c>
       <c r="I73" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="J73" t="s">
         <v>238</v>
@@ -6124,7 +6124,7 @@
         <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>253</v>
+        <v>314</v>
       </c>
       <c r="F74" t="s">
         <v>234</v>
@@ -6136,7 +6136,7 @@
         <v>236</v>
       </c>
       <c r="I74" t="s">
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="J74" t="s">
         <v>238</v>
@@ -6159,7 +6159,7 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>253</v>
+        <v>319</v>
       </c>
       <c r="F75" t="s">
         <v>234</v>
@@ -6171,7 +6171,7 @@
         <v>236</v>
       </c>
       <c r="I75" t="s">
-        <v>319</v>
+        <v>254</v>
       </c>
       <c r="J75" t="s">
         <v>238</v>
@@ -6194,7 +6194,7 @@
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="F76" t="s">
         <v>234</v>
@@ -6206,7 +6206,7 @@
         <v>236</v>
       </c>
       <c r="I76" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="J76" t="s">
         <v>238</v>
@@ -6229,7 +6229,7 @@
         <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="F77" t="s">
         <v>234</v>
@@ -6241,7 +6241,7 @@
         <v>236</v>
       </c>
       <c r="I77" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="J77" t="s">
         <v>238</v>
@@ -6264,7 +6264,7 @@
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>253</v>
+        <v>314</v>
       </c>
       <c r="F78" t="s">
         <v>234</v>
@@ -6276,7 +6276,7 @@
         <v>236</v>
       </c>
       <c r="I78" t="s">
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="J78" t="s">
         <v>238</v>
@@ -6296,7 +6296,7 @@
         <v>14</v>
       </c>
       <c r="E79" t="s">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="F79" t="s">
         <v>234</v>
@@ -6308,7 +6308,7 @@
         <v>236</v>
       </c>
       <c r="I79" t="s">
-        <v>332</v>
+        <v>254</v>
       </c>
       <c r="J79" t="s">
         <v>238</v>
@@ -6448,13 +6448,13 @@
         <v>236</v>
       </c>
       <c r="I83" t="s">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="J83" t="s">
         <v>238</v>
       </c>
       <c r="K83" t="s">
-        <v>239</v>
+        <v>296</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -6471,7 +6471,7 @@
         <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="F84" t="s">
         <v>234</v>
@@ -6483,7 +6483,7 @@
         <v>236</v>
       </c>
       <c r="I84" t="s">
-        <v>352</v>
+        <v>237</v>
       </c>
       <c r="J84" t="s">
         <v>238</v>
@@ -6506,7 +6506,7 @@
         <v>14</v>
       </c>
       <c r="E85" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F85" t="s">
         <v>234</v>
@@ -6518,13 +6518,13 @@
         <v>236</v>
       </c>
       <c r="I85" t="s">
-        <v>357</v>
+        <v>237</v>
       </c>
       <c r="J85" t="s">
         <v>238</v>
       </c>
       <c r="K85" t="s">
-        <v>244</v>
+        <v>357</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -6541,7 +6541,7 @@
         <v>14</v>
       </c>
       <c r="E86" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="F86" t="s">
         <v>234</v>
@@ -6553,7 +6553,7 @@
         <v>236</v>
       </c>
       <c r="I86" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J86" t="s">
         <v>238</v>
@@ -6576,7 +6576,7 @@
         <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F87" t="s">
         <v>234</v>
@@ -6588,13 +6588,13 @@
         <v>236</v>
       </c>
       <c r="I87" t="s">
-        <v>357</v>
+        <v>237</v>
       </c>
       <c r="J87" t="s">
         <v>238</v>
       </c>
       <c r="K87" t="s">
-        <v>244</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -6608,7 +6608,7 @@
         <v>14</v>
       </c>
       <c r="E88" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F88" t="s">
         <v>234</v>
@@ -6620,7 +6620,7 @@
         <v>236</v>
       </c>
       <c r="I88" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J88" t="s">
         <v>238</v>
@@ -6643,7 +6643,7 @@
         <v>14</v>
       </c>
       <c r="E89" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F89" t="s">
         <v>234</v>
@@ -6655,7 +6655,7 @@
         <v>236</v>
       </c>
       <c r="I89" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J89" t="s">
         <v>238</v>
@@ -6783,7 +6783,7 @@
         <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F93" t="s">
         <v>234</v>
@@ -6795,7 +6795,7 @@
         <v>236</v>
       </c>
       <c r="I93" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="J93" t="s">
         <v>238</v>
@@ -6853,7 +6853,7 @@
         <v>14</v>
       </c>
       <c r="E95" t="s">
-        <v>233</v>
+        <v>392</v>
       </c>
       <c r="F95" t="s">
         <v>234</v>
@@ -6865,7 +6865,7 @@
         <v>236</v>
       </c>
       <c r="I95" t="s">
-        <v>392</v>
+        <v>237</v>
       </c>
       <c r="J95" t="s">
         <v>238</v>
@@ -6897,13 +6897,13 @@
         <v>235</v>
       </c>
       <c r="H96" t="s">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="I96" t="s">
         <v>254</v>
       </c>
       <c r="J96" t="s">
-        <v>238</v>
+        <v>398</v>
       </c>
       <c r="K96" t="s">
         <v>255</v>
@@ -6932,13 +6932,13 @@
         <v>235</v>
       </c>
       <c r="H97" t="s">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="I97" t="s">
         <v>254</v>
       </c>
       <c r="J97" t="s">
-        <v>238</v>
+        <v>398</v>
       </c>
       <c r="K97" t="s">
         <v>255</v>
@@ -6967,13 +6967,13 @@
         <v>235</v>
       </c>
       <c r="H98" t="s">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="I98" t="s">
         <v>406</v>
       </c>
       <c r="J98" t="s">
-        <v>238</v>
+        <v>398</v>
       </c>
       <c r="K98" t="s">
         <v>407</v>
@@ -7002,13 +7002,13 @@
         <v>235</v>
       </c>
       <c r="H99" t="s">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="I99" t="s">
         <v>254</v>
       </c>
       <c r="J99" t="s">
-        <v>238</v>
+        <v>398</v>
       </c>
       <c r="K99" t="s">
         <v>255</v>
@@ -7028,7 +7028,7 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
-        <v>253</v>
+        <v>319</v>
       </c>
       <c r="F100" t="s">
         <v>397</v>
@@ -7037,13 +7037,13 @@
         <v>235</v>
       </c>
       <c r="H100" t="s">
+        <v>236</v>
+      </c>
+      <c r="I100" t="s">
+        <v>254</v>
+      </c>
+      <c r="J100" t="s">
         <v>398</v>
-      </c>
-      <c r="I100" t="s">
-        <v>319</v>
-      </c>
-      <c r="J100" t="s">
-        <v>238</v>
       </c>
       <c r="K100" t="s">
         <v>320</v>
@@ -7072,13 +7072,13 @@
         <v>235</v>
       </c>
       <c r="H101" t="s">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="I101" t="s">
         <v>254</v>
       </c>
       <c r="J101" t="s">
-        <v>238</v>
+        <v>398</v>
       </c>
       <c r="K101" t="s">
         <v>255</v>
@@ -7098,16 +7098,16 @@
         <v>14</v>
       </c>
       <c r="E102" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="G102" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H102" t="s">
+        <v>422</v>
       </c>
       <c r="I102" t="s">
-        <v>421</v>
-      </c>
-      <c r="J102" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K102" t="s">
         <v>423</v>
@@ -7127,16 +7127,16 @@
         <v>14</v>
       </c>
       <c r="E103" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="G103" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H103" t="s">
+        <v>422</v>
       </c>
       <c r="I103" t="s">
-        <v>421</v>
-      </c>
-      <c r="J103" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K103" t="s">
         <v>423</v>
@@ -7156,16 +7156,16 @@
         <v>14</v>
       </c>
       <c r="E104" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="G104" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H104" t="s">
+        <v>422</v>
       </c>
       <c r="I104" t="s">
-        <v>421</v>
-      </c>
-      <c r="J104" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K104" t="s">
         <v>423</v>
@@ -7185,16 +7185,16 @@
         <v>14</v>
       </c>
       <c r="E105" t="s">
-        <v>377</v>
+        <v>433</v>
       </c>
       <c r="G105" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H105" t="s">
+        <v>422</v>
       </c>
       <c r="I105" t="s">
-        <v>433</v>
-      </c>
-      <c r="J105" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K105" t="s">
         <v>434</v>
@@ -7214,16 +7214,16 @@
         <v>14</v>
       </c>
       <c r="E106" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="G106" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H106" t="s">
+        <v>422</v>
       </c>
       <c r="I106" t="s">
-        <v>421</v>
-      </c>
-      <c r="J106" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K106" t="s">
         <v>423</v>
@@ -7246,13 +7246,13 @@
         <v>377</v>
       </c>
       <c r="G107" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H107" t="s">
+        <v>422</v>
       </c>
       <c r="I107" t="s">
         <v>378</v>
-      </c>
-      <c r="J107" t="s">
-        <v>422</v>
       </c>
       <c r="K107" t="s">
         <v>379</v>
@@ -7272,16 +7272,16 @@
         <v>14</v>
       </c>
       <c r="E108" t="s">
-        <v>377</v>
+        <v>444</v>
       </c>
       <c r="G108" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H108" t="s">
+        <v>422</v>
       </c>
       <c r="I108" t="s">
-        <v>444</v>
-      </c>
-      <c r="J108" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K108" t="s">
         <v>445</v>
@@ -7301,16 +7301,16 @@
         <v>14</v>
       </c>
       <c r="E109" t="s">
-        <v>188</v>
+        <v>449</v>
       </c>
       <c r="G109" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H109" t="s">
+        <v>422</v>
       </c>
       <c r="I109" t="s">
-        <v>449</v>
-      </c>
-      <c r="J109" t="s">
-        <v>422</v>
+        <v>191</v>
       </c>
       <c r="K109" t="s">
         <v>450</v>
@@ -7330,16 +7330,16 @@
         <v>14</v>
       </c>
       <c r="E110" t="s">
-        <v>188</v>
+        <v>454</v>
       </c>
       <c r="G110" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H110" t="s">
+        <v>422</v>
       </c>
       <c r="I110" t="s">
-        <v>454</v>
-      </c>
-      <c r="J110" t="s">
-        <v>422</v>
+        <v>191</v>
       </c>
       <c r="K110" t="s">
         <v>455</v>
@@ -7359,16 +7359,16 @@
         <v>14</v>
       </c>
       <c r="E111" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="G111" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H111" t="s">
+        <v>422</v>
       </c>
       <c r="I111" t="s">
-        <v>421</v>
-      </c>
-      <c r="J111" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K111" t="s">
         <v>423</v>
@@ -7391,13 +7391,13 @@
         <v>462</v>
       </c>
       <c r="G112" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H112" t="s">
+        <v>422</v>
       </c>
       <c r="I112" t="s">
         <v>463</v>
-      </c>
-      <c r="J112" t="s">
-        <v>422</v>
       </c>
       <c r="K112" t="s">
         <v>464</v>
@@ -7420,16 +7420,16 @@
         <v>233</v>
       </c>
       <c r="G113" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H113" t="s">
+        <v>422</v>
       </c>
       <c r="I113" t="s">
+        <v>237</v>
+      </c>
+      <c r="K113" t="s">
         <v>296</v>
-      </c>
-      <c r="J113" t="s">
-        <v>422</v>
-      </c>
-      <c r="K113" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -7446,16 +7446,16 @@
         <v>14</v>
       </c>
       <c r="E114" t="s">
-        <v>253</v>
+        <v>314</v>
       </c>
       <c r="G114" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H114" t="s">
+        <v>422</v>
       </c>
       <c r="I114" t="s">
-        <v>314</v>
-      </c>
-      <c r="J114" t="s">
-        <v>422</v>
+        <v>254</v>
       </c>
       <c r="K114" t="s">
         <v>315</v>
@@ -7478,13 +7478,13 @@
         <v>377</v>
       </c>
       <c r="G115" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H115" t="s">
+        <v>422</v>
       </c>
       <c r="I115" t="s">
         <v>378</v>
-      </c>
-      <c r="J115" t="s">
-        <v>422</v>
       </c>
       <c r="K115" t="s">
         <v>379</v>
@@ -7501,16 +7501,16 @@
         <v>14</v>
       </c>
       <c r="E116" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="G116" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H116" t="s">
+        <v>422</v>
       </c>
       <c r="I116" t="s">
-        <v>476</v>
-      </c>
-      <c r="J116" t="s">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="K116" t="s">
         <v>477</v>
@@ -7530,13 +7530,13 @@
         <v>462</v>
       </c>
       <c r="G117" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H117" t="s">
+        <v>422</v>
       </c>
       <c r="I117" t="s">
         <v>463</v>
-      </c>
-      <c r="J117" t="s">
-        <v>422</v>
       </c>
       <c r="K117" t="s">
         <v>464</v>
@@ -7559,16 +7559,16 @@
         <v>337</v>
       </c>
       <c r="G118" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H118" t="s">
+        <v>422</v>
       </c>
       <c r="I118" t="s">
+        <v>338</v>
+      </c>
+      <c r="K118" t="s">
         <v>483</v>
-      </c>
-      <c r="J118" t="s">
-        <v>422</v>
-      </c>
-      <c r="K118" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -7588,13 +7588,13 @@
         <v>377</v>
       </c>
       <c r="G119" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="H119" t="s">
+        <v>422</v>
       </c>
       <c r="I119" t="s">
         <v>378</v>
-      </c>
-      <c r="J119" t="s">
-        <v>422</v>
       </c>
       <c r="K119" t="s">
         <v>379</v>
@@ -7614,16 +7614,16 @@
         <v>14</v>
       </c>
       <c r="E120" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="G120" t="s">
         <v>490</v>
       </c>
+      <c r="H120" t="s">
+        <v>491</v>
+      </c>
       <c r="I120" t="s">
-        <v>352</v>
-      </c>
-      <c r="J120" t="s">
-        <v>491</v>
+        <v>237</v>
       </c>
       <c r="K120" t="s">
         <v>353</v>
@@ -7648,14 +7648,14 @@
       <c r="G121" t="s">
         <v>490</v>
       </c>
+      <c r="H121" t="s">
+        <v>491</v>
+      </c>
       <c r="I121" t="s">
+        <v>237</v>
+      </c>
+      <c r="K121" t="s">
         <v>296</v>
-      </c>
-      <c r="J121" t="s">
-        <v>491</v>
-      </c>
-      <c r="K121" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -7672,16 +7672,16 @@
         <v>14</v>
       </c>
       <c r="E122" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="G122" t="s">
         <v>490</v>
       </c>
+      <c r="H122" t="s">
+        <v>491</v>
+      </c>
       <c r="I122" t="s">
-        <v>352</v>
-      </c>
-      <c r="J122" t="s">
-        <v>491</v>
+        <v>237</v>
       </c>
       <c r="K122" t="s">
         <v>353</v>
@@ -7701,16 +7701,16 @@
         <v>14</v>
       </c>
       <c r="E123" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="G123" t="s">
         <v>490</v>
       </c>
+      <c r="H123" t="s">
+        <v>491</v>
+      </c>
       <c r="I123" t="s">
-        <v>352</v>
-      </c>
-      <c r="J123" t="s">
-        <v>491</v>
+        <v>237</v>
       </c>
       <c r="K123" t="s">
         <v>353</v>
@@ -7730,16 +7730,16 @@
         <v>14</v>
       </c>
       <c r="E124" t="s">
-        <v>337</v>
+        <v>504</v>
       </c>
       <c r="G124" t="s">
         <v>490</v>
       </c>
+      <c r="H124" t="s">
+        <v>491</v>
+      </c>
       <c r="I124" t="s">
-        <v>504</v>
-      </c>
-      <c r="J124" t="s">
-        <v>491</v>
+        <v>338</v>
       </c>
       <c r="K124" t="s">
         <v>505</v>
@@ -7759,16 +7759,16 @@
         <v>14</v>
       </c>
       <c r="E125" t="s">
-        <v>337</v>
+        <v>504</v>
       </c>
       <c r="G125" t="s">
         <v>490</v>
       </c>
+      <c r="H125" t="s">
+        <v>491</v>
+      </c>
       <c r="I125" t="s">
-        <v>504</v>
-      </c>
-      <c r="J125" t="s">
-        <v>491</v>
+        <v>338</v>
       </c>
       <c r="K125" t="s">
         <v>505</v>
@@ -7788,16 +7788,16 @@
         <v>14</v>
       </c>
       <c r="E126" t="s">
-        <v>337</v>
+        <v>504</v>
       </c>
       <c r="G126" t="s">
         <v>490</v>
       </c>
+      <c r="H126" t="s">
+        <v>491</v>
+      </c>
       <c r="I126" t="s">
-        <v>504</v>
-      </c>
-      <c r="J126" t="s">
-        <v>491</v>
+        <v>338</v>
       </c>
       <c r="K126" t="s">
         <v>505</v>
@@ -7817,16 +7817,16 @@
         <v>14</v>
       </c>
       <c r="E127" t="s">
-        <v>337</v>
+        <v>504</v>
       </c>
       <c r="G127" t="s">
         <v>490</v>
       </c>
+      <c r="H127" t="s">
+        <v>491</v>
+      </c>
       <c r="I127" t="s">
-        <v>504</v>
-      </c>
-      <c r="J127" t="s">
-        <v>491</v>
+        <v>338</v>
       </c>
       <c r="K127" t="s">
         <v>505</v>
@@ -7846,16 +7846,16 @@
         <v>14</v>
       </c>
       <c r="E128" t="s">
-        <v>337</v>
+        <v>504</v>
       </c>
       <c r="G128" t="s">
         <v>490</v>
       </c>
+      <c r="H128" t="s">
+        <v>491</v>
+      </c>
       <c r="I128" t="s">
-        <v>504</v>
-      </c>
-      <c r="J128" t="s">
-        <v>491</v>
+        <v>338</v>
       </c>
       <c r="K128" t="s">
         <v>505</v>
@@ -7875,19 +7875,19 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>337</v>
+        <v>504</v>
       </c>
       <c r="G129" t="s">
         <v>490</v>
       </c>
+      <c r="H129" t="s">
+        <v>491</v>
+      </c>
       <c r="I129" t="s">
+        <v>338</v>
+      </c>
+      <c r="K129" t="s">
         <v>521</v>
-      </c>
-      <c r="J129" t="s">
-        <v>491</v>
-      </c>
-      <c r="K129" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7904,19 +7904,19 @@
         <v>14</v>
       </c>
       <c r="E130" t="s">
-        <v>337</v>
+        <v>504</v>
       </c>
       <c r="G130" t="s">
         <v>490</v>
       </c>
+      <c r="H130" t="s">
+        <v>491</v>
+      </c>
       <c r="I130" t="s">
+        <v>338</v>
+      </c>
+      <c r="K130" t="s">
         <v>525</v>
-      </c>
-      <c r="J130" t="s">
-        <v>491</v>
-      </c>
-      <c r="K130" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7933,19 +7933,19 @@
         <v>14</v>
       </c>
       <c r="E131" t="s">
-        <v>337</v>
+        <v>504</v>
       </c>
       <c r="G131" t="s">
         <v>490</v>
       </c>
+      <c r="H131" t="s">
+        <v>491</v>
+      </c>
       <c r="I131" t="s">
+        <v>338</v>
+      </c>
+      <c r="K131" t="s">
         <v>529</v>
-      </c>
-      <c r="J131" t="s">
-        <v>491</v>
-      </c>
-      <c r="K131" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7962,16 +7962,16 @@
         <v>14</v>
       </c>
       <c r="E132" t="s">
-        <v>337</v>
+        <v>533</v>
       </c>
       <c r="G132" t="s">
         <v>490</v>
       </c>
+      <c r="H132" t="s">
+        <v>491</v>
+      </c>
       <c r="I132" t="s">
-        <v>533</v>
-      </c>
-      <c r="J132" t="s">
-        <v>491</v>
+        <v>338</v>
       </c>
       <c r="K132" t="s">
         <v>534</v>
@@ -7988,16 +7988,16 @@
         <v>14</v>
       </c>
       <c r="E133" t="s">
-        <v>233</v>
+        <v>392</v>
       </c>
       <c r="G133" t="s">
         <v>490</v>
       </c>
+      <c r="H133" t="s">
+        <v>491</v>
+      </c>
       <c r="I133" t="s">
-        <v>392</v>
-      </c>
-      <c r="J133" t="s">
-        <v>491</v>
+        <v>237</v>
       </c>
       <c r="K133" t="s">
         <v>393</v>
@@ -8017,16 +8017,16 @@
         <v>14</v>
       </c>
       <c r="E134" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="G134" t="s">
         <v>540</v>
       </c>
+      <c r="H134" t="s">
+        <v>541</v>
+      </c>
       <c r="I134" t="s">
-        <v>361</v>
-      </c>
-      <c r="J134" t="s">
-        <v>541</v>
+        <v>338</v>
       </c>
       <c r="K134" t="s">
         <v>362</v>
@@ -8043,16 +8043,16 @@
         <v>14</v>
       </c>
       <c r="E135" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="G135" t="s">
         <v>540</v>
       </c>
+      <c r="H135" t="s">
+        <v>541</v>
+      </c>
       <c r="I135" t="s">
-        <v>361</v>
-      </c>
-      <c r="J135" t="s">
-        <v>541</v>
+        <v>338</v>
       </c>
       <c r="K135" t="s">
         <v>362</v>
@@ -8072,16 +8072,16 @@
         <v>14</v>
       </c>
       <c r="E136" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="G136" t="s">
         <v>540</v>
       </c>
+      <c r="H136" t="s">
+        <v>541</v>
+      </c>
       <c r="I136" t="s">
-        <v>361</v>
-      </c>
-      <c r="J136" t="s">
-        <v>541</v>
+        <v>338</v>
       </c>
       <c r="K136" t="s">
         <v>362</v>
@@ -8101,16 +8101,16 @@
         <v>14</v>
       </c>
       <c r="E137" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="G137" t="s">
         <v>540</v>
       </c>
+      <c r="H137" t="s">
+        <v>541</v>
+      </c>
       <c r="I137" t="s">
-        <v>361</v>
-      </c>
-      <c r="J137" t="s">
-        <v>541</v>
+        <v>338</v>
       </c>
       <c r="K137" t="s">
         <v>362</v>
@@ -8130,16 +8130,16 @@
         <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="G138" t="s">
         <v>540</v>
       </c>
+      <c r="H138" t="s">
+        <v>541</v>
+      </c>
       <c r="I138" t="s">
-        <v>361</v>
-      </c>
-      <c r="J138" t="s">
-        <v>541</v>
+        <v>338</v>
       </c>
       <c r="K138" t="s">
         <v>362</v>
@@ -8159,16 +8159,16 @@
         <v>14</v>
       </c>
       <c r="E139" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
       <c r="G139" t="s">
         <v>540</v>
       </c>
+      <c r="H139" t="s">
+        <v>541</v>
+      </c>
       <c r="I139" t="s">
-        <v>556</v>
-      </c>
-      <c r="J139" t="s">
-        <v>541</v>
+        <v>463</v>
       </c>
       <c r="K139" t="s">
         <v>557</v>
@@ -8188,16 +8188,16 @@
         <v>14</v>
       </c>
       <c r="E140" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="G140" t="s">
         <v>540</v>
       </c>
+      <c r="H140" t="s">
+        <v>541</v>
+      </c>
       <c r="I140" t="s">
-        <v>361</v>
-      </c>
-      <c r="J140" t="s">
-        <v>541</v>
+        <v>338</v>
       </c>
       <c r="K140" t="s">
         <v>362</v>
@@ -8217,19 +8217,19 @@
         <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F141" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G141" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H141" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I141" t="s">
-        <v>567</v>
+        <v>338</v>
       </c>
       <c r="J141" t="s">
         <v>568</v>
@@ -8249,19 +8249,19 @@
         <v>14</v>
       </c>
       <c r="E142" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F142" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G142" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H142" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I142" t="s">
-        <v>567</v>
+        <v>338</v>
       </c>
       <c r="J142" t="s">
         <v>568</v>
@@ -8284,19 +8284,19 @@
         <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>337</v>
+        <v>575</v>
       </c>
       <c r="F143" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G143" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H143" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I143" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="J143" t="s">
         <v>568</v>
@@ -8319,19 +8319,19 @@
         <v>14</v>
       </c>
       <c r="E144" t="s">
-        <v>337</v>
+        <v>575</v>
       </c>
       <c r="F144" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G144" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H144" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I144" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="J144" t="s">
         <v>568</v>
@@ -8354,19 +8354,19 @@
         <v>14</v>
       </c>
       <c r="E145" t="s">
-        <v>337</v>
+        <v>575</v>
       </c>
       <c r="F145" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G145" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H145" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I145" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="J145" t="s">
         <v>568</v>
@@ -8389,19 +8389,19 @@
         <v>14</v>
       </c>
       <c r="E146" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F146" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G146" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H146" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I146" t="s">
-        <v>567</v>
+        <v>338</v>
       </c>
       <c r="J146" t="s">
         <v>568</v>
@@ -8424,22 +8424,22 @@
         <v>14</v>
       </c>
       <c r="E147" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F147" t="s">
         <v>589</v>
       </c>
       <c r="G147" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H147" t="s">
+        <v>567</v>
+      </c>
+      <c r="I147" t="s">
+        <v>338</v>
+      </c>
+      <c r="J147" t="s">
         <v>590</v>
-      </c>
-      <c r="I147" t="s">
-        <v>567</v>
-      </c>
-      <c r="J147" t="s">
-        <v>568</v>
       </c>
       <c r="K147" t="s">
         <v>569</v>
@@ -8459,22 +8459,22 @@
         <v>14</v>
       </c>
       <c r="E148" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F148" t="s">
         <v>589</v>
       </c>
       <c r="G148" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H148" t="s">
+        <v>567</v>
+      </c>
+      <c r="I148" t="s">
+        <v>338</v>
+      </c>
+      <c r="J148" t="s">
         <v>590</v>
-      </c>
-      <c r="I148" t="s">
-        <v>567</v>
-      </c>
-      <c r="J148" t="s">
-        <v>568</v>
       </c>
       <c r="K148" t="s">
         <v>569</v>
@@ -8494,22 +8494,22 @@
         <v>14</v>
       </c>
       <c r="E149" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F149" t="s">
         <v>589</v>
       </c>
       <c r="G149" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H149" t="s">
+        <v>567</v>
+      </c>
+      <c r="I149" t="s">
+        <v>338</v>
+      </c>
+      <c r="J149" t="s">
         <v>590</v>
-      </c>
-      <c r="I149" t="s">
-        <v>567</v>
-      </c>
-      <c r="J149" t="s">
-        <v>568</v>
       </c>
       <c r="K149" t="s">
         <v>569</v>
@@ -8529,22 +8529,22 @@
         <v>14</v>
       </c>
       <c r="E150" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F150" t="s">
         <v>589</v>
       </c>
       <c r="G150" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H150" t="s">
+        <v>567</v>
+      </c>
+      <c r="I150" t="s">
+        <v>338</v>
+      </c>
+      <c r="J150" t="s">
         <v>590</v>
-      </c>
-      <c r="I150" t="s">
-        <v>567</v>
-      </c>
-      <c r="J150" t="s">
-        <v>568</v>
       </c>
       <c r="K150" t="s">
         <v>569</v>
@@ -8564,22 +8564,22 @@
         <v>14</v>
       </c>
       <c r="E151" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F151" t="s">
         <v>589</v>
       </c>
       <c r="G151" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H151" t="s">
+        <v>567</v>
+      </c>
+      <c r="I151" t="s">
+        <v>338</v>
+      </c>
+      <c r="J151" t="s">
         <v>590</v>
-      </c>
-      <c r="I151" t="s">
-        <v>567</v>
-      </c>
-      <c r="J151" t="s">
-        <v>568</v>
       </c>
       <c r="K151" t="s">
         <v>569</v>
@@ -8599,22 +8599,22 @@
         <v>14</v>
       </c>
       <c r="E152" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F152" t="s">
         <v>589</v>
       </c>
       <c r="G152" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H152" t="s">
+        <v>567</v>
+      </c>
+      <c r="I152" t="s">
+        <v>338</v>
+      </c>
+      <c r="J152" t="s">
         <v>590</v>
-      </c>
-      <c r="I152" t="s">
-        <v>567</v>
-      </c>
-      <c r="J152" t="s">
-        <v>568</v>
       </c>
       <c r="K152" t="s">
         <v>569</v>
@@ -8634,22 +8634,22 @@
         <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F153" t="s">
         <v>589</v>
       </c>
       <c r="G153" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H153" t="s">
+        <v>567</v>
+      </c>
+      <c r="I153" t="s">
+        <v>338</v>
+      </c>
+      <c r="J153" t="s">
         <v>590</v>
-      </c>
-      <c r="I153" t="s">
-        <v>567</v>
-      </c>
-      <c r="J153" t="s">
-        <v>568</v>
       </c>
       <c r="K153" t="s">
         <v>569</v>
@@ -8669,22 +8669,22 @@
         <v>14</v>
       </c>
       <c r="E154" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F154" t="s">
         <v>589</v>
       </c>
       <c r="G154" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H154" t="s">
+        <v>567</v>
+      </c>
+      <c r="I154" t="s">
+        <v>338</v>
+      </c>
+      <c r="J154" t="s">
         <v>590</v>
-      </c>
-      <c r="I154" t="s">
-        <v>567</v>
-      </c>
-      <c r="J154" t="s">
-        <v>568</v>
       </c>
       <c r="K154" t="s">
         <v>569</v>
@@ -8704,22 +8704,22 @@
         <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F155" t="s">
         <v>589</v>
       </c>
       <c r="G155" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H155" t="s">
+        <v>567</v>
+      </c>
+      <c r="I155" t="s">
+        <v>338</v>
+      </c>
+      <c r="J155" t="s">
         <v>590</v>
-      </c>
-      <c r="I155" t="s">
-        <v>567</v>
-      </c>
-      <c r="J155" t="s">
-        <v>568</v>
       </c>
       <c r="K155" t="s">
         <v>569</v>
@@ -8739,22 +8739,22 @@
         <v>14</v>
       </c>
       <c r="E156" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F156" t="s">
         <v>618</v>
       </c>
       <c r="G156" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H156" t="s">
+        <v>567</v>
+      </c>
+      <c r="I156" t="s">
+        <v>338</v>
+      </c>
+      <c r="J156" t="s">
         <v>619</v>
-      </c>
-      <c r="I156" t="s">
-        <v>567</v>
-      </c>
-      <c r="J156" t="s">
-        <v>568</v>
       </c>
       <c r="K156" t="s">
         <v>569</v>
@@ -8774,25 +8774,25 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F157" t="s">
         <v>618</v>
       </c>
       <c r="G157" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H157" t="s">
+        <v>567</v>
+      </c>
+      <c r="I157" t="s">
+        <v>338</v>
+      </c>
+      <c r="J157" t="s">
         <v>619</v>
       </c>
-      <c r="I157" t="s">
+      <c r="K157" t="s">
         <v>623</v>
-      </c>
-      <c r="J157" t="s">
-        <v>568</v>
-      </c>
-      <c r="K157" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -8809,22 +8809,22 @@
         <v>14</v>
       </c>
       <c r="E158" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F158" t="s">
         <v>618</v>
       </c>
       <c r="G158" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H158" t="s">
+        <v>567</v>
+      </c>
+      <c r="I158" t="s">
+        <v>338</v>
+      </c>
+      <c r="J158" t="s">
         <v>619</v>
-      </c>
-      <c r="I158" t="s">
-        <v>567</v>
-      </c>
-      <c r="J158" t="s">
-        <v>568</v>
       </c>
       <c r="K158" t="s">
         <v>569</v>
@@ -8844,22 +8844,22 @@
         <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F159" t="s">
         <v>618</v>
       </c>
       <c r="G159" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H159" t="s">
+        <v>567</v>
+      </c>
+      <c r="I159" t="s">
+        <v>338</v>
+      </c>
+      <c r="J159" t="s">
         <v>619</v>
-      </c>
-      <c r="I159" t="s">
-        <v>567</v>
-      </c>
-      <c r="J159" t="s">
-        <v>568</v>
       </c>
       <c r="K159" t="s">
         <v>569</v>
@@ -8879,22 +8879,22 @@
         <v>14</v>
       </c>
       <c r="E160" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F160" t="s">
         <v>618</v>
       </c>
       <c r="G160" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H160" t="s">
+        <v>567</v>
+      </c>
+      <c r="I160" t="s">
+        <v>338</v>
+      </c>
+      <c r="J160" t="s">
         <v>619</v>
-      </c>
-      <c r="I160" t="s">
-        <v>567</v>
-      </c>
-      <c r="J160" t="s">
-        <v>568</v>
       </c>
       <c r="K160" t="s">
         <v>569</v>
@@ -8914,22 +8914,22 @@
         <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F161" t="s">
         <v>618</v>
       </c>
       <c r="G161" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H161" t="s">
+        <v>567</v>
+      </c>
+      <c r="I161" t="s">
+        <v>338</v>
+      </c>
+      <c r="J161" t="s">
         <v>619</v>
-      </c>
-      <c r="I161" t="s">
-        <v>567</v>
-      </c>
-      <c r="J161" t="s">
-        <v>568</v>
       </c>
       <c r="K161" t="s">
         <v>569</v>
@@ -8949,22 +8949,22 @@
         <v>14</v>
       </c>
       <c r="E162" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F162" t="s">
         <v>639</v>
       </c>
       <c r="G162" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H162" t="s">
+        <v>567</v>
+      </c>
+      <c r="I162" t="s">
+        <v>338</v>
+      </c>
+      <c r="J162" t="s">
         <v>640</v>
-      </c>
-      <c r="I162" t="s">
-        <v>567</v>
-      </c>
-      <c r="J162" t="s">
-        <v>568</v>
       </c>
       <c r="K162" t="s">
         <v>569</v>
@@ -8984,25 +8984,25 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F163" t="s">
         <v>644</v>
       </c>
       <c r="G163" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H163" t="s">
+        <v>567</v>
+      </c>
+      <c r="I163" t="s">
+        <v>338</v>
+      </c>
+      <c r="J163" t="s">
         <v>642</v>
       </c>
-      <c r="I163" t="s">
+      <c r="K163" t="s">
         <v>645</v>
-      </c>
-      <c r="J163" t="s">
-        <v>568</v>
-      </c>
-      <c r="K163" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -9019,22 +9019,22 @@
         <v>14</v>
       </c>
       <c r="E164" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F164" t="s">
         <v>649</v>
       </c>
       <c r="G164" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H164" t="s">
+        <v>567</v>
+      </c>
+      <c r="I164" t="s">
+        <v>338</v>
+      </c>
+      <c r="J164" t="s">
         <v>650</v>
-      </c>
-      <c r="I164" t="s">
-        <v>567</v>
-      </c>
-      <c r="J164" t="s">
-        <v>568</v>
       </c>
       <c r="K164" t="s">
         <v>569</v>
@@ -9054,22 +9054,22 @@
         <v>14</v>
       </c>
       <c r="E165" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F165" t="s">
         <v>649</v>
       </c>
       <c r="G165" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H165" t="s">
+        <v>567</v>
+      </c>
+      <c r="I165" t="s">
+        <v>338</v>
+      </c>
+      <c r="J165" t="s">
         <v>650</v>
-      </c>
-      <c r="I165" t="s">
-        <v>567</v>
-      </c>
-      <c r="J165" t="s">
-        <v>568</v>
       </c>
       <c r="K165" t="s">
         <v>569</v>
@@ -9089,22 +9089,22 @@
         <v>14</v>
       </c>
       <c r="E166" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F166" t="s">
         <v>649</v>
       </c>
       <c r="G166" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H166" t="s">
+        <v>567</v>
+      </c>
+      <c r="I166" t="s">
+        <v>338</v>
+      </c>
+      <c r="J166" t="s">
         <v>650</v>
-      </c>
-      <c r="I166" t="s">
-        <v>567</v>
-      </c>
-      <c r="J166" t="s">
-        <v>568</v>
       </c>
       <c r="K166" t="s">
         <v>569</v>
@@ -9124,22 +9124,22 @@
         <v>14</v>
       </c>
       <c r="E167" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F167" t="s">
         <v>649</v>
       </c>
       <c r="G167" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H167" t="s">
+        <v>567</v>
+      </c>
+      <c r="I167" t="s">
+        <v>338</v>
+      </c>
+      <c r="J167" t="s">
         <v>650</v>
-      </c>
-      <c r="I167" t="s">
-        <v>567</v>
-      </c>
-      <c r="J167" t="s">
-        <v>568</v>
       </c>
       <c r="K167" t="s">
         <v>569</v>
@@ -9159,25 +9159,25 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F168" t="s">
         <v>649</v>
       </c>
       <c r="G168" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H168" t="s">
+        <v>567</v>
+      </c>
+      <c r="I168" t="s">
+        <v>338</v>
+      </c>
+      <c r="J168" t="s">
         <v>650</v>
       </c>
-      <c r="I168" t="s">
+      <c r="K168" t="s">
         <v>663</v>
-      </c>
-      <c r="J168" t="s">
-        <v>568</v>
-      </c>
-      <c r="K168" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -9191,25 +9191,25 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F169" t="s">
         <v>649</v>
       </c>
       <c r="G169" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H169" t="s">
+        <v>567</v>
+      </c>
+      <c r="I169" t="s">
+        <v>338</v>
+      </c>
+      <c r="J169" t="s">
         <v>650</v>
       </c>
-      <c r="I169" t="s">
+      <c r="K169" t="s">
         <v>663</v>
-      </c>
-      <c r="J169" t="s">
-        <v>568</v>
-      </c>
-      <c r="K169" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -9226,22 +9226,22 @@
         <v>14</v>
       </c>
       <c r="E170" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F170" t="s">
         <v>649</v>
       </c>
       <c r="G170" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H170" t="s">
+        <v>567</v>
+      </c>
+      <c r="I170" t="s">
+        <v>338</v>
+      </c>
+      <c r="J170" t="s">
         <v>650</v>
-      </c>
-      <c r="I170" t="s">
-        <v>567</v>
-      </c>
-      <c r="J170" t="s">
-        <v>568</v>
       </c>
       <c r="K170" t="s">
         <v>569</v>
@@ -9266,11 +9266,11 @@
       <c r="G171" t="s">
         <v>672</v>
       </c>
+      <c r="H171" t="s">
+        <v>673</v>
+      </c>
       <c r="I171" t="s">
         <v>338</v>
-      </c>
-      <c r="J171" t="s">
-        <v>673</v>
       </c>
       <c r="K171" t="s">
         <v>339</v>
@@ -9290,16 +9290,16 @@
         <v>14</v>
       </c>
       <c r="E172" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G172" t="s">
         <v>672</v>
       </c>
+      <c r="H172" t="s">
+        <v>673</v>
+      </c>
       <c r="I172" t="s">
-        <v>243</v>
-      </c>
-      <c r="J172" t="s">
-        <v>673</v>
+        <v>237</v>
       </c>
       <c r="K172" t="s">
         <v>244</v>
@@ -9324,11 +9324,11 @@
       <c r="G173" t="s">
         <v>672</v>
       </c>
+      <c r="H173" t="s">
+        <v>673</v>
+      </c>
       <c r="I173" t="s">
         <v>338</v>
-      </c>
-      <c r="J173" t="s">
-        <v>673</v>
       </c>
       <c r="K173" t="s">
         <v>339</v>
@@ -9353,11 +9353,11 @@
       <c r="G174" t="s">
         <v>672</v>
       </c>
+      <c r="H174" t="s">
+        <v>673</v>
+      </c>
       <c r="I174" t="s">
         <v>338</v>
-      </c>
-      <c r="J174" t="s">
-        <v>673</v>
       </c>
       <c r="K174" t="s">
         <v>339</v>
@@ -9382,11 +9382,11 @@
       <c r="G175" t="s">
         <v>672</v>
       </c>
+      <c r="H175" t="s">
+        <v>673</v>
+      </c>
       <c r="I175" t="s">
         <v>338</v>
-      </c>
-      <c r="J175" t="s">
-        <v>673</v>
       </c>
       <c r="K175" t="s">
         <v>339</v>
@@ -9408,11 +9408,11 @@
       <c r="G176" t="s">
         <v>672</v>
       </c>
+      <c r="H176" t="s">
+        <v>673</v>
+      </c>
       <c r="I176" t="s">
         <v>338</v>
-      </c>
-      <c r="J176" t="s">
-        <v>673</v>
       </c>
       <c r="K176" t="s">
         <v>339</v>
@@ -9437,11 +9437,11 @@
       <c r="G177" t="s">
         <v>691</v>
       </c>
+      <c r="H177" t="s">
+        <v>692</v>
+      </c>
       <c r="I177" t="s">
         <v>338</v>
-      </c>
-      <c r="J177" t="s">
-        <v>692</v>
       </c>
       <c r="K177" t="s">
         <v>339</v>
@@ -9466,11 +9466,11 @@
       <c r="G178" t="s">
         <v>691</v>
       </c>
+      <c r="H178" t="s">
+        <v>692</v>
+      </c>
       <c r="I178" t="s">
         <v>338</v>
-      </c>
-      <c r="J178" t="s">
-        <v>692</v>
       </c>
       <c r="K178" t="s">
         <v>339</v>
@@ -9495,11 +9495,11 @@
       <c r="G179" t="s">
         <v>691</v>
       </c>
+      <c r="H179" t="s">
+        <v>692</v>
+      </c>
       <c r="I179" t="s">
         <v>338</v>
-      </c>
-      <c r="J179" t="s">
-        <v>692</v>
       </c>
       <c r="K179" t="s">
         <v>339</v>
@@ -9524,11 +9524,11 @@
       <c r="G180" t="s">
         <v>691</v>
       </c>
+      <c r="H180" t="s">
+        <v>692</v>
+      </c>
       <c r="I180" t="s">
         <v>338</v>
-      </c>
-      <c r="J180" t="s">
-        <v>692</v>
       </c>
       <c r="K180" t="s">
         <v>339</v>
@@ -9548,19 +9548,19 @@
         <v>14</v>
       </c>
       <c r="E181" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F181" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G181" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H181" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I181" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J181" t="s">
         <v>709</v>
@@ -9583,19 +9583,19 @@
         <v>14</v>
       </c>
       <c r="E182" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F182" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G182" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H182" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I182" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J182" t="s">
         <v>709</v>
@@ -9618,19 +9618,19 @@
         <v>14</v>
       </c>
       <c r="E183" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F183" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G183" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H183" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I183" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J183" t="s">
         <v>709</v>
@@ -9653,19 +9653,19 @@
         <v>14</v>
       </c>
       <c r="E184" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F184" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G184" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H184" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I184" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J184" t="s">
         <v>709</v>
@@ -9688,19 +9688,19 @@
         <v>14</v>
       </c>
       <c r="E185" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F185" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G185" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H185" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I185" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J185" t="s">
         <v>709</v>
@@ -9723,19 +9723,19 @@
         <v>14</v>
       </c>
       <c r="E186" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F186" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G186" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H186" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I186" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J186" t="s">
         <v>709</v>
@@ -9758,19 +9758,19 @@
         <v>14</v>
       </c>
       <c r="E187" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F187" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G187" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H187" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I187" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J187" t="s">
         <v>709</v>
@@ -9793,19 +9793,19 @@
         <v>14</v>
       </c>
       <c r="E188" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F188" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G188" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H188" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I188" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J188" t="s">
         <v>709</v>
@@ -9828,19 +9828,19 @@
         <v>14</v>
       </c>
       <c r="E189" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F189" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G189" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H189" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I189" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J189" t="s">
         <v>709</v>
@@ -9863,19 +9863,19 @@
         <v>14</v>
       </c>
       <c r="E190" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F190" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G190" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H190" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I190" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J190" t="s">
         <v>709</v>
@@ -9898,19 +9898,19 @@
         <v>14</v>
       </c>
       <c r="E191" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F191" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G191" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H191" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I191" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J191" t="s">
         <v>709</v>
@@ -9930,19 +9930,19 @@
         <v>14</v>
       </c>
       <c r="E192" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F192" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G192" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H192" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I192" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J192" t="s">
         <v>709</v>
@@ -9965,25 +9965,25 @@
         <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>337</v>
+        <v>575</v>
       </c>
       <c r="F193" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G193" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H193" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I193" t="s">
-        <v>746</v>
+        <v>338</v>
       </c>
       <c r="J193" t="s">
         <v>709</v>
       </c>
       <c r="K193" t="s">
-        <v>576</v>
+        <v>746</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -10000,19 +10000,19 @@
         <v>14</v>
       </c>
       <c r="E194" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F194" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G194" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H194" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I194" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J194" t="s">
         <v>709</v>
@@ -10035,19 +10035,19 @@
         <v>14</v>
       </c>
       <c r="E195" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F195" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G195" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H195" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I195" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J195" t="s">
         <v>709</v>
@@ -10070,19 +10070,19 @@
         <v>14</v>
       </c>
       <c r="E196" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F196" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G196" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H196" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I196" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J196" t="s">
         <v>709</v>
@@ -10105,19 +10105,19 @@
         <v>14</v>
       </c>
       <c r="E197" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F197" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G197" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H197" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I197" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J197" t="s">
         <v>709</v>
@@ -10140,19 +10140,19 @@
         <v>14</v>
       </c>
       <c r="E198" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F198" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G198" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H198" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I198" t="s">
-        <v>708</v>
+        <v>338</v>
       </c>
       <c r="J198" t="s">
         <v>709</v>
@@ -10175,25 +10175,25 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F199" t="s">
         <v>765</v>
       </c>
       <c r="G199" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H199" t="s">
+        <v>708</v>
+      </c>
+      <c r="I199" t="s">
+        <v>338</v>
+      </c>
+      <c r="J199" t="s">
         <v>766</v>
       </c>
-      <c r="I199" t="s">
+      <c r="K199" t="s">
         <v>767</v>
-      </c>
-      <c r="J199" t="s">
-        <v>709</v>
-      </c>
-      <c r="K199" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -10210,25 +10210,25 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F200" t="s">
         <v>765</v>
       </c>
       <c r="G200" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H200" t="s">
+        <v>708</v>
+      </c>
+      <c r="I200" t="s">
+        <v>338</v>
+      </c>
+      <c r="J200" t="s">
         <v>766</v>
       </c>
-      <c r="I200" t="s">
+      <c r="K200" t="s">
         <v>767</v>
-      </c>
-      <c r="J200" t="s">
-        <v>709</v>
-      </c>
-      <c r="K200" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -10245,25 +10245,25 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F201" t="s">
         <v>765</v>
       </c>
       <c r="G201" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H201" t="s">
+        <v>708</v>
+      </c>
+      <c r="I201" t="s">
+        <v>338</v>
+      </c>
+      <c r="J201" t="s">
         <v>766</v>
       </c>
-      <c r="I201" t="s">
+      <c r="K201" t="s">
         <v>767</v>
-      </c>
-      <c r="J201" t="s">
-        <v>709</v>
-      </c>
-      <c r="K201" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -10277,25 +10277,25 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F202" t="s">
         <v>765</v>
       </c>
       <c r="G202" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H202" t="s">
+        <v>708</v>
+      </c>
+      <c r="I202" t="s">
+        <v>338</v>
+      </c>
+      <c r="J202" t="s">
         <v>766</v>
       </c>
-      <c r="I202" t="s">
+      <c r="K202" t="s">
         <v>767</v>
-      </c>
-      <c r="J202" t="s">
-        <v>709</v>
-      </c>
-      <c r="K202" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -10312,25 +10312,25 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
-        <v>337</v>
+        <v>575</v>
       </c>
       <c r="F203" t="s">
         <v>765</v>
       </c>
       <c r="G203" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H203" t="s">
+        <v>708</v>
+      </c>
+      <c r="I203" t="s">
+        <v>338</v>
+      </c>
+      <c r="J203" t="s">
         <v>766</v>
       </c>
-      <c r="I203" t="s">
+      <c r="K203" t="s">
         <v>746</v>
-      </c>
-      <c r="J203" t="s">
-        <v>709</v>
-      </c>
-      <c r="K203" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10344,25 +10344,25 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F204" t="s">
         <v>765</v>
       </c>
       <c r="G204" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H204" t="s">
+        <v>708</v>
+      </c>
+      <c r="I204" t="s">
+        <v>338</v>
+      </c>
+      <c r="J204" t="s">
         <v>766</v>
       </c>
-      <c r="I204" t="s">
+      <c r="K204" t="s">
         <v>767</v>
-      </c>
-      <c r="J204" t="s">
-        <v>709</v>
-      </c>
-      <c r="K204" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -10379,25 +10379,25 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F205" t="s">
         <v>784</v>
       </c>
       <c r="G205" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H205" t="s">
+        <v>708</v>
+      </c>
+      <c r="I205" t="s">
+        <v>338</v>
+      </c>
+      <c r="J205" t="s">
         <v>785</v>
       </c>
-      <c r="I205" t="s">
+      <c r="K205" t="s">
         <v>786</v>
-      </c>
-      <c r="J205" t="s">
-        <v>709</v>
-      </c>
-      <c r="K205" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -10414,25 +10414,25 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F206" t="s">
         <v>784</v>
       </c>
       <c r="G206" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H206" t="s">
+        <v>708</v>
+      </c>
+      <c r="I206" t="s">
+        <v>338</v>
+      </c>
+      <c r="J206" t="s">
         <v>785</v>
       </c>
-      <c r="I206" t="s">
+      <c r="K206" t="s">
         <v>786</v>
-      </c>
-      <c r="J206" t="s">
-        <v>709</v>
-      </c>
-      <c r="K206" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -10446,25 +10446,25 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F207" t="s">
         <v>784</v>
       </c>
       <c r="G207" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H207" t="s">
+        <v>708</v>
+      </c>
+      <c r="I207" t="s">
+        <v>338</v>
+      </c>
+      <c r="J207" t="s">
         <v>785</v>
       </c>
-      <c r="I207" t="s">
+      <c r="K207" t="s">
         <v>786</v>
-      </c>
-      <c r="J207" t="s">
-        <v>709</v>
-      </c>
-      <c r="K207" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -10481,25 +10481,25 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
-        <v>337</v>
+        <v>575</v>
       </c>
       <c r="F208" t="s">
         <v>784</v>
       </c>
       <c r="G208" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H208" t="s">
+        <v>708</v>
+      </c>
+      <c r="I208" t="s">
+        <v>338</v>
+      </c>
+      <c r="J208" t="s">
         <v>785</v>
       </c>
-      <c r="I208" t="s">
+      <c r="K208" t="s">
         <v>746</v>
-      </c>
-      <c r="J208" t="s">
-        <v>709</v>
-      </c>
-      <c r="K208" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10516,25 +10516,25 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F209" t="s">
         <v>784</v>
       </c>
       <c r="G209" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H209" t="s">
+        <v>708</v>
+      </c>
+      <c r="I209" t="s">
+        <v>338</v>
+      </c>
+      <c r="J209" t="s">
         <v>785</v>
       </c>
-      <c r="I209" t="s">
+      <c r="K209" t="s">
         <v>786</v>
-      </c>
-      <c r="J209" t="s">
-        <v>709</v>
-      </c>
-      <c r="K209" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -10551,19 +10551,19 @@
         <v>14</v>
       </c>
       <c r="E210" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F210" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G210" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H210" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I210" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J210" t="s">
         <v>805</v>
@@ -10583,19 +10583,19 @@
         <v>14</v>
       </c>
       <c r="E211" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F211" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G211" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H211" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I211" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J211" t="s">
         <v>805</v>
@@ -10618,19 +10618,19 @@
         <v>14</v>
       </c>
       <c r="E212" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F212" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G212" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H212" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I212" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J212" t="s">
         <v>805</v>
@@ -10650,19 +10650,19 @@
         <v>14</v>
       </c>
       <c r="E213" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F213" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G213" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H213" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I213" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J213" t="s">
         <v>805</v>
@@ -10685,19 +10685,19 @@
         <v>14</v>
       </c>
       <c r="E214" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F214" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G214" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H214" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I214" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J214" t="s">
         <v>805</v>
@@ -10720,25 +10720,25 @@
         <v>14</v>
       </c>
       <c r="E215" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F215" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G215" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H215" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I215" t="s">
-        <v>767</v>
+        <v>338</v>
       </c>
       <c r="J215" t="s">
         <v>805</v>
       </c>
       <c r="K215" t="s">
-        <v>710</v>
+        <v>767</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -10755,19 +10755,19 @@
         <v>14</v>
       </c>
       <c r="E216" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F216" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G216" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H216" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I216" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J216" t="s">
         <v>805</v>
@@ -10790,19 +10790,19 @@
         <v>14</v>
       </c>
       <c r="E217" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F217" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G217" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H217" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I217" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J217" t="s">
         <v>805</v>
@@ -10822,19 +10822,19 @@
         <v>14</v>
       </c>
       <c r="E218" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F218" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G218" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H218" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I218" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J218" t="s">
         <v>805</v>
@@ -10854,19 +10854,19 @@
         <v>14</v>
       </c>
       <c r="E219" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F219" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G219" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H219" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I219" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J219" t="s">
         <v>805</v>
@@ -10889,25 +10889,25 @@
         <v>14</v>
       </c>
       <c r="E220" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F220" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G220" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H220" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I220" t="s">
-        <v>663</v>
+        <v>338</v>
       </c>
       <c r="J220" t="s">
         <v>805</v>
       </c>
       <c r="K220" t="s">
-        <v>569</v>
+        <v>663</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -10924,19 +10924,19 @@
         <v>14</v>
       </c>
       <c r="E221" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F221" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G221" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H221" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I221" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J221" t="s">
         <v>805</v>
@@ -10959,19 +10959,19 @@
         <v>14</v>
       </c>
       <c r="E222" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F222" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G222" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H222" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I222" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J222" t="s">
         <v>805</v>
@@ -10991,19 +10991,19 @@
         <v>14</v>
       </c>
       <c r="E223" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F223" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G223" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H223" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I223" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J223" t="s">
         <v>805</v>
@@ -11026,19 +11026,19 @@
         <v>14</v>
       </c>
       <c r="E224" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F224" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G224" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H224" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I224" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J224" t="s">
         <v>805</v>
@@ -11061,19 +11061,19 @@
         <v>14</v>
       </c>
       <c r="E225" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F225" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G225" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H225" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I225" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J225" t="s">
         <v>805</v>
@@ -11096,19 +11096,19 @@
         <v>14</v>
       </c>
       <c r="E226" t="s">
-        <v>337</v>
+        <v>575</v>
       </c>
       <c r="F226" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G226" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H226" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I226" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="J226" t="s">
         <v>805</v>
@@ -11131,19 +11131,19 @@
         <v>14</v>
       </c>
       <c r="E227" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F227" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G227" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H227" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I227" t="s">
-        <v>804</v>
+        <v>338</v>
       </c>
       <c r="J227" t="s">
         <v>805</v>
@@ -11169,13 +11169,13 @@
         <v>337</v>
       </c>
       <c r="F228" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G228" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H228" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I228" t="s">
         <v>338</v>
@@ -11201,25 +11201,25 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F229" t="s">
         <v>859</v>
       </c>
       <c r="G229" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H229" t="s">
+        <v>804</v>
+      </c>
+      <c r="I229" t="s">
+        <v>338</v>
+      </c>
+      <c r="J229" t="s">
         <v>860</v>
       </c>
-      <c r="I229" t="s">
+      <c r="K229" t="s">
         <v>861</v>
-      </c>
-      <c r="J229" t="s">
-        <v>805</v>
-      </c>
-      <c r="K229" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -11236,25 +11236,25 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F230" t="s">
         <v>859</v>
       </c>
       <c r="G230" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H230" t="s">
+        <v>804</v>
+      </c>
+      <c r="I230" t="s">
+        <v>338</v>
+      </c>
+      <c r="J230" t="s">
         <v>860</v>
       </c>
-      <c r="I230" t="s">
+      <c r="K230" t="s">
         <v>861</v>
-      </c>
-      <c r="J230" t="s">
-        <v>805</v>
-      </c>
-      <c r="K230" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -11271,25 +11271,25 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F231" t="s">
         <v>859</v>
       </c>
       <c r="G231" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H231" t="s">
+        <v>804</v>
+      </c>
+      <c r="I231" t="s">
+        <v>338</v>
+      </c>
+      <c r="J231" t="s">
         <v>860</v>
       </c>
-      <c r="I231" t="s">
+      <c r="K231" t="s">
         <v>623</v>
-      </c>
-      <c r="J231" t="s">
-        <v>805</v>
-      </c>
-      <c r="K231" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11306,25 +11306,25 @@
         <v>14</v>
       </c>
       <c r="E232" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F232" t="s">
         <v>859</v>
       </c>
       <c r="G232" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H232" t="s">
+        <v>804</v>
+      </c>
+      <c r="I232" t="s">
+        <v>338</v>
+      </c>
+      <c r="J232" t="s">
         <v>860</v>
       </c>
-      <c r="I232" t="s">
+      <c r="K232" t="s">
         <v>663</v>
-      </c>
-      <c r="J232" t="s">
-        <v>805</v>
-      </c>
-      <c r="K232" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11341,25 +11341,25 @@
         <v>14</v>
       </c>
       <c r="E233" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F233" t="s">
         <v>859</v>
       </c>
       <c r="G233" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H233" t="s">
+        <v>804</v>
+      </c>
+      <c r="I233" t="s">
+        <v>338</v>
+      </c>
+      <c r="J233" t="s">
         <v>860</v>
       </c>
-      <c r="I233" t="s">
+      <c r="K233" t="s">
         <v>861</v>
-      </c>
-      <c r="J233" t="s">
-        <v>805</v>
-      </c>
-      <c r="K233" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -11376,25 +11376,25 @@
         <v>14</v>
       </c>
       <c r="E234" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F234" t="s">
         <v>859</v>
       </c>
       <c r="G234" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H234" t="s">
+        <v>804</v>
+      </c>
+      <c r="I234" t="s">
+        <v>338</v>
+      </c>
+      <c r="J234" t="s">
         <v>860</v>
       </c>
-      <c r="I234" t="s">
+      <c r="K234" t="s">
         <v>861</v>
-      </c>
-      <c r="J234" t="s">
-        <v>805</v>
-      </c>
-      <c r="K234" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -11411,25 +11411,25 @@
         <v>14</v>
       </c>
       <c r="E235" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F235" t="s">
         <v>859</v>
       </c>
       <c r="G235" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H235" t="s">
+        <v>804</v>
+      </c>
+      <c r="I235" t="s">
+        <v>338</v>
+      </c>
+      <c r="J235" t="s">
         <v>860</v>
       </c>
-      <c r="I235" t="s">
+      <c r="K235" t="s">
         <v>861</v>
-      </c>
-      <c r="J235" t="s">
-        <v>805</v>
-      </c>
-      <c r="K235" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -11446,25 +11446,25 @@
         <v>14</v>
       </c>
       <c r="E236" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F236" t="s">
         <v>859</v>
       </c>
       <c r="G236" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H236" t="s">
+        <v>804</v>
+      </c>
+      <c r="I236" t="s">
+        <v>338</v>
+      </c>
+      <c r="J236" t="s">
         <v>860</v>
       </c>
-      <c r="I236" t="s">
+      <c r="K236" t="s">
         <v>861</v>
-      </c>
-      <c r="J236" t="s">
-        <v>805</v>
-      </c>
-      <c r="K236" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -11481,25 +11481,25 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F237" t="s">
         <v>859</v>
       </c>
       <c r="G237" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H237" t="s">
+        <v>804</v>
+      </c>
+      <c r="I237" t="s">
+        <v>338</v>
+      </c>
+      <c r="J237" t="s">
         <v>860</v>
       </c>
-      <c r="I237" t="s">
+      <c r="K237" t="s">
         <v>861</v>
-      </c>
-      <c r="J237" t="s">
-        <v>805</v>
-      </c>
-      <c r="K237" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -11516,25 +11516,25 @@
         <v>14</v>
       </c>
       <c r="E238" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F238" t="s">
         <v>859</v>
       </c>
       <c r="G238" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H238" t="s">
+        <v>804</v>
+      </c>
+      <c r="I238" t="s">
+        <v>338</v>
+      </c>
+      <c r="J238" t="s">
         <v>860</v>
       </c>
-      <c r="I238" t="s">
+      <c r="K238" t="s">
         <v>861</v>
-      </c>
-      <c r="J238" t="s">
-        <v>805</v>
-      </c>
-      <c r="K238" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -11551,25 +11551,25 @@
         <v>14</v>
       </c>
       <c r="E239" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F239" t="s">
         <v>892</v>
       </c>
       <c r="G239" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H239" t="s">
+        <v>804</v>
+      </c>
+      <c r="I239" t="s">
+        <v>338</v>
+      </c>
+      <c r="J239" t="s">
         <v>893</v>
       </c>
-      <c r="I239" t="s">
+      <c r="K239" t="s">
         <v>894</v>
-      </c>
-      <c r="J239" t="s">
-        <v>805</v>
-      </c>
-      <c r="K239" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -11601,7 +11601,7 @@
         <v>338</v>
       </c>
       <c r="J240" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K240" t="s">
         <v>339</v>
@@ -11636,7 +11636,7 @@
         <v>338</v>
       </c>
       <c r="J241" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K241" t="s">
         <v>339</v>
@@ -11671,7 +11671,7 @@
         <v>338</v>
       </c>
       <c r="J242" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K242" t="s">
         <v>339</v>
@@ -11706,7 +11706,7 @@
         <v>338</v>
       </c>
       <c r="J243" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K243" t="s">
         <v>339</v>
@@ -11741,7 +11741,7 @@
         <v>338</v>
       </c>
       <c r="J244" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K244" t="s">
         <v>339</v>
@@ -11776,7 +11776,7 @@
         <v>338</v>
       </c>
       <c r="J245" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K245" t="s">
         <v>339</v>
@@ -11793,7 +11793,7 @@
         <v>14</v>
       </c>
       <c r="E246" t="s">
-        <v>337</v>
+        <v>533</v>
       </c>
       <c r="F246" t="s">
         <v>918</v>
@@ -11802,16 +11802,16 @@
         <v>899</v>
       </c>
       <c r="H246" t="s">
+        <v>900</v>
+      </c>
+      <c r="I246" t="s">
+        <v>338</v>
+      </c>
+      <c r="J246" t="s">
         <v>919</v>
       </c>
-      <c r="I246" t="s">
+      <c r="K246" t="s">
         <v>920</v>
-      </c>
-      <c r="J246" t="s">
-        <v>900</v>
-      </c>
-      <c r="K246" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11833,11 +11833,11 @@
       <c r="G247" t="s">
         <v>924</v>
       </c>
+      <c r="H247" t="s">
+        <v>925</v>
+      </c>
       <c r="I247" t="s">
         <v>197</v>
-      </c>
-      <c r="J247" t="s">
-        <v>925</v>
       </c>
       <c r="K247" t="s">
         <v>198</v>
@@ -11862,11 +11862,11 @@
       <c r="G248" t="s">
         <v>924</v>
       </c>
+      <c r="H248" t="s">
+        <v>925</v>
+      </c>
       <c r="I248" t="s">
         <v>197</v>
-      </c>
-      <c r="J248" t="s">
-        <v>925</v>
       </c>
       <c r="K248" t="s">
         <v>198</v>
@@ -11886,16 +11886,16 @@
         <v>14</v>
       </c>
       <c r="E249" t="s">
-        <v>196</v>
+        <v>932</v>
       </c>
       <c r="G249" t="s">
         <v>924</v>
       </c>
+      <c r="H249" t="s">
+        <v>925</v>
+      </c>
       <c r="I249" t="s">
-        <v>932</v>
-      </c>
-      <c r="J249" t="s">
-        <v>925</v>
+        <v>197</v>
       </c>
       <c r="K249" t="s">
         <v>933</v>
@@ -11920,11 +11920,11 @@
       <c r="G250" t="s">
         <v>924</v>
       </c>
+      <c r="H250" t="s">
+        <v>925</v>
+      </c>
       <c r="I250" t="s">
         <v>197</v>
-      </c>
-      <c r="J250" t="s">
-        <v>925</v>
       </c>
       <c r="K250" t="s">
         <v>198</v>
@@ -11946,11 +11946,11 @@
       <c r="G251" t="s">
         <v>924</v>
       </c>
+      <c r="H251" t="s">
+        <v>925</v>
+      </c>
       <c r="I251" t="s">
         <v>197</v>
-      </c>
-      <c r="J251" t="s">
-        <v>925</v>
       </c>
       <c r="K251" t="s">
         <v>198</v>
@@ -11975,11 +11975,11 @@
       <c r="G252" t="s">
         <v>924</v>
       </c>
+      <c r="H252" t="s">
+        <v>925</v>
+      </c>
       <c r="I252" t="s">
         <v>197</v>
-      </c>
-      <c r="J252" t="s">
-        <v>925</v>
       </c>
       <c r="K252" t="s">
         <v>198</v>
@@ -11996,16 +11996,16 @@
         <v>14</v>
       </c>
       <c r="E253" t="s">
-        <v>337</v>
+        <v>944</v>
       </c>
       <c r="G253" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H253" t="s">
+        <v>946</v>
       </c>
       <c r="I253" t="s">
-        <v>945</v>
-      </c>
-      <c r="J253" t="s">
-        <v>946</v>
+        <v>338</v>
       </c>
       <c r="K253" t="s">
         <v>947</v>
@@ -12025,16 +12025,16 @@
         <v>14</v>
       </c>
       <c r="E254" t="s">
-        <v>188</v>
+        <v>454</v>
       </c>
       <c r="G254" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H254" t="s">
+        <v>946</v>
       </c>
       <c r="I254" t="s">
-        <v>454</v>
-      </c>
-      <c r="J254" t="s">
-        <v>946</v>
+        <v>191</v>
       </c>
       <c r="K254" t="s">
         <v>455</v>
@@ -12054,16 +12054,16 @@
         <v>14</v>
       </c>
       <c r="E255" t="s">
-        <v>188</v>
+        <v>954</v>
       </c>
       <c r="G255" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H255" t="s">
+        <v>946</v>
       </c>
       <c r="I255" t="s">
-        <v>954</v>
-      </c>
-      <c r="J255" t="s">
-        <v>946</v>
+        <v>191</v>
       </c>
       <c r="K255" t="s">
         <v>955</v>
@@ -12083,16 +12083,16 @@
         <v>14</v>
       </c>
       <c r="E256" t="s">
-        <v>188</v>
+        <v>954</v>
       </c>
       <c r="G256" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H256" t="s">
+        <v>946</v>
       </c>
       <c r="I256" t="s">
-        <v>954</v>
-      </c>
-      <c r="J256" t="s">
-        <v>946</v>
+        <v>191</v>
       </c>
       <c r="K256" t="s">
         <v>955</v>
@@ -12112,16 +12112,16 @@
         <v>14</v>
       </c>
       <c r="E257" t="s">
-        <v>188</v>
+        <v>954</v>
       </c>
       <c r="G257" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H257" t="s">
+        <v>946</v>
       </c>
       <c r="I257" t="s">
-        <v>954</v>
-      </c>
-      <c r="J257" t="s">
-        <v>946</v>
+        <v>191</v>
       </c>
       <c r="K257" t="s">
         <v>955</v>
@@ -12141,16 +12141,16 @@
         <v>14</v>
       </c>
       <c r="E258" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="G258" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H258" t="s">
+        <v>946</v>
       </c>
       <c r="I258" t="s">
-        <v>708</v>
-      </c>
-      <c r="J258" t="s">
-        <v>946</v>
+        <v>338</v>
       </c>
       <c r="K258" t="s">
         <v>710</v>
@@ -12170,16 +12170,16 @@
         <v>14</v>
       </c>
       <c r="E259" t="s">
-        <v>188</v>
+        <v>954</v>
       </c>
       <c r="G259" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H259" t="s">
+        <v>946</v>
       </c>
       <c r="I259" t="s">
-        <v>954</v>
-      </c>
-      <c r="J259" t="s">
-        <v>946</v>
+        <v>191</v>
       </c>
       <c r="K259" t="s">
         <v>955</v>
@@ -12202,13 +12202,13 @@
         <v>337</v>
       </c>
       <c r="G260" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H260" t="s">
+        <v>946</v>
       </c>
       <c r="I260" t="s">
         <v>338</v>
-      </c>
-      <c r="J260" t="s">
-        <v>946</v>
       </c>
       <c r="K260" t="s">
         <v>339</v>
@@ -12228,16 +12228,16 @@
         <v>14</v>
       </c>
       <c r="E261" t="s">
-        <v>405</v>
+        <v>973</v>
       </c>
       <c r="G261" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H261" t="s">
+        <v>946</v>
       </c>
       <c r="I261" t="s">
-        <v>973</v>
-      </c>
-      <c r="J261" t="s">
-        <v>946</v>
+        <v>406</v>
       </c>
       <c r="K261" t="s">
         <v>974</v>
@@ -12260,13 +12260,13 @@
         <v>337</v>
       </c>
       <c r="G262" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H262" t="s">
+        <v>946</v>
       </c>
       <c r="I262" t="s">
         <v>338</v>
-      </c>
-      <c r="J262" t="s">
-        <v>946</v>
       </c>
       <c r="K262" t="s">
         <v>339</v>
@@ -12286,16 +12286,16 @@
         <v>14</v>
       </c>
       <c r="E263" t="s">
-        <v>377</v>
+        <v>981</v>
       </c>
       <c r="G263" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H263" t="s">
+        <v>946</v>
       </c>
       <c r="I263" t="s">
-        <v>981</v>
-      </c>
-      <c r="J263" t="s">
-        <v>946</v>
+        <v>378</v>
       </c>
       <c r="K263" t="s">
         <v>982</v>
@@ -12318,13 +12318,13 @@
         <v>58</v>
       </c>
       <c r="G264" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H264" t="s">
+        <v>946</v>
       </c>
       <c r="I264" t="s">
         <v>59</v>
-      </c>
-      <c r="J264" t="s">
-        <v>946</v>
       </c>
       <c r="K264" t="s">
         <v>60</v>
@@ -12347,13 +12347,13 @@
         <v>15</v>
       </c>
       <c r="G265" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H265" t="s">
+        <v>946</v>
       </c>
       <c r="I265" t="s">
         <v>19</v>
-      </c>
-      <c r="J265" t="s">
-        <v>946</v>
       </c>
       <c r="K265" t="s">
         <v>21</v>
@@ -12373,16 +12373,16 @@
         <v>14</v>
       </c>
       <c r="E266" t="s">
-        <v>233</v>
+        <v>992</v>
       </c>
       <c r="G266" t="s">
-        <v>944</v>
+        <v>945</v>
+      </c>
+      <c r="H266" t="s">
+        <v>946</v>
       </c>
       <c r="I266" t="s">
-        <v>992</v>
-      </c>
-      <c r="J266" t="s">
-        <v>946</v>
+        <v>237</v>
       </c>
       <c r="K266" t="s">
         <v>993</v>
@@ -12402,16 +12402,16 @@
         <v>14</v>
       </c>
       <c r="E267" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G267" t="s">
         <v>997</v>
       </c>
+      <c r="H267" t="s">
+        <v>998</v>
+      </c>
       <c r="I267" t="s">
-        <v>243</v>
-      </c>
-      <c r="J267" t="s">
-        <v>998</v>
+        <v>237</v>
       </c>
       <c r="K267" t="s">
         <v>244</v>
@@ -12431,16 +12431,16 @@
         <v>14</v>
       </c>
       <c r="E268" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="G268" t="s">
         <v>1002</v>
       </c>
+      <c r="H268" t="s">
+        <v>1003</v>
+      </c>
       <c r="I268" t="s">
-        <v>421</v>
-      </c>
-      <c r="J268" t="s">
-        <v>1003</v>
+        <v>378</v>
       </c>
       <c r="K268" t="s">
         <v>423</v>
@@ -12460,16 +12460,16 @@
         <v>14</v>
       </c>
       <c r="E269" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G269" t="s">
         <v>1007</v>
       </c>
+      <c r="H269" t="s">
+        <v>1008</v>
+      </c>
       <c r="I269" t="s">
-        <v>243</v>
-      </c>
-      <c r="J269" t="s">
-        <v>1008</v>
+        <v>237</v>
       </c>
       <c r="K269" t="s">
         <v>244</v>
@@ -12489,16 +12489,16 @@
         <v>14</v>
       </c>
       <c r="E270" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G270" t="s">
         <v>1007</v>
       </c>
+      <c r="H270" t="s">
+        <v>1008</v>
+      </c>
       <c r="I270" t="s">
-        <v>243</v>
-      </c>
-      <c r="J270" t="s">
-        <v>1008</v>
+        <v>237</v>
       </c>
       <c r="K270" t="s">
         <v>244</v>
@@ -12518,16 +12518,16 @@
         <v>14</v>
       </c>
       <c r="E271" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="G271" t="s">
-        <v>1015</v>
+        <v>1016</v>
+      </c>
+      <c r="H271" t="s">
+        <v>1017</v>
       </c>
       <c r="I271" t="s">
-        <v>1016</v>
-      </c>
-      <c r="J271" t="s">
-        <v>1017</v>
+        <v>237</v>
       </c>
       <c r="K271" t="s">
         <v>1018</v>
@@ -12544,16 +12544,16 @@
         <v>14</v>
       </c>
       <c r="E272" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="G272" t="s">
-        <v>1015</v>
+        <v>1016</v>
+      </c>
+      <c r="H272" t="s">
+        <v>1017</v>
       </c>
       <c r="I272" t="s">
-        <v>1016</v>
-      </c>
-      <c r="J272" t="s">
-        <v>1017</v>
+        <v>237</v>
       </c>
       <c r="K272" t="s">
         <v>1018</v>
@@ -12573,16 +12573,16 @@
         <v>14</v>
       </c>
       <c r="E273" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="G273" t="s">
-        <v>1015</v>
+        <v>1016</v>
+      </c>
+      <c r="H273" t="s">
+        <v>1017</v>
       </c>
       <c r="I273" t="s">
-        <v>1016</v>
-      </c>
-      <c r="J273" t="s">
-        <v>1017</v>
+        <v>237</v>
       </c>
       <c r="K273" t="s">
         <v>1018</v>
@@ -12599,16 +12599,16 @@
         <v>14</v>
       </c>
       <c r="E274" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="G274" t="s">
-        <v>1015</v>
+        <v>1016</v>
+      </c>
+      <c r="H274" t="s">
+        <v>1017</v>
       </c>
       <c r="I274" t="s">
-        <v>1016</v>
-      </c>
-      <c r="J274" t="s">
-        <v>1017</v>
+        <v>237</v>
       </c>
       <c r="K274" t="s">
         <v>1018</v>
@@ -12628,16 +12628,16 @@
         <v>14</v>
       </c>
       <c r="E275" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="G275" t="s">
-        <v>1015</v>
+        <v>1016</v>
+      </c>
+      <c r="H275" t="s">
+        <v>1017</v>
       </c>
       <c r="I275" t="s">
-        <v>1016</v>
-      </c>
-      <c r="J275" t="s">
-        <v>1017</v>
+        <v>237</v>
       </c>
       <c r="K275" t="s">
         <v>1018</v>
@@ -12657,16 +12657,16 @@
         <v>14</v>
       </c>
       <c r="E276" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="G276" t="s">
-        <v>1015</v>
+        <v>1016</v>
+      </c>
+      <c r="H276" t="s">
+        <v>1017</v>
       </c>
       <c r="I276" t="s">
-        <v>1016</v>
-      </c>
-      <c r="J276" t="s">
-        <v>1017</v>
+        <v>237</v>
       </c>
       <c r="K276" t="s">
         <v>1018</v>
@@ -12686,16 +12686,16 @@
         <v>14</v>
       </c>
       <c r="E277" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="G277" t="s">
-        <v>1015</v>
+        <v>1016</v>
+      </c>
+      <c r="H277" t="s">
+        <v>1017</v>
       </c>
       <c r="I277" t="s">
-        <v>1016</v>
-      </c>
-      <c r="J277" t="s">
-        <v>1017</v>
+        <v>237</v>
       </c>
       <c r="K277" t="s">
         <v>1018</v>
@@ -12715,16 +12715,16 @@
         <v>14</v>
       </c>
       <c r="E278" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="G278" t="s">
         <v>1038</v>
       </c>
+      <c r="H278" t="s">
+        <v>1039</v>
+      </c>
       <c r="I278" t="s">
-        <v>421</v>
-      </c>
-      <c r="J278" t="s">
-        <v>1039</v>
+        <v>378</v>
       </c>
       <c r="K278" t="s">
         <v>423</v>
@@ -12744,16 +12744,16 @@
         <v>14</v>
       </c>
       <c r="E279" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G279" t="s">
         <v>1038</v>
       </c>
+      <c r="H279" t="s">
+        <v>1039</v>
+      </c>
       <c r="I279" t="s">
-        <v>95</v>
-      </c>
-      <c r="J279" t="s">
-        <v>1039</v>
+        <v>59</v>
       </c>
       <c r="K279" t="s">
         <v>97</v>
@@ -12778,11 +12778,11 @@
       <c r="G280" t="s">
         <v>1038</v>
       </c>
+      <c r="H280" t="s">
+        <v>1039</v>
+      </c>
       <c r="I280" t="s">
         <v>19</v>
-      </c>
-      <c r="J280" t="s">
-        <v>1039</v>
       </c>
       <c r="K280" t="s">
         <v>21</v>
@@ -12802,16 +12802,16 @@
         <v>14</v>
       </c>
       <c r="E281" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="G281" t="s">
         <v>1038</v>
       </c>
+      <c r="H281" t="s">
+        <v>1039</v>
+      </c>
       <c r="I281" t="s">
-        <v>352</v>
-      </c>
-      <c r="J281" t="s">
-        <v>1039</v>
+        <v>237</v>
       </c>
       <c r="K281" t="s">
         <v>353</v>
@@ -12836,11 +12836,11 @@
       <c r="G282" t="s">
         <v>1038</v>
       </c>
+      <c r="H282" t="s">
+        <v>1039</v>
+      </c>
       <c r="I282" t="s">
         <v>254</v>
-      </c>
-      <c r="J282" t="s">
-        <v>1039</v>
       </c>
       <c r="K282" t="s">
         <v>255</v>
@@ -12860,19 +12860,19 @@
         <v>14</v>
       </c>
       <c r="E283" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="G283" t="s">
         <v>1055</v>
       </c>
+      <c r="H283" t="s">
+        <v>1056</v>
+      </c>
       <c r="I283" t="s">
+        <v>338</v>
+      </c>
+      <c r="K283" t="s">
         <v>894</v>
-      </c>
-      <c r="J283" t="s">
-        <v>1056</v>
-      </c>
-      <c r="K283" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -12894,11 +12894,11 @@
       <c r="G284" t="s">
         <v>1060</v>
       </c>
+      <c r="H284" t="s">
+        <v>1061</v>
+      </c>
       <c r="I284" t="s">
         <v>254</v>
-      </c>
-      <c r="J284" t="s">
-        <v>1061</v>
       </c>
       <c r="K284" t="s">
         <v>255</v>
@@ -12915,16 +12915,16 @@
         <v>14</v>
       </c>
       <c r="E285" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="G285" t="s">
         <v>1064</v>
       </c>
+      <c r="H285" t="s">
+        <v>1065</v>
+      </c>
       <c r="I285" t="s">
-        <v>352</v>
-      </c>
-      <c r="J285" t="s">
-        <v>1065</v>
+        <v>237</v>
       </c>
       <c r="K285" t="s">
         <v>353</v>
@@ -12944,16 +12944,16 @@
         <v>14</v>
       </c>
       <c r="E286" t="s">
-        <v>377</v>
+        <v>981</v>
       </c>
       <c r="G286" t="s">
         <v>1069</v>
       </c>
+      <c r="H286" t="s">
+        <v>1070</v>
+      </c>
       <c r="I286" t="s">
-        <v>981</v>
-      </c>
-      <c r="J286" t="s">
-        <v>1070</v>
+        <v>378</v>
       </c>
       <c r="K286" t="s">
         <v>982</v>
@@ -12973,16 +12973,16 @@
         <v>14</v>
       </c>
       <c r="E287" t="s">
-        <v>377</v>
+        <v>981</v>
       </c>
       <c r="G287" t="s">
         <v>1069</v>
       </c>
+      <c r="H287" t="s">
+        <v>1070</v>
+      </c>
       <c r="I287" t="s">
-        <v>981</v>
-      </c>
-      <c r="J287" t="s">
-        <v>1070</v>
+        <v>378</v>
       </c>
       <c r="K287" t="s">
         <v>982</v>
@@ -13002,16 +13002,16 @@
         <v>14</v>
       </c>
       <c r="E288" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="G288" t="s">
         <v>1069</v>
       </c>
+      <c r="H288" t="s">
+        <v>1070</v>
+      </c>
       <c r="I288" t="s">
-        <v>75</v>
-      </c>
-      <c r="J288" t="s">
-        <v>1070</v>
+        <v>19</v>
       </c>
       <c r="K288" t="s">
         <v>76</v>
@@ -13036,11 +13036,11 @@
       <c r="G289" t="s">
         <v>1069</v>
       </c>
+      <c r="H289" t="s">
+        <v>1070</v>
+      </c>
       <c r="I289" t="s">
         <v>59</v>
-      </c>
-      <c r="J289" t="s">
-        <v>1070</v>
       </c>
       <c r="K289" t="s">
         <v>60</v>
@@ -13065,11 +13065,11 @@
       <c r="G290" t="s">
         <v>1069</v>
       </c>
+      <c r="H290" t="s">
+        <v>1070</v>
+      </c>
       <c r="I290" t="s">
         <v>59</v>
-      </c>
-      <c r="J290" t="s">
-        <v>1070</v>
       </c>
       <c r="K290" t="s">
         <v>60</v>
@@ -13089,16 +13089,16 @@
         <v>14</v>
       </c>
       <c r="E291" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="G291" t="s">
         <v>1069</v>
       </c>
+      <c r="H291" t="s">
+        <v>1070</v>
+      </c>
       <c r="I291" t="s">
-        <v>352</v>
-      </c>
-      <c r="J291" t="s">
-        <v>1070</v>
+        <v>237</v>
       </c>
       <c r="K291" t="s">
         <v>353</v>
@@ -13118,16 +13118,16 @@
         <v>14</v>
       </c>
       <c r="E292" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="G292" t="s">
         <v>1069</v>
       </c>
+      <c r="H292" t="s">
+        <v>1070</v>
+      </c>
       <c r="I292" t="s">
-        <v>352</v>
-      </c>
-      <c r="J292" t="s">
-        <v>1070</v>
+        <v>237</v>
       </c>
       <c r="K292" t="s">
         <v>353</v>
@@ -13147,16 +13147,16 @@
         <v>14</v>
       </c>
       <c r="E293" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="G293" t="s">
         <v>1069</v>
       </c>
+      <c r="H293" t="s">
+        <v>1070</v>
+      </c>
       <c r="I293" t="s">
-        <v>352</v>
-      </c>
-      <c r="J293" t="s">
-        <v>1070</v>
+        <v>237</v>
       </c>
       <c r="K293" t="s">
         <v>353</v>
@@ -13176,16 +13176,16 @@
         <v>14</v>
       </c>
       <c r="E294" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="G294" t="s">
         <v>1069</v>
       </c>
+      <c r="H294" t="s">
+        <v>1070</v>
+      </c>
       <c r="I294" t="s">
-        <v>352</v>
-      </c>
-      <c r="J294" t="s">
-        <v>1070</v>
+        <v>237</v>
       </c>
       <c r="K294" t="s">
         <v>353</v>
@@ -13205,16 +13205,16 @@
         <v>14</v>
       </c>
       <c r="E295" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="G295" t="s">
         <v>1098</v>
       </c>
+      <c r="H295" t="s">
+        <v>1099</v>
+      </c>
       <c r="I295" t="s">
-        <v>352</v>
-      </c>
-      <c r="J295" t="s">
-        <v>1099</v>
+        <v>237</v>
       </c>
       <c r="K295" t="s">
         <v>353</v>
@@ -13234,16 +13234,16 @@
         <v>14</v>
       </c>
       <c r="E296" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="G296" t="s">
         <v>1098</v>
       </c>
+      <c r="H296" t="s">
+        <v>1099</v>
+      </c>
       <c r="I296" t="s">
-        <v>352</v>
-      </c>
-      <c r="J296" t="s">
-        <v>1099</v>
+        <v>237</v>
       </c>
       <c r="K296" t="s">
         <v>353</v>

--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -28,27 +28,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -61,27 +61,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -190,12 +190,12 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
@@ -298,18 +298,18 @@
     <t>121</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -520,12 +520,12 @@
     <t>Population/development policies; demographic research/analysis; reproductive health research; unspecified population activities. (Use purpose code 15190 for data on migration and refugees. Use code 13096 for census work, vital registration and migration data collection.)</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -580,21 +580,21 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
@@ -715,27 +715,27 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
     <t>151</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -775,12 +775,12 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
@@ -1027,12 +1027,12 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
@@ -1147,12 +1147,12 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
@@ -1231,12 +1231,12 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
@@ -1279,15 +1279,15 @@
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1402,12 +1402,12 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
@@ -1486,12 +1486,12 @@
     <t>Transport sector policy, planning and programmes; aid to transport ministries; institution capacity building and advice; unspecified transport; activities that combine road, rail, water and/or air transport. Includes prevention of road accidents. Whenever possible, report transport of goods under the sector of the good being transported.</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21011</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>Communications sector policy, planning and programmes; institution capacity building and advice; including postal services development; unspecified communications activities.</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22011</t>
   </si>
   <si>
@@ -1714,18 +1714,18 @@
     <t>231</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -2032,12 +2032,12 @@
     <t>Finance sector policy, planning and programmes; institution capacity building and advice; financial markets and systems.</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -2089,12 +2089,12 @@
     <t>Public sector policies and institution support to the business environment and investment climate, including business regulations, property rights, non-discrimination, investment promotion, competition policy, enterprises law, private-public partnerships.</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -2137,18 +2137,18 @@
     <t>311</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2425,18 +2425,18 @@
     <t>321</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2788,12 +2788,12 @@
     <t>Environmental policy, laws, regulations and economic instruments; administrational institutions and practices; environmental and land use planning and decision-making procedures; seminars, meetings; miscellaneous conservation and protection measures not specified below.</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -2851,15 +2851,15 @@
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -3007,12 +3007,12 @@
     <t>Unearmarked contributions to the government budget; support for the implementation of macroeconomic reforms (structural adjustment programmes, poverty reduction strategies); general programme assistance (when not allocable by sector).</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
@@ -3022,12 +3022,12 @@
     <t>Supply of edible human food under national or international programmes including transport costs, cash payments made for food supplies; project food assistance aid and food assistance aid for market sales when benefiting sector not specified. Excludes food security policy and administrative management (43071), household food security programmes (43072) and emergency food assistance aid (72040). Report as multilateral: i) food assistance aid by EU financed out of its budget and allocated pro rata to EU member countries; and ii) core contributions to the World Food Programme.</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
@@ -3037,12 +3037,12 @@
     <t>Capital goods and services; lines of credit.</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -3064,15 +3064,15 @@
     <t>01.7 - Public debt transactions</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -3130,12 +3130,12 @@
     <t>Shelter, water, sanitation, education, health services including supply of medicines and malnutrition management, including medical nutrition management; supply of other nonfood relief items (including cash and voucher delivery modalities) for the benefit of crisisaffected people, including refugees and internally displaced people in developing countries, Includes assistance delivered by or coordinated by international civil protection units in the immediate aftermath of a disaster (in-kind assistance, deployment of specially-equipped teams, logistics and transportation, or assessment and coordination by experts sent to the field). Also includes measures to promote and protect the safety, well-being, dignity and integrity of crisis-affected people including refugees and internally displaced persons in developing countries. (Activities designed to protect the security of persons or properties through the use or display of force are not reportable as ODA.)</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72011</t>
   </si>
   <si>
@@ -3181,12 +3181,12 @@
     <t>Social and economic rehabilitation in the aftermath of emergencies to facilitate recovery and resilience building and enable populations to restore their livelihoods in the wake of an emergency situation (e.g. trauma counselling and treatment, employment programmes). Includes infrastructure necessary for the delivery of humanitarian aid; restoring pre-existing essential infrastructure and facilities (e.g. water and sanitation, shelter, health care services, education); rehabilitation of basic agricultural inputs and livestock. Excludes longer-term reconstruction ('build back better') which is reportable against relevant sectors.</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
@@ -3196,24 +3196,24 @@
     <t>Building the responsiveness, capability and capacity of international, regional and national humanitarian actors to disasters. Support to the institutional capacities of national and local government, specialised humanitarian bodies, and civil society organisations to anticipate, respond and recover from the impact of potential, imminent and current hazardous events and emergency situations that pose humanitarian threats and could call for a humanitarian response. This includes risk analysis and assessment, mitigation, preparedness, such as stockpiling of emergency items and training and capacity building aimed to increase the speed and effectiveness of lifesaving assistance delivered in the occurrence of crisis.</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
@@ -3223,12 +3223,12 @@
     <t>Costs incurred in donor countries for basic assistance to asylum seekers and refugees from developing countries, up to 12 months, when costs cannot be disaggregated. See section II.6 and Annex 17.</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>93011</t>
   </si>
   <si>
@@ -3310,10 +3310,10 @@
     <t>Contributions to general development of the recipient should be included under programme assistance (51010).</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -3741,10 +3741,10 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
@@ -3756,10 +3756,10 @@
         <v>19</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3811,10 +3811,10 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
         <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
@@ -3826,10 +3826,10 @@
         <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3846,25 +3846,25 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>39</v>
       </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
         <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3884,19 +3884,19 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
         <v>39</v>
       </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
         <v>19</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -3916,25 +3916,25 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>39</v>
       </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
       </c>
       <c r="J8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3951,25 +3951,25 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
         <v>38</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>39</v>
       </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
       </c>
       <c r="J9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3986,25 +3986,25 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
         <v>38</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>39</v>
       </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
       </c>
       <c r="J10" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4024,22 +4024,22 @@
         <v>58</v>
       </c>
       <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
         <v>39</v>
       </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J11" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K11" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4056,25 +4056,25 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
         <v>64</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="K12" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4091,25 +4091,25 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
         <v>64</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>69</v>
       </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="I13" t="s">
         <v>19</v>
       </c>
       <c r="J13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K13" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4126,25 +4126,25 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
         <v>75</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>69</v>
       </c>
-      <c r="G14" t="s">
-        <v>17</v>
-      </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
         <v>19</v>
       </c>
       <c r="J14" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K14" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4161,25 +4161,25 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
         <v>80</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>81</v>
       </c>
-      <c r="G15" t="s">
-        <v>17</v>
-      </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s">
         <v>19</v>
       </c>
       <c r="J15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K15" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4196,25 +4196,25 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
         <v>87</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>81</v>
       </c>
-      <c r="G16" t="s">
-        <v>17</v>
-      </c>
       <c r="H16" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s">
         <v>19</v>
       </c>
       <c r="J16" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4231,19 +4231,19 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" t="s">
         <v>92</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>93</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>94</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>95</v>
-      </c>
-      <c r="I17" t="s">
-        <v>59</v>
       </c>
       <c r="J17" t="s">
         <v>96</v>
@@ -4266,19 +4266,19 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" t="s">
         <v>92</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>93</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>94</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>95</v>
-      </c>
-      <c r="I18" t="s">
-        <v>59</v>
       </c>
       <c r="J18" t="s">
         <v>96</v>
@@ -4301,25 +4301,25 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" t="s">
         <v>104</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>93</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>94</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>95</v>
       </c>
-      <c r="I19" t="s">
-        <v>59</v>
-      </c>
       <c r="J19" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="K19" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4336,25 +4336,25 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" t="s">
         <v>109</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>93</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>94</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>95</v>
       </c>
-      <c r="I20" t="s">
-        <v>59</v>
-      </c>
       <c r="J20" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="K20" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4371,19 +4371,19 @@
         <v>14</v>
       </c>
       <c r="E21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" t="s">
         <v>92</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>93</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>94</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>95</v>
-      </c>
-      <c r="I21" t="s">
-        <v>59</v>
       </c>
       <c r="J21" t="s">
         <v>96</v>
@@ -4409,22 +4409,22 @@
         <v>58</v>
       </c>
       <c r="F22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" t="s">
         <v>117</v>
       </c>
-      <c r="G22" t="s">
-        <v>94</v>
-      </c>
       <c r="H22" t="s">
+        <v>118</v>
+      </c>
+      <c r="I22" t="s">
         <v>95</v>
       </c>
-      <c r="I22" t="s">
-        <v>59</v>
-      </c>
       <c r="J22" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="K22" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4441,25 +4441,25 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" t="s">
         <v>122</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>117</v>
       </c>
-      <c r="G23" t="s">
-        <v>94</v>
-      </c>
       <c r="H23" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" t="s">
         <v>95</v>
       </c>
-      <c r="I23" t="s">
-        <v>59</v>
-      </c>
       <c r="J23" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K23" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4479,22 +4479,22 @@
         <v>58</v>
       </c>
       <c r="F24" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" t="s">
         <v>117</v>
       </c>
-      <c r="G24" t="s">
-        <v>94</v>
-      </c>
       <c r="H24" t="s">
+        <v>118</v>
+      </c>
+      <c r="I24" t="s">
         <v>95</v>
       </c>
-      <c r="I24" t="s">
-        <v>59</v>
-      </c>
       <c r="J24" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="K24" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4514,22 +4514,22 @@
         <v>58</v>
       </c>
       <c r="F25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" t="s">
         <v>117</v>
       </c>
-      <c r="G25" t="s">
-        <v>94</v>
-      </c>
       <c r="H25" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" t="s">
         <v>95</v>
       </c>
-      <c r="I25" t="s">
-        <v>59</v>
-      </c>
       <c r="J25" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="K25" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4549,22 +4549,22 @@
         <v>58</v>
       </c>
       <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" t="s">
         <v>117</v>
       </c>
-      <c r="G26" t="s">
-        <v>94</v>
-      </c>
       <c r="H26" t="s">
+        <v>118</v>
+      </c>
+      <c r="I26" t="s">
         <v>95</v>
       </c>
-      <c r="I26" t="s">
-        <v>59</v>
-      </c>
       <c r="J26" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="K26" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4584,22 +4584,22 @@
         <v>58</v>
       </c>
       <c r="F27" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" t="s">
         <v>117</v>
       </c>
-      <c r="G27" t="s">
-        <v>94</v>
-      </c>
       <c r="H27" t="s">
+        <v>118</v>
+      </c>
+      <c r="I27" t="s">
         <v>95</v>
       </c>
-      <c r="I27" t="s">
-        <v>59</v>
-      </c>
       <c r="J27" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="K27" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4619,22 +4619,22 @@
         <v>58</v>
       </c>
       <c r="F28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" t="s">
         <v>117</v>
       </c>
-      <c r="G28" t="s">
-        <v>94</v>
-      </c>
       <c r="H28" t="s">
+        <v>118</v>
+      </c>
+      <c r="I28" t="s">
         <v>95</v>
       </c>
-      <c r="I28" t="s">
-        <v>59</v>
-      </c>
       <c r="J28" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="K28" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4654,22 +4654,22 @@
         <v>58</v>
       </c>
       <c r="F29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" t="s">
         <v>117</v>
       </c>
-      <c r="G29" t="s">
-        <v>94</v>
-      </c>
       <c r="H29" t="s">
+        <v>118</v>
+      </c>
+      <c r="I29" t="s">
         <v>95</v>
       </c>
-      <c r="I29" t="s">
-        <v>59</v>
-      </c>
       <c r="J29" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="K29" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4686,22 +4686,22 @@
         <v>14</v>
       </c>
       <c r="E30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" t="s">
         <v>92</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>117</v>
       </c>
-      <c r="G30" t="s">
-        <v>94</v>
-      </c>
       <c r="H30" t="s">
+        <v>118</v>
+      </c>
+      <c r="I30" t="s">
         <v>95</v>
       </c>
-      <c r="I30" t="s">
-        <v>59</v>
-      </c>
       <c r="J30" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="K30" t="s">
         <v>97</v>
@@ -4724,22 +4724,22 @@
         <v>58</v>
       </c>
       <c r="F31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" t="s">
         <v>148</v>
       </c>
-      <c r="G31" t="s">
-        <v>94</v>
-      </c>
       <c r="H31" t="s">
+        <v>149</v>
+      </c>
+      <c r="I31" t="s">
         <v>95</v>
       </c>
-      <c r="I31" t="s">
-        <v>59</v>
-      </c>
       <c r="J31" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="K31" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4759,22 +4759,22 @@
         <v>58</v>
       </c>
       <c r="F32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" t="s">
         <v>148</v>
       </c>
-      <c r="G32" t="s">
-        <v>94</v>
-      </c>
       <c r="H32" t="s">
+        <v>149</v>
+      </c>
+      <c r="I32" t="s">
         <v>95</v>
       </c>
-      <c r="I32" t="s">
-        <v>59</v>
-      </c>
       <c r="J32" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="K32" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4794,22 +4794,22 @@
         <v>58</v>
       </c>
       <c r="F33" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" t="s">
         <v>148</v>
       </c>
-      <c r="G33" t="s">
-        <v>94</v>
-      </c>
       <c r="H33" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" t="s">
         <v>95</v>
       </c>
-      <c r="I33" t="s">
-        <v>59</v>
-      </c>
       <c r="J33" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="K33" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4829,22 +4829,22 @@
         <v>58</v>
       </c>
       <c r="F34" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" t="s">
         <v>148</v>
       </c>
-      <c r="G34" t="s">
-        <v>94</v>
-      </c>
       <c r="H34" t="s">
+        <v>149</v>
+      </c>
+      <c r="I34" t="s">
         <v>95</v>
       </c>
-      <c r="I34" t="s">
-        <v>59</v>
-      </c>
       <c r="J34" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="K34" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4864,22 +4864,22 @@
         <v>58</v>
       </c>
       <c r="F35" t="s">
+        <v>59</v>
+      </c>
+      <c r="G35" t="s">
         <v>148</v>
       </c>
-      <c r="G35" t="s">
-        <v>94</v>
-      </c>
       <c r="H35" t="s">
+        <v>149</v>
+      </c>
+      <c r="I35" t="s">
         <v>95</v>
       </c>
-      <c r="I35" t="s">
-        <v>59</v>
-      </c>
       <c r="J35" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="K35" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4896,25 +4896,25 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" t="s">
         <v>104</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>148</v>
       </c>
-      <c r="G36" t="s">
-        <v>94</v>
-      </c>
       <c r="H36" t="s">
+        <v>149</v>
+      </c>
+      <c r="I36" t="s">
         <v>95</v>
       </c>
-      <c r="I36" t="s">
-        <v>59</v>
-      </c>
       <c r="J36" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="K36" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4933,17 +4933,17 @@
       <c r="E37" t="s">
         <v>58</v>
       </c>
-      <c r="G37" t="s">
+      <c r="F37" t="s">
+        <v>59</v>
+      </c>
+      <c r="I37" t="s">
         <v>168</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K37" t="s">
         <v>169</v>
-      </c>
-      <c r="I37" t="s">
-        <v>59</v>
-      </c>
-      <c r="K37" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4962,17 +4962,17 @@
       <c r="E38" t="s">
         <v>58</v>
       </c>
-      <c r="G38" t="s">
+      <c r="F38" t="s">
+        <v>59</v>
+      </c>
+      <c r="I38" t="s">
         <v>168</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K38" t="s">
         <v>169</v>
-      </c>
-      <c r="I38" t="s">
-        <v>59</v>
-      </c>
-      <c r="K38" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4991,17 +4991,17 @@
       <c r="E39" t="s">
         <v>58</v>
       </c>
-      <c r="G39" t="s">
+      <c r="F39" t="s">
+        <v>59</v>
+      </c>
+      <c r="I39" t="s">
         <v>168</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" t="s">
+        <v>60</v>
+      </c>
+      <c r="K39" t="s">
         <v>169</v>
-      </c>
-      <c r="I39" t="s">
-        <v>59</v>
-      </c>
-      <c r="K39" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5020,17 +5020,17 @@
       <c r="E40" t="s">
         <v>58</v>
       </c>
-      <c r="G40" t="s">
+      <c r="F40" t="s">
+        <v>59</v>
+      </c>
+      <c r="I40" t="s">
         <v>168</v>
       </c>
-      <c r="H40" t="s">
+      <c r="J40" t="s">
+        <v>60</v>
+      </c>
+      <c r="K40" t="s">
         <v>169</v>
-      </c>
-      <c r="I40" t="s">
-        <v>59</v>
-      </c>
-      <c r="K40" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5047,19 +5047,19 @@
         <v>14</v>
       </c>
       <c r="E41" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" t="s">
         <v>92</v>
       </c>
-      <c r="G41" t="s">
+      <c r="I41" t="s">
         <v>168</v>
       </c>
-      <c r="H41" t="s">
+      <c r="J41" t="s">
+        <v>96</v>
+      </c>
+      <c r="K41" t="s">
         <v>169</v>
-      </c>
-      <c r="I41" t="s">
-        <v>59</v>
-      </c>
-      <c r="K41" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5076,19 +5076,19 @@
         <v>14</v>
       </c>
       <c r="E42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42" t="s">
         <v>104</v>
       </c>
-      <c r="G42" t="s">
+      <c r="I42" t="s">
         <v>168</v>
       </c>
-      <c r="H42" t="s">
+      <c r="J42" t="s">
+        <v>105</v>
+      </c>
+      <c r="K42" t="s">
         <v>169</v>
-      </c>
-      <c r="I42" t="s">
-        <v>59</v>
-      </c>
-      <c r="K42" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5107,13 +5107,13 @@
       <c r="E43" t="s">
         <v>188</v>
       </c>
-      <c r="G43" t="s">
+      <c r="F43" t="s">
         <v>189</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>190</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>191</v>
       </c>
       <c r="K43" t="s">
@@ -5136,17 +5136,17 @@
       <c r="E44" t="s">
         <v>196</v>
       </c>
-      <c r="G44" t="s">
-        <v>189</v>
-      </c>
-      <c r="H44" t="s">
+      <c r="F44" t="s">
+        <v>197</v>
+      </c>
+      <c r="I44" t="s">
         <v>190</v>
       </c>
-      <c r="I44" t="s">
-        <v>197</v>
+      <c r="J44" t="s">
+        <v>198</v>
       </c>
       <c r="K44" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5165,13 +5165,13 @@
       <c r="E45" t="s">
         <v>188</v>
       </c>
-      <c r="G45" t="s">
+      <c r="F45" t="s">
         <v>189</v>
       </c>
-      <c r="H45" t="s">
+      <c r="I45" t="s">
         <v>190</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>191</v>
       </c>
       <c r="K45" t="s">
@@ -5194,13 +5194,13 @@
       <c r="E46" t="s">
         <v>188</v>
       </c>
-      <c r="G46" t="s">
+      <c r="F46" t="s">
         <v>189</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>190</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>191</v>
       </c>
       <c r="K46" t="s">
@@ -5221,19 +5221,19 @@
         <v>14</v>
       </c>
       <c r="E47" t="s">
+        <v>196</v>
+      </c>
+      <c r="F47" t="s">
         <v>208</v>
       </c>
-      <c r="G47" t="s">
-        <v>189</v>
-      </c>
-      <c r="H47" t="s">
+      <c r="I47" t="s">
         <v>190</v>
       </c>
-      <c r="I47" t="s">
-        <v>197</v>
+      <c r="J47" t="s">
+        <v>209</v>
       </c>
       <c r="K47" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5252,13 +5252,13 @@
       <c r="E48" t="s">
         <v>188</v>
       </c>
-      <c r="G48" t="s">
+      <c r="F48" t="s">
         <v>189</v>
       </c>
-      <c r="H48" t="s">
+      <c r="I48" t="s">
         <v>190</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>191</v>
       </c>
       <c r="K48" t="s">
@@ -5281,13 +5281,13 @@
       <c r="E49" t="s">
         <v>188</v>
       </c>
-      <c r="G49" t="s">
+      <c r="F49" t="s">
         <v>189</v>
       </c>
-      <c r="H49" t="s">
+      <c r="I49" t="s">
         <v>190</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>191</v>
       </c>
       <c r="K49" t="s">
@@ -5308,19 +5308,19 @@
         <v>14</v>
       </c>
       <c r="E50" t="s">
+        <v>196</v>
+      </c>
+      <c r="F50" t="s">
         <v>208</v>
       </c>
-      <c r="G50" t="s">
-        <v>189</v>
-      </c>
-      <c r="H50" t="s">
+      <c r="I50" t="s">
         <v>190</v>
       </c>
-      <c r="I50" t="s">
-        <v>197</v>
+      <c r="J50" t="s">
+        <v>209</v>
       </c>
       <c r="K50" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5339,13 +5339,13 @@
       <c r="E51" t="s">
         <v>188</v>
       </c>
-      <c r="G51" t="s">
+      <c r="F51" t="s">
         <v>189</v>
       </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>190</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>191</v>
       </c>
       <c r="K51" t="s">
@@ -5366,19 +5366,19 @@
         <v>14</v>
       </c>
       <c r="E52" t="s">
+        <v>196</v>
+      </c>
+      <c r="F52" t="s">
         <v>225</v>
       </c>
-      <c r="G52" t="s">
-        <v>189</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="I52" t="s">
         <v>190</v>
       </c>
-      <c r="I52" t="s">
-        <v>197</v>
+      <c r="J52" t="s">
+        <v>226</v>
       </c>
       <c r="K52" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5397,17 +5397,17 @@
       <c r="E53" t="s">
         <v>15</v>
       </c>
-      <c r="G53" t="s">
-        <v>189</v>
-      </c>
-      <c r="H53" t="s">
+      <c r="F53" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" t="s">
         <v>190</v>
       </c>
-      <c r="I53" t="s">
-        <v>19</v>
+      <c r="J53" t="s">
+        <v>20</v>
       </c>
       <c r="K53" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5459,10 +5459,10 @@
         <v>14</v>
       </c>
       <c r="E55" t="s">
+        <v>233</v>
+      </c>
+      <c r="F55" t="s">
         <v>243</v>
-      </c>
-      <c r="F55" t="s">
-        <v>234</v>
       </c>
       <c r="G55" t="s">
         <v>235</v>
@@ -5474,10 +5474,10 @@
         <v>237</v>
       </c>
       <c r="J55" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K55" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -5494,10 +5494,10 @@
         <v>14</v>
       </c>
       <c r="E56" t="s">
+        <v>233</v>
+      </c>
+      <c r="F56" t="s">
         <v>248</v>
-      </c>
-      <c r="F56" t="s">
-        <v>234</v>
       </c>
       <c r="G56" t="s">
         <v>235</v>
@@ -5509,10 +5509,10 @@
         <v>237</v>
       </c>
       <c r="J56" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="K56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -5532,7 +5532,7 @@
         <v>253</v>
       </c>
       <c r="F57" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="G57" t="s">
         <v>235</v>
@@ -5541,13 +5541,13 @@
         <v>236</v>
       </c>
       <c r="I57" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J57" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K57" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5564,10 +5564,10 @@
         <v>14</v>
       </c>
       <c r="E58" t="s">
+        <v>233</v>
+      </c>
+      <c r="F58" t="s">
         <v>243</v>
-      </c>
-      <c r="F58" t="s">
-        <v>234</v>
       </c>
       <c r="G58" t="s">
         <v>235</v>
@@ -5579,10 +5579,10 @@
         <v>237</v>
       </c>
       <c r="J58" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K58" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5599,10 +5599,10 @@
         <v>14</v>
       </c>
       <c r="E59" t="s">
+        <v>233</v>
+      </c>
+      <c r="F59" t="s">
         <v>243</v>
-      </c>
-      <c r="F59" t="s">
-        <v>234</v>
       </c>
       <c r="G59" t="s">
         <v>235</v>
@@ -5614,10 +5614,10 @@
         <v>237</v>
       </c>
       <c r="J59" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K59" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5634,10 +5634,10 @@
         <v>14</v>
       </c>
       <c r="E60" t="s">
+        <v>233</v>
+      </c>
+      <c r="F60" t="s">
         <v>243</v>
-      </c>
-      <c r="F60" t="s">
-        <v>234</v>
       </c>
       <c r="G60" t="s">
         <v>235</v>
@@ -5649,10 +5649,10 @@
         <v>237</v>
       </c>
       <c r="J60" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K60" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -5669,10 +5669,10 @@
         <v>14</v>
       </c>
       <c r="E61" t="s">
+        <v>233</v>
+      </c>
+      <c r="F61" t="s">
         <v>243</v>
-      </c>
-      <c r="F61" t="s">
-        <v>234</v>
       </c>
       <c r="G61" t="s">
         <v>235</v>
@@ -5684,10 +5684,10 @@
         <v>237</v>
       </c>
       <c r="J61" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K61" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -5704,10 +5704,10 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
+        <v>233</v>
+      </c>
+      <c r="F62" t="s">
         <v>243</v>
-      </c>
-      <c r="F62" t="s">
-        <v>234</v>
       </c>
       <c r="G62" t="s">
         <v>235</v>
@@ -5719,10 +5719,10 @@
         <v>237</v>
       </c>
       <c r="J62" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K62" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -5739,10 +5739,10 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
+        <v>233</v>
+      </c>
+      <c r="F63" t="s">
         <v>243</v>
-      </c>
-      <c r="F63" t="s">
-        <v>234</v>
       </c>
       <c r="G63" t="s">
         <v>235</v>
@@ -5754,10 +5754,10 @@
         <v>237</v>
       </c>
       <c r="J63" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="K63" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -5774,10 +5774,10 @@
         <v>14</v>
       </c>
       <c r="E64" t="s">
+        <v>233</v>
+      </c>
+      <c r="F64" t="s">
         <v>243</v>
-      </c>
-      <c r="F64" t="s">
-        <v>234</v>
       </c>
       <c r="G64" t="s">
         <v>235</v>
@@ -5789,10 +5789,10 @@
         <v>237</v>
       </c>
       <c r="J64" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="K64" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -5809,10 +5809,10 @@
         <v>14</v>
       </c>
       <c r="E65" t="s">
+        <v>233</v>
+      </c>
+      <c r="F65" t="s">
         <v>281</v>
-      </c>
-      <c r="F65" t="s">
-        <v>234</v>
       </c>
       <c r="G65" t="s">
         <v>235</v>
@@ -5824,10 +5824,10 @@
         <v>237</v>
       </c>
       <c r="J65" t="s">
-        <v>238</v>
+        <v>282</v>
       </c>
       <c r="K65" t="s">
-        <v>282</v>
+        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5879,10 +5879,10 @@
         <v>14</v>
       </c>
       <c r="E67" t="s">
+        <v>233</v>
+      </c>
+      <c r="F67" t="s">
         <v>243</v>
-      </c>
-      <c r="F67" t="s">
-        <v>234</v>
       </c>
       <c r="G67" t="s">
         <v>235</v>
@@ -5894,10 +5894,10 @@
         <v>237</v>
       </c>
       <c r="J67" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K67" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5929,10 +5929,10 @@
         <v>237</v>
       </c>
       <c r="J68" t="s">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="K68" t="s">
-        <v>292</v>
+        <v>239</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -5964,10 +5964,10 @@
         <v>237</v>
       </c>
       <c r="J69" t="s">
-        <v>238</v>
+        <v>296</v>
       </c>
       <c r="K69" t="s">
-        <v>296</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -5984,10 +5984,10 @@
         <v>14</v>
       </c>
       <c r="E70" t="s">
+        <v>233</v>
+      </c>
+      <c r="F70" t="s">
         <v>248</v>
-      </c>
-      <c r="F70" t="s">
-        <v>234</v>
       </c>
       <c r="G70" t="s">
         <v>235</v>
@@ -5999,10 +5999,10 @@
         <v>237</v>
       </c>
       <c r="J70" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="K70" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -6019,10 +6019,10 @@
         <v>14</v>
       </c>
       <c r="E71" t="s">
+        <v>233</v>
+      </c>
+      <c r="F71" t="s">
         <v>248</v>
-      </c>
-      <c r="F71" t="s">
-        <v>234</v>
       </c>
       <c r="G71" t="s">
         <v>235</v>
@@ -6034,10 +6034,10 @@
         <v>237</v>
       </c>
       <c r="J71" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="K71" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6089,10 +6089,10 @@
         <v>14</v>
       </c>
       <c r="E73" t="s">
+        <v>253</v>
+      </c>
+      <c r="F73" t="s">
         <v>309</v>
-      </c>
-      <c r="F73" t="s">
-        <v>234</v>
       </c>
       <c r="G73" t="s">
         <v>235</v>
@@ -6101,13 +6101,13 @@
         <v>236</v>
       </c>
       <c r="I73" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J73" t="s">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="K73" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6124,10 +6124,10 @@
         <v>14</v>
       </c>
       <c r="E74" t="s">
+        <v>253</v>
+      </c>
+      <c r="F74" t="s">
         <v>314</v>
-      </c>
-      <c r="F74" t="s">
-        <v>234</v>
       </c>
       <c r="G74" t="s">
         <v>235</v>
@@ -6136,13 +6136,13 @@
         <v>236</v>
       </c>
       <c r="I74" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J74" t="s">
-        <v>238</v>
+        <v>315</v>
       </c>
       <c r="K74" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6159,10 +6159,10 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
+        <v>253</v>
+      </c>
+      <c r="F75" t="s">
         <v>319</v>
-      </c>
-      <c r="F75" t="s">
-        <v>234</v>
       </c>
       <c r="G75" t="s">
         <v>235</v>
@@ -6171,13 +6171,13 @@
         <v>236</v>
       </c>
       <c r="I75" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J75" t="s">
-        <v>238</v>
+        <v>320</v>
       </c>
       <c r="K75" t="s">
-        <v>320</v>
+        <v>239</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6194,10 +6194,10 @@
         <v>14</v>
       </c>
       <c r="E76" t="s">
+        <v>253</v>
+      </c>
+      <c r="F76" t="s">
         <v>309</v>
-      </c>
-      <c r="F76" t="s">
-        <v>234</v>
       </c>
       <c r="G76" t="s">
         <v>235</v>
@@ -6206,13 +6206,13 @@
         <v>236</v>
       </c>
       <c r="I76" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J76" t="s">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="K76" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -6229,10 +6229,10 @@
         <v>14</v>
       </c>
       <c r="E77" t="s">
+        <v>253</v>
+      </c>
+      <c r="F77" t="s">
         <v>309</v>
-      </c>
-      <c r="F77" t="s">
-        <v>234</v>
       </c>
       <c r="G77" t="s">
         <v>235</v>
@@ -6241,13 +6241,13 @@
         <v>236</v>
       </c>
       <c r="I77" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J77" t="s">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="K77" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -6264,10 +6264,10 @@
         <v>14</v>
       </c>
       <c r="E78" t="s">
+        <v>253</v>
+      </c>
+      <c r="F78" t="s">
         <v>314</v>
-      </c>
-      <c r="F78" t="s">
-        <v>234</v>
       </c>
       <c r="G78" t="s">
         <v>235</v>
@@ -6276,13 +6276,13 @@
         <v>236</v>
       </c>
       <c r="I78" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J78" t="s">
-        <v>238</v>
+        <v>315</v>
       </c>
       <c r="K78" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -6296,10 +6296,10 @@
         <v>14</v>
       </c>
       <c r="E79" t="s">
+        <v>253</v>
+      </c>
+      <c r="F79" t="s">
         <v>332</v>
-      </c>
-      <c r="F79" t="s">
-        <v>234</v>
       </c>
       <c r="G79" t="s">
         <v>235</v>
@@ -6308,13 +6308,13 @@
         <v>236</v>
       </c>
       <c r="I79" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J79" t="s">
-        <v>238</v>
+        <v>333</v>
       </c>
       <c r="K79" t="s">
-        <v>333</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -6334,7 +6334,7 @@
         <v>337</v>
       </c>
       <c r="F80" t="s">
-        <v>234</v>
+        <v>338</v>
       </c>
       <c r="G80" t="s">
         <v>235</v>
@@ -6343,13 +6343,13 @@
         <v>236</v>
       </c>
       <c r="I80" t="s">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="J80" t="s">
-        <v>238</v>
+        <v>339</v>
       </c>
       <c r="K80" t="s">
-        <v>339</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -6369,7 +6369,7 @@
         <v>337</v>
       </c>
       <c r="F81" t="s">
-        <v>234</v>
+        <v>338</v>
       </c>
       <c r="G81" t="s">
         <v>235</v>
@@ -6378,13 +6378,13 @@
         <v>236</v>
       </c>
       <c r="I81" t="s">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="J81" t="s">
-        <v>238</v>
+        <v>339</v>
       </c>
       <c r="K81" t="s">
-        <v>339</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -6404,7 +6404,7 @@
         <v>337</v>
       </c>
       <c r="F82" t="s">
-        <v>234</v>
+        <v>338</v>
       </c>
       <c r="G82" t="s">
         <v>235</v>
@@ -6413,13 +6413,13 @@
         <v>236</v>
       </c>
       <c r="I82" t="s">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="J82" t="s">
-        <v>238</v>
+        <v>339</v>
       </c>
       <c r="K82" t="s">
-        <v>339</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -6451,10 +6451,10 @@
         <v>237</v>
       </c>
       <c r="J83" t="s">
-        <v>238</v>
+        <v>296</v>
       </c>
       <c r="K83" t="s">
-        <v>296</v>
+        <v>239</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -6471,10 +6471,10 @@
         <v>14</v>
       </c>
       <c r="E84" t="s">
+        <v>233</v>
+      </c>
+      <c r="F84" t="s">
         <v>352</v>
-      </c>
-      <c r="F84" t="s">
-        <v>234</v>
       </c>
       <c r="G84" t="s">
         <v>235</v>
@@ -6486,10 +6486,10 @@
         <v>237</v>
       </c>
       <c r="J84" t="s">
-        <v>238</v>
+        <v>353</v>
       </c>
       <c r="K84" t="s">
-        <v>353</v>
+        <v>239</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -6506,10 +6506,10 @@
         <v>14</v>
       </c>
       <c r="E85" t="s">
+        <v>233</v>
+      </c>
+      <c r="F85" t="s">
         <v>243</v>
-      </c>
-      <c r="F85" t="s">
-        <v>234</v>
       </c>
       <c r="G85" t="s">
         <v>235</v>
@@ -6521,10 +6521,10 @@
         <v>237</v>
       </c>
       <c r="J85" t="s">
-        <v>238</v>
+        <v>357</v>
       </c>
       <c r="K85" t="s">
-        <v>357</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -6541,10 +6541,10 @@
         <v>14</v>
       </c>
       <c r="E86" t="s">
+        <v>337</v>
+      </c>
+      <c r="F86" t="s">
         <v>361</v>
-      </c>
-      <c r="F86" t="s">
-        <v>234</v>
       </c>
       <c r="G86" t="s">
         <v>235</v>
@@ -6553,13 +6553,13 @@
         <v>236</v>
       </c>
       <c r="I86" t="s">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="J86" t="s">
-        <v>238</v>
+        <v>362</v>
       </c>
       <c r="K86" t="s">
-        <v>362</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -6576,10 +6576,10 @@
         <v>14</v>
       </c>
       <c r="E87" t="s">
+        <v>233</v>
+      </c>
+      <c r="F87" t="s">
         <v>243</v>
-      </c>
-      <c r="F87" t="s">
-        <v>234</v>
       </c>
       <c r="G87" t="s">
         <v>235</v>
@@ -6591,10 +6591,10 @@
         <v>237</v>
       </c>
       <c r="J87" t="s">
-        <v>238</v>
+        <v>357</v>
       </c>
       <c r="K87" t="s">
-        <v>357</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -6608,10 +6608,10 @@
         <v>14</v>
       </c>
       <c r="E88" t="s">
+        <v>233</v>
+      </c>
+      <c r="F88" t="s">
         <v>243</v>
-      </c>
-      <c r="F88" t="s">
-        <v>234</v>
       </c>
       <c r="G88" t="s">
         <v>235</v>
@@ -6623,10 +6623,10 @@
         <v>237</v>
       </c>
       <c r="J88" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K88" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -6643,10 +6643,10 @@
         <v>14</v>
       </c>
       <c r="E89" t="s">
+        <v>233</v>
+      </c>
+      <c r="F89" t="s">
         <v>243</v>
-      </c>
-      <c r="F89" t="s">
-        <v>234</v>
       </c>
       <c r="G89" t="s">
         <v>235</v>
@@ -6658,10 +6658,10 @@
         <v>237</v>
       </c>
       <c r="J89" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K89" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -6681,7 +6681,7 @@
         <v>253</v>
       </c>
       <c r="F90" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="G90" t="s">
         <v>235</v>
@@ -6690,13 +6690,13 @@
         <v>236</v>
       </c>
       <c r="I90" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J90" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K90" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -6716,7 +6716,7 @@
         <v>377</v>
       </c>
       <c r="F91" t="s">
-        <v>234</v>
+        <v>378</v>
       </c>
       <c r="G91" t="s">
         <v>235</v>
@@ -6725,13 +6725,13 @@
         <v>236</v>
       </c>
       <c r="I91" t="s">
-        <v>378</v>
+        <v>237</v>
       </c>
       <c r="J91" t="s">
-        <v>238</v>
+        <v>379</v>
       </c>
       <c r="K91" t="s">
-        <v>379</v>
+        <v>239</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -6751,7 +6751,7 @@
         <v>253</v>
       </c>
       <c r="F92" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="G92" t="s">
         <v>235</v>
@@ -6760,13 +6760,13 @@
         <v>236</v>
       </c>
       <c r="I92" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J92" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K92" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -6783,10 +6783,10 @@
         <v>14</v>
       </c>
       <c r="E93" t="s">
+        <v>233</v>
+      </c>
+      <c r="F93" t="s">
         <v>248</v>
-      </c>
-      <c r="F93" t="s">
-        <v>234</v>
       </c>
       <c r="G93" t="s">
         <v>235</v>
@@ -6798,10 +6798,10 @@
         <v>237</v>
       </c>
       <c r="J93" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="K93" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -6821,7 +6821,7 @@
         <v>253</v>
       </c>
       <c r="F94" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="G94" t="s">
         <v>235</v>
@@ -6830,13 +6830,13 @@
         <v>236</v>
       </c>
       <c r="I94" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J94" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K94" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -6853,10 +6853,10 @@
         <v>14</v>
       </c>
       <c r="E95" t="s">
+        <v>233</v>
+      </c>
+      <c r="F95" t="s">
         <v>392</v>
-      </c>
-      <c r="F95" t="s">
-        <v>234</v>
       </c>
       <c r="G95" t="s">
         <v>235</v>
@@ -6868,10 +6868,10 @@
         <v>237</v>
       </c>
       <c r="J95" t="s">
-        <v>238</v>
+        <v>393</v>
       </c>
       <c r="K95" t="s">
-        <v>393</v>
+        <v>239</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -6891,22 +6891,22 @@
         <v>253</v>
       </c>
       <c r="F96" t="s">
+        <v>254</v>
+      </c>
+      <c r="G96" t="s">
         <v>397</v>
       </c>
-      <c r="G96" t="s">
-        <v>235</v>
-      </c>
       <c r="H96" t="s">
-        <v>236</v>
+        <v>398</v>
       </c>
       <c r="I96" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J96" t="s">
-        <v>398</v>
+        <v>255</v>
       </c>
       <c r="K96" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -6926,22 +6926,22 @@
         <v>253</v>
       </c>
       <c r="F97" t="s">
+        <v>254</v>
+      </c>
+      <c r="G97" t="s">
         <v>397</v>
       </c>
-      <c r="G97" t="s">
-        <v>235</v>
-      </c>
       <c r="H97" t="s">
-        <v>236</v>
+        <v>398</v>
       </c>
       <c r="I97" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J97" t="s">
-        <v>398</v>
+        <v>255</v>
       </c>
       <c r="K97" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -6961,22 +6961,22 @@
         <v>405</v>
       </c>
       <c r="F98" t="s">
+        <v>406</v>
+      </c>
+      <c r="G98" t="s">
         <v>397</v>
       </c>
-      <c r="G98" t="s">
-        <v>235</v>
-      </c>
       <c r="H98" t="s">
-        <v>236</v>
+        <v>398</v>
       </c>
       <c r="I98" t="s">
-        <v>406</v>
+        <v>237</v>
       </c>
       <c r="J98" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="K98" t="s">
-        <v>407</v>
+        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -6996,22 +6996,22 @@
         <v>253</v>
       </c>
       <c r="F99" t="s">
+        <v>254</v>
+      </c>
+      <c r="G99" t="s">
         <v>397</v>
       </c>
-      <c r="G99" t="s">
-        <v>235</v>
-      </c>
       <c r="H99" t="s">
-        <v>236</v>
+        <v>398</v>
       </c>
       <c r="I99" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J99" t="s">
-        <v>398</v>
+        <v>255</v>
       </c>
       <c r="K99" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -7028,25 +7028,25 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
+        <v>253</v>
+      </c>
+      <c r="F100" t="s">
         <v>319</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>397</v>
       </c>
-      <c r="G100" t="s">
-        <v>235</v>
-      </c>
       <c r="H100" t="s">
-        <v>236</v>
+        <v>398</v>
       </c>
       <c r="I100" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J100" t="s">
-        <v>398</v>
+        <v>320</v>
       </c>
       <c r="K100" t="s">
-        <v>320</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -7066,22 +7066,22 @@
         <v>253</v>
       </c>
       <c r="F101" t="s">
+        <v>254</v>
+      </c>
+      <c r="G101" t="s">
         <v>397</v>
       </c>
-      <c r="G101" t="s">
-        <v>235</v>
-      </c>
       <c r="H101" t="s">
-        <v>236</v>
+        <v>398</v>
       </c>
       <c r="I101" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J101" t="s">
-        <v>398</v>
+        <v>255</v>
       </c>
       <c r="K101" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -7098,16 +7098,16 @@
         <v>14</v>
       </c>
       <c r="E102" t="s">
+        <v>377</v>
+      </c>
+      <c r="F102" t="s">
         <v>420</v>
       </c>
-      <c r="G102" t="s">
+      <c r="I102" t="s">
         <v>421</v>
       </c>
-      <c r="H102" t="s">
+      <c r="J102" t="s">
         <v>422</v>
-      </c>
-      <c r="I102" t="s">
-        <v>378</v>
       </c>
       <c r="K102" t="s">
         <v>423</v>
@@ -7127,16 +7127,16 @@
         <v>14</v>
       </c>
       <c r="E103" t="s">
+        <v>377</v>
+      </c>
+      <c r="F103" t="s">
         <v>420</v>
       </c>
-      <c r="G103" t="s">
+      <c r="I103" t="s">
         <v>421</v>
       </c>
-      <c r="H103" t="s">
+      <c r="J103" t="s">
         <v>422</v>
-      </c>
-      <c r="I103" t="s">
-        <v>378</v>
       </c>
       <c r="K103" t="s">
         <v>423</v>
@@ -7156,16 +7156,16 @@
         <v>14</v>
       </c>
       <c r="E104" t="s">
+        <v>377</v>
+      </c>
+      <c r="F104" t="s">
         <v>420</v>
       </c>
-      <c r="G104" t="s">
+      <c r="I104" t="s">
         <v>421</v>
       </c>
-      <c r="H104" t="s">
+      <c r="J104" t="s">
         <v>422</v>
-      </c>
-      <c r="I104" t="s">
-        <v>378</v>
       </c>
       <c r="K104" t="s">
         <v>423</v>
@@ -7185,19 +7185,19 @@
         <v>14</v>
       </c>
       <c r="E105" t="s">
+        <v>377</v>
+      </c>
+      <c r="F105" t="s">
         <v>433</v>
       </c>
-      <c r="G105" t="s">
+      <c r="I105" t="s">
         <v>421</v>
       </c>
-      <c r="H105" t="s">
-        <v>422</v>
-      </c>
-      <c r="I105" t="s">
-        <v>378</v>
+      <c r="J105" t="s">
+        <v>434</v>
       </c>
       <c r="K105" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7214,16 +7214,16 @@
         <v>14</v>
       </c>
       <c r="E106" t="s">
+        <v>377</v>
+      </c>
+      <c r="F106" t="s">
         <v>420</v>
       </c>
-      <c r="G106" t="s">
+      <c r="I106" t="s">
         <v>421</v>
       </c>
-      <c r="H106" t="s">
+      <c r="J106" t="s">
         <v>422</v>
-      </c>
-      <c r="I106" t="s">
-        <v>378</v>
       </c>
       <c r="K106" t="s">
         <v>423</v>
@@ -7245,17 +7245,17 @@
       <c r="E107" t="s">
         <v>377</v>
       </c>
-      <c r="G107" t="s">
+      <c r="F107" t="s">
+        <v>378</v>
+      </c>
+      <c r="I107" t="s">
         <v>421</v>
       </c>
-      <c r="H107" t="s">
-        <v>422</v>
-      </c>
-      <c r="I107" t="s">
-        <v>378</v>
+      <c r="J107" t="s">
+        <v>379</v>
       </c>
       <c r="K107" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -7272,19 +7272,19 @@
         <v>14</v>
       </c>
       <c r="E108" t="s">
+        <v>377</v>
+      </c>
+      <c r="F108" t="s">
         <v>444</v>
       </c>
-      <c r="G108" t="s">
+      <c r="I108" t="s">
         <v>421</v>
       </c>
-      <c r="H108" t="s">
-        <v>422</v>
-      </c>
-      <c r="I108" t="s">
-        <v>378</v>
+      <c r="J108" t="s">
+        <v>445</v>
       </c>
       <c r="K108" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7301,19 +7301,19 @@
         <v>14</v>
       </c>
       <c r="E109" t="s">
+        <v>188</v>
+      </c>
+      <c r="F109" t="s">
         <v>449</v>
       </c>
-      <c r="G109" t="s">
+      <c r="I109" t="s">
         <v>421</v>
       </c>
-      <c r="H109" t="s">
-        <v>422</v>
-      </c>
-      <c r="I109" t="s">
-        <v>191</v>
+      <c r="J109" t="s">
+        <v>450</v>
       </c>
       <c r="K109" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -7330,19 +7330,19 @@
         <v>14</v>
       </c>
       <c r="E110" t="s">
+        <v>188</v>
+      </c>
+      <c r="F110" t="s">
         <v>454</v>
       </c>
-      <c r="G110" t="s">
+      <c r="I110" t="s">
         <v>421</v>
       </c>
-      <c r="H110" t="s">
-        <v>422</v>
-      </c>
-      <c r="I110" t="s">
-        <v>191</v>
+      <c r="J110" t="s">
+        <v>455</v>
       </c>
       <c r="K110" t="s">
-        <v>455</v>
+        <v>423</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -7359,16 +7359,16 @@
         <v>14</v>
       </c>
       <c r="E111" t="s">
+        <v>377</v>
+      </c>
+      <c r="F111" t="s">
         <v>420</v>
       </c>
-      <c r="G111" t="s">
+      <c r="I111" t="s">
         <v>421</v>
       </c>
-      <c r="H111" t="s">
+      <c r="J111" t="s">
         <v>422</v>
-      </c>
-      <c r="I111" t="s">
-        <v>378</v>
       </c>
       <c r="K111" t="s">
         <v>423</v>
@@ -7390,17 +7390,17 @@
       <c r="E112" t="s">
         <v>462</v>
       </c>
-      <c r="G112" t="s">
+      <c r="F112" t="s">
+        <v>463</v>
+      </c>
+      <c r="I112" t="s">
         <v>421</v>
       </c>
-      <c r="H112" t="s">
-        <v>422</v>
-      </c>
-      <c r="I112" t="s">
-        <v>463</v>
+      <c r="J112" t="s">
+        <v>464</v>
       </c>
       <c r="K112" t="s">
-        <v>464</v>
+        <v>423</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -7419,17 +7419,17 @@
       <c r="E113" t="s">
         <v>233</v>
       </c>
-      <c r="G113" t="s">
+      <c r="F113" t="s">
+        <v>234</v>
+      </c>
+      <c r="I113" t="s">
         <v>421</v>
       </c>
-      <c r="H113" t="s">
-        <v>422</v>
-      </c>
-      <c r="I113" t="s">
-        <v>237</v>
+      <c r="J113" t="s">
+        <v>296</v>
       </c>
       <c r="K113" t="s">
-        <v>296</v>
+        <v>423</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -7446,19 +7446,19 @@
         <v>14</v>
       </c>
       <c r="E114" t="s">
+        <v>253</v>
+      </c>
+      <c r="F114" t="s">
         <v>314</v>
       </c>
-      <c r="G114" t="s">
+      <c r="I114" t="s">
         <v>421</v>
       </c>
-      <c r="H114" t="s">
-        <v>422</v>
-      </c>
-      <c r="I114" t="s">
-        <v>254</v>
+      <c r="J114" t="s">
+        <v>315</v>
       </c>
       <c r="K114" t="s">
-        <v>315</v>
+        <v>423</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -7477,17 +7477,17 @@
       <c r="E115" t="s">
         <v>377</v>
       </c>
-      <c r="G115" t="s">
+      <c r="F115" t="s">
+        <v>378</v>
+      </c>
+      <c r="I115" t="s">
         <v>421</v>
       </c>
-      <c r="H115" t="s">
-        <v>422</v>
-      </c>
-      <c r="I115" t="s">
-        <v>378</v>
+      <c r="J115" t="s">
+        <v>379</v>
       </c>
       <c r="K115" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -7501,19 +7501,19 @@
         <v>14</v>
       </c>
       <c r="E116" t="s">
+        <v>462</v>
+      </c>
+      <c r="F116" t="s">
         <v>476</v>
       </c>
-      <c r="G116" t="s">
+      <c r="I116" t="s">
         <v>421</v>
       </c>
-      <c r="H116" t="s">
-        <v>422</v>
-      </c>
-      <c r="I116" t="s">
-        <v>463</v>
+      <c r="J116" t="s">
+        <v>477</v>
       </c>
       <c r="K116" t="s">
-        <v>477</v>
+        <v>423</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -7529,17 +7529,17 @@
       <c r="E117" t="s">
         <v>462</v>
       </c>
-      <c r="G117" t="s">
+      <c r="F117" t="s">
+        <v>463</v>
+      </c>
+      <c r="I117" t="s">
         <v>421</v>
       </c>
-      <c r="H117" t="s">
-        <v>422</v>
-      </c>
-      <c r="I117" t="s">
-        <v>463</v>
+      <c r="J117" t="s">
+        <v>464</v>
       </c>
       <c r="K117" t="s">
-        <v>464</v>
+        <v>423</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -7558,17 +7558,17 @@
       <c r="E118" t="s">
         <v>337</v>
       </c>
-      <c r="G118" t="s">
+      <c r="F118" t="s">
+        <v>338</v>
+      </c>
+      <c r="I118" t="s">
         <v>421</v>
       </c>
-      <c r="H118" t="s">
-        <v>422</v>
-      </c>
-      <c r="I118" t="s">
-        <v>338</v>
+      <c r="J118" t="s">
+        <v>483</v>
       </c>
       <c r="K118" t="s">
-        <v>483</v>
+        <v>423</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -7587,17 +7587,17 @@
       <c r="E119" t="s">
         <v>377</v>
       </c>
-      <c r="G119" t="s">
+      <c r="F119" t="s">
+        <v>378</v>
+      </c>
+      <c r="I119" t="s">
         <v>421</v>
       </c>
-      <c r="H119" t="s">
-        <v>422</v>
-      </c>
-      <c r="I119" t="s">
-        <v>378</v>
+      <c r="J119" t="s">
+        <v>379</v>
       </c>
       <c r="K119" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -7614,19 +7614,19 @@
         <v>14</v>
       </c>
       <c r="E120" t="s">
+        <v>233</v>
+      </c>
+      <c r="F120" t="s">
         <v>352</v>
       </c>
-      <c r="G120" t="s">
+      <c r="I120" t="s">
         <v>490</v>
       </c>
-      <c r="H120" t="s">
+      <c r="J120" t="s">
+        <v>353</v>
+      </c>
+      <c r="K120" t="s">
         <v>491</v>
-      </c>
-      <c r="I120" t="s">
-        <v>237</v>
-      </c>
-      <c r="K120" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -7645,17 +7645,17 @@
       <c r="E121" t="s">
         <v>233</v>
       </c>
-      <c r="G121" t="s">
+      <c r="F121" t="s">
+        <v>234</v>
+      </c>
+      <c r="I121" t="s">
         <v>490</v>
       </c>
-      <c r="H121" t="s">
+      <c r="J121" t="s">
+        <v>296</v>
+      </c>
+      <c r="K121" t="s">
         <v>491</v>
-      </c>
-      <c r="I121" t="s">
-        <v>237</v>
-      </c>
-      <c r="K121" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -7672,19 +7672,19 @@
         <v>14</v>
       </c>
       <c r="E122" t="s">
+        <v>233</v>
+      </c>
+      <c r="F122" t="s">
         <v>352</v>
       </c>
-      <c r="G122" t="s">
+      <c r="I122" t="s">
         <v>490</v>
       </c>
-      <c r="H122" t="s">
+      <c r="J122" t="s">
+        <v>353</v>
+      </c>
+      <c r="K122" t="s">
         <v>491</v>
-      </c>
-      <c r="I122" t="s">
-        <v>237</v>
-      </c>
-      <c r="K122" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -7701,19 +7701,19 @@
         <v>14</v>
       </c>
       <c r="E123" t="s">
+        <v>233</v>
+      </c>
+      <c r="F123" t="s">
         <v>352</v>
       </c>
-      <c r="G123" t="s">
+      <c r="I123" t="s">
         <v>490</v>
       </c>
-      <c r="H123" t="s">
+      <c r="J123" t="s">
+        <v>353</v>
+      </c>
+      <c r="K123" t="s">
         <v>491</v>
-      </c>
-      <c r="I123" t="s">
-        <v>237</v>
-      </c>
-      <c r="K123" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -7730,19 +7730,19 @@
         <v>14</v>
       </c>
       <c r="E124" t="s">
+        <v>337</v>
+      </c>
+      <c r="F124" t="s">
         <v>504</v>
       </c>
-      <c r="G124" t="s">
+      <c r="I124" t="s">
         <v>490</v>
       </c>
-      <c r="H124" t="s">
+      <c r="J124" t="s">
+        <v>505</v>
+      </c>
+      <c r="K124" t="s">
         <v>491</v>
-      </c>
-      <c r="I124" t="s">
-        <v>338</v>
-      </c>
-      <c r="K124" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -7759,19 +7759,19 @@
         <v>14</v>
       </c>
       <c r="E125" t="s">
+        <v>337</v>
+      </c>
+      <c r="F125" t="s">
         <v>504</v>
       </c>
-      <c r="G125" t="s">
+      <c r="I125" t="s">
         <v>490</v>
       </c>
-      <c r="H125" t="s">
+      <c r="J125" t="s">
+        <v>505</v>
+      </c>
+      <c r="K125" t="s">
         <v>491</v>
-      </c>
-      <c r="I125" t="s">
-        <v>338</v>
-      </c>
-      <c r="K125" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -7788,19 +7788,19 @@
         <v>14</v>
       </c>
       <c r="E126" t="s">
+        <v>337</v>
+      </c>
+      <c r="F126" t="s">
         <v>504</v>
       </c>
-      <c r="G126" t="s">
+      <c r="I126" t="s">
         <v>490</v>
       </c>
-      <c r="H126" t="s">
+      <c r="J126" t="s">
+        <v>505</v>
+      </c>
+      <c r="K126" t="s">
         <v>491</v>
-      </c>
-      <c r="I126" t="s">
-        <v>338</v>
-      </c>
-      <c r="K126" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -7817,19 +7817,19 @@
         <v>14</v>
       </c>
       <c r="E127" t="s">
+        <v>337</v>
+      </c>
+      <c r="F127" t="s">
         <v>504</v>
       </c>
-      <c r="G127" t="s">
+      <c r="I127" t="s">
         <v>490</v>
       </c>
-      <c r="H127" t="s">
+      <c r="J127" t="s">
+        <v>505</v>
+      </c>
+      <c r="K127" t="s">
         <v>491</v>
-      </c>
-      <c r="I127" t="s">
-        <v>338</v>
-      </c>
-      <c r="K127" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -7846,19 +7846,19 @@
         <v>14</v>
       </c>
       <c r="E128" t="s">
+        <v>337</v>
+      </c>
+      <c r="F128" t="s">
         <v>504</v>
       </c>
-      <c r="G128" t="s">
+      <c r="I128" t="s">
         <v>490</v>
       </c>
-      <c r="H128" t="s">
+      <c r="J128" t="s">
+        <v>505</v>
+      </c>
+      <c r="K128" t="s">
         <v>491</v>
-      </c>
-      <c r="I128" t="s">
-        <v>338</v>
-      </c>
-      <c r="K128" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -7875,19 +7875,19 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
+        <v>337</v>
+      </c>
+      <c r="F129" t="s">
         <v>504</v>
       </c>
-      <c r="G129" t="s">
+      <c r="I129" t="s">
         <v>490</v>
       </c>
-      <c r="H129" t="s">
+      <c r="J129" t="s">
+        <v>521</v>
+      </c>
+      <c r="K129" t="s">
         <v>491</v>
-      </c>
-      <c r="I129" t="s">
-        <v>338</v>
-      </c>
-      <c r="K129" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7904,19 +7904,19 @@
         <v>14</v>
       </c>
       <c r="E130" t="s">
+        <v>337</v>
+      </c>
+      <c r="F130" t="s">
         <v>504</v>
       </c>
-      <c r="G130" t="s">
+      <c r="I130" t="s">
         <v>490</v>
       </c>
-      <c r="H130" t="s">
+      <c r="J130" t="s">
+        <v>525</v>
+      </c>
+      <c r="K130" t="s">
         <v>491</v>
-      </c>
-      <c r="I130" t="s">
-        <v>338</v>
-      </c>
-      <c r="K130" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7933,19 +7933,19 @@
         <v>14</v>
       </c>
       <c r="E131" t="s">
+        <v>337</v>
+      </c>
+      <c r="F131" t="s">
         <v>504</v>
       </c>
-      <c r="G131" t="s">
+      <c r="I131" t="s">
         <v>490</v>
       </c>
-      <c r="H131" t="s">
+      <c r="J131" t="s">
+        <v>529</v>
+      </c>
+      <c r="K131" t="s">
         <v>491</v>
-      </c>
-      <c r="I131" t="s">
-        <v>338</v>
-      </c>
-      <c r="K131" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7962,19 +7962,19 @@
         <v>14</v>
       </c>
       <c r="E132" t="s">
+        <v>337</v>
+      </c>
+      <c r="F132" t="s">
         <v>533</v>
       </c>
-      <c r="G132" t="s">
+      <c r="I132" t="s">
         <v>490</v>
       </c>
-      <c r="H132" t="s">
+      <c r="J132" t="s">
+        <v>534</v>
+      </c>
+      <c r="K132" t="s">
         <v>491</v>
-      </c>
-      <c r="I132" t="s">
-        <v>338</v>
-      </c>
-      <c r="K132" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -7988,19 +7988,19 @@
         <v>14</v>
       </c>
       <c r="E133" t="s">
+        <v>233</v>
+      </c>
+      <c r="F133" t="s">
         <v>392</v>
       </c>
-      <c r="G133" t="s">
+      <c r="I133" t="s">
         <v>490</v>
       </c>
-      <c r="H133" t="s">
+      <c r="J133" t="s">
+        <v>393</v>
+      </c>
+      <c r="K133" t="s">
         <v>491</v>
-      </c>
-      <c r="I133" t="s">
-        <v>237</v>
-      </c>
-      <c r="K133" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -8017,19 +8017,19 @@
         <v>14</v>
       </c>
       <c r="E134" t="s">
+        <v>337</v>
+      </c>
+      <c r="F134" t="s">
         <v>361</v>
       </c>
-      <c r="G134" t="s">
+      <c r="I134" t="s">
         <v>540</v>
       </c>
-      <c r="H134" t="s">
+      <c r="J134" t="s">
+        <v>362</v>
+      </c>
+      <c r="K134" t="s">
         <v>541</v>
-      </c>
-      <c r="I134" t="s">
-        <v>338</v>
-      </c>
-      <c r="K134" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -8043,19 +8043,19 @@
         <v>14</v>
       </c>
       <c r="E135" t="s">
+        <v>337</v>
+      </c>
+      <c r="F135" t="s">
         <v>361</v>
       </c>
-      <c r="G135" t="s">
+      <c r="I135" t="s">
         <v>540</v>
       </c>
-      <c r="H135" t="s">
+      <c r="J135" t="s">
+        <v>362</v>
+      </c>
+      <c r="K135" t="s">
         <v>541</v>
-      </c>
-      <c r="I135" t="s">
-        <v>338</v>
-      </c>
-      <c r="K135" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -8072,19 +8072,19 @@
         <v>14</v>
       </c>
       <c r="E136" t="s">
+        <v>337</v>
+      </c>
+      <c r="F136" t="s">
         <v>361</v>
       </c>
-      <c r="G136" t="s">
+      <c r="I136" t="s">
         <v>540</v>
       </c>
-      <c r="H136" t="s">
+      <c r="J136" t="s">
+        <v>362</v>
+      </c>
+      <c r="K136" t="s">
         <v>541</v>
-      </c>
-      <c r="I136" t="s">
-        <v>338</v>
-      </c>
-      <c r="K136" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -8101,19 +8101,19 @@
         <v>14</v>
       </c>
       <c r="E137" t="s">
+        <v>337</v>
+      </c>
+      <c r="F137" t="s">
         <v>361</v>
       </c>
-      <c r="G137" t="s">
+      <c r="I137" t="s">
         <v>540</v>
       </c>
-      <c r="H137" t="s">
+      <c r="J137" t="s">
+        <v>362</v>
+      </c>
+      <c r="K137" t="s">
         <v>541</v>
-      </c>
-      <c r="I137" t="s">
-        <v>338</v>
-      </c>
-      <c r="K137" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -8130,19 +8130,19 @@
         <v>14</v>
       </c>
       <c r="E138" t="s">
+        <v>337</v>
+      </c>
+      <c r="F138" t="s">
         <v>361</v>
       </c>
-      <c r="G138" t="s">
+      <c r="I138" t="s">
         <v>540</v>
       </c>
-      <c r="H138" t="s">
+      <c r="J138" t="s">
+        <v>362</v>
+      </c>
+      <c r="K138" t="s">
         <v>541</v>
-      </c>
-      <c r="I138" t="s">
-        <v>338</v>
-      </c>
-      <c r="K138" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -8159,19 +8159,19 @@
         <v>14</v>
       </c>
       <c r="E139" t="s">
+        <v>462</v>
+      </c>
+      <c r="F139" t="s">
         <v>556</v>
       </c>
-      <c r="G139" t="s">
+      <c r="I139" t="s">
         <v>540</v>
       </c>
-      <c r="H139" t="s">
+      <c r="J139" t="s">
+        <v>557</v>
+      </c>
+      <c r="K139" t="s">
         <v>541</v>
-      </c>
-      <c r="I139" t="s">
-        <v>463</v>
-      </c>
-      <c r="K139" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -8188,19 +8188,19 @@
         <v>14</v>
       </c>
       <c r="E140" t="s">
+        <v>337</v>
+      </c>
+      <c r="F140" t="s">
         <v>361</v>
       </c>
-      <c r="G140" t="s">
+      <c r="I140" t="s">
         <v>540</v>
       </c>
-      <c r="H140" t="s">
+      <c r="J140" t="s">
+        <v>362</v>
+      </c>
+      <c r="K140" t="s">
         <v>541</v>
-      </c>
-      <c r="I140" t="s">
-        <v>338</v>
-      </c>
-      <c r="K140" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -8217,19 +8217,19 @@
         <v>14</v>
       </c>
       <c r="E141" t="s">
+        <v>337</v>
+      </c>
+      <c r="F141" t="s">
         <v>564</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>565</v>
       </c>
-      <c r="G141" t="s">
+      <c r="H141" t="s">
         <v>566</v>
       </c>
-      <c r="H141" t="s">
+      <c r="I141" t="s">
         <v>567</v>
-      </c>
-      <c r="I141" t="s">
-        <v>338</v>
       </c>
       <c r="J141" t="s">
         <v>568</v>
@@ -8249,19 +8249,19 @@
         <v>14</v>
       </c>
       <c r="E142" t="s">
+        <v>337</v>
+      </c>
+      <c r="F142" t="s">
         <v>564</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>565</v>
       </c>
-      <c r="G142" t="s">
+      <c r="H142" t="s">
         <v>566</v>
       </c>
-      <c r="H142" t="s">
+      <c r="I142" t="s">
         <v>567</v>
-      </c>
-      <c r="I142" t="s">
-        <v>338</v>
       </c>
       <c r="J142" t="s">
         <v>568</v>
@@ -8284,25 +8284,25 @@
         <v>14</v>
       </c>
       <c r="E143" t="s">
+        <v>337</v>
+      </c>
+      <c r="F143" t="s">
         <v>575</v>
       </c>
-      <c r="F143" t="s">
+      <c r="G143" t="s">
         <v>565</v>
       </c>
-      <c r="G143" t="s">
+      <c r="H143" t="s">
         <v>566</v>
       </c>
-      <c r="H143" t="s">
+      <c r="I143" t="s">
         <v>567</v>
       </c>
-      <c r="I143" t="s">
-        <v>338</v>
-      </c>
       <c r="J143" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K143" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -8319,25 +8319,25 @@
         <v>14</v>
       </c>
       <c r="E144" t="s">
+        <v>337</v>
+      </c>
+      <c r="F144" t="s">
         <v>575</v>
       </c>
-      <c r="F144" t="s">
+      <c r="G144" t="s">
         <v>565</v>
       </c>
-      <c r="G144" t="s">
+      <c r="H144" t="s">
         <v>566</v>
       </c>
-      <c r="H144" t="s">
+      <c r="I144" t="s">
         <v>567</v>
       </c>
-      <c r="I144" t="s">
-        <v>338</v>
-      </c>
       <c r="J144" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K144" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -8354,25 +8354,25 @@
         <v>14</v>
       </c>
       <c r="E145" t="s">
+        <v>337</v>
+      </c>
+      <c r="F145" t="s">
         <v>575</v>
       </c>
-      <c r="F145" t="s">
+      <c r="G145" t="s">
         <v>565</v>
       </c>
-      <c r="G145" t="s">
+      <c r="H145" t="s">
         <v>566</v>
       </c>
-      <c r="H145" t="s">
+      <c r="I145" t="s">
         <v>567</v>
       </c>
-      <c r="I145" t="s">
-        <v>338</v>
-      </c>
       <c r="J145" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K145" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -8389,19 +8389,19 @@
         <v>14</v>
       </c>
       <c r="E146" t="s">
+        <v>337</v>
+      </c>
+      <c r="F146" t="s">
         <v>564</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>565</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" t="s">
         <v>566</v>
       </c>
-      <c r="H146" t="s">
+      <c r="I146" t="s">
         <v>567</v>
-      </c>
-      <c r="I146" t="s">
-        <v>338</v>
       </c>
       <c r="J146" t="s">
         <v>568</v>
@@ -8424,22 +8424,22 @@
         <v>14</v>
       </c>
       <c r="E147" t="s">
+        <v>337</v>
+      </c>
+      <c r="F147" t="s">
         <v>564</v>
       </c>
-      <c r="F147" t="s">
+      <c r="G147" t="s">
         <v>589</v>
       </c>
-      <c r="G147" t="s">
-        <v>566</v>
-      </c>
       <c r="H147" t="s">
+        <v>590</v>
+      </c>
+      <c r="I147" t="s">
         <v>567</v>
       </c>
-      <c r="I147" t="s">
-        <v>338</v>
-      </c>
       <c r="J147" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K147" t="s">
         <v>569</v>
@@ -8459,22 +8459,22 @@
         <v>14</v>
       </c>
       <c r="E148" t="s">
+        <v>337</v>
+      </c>
+      <c r="F148" t="s">
         <v>564</v>
       </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
         <v>589</v>
       </c>
-      <c r="G148" t="s">
-        <v>566</v>
-      </c>
       <c r="H148" t="s">
+        <v>590</v>
+      </c>
+      <c r="I148" t="s">
         <v>567</v>
       </c>
-      <c r="I148" t="s">
-        <v>338</v>
-      </c>
       <c r="J148" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K148" t="s">
         <v>569</v>
@@ -8494,22 +8494,22 @@
         <v>14</v>
       </c>
       <c r="E149" t="s">
+        <v>337</v>
+      </c>
+      <c r="F149" t="s">
         <v>564</v>
       </c>
-      <c r="F149" t="s">
+      <c r="G149" t="s">
         <v>589</v>
       </c>
-      <c r="G149" t="s">
-        <v>566</v>
-      </c>
       <c r="H149" t="s">
+        <v>590</v>
+      </c>
+      <c r="I149" t="s">
         <v>567</v>
       </c>
-      <c r="I149" t="s">
-        <v>338</v>
-      </c>
       <c r="J149" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K149" t="s">
         <v>569</v>
@@ -8529,22 +8529,22 @@
         <v>14</v>
       </c>
       <c r="E150" t="s">
+        <v>337</v>
+      </c>
+      <c r="F150" t="s">
         <v>564</v>
       </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
         <v>589</v>
       </c>
-      <c r="G150" t="s">
-        <v>566</v>
-      </c>
       <c r="H150" t="s">
+        <v>590</v>
+      </c>
+      <c r="I150" t="s">
         <v>567</v>
       </c>
-      <c r="I150" t="s">
-        <v>338</v>
-      </c>
       <c r="J150" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K150" t="s">
         <v>569</v>
@@ -8564,22 +8564,22 @@
         <v>14</v>
       </c>
       <c r="E151" t="s">
+        <v>337</v>
+      </c>
+      <c r="F151" t="s">
         <v>564</v>
       </c>
-      <c r="F151" t="s">
+      <c r="G151" t="s">
         <v>589</v>
       </c>
-      <c r="G151" t="s">
-        <v>566</v>
-      </c>
       <c r="H151" t="s">
+        <v>590</v>
+      </c>
+      <c r="I151" t="s">
         <v>567</v>
       </c>
-      <c r="I151" t="s">
-        <v>338</v>
-      </c>
       <c r="J151" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K151" t="s">
         <v>569</v>
@@ -8599,22 +8599,22 @@
         <v>14</v>
       </c>
       <c r="E152" t="s">
+        <v>337</v>
+      </c>
+      <c r="F152" t="s">
         <v>564</v>
       </c>
-      <c r="F152" t="s">
+      <c r="G152" t="s">
         <v>589</v>
       </c>
-      <c r="G152" t="s">
-        <v>566</v>
-      </c>
       <c r="H152" t="s">
+        <v>590</v>
+      </c>
+      <c r="I152" t="s">
         <v>567</v>
       </c>
-      <c r="I152" t="s">
-        <v>338</v>
-      </c>
       <c r="J152" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K152" t="s">
         <v>569</v>
@@ -8634,22 +8634,22 @@
         <v>14</v>
       </c>
       <c r="E153" t="s">
+        <v>337</v>
+      </c>
+      <c r="F153" t="s">
         <v>564</v>
       </c>
-      <c r="F153" t="s">
+      <c r="G153" t="s">
         <v>589</v>
       </c>
-      <c r="G153" t="s">
-        <v>566</v>
-      </c>
       <c r="H153" t="s">
+        <v>590</v>
+      </c>
+      <c r="I153" t="s">
         <v>567</v>
       </c>
-      <c r="I153" t="s">
-        <v>338</v>
-      </c>
       <c r="J153" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K153" t="s">
         <v>569</v>
@@ -8669,22 +8669,22 @@
         <v>14</v>
       </c>
       <c r="E154" t="s">
+        <v>337</v>
+      </c>
+      <c r="F154" t="s">
         <v>564</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>589</v>
       </c>
-      <c r="G154" t="s">
-        <v>566</v>
-      </c>
       <c r="H154" t="s">
+        <v>590</v>
+      </c>
+      <c r="I154" t="s">
         <v>567</v>
       </c>
-      <c r="I154" t="s">
-        <v>338</v>
-      </c>
       <c r="J154" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K154" t="s">
         <v>569</v>
@@ -8704,22 +8704,22 @@
         <v>14</v>
       </c>
       <c r="E155" t="s">
+        <v>337</v>
+      </c>
+      <c r="F155" t="s">
         <v>564</v>
       </c>
-      <c r="F155" t="s">
+      <c r="G155" t="s">
         <v>589</v>
       </c>
-      <c r="G155" t="s">
-        <v>566</v>
-      </c>
       <c r="H155" t="s">
+        <v>590</v>
+      </c>
+      <c r="I155" t="s">
         <v>567</v>
       </c>
-      <c r="I155" t="s">
-        <v>338</v>
-      </c>
       <c r="J155" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K155" t="s">
         <v>569</v>
@@ -8739,22 +8739,22 @@
         <v>14</v>
       </c>
       <c r="E156" t="s">
+        <v>337</v>
+      </c>
+      <c r="F156" t="s">
         <v>564</v>
       </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
         <v>618</v>
       </c>
-      <c r="G156" t="s">
-        <v>566</v>
-      </c>
       <c r="H156" t="s">
+        <v>619</v>
+      </c>
+      <c r="I156" t="s">
         <v>567</v>
       </c>
-      <c r="I156" t="s">
-        <v>338</v>
-      </c>
       <c r="J156" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="K156" t="s">
         <v>569</v>
@@ -8774,25 +8774,25 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
+        <v>337</v>
+      </c>
+      <c r="F157" t="s">
         <v>564</v>
       </c>
-      <c r="F157" t="s">
+      <c r="G157" t="s">
         <v>618</v>
       </c>
-      <c r="G157" t="s">
-        <v>566</v>
-      </c>
       <c r="H157" t="s">
+        <v>619</v>
+      </c>
+      <c r="I157" t="s">
         <v>567</v>
       </c>
-      <c r="I157" t="s">
-        <v>338</v>
-      </c>
       <c r="J157" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="K157" t="s">
-        <v>623</v>
+        <v>569</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -8809,22 +8809,22 @@
         <v>14</v>
       </c>
       <c r="E158" t="s">
+        <v>337</v>
+      </c>
+      <c r="F158" t="s">
         <v>564</v>
       </c>
-      <c r="F158" t="s">
+      <c r="G158" t="s">
         <v>618</v>
       </c>
-      <c r="G158" t="s">
-        <v>566</v>
-      </c>
       <c r="H158" t="s">
+        <v>619</v>
+      </c>
+      <c r="I158" t="s">
         <v>567</v>
       </c>
-      <c r="I158" t="s">
-        <v>338</v>
-      </c>
       <c r="J158" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="K158" t="s">
         <v>569</v>
@@ -8844,22 +8844,22 @@
         <v>14</v>
       </c>
       <c r="E159" t="s">
+        <v>337</v>
+      </c>
+      <c r="F159" t="s">
         <v>564</v>
       </c>
-      <c r="F159" t="s">
+      <c r="G159" t="s">
         <v>618</v>
       </c>
-      <c r="G159" t="s">
-        <v>566</v>
-      </c>
       <c r="H159" t="s">
+        <v>619</v>
+      </c>
+      <c r="I159" t="s">
         <v>567</v>
       </c>
-      <c r="I159" t="s">
-        <v>338</v>
-      </c>
       <c r="J159" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="K159" t="s">
         <v>569</v>
@@ -8879,22 +8879,22 @@
         <v>14</v>
       </c>
       <c r="E160" t="s">
+        <v>337</v>
+      </c>
+      <c r="F160" t="s">
         <v>564</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
         <v>618</v>
       </c>
-      <c r="G160" t="s">
-        <v>566</v>
-      </c>
       <c r="H160" t="s">
+        <v>619</v>
+      </c>
+      <c r="I160" t="s">
         <v>567</v>
       </c>
-      <c r="I160" t="s">
-        <v>338</v>
-      </c>
       <c r="J160" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="K160" t="s">
         <v>569</v>
@@ -8914,22 +8914,22 @@
         <v>14</v>
       </c>
       <c r="E161" t="s">
+        <v>337</v>
+      </c>
+      <c r="F161" t="s">
         <v>564</v>
       </c>
-      <c r="F161" t="s">
+      <c r="G161" t="s">
         <v>618</v>
       </c>
-      <c r="G161" t="s">
-        <v>566</v>
-      </c>
       <c r="H161" t="s">
+        <v>619</v>
+      </c>
+      <c r="I161" t="s">
         <v>567</v>
       </c>
-      <c r="I161" t="s">
-        <v>338</v>
-      </c>
       <c r="J161" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="K161" t="s">
         <v>569</v>
@@ -8949,22 +8949,22 @@
         <v>14</v>
       </c>
       <c r="E162" t="s">
+        <v>337</v>
+      </c>
+      <c r="F162" t="s">
         <v>564</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>639</v>
       </c>
-      <c r="G162" t="s">
-        <v>566</v>
-      </c>
       <c r="H162" t="s">
+        <v>640</v>
+      </c>
+      <c r="I162" t="s">
         <v>567</v>
       </c>
-      <c r="I162" t="s">
-        <v>338</v>
-      </c>
       <c r="J162" t="s">
-        <v>640</v>
+        <v>568</v>
       </c>
       <c r="K162" t="s">
         <v>569</v>
@@ -8984,25 +8984,25 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
+        <v>337</v>
+      </c>
+      <c r="F163" t="s">
         <v>564</v>
       </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
         <v>644</v>
       </c>
-      <c r="G163" t="s">
-        <v>566</v>
-      </c>
       <c r="H163" t="s">
+        <v>642</v>
+      </c>
+      <c r="I163" t="s">
         <v>567</v>
       </c>
-      <c r="I163" t="s">
-        <v>338</v>
-      </c>
       <c r="J163" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="K163" t="s">
-        <v>645</v>
+        <v>569</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -9019,22 +9019,22 @@
         <v>14</v>
       </c>
       <c r="E164" t="s">
+        <v>337</v>
+      </c>
+      <c r="F164" t="s">
         <v>564</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>649</v>
       </c>
-      <c r="G164" t="s">
-        <v>566</v>
-      </c>
       <c r="H164" t="s">
+        <v>650</v>
+      </c>
+      <c r="I164" t="s">
         <v>567</v>
       </c>
-      <c r="I164" t="s">
-        <v>338</v>
-      </c>
       <c r="J164" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K164" t="s">
         <v>569</v>
@@ -9054,22 +9054,22 @@
         <v>14</v>
       </c>
       <c r="E165" t="s">
+        <v>337</v>
+      </c>
+      <c r="F165" t="s">
         <v>564</v>
       </c>
-      <c r="F165" t="s">
+      <c r="G165" t="s">
         <v>649</v>
       </c>
-      <c r="G165" t="s">
-        <v>566</v>
-      </c>
       <c r="H165" t="s">
+        <v>650</v>
+      </c>
+      <c r="I165" t="s">
         <v>567</v>
       </c>
-      <c r="I165" t="s">
-        <v>338</v>
-      </c>
       <c r="J165" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K165" t="s">
         <v>569</v>
@@ -9089,22 +9089,22 @@
         <v>14</v>
       </c>
       <c r="E166" t="s">
+        <v>337</v>
+      </c>
+      <c r="F166" t="s">
         <v>564</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>649</v>
       </c>
-      <c r="G166" t="s">
-        <v>566</v>
-      </c>
       <c r="H166" t="s">
+        <v>650</v>
+      </c>
+      <c r="I166" t="s">
         <v>567</v>
       </c>
-      <c r="I166" t="s">
-        <v>338</v>
-      </c>
       <c r="J166" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K166" t="s">
         <v>569</v>
@@ -9124,22 +9124,22 @@
         <v>14</v>
       </c>
       <c r="E167" t="s">
+        <v>337</v>
+      </c>
+      <c r="F167" t="s">
         <v>564</v>
       </c>
-      <c r="F167" t="s">
+      <c r="G167" t="s">
         <v>649</v>
       </c>
-      <c r="G167" t="s">
-        <v>566</v>
-      </c>
       <c r="H167" t="s">
+        <v>650</v>
+      </c>
+      <c r="I167" t="s">
         <v>567</v>
       </c>
-      <c r="I167" t="s">
-        <v>338</v>
-      </c>
       <c r="J167" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K167" t="s">
         <v>569</v>
@@ -9159,25 +9159,25 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
+        <v>337</v>
+      </c>
+      <c r="F168" t="s">
         <v>564</v>
       </c>
-      <c r="F168" t="s">
+      <c r="G168" t="s">
         <v>649</v>
       </c>
-      <c r="G168" t="s">
-        <v>566</v>
-      </c>
       <c r="H168" t="s">
+        <v>650</v>
+      </c>
+      <c r="I168" t="s">
         <v>567</v>
       </c>
-      <c r="I168" t="s">
-        <v>338</v>
-      </c>
       <c r="J168" t="s">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="K168" t="s">
-        <v>663</v>
+        <v>569</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -9191,25 +9191,25 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
+        <v>337</v>
+      </c>
+      <c r="F169" t="s">
         <v>564</v>
       </c>
-      <c r="F169" t="s">
+      <c r="G169" t="s">
         <v>649</v>
       </c>
-      <c r="G169" t="s">
-        <v>566</v>
-      </c>
       <c r="H169" t="s">
+        <v>650</v>
+      </c>
+      <c r="I169" t="s">
         <v>567</v>
       </c>
-      <c r="I169" t="s">
-        <v>338</v>
-      </c>
       <c r="J169" t="s">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="K169" t="s">
-        <v>663</v>
+        <v>569</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -9226,22 +9226,22 @@
         <v>14</v>
       </c>
       <c r="E170" t="s">
+        <v>337</v>
+      </c>
+      <c r="F170" t="s">
         <v>564</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>649</v>
       </c>
-      <c r="G170" t="s">
-        <v>566</v>
-      </c>
       <c r="H170" t="s">
+        <v>650</v>
+      </c>
+      <c r="I170" t="s">
         <v>567</v>
       </c>
-      <c r="I170" t="s">
-        <v>338</v>
-      </c>
       <c r="J170" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K170" t="s">
         <v>569</v>
@@ -9263,17 +9263,17 @@
       <c r="E171" t="s">
         <v>337</v>
       </c>
-      <c r="G171" t="s">
+      <c r="F171" t="s">
+        <v>338</v>
+      </c>
+      <c r="I171" t="s">
         <v>672</v>
       </c>
-      <c r="H171" t="s">
+      <c r="J171" t="s">
+        <v>339</v>
+      </c>
+      <c r="K171" t="s">
         <v>673</v>
-      </c>
-      <c r="I171" t="s">
-        <v>338</v>
-      </c>
-      <c r="K171" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -9290,19 +9290,19 @@
         <v>14</v>
       </c>
       <c r="E172" t="s">
+        <v>233</v>
+      </c>
+      <c r="F172" t="s">
         <v>243</v>
       </c>
-      <c r="G172" t="s">
+      <c r="I172" t="s">
         <v>672</v>
       </c>
-      <c r="H172" t="s">
+      <c r="J172" t="s">
+        <v>244</v>
+      </c>
+      <c r="K172" t="s">
         <v>673</v>
-      </c>
-      <c r="I172" t="s">
-        <v>237</v>
-      </c>
-      <c r="K172" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -9321,17 +9321,17 @@
       <c r="E173" t="s">
         <v>337</v>
       </c>
-      <c r="G173" t="s">
+      <c r="F173" t="s">
+        <v>338</v>
+      </c>
+      <c r="I173" t="s">
         <v>672</v>
       </c>
-      <c r="H173" t="s">
+      <c r="J173" t="s">
+        <v>339</v>
+      </c>
+      <c r="K173" t="s">
         <v>673</v>
-      </c>
-      <c r="I173" t="s">
-        <v>338</v>
-      </c>
-      <c r="K173" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -9350,17 +9350,17 @@
       <c r="E174" t="s">
         <v>337</v>
       </c>
-      <c r="G174" t="s">
+      <c r="F174" t="s">
+        <v>338</v>
+      </c>
+      <c r="I174" t="s">
         <v>672</v>
       </c>
-      <c r="H174" t="s">
+      <c r="J174" t="s">
+        <v>339</v>
+      </c>
+      <c r="K174" t="s">
         <v>673</v>
-      </c>
-      <c r="I174" t="s">
-        <v>338</v>
-      </c>
-      <c r="K174" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -9379,17 +9379,17 @@
       <c r="E175" t="s">
         <v>337</v>
       </c>
-      <c r="G175" t="s">
+      <c r="F175" t="s">
+        <v>338</v>
+      </c>
+      <c r="I175" t="s">
         <v>672</v>
       </c>
-      <c r="H175" t="s">
+      <c r="J175" t="s">
+        <v>339</v>
+      </c>
+      <c r="K175" t="s">
         <v>673</v>
-      </c>
-      <c r="I175" t="s">
-        <v>338</v>
-      </c>
-      <c r="K175" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -9405,17 +9405,17 @@
       <c r="E176" t="s">
         <v>337</v>
       </c>
-      <c r="G176" t="s">
+      <c r="F176" t="s">
+        <v>338</v>
+      </c>
+      <c r="I176" t="s">
         <v>672</v>
       </c>
-      <c r="H176" t="s">
+      <c r="J176" t="s">
+        <v>339</v>
+      </c>
+      <c r="K176" t="s">
         <v>673</v>
-      </c>
-      <c r="I176" t="s">
-        <v>338</v>
-      </c>
-      <c r="K176" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -9434,17 +9434,17 @@
       <c r="E177" t="s">
         <v>337</v>
       </c>
-      <c r="G177" t="s">
+      <c r="F177" t="s">
+        <v>338</v>
+      </c>
+      <c r="I177" t="s">
         <v>691</v>
       </c>
-      <c r="H177" t="s">
+      <c r="J177" t="s">
+        <v>339</v>
+      </c>
+      <c r="K177" t="s">
         <v>692</v>
-      </c>
-      <c r="I177" t="s">
-        <v>338</v>
-      </c>
-      <c r="K177" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -9463,17 +9463,17 @@
       <c r="E178" t="s">
         <v>337</v>
       </c>
-      <c r="G178" t="s">
+      <c r="F178" t="s">
+        <v>338</v>
+      </c>
+      <c r="I178" t="s">
         <v>691</v>
       </c>
-      <c r="H178" t="s">
+      <c r="J178" t="s">
+        <v>339</v>
+      </c>
+      <c r="K178" t="s">
         <v>692</v>
-      </c>
-      <c r="I178" t="s">
-        <v>338</v>
-      </c>
-      <c r="K178" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -9492,17 +9492,17 @@
       <c r="E179" t="s">
         <v>337</v>
       </c>
-      <c r="G179" t="s">
+      <c r="F179" t="s">
+        <v>338</v>
+      </c>
+      <c r="I179" t="s">
         <v>691</v>
       </c>
-      <c r="H179" t="s">
+      <c r="J179" t="s">
+        <v>339</v>
+      </c>
+      <c r="K179" t="s">
         <v>692</v>
-      </c>
-      <c r="I179" t="s">
-        <v>338</v>
-      </c>
-      <c r="K179" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -9521,17 +9521,17 @@
       <c r="E180" t="s">
         <v>337</v>
       </c>
-      <c r="G180" t="s">
+      <c r="F180" t="s">
+        <v>338</v>
+      </c>
+      <c r="I180" t="s">
         <v>691</v>
       </c>
-      <c r="H180" t="s">
+      <c r="J180" t="s">
+        <v>339</v>
+      </c>
+      <c r="K180" t="s">
         <v>692</v>
-      </c>
-      <c r="I180" t="s">
-        <v>338</v>
-      </c>
-      <c r="K180" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -9548,19 +9548,19 @@
         <v>14</v>
       </c>
       <c r="E181" t="s">
+        <v>337</v>
+      </c>
+      <c r="F181" t="s">
         <v>705</v>
       </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
         <v>706</v>
       </c>
-      <c r="G181" t="s">
+      <c r="H181" t="s">
         <v>707</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>708</v>
-      </c>
-      <c r="I181" t="s">
-        <v>338</v>
       </c>
       <c r="J181" t="s">
         <v>709</v>
@@ -9583,19 +9583,19 @@
         <v>14</v>
       </c>
       <c r="E182" t="s">
+        <v>337</v>
+      </c>
+      <c r="F182" t="s">
         <v>705</v>
       </c>
-      <c r="F182" t="s">
+      <c r="G182" t="s">
         <v>706</v>
       </c>
-      <c r="G182" t="s">
+      <c r="H182" t="s">
         <v>707</v>
       </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>708</v>
-      </c>
-      <c r="I182" t="s">
-        <v>338</v>
       </c>
       <c r="J182" t="s">
         <v>709</v>
@@ -9618,19 +9618,19 @@
         <v>14</v>
       </c>
       <c r="E183" t="s">
+        <v>337</v>
+      </c>
+      <c r="F183" t="s">
         <v>705</v>
       </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
         <v>706</v>
       </c>
-      <c r="G183" t="s">
+      <c r="H183" t="s">
         <v>707</v>
       </c>
-      <c r="H183" t="s">
+      <c r="I183" t="s">
         <v>708</v>
-      </c>
-      <c r="I183" t="s">
-        <v>338</v>
       </c>
       <c r="J183" t="s">
         <v>709</v>
@@ -9653,19 +9653,19 @@
         <v>14</v>
       </c>
       <c r="E184" t="s">
+        <v>337</v>
+      </c>
+      <c r="F184" t="s">
         <v>705</v>
       </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
         <v>706</v>
       </c>
-      <c r="G184" t="s">
+      <c r="H184" t="s">
         <v>707</v>
       </c>
-      <c r="H184" t="s">
+      <c r="I184" t="s">
         <v>708</v>
-      </c>
-      <c r="I184" t="s">
-        <v>338</v>
       </c>
       <c r="J184" t="s">
         <v>709</v>
@@ -9688,19 +9688,19 @@
         <v>14</v>
       </c>
       <c r="E185" t="s">
+        <v>337</v>
+      </c>
+      <c r="F185" t="s">
         <v>705</v>
       </c>
-      <c r="F185" t="s">
+      <c r="G185" t="s">
         <v>706</v>
       </c>
-      <c r="G185" t="s">
+      <c r="H185" t="s">
         <v>707</v>
       </c>
-      <c r="H185" t="s">
+      <c r="I185" t="s">
         <v>708</v>
-      </c>
-      <c r="I185" t="s">
-        <v>338</v>
       </c>
       <c r="J185" t="s">
         <v>709</v>
@@ -9723,19 +9723,19 @@
         <v>14</v>
       </c>
       <c r="E186" t="s">
+        <v>337</v>
+      </c>
+      <c r="F186" t="s">
         <v>705</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>706</v>
       </c>
-      <c r="G186" t="s">
+      <c r="H186" t="s">
         <v>707</v>
       </c>
-      <c r="H186" t="s">
+      <c r="I186" t="s">
         <v>708</v>
-      </c>
-      <c r="I186" t="s">
-        <v>338</v>
       </c>
       <c r="J186" t="s">
         <v>709</v>
@@ -9758,19 +9758,19 @@
         <v>14</v>
       </c>
       <c r="E187" t="s">
+        <v>337</v>
+      </c>
+      <c r="F187" t="s">
         <v>705</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>706</v>
       </c>
-      <c r="G187" t="s">
+      <c r="H187" t="s">
         <v>707</v>
       </c>
-      <c r="H187" t="s">
+      <c r="I187" t="s">
         <v>708</v>
-      </c>
-      <c r="I187" t="s">
-        <v>338</v>
       </c>
       <c r="J187" t="s">
         <v>709</v>
@@ -9793,19 +9793,19 @@
         <v>14</v>
       </c>
       <c r="E188" t="s">
+        <v>337</v>
+      </c>
+      <c r="F188" t="s">
         <v>705</v>
       </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>706</v>
       </c>
-      <c r="G188" t="s">
+      <c r="H188" t="s">
         <v>707</v>
       </c>
-      <c r="H188" t="s">
+      <c r="I188" t="s">
         <v>708</v>
-      </c>
-      <c r="I188" t="s">
-        <v>338</v>
       </c>
       <c r="J188" t="s">
         <v>709</v>
@@ -9828,19 +9828,19 @@
         <v>14</v>
       </c>
       <c r="E189" t="s">
+        <v>337</v>
+      </c>
+      <c r="F189" t="s">
         <v>705</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>706</v>
       </c>
-      <c r="G189" t="s">
+      <c r="H189" t="s">
         <v>707</v>
       </c>
-      <c r="H189" t="s">
+      <c r="I189" t="s">
         <v>708</v>
-      </c>
-      <c r="I189" t="s">
-        <v>338</v>
       </c>
       <c r="J189" t="s">
         <v>709</v>
@@ -9863,19 +9863,19 @@
         <v>14</v>
       </c>
       <c r="E190" t="s">
+        <v>337</v>
+      </c>
+      <c r="F190" t="s">
         <v>705</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>706</v>
       </c>
-      <c r="G190" t="s">
+      <c r="H190" t="s">
         <v>707</v>
       </c>
-      <c r="H190" t="s">
+      <c r="I190" t="s">
         <v>708</v>
-      </c>
-      <c r="I190" t="s">
-        <v>338</v>
       </c>
       <c r="J190" t="s">
         <v>709</v>
@@ -9898,19 +9898,19 @@
         <v>14</v>
       </c>
       <c r="E191" t="s">
+        <v>337</v>
+      </c>
+      <c r="F191" t="s">
         <v>705</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>706</v>
       </c>
-      <c r="G191" t="s">
+      <c r="H191" t="s">
         <v>707</v>
       </c>
-      <c r="H191" t="s">
+      <c r="I191" t="s">
         <v>708</v>
-      </c>
-      <c r="I191" t="s">
-        <v>338</v>
       </c>
       <c r="J191" t="s">
         <v>709</v>
@@ -9930,19 +9930,19 @@
         <v>14</v>
       </c>
       <c r="E192" t="s">
+        <v>337</v>
+      </c>
+      <c r="F192" t="s">
         <v>705</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>706</v>
       </c>
-      <c r="G192" t="s">
+      <c r="H192" t="s">
         <v>707</v>
       </c>
-      <c r="H192" t="s">
+      <c r="I192" t="s">
         <v>708</v>
-      </c>
-      <c r="I192" t="s">
-        <v>338</v>
       </c>
       <c r="J192" t="s">
         <v>709</v>
@@ -9965,25 +9965,25 @@
         <v>14</v>
       </c>
       <c r="E193" t="s">
+        <v>337</v>
+      </c>
+      <c r="F193" t="s">
         <v>575</v>
       </c>
-      <c r="F193" t="s">
+      <c r="G193" t="s">
         <v>706</v>
       </c>
-      <c r="G193" t="s">
+      <c r="H193" t="s">
         <v>707</v>
       </c>
-      <c r="H193" t="s">
+      <c r="I193" t="s">
         <v>708</v>
       </c>
-      <c r="I193" t="s">
-        <v>338</v>
-      </c>
       <c r="J193" t="s">
-        <v>709</v>
+        <v>746</v>
       </c>
       <c r="K193" t="s">
-        <v>746</v>
+        <v>710</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -10000,19 +10000,19 @@
         <v>14</v>
       </c>
       <c r="E194" t="s">
+        <v>337</v>
+      </c>
+      <c r="F194" t="s">
         <v>705</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>706</v>
       </c>
-      <c r="G194" t="s">
+      <c r="H194" t="s">
         <v>707</v>
       </c>
-      <c r="H194" t="s">
+      <c r="I194" t="s">
         <v>708</v>
-      </c>
-      <c r="I194" t="s">
-        <v>338</v>
       </c>
       <c r="J194" t="s">
         <v>709</v>
@@ -10035,19 +10035,19 @@
         <v>14</v>
       </c>
       <c r="E195" t="s">
+        <v>337</v>
+      </c>
+      <c r="F195" t="s">
         <v>705</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>706</v>
       </c>
-      <c r="G195" t="s">
+      <c r="H195" t="s">
         <v>707</v>
       </c>
-      <c r="H195" t="s">
+      <c r="I195" t="s">
         <v>708</v>
-      </c>
-      <c r="I195" t="s">
-        <v>338</v>
       </c>
       <c r="J195" t="s">
         <v>709</v>
@@ -10070,19 +10070,19 @@
         <v>14</v>
       </c>
       <c r="E196" t="s">
+        <v>337</v>
+      </c>
+      <c r="F196" t="s">
         <v>705</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>706</v>
       </c>
-      <c r="G196" t="s">
+      <c r="H196" t="s">
         <v>707</v>
       </c>
-      <c r="H196" t="s">
+      <c r="I196" t="s">
         <v>708</v>
-      </c>
-      <c r="I196" t="s">
-        <v>338</v>
       </c>
       <c r="J196" t="s">
         <v>709</v>
@@ -10105,19 +10105,19 @@
         <v>14</v>
       </c>
       <c r="E197" t="s">
+        <v>337</v>
+      </c>
+      <c r="F197" t="s">
         <v>705</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
         <v>706</v>
       </c>
-      <c r="G197" t="s">
+      <c r="H197" t="s">
         <v>707</v>
       </c>
-      <c r="H197" t="s">
+      <c r="I197" t="s">
         <v>708</v>
-      </c>
-      <c r="I197" t="s">
-        <v>338</v>
       </c>
       <c r="J197" t="s">
         <v>709</v>
@@ -10140,19 +10140,19 @@
         <v>14</v>
       </c>
       <c r="E198" t="s">
+        <v>337</v>
+      </c>
+      <c r="F198" t="s">
         <v>705</v>
       </c>
-      <c r="F198" t="s">
+      <c r="G198" t="s">
         <v>706</v>
       </c>
-      <c r="G198" t="s">
+      <c r="H198" t="s">
         <v>707</v>
       </c>
-      <c r="H198" t="s">
+      <c r="I198" t="s">
         <v>708</v>
-      </c>
-      <c r="I198" t="s">
-        <v>338</v>
       </c>
       <c r="J198" t="s">
         <v>709</v>
@@ -10175,25 +10175,25 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
+        <v>337</v>
+      </c>
+      <c r="F199" t="s">
         <v>705</v>
       </c>
-      <c r="F199" t="s">
+      <c r="G199" t="s">
         <v>765</v>
       </c>
-      <c r="G199" t="s">
-        <v>707</v>
-      </c>
       <c r="H199" t="s">
+        <v>766</v>
+      </c>
+      <c r="I199" t="s">
         <v>708</v>
       </c>
-      <c r="I199" t="s">
-        <v>338</v>
-      </c>
       <c r="J199" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="K199" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -10210,25 +10210,25 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
+        <v>337</v>
+      </c>
+      <c r="F200" t="s">
         <v>705</v>
       </c>
-      <c r="F200" t="s">
+      <c r="G200" t="s">
         <v>765</v>
       </c>
-      <c r="G200" t="s">
-        <v>707</v>
-      </c>
       <c r="H200" t="s">
+        <v>766</v>
+      </c>
+      <c r="I200" t="s">
         <v>708</v>
       </c>
-      <c r="I200" t="s">
-        <v>338</v>
-      </c>
       <c r="J200" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="K200" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -10245,25 +10245,25 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
+        <v>337</v>
+      </c>
+      <c r="F201" t="s">
         <v>705</v>
       </c>
-      <c r="F201" t="s">
+      <c r="G201" t="s">
         <v>765</v>
       </c>
-      <c r="G201" t="s">
-        <v>707</v>
-      </c>
       <c r="H201" t="s">
+        <v>766</v>
+      </c>
+      <c r="I201" t="s">
         <v>708</v>
       </c>
-      <c r="I201" t="s">
-        <v>338</v>
-      </c>
       <c r="J201" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="K201" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -10277,25 +10277,25 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
+        <v>337</v>
+      </c>
+      <c r="F202" t="s">
         <v>705</v>
       </c>
-      <c r="F202" t="s">
+      <c r="G202" t="s">
         <v>765</v>
       </c>
-      <c r="G202" t="s">
-        <v>707</v>
-      </c>
       <c r="H202" t="s">
+        <v>766</v>
+      </c>
+      <c r="I202" t="s">
         <v>708</v>
       </c>
-      <c r="I202" t="s">
-        <v>338</v>
-      </c>
       <c r="J202" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="K202" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -10312,25 +10312,25 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
+        <v>337</v>
+      </c>
+      <c r="F203" t="s">
         <v>575</v>
       </c>
-      <c r="F203" t="s">
+      <c r="G203" t="s">
         <v>765</v>
       </c>
-      <c r="G203" t="s">
-        <v>707</v>
-      </c>
       <c r="H203" t="s">
+        <v>766</v>
+      </c>
+      <c r="I203" t="s">
         <v>708</v>
       </c>
-      <c r="I203" t="s">
-        <v>338</v>
-      </c>
       <c r="J203" t="s">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="K203" t="s">
-        <v>746</v>
+        <v>710</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10344,25 +10344,25 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
+        <v>337</v>
+      </c>
+      <c r="F204" t="s">
         <v>705</v>
       </c>
-      <c r="F204" t="s">
+      <c r="G204" t="s">
         <v>765</v>
       </c>
-      <c r="G204" t="s">
-        <v>707</v>
-      </c>
       <c r="H204" t="s">
+        <v>766</v>
+      </c>
+      <c r="I204" t="s">
         <v>708</v>
       </c>
-      <c r="I204" t="s">
-        <v>338</v>
-      </c>
       <c r="J204" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="K204" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -10379,25 +10379,25 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
+        <v>337</v>
+      </c>
+      <c r="F205" t="s">
         <v>705</v>
       </c>
-      <c r="F205" t="s">
+      <c r="G205" t="s">
         <v>784</v>
       </c>
-      <c r="G205" t="s">
-        <v>707</v>
-      </c>
       <c r="H205" t="s">
+        <v>785</v>
+      </c>
+      <c r="I205" t="s">
         <v>708</v>
       </c>
-      <c r="I205" t="s">
-        <v>338</v>
-      </c>
       <c r="J205" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="K205" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -10414,25 +10414,25 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
+        <v>337</v>
+      </c>
+      <c r="F206" t="s">
         <v>705</v>
       </c>
-      <c r="F206" t="s">
+      <c r="G206" t="s">
         <v>784</v>
       </c>
-      <c r="G206" t="s">
-        <v>707</v>
-      </c>
       <c r="H206" t="s">
+        <v>785</v>
+      </c>
+      <c r="I206" t="s">
         <v>708</v>
       </c>
-      <c r="I206" t="s">
-        <v>338</v>
-      </c>
       <c r="J206" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="K206" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -10446,25 +10446,25 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
+        <v>337</v>
+      </c>
+      <c r="F207" t="s">
         <v>705</v>
       </c>
-      <c r="F207" t="s">
+      <c r="G207" t="s">
         <v>784</v>
       </c>
-      <c r="G207" t="s">
-        <v>707</v>
-      </c>
       <c r="H207" t="s">
+        <v>785</v>
+      </c>
+      <c r="I207" t="s">
         <v>708</v>
       </c>
-      <c r="I207" t="s">
-        <v>338</v>
-      </c>
       <c r="J207" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="K207" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -10481,25 +10481,25 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
+        <v>337</v>
+      </c>
+      <c r="F208" t="s">
         <v>575</v>
       </c>
-      <c r="F208" t="s">
+      <c r="G208" t="s">
         <v>784</v>
       </c>
-      <c r="G208" t="s">
-        <v>707</v>
-      </c>
       <c r="H208" t="s">
+        <v>785</v>
+      </c>
+      <c r="I208" t="s">
         <v>708</v>
       </c>
-      <c r="I208" t="s">
-        <v>338</v>
-      </c>
       <c r="J208" t="s">
-        <v>785</v>
+        <v>746</v>
       </c>
       <c r="K208" t="s">
-        <v>746</v>
+        <v>710</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10516,25 +10516,25 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
+        <v>337</v>
+      </c>
+      <c r="F209" t="s">
         <v>705</v>
       </c>
-      <c r="F209" t="s">
+      <c r="G209" t="s">
         <v>784</v>
       </c>
-      <c r="G209" t="s">
-        <v>707</v>
-      </c>
       <c r="H209" t="s">
+        <v>785</v>
+      </c>
+      <c r="I209" t="s">
         <v>708</v>
       </c>
-      <c r="I209" t="s">
-        <v>338</v>
-      </c>
       <c r="J209" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="K209" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -10551,19 +10551,19 @@
         <v>14</v>
       </c>
       <c r="E210" t="s">
+        <v>337</v>
+      </c>
+      <c r="F210" t="s">
         <v>801</v>
       </c>
-      <c r="F210" t="s">
+      <c r="G210" t="s">
         <v>802</v>
       </c>
-      <c r="G210" t="s">
+      <c r="H210" t="s">
         <v>803</v>
       </c>
-      <c r="H210" t="s">
+      <c r="I210" t="s">
         <v>804</v>
-      </c>
-      <c r="I210" t="s">
-        <v>338</v>
       </c>
       <c r="J210" t="s">
         <v>805</v>
@@ -10583,19 +10583,19 @@
         <v>14</v>
       </c>
       <c r="E211" t="s">
+        <v>337</v>
+      </c>
+      <c r="F211" t="s">
         <v>801</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>802</v>
       </c>
-      <c r="G211" t="s">
+      <c r="H211" t="s">
         <v>803</v>
       </c>
-      <c r="H211" t="s">
+      <c r="I211" t="s">
         <v>804</v>
-      </c>
-      <c r="I211" t="s">
-        <v>338</v>
       </c>
       <c r="J211" t="s">
         <v>805</v>
@@ -10618,19 +10618,19 @@
         <v>14</v>
       </c>
       <c r="E212" t="s">
+        <v>337</v>
+      </c>
+      <c r="F212" t="s">
         <v>801</v>
       </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>802</v>
       </c>
-      <c r="G212" t="s">
+      <c r="H212" t="s">
         <v>803</v>
       </c>
-      <c r="H212" t="s">
+      <c r="I212" t="s">
         <v>804</v>
-      </c>
-      <c r="I212" t="s">
-        <v>338</v>
       </c>
       <c r="J212" t="s">
         <v>805</v>
@@ -10650,19 +10650,19 @@
         <v>14</v>
       </c>
       <c r="E213" t="s">
+        <v>337</v>
+      </c>
+      <c r="F213" t="s">
         <v>801</v>
       </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>802</v>
       </c>
-      <c r="G213" t="s">
+      <c r="H213" t="s">
         <v>803</v>
       </c>
-      <c r="H213" t="s">
+      <c r="I213" t="s">
         <v>804</v>
-      </c>
-      <c r="I213" t="s">
-        <v>338</v>
       </c>
       <c r="J213" t="s">
         <v>805</v>
@@ -10685,19 +10685,19 @@
         <v>14</v>
       </c>
       <c r="E214" t="s">
+        <v>337</v>
+      </c>
+      <c r="F214" t="s">
         <v>801</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>802</v>
       </c>
-      <c r="G214" t="s">
+      <c r="H214" t="s">
         <v>803</v>
       </c>
-      <c r="H214" t="s">
+      <c r="I214" t="s">
         <v>804</v>
-      </c>
-      <c r="I214" t="s">
-        <v>338</v>
       </c>
       <c r="J214" t="s">
         <v>805</v>
@@ -10720,25 +10720,25 @@
         <v>14</v>
       </c>
       <c r="E215" t="s">
+        <v>337</v>
+      </c>
+      <c r="F215" t="s">
         <v>705</v>
       </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
         <v>802</v>
       </c>
-      <c r="G215" t="s">
+      <c r="H215" t="s">
         <v>803</v>
       </c>
-      <c r="H215" t="s">
+      <c r="I215" t="s">
         <v>804</v>
       </c>
-      <c r="I215" t="s">
-        <v>338</v>
-      </c>
       <c r="J215" t="s">
-        <v>805</v>
+        <v>767</v>
       </c>
       <c r="K215" t="s">
-        <v>767</v>
+        <v>806</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -10755,19 +10755,19 @@
         <v>14</v>
       </c>
       <c r="E216" t="s">
+        <v>337</v>
+      </c>
+      <c r="F216" t="s">
         <v>801</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>802</v>
       </c>
-      <c r="G216" t="s">
+      <c r="H216" t="s">
         <v>803</v>
       </c>
-      <c r="H216" t="s">
+      <c r="I216" t="s">
         <v>804</v>
-      </c>
-      <c r="I216" t="s">
-        <v>338</v>
       </c>
       <c r="J216" t="s">
         <v>805</v>
@@ -10790,19 +10790,19 @@
         <v>14</v>
       </c>
       <c r="E217" t="s">
+        <v>337</v>
+      </c>
+      <c r="F217" t="s">
         <v>801</v>
       </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
         <v>802</v>
       </c>
-      <c r="G217" t="s">
+      <c r="H217" t="s">
         <v>803</v>
       </c>
-      <c r="H217" t="s">
+      <c r="I217" t="s">
         <v>804</v>
-      </c>
-      <c r="I217" t="s">
-        <v>338</v>
       </c>
       <c r="J217" t="s">
         <v>805</v>
@@ -10822,19 +10822,19 @@
         <v>14</v>
       </c>
       <c r="E218" t="s">
+        <v>337</v>
+      </c>
+      <c r="F218" t="s">
         <v>801</v>
       </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>802</v>
       </c>
-      <c r="G218" t="s">
+      <c r="H218" t="s">
         <v>803</v>
       </c>
-      <c r="H218" t="s">
+      <c r="I218" t="s">
         <v>804</v>
-      </c>
-      <c r="I218" t="s">
-        <v>338</v>
       </c>
       <c r="J218" t="s">
         <v>805</v>
@@ -10854,19 +10854,19 @@
         <v>14</v>
       </c>
       <c r="E219" t="s">
+        <v>337</v>
+      </c>
+      <c r="F219" t="s">
         <v>801</v>
       </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>802</v>
       </c>
-      <c r="G219" t="s">
+      <c r="H219" t="s">
         <v>803</v>
       </c>
-      <c r="H219" t="s">
+      <c r="I219" t="s">
         <v>804</v>
-      </c>
-      <c r="I219" t="s">
-        <v>338</v>
       </c>
       <c r="J219" t="s">
         <v>805</v>
@@ -10889,25 +10889,25 @@
         <v>14</v>
       </c>
       <c r="E220" t="s">
+        <v>337</v>
+      </c>
+      <c r="F220" t="s">
         <v>564</v>
       </c>
-      <c r="F220" t="s">
+      <c r="G220" t="s">
         <v>802</v>
       </c>
-      <c r="G220" t="s">
+      <c r="H220" t="s">
         <v>803</v>
       </c>
-      <c r="H220" t="s">
+      <c r="I220" t="s">
         <v>804</v>
       </c>
-      <c r="I220" t="s">
-        <v>338</v>
-      </c>
       <c r="J220" t="s">
-        <v>805</v>
+        <v>663</v>
       </c>
       <c r="K220" t="s">
-        <v>663</v>
+        <v>806</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -10924,19 +10924,19 @@
         <v>14</v>
       </c>
       <c r="E221" t="s">
+        <v>337</v>
+      </c>
+      <c r="F221" t="s">
         <v>801</v>
       </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>802</v>
       </c>
-      <c r="G221" t="s">
+      <c r="H221" t="s">
         <v>803</v>
       </c>
-      <c r="H221" t="s">
+      <c r="I221" t="s">
         <v>804</v>
-      </c>
-      <c r="I221" t="s">
-        <v>338</v>
       </c>
       <c r="J221" t="s">
         <v>805</v>
@@ -10959,19 +10959,19 @@
         <v>14</v>
       </c>
       <c r="E222" t="s">
+        <v>337</v>
+      </c>
+      <c r="F222" t="s">
         <v>801</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>802</v>
       </c>
-      <c r="G222" t="s">
+      <c r="H222" t="s">
         <v>803</v>
       </c>
-      <c r="H222" t="s">
+      <c r="I222" t="s">
         <v>804</v>
-      </c>
-      <c r="I222" t="s">
-        <v>338</v>
       </c>
       <c r="J222" t="s">
         <v>805</v>
@@ -10991,19 +10991,19 @@
         <v>14</v>
       </c>
       <c r="E223" t="s">
+        <v>337</v>
+      </c>
+      <c r="F223" t="s">
         <v>801</v>
       </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>802</v>
       </c>
-      <c r="G223" t="s">
+      <c r="H223" t="s">
         <v>803</v>
       </c>
-      <c r="H223" t="s">
+      <c r="I223" t="s">
         <v>804</v>
-      </c>
-      <c r="I223" t="s">
-        <v>338</v>
       </c>
       <c r="J223" t="s">
         <v>805</v>
@@ -11026,19 +11026,19 @@
         <v>14</v>
       </c>
       <c r="E224" t="s">
+        <v>337</v>
+      </c>
+      <c r="F224" t="s">
         <v>801</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>802</v>
       </c>
-      <c r="G224" t="s">
+      <c r="H224" t="s">
         <v>803</v>
       </c>
-      <c r="H224" t="s">
+      <c r="I224" t="s">
         <v>804</v>
-      </c>
-      <c r="I224" t="s">
-        <v>338</v>
       </c>
       <c r="J224" t="s">
         <v>805</v>
@@ -11061,19 +11061,19 @@
         <v>14</v>
       </c>
       <c r="E225" t="s">
+        <v>337</v>
+      </c>
+      <c r="F225" t="s">
         <v>801</v>
       </c>
-      <c r="F225" t="s">
+      <c r="G225" t="s">
         <v>802</v>
       </c>
-      <c r="G225" t="s">
+      <c r="H225" t="s">
         <v>803</v>
       </c>
-      <c r="H225" t="s">
+      <c r="I225" t="s">
         <v>804</v>
-      </c>
-      <c r="I225" t="s">
-        <v>338</v>
       </c>
       <c r="J225" t="s">
         <v>805</v>
@@ -11096,25 +11096,25 @@
         <v>14</v>
       </c>
       <c r="E226" t="s">
+        <v>337</v>
+      </c>
+      <c r="F226" t="s">
         <v>575</v>
       </c>
-      <c r="F226" t="s">
+      <c r="G226" t="s">
         <v>802</v>
       </c>
-      <c r="G226" t="s">
+      <c r="H226" t="s">
         <v>803</v>
       </c>
-      <c r="H226" t="s">
+      <c r="I226" t="s">
         <v>804</v>
       </c>
-      <c r="I226" t="s">
-        <v>338</v>
-      </c>
       <c r="J226" t="s">
-        <v>805</v>
+        <v>576</v>
       </c>
       <c r="K226" t="s">
-        <v>576</v>
+        <v>806</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -11131,19 +11131,19 @@
         <v>14</v>
       </c>
       <c r="E227" t="s">
+        <v>337</v>
+      </c>
+      <c r="F227" t="s">
         <v>801</v>
       </c>
-      <c r="F227" t="s">
+      <c r="G227" t="s">
         <v>802</v>
       </c>
-      <c r="G227" t="s">
+      <c r="H227" t="s">
         <v>803</v>
       </c>
-      <c r="H227" t="s">
+      <c r="I227" t="s">
         <v>804</v>
-      </c>
-      <c r="I227" t="s">
-        <v>338</v>
       </c>
       <c r="J227" t="s">
         <v>805</v>
@@ -11169,22 +11169,22 @@
         <v>337</v>
       </c>
       <c r="F228" t="s">
+        <v>338</v>
+      </c>
+      <c r="G228" t="s">
         <v>802</v>
       </c>
-      <c r="G228" t="s">
+      <c r="H228" t="s">
         <v>803</v>
       </c>
-      <c r="H228" t="s">
+      <c r="I228" t="s">
         <v>804</v>
       </c>
-      <c r="I228" t="s">
-        <v>338</v>
-      </c>
       <c r="J228" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K228" t="s">
-        <v>339</v>
+        <v>806</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -11201,25 +11201,25 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
+        <v>337</v>
+      </c>
+      <c r="F229" t="s">
         <v>801</v>
       </c>
-      <c r="F229" t="s">
+      <c r="G229" t="s">
         <v>859</v>
       </c>
-      <c r="G229" t="s">
-        <v>803</v>
-      </c>
       <c r="H229" t="s">
+        <v>860</v>
+      </c>
+      <c r="I229" t="s">
         <v>804</v>
       </c>
-      <c r="I229" t="s">
-        <v>338</v>
-      </c>
       <c r="J229" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="K229" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -11236,25 +11236,25 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
+        <v>337</v>
+      </c>
+      <c r="F230" t="s">
         <v>801</v>
       </c>
-      <c r="F230" t="s">
+      <c r="G230" t="s">
         <v>859</v>
       </c>
-      <c r="G230" t="s">
-        <v>803</v>
-      </c>
       <c r="H230" t="s">
+        <v>860</v>
+      </c>
+      <c r="I230" t="s">
         <v>804</v>
       </c>
-      <c r="I230" t="s">
-        <v>338</v>
-      </c>
       <c r="J230" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="K230" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -11271,25 +11271,25 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
+        <v>337</v>
+      </c>
+      <c r="F231" t="s">
         <v>564</v>
       </c>
-      <c r="F231" t="s">
+      <c r="G231" t="s">
         <v>859</v>
       </c>
-      <c r="G231" t="s">
-        <v>803</v>
-      </c>
       <c r="H231" t="s">
+        <v>860</v>
+      </c>
+      <c r="I231" t="s">
         <v>804</v>
       </c>
-      <c r="I231" t="s">
-        <v>338</v>
-      </c>
       <c r="J231" t="s">
-        <v>860</v>
+        <v>623</v>
       </c>
       <c r="K231" t="s">
-        <v>623</v>
+        <v>806</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11306,25 +11306,25 @@
         <v>14</v>
       </c>
       <c r="E232" t="s">
+        <v>337</v>
+      </c>
+      <c r="F232" t="s">
         <v>564</v>
       </c>
-      <c r="F232" t="s">
+      <c r="G232" t="s">
         <v>859</v>
       </c>
-      <c r="G232" t="s">
-        <v>803</v>
-      </c>
       <c r="H232" t="s">
+        <v>860</v>
+      </c>
+      <c r="I232" t="s">
         <v>804</v>
       </c>
-      <c r="I232" t="s">
-        <v>338</v>
-      </c>
       <c r="J232" t="s">
-        <v>860</v>
+        <v>663</v>
       </c>
       <c r="K232" t="s">
-        <v>663</v>
+        <v>806</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11341,25 +11341,25 @@
         <v>14</v>
       </c>
       <c r="E233" t="s">
+        <v>337</v>
+      </c>
+      <c r="F233" t="s">
         <v>801</v>
       </c>
-      <c r="F233" t="s">
+      <c r="G233" t="s">
         <v>859</v>
       </c>
-      <c r="G233" t="s">
-        <v>803</v>
-      </c>
       <c r="H233" t="s">
+        <v>860</v>
+      </c>
+      <c r="I233" t="s">
         <v>804</v>
       </c>
-      <c r="I233" t="s">
-        <v>338</v>
-      </c>
       <c r="J233" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="K233" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -11376,25 +11376,25 @@
         <v>14</v>
       </c>
       <c r="E234" t="s">
+        <v>337</v>
+      </c>
+      <c r="F234" t="s">
         <v>801</v>
       </c>
-      <c r="F234" t="s">
+      <c r="G234" t="s">
         <v>859</v>
       </c>
-      <c r="G234" t="s">
-        <v>803</v>
-      </c>
       <c r="H234" t="s">
+        <v>860</v>
+      </c>
+      <c r="I234" t="s">
         <v>804</v>
       </c>
-      <c r="I234" t="s">
-        <v>338</v>
-      </c>
       <c r="J234" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="K234" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -11411,25 +11411,25 @@
         <v>14</v>
       </c>
       <c r="E235" t="s">
+        <v>337</v>
+      </c>
+      <c r="F235" t="s">
         <v>801</v>
       </c>
-      <c r="F235" t="s">
+      <c r="G235" t="s">
         <v>859</v>
       </c>
-      <c r="G235" t="s">
-        <v>803</v>
-      </c>
       <c r="H235" t="s">
+        <v>860</v>
+      </c>
+      <c r="I235" t="s">
         <v>804</v>
       </c>
-      <c r="I235" t="s">
-        <v>338</v>
-      </c>
       <c r="J235" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="K235" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -11446,25 +11446,25 @@
         <v>14</v>
       </c>
       <c r="E236" t="s">
+        <v>337</v>
+      </c>
+      <c r="F236" t="s">
         <v>801</v>
       </c>
-      <c r="F236" t="s">
+      <c r="G236" t="s">
         <v>859</v>
       </c>
-      <c r="G236" t="s">
-        <v>803</v>
-      </c>
       <c r="H236" t="s">
+        <v>860</v>
+      </c>
+      <c r="I236" t="s">
         <v>804</v>
       </c>
-      <c r="I236" t="s">
-        <v>338</v>
-      </c>
       <c r="J236" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="K236" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -11481,25 +11481,25 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
+        <v>337</v>
+      </c>
+      <c r="F237" t="s">
         <v>801</v>
       </c>
-      <c r="F237" t="s">
+      <c r="G237" t="s">
         <v>859</v>
       </c>
-      <c r="G237" t="s">
-        <v>803</v>
-      </c>
       <c r="H237" t="s">
+        <v>860</v>
+      </c>
+      <c r="I237" t="s">
         <v>804</v>
       </c>
-      <c r="I237" t="s">
-        <v>338</v>
-      </c>
       <c r="J237" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="K237" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -11516,25 +11516,25 @@
         <v>14</v>
       </c>
       <c r="E238" t="s">
+        <v>337</v>
+      </c>
+      <c r="F238" t="s">
         <v>801</v>
       </c>
-      <c r="F238" t="s">
+      <c r="G238" t="s">
         <v>859</v>
       </c>
-      <c r="G238" t="s">
-        <v>803</v>
-      </c>
       <c r="H238" t="s">
+        <v>860</v>
+      </c>
+      <c r="I238" t="s">
         <v>804</v>
       </c>
-      <c r="I238" t="s">
-        <v>338</v>
-      </c>
       <c r="J238" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="K238" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -11551,25 +11551,25 @@
         <v>14</v>
       </c>
       <c r="E239" t="s">
+        <v>337</v>
+      </c>
+      <c r="F239" t="s">
         <v>801</v>
       </c>
-      <c r="F239" t="s">
+      <c r="G239" t="s">
         <v>892</v>
       </c>
-      <c r="G239" t="s">
-        <v>803</v>
-      </c>
       <c r="H239" t="s">
+        <v>893</v>
+      </c>
+      <c r="I239" t="s">
         <v>804</v>
       </c>
-      <c r="I239" t="s">
-        <v>338</v>
-      </c>
       <c r="J239" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="K239" t="s">
-        <v>894</v>
+        <v>806</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -11589,22 +11589,22 @@
         <v>337</v>
       </c>
       <c r="F240" t="s">
+        <v>338</v>
+      </c>
+      <c r="G240" t="s">
         <v>898</v>
       </c>
-      <c r="G240" t="s">
+      <c r="H240" t="s">
         <v>899</v>
       </c>
-      <c r="H240" t="s">
+      <c r="I240" t="s">
         <v>900</v>
       </c>
-      <c r="I240" t="s">
-        <v>338</v>
-      </c>
       <c r="J240" t="s">
+        <v>339</v>
+      </c>
+      <c r="K240" t="s">
         <v>899</v>
-      </c>
-      <c r="K240" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -11624,22 +11624,22 @@
         <v>337</v>
       </c>
       <c r="F241" t="s">
+        <v>338</v>
+      </c>
+      <c r="G241" t="s">
         <v>898</v>
       </c>
-      <c r="G241" t="s">
+      <c r="H241" t="s">
         <v>899</v>
       </c>
-      <c r="H241" t="s">
+      <c r="I241" t="s">
         <v>900</v>
       </c>
-      <c r="I241" t="s">
-        <v>338</v>
-      </c>
       <c r="J241" t="s">
+        <v>339</v>
+      </c>
+      <c r="K241" t="s">
         <v>899</v>
-      </c>
-      <c r="K241" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -11659,22 +11659,22 @@
         <v>337</v>
       </c>
       <c r="F242" t="s">
+        <v>338</v>
+      </c>
+      <c r="G242" t="s">
         <v>898</v>
       </c>
-      <c r="G242" t="s">
+      <c r="H242" t="s">
         <v>899</v>
       </c>
-      <c r="H242" t="s">
+      <c r="I242" t="s">
         <v>900</v>
       </c>
-      <c r="I242" t="s">
-        <v>338</v>
-      </c>
       <c r="J242" t="s">
+        <v>339</v>
+      </c>
+      <c r="K242" t="s">
         <v>899</v>
-      </c>
-      <c r="K242" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -11694,22 +11694,22 @@
         <v>337</v>
       </c>
       <c r="F243" t="s">
+        <v>338</v>
+      </c>
+      <c r="G243" t="s">
         <v>898</v>
       </c>
-      <c r="G243" t="s">
+      <c r="H243" t="s">
         <v>899</v>
       </c>
-      <c r="H243" t="s">
+      <c r="I243" t="s">
         <v>900</v>
       </c>
-      <c r="I243" t="s">
-        <v>338</v>
-      </c>
       <c r="J243" t="s">
+        <v>339</v>
+      </c>
+      <c r="K243" t="s">
         <v>899</v>
-      </c>
-      <c r="K243" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -11729,22 +11729,22 @@
         <v>337</v>
       </c>
       <c r="F244" t="s">
+        <v>338</v>
+      </c>
+      <c r="G244" t="s">
         <v>898</v>
       </c>
-      <c r="G244" t="s">
+      <c r="H244" t="s">
         <v>899</v>
       </c>
-      <c r="H244" t="s">
+      <c r="I244" t="s">
         <v>900</v>
       </c>
-      <c r="I244" t="s">
-        <v>338</v>
-      </c>
       <c r="J244" t="s">
+        <v>339</v>
+      </c>
+      <c r="K244" t="s">
         <v>899</v>
-      </c>
-      <c r="K244" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -11764,22 +11764,22 @@
         <v>337</v>
       </c>
       <c r="F245" t="s">
+        <v>338</v>
+      </c>
+      <c r="G245" t="s">
         <v>898</v>
       </c>
-      <c r="G245" t="s">
+      <c r="H245" t="s">
         <v>899</v>
       </c>
-      <c r="H245" t="s">
+      <c r="I245" t="s">
         <v>900</v>
       </c>
-      <c r="I245" t="s">
-        <v>338</v>
-      </c>
       <c r="J245" t="s">
+        <v>339</v>
+      </c>
+      <c r="K245" t="s">
         <v>899</v>
-      </c>
-      <c r="K245" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -11793,25 +11793,25 @@
         <v>14</v>
       </c>
       <c r="E246" t="s">
+        <v>337</v>
+      </c>
+      <c r="F246" t="s">
         <v>533</v>
       </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
         <v>918</v>
       </c>
-      <c r="G246" t="s">
+      <c r="H246" t="s">
+        <v>919</v>
+      </c>
+      <c r="I246" t="s">
+        <v>900</v>
+      </c>
+      <c r="J246" t="s">
+        <v>920</v>
+      </c>
+      <c r="K246" t="s">
         <v>899</v>
-      </c>
-      <c r="H246" t="s">
-        <v>900</v>
-      </c>
-      <c r="I246" t="s">
-        <v>338</v>
-      </c>
-      <c r="J246" t="s">
-        <v>919</v>
-      </c>
-      <c r="K246" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11830,17 +11830,17 @@
       <c r="E247" t="s">
         <v>196</v>
       </c>
-      <c r="G247" t="s">
+      <c r="F247" t="s">
+        <v>197</v>
+      </c>
+      <c r="I247" t="s">
         <v>924</v>
       </c>
-      <c r="H247" t="s">
+      <c r="J247" t="s">
+        <v>198</v>
+      </c>
+      <c r="K247" t="s">
         <v>925</v>
-      </c>
-      <c r="I247" t="s">
-        <v>197</v>
-      </c>
-      <c r="K247" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -11859,17 +11859,17 @@
       <c r="E248" t="s">
         <v>196</v>
       </c>
-      <c r="G248" t="s">
+      <c r="F248" t="s">
+        <v>197</v>
+      </c>
+      <c r="I248" t="s">
         <v>924</v>
       </c>
-      <c r="H248" t="s">
+      <c r="J248" t="s">
+        <v>198</v>
+      </c>
+      <c r="K248" t="s">
         <v>925</v>
-      </c>
-      <c r="I248" t="s">
-        <v>197</v>
-      </c>
-      <c r="K248" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -11886,19 +11886,19 @@
         <v>14</v>
       </c>
       <c r="E249" t="s">
+        <v>196</v>
+      </c>
+      <c r="F249" t="s">
         <v>932</v>
       </c>
-      <c r="G249" t="s">
+      <c r="I249" t="s">
         <v>924</v>
       </c>
-      <c r="H249" t="s">
+      <c r="J249" t="s">
+        <v>933</v>
+      </c>
+      <c r="K249" t="s">
         <v>925</v>
-      </c>
-      <c r="I249" t="s">
-        <v>197</v>
-      </c>
-      <c r="K249" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -11917,17 +11917,17 @@
       <c r="E250" t="s">
         <v>196</v>
       </c>
-      <c r="G250" t="s">
+      <c r="F250" t="s">
+        <v>197</v>
+      </c>
+      <c r="I250" t="s">
         <v>924</v>
       </c>
-      <c r="H250" t="s">
+      <c r="J250" t="s">
+        <v>198</v>
+      </c>
+      <c r="K250" t="s">
         <v>925</v>
-      </c>
-      <c r="I250" t="s">
-        <v>197</v>
-      </c>
-      <c r="K250" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -11943,17 +11943,17 @@
       <c r="E251" t="s">
         <v>196</v>
       </c>
-      <c r="G251" t="s">
+      <c r="F251" t="s">
+        <v>197</v>
+      </c>
+      <c r="I251" t="s">
         <v>924</v>
       </c>
-      <c r="H251" t="s">
+      <c r="J251" t="s">
+        <v>198</v>
+      </c>
+      <c r="K251" t="s">
         <v>925</v>
-      </c>
-      <c r="I251" t="s">
-        <v>197</v>
-      </c>
-      <c r="K251" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -11972,17 +11972,17 @@
       <c r="E252" t="s">
         <v>196</v>
       </c>
-      <c r="G252" t="s">
+      <c r="F252" t="s">
+        <v>197</v>
+      </c>
+      <c r="I252" t="s">
         <v>924</v>
       </c>
-      <c r="H252" t="s">
+      <c r="J252" t="s">
+        <v>198</v>
+      </c>
+      <c r="K252" t="s">
         <v>925</v>
-      </c>
-      <c r="I252" t="s">
-        <v>197</v>
-      </c>
-      <c r="K252" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -11996,16 +11996,16 @@
         <v>14</v>
       </c>
       <c r="E253" t="s">
+        <v>337</v>
+      </c>
+      <c r="F253" t="s">
         <v>944</v>
       </c>
-      <c r="G253" t="s">
+      <c r="I253" t="s">
         <v>945</v>
       </c>
-      <c r="H253" t="s">
+      <c r="J253" t="s">
         <v>946</v>
-      </c>
-      <c r="I253" t="s">
-        <v>338</v>
       </c>
       <c r="K253" t="s">
         <v>947</v>
@@ -12025,19 +12025,19 @@
         <v>14</v>
       </c>
       <c r="E254" t="s">
+        <v>188</v>
+      </c>
+      <c r="F254" t="s">
         <v>454</v>
       </c>
-      <c r="G254" t="s">
+      <c r="I254" t="s">
         <v>945</v>
       </c>
-      <c r="H254" t="s">
-        <v>946</v>
-      </c>
-      <c r="I254" t="s">
-        <v>191</v>
+      <c r="J254" t="s">
+        <v>455</v>
       </c>
       <c r="K254" t="s">
-        <v>455</v>
+        <v>947</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -12054,19 +12054,19 @@
         <v>14</v>
       </c>
       <c r="E255" t="s">
+        <v>188</v>
+      </c>
+      <c r="F255" t="s">
         <v>954</v>
       </c>
-      <c r="G255" t="s">
+      <c r="I255" t="s">
         <v>945</v>
       </c>
-      <c r="H255" t="s">
-        <v>946</v>
-      </c>
-      <c r="I255" t="s">
-        <v>191</v>
+      <c r="J255" t="s">
+        <v>955</v>
       </c>
       <c r="K255" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -12083,19 +12083,19 @@
         <v>14</v>
       </c>
       <c r="E256" t="s">
+        <v>188</v>
+      </c>
+      <c r="F256" t="s">
         <v>954</v>
       </c>
-      <c r="G256" t="s">
+      <c r="I256" t="s">
         <v>945</v>
       </c>
-      <c r="H256" t="s">
-        <v>946</v>
-      </c>
-      <c r="I256" t="s">
-        <v>191</v>
+      <c r="J256" t="s">
+        <v>955</v>
       </c>
       <c r="K256" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -12112,19 +12112,19 @@
         <v>14</v>
       </c>
       <c r="E257" t="s">
+        <v>188</v>
+      </c>
+      <c r="F257" t="s">
         <v>954</v>
       </c>
-      <c r="G257" t="s">
+      <c r="I257" t="s">
         <v>945</v>
       </c>
-      <c r="H257" t="s">
-        <v>946</v>
-      </c>
-      <c r="I257" t="s">
-        <v>191</v>
+      <c r="J257" t="s">
+        <v>955</v>
       </c>
       <c r="K257" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -12141,19 +12141,19 @@
         <v>14</v>
       </c>
       <c r="E258" t="s">
+        <v>337</v>
+      </c>
+      <c r="F258" t="s">
         <v>705</v>
       </c>
-      <c r="G258" t="s">
+      <c r="I258" t="s">
         <v>945</v>
       </c>
-      <c r="H258" t="s">
-        <v>946</v>
-      </c>
-      <c r="I258" t="s">
-        <v>338</v>
+      <c r="J258" t="s">
+        <v>709</v>
       </c>
       <c r="K258" t="s">
-        <v>710</v>
+        <v>947</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -12170,19 +12170,19 @@
         <v>14</v>
       </c>
       <c r="E259" t="s">
+        <v>188</v>
+      </c>
+      <c r="F259" t="s">
         <v>954</v>
       </c>
-      <c r="G259" t="s">
+      <c r="I259" t="s">
         <v>945</v>
       </c>
-      <c r="H259" t="s">
-        <v>946</v>
-      </c>
-      <c r="I259" t="s">
-        <v>191</v>
+      <c r="J259" t="s">
+        <v>955</v>
       </c>
       <c r="K259" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -12201,17 +12201,17 @@
       <c r="E260" t="s">
         <v>337</v>
       </c>
-      <c r="G260" t="s">
+      <c r="F260" t="s">
+        <v>338</v>
+      </c>
+      <c r="I260" t="s">
         <v>945</v>
       </c>
-      <c r="H260" t="s">
-        <v>946</v>
-      </c>
-      <c r="I260" t="s">
-        <v>338</v>
+      <c r="J260" t="s">
+        <v>339</v>
       </c>
       <c r="K260" t="s">
-        <v>339</v>
+        <v>947</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -12228,19 +12228,19 @@
         <v>14</v>
       </c>
       <c r="E261" t="s">
+        <v>405</v>
+      </c>
+      <c r="F261" t="s">
         <v>973</v>
       </c>
-      <c r="G261" t="s">
+      <c r="I261" t="s">
         <v>945</v>
       </c>
-      <c r="H261" t="s">
-        <v>946</v>
-      </c>
-      <c r="I261" t="s">
-        <v>406</v>
+      <c r="J261" t="s">
+        <v>974</v>
       </c>
       <c r="K261" t="s">
-        <v>974</v>
+        <v>947</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -12259,17 +12259,17 @@
       <c r="E262" t="s">
         <v>337</v>
       </c>
-      <c r="G262" t="s">
+      <c r="F262" t="s">
+        <v>338</v>
+      </c>
+      <c r="I262" t="s">
         <v>945</v>
       </c>
-      <c r="H262" t="s">
-        <v>946</v>
-      </c>
-      <c r="I262" t="s">
-        <v>338</v>
+      <c r="J262" t="s">
+        <v>339</v>
       </c>
       <c r="K262" t="s">
-        <v>339</v>
+        <v>947</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -12286,19 +12286,19 @@
         <v>14</v>
       </c>
       <c r="E263" t="s">
+        <v>377</v>
+      </c>
+      <c r="F263" t="s">
         <v>981</v>
       </c>
-      <c r="G263" t="s">
+      <c r="I263" t="s">
         <v>945</v>
       </c>
-      <c r="H263" t="s">
-        <v>946</v>
-      </c>
-      <c r="I263" t="s">
-        <v>378</v>
+      <c r="J263" t="s">
+        <v>982</v>
       </c>
       <c r="K263" t="s">
-        <v>982</v>
+        <v>947</v>
       </c>
     </row>
     <row r="264" spans="1:11">
@@ -12317,17 +12317,17 @@
       <c r="E264" t="s">
         <v>58</v>
       </c>
-      <c r="G264" t="s">
+      <c r="F264" t="s">
+        <v>59</v>
+      </c>
+      <c r="I264" t="s">
         <v>945</v>
       </c>
-      <c r="H264" t="s">
-        <v>946</v>
-      </c>
-      <c r="I264" t="s">
-        <v>59</v>
+      <c r="J264" t="s">
+        <v>60</v>
       </c>
       <c r="K264" t="s">
-        <v>60</v>
+        <v>947</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -12346,17 +12346,17 @@
       <c r="E265" t="s">
         <v>15</v>
       </c>
-      <c r="G265" t="s">
+      <c r="F265" t="s">
+        <v>16</v>
+      </c>
+      <c r="I265" t="s">
         <v>945</v>
       </c>
-      <c r="H265" t="s">
-        <v>946</v>
-      </c>
-      <c r="I265" t="s">
-        <v>19</v>
+      <c r="J265" t="s">
+        <v>20</v>
       </c>
       <c r="K265" t="s">
-        <v>21</v>
+        <v>947</v>
       </c>
     </row>
     <row r="266" spans="1:11">
@@ -12373,19 +12373,19 @@
         <v>14</v>
       </c>
       <c r="E266" t="s">
+        <v>233</v>
+      </c>
+      <c r="F266" t="s">
         <v>992</v>
       </c>
-      <c r="G266" t="s">
+      <c r="I266" t="s">
         <v>945</v>
       </c>
-      <c r="H266" t="s">
-        <v>946</v>
-      </c>
-      <c r="I266" t="s">
-        <v>237</v>
+      <c r="J266" t="s">
+        <v>993</v>
       </c>
       <c r="K266" t="s">
-        <v>993</v>
+        <v>947</v>
       </c>
     </row>
     <row r="267" spans="1:11">
@@ -12402,19 +12402,19 @@
         <v>14</v>
       </c>
       <c r="E267" t="s">
+        <v>233</v>
+      </c>
+      <c r="F267" t="s">
         <v>243</v>
       </c>
-      <c r="G267" t="s">
+      <c r="I267" t="s">
         <v>997</v>
       </c>
-      <c r="H267" t="s">
+      <c r="J267" t="s">
+        <v>244</v>
+      </c>
+      <c r="K267" t="s">
         <v>998</v>
-      </c>
-      <c r="I267" t="s">
-        <v>237</v>
-      </c>
-      <c r="K267" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -12431,19 +12431,19 @@
         <v>14</v>
       </c>
       <c r="E268" t="s">
+        <v>377</v>
+      </c>
+      <c r="F268" t="s">
         <v>420</v>
       </c>
-      <c r="G268" t="s">
+      <c r="I268" t="s">
         <v>1002</v>
       </c>
-      <c r="H268" t="s">
+      <c r="J268" t="s">
+        <v>422</v>
+      </c>
+      <c r="K268" t="s">
         <v>1003</v>
-      </c>
-      <c r="I268" t="s">
-        <v>378</v>
-      </c>
-      <c r="K268" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -12460,19 +12460,19 @@
         <v>14</v>
       </c>
       <c r="E269" t="s">
+        <v>233</v>
+      </c>
+      <c r="F269" t="s">
         <v>243</v>
       </c>
-      <c r="G269" t="s">
+      <c r="I269" t="s">
         <v>1007</v>
       </c>
-      <c r="H269" t="s">
+      <c r="J269" t="s">
+        <v>244</v>
+      </c>
+      <c r="K269" t="s">
         <v>1008</v>
-      </c>
-      <c r="I269" t="s">
-        <v>237</v>
-      </c>
-      <c r="K269" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -12489,19 +12489,19 @@
         <v>14</v>
       </c>
       <c r="E270" t="s">
+        <v>233</v>
+      </c>
+      <c r="F270" t="s">
         <v>243</v>
       </c>
-      <c r="G270" t="s">
+      <c r="I270" t="s">
         <v>1007</v>
       </c>
-      <c r="H270" t="s">
+      <c r="J270" t="s">
+        <v>244</v>
+      </c>
+      <c r="K270" t="s">
         <v>1008</v>
-      </c>
-      <c r="I270" t="s">
-        <v>237</v>
-      </c>
-      <c r="K270" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -12518,16 +12518,16 @@
         <v>14</v>
       </c>
       <c r="E271" t="s">
+        <v>233</v>
+      </c>
+      <c r="F271" t="s">
         <v>1015</v>
       </c>
-      <c r="G271" t="s">
+      <c r="I271" t="s">
         <v>1016</v>
       </c>
-      <c r="H271" t="s">
+      <c r="J271" t="s">
         <v>1017</v>
-      </c>
-      <c r="I271" t="s">
-        <v>237</v>
       </c>
       <c r="K271" t="s">
         <v>1018</v>
@@ -12544,16 +12544,16 @@
         <v>14</v>
       </c>
       <c r="E272" t="s">
+        <v>233</v>
+      </c>
+      <c r="F272" t="s">
         <v>1015</v>
       </c>
-      <c r="G272" t="s">
+      <c r="I272" t="s">
         <v>1016</v>
       </c>
-      <c r="H272" t="s">
+      <c r="J272" t="s">
         <v>1017</v>
-      </c>
-      <c r="I272" t="s">
-        <v>237</v>
       </c>
       <c r="K272" t="s">
         <v>1018</v>
@@ -12573,16 +12573,16 @@
         <v>14</v>
       </c>
       <c r="E273" t="s">
+        <v>233</v>
+      </c>
+      <c r="F273" t="s">
         <v>1015</v>
       </c>
-      <c r="G273" t="s">
+      <c r="I273" t="s">
         <v>1016</v>
       </c>
-      <c r="H273" t="s">
+      <c r="J273" t="s">
         <v>1017</v>
-      </c>
-      <c r="I273" t="s">
-        <v>237</v>
       </c>
       <c r="K273" t="s">
         <v>1018</v>
@@ -12599,16 +12599,16 @@
         <v>14</v>
       </c>
       <c r="E274" t="s">
+        <v>233</v>
+      </c>
+      <c r="F274" t="s">
         <v>1015</v>
       </c>
-      <c r="G274" t="s">
+      <c r="I274" t="s">
         <v>1016</v>
       </c>
-      <c r="H274" t="s">
+      <c r="J274" t="s">
         <v>1017</v>
-      </c>
-      <c r="I274" t="s">
-        <v>237</v>
       </c>
       <c r="K274" t="s">
         <v>1018</v>
@@ -12628,16 +12628,16 @@
         <v>14</v>
       </c>
       <c r="E275" t="s">
+        <v>233</v>
+      </c>
+      <c r="F275" t="s">
         <v>1015</v>
       </c>
-      <c r="G275" t="s">
+      <c r="I275" t="s">
         <v>1016</v>
       </c>
-      <c r="H275" t="s">
+      <c r="J275" t="s">
         <v>1017</v>
-      </c>
-      <c r="I275" t="s">
-        <v>237</v>
       </c>
       <c r="K275" t="s">
         <v>1018</v>
@@ -12657,16 +12657,16 @@
         <v>14</v>
       </c>
       <c r="E276" t="s">
+        <v>233</v>
+      </c>
+      <c r="F276" t="s">
         <v>1015</v>
       </c>
-      <c r="G276" t="s">
+      <c r="I276" t="s">
         <v>1016</v>
       </c>
-      <c r="H276" t="s">
+      <c r="J276" t="s">
         <v>1017</v>
-      </c>
-      <c r="I276" t="s">
-        <v>237</v>
       </c>
       <c r="K276" t="s">
         <v>1018</v>
@@ -12686,16 +12686,16 @@
         <v>14</v>
       </c>
       <c r="E277" t="s">
+        <v>233</v>
+      </c>
+      <c r="F277" t="s">
         <v>1015</v>
       </c>
-      <c r="G277" t="s">
+      <c r="I277" t="s">
         <v>1016</v>
       </c>
-      <c r="H277" t="s">
+      <c r="J277" t="s">
         <v>1017</v>
-      </c>
-      <c r="I277" t="s">
-        <v>237</v>
       </c>
       <c r="K277" t="s">
         <v>1018</v>
@@ -12715,19 +12715,19 @@
         <v>14</v>
       </c>
       <c r="E278" t="s">
+        <v>377</v>
+      </c>
+      <c r="F278" t="s">
         <v>420</v>
       </c>
-      <c r="G278" t="s">
+      <c r="I278" t="s">
         <v>1038</v>
       </c>
-      <c r="H278" t="s">
+      <c r="J278" t="s">
+        <v>422</v>
+      </c>
+      <c r="K278" t="s">
         <v>1039</v>
-      </c>
-      <c r="I278" t="s">
-        <v>378</v>
-      </c>
-      <c r="K278" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -12744,19 +12744,19 @@
         <v>14</v>
       </c>
       <c r="E279" t="s">
+        <v>58</v>
+      </c>
+      <c r="F279" t="s">
         <v>92</v>
       </c>
-      <c r="G279" t="s">
+      <c r="I279" t="s">
         <v>1038</v>
       </c>
-      <c r="H279" t="s">
+      <c r="J279" t="s">
+        <v>96</v>
+      </c>
+      <c r="K279" t="s">
         <v>1039</v>
-      </c>
-      <c r="I279" t="s">
-        <v>59</v>
-      </c>
-      <c r="K279" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -12775,17 +12775,17 @@
       <c r="E280" t="s">
         <v>15</v>
       </c>
-      <c r="G280" t="s">
+      <c r="F280" t="s">
+        <v>16</v>
+      </c>
+      <c r="I280" t="s">
         <v>1038</v>
       </c>
-      <c r="H280" t="s">
+      <c r="J280" t="s">
+        <v>20</v>
+      </c>
+      <c r="K280" t="s">
         <v>1039</v>
-      </c>
-      <c r="I280" t="s">
-        <v>19</v>
-      </c>
-      <c r="K280" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="281" spans="1:11">
@@ -12802,19 +12802,19 @@
         <v>14</v>
       </c>
       <c r="E281" t="s">
+        <v>233</v>
+      </c>
+      <c r="F281" t="s">
         <v>352</v>
       </c>
-      <c r="G281" t="s">
+      <c r="I281" t="s">
         <v>1038</v>
       </c>
-      <c r="H281" t="s">
+      <c r="J281" t="s">
+        <v>353</v>
+      </c>
+      <c r="K281" t="s">
         <v>1039</v>
-      </c>
-      <c r="I281" t="s">
-        <v>237</v>
-      </c>
-      <c r="K281" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -12833,17 +12833,17 @@
       <c r="E282" t="s">
         <v>253</v>
       </c>
-      <c r="G282" t="s">
+      <c r="F282" t="s">
+        <v>254</v>
+      </c>
+      <c r="I282" t="s">
         <v>1038</v>
       </c>
-      <c r="H282" t="s">
+      <c r="J282" t="s">
+        <v>255</v>
+      </c>
+      <c r="K282" t="s">
         <v>1039</v>
-      </c>
-      <c r="I282" t="s">
-        <v>254</v>
-      </c>
-      <c r="K282" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -12860,19 +12860,19 @@
         <v>14</v>
       </c>
       <c r="E283" t="s">
+        <v>337</v>
+      </c>
+      <c r="F283" t="s">
         <v>801</v>
       </c>
-      <c r="G283" t="s">
+      <c r="I283" t="s">
         <v>1055</v>
       </c>
-      <c r="H283" t="s">
+      <c r="J283" t="s">
+        <v>894</v>
+      </c>
+      <c r="K283" t="s">
         <v>1056</v>
-      </c>
-      <c r="I283" t="s">
-        <v>338</v>
-      </c>
-      <c r="K283" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -12891,17 +12891,17 @@
       <c r="E284" t="s">
         <v>253</v>
       </c>
-      <c r="G284" t="s">
+      <c r="F284" t="s">
+        <v>254</v>
+      </c>
+      <c r="I284" t="s">
         <v>1060</v>
       </c>
-      <c r="H284" t="s">
+      <c r="J284" t="s">
+        <v>255</v>
+      </c>
+      <c r="K284" t="s">
         <v>1061</v>
-      </c>
-      <c r="I284" t="s">
-        <v>254</v>
-      </c>
-      <c r="K284" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -12915,19 +12915,19 @@
         <v>14</v>
       </c>
       <c r="E285" t="s">
+        <v>233</v>
+      </c>
+      <c r="F285" t="s">
         <v>352</v>
       </c>
-      <c r="G285" t="s">
+      <c r="I285" t="s">
         <v>1064</v>
       </c>
-      <c r="H285" t="s">
+      <c r="J285" t="s">
+        <v>353</v>
+      </c>
+      <c r="K285" t="s">
         <v>1065</v>
-      </c>
-      <c r="I285" t="s">
-        <v>237</v>
-      </c>
-      <c r="K285" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -12944,19 +12944,19 @@
         <v>14</v>
       </c>
       <c r="E286" t="s">
+        <v>377</v>
+      </c>
+      <c r="F286" t="s">
         <v>981</v>
       </c>
-      <c r="G286" t="s">
+      <c r="I286" t="s">
         <v>1069</v>
       </c>
-      <c r="H286" t="s">
+      <c r="J286" t="s">
+        <v>982</v>
+      </c>
+      <c r="K286" t="s">
         <v>1070</v>
-      </c>
-      <c r="I286" t="s">
-        <v>378</v>
-      </c>
-      <c r="K286" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -12973,19 +12973,19 @@
         <v>14</v>
       </c>
       <c r="E287" t="s">
+        <v>377</v>
+      </c>
+      <c r="F287" t="s">
         <v>981</v>
       </c>
-      <c r="G287" t="s">
+      <c r="I287" t="s">
         <v>1069</v>
       </c>
-      <c r="H287" t="s">
+      <c r="J287" t="s">
+        <v>982</v>
+      </c>
+      <c r="K287" t="s">
         <v>1070</v>
-      </c>
-      <c r="I287" t="s">
-        <v>378</v>
-      </c>
-      <c r="K287" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -13002,19 +13002,19 @@
         <v>14</v>
       </c>
       <c r="E288" t="s">
+        <v>15</v>
+      </c>
+      <c r="F288" t="s">
         <v>75</v>
       </c>
-      <c r="G288" t="s">
+      <c r="I288" t="s">
         <v>1069</v>
       </c>
-      <c r="H288" t="s">
+      <c r="J288" t="s">
+        <v>76</v>
+      </c>
+      <c r="K288" t="s">
         <v>1070</v>
-      </c>
-      <c r="I288" t="s">
-        <v>19</v>
-      </c>
-      <c r="K288" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -13033,17 +13033,17 @@
       <c r="E289" t="s">
         <v>58</v>
       </c>
-      <c r="G289" t="s">
+      <c r="F289" t="s">
+        <v>59</v>
+      </c>
+      <c r="I289" t="s">
         <v>1069</v>
       </c>
-      <c r="H289" t="s">
+      <c r="J289" t="s">
+        <v>60</v>
+      </c>
+      <c r="K289" t="s">
         <v>1070</v>
-      </c>
-      <c r="I289" t="s">
-        <v>59</v>
-      </c>
-      <c r="K289" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="290" spans="1:11">
@@ -13062,17 +13062,17 @@
       <c r="E290" t="s">
         <v>58</v>
       </c>
-      <c r="G290" t="s">
+      <c r="F290" t="s">
+        <v>59</v>
+      </c>
+      <c r="I290" t="s">
         <v>1069</v>
       </c>
-      <c r="H290" t="s">
+      <c r="J290" t="s">
+        <v>60</v>
+      </c>
+      <c r="K290" t="s">
         <v>1070</v>
-      </c>
-      <c r="I290" t="s">
-        <v>59</v>
-      </c>
-      <c r="K290" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -13089,19 +13089,19 @@
         <v>14</v>
       </c>
       <c r="E291" t="s">
+        <v>233</v>
+      </c>
+      <c r="F291" t="s">
         <v>352</v>
       </c>
-      <c r="G291" t="s">
+      <c r="I291" t="s">
         <v>1069</v>
       </c>
-      <c r="H291" t="s">
+      <c r="J291" t="s">
+        <v>353</v>
+      </c>
+      <c r="K291" t="s">
         <v>1070</v>
-      </c>
-      <c r="I291" t="s">
-        <v>237</v>
-      </c>
-      <c r="K291" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -13118,19 +13118,19 @@
         <v>14</v>
       </c>
       <c r="E292" t="s">
+        <v>233</v>
+      </c>
+      <c r="F292" t="s">
         <v>352</v>
       </c>
-      <c r="G292" t="s">
+      <c r="I292" t="s">
         <v>1069</v>
       </c>
-      <c r="H292" t="s">
+      <c r="J292" t="s">
+        <v>353</v>
+      </c>
+      <c r="K292" t="s">
         <v>1070</v>
-      </c>
-      <c r="I292" t="s">
-        <v>237</v>
-      </c>
-      <c r="K292" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -13147,19 +13147,19 @@
         <v>14</v>
       </c>
       <c r="E293" t="s">
+        <v>233</v>
+      </c>
+      <c r="F293" t="s">
         <v>352</v>
       </c>
-      <c r="G293" t="s">
+      <c r="I293" t="s">
         <v>1069</v>
       </c>
-      <c r="H293" t="s">
+      <c r="J293" t="s">
+        <v>353</v>
+      </c>
+      <c r="K293" t="s">
         <v>1070</v>
-      </c>
-      <c r="I293" t="s">
-        <v>237</v>
-      </c>
-      <c r="K293" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -13176,19 +13176,19 @@
         <v>14</v>
       </c>
       <c r="E294" t="s">
+        <v>233</v>
+      </c>
+      <c r="F294" t="s">
         <v>352</v>
       </c>
-      <c r="G294" t="s">
+      <c r="I294" t="s">
         <v>1069</v>
       </c>
-      <c r="H294" t="s">
+      <c r="J294" t="s">
+        <v>353</v>
+      </c>
+      <c r="K294" t="s">
         <v>1070</v>
-      </c>
-      <c r="I294" t="s">
-        <v>237</v>
-      </c>
-      <c r="K294" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -13205,19 +13205,19 @@
         <v>14</v>
       </c>
       <c r="E295" t="s">
+        <v>233</v>
+      </c>
+      <c r="F295" t="s">
         <v>352</v>
       </c>
-      <c r="G295" t="s">
+      <c r="I295" t="s">
         <v>1098</v>
       </c>
-      <c r="H295" t="s">
+      <c r="J295" t="s">
+        <v>353</v>
+      </c>
+      <c r="K295" t="s">
         <v>1099</v>
-      </c>
-      <c r="I295" t="s">
-        <v>237</v>
-      </c>
-      <c r="K295" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="296" spans="1:11">
@@ -13234,19 +13234,19 @@
         <v>14</v>
       </c>
       <c r="E296" t="s">
+        <v>233</v>
+      </c>
+      <c r="F296" t="s">
         <v>352</v>
       </c>
-      <c r="G296" t="s">
+      <c r="I296" t="s">
         <v>1098</v>
       </c>
-      <c r="H296" t="s">
+      <c r="J296" t="s">
+        <v>353</v>
+      </c>
+      <c r="K296" t="s">
         <v>1099</v>
-      </c>
-      <c r="I296" t="s">
-        <v>237</v>
-      </c>
-      <c r="K296" t="s">
-        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -28,27 +28,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -61,27 +61,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -91,12 +91,12 @@
     <t>Educational buildings, equipment, materials; subsidiary services to education (boarding facilities, staff housing); language training; colloquia, seminars, lectures, etc.</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Research and studies on education effectiveness, relevance and quality; systematic evaluation and monitoring.</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
@@ -130,18 +130,18 @@
     <t>Formal and non-formal primary education for children; all elementary and first cycle systematic instruction; provision of learning materials.</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07 - Health</t>
   </si>
   <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>Second cycle systematic instruction at junior level.</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -223,15 +223,15 @@
     <t>Second cycle systematic instruction at senior levels.</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Elementary vocational training and secondary level technical education; on-the job training; apprenticeships; including informal vocational training.</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
@@ -256,18 +256,18 @@
     <t>Degree and diploma programmes at universities, colleges and polytechnics; scholarships.</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -277,12 +277,12 @@
     <t>Professional-level vocational training programmes and in-service training.</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
@@ -292,24 +292,24 @@
     <t>Health sector policy, planning and programmes; aid to health ministries, public health administration; institution capacity building and advice; medical insurance programmes; including health system strengthening and health governance; unspecified health activities.</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -328,12 +328,12 @@
     <t>General medical research (excluding basic health research and research for prevention and control of NCDs (12382)).</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>Laboratories, specialised clinics and hospitals (including equipment and supplies); ambulances; dental services; medical rehabilitation. Excludes noncommunicable diseases (123xx).</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -367,12 +367,12 @@
     <t>Basic and primary health care programmes; paramedical and nursing care programmes; supply of drugs, medicines and vaccines related to basic health care; activities aimed at achieving universal health coverage.</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -382,12 +382,12 @@
     <t>District-level hospitals, clinics and dispensaries and related medical equipment; excluding specialised hospitals and clinics (12191).</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -460,12 +460,12 @@
     <t>Programmes for the prevention and control of NCDs which cannot be broken down into the codes below.</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -520,12 +520,12 @@
     <t>Population/development policies; demographic research/analysis; reproductive health research; unspecified population activities. (Use purpose code 15190 for data on migration and refugees. Use code 13096 for census work, vital registration and migration data collection.)</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -580,21 +580,21 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -604,15 +604,15 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>Large scale sewerage including trunk sewers and sewage pumping stations; domestic and industrial waste water treatment plants.</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>Municipal and industrial solid waste management, including hazardous and toxic waste; collection, disposal and treatment; landfill areas; composting and reuse.</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -715,27 +715,27 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Fiscal policy and planning; support to ministries of finance; strengthening financial and managerial accountability; public expenditure management; improving financial management systems; budget drafting; inter-governmental fiscal relations, public audit, public debt. (Use code 15114 for domestic revenue mobilisation and code 33120 for customs).</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
@@ -760,12 +760,12 @@
     <t>Decentralisation processes (including political, administrative and fiscal dimensions); intergovernmental relations and federalism; strengthening departments of regional and local government, regional and local authorities and their national associations. (Use specific sector codes for decentralisation of sector management and services.)</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
@@ -775,15 +775,15 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -859,12 +859,12 @@
     <t>Support to administration of developing countries' foreign aid (including triangular and south-south cooperation).</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -943,12 +943,12 @@
     <t>Judicial law and order sectors; policy development within ministries of justice or equivalents.</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
@@ -958,12 +958,12 @@
     <t>Police affairs and services.</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Fire-prevention and fire-fighting affairs and services.</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>Prisons</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
@@ -1027,15 +1027,15 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -1072,12 +1072,12 @@
     <t>Electoral management bodies and processes, election observation, voters' education. (Use code 15230 when in the context of an international peacekeeping operation.)</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -1099,12 +1099,12 @@
     <t>Activities that support free and uncensored flow of information on public issues; activities that increase the editorial and technical skills and the integrity of the print and broadcast media, e.g. training of journalists. (Use codes 22010-22040 for provision of equipment and capital assistance to media.)</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -1147,15 +1147,15 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -1192,12 +1192,12 @@
     <t>Collection, production, management and dissemination of statistics and data related to Government &amp; Civil Society. Includes macroeconomic statistics, government finance, fiscal and public sector statistics, support to development of administrative data infrastructure, civil society surveys.</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -1207,12 +1207,12 @@
     <t>Technical co-operation provided to parliament, government ministries, law enforcement agencies and the judiciary to assist review and reform of the security system to improve democratic governance and civilian control; technical co-operation provided to government to improve civilian oversight and democratic control of budgeting, management, accountability and auditing of security expenditure, including military budgets, as part of a public expenditure management programme; assistance to civil society to enhance its competence and capacity to scrutinise the security system so that it is managed in accordance with democratic norms and principles of accountability, transparency and good governance. [Other than in the context of an international peacekeeping operation (15230)].</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -1231,15 +1231,15 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02 - Defence</t>
   </si>
   <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -1276,18 +1276,18 @@
     <t>Social protection or social security strategies, legislation and administration; institution capacity building and advice; social security and other social schemes; support programmes, cash benefits, pensions and special programmes for older persons, orphans, persons with disabilities, children, mothers with newborns, those living in poverty, without jobs and other vulnerable groups; social dimensions of structural adjustment.</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Social protection schemes in the form of cash or in-kind benefits, including pensions, against the risks linked to old age.</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -1348,12 +1348,12 @@
     <t>Employment policy and planning; institution capacity building and advice; employment creation and income generation programmes; including activities specifically designed for the needs of vulnerable groups.</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
@@ -1363,12 +1363,12 @@
     <t>Housing sector policy, planning and programmes; excluding low-cost housing and slum clearance (16040).</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
@@ -1378,12 +1378,12 @@
     <t>Including slum clearance.</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -1402,15 +1402,15 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -1444,12 +1444,12 @@
     <t>Recreation and sport</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -1486,12 +1486,12 @@
     <t>Transport sector policy, planning and programmes; aid to transport ministries; institution capacity building and advice; unspecified transport; activities that combine road, rail, water and/or air transport. Includes prevention of road accidents. Whenever possible, report transport of goods under the sector of the good being transported.</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21011</t>
   </si>
   <si>
@@ -1528,12 +1528,12 @@
     <t>Road infrastructure, road vehicles; passenger road transport, motor passenger cars.</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -1615,12 +1615,12 @@
     <t>Whether or not related to transportation. Whenever possible, report storage projects under the sector of the resource being stored.</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>Communications sector policy, planning and programmes; institution capacity building and advice; including postal services development; unspecified communications activities.</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22011</t>
   </si>
   <si>
@@ -1684,12 +1684,12 @@
     <t>Radio and TV links, equipment; newspapers; printing and publishing.</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -1708,24 +1708,24 @@
     <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -1741,12 +1741,12 @@
     <t>Regulation of the energy sector, including wholesale and retail electricity provision.</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>Renewable energy generation programmes that cannot be attributed to one single technology (codes 23220 through 23280 below). Fuelwood/charcoal production should be included under forestry 31261.</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -1870,12 +1870,12 @@
     <t>Thermal power plants including when energy source cannot be determined; combined gas-coal power plants.</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -1933,12 +1933,12 @@
     <t>Electric power plants that make use of both non-renewable and renewable energy sources.</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
@@ -1948,12 +1948,12 @@
     <t>See note regarding ODA eligibility of nuclear energy.</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -1963,12 +1963,12 @@
     <t>Power plants which are designed to produce heat only.</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -2032,12 +2032,12 @@
     <t>Finance sector policy, planning and programmes; institution capacity building and advice; financial markets and systems.</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -2089,12 +2089,12 @@
     <t>Public sector policies and institution support to the business environment and investment climate, including business regulations, property rights, non-discrimination, investment promotion, competition policy, enterprises law, private-public partnerships.</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -2131,24 +2131,24 @@
     <t>Agricultural sector policy, planning and programmes; aid to agricultural ministries; institution capacity building and advice; unspecified agriculture.</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2311,15 +2311,15 @@
     <t>Forestry sector policy, planning and programmes; institution capacity building and advice; forest surveys; unspecified forestry and agro-forestry activities.</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -2368,15 +2368,15 @@
     <t>Fishing sector policy, planning and programmes; institution capacity building and advice; ocean and coastal fishing; marine and freshwater fish surveys and prospecting; fishing boats/equipment; unspecified fishing activities.</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -2419,24 +2419,24 @@
     <t>Industrial sector policy, planning and programmes; institution capacity building and advice; unspecified industrial activities; manufacturing of goods not specified below.</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2593,15 +2593,15 @@
     <t>Mineral and mining sector policy, planning and programmes; mining legislation, mining cadastre, mineral resources inventory, information systems, institution capacity building and advice; unspecified mineral resources exploitation.</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -2692,15 +2692,15 @@
     <t>Construction sector policy and planning; excluding construction activities within specific sectors (e.g., hospital or school construction).</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -2710,12 +2710,12 @@
     <t>Trade policy and planning; support to ministries and departments responsible for trade policy; trade-related legislation and regulatory reforms; policy analysis and implementation of multilateral trade agreements e.g. technical barriers to trade and sanitary and phytosanitary measures (TBT/SPS) except at regional level (see 33130); mainstreaming trade in national development strategies (e.g. poverty reduction strategy papers); wholesale/retail trade; unspecified trade and trade promotion activities.</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>330</t>
   </si>
   <si>
@@ -2770,15 +2770,15 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
-    <t>04.7.3 - Tourism (CS)</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -2788,12 +2788,12 @@
     <t>Environmental policy, laws, regulations and economic instruments; administrational institutions and practices; environmental and land use planning and decision-making procedures; seminars, meetings; miscellaneous conservation and protection measures not specified below.</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -2812,12 +2812,12 @@
     <t>Including natural reserves and actions in the surrounding areas; other measures to protect endangered or vulnerable species and their habitats (e.g. wetlands preservation).</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -2848,18 +2848,18 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -2878,12 +2878,12 @@
     <t>Urban development and planning; urban management, land information systems.</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -2935,12 +2935,12 @@
     <t>Disaster risk reduction activities if not sector specific. Comprises risk assessments, structural prevention measures (e.g. flood prevention infrastructure), preparedness measures (e.g. early warning systems) normative prevention measures (e.g. building codes, land-use planning), and risk transfer systems (e.g. insurance schemes, risk funds). Also includes building local and national capacities and supporting the establishment of efficient and sustainable national structures able to promote disaster risk reduction.</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
@@ -2959,12 +2959,12 @@
     <t>Short or longer term household food security programmes and activities that improve the access of households to nutritionally adequate diets (excluding any cash transfers within broader social welfare programmes that do not have a specific food security, food acquisition or nutrition focus which should be reported under code 16010).</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -2992,12 +2992,12 @@
     <t>When sector cannot be identified.</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -3007,12 +3007,12 @@
     <t>Unearmarked contributions to the government budget; support for the implementation of macroeconomic reforms (structural adjustment programmes, poverty reduction strategies); general programme assistance (when not allocable by sector).</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
@@ -3022,12 +3022,12 @@
     <t>Supply of edible human food under national or international programmes including transport costs, cash payments made for food supplies; project food assistance aid and food assistance aid for market sales when benefiting sector not specified. Excludes food security policy and administrative management (43071), household food security programmes (43072) and emergency food assistance aid (72040). Report as multilateral: i) food assistance aid by EU financed out of its budget and allocated pro rata to EU member countries; and ii) core contributions to the World Food Programme.</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
@@ -3037,12 +3037,12 @@
     <t>Capital goods and services; lines of credit.</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -3061,18 +3061,18 @@
     <t>Actions falling outside the code headings below.</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -3130,12 +3130,12 @@
     <t>Shelter, water, sanitation, education, health services including supply of medicines and malnutrition management, including medical nutrition management; supply of other nonfood relief items (including cash and voucher delivery modalities) for the benefit of crisisaffected people, including refugees and internally displaced people in developing countries, Includes assistance delivered by or coordinated by international civil protection units in the immediate aftermath of a disaster (in-kind assistance, deployment of specially-equipped teams, logistics and transportation, or assessment and coordination by experts sent to the field). Also includes measures to promote and protect the safety, well-being, dignity and integrity of crisis-affected people including refugees and internally displaced persons in developing countries. (Activities designed to protect the security of persons or properties through the use or display of force are not reportable as ODA.)</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72011</t>
   </si>
   <si>
@@ -3181,12 +3181,12 @@
     <t>Social and economic rehabilitation in the aftermath of emergencies to facilitate recovery and resilience building and enable populations to restore their livelihoods in the wake of an emergency situation (e.g. trauma counselling and treatment, employment programmes). Includes infrastructure necessary for the delivery of humanitarian aid; restoring pre-existing essential infrastructure and facilities (e.g. water and sanitation, shelter, health care services, education); rehabilitation of basic agricultural inputs and livestock. Excludes longer-term reconstruction ('build back better') which is reportable against relevant sectors.</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
@@ -3196,24 +3196,24 @@
     <t>Building the responsiveness, capability and capacity of international, regional and national humanitarian actors to disasters. Support to the institutional capacities of national and local government, specialised humanitarian bodies, and civil society organisations to anticipate, respond and recover from the impact of potential, imminent and current hazardous events and emergency situations that pose humanitarian threats and could call for a humanitarian response. This includes risk analysis and assessment, mitigation, preparedness, such as stockpiling of emergency items and training and capacity building aimed to increase the speed and effectiveness of lifesaving assistance delivered in the occurrence of crisis.</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
@@ -3223,12 +3223,12 @@
     <t>Costs incurred in donor countries for basic assistance to asylum seekers and refugees from developing countries, up to 12 months, when costs cannot be disaggregated. See section II.6 and Annex 17.</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>93011</t>
   </si>
   <si>
@@ -3310,10 +3310,10 @@
     <t>Contributions to general development of the recipient should be included under programme assistance (51010).</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -3741,10 +3741,10 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
@@ -3756,10 +3756,10 @@
         <v>19</v>
       </c>
       <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
         <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3811,10 +3811,10 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
@@ -3826,10 +3826,10 @@
         <v>19</v>
       </c>
       <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
         <v>34</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3846,25 +3846,25 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
         <v>19</v>
       </c>
       <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
         <v>41</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3884,13 +3884,13 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
         <v>19</v>
@@ -3916,25 +3916,25 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
       </c>
       <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
         <v>41</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3951,25 +3951,25 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
       </c>
       <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s">
         <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3986,25 +3986,25 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
       </c>
       <c r="J10" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4024,22 +4024,22 @@
         <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
       </c>
       <c r="J11" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" t="s">
         <v>60</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4056,25 +4056,25 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
         <v>65</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4091,25 +4091,25 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
         <v>19</v>
       </c>
       <c r="J13" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4126,25 +4126,25 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
         <v>19</v>
       </c>
       <c r="J14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" t="s">
         <v>76</v>
-      </c>
-      <c r="K14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4161,25 +4161,25 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
         <v>19</v>
       </c>
       <c r="J15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" t="s">
         <v>83</v>
-      </c>
-      <c r="K15" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4196,25 +4196,25 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
         <v>19</v>
       </c>
       <c r="J16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" t="s">
         <v>88</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4231,22 +4231,22 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="K17" t="s">
         <v>97</v>
@@ -4266,22 +4266,22 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J18" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="K18" t="s">
         <v>97</v>
@@ -4301,25 +4301,25 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J19" t="s">
+        <v>59</v>
+      </c>
+      <c r="K19" t="s">
         <v>105</v>
-      </c>
-      <c r="K19" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4336,25 +4336,25 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="F20" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J20" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" t="s">
         <v>110</v>
-      </c>
-      <c r="K20" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4371,22 +4371,22 @@
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J21" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="K21" t="s">
         <v>97</v>
@@ -4409,22 +4409,22 @@
         <v>58</v>
       </c>
       <c r="F22" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22" t="s">
+        <v>118</v>
+      </c>
+      <c r="H22" t="s">
+        <v>95</v>
+      </c>
+      <c r="I22" t="s">
+        <v>96</v>
+      </c>
+      <c r="J22" t="s">
         <v>59</v>
       </c>
-      <c r="G22" t="s">
-        <v>117</v>
-      </c>
-      <c r="H22" t="s">
-        <v>118</v>
-      </c>
-      <c r="I22" t="s">
-        <v>95</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>60</v>
-      </c>
-      <c r="K22" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4441,25 +4441,25 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H23" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J23" t="s">
+        <v>59</v>
+      </c>
+      <c r="K23" t="s">
         <v>123</v>
-      </c>
-      <c r="K23" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4479,22 +4479,22 @@
         <v>58</v>
       </c>
       <c r="F24" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" t="s">
+        <v>118</v>
+      </c>
+      <c r="H24" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" t="s">
+        <v>96</v>
+      </c>
+      <c r="J24" t="s">
         <v>59</v>
       </c>
-      <c r="G24" t="s">
-        <v>117</v>
-      </c>
-      <c r="H24" t="s">
-        <v>118</v>
-      </c>
-      <c r="I24" t="s">
-        <v>95</v>
-      </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>60</v>
-      </c>
-      <c r="K24" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4514,22 +4514,22 @@
         <v>58</v>
       </c>
       <c r="F25" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25" t="s">
+        <v>118</v>
+      </c>
+      <c r="H25" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" t="s">
+        <v>96</v>
+      </c>
+      <c r="J25" t="s">
         <v>59</v>
       </c>
-      <c r="G25" t="s">
-        <v>117</v>
-      </c>
-      <c r="H25" t="s">
-        <v>118</v>
-      </c>
-      <c r="I25" t="s">
-        <v>95</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>60</v>
-      </c>
-      <c r="K25" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4549,22 +4549,22 @@
         <v>58</v>
       </c>
       <c r="F26" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" t="s">
+        <v>118</v>
+      </c>
+      <c r="H26" t="s">
+        <v>95</v>
+      </c>
+      <c r="I26" t="s">
+        <v>96</v>
+      </c>
+      <c r="J26" t="s">
         <v>59</v>
       </c>
-      <c r="G26" t="s">
-        <v>117</v>
-      </c>
-      <c r="H26" t="s">
-        <v>118</v>
-      </c>
-      <c r="I26" t="s">
-        <v>95</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>60</v>
-      </c>
-      <c r="K26" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4584,22 +4584,22 @@
         <v>58</v>
       </c>
       <c r="F27" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27" t="s">
+        <v>118</v>
+      </c>
+      <c r="H27" t="s">
+        <v>95</v>
+      </c>
+      <c r="I27" t="s">
+        <v>96</v>
+      </c>
+      <c r="J27" t="s">
         <v>59</v>
       </c>
-      <c r="G27" t="s">
-        <v>117</v>
-      </c>
-      <c r="H27" t="s">
-        <v>118</v>
-      </c>
-      <c r="I27" t="s">
-        <v>95</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>60</v>
-      </c>
-      <c r="K27" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4619,22 +4619,22 @@
         <v>58</v>
       </c>
       <c r="F28" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" t="s">
+        <v>118</v>
+      </c>
+      <c r="H28" t="s">
+        <v>95</v>
+      </c>
+      <c r="I28" t="s">
+        <v>96</v>
+      </c>
+      <c r="J28" t="s">
         <v>59</v>
       </c>
-      <c r="G28" t="s">
-        <v>117</v>
-      </c>
-      <c r="H28" t="s">
-        <v>118</v>
-      </c>
-      <c r="I28" t="s">
-        <v>95</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>60</v>
-      </c>
-      <c r="K28" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4654,22 +4654,22 @@
         <v>58</v>
       </c>
       <c r="F29" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" t="s">
+        <v>118</v>
+      </c>
+      <c r="H29" t="s">
+        <v>95</v>
+      </c>
+      <c r="I29" t="s">
+        <v>96</v>
+      </c>
+      <c r="J29" t="s">
         <v>59</v>
       </c>
-      <c r="G29" t="s">
-        <v>117</v>
-      </c>
-      <c r="H29" t="s">
-        <v>118</v>
-      </c>
-      <c r="I29" t="s">
-        <v>95</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>60</v>
-      </c>
-      <c r="K29" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4686,22 +4686,22 @@
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="G30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H30" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J30" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="K30" t="s">
         <v>97</v>
@@ -4724,22 +4724,22 @@
         <v>58</v>
       </c>
       <c r="F31" t="s">
+        <v>148</v>
+      </c>
+      <c r="G31" t="s">
+        <v>149</v>
+      </c>
+      <c r="H31" t="s">
+        <v>95</v>
+      </c>
+      <c r="I31" t="s">
+        <v>96</v>
+      </c>
+      <c r="J31" t="s">
         <v>59</v>
       </c>
-      <c r="G31" t="s">
-        <v>148</v>
-      </c>
-      <c r="H31" t="s">
-        <v>149</v>
-      </c>
-      <c r="I31" t="s">
-        <v>95</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>60</v>
-      </c>
-      <c r="K31" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4759,22 +4759,22 @@
         <v>58</v>
       </c>
       <c r="F32" t="s">
+        <v>148</v>
+      </c>
+      <c r="G32" t="s">
+        <v>149</v>
+      </c>
+      <c r="H32" t="s">
+        <v>95</v>
+      </c>
+      <c r="I32" t="s">
+        <v>96</v>
+      </c>
+      <c r="J32" t="s">
         <v>59</v>
       </c>
-      <c r="G32" t="s">
-        <v>148</v>
-      </c>
-      <c r="H32" t="s">
-        <v>149</v>
-      </c>
-      <c r="I32" t="s">
-        <v>95</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>60</v>
-      </c>
-      <c r="K32" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4794,22 +4794,22 @@
         <v>58</v>
       </c>
       <c r="F33" t="s">
+        <v>148</v>
+      </c>
+      <c r="G33" t="s">
+        <v>149</v>
+      </c>
+      <c r="H33" t="s">
+        <v>95</v>
+      </c>
+      <c r="I33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J33" t="s">
         <v>59</v>
       </c>
-      <c r="G33" t="s">
-        <v>148</v>
-      </c>
-      <c r="H33" t="s">
-        <v>149</v>
-      </c>
-      <c r="I33" t="s">
-        <v>95</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>60</v>
-      </c>
-      <c r="K33" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4829,22 +4829,22 @@
         <v>58</v>
       </c>
       <c r="F34" t="s">
+        <v>148</v>
+      </c>
+      <c r="G34" t="s">
+        <v>149</v>
+      </c>
+      <c r="H34" t="s">
+        <v>95</v>
+      </c>
+      <c r="I34" t="s">
+        <v>96</v>
+      </c>
+      <c r="J34" t="s">
         <v>59</v>
       </c>
-      <c r="G34" t="s">
-        <v>148</v>
-      </c>
-      <c r="H34" t="s">
-        <v>149</v>
-      </c>
-      <c r="I34" t="s">
-        <v>95</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>60</v>
-      </c>
-      <c r="K34" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4864,22 +4864,22 @@
         <v>58</v>
       </c>
       <c r="F35" t="s">
+        <v>148</v>
+      </c>
+      <c r="G35" t="s">
+        <v>149</v>
+      </c>
+      <c r="H35" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" t="s">
         <v>59</v>
       </c>
-      <c r="G35" t="s">
-        <v>148</v>
-      </c>
-      <c r="H35" t="s">
-        <v>149</v>
-      </c>
-      <c r="I35" t="s">
-        <v>95</v>
-      </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>60</v>
-      </c>
-      <c r="K35" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4896,25 +4896,25 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="F36" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="G36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H36" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="I36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J36" t="s">
+        <v>59</v>
+      </c>
+      <c r="K36" t="s">
         <v>105</v>
-      </c>
-      <c r="K36" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4933,17 +4933,17 @@
       <c r="E37" t="s">
         <v>58</v>
       </c>
-      <c r="F37" t="s">
+      <c r="H37" t="s">
+        <v>168</v>
+      </c>
+      <c r="I37" t="s">
+        <v>169</v>
+      </c>
+      <c r="J37" t="s">
         <v>59</v>
       </c>
-      <c r="I37" t="s">
-        <v>168</v>
-      </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>60</v>
-      </c>
-      <c r="K37" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4962,17 +4962,17 @@
       <c r="E38" t="s">
         <v>58</v>
       </c>
-      <c r="F38" t="s">
+      <c r="H38" t="s">
+        <v>168</v>
+      </c>
+      <c r="I38" t="s">
+        <v>169</v>
+      </c>
+      <c r="J38" t="s">
         <v>59</v>
       </c>
-      <c r="I38" t="s">
-        <v>168</v>
-      </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>60</v>
-      </c>
-      <c r="K38" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4991,17 +4991,17 @@
       <c r="E39" t="s">
         <v>58</v>
       </c>
-      <c r="F39" t="s">
+      <c r="H39" t="s">
+        <v>168</v>
+      </c>
+      <c r="I39" t="s">
+        <v>169</v>
+      </c>
+      <c r="J39" t="s">
         <v>59</v>
       </c>
-      <c r="I39" t="s">
-        <v>168</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>60</v>
-      </c>
-      <c r="K39" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5020,17 +5020,17 @@
       <c r="E40" t="s">
         <v>58</v>
       </c>
-      <c r="F40" t="s">
+      <c r="H40" t="s">
+        <v>168</v>
+      </c>
+      <c r="I40" t="s">
+        <v>169</v>
+      </c>
+      <c r="J40" t="s">
         <v>59</v>
       </c>
-      <c r="I40" t="s">
-        <v>168</v>
-      </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>60</v>
-      </c>
-      <c r="K40" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5047,19 +5047,19 @@
         <v>14</v>
       </c>
       <c r="E41" t="s">
-        <v>58</v>
-      </c>
-      <c r="F41" t="s">
         <v>92</v>
       </c>
+      <c r="H41" t="s">
+        <v>168</v>
+      </c>
       <c r="I41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J41" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="K41" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5076,19 +5076,19 @@
         <v>14</v>
       </c>
       <c r="E42" t="s">
-        <v>58</v>
-      </c>
-      <c r="F42" t="s">
         <v>104</v>
       </c>
+      <c r="H42" t="s">
+        <v>168</v>
+      </c>
       <c r="I42" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J42" t="s">
+        <v>59</v>
+      </c>
+      <c r="K42" t="s">
         <v>105</v>
-      </c>
-      <c r="K42" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5107,7 +5107,7 @@
       <c r="E43" t="s">
         <v>188</v>
       </c>
-      <c r="F43" t="s">
+      <c r="H43" t="s">
         <v>189</v>
       </c>
       <c r="I43" t="s">
@@ -5136,17 +5136,17 @@
       <c r="E44" t="s">
         <v>196</v>
       </c>
-      <c r="F44" t="s">
-        <v>197</v>
+      <c r="H44" t="s">
+        <v>189</v>
       </c>
       <c r="I44" t="s">
         <v>190</v>
       </c>
       <c r="J44" t="s">
+        <v>197</v>
+      </c>
+      <c r="K44" t="s">
         <v>198</v>
-      </c>
-      <c r="K44" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5165,7 +5165,7 @@
       <c r="E45" t="s">
         <v>188</v>
       </c>
-      <c r="F45" t="s">
+      <c r="H45" t="s">
         <v>189</v>
       </c>
       <c r="I45" t="s">
@@ -5194,7 +5194,7 @@
       <c r="E46" t="s">
         <v>188</v>
       </c>
-      <c r="F46" t="s">
+      <c r="H46" t="s">
         <v>189</v>
       </c>
       <c r="I46" t="s">
@@ -5221,19 +5221,19 @@
         <v>14</v>
       </c>
       <c r="E47" t="s">
-        <v>196</v>
-      </c>
-      <c r="F47" t="s">
         <v>208</v>
+      </c>
+      <c r="H47" t="s">
+        <v>189</v>
       </c>
       <c r="I47" t="s">
         <v>190</v>
       </c>
       <c r="J47" t="s">
+        <v>197</v>
+      </c>
+      <c r="K47" t="s">
         <v>209</v>
-      </c>
-      <c r="K47" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5252,7 +5252,7 @@
       <c r="E48" t="s">
         <v>188</v>
       </c>
-      <c r="F48" t="s">
+      <c r="H48" t="s">
         <v>189</v>
       </c>
       <c r="I48" t="s">
@@ -5281,7 +5281,7 @@
       <c r="E49" t="s">
         <v>188</v>
       </c>
-      <c r="F49" t="s">
+      <c r="H49" t="s">
         <v>189</v>
       </c>
       <c r="I49" t="s">
@@ -5308,19 +5308,19 @@
         <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>196</v>
-      </c>
-      <c r="F50" t="s">
         <v>208</v>
+      </c>
+      <c r="H50" t="s">
+        <v>189</v>
       </c>
       <c r="I50" t="s">
         <v>190</v>
       </c>
       <c r="J50" t="s">
+        <v>197</v>
+      </c>
+      <c r="K50" t="s">
         <v>209</v>
-      </c>
-      <c r="K50" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5339,7 +5339,7 @@
       <c r="E51" t="s">
         <v>188</v>
       </c>
-      <c r="F51" t="s">
+      <c r="H51" t="s">
         <v>189</v>
       </c>
       <c r="I51" t="s">
@@ -5366,19 +5366,19 @@
         <v>14</v>
       </c>
       <c r="E52" t="s">
-        <v>196</v>
-      </c>
-      <c r="F52" t="s">
         <v>225</v>
+      </c>
+      <c r="H52" t="s">
+        <v>189</v>
       </c>
       <c r="I52" t="s">
         <v>190</v>
       </c>
       <c r="J52" t="s">
+        <v>197</v>
+      </c>
+      <c r="K52" t="s">
         <v>226</v>
-      </c>
-      <c r="K52" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5397,8 +5397,8 @@
       <c r="E53" t="s">
         <v>15</v>
       </c>
-      <c r="F53" t="s">
-        <v>16</v>
+      <c r="H53" t="s">
+        <v>189</v>
       </c>
       <c r="I53" t="s">
         <v>190</v>
@@ -5407,7 +5407,7 @@
         <v>20</v>
       </c>
       <c r="K53" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5459,10 +5459,10 @@
         <v>14</v>
       </c>
       <c r="E55" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F55" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G55" t="s">
         <v>235</v>
@@ -5474,10 +5474,10 @@
         <v>237</v>
       </c>
       <c r="J55" t="s">
+        <v>238</v>
+      </c>
+      <c r="K55" t="s">
         <v>244</v>
-      </c>
-      <c r="K55" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -5494,10 +5494,10 @@
         <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F56" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G56" t="s">
         <v>235</v>
@@ -5509,10 +5509,10 @@
         <v>237</v>
       </c>
       <c r="J56" t="s">
+        <v>238</v>
+      </c>
+      <c r="K56" t="s">
         <v>249</v>
-      </c>
-      <c r="K56" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -5532,7 +5532,7 @@
         <v>253</v>
       </c>
       <c r="F57" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="G57" t="s">
         <v>235</v>
@@ -5544,10 +5544,10 @@
         <v>237</v>
       </c>
       <c r="J57" t="s">
+        <v>254</v>
+      </c>
+      <c r="K57" t="s">
         <v>255</v>
-      </c>
-      <c r="K57" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5564,10 +5564,10 @@
         <v>14</v>
       </c>
       <c r="E58" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F58" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G58" t="s">
         <v>235</v>
@@ -5579,10 +5579,10 @@
         <v>237</v>
       </c>
       <c r="J58" t="s">
+        <v>238</v>
+      </c>
+      <c r="K58" t="s">
         <v>244</v>
-      </c>
-      <c r="K58" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5599,10 +5599,10 @@
         <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F59" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G59" t="s">
         <v>235</v>
@@ -5614,10 +5614,10 @@
         <v>237</v>
       </c>
       <c r="J59" t="s">
+        <v>238</v>
+      </c>
+      <c r="K59" t="s">
         <v>244</v>
-      </c>
-      <c r="K59" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5634,10 +5634,10 @@
         <v>14</v>
       </c>
       <c r="E60" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F60" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G60" t="s">
         <v>235</v>
@@ -5649,10 +5649,10 @@
         <v>237</v>
       </c>
       <c r="J60" t="s">
+        <v>238</v>
+      </c>
+      <c r="K60" t="s">
         <v>244</v>
-      </c>
-      <c r="K60" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -5669,10 +5669,10 @@
         <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F61" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G61" t="s">
         <v>235</v>
@@ -5684,10 +5684,10 @@
         <v>237</v>
       </c>
       <c r="J61" t="s">
+        <v>238</v>
+      </c>
+      <c r="K61" t="s">
         <v>244</v>
-      </c>
-      <c r="K61" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -5704,10 +5704,10 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F62" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G62" t="s">
         <v>235</v>
@@ -5719,10 +5719,10 @@
         <v>237</v>
       </c>
       <c r="J62" t="s">
+        <v>238</v>
+      </c>
+      <c r="K62" t="s">
         <v>244</v>
-      </c>
-      <c r="K62" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -5739,10 +5739,10 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="F63" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G63" t="s">
         <v>235</v>
@@ -5754,10 +5754,10 @@
         <v>237</v>
       </c>
       <c r="J63" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="K63" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -5774,10 +5774,10 @@
         <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="F64" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G64" t="s">
         <v>235</v>
@@ -5789,10 +5789,10 @@
         <v>237</v>
       </c>
       <c r="J64" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="K64" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -5809,10 +5809,10 @@
         <v>14</v>
       </c>
       <c r="E65" t="s">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="F65" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="G65" t="s">
         <v>235</v>
@@ -5824,10 +5824,10 @@
         <v>237</v>
       </c>
       <c r="J65" t="s">
+        <v>238</v>
+      </c>
+      <c r="K65" t="s">
         <v>282</v>
-      </c>
-      <c r="K65" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5879,10 +5879,10 @@
         <v>14</v>
       </c>
       <c r="E67" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F67" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G67" t="s">
         <v>235</v>
@@ -5894,10 +5894,10 @@
         <v>237</v>
       </c>
       <c r="J67" t="s">
+        <v>238</v>
+      </c>
+      <c r="K67" t="s">
         <v>244</v>
-      </c>
-      <c r="K67" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5914,7 +5914,7 @@
         <v>14</v>
       </c>
       <c r="E68" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="F68" t="s">
         <v>234</v>
@@ -5929,7 +5929,7 @@
         <v>237</v>
       </c>
       <c r="J68" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="K68" t="s">
         <v>239</v>
@@ -5949,7 +5949,7 @@
         <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="F69" t="s">
         <v>234</v>
@@ -5964,7 +5964,7 @@
         <v>237</v>
       </c>
       <c r="J69" t="s">
-        <v>296</v>
+        <v>238</v>
       </c>
       <c r="K69" t="s">
         <v>239</v>
@@ -5984,10 +5984,10 @@
         <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F70" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G70" t="s">
         <v>235</v>
@@ -5999,10 +5999,10 @@
         <v>237</v>
       </c>
       <c r="J70" t="s">
+        <v>238</v>
+      </c>
+      <c r="K70" t="s">
         <v>249</v>
-      </c>
-      <c r="K70" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -6019,10 +6019,10 @@
         <v>14</v>
       </c>
       <c r="E71" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F71" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G71" t="s">
         <v>235</v>
@@ -6034,10 +6034,10 @@
         <v>237</v>
       </c>
       <c r="J71" t="s">
+        <v>238</v>
+      </c>
+      <c r="K71" t="s">
         <v>249</v>
-      </c>
-      <c r="K71" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6089,10 +6089,10 @@
         <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="F73" t="s">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="G73" t="s">
         <v>235</v>
@@ -6104,10 +6104,10 @@
         <v>237</v>
       </c>
       <c r="J73" t="s">
+        <v>254</v>
+      </c>
+      <c r="K73" t="s">
         <v>310</v>
-      </c>
-      <c r="K73" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6124,10 +6124,10 @@
         <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>253</v>
+        <v>314</v>
       </c>
       <c r="F74" t="s">
-        <v>314</v>
+        <v>234</v>
       </c>
       <c r="G74" t="s">
         <v>235</v>
@@ -6139,10 +6139,10 @@
         <v>237</v>
       </c>
       <c r="J74" t="s">
+        <v>254</v>
+      </c>
+      <c r="K74" t="s">
         <v>315</v>
-      </c>
-      <c r="K74" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6159,10 +6159,10 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>253</v>
+        <v>319</v>
       </c>
       <c r="F75" t="s">
-        <v>319</v>
+        <v>234</v>
       </c>
       <c r="G75" t="s">
         <v>235</v>
@@ -6174,10 +6174,10 @@
         <v>237</v>
       </c>
       <c r="J75" t="s">
+        <v>254</v>
+      </c>
+      <c r="K75" t="s">
         <v>320</v>
-      </c>
-      <c r="K75" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6194,10 +6194,10 @@
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="F76" t="s">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="G76" t="s">
         <v>235</v>
@@ -6209,10 +6209,10 @@
         <v>237</v>
       </c>
       <c r="J76" t="s">
+        <v>254</v>
+      </c>
+      <c r="K76" t="s">
         <v>310</v>
-      </c>
-      <c r="K76" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -6229,10 +6229,10 @@
         <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="F77" t="s">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="G77" t="s">
         <v>235</v>
@@ -6244,10 +6244,10 @@
         <v>237</v>
       </c>
       <c r="J77" t="s">
+        <v>254</v>
+      </c>
+      <c r="K77" t="s">
         <v>310</v>
-      </c>
-      <c r="K77" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -6264,10 +6264,10 @@
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>253</v>
+        <v>314</v>
       </c>
       <c r="F78" t="s">
-        <v>314</v>
+        <v>234</v>
       </c>
       <c r="G78" t="s">
         <v>235</v>
@@ -6279,10 +6279,10 @@
         <v>237</v>
       </c>
       <c r="J78" t="s">
+        <v>254</v>
+      </c>
+      <c r="K78" t="s">
         <v>315</v>
-      </c>
-      <c r="K78" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -6296,10 +6296,10 @@
         <v>14</v>
       </c>
       <c r="E79" t="s">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="F79" t="s">
-        <v>332</v>
+        <v>234</v>
       </c>
       <c r="G79" t="s">
         <v>235</v>
@@ -6311,10 +6311,10 @@
         <v>237</v>
       </c>
       <c r="J79" t="s">
+        <v>254</v>
+      </c>
+      <c r="K79" t="s">
         <v>333</v>
-      </c>
-      <c r="K79" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -6334,7 +6334,7 @@
         <v>337</v>
       </c>
       <c r="F80" t="s">
-        <v>338</v>
+        <v>234</v>
       </c>
       <c r="G80" t="s">
         <v>235</v>
@@ -6346,10 +6346,10 @@
         <v>237</v>
       </c>
       <c r="J80" t="s">
+        <v>338</v>
+      </c>
+      <c r="K80" t="s">
         <v>339</v>
-      </c>
-      <c r="K80" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -6369,7 +6369,7 @@
         <v>337</v>
       </c>
       <c r="F81" t="s">
-        <v>338</v>
+        <v>234</v>
       </c>
       <c r="G81" t="s">
         <v>235</v>
@@ -6381,10 +6381,10 @@
         <v>237</v>
       </c>
       <c r="J81" t="s">
+        <v>338</v>
+      </c>
+      <c r="K81" t="s">
         <v>339</v>
-      </c>
-      <c r="K81" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -6404,7 +6404,7 @@
         <v>337</v>
       </c>
       <c r="F82" t="s">
-        <v>338</v>
+        <v>234</v>
       </c>
       <c r="G82" t="s">
         <v>235</v>
@@ -6416,10 +6416,10 @@
         <v>237</v>
       </c>
       <c r="J82" t="s">
+        <v>338</v>
+      </c>
+      <c r="K82" t="s">
         <v>339</v>
-      </c>
-      <c r="K82" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -6436,7 +6436,7 @@
         <v>14</v>
       </c>
       <c r="E83" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="F83" t="s">
         <v>234</v>
@@ -6451,7 +6451,7 @@
         <v>237</v>
       </c>
       <c r="J83" t="s">
-        <v>296</v>
+        <v>238</v>
       </c>
       <c r="K83" t="s">
         <v>239</v>
@@ -6471,10 +6471,10 @@
         <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="F84" t="s">
-        <v>352</v>
+        <v>234</v>
       </c>
       <c r="G84" t="s">
         <v>235</v>
@@ -6486,10 +6486,10 @@
         <v>237</v>
       </c>
       <c r="J84" t="s">
+        <v>238</v>
+      </c>
+      <c r="K84" t="s">
         <v>353</v>
-      </c>
-      <c r="K84" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -6506,10 +6506,10 @@
         <v>14</v>
       </c>
       <c r="E85" t="s">
-        <v>233</v>
+        <v>357</v>
       </c>
       <c r="F85" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G85" t="s">
         <v>235</v>
@@ -6521,10 +6521,10 @@
         <v>237</v>
       </c>
       <c r="J85" t="s">
-        <v>357</v>
+        <v>238</v>
       </c>
       <c r="K85" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -6541,10 +6541,10 @@
         <v>14</v>
       </c>
       <c r="E86" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="F86" t="s">
-        <v>361</v>
+        <v>234</v>
       </c>
       <c r="G86" t="s">
         <v>235</v>
@@ -6556,10 +6556,10 @@
         <v>237</v>
       </c>
       <c r="J86" t="s">
+        <v>338</v>
+      </c>
+      <c r="K86" t="s">
         <v>362</v>
-      </c>
-      <c r="K86" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -6576,10 +6576,10 @@
         <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>233</v>
+        <v>357</v>
       </c>
       <c r="F87" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G87" t="s">
         <v>235</v>
@@ -6591,10 +6591,10 @@
         <v>237</v>
       </c>
       <c r="J87" t="s">
-        <v>357</v>
+        <v>238</v>
       </c>
       <c r="K87" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -6608,10 +6608,10 @@
         <v>14</v>
       </c>
       <c r="E88" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F88" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G88" t="s">
         <v>235</v>
@@ -6623,10 +6623,10 @@
         <v>237</v>
       </c>
       <c r="J88" t="s">
+        <v>238</v>
+      </c>
+      <c r="K88" t="s">
         <v>244</v>
-      </c>
-      <c r="K88" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -6643,10 +6643,10 @@
         <v>14</v>
       </c>
       <c r="E89" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F89" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G89" t="s">
         <v>235</v>
@@ -6658,10 +6658,10 @@
         <v>237</v>
       </c>
       <c r="J89" t="s">
+        <v>238</v>
+      </c>
+      <c r="K89" t="s">
         <v>244</v>
-      </c>
-      <c r="K89" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -6681,7 +6681,7 @@
         <v>253</v>
       </c>
       <c r="F90" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="G90" t="s">
         <v>235</v>
@@ -6693,10 +6693,10 @@
         <v>237</v>
       </c>
       <c r="J90" t="s">
+        <v>254</v>
+      </c>
+      <c r="K90" t="s">
         <v>255</v>
-      </c>
-      <c r="K90" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -6716,7 +6716,7 @@
         <v>377</v>
       </c>
       <c r="F91" t="s">
-        <v>378</v>
+        <v>234</v>
       </c>
       <c r="G91" t="s">
         <v>235</v>
@@ -6728,10 +6728,10 @@
         <v>237</v>
       </c>
       <c r="J91" t="s">
+        <v>378</v>
+      </c>
+      <c r="K91" t="s">
         <v>379</v>
-      </c>
-      <c r="K91" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -6751,7 +6751,7 @@
         <v>253</v>
       </c>
       <c r="F92" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="G92" t="s">
         <v>235</v>
@@ -6763,10 +6763,10 @@
         <v>237</v>
       </c>
       <c r="J92" t="s">
+        <v>254</v>
+      </c>
+      <c r="K92" t="s">
         <v>255</v>
-      </c>
-      <c r="K92" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -6783,10 +6783,10 @@
         <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F93" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G93" t="s">
         <v>235</v>
@@ -6798,10 +6798,10 @@
         <v>237</v>
       </c>
       <c r="J93" t="s">
+        <v>238</v>
+      </c>
+      <c r="K93" t="s">
         <v>249</v>
-      </c>
-      <c r="K93" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -6821,7 +6821,7 @@
         <v>253</v>
       </c>
       <c r="F94" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="G94" t="s">
         <v>235</v>
@@ -6833,10 +6833,10 @@
         <v>237</v>
       </c>
       <c r="J94" t="s">
+        <v>254</v>
+      </c>
+      <c r="K94" t="s">
         <v>255</v>
-      </c>
-      <c r="K94" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -6853,10 +6853,10 @@
         <v>14</v>
       </c>
       <c r="E95" t="s">
-        <v>233</v>
+        <v>392</v>
       </c>
       <c r="F95" t="s">
-        <v>392</v>
+        <v>234</v>
       </c>
       <c r="G95" t="s">
         <v>235</v>
@@ -6868,10 +6868,10 @@
         <v>237</v>
       </c>
       <c r="J95" t="s">
+        <v>238</v>
+      </c>
+      <c r="K95" t="s">
         <v>393</v>
-      </c>
-      <c r="K95" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -6891,22 +6891,22 @@
         <v>253</v>
       </c>
       <c r="F96" t="s">
-        <v>254</v>
+        <v>397</v>
       </c>
       <c r="G96" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H96" t="s">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="I96" t="s">
         <v>237</v>
       </c>
       <c r="J96" t="s">
+        <v>254</v>
+      </c>
+      <c r="K96" t="s">
         <v>255</v>
-      </c>
-      <c r="K96" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -6926,22 +6926,22 @@
         <v>253</v>
       </c>
       <c r="F97" t="s">
-        <v>254</v>
+        <v>397</v>
       </c>
       <c r="G97" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H97" t="s">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="I97" t="s">
         <v>237</v>
       </c>
       <c r="J97" t="s">
+        <v>254</v>
+      </c>
+      <c r="K97" t="s">
         <v>255</v>
-      </c>
-      <c r="K97" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -6961,22 +6961,22 @@
         <v>405</v>
       </c>
       <c r="F98" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="G98" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H98" t="s">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="I98" t="s">
         <v>237</v>
       </c>
       <c r="J98" t="s">
+        <v>406</v>
+      </c>
+      <c r="K98" t="s">
         <v>407</v>
-      </c>
-      <c r="K98" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -6996,22 +6996,22 @@
         <v>253</v>
       </c>
       <c r="F99" t="s">
-        <v>254</v>
+        <v>397</v>
       </c>
       <c r="G99" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H99" t="s">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="I99" t="s">
         <v>237</v>
       </c>
       <c r="J99" t="s">
+        <v>254</v>
+      </c>
+      <c r="K99" t="s">
         <v>255</v>
-      </c>
-      <c r="K99" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -7028,25 +7028,25 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
-        <v>253</v>
+        <v>319</v>
       </c>
       <c r="F100" t="s">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="G100" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H100" t="s">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="I100" t="s">
         <v>237</v>
       </c>
       <c r="J100" t="s">
+        <v>254</v>
+      </c>
+      <c r="K100" t="s">
         <v>320</v>
-      </c>
-      <c r="K100" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -7066,22 +7066,22 @@
         <v>253</v>
       </c>
       <c r="F101" t="s">
-        <v>254</v>
+        <v>397</v>
       </c>
       <c r="G101" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H101" t="s">
-        <v>398</v>
+        <v>236</v>
       </c>
       <c r="I101" t="s">
         <v>237</v>
       </c>
       <c r="J101" t="s">
+        <v>254</v>
+      </c>
+      <c r="K101" t="s">
         <v>255</v>
-      </c>
-      <c r="K101" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -7098,16 +7098,16 @@
         <v>14</v>
       </c>
       <c r="E102" t="s">
-        <v>377</v>
-      </c>
-      <c r="F102" t="s">
         <v>420</v>
       </c>
+      <c r="H102" t="s">
+        <v>421</v>
+      </c>
       <c r="I102" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J102" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K102" t="s">
         <v>423</v>
@@ -7127,16 +7127,16 @@
         <v>14</v>
       </c>
       <c r="E103" t="s">
-        <v>377</v>
-      </c>
-      <c r="F103" t="s">
         <v>420</v>
       </c>
+      <c r="H103" t="s">
+        <v>421</v>
+      </c>
       <c r="I103" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J103" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K103" t="s">
         <v>423</v>
@@ -7156,16 +7156,16 @@
         <v>14</v>
       </c>
       <c r="E104" t="s">
-        <v>377</v>
-      </c>
-      <c r="F104" t="s">
         <v>420</v>
       </c>
+      <c r="H104" t="s">
+        <v>421</v>
+      </c>
       <c r="I104" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J104" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K104" t="s">
         <v>423</v>
@@ -7185,19 +7185,19 @@
         <v>14</v>
       </c>
       <c r="E105" t="s">
-        <v>377</v>
-      </c>
-      <c r="F105" t="s">
         <v>433</v>
       </c>
+      <c r="H105" t="s">
+        <v>421</v>
+      </c>
       <c r="I105" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J105" t="s">
+        <v>378</v>
+      </c>
+      <c r="K105" t="s">
         <v>434</v>
-      </c>
-      <c r="K105" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7214,16 +7214,16 @@
         <v>14</v>
       </c>
       <c r="E106" t="s">
-        <v>377</v>
-      </c>
-      <c r="F106" t="s">
         <v>420</v>
       </c>
+      <c r="H106" t="s">
+        <v>421</v>
+      </c>
       <c r="I106" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J106" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K106" t="s">
         <v>423</v>
@@ -7245,17 +7245,17 @@
       <c r="E107" t="s">
         <v>377</v>
       </c>
-      <c r="F107" t="s">
+      <c r="H107" t="s">
+        <v>421</v>
+      </c>
+      <c r="I107" t="s">
+        <v>422</v>
+      </c>
+      <c r="J107" t="s">
         <v>378</v>
       </c>
-      <c r="I107" t="s">
-        <v>421</v>
-      </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
         <v>379</v>
-      </c>
-      <c r="K107" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -7272,19 +7272,19 @@
         <v>14</v>
       </c>
       <c r="E108" t="s">
-        <v>377</v>
-      </c>
-      <c r="F108" t="s">
         <v>444</v>
       </c>
+      <c r="H108" t="s">
+        <v>421</v>
+      </c>
       <c r="I108" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J108" t="s">
+        <v>378</v>
+      </c>
+      <c r="K108" t="s">
         <v>445</v>
-      </c>
-      <c r="K108" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7301,19 +7301,19 @@
         <v>14</v>
       </c>
       <c r="E109" t="s">
-        <v>188</v>
-      </c>
-      <c r="F109" t="s">
         <v>449</v>
       </c>
+      <c r="H109" t="s">
+        <v>421</v>
+      </c>
       <c r="I109" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J109" t="s">
+        <v>191</v>
+      </c>
+      <c r="K109" t="s">
         <v>450</v>
-      </c>
-      <c r="K109" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -7330,19 +7330,19 @@
         <v>14</v>
       </c>
       <c r="E110" t="s">
-        <v>188</v>
-      </c>
-      <c r="F110" t="s">
         <v>454</v>
       </c>
+      <c r="H110" t="s">
+        <v>421</v>
+      </c>
       <c r="I110" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J110" t="s">
+        <v>191</v>
+      </c>
+      <c r="K110" t="s">
         <v>455</v>
-      </c>
-      <c r="K110" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -7359,16 +7359,16 @@
         <v>14</v>
       </c>
       <c r="E111" t="s">
-        <v>377</v>
-      </c>
-      <c r="F111" t="s">
         <v>420</v>
       </c>
+      <c r="H111" t="s">
+        <v>421</v>
+      </c>
       <c r="I111" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J111" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K111" t="s">
         <v>423</v>
@@ -7390,17 +7390,17 @@
       <c r="E112" t="s">
         <v>462</v>
       </c>
-      <c r="F112" t="s">
+      <c r="H112" t="s">
+        <v>421</v>
+      </c>
+      <c r="I112" t="s">
+        <v>422</v>
+      </c>
+      <c r="J112" t="s">
         <v>463</v>
       </c>
-      <c r="I112" t="s">
-        <v>421</v>
-      </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>464</v>
-      </c>
-      <c r="K112" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -7417,19 +7417,19 @@
         <v>14</v>
       </c>
       <c r="E113" t="s">
-        <v>233</v>
-      </c>
-      <c r="F113" t="s">
-        <v>234</v>
+        <v>296</v>
+      </c>
+      <c r="H113" t="s">
+        <v>421</v>
       </c>
       <c r="I113" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J113" t="s">
-        <v>296</v>
+        <v>238</v>
       </c>
       <c r="K113" t="s">
-        <v>423</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -7446,19 +7446,19 @@
         <v>14</v>
       </c>
       <c r="E114" t="s">
-        <v>253</v>
-      </c>
-      <c r="F114" t="s">
         <v>314</v>
       </c>
+      <c r="H114" t="s">
+        <v>421</v>
+      </c>
       <c r="I114" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J114" t="s">
+        <v>254</v>
+      </c>
+      <c r="K114" t="s">
         <v>315</v>
-      </c>
-      <c r="K114" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -7477,17 +7477,17 @@
       <c r="E115" t="s">
         <v>377</v>
       </c>
-      <c r="F115" t="s">
+      <c r="H115" t="s">
+        <v>421</v>
+      </c>
+      <c r="I115" t="s">
+        <v>422</v>
+      </c>
+      <c r="J115" t="s">
         <v>378</v>
       </c>
-      <c r="I115" t="s">
-        <v>421</v>
-      </c>
-      <c r="J115" t="s">
+      <c r="K115" t="s">
         <v>379</v>
-      </c>
-      <c r="K115" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -7501,19 +7501,19 @@
         <v>14</v>
       </c>
       <c r="E116" t="s">
-        <v>462</v>
-      </c>
-      <c r="F116" t="s">
         <v>476</v>
       </c>
+      <c r="H116" t="s">
+        <v>421</v>
+      </c>
       <c r="I116" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J116" t="s">
+        <v>463</v>
+      </c>
+      <c r="K116" t="s">
         <v>477</v>
-      </c>
-      <c r="K116" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -7529,17 +7529,17 @@
       <c r="E117" t="s">
         <v>462</v>
       </c>
-      <c r="F117" t="s">
+      <c r="H117" t="s">
+        <v>421</v>
+      </c>
+      <c r="I117" t="s">
+        <v>422</v>
+      </c>
+      <c r="J117" t="s">
         <v>463</v>
       </c>
-      <c r="I117" t="s">
-        <v>421</v>
-      </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
         <v>464</v>
-      </c>
-      <c r="K117" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -7556,19 +7556,19 @@
         <v>14</v>
       </c>
       <c r="E118" t="s">
-        <v>337</v>
-      </c>
-      <c r="F118" t="s">
+        <v>483</v>
+      </c>
+      <c r="H118" t="s">
+        <v>421</v>
+      </c>
+      <c r="I118" t="s">
+        <v>422</v>
+      </c>
+      <c r="J118" t="s">
         <v>338</v>
       </c>
-      <c r="I118" t="s">
-        <v>421</v>
-      </c>
-      <c r="J118" t="s">
-        <v>483</v>
-      </c>
       <c r="K118" t="s">
-        <v>423</v>
+        <v>339</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -7587,17 +7587,17 @@
       <c r="E119" t="s">
         <v>377</v>
       </c>
-      <c r="F119" t="s">
+      <c r="H119" t="s">
+        <v>421</v>
+      </c>
+      <c r="I119" t="s">
+        <v>422</v>
+      </c>
+      <c r="J119" t="s">
         <v>378</v>
       </c>
-      <c r="I119" t="s">
-        <v>421</v>
-      </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
         <v>379</v>
-      </c>
-      <c r="K119" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -7614,19 +7614,19 @@
         <v>14</v>
       </c>
       <c r="E120" t="s">
-        <v>233</v>
-      </c>
-      <c r="F120" t="s">
         <v>352</v>
       </c>
+      <c r="H120" t="s">
+        <v>490</v>
+      </c>
       <c r="I120" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J120" t="s">
+        <v>238</v>
+      </c>
+      <c r="K120" t="s">
         <v>353</v>
-      </c>
-      <c r="K120" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -7643,19 +7643,19 @@
         <v>14</v>
       </c>
       <c r="E121" t="s">
-        <v>233</v>
-      </c>
-      <c r="F121" t="s">
-        <v>234</v>
+        <v>296</v>
+      </c>
+      <c r="H121" t="s">
+        <v>490</v>
       </c>
       <c r="I121" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J121" t="s">
-        <v>296</v>
+        <v>238</v>
       </c>
       <c r="K121" t="s">
-        <v>491</v>
+        <v>239</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -7672,19 +7672,19 @@
         <v>14</v>
       </c>
       <c r="E122" t="s">
-        <v>233</v>
-      </c>
-      <c r="F122" t="s">
         <v>352</v>
       </c>
+      <c r="H122" t="s">
+        <v>490</v>
+      </c>
       <c r="I122" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J122" t="s">
+        <v>238</v>
+      </c>
+      <c r="K122" t="s">
         <v>353</v>
-      </c>
-      <c r="K122" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -7701,19 +7701,19 @@
         <v>14</v>
       </c>
       <c r="E123" t="s">
-        <v>233</v>
-      </c>
-      <c r="F123" t="s">
         <v>352</v>
       </c>
+      <c r="H123" t="s">
+        <v>490</v>
+      </c>
       <c r="I123" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J123" t="s">
+        <v>238</v>
+      </c>
+      <c r="K123" t="s">
         <v>353</v>
-      </c>
-      <c r="K123" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -7730,19 +7730,19 @@
         <v>14</v>
       </c>
       <c r="E124" t="s">
-        <v>337</v>
-      </c>
-      <c r="F124" t="s">
         <v>504</v>
       </c>
+      <c r="H124" t="s">
+        <v>490</v>
+      </c>
       <c r="I124" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J124" t="s">
+        <v>338</v>
+      </c>
+      <c r="K124" t="s">
         <v>505</v>
-      </c>
-      <c r="K124" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -7759,19 +7759,19 @@
         <v>14</v>
       </c>
       <c r="E125" t="s">
-        <v>337</v>
-      </c>
-      <c r="F125" t="s">
         <v>504</v>
       </c>
+      <c r="H125" t="s">
+        <v>490</v>
+      </c>
       <c r="I125" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J125" t="s">
+        <v>338</v>
+      </c>
+      <c r="K125" t="s">
         <v>505</v>
-      </c>
-      <c r="K125" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -7788,19 +7788,19 @@
         <v>14</v>
       </c>
       <c r="E126" t="s">
-        <v>337</v>
-      </c>
-      <c r="F126" t="s">
         <v>504</v>
       </c>
+      <c r="H126" t="s">
+        <v>490</v>
+      </c>
       <c r="I126" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J126" t="s">
+        <v>338</v>
+      </c>
+      <c r="K126" t="s">
         <v>505</v>
-      </c>
-      <c r="K126" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -7817,19 +7817,19 @@
         <v>14</v>
       </c>
       <c r="E127" t="s">
-        <v>337</v>
-      </c>
-      <c r="F127" t="s">
         <v>504</v>
       </c>
+      <c r="H127" t="s">
+        <v>490</v>
+      </c>
       <c r="I127" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J127" t="s">
+        <v>338</v>
+      </c>
+      <c r="K127" t="s">
         <v>505</v>
-      </c>
-      <c r="K127" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -7846,19 +7846,19 @@
         <v>14</v>
       </c>
       <c r="E128" t="s">
-        <v>337</v>
-      </c>
-      <c r="F128" t="s">
         <v>504</v>
       </c>
+      <c r="H128" t="s">
+        <v>490</v>
+      </c>
       <c r="I128" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J128" t="s">
+        <v>338</v>
+      </c>
+      <c r="K128" t="s">
         <v>505</v>
-      </c>
-      <c r="K128" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -7875,19 +7875,19 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>337</v>
-      </c>
-      <c r="F129" t="s">
-        <v>504</v>
+        <v>521</v>
+      </c>
+      <c r="H129" t="s">
+        <v>490</v>
       </c>
       <c r="I129" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J129" t="s">
-        <v>521</v>
+        <v>338</v>
       </c>
       <c r="K129" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7904,19 +7904,19 @@
         <v>14</v>
       </c>
       <c r="E130" t="s">
-        <v>337</v>
-      </c>
-      <c r="F130" t="s">
-        <v>504</v>
+        <v>525</v>
+      </c>
+      <c r="H130" t="s">
+        <v>490</v>
       </c>
       <c r="I130" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J130" t="s">
-        <v>525</v>
+        <v>338</v>
       </c>
       <c r="K130" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7933,19 +7933,19 @@
         <v>14</v>
       </c>
       <c r="E131" t="s">
-        <v>337</v>
-      </c>
-      <c r="F131" t="s">
-        <v>504</v>
+        <v>529</v>
+      </c>
+      <c r="H131" t="s">
+        <v>490</v>
       </c>
       <c r="I131" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J131" t="s">
-        <v>529</v>
+        <v>338</v>
       </c>
       <c r="K131" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7962,19 +7962,19 @@
         <v>14</v>
       </c>
       <c r="E132" t="s">
-        <v>337</v>
-      </c>
-      <c r="F132" t="s">
         <v>533</v>
       </c>
+      <c r="H132" t="s">
+        <v>490</v>
+      </c>
       <c r="I132" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J132" t="s">
+        <v>338</v>
+      </c>
+      <c r="K132" t="s">
         <v>534</v>
-      </c>
-      <c r="K132" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -7988,19 +7988,19 @@
         <v>14</v>
       </c>
       <c r="E133" t="s">
-        <v>233</v>
-      </c>
-      <c r="F133" t="s">
         <v>392</v>
       </c>
+      <c r="H133" t="s">
+        <v>490</v>
+      </c>
       <c r="I133" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J133" t="s">
+        <v>238</v>
+      </c>
+      <c r="K133" t="s">
         <v>393</v>
-      </c>
-      <c r="K133" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -8017,19 +8017,19 @@
         <v>14</v>
       </c>
       <c r="E134" t="s">
-        <v>337</v>
-      </c>
-      <c r="F134" t="s">
         <v>361</v>
       </c>
+      <c r="H134" t="s">
+        <v>540</v>
+      </c>
       <c r="I134" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J134" t="s">
+        <v>338</v>
+      </c>
+      <c r="K134" t="s">
         <v>362</v>
-      </c>
-      <c r="K134" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -8043,19 +8043,19 @@
         <v>14</v>
       </c>
       <c r="E135" t="s">
-        <v>337</v>
-      </c>
-      <c r="F135" t="s">
         <v>361</v>
       </c>
+      <c r="H135" t="s">
+        <v>540</v>
+      </c>
       <c r="I135" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J135" t="s">
+        <v>338</v>
+      </c>
+      <c r="K135" t="s">
         <v>362</v>
-      </c>
-      <c r="K135" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -8072,19 +8072,19 @@
         <v>14</v>
       </c>
       <c r="E136" t="s">
-        <v>337</v>
-      </c>
-      <c r="F136" t="s">
         <v>361</v>
       </c>
+      <c r="H136" t="s">
+        <v>540</v>
+      </c>
       <c r="I136" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J136" t="s">
+        <v>338</v>
+      </c>
+      <c r="K136" t="s">
         <v>362</v>
-      </c>
-      <c r="K136" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -8101,19 +8101,19 @@
         <v>14</v>
       </c>
       <c r="E137" t="s">
-        <v>337</v>
-      </c>
-      <c r="F137" t="s">
         <v>361</v>
       </c>
+      <c r="H137" t="s">
+        <v>540</v>
+      </c>
       <c r="I137" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J137" t="s">
+        <v>338</v>
+      </c>
+      <c r="K137" t="s">
         <v>362</v>
-      </c>
-      <c r="K137" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -8130,19 +8130,19 @@
         <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>337</v>
-      </c>
-      <c r="F138" t="s">
         <v>361</v>
       </c>
+      <c r="H138" t="s">
+        <v>540</v>
+      </c>
       <c r="I138" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J138" t="s">
+        <v>338</v>
+      </c>
+      <c r="K138" t="s">
         <v>362</v>
-      </c>
-      <c r="K138" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -8159,19 +8159,19 @@
         <v>14</v>
       </c>
       <c r="E139" t="s">
-        <v>462</v>
-      </c>
-      <c r="F139" t="s">
         <v>556</v>
       </c>
+      <c r="H139" t="s">
+        <v>540</v>
+      </c>
       <c r="I139" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J139" t="s">
+        <v>463</v>
+      </c>
+      <c r="K139" t="s">
         <v>557</v>
-      </c>
-      <c r="K139" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -8188,19 +8188,19 @@
         <v>14</v>
       </c>
       <c r="E140" t="s">
-        <v>337</v>
-      </c>
-      <c r="F140" t="s">
         <v>361</v>
       </c>
+      <c r="H140" t="s">
+        <v>540</v>
+      </c>
       <c r="I140" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J140" t="s">
+        <v>338</v>
+      </c>
+      <c r="K140" t="s">
         <v>362</v>
-      </c>
-      <c r="K140" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -8217,22 +8217,22 @@
         <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F141" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G141" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H141" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I141" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J141" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K141" t="s">
         <v>569</v>
@@ -8249,22 +8249,22 @@
         <v>14</v>
       </c>
       <c r="E142" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F142" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G142" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H142" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I142" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J142" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K142" t="s">
         <v>569</v>
@@ -8284,25 +8284,25 @@
         <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>337</v>
+        <v>575</v>
       </c>
       <c r="F143" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="G143" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H143" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I143" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J143" t="s">
+        <v>338</v>
+      </c>
+      <c r="K143" t="s">
         <v>576</v>
-      </c>
-      <c r="K143" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -8319,25 +8319,25 @@
         <v>14</v>
       </c>
       <c r="E144" t="s">
-        <v>337</v>
+        <v>575</v>
       </c>
       <c r="F144" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="G144" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H144" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I144" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J144" t="s">
+        <v>338</v>
+      </c>
+      <c r="K144" t="s">
         <v>576</v>
-      </c>
-      <c r="K144" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -8354,25 +8354,25 @@
         <v>14</v>
       </c>
       <c r="E145" t="s">
-        <v>337</v>
+        <v>575</v>
       </c>
       <c r="F145" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="G145" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H145" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I145" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J145" t="s">
+        <v>338</v>
+      </c>
+      <c r="K145" t="s">
         <v>576</v>
-      </c>
-      <c r="K145" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -8389,22 +8389,22 @@
         <v>14</v>
       </c>
       <c r="E146" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F146" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G146" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H146" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I146" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J146" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K146" t="s">
         <v>569</v>
@@ -8424,22 +8424,22 @@
         <v>14</v>
       </c>
       <c r="E147" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F147" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="G147" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H147" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="I147" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J147" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K147" t="s">
         <v>569</v>
@@ -8459,22 +8459,22 @@
         <v>14</v>
       </c>
       <c r="E148" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F148" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="G148" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H148" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="I148" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J148" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K148" t="s">
         <v>569</v>
@@ -8494,22 +8494,22 @@
         <v>14</v>
       </c>
       <c r="E149" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F149" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="G149" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H149" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="I149" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J149" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K149" t="s">
         <v>569</v>
@@ -8529,22 +8529,22 @@
         <v>14</v>
       </c>
       <c r="E150" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F150" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="G150" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H150" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="I150" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J150" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K150" t="s">
         <v>569</v>
@@ -8564,22 +8564,22 @@
         <v>14</v>
       </c>
       <c r="E151" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F151" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="G151" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H151" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="I151" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J151" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K151" t="s">
         <v>569</v>
@@ -8599,22 +8599,22 @@
         <v>14</v>
       </c>
       <c r="E152" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F152" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="G152" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H152" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="I152" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J152" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K152" t="s">
         <v>569</v>
@@ -8634,22 +8634,22 @@
         <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F153" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="G153" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H153" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="I153" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J153" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K153" t="s">
         <v>569</v>
@@ -8669,22 +8669,22 @@
         <v>14</v>
       </c>
       <c r="E154" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F154" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="G154" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H154" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="I154" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J154" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K154" t="s">
         <v>569</v>
@@ -8704,22 +8704,22 @@
         <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F155" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="G155" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H155" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="I155" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J155" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K155" t="s">
         <v>569</v>
@@ -8739,22 +8739,22 @@
         <v>14</v>
       </c>
       <c r="E156" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F156" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="G156" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H156" t="s">
-        <v>619</v>
+        <v>567</v>
       </c>
       <c r="I156" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J156" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K156" t="s">
         <v>569</v>
@@ -8774,22 +8774,22 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>337</v>
+        <v>623</v>
       </c>
       <c r="F157" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="G157" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H157" t="s">
-        <v>619</v>
+        <v>567</v>
       </c>
       <c r="I157" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J157" t="s">
-        <v>623</v>
+        <v>338</v>
       </c>
       <c r="K157" t="s">
         <v>569</v>
@@ -8809,22 +8809,22 @@
         <v>14</v>
       </c>
       <c r="E158" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F158" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="G158" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H158" t="s">
-        <v>619</v>
+        <v>567</v>
       </c>
       <c r="I158" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J158" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K158" t="s">
         <v>569</v>
@@ -8844,22 +8844,22 @@
         <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F159" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="G159" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H159" t="s">
-        <v>619</v>
+        <v>567</v>
       </c>
       <c r="I159" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J159" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K159" t="s">
         <v>569</v>
@@ -8879,22 +8879,22 @@
         <v>14</v>
       </c>
       <c r="E160" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F160" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="G160" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H160" t="s">
-        <v>619</v>
+        <v>567</v>
       </c>
       <c r="I160" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J160" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K160" t="s">
         <v>569</v>
@@ -8914,22 +8914,22 @@
         <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F161" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="G161" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H161" t="s">
-        <v>619</v>
+        <v>567</v>
       </c>
       <c r="I161" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J161" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K161" t="s">
         <v>569</v>
@@ -8949,22 +8949,22 @@
         <v>14</v>
       </c>
       <c r="E162" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F162" t="s">
-        <v>564</v>
+        <v>639</v>
       </c>
       <c r="G162" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H162" t="s">
-        <v>640</v>
+        <v>567</v>
       </c>
       <c r="I162" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J162" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K162" t="s">
         <v>569</v>
@@ -8984,22 +8984,22 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>337</v>
+        <v>644</v>
       </c>
       <c r="F163" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
       <c r="G163" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H163" t="s">
-        <v>642</v>
+        <v>567</v>
       </c>
       <c r="I163" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J163" t="s">
-        <v>645</v>
+        <v>338</v>
       </c>
       <c r="K163" t="s">
         <v>569</v>
@@ -9019,22 +9019,22 @@
         <v>14</v>
       </c>
       <c r="E164" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F164" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="G164" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H164" t="s">
-        <v>650</v>
+        <v>567</v>
       </c>
       <c r="I164" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J164" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K164" t="s">
         <v>569</v>
@@ -9054,22 +9054,22 @@
         <v>14</v>
       </c>
       <c r="E165" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F165" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="G165" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H165" t="s">
-        <v>650</v>
+        <v>567</v>
       </c>
       <c r="I165" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J165" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K165" t="s">
         <v>569</v>
@@ -9089,22 +9089,22 @@
         <v>14</v>
       </c>
       <c r="E166" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F166" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="G166" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H166" t="s">
-        <v>650</v>
+        <v>567</v>
       </c>
       <c r="I166" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J166" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K166" t="s">
         <v>569</v>
@@ -9124,22 +9124,22 @@
         <v>14</v>
       </c>
       <c r="E167" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F167" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="G167" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H167" t="s">
-        <v>650</v>
+        <v>567</v>
       </c>
       <c r="I167" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J167" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K167" t="s">
         <v>569</v>
@@ -9159,22 +9159,22 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>337</v>
+        <v>663</v>
       </c>
       <c r="F168" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="G168" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H168" t="s">
-        <v>650</v>
+        <v>567</v>
       </c>
       <c r="I168" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J168" t="s">
-        <v>663</v>
+        <v>338</v>
       </c>
       <c r="K168" t="s">
         <v>569</v>
@@ -9191,22 +9191,22 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>337</v>
+        <v>663</v>
       </c>
       <c r="F169" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="G169" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H169" t="s">
-        <v>650</v>
+        <v>567</v>
       </c>
       <c r="I169" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J169" t="s">
-        <v>663</v>
+        <v>338</v>
       </c>
       <c r="K169" t="s">
         <v>569</v>
@@ -9226,22 +9226,22 @@
         <v>14</v>
       </c>
       <c r="E170" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F170" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="G170" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H170" t="s">
-        <v>650</v>
+        <v>567</v>
       </c>
       <c r="I170" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J170" t="s">
-        <v>568</v>
+        <v>338</v>
       </c>
       <c r="K170" t="s">
         <v>569</v>
@@ -9263,17 +9263,17 @@
       <c r="E171" t="s">
         <v>337</v>
       </c>
-      <c r="F171" t="s">
+      <c r="H171" t="s">
+        <v>672</v>
+      </c>
+      <c r="I171" t="s">
+        <v>673</v>
+      </c>
+      <c r="J171" t="s">
         <v>338</v>
       </c>
-      <c r="I171" t="s">
-        <v>672</v>
-      </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>339</v>
-      </c>
-      <c r="K171" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -9290,19 +9290,19 @@
         <v>14</v>
       </c>
       <c r="E172" t="s">
-        <v>233</v>
-      </c>
-      <c r="F172" t="s">
         <v>243</v>
       </c>
+      <c r="H172" t="s">
+        <v>672</v>
+      </c>
       <c r="I172" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="J172" t="s">
+        <v>238</v>
+      </c>
+      <c r="K172" t="s">
         <v>244</v>
-      </c>
-      <c r="K172" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -9321,17 +9321,17 @@
       <c r="E173" t="s">
         <v>337</v>
       </c>
-      <c r="F173" t="s">
+      <c r="H173" t="s">
+        <v>672</v>
+      </c>
+      <c r="I173" t="s">
+        <v>673</v>
+      </c>
+      <c r="J173" t="s">
         <v>338</v>
       </c>
-      <c r="I173" t="s">
-        <v>672</v>
-      </c>
-      <c r="J173" t="s">
+      <c r="K173" t="s">
         <v>339</v>
-      </c>
-      <c r="K173" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -9350,17 +9350,17 @@
       <c r="E174" t="s">
         <v>337</v>
       </c>
-      <c r="F174" t="s">
+      <c r="H174" t="s">
+        <v>672</v>
+      </c>
+      <c r="I174" t="s">
+        <v>673</v>
+      </c>
+      <c r="J174" t="s">
         <v>338</v>
       </c>
-      <c r="I174" t="s">
-        <v>672</v>
-      </c>
-      <c r="J174" t="s">
+      <c r="K174" t="s">
         <v>339</v>
-      </c>
-      <c r="K174" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -9379,17 +9379,17 @@
       <c r="E175" t="s">
         <v>337</v>
       </c>
-      <c r="F175" t="s">
+      <c r="H175" t="s">
+        <v>672</v>
+      </c>
+      <c r="I175" t="s">
+        <v>673</v>
+      </c>
+      <c r="J175" t="s">
         <v>338</v>
       </c>
-      <c r="I175" t="s">
-        <v>672</v>
-      </c>
-      <c r="J175" t="s">
+      <c r="K175" t="s">
         <v>339</v>
-      </c>
-      <c r="K175" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -9405,17 +9405,17 @@
       <c r="E176" t="s">
         <v>337</v>
       </c>
-      <c r="F176" t="s">
+      <c r="H176" t="s">
+        <v>672</v>
+      </c>
+      <c r="I176" t="s">
+        <v>673</v>
+      </c>
+      <c r="J176" t="s">
         <v>338</v>
       </c>
-      <c r="I176" t="s">
-        <v>672</v>
-      </c>
-      <c r="J176" t="s">
+      <c r="K176" t="s">
         <v>339</v>
-      </c>
-      <c r="K176" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -9434,17 +9434,17 @@
       <c r="E177" t="s">
         <v>337</v>
       </c>
-      <c r="F177" t="s">
+      <c r="H177" t="s">
+        <v>691</v>
+      </c>
+      <c r="I177" t="s">
+        <v>692</v>
+      </c>
+      <c r="J177" t="s">
         <v>338</v>
       </c>
-      <c r="I177" t="s">
-        <v>691</v>
-      </c>
-      <c r="J177" t="s">
+      <c r="K177" t="s">
         <v>339</v>
-      </c>
-      <c r="K177" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -9463,17 +9463,17 @@
       <c r="E178" t="s">
         <v>337</v>
       </c>
-      <c r="F178" t="s">
+      <c r="H178" t="s">
+        <v>691</v>
+      </c>
+      <c r="I178" t="s">
+        <v>692</v>
+      </c>
+      <c r="J178" t="s">
         <v>338</v>
       </c>
-      <c r="I178" t="s">
-        <v>691</v>
-      </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>339</v>
-      </c>
-      <c r="K178" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -9492,17 +9492,17 @@
       <c r="E179" t="s">
         <v>337</v>
       </c>
-      <c r="F179" t="s">
+      <c r="H179" t="s">
+        <v>691</v>
+      </c>
+      <c r="I179" t="s">
+        <v>692</v>
+      </c>
+      <c r="J179" t="s">
         <v>338</v>
       </c>
-      <c r="I179" t="s">
-        <v>691</v>
-      </c>
-      <c r="J179" t="s">
+      <c r="K179" t="s">
         <v>339</v>
-      </c>
-      <c r="K179" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -9521,17 +9521,17 @@
       <c r="E180" t="s">
         <v>337</v>
       </c>
-      <c r="F180" t="s">
+      <c r="H180" t="s">
+        <v>691</v>
+      </c>
+      <c r="I180" t="s">
+        <v>692</v>
+      </c>
+      <c r="J180" t="s">
         <v>338</v>
       </c>
-      <c r="I180" t="s">
-        <v>691</v>
-      </c>
-      <c r="J180" t="s">
+      <c r="K180" t="s">
         <v>339</v>
-      </c>
-      <c r="K180" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -9548,22 +9548,22 @@
         <v>14</v>
       </c>
       <c r="E181" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F181" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G181" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H181" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I181" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J181" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K181" t="s">
         <v>710</v>
@@ -9583,22 +9583,22 @@
         <v>14</v>
       </c>
       <c r="E182" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F182" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G182" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H182" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I182" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J182" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K182" t="s">
         <v>710</v>
@@ -9618,22 +9618,22 @@
         <v>14</v>
       </c>
       <c r="E183" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F183" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G183" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H183" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I183" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J183" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K183" t="s">
         <v>710</v>
@@ -9653,22 +9653,22 @@
         <v>14</v>
       </c>
       <c r="E184" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F184" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G184" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H184" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I184" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J184" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K184" t="s">
         <v>710</v>
@@ -9688,22 +9688,22 @@
         <v>14</v>
       </c>
       <c r="E185" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F185" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G185" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H185" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I185" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J185" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K185" t="s">
         <v>710</v>
@@ -9723,22 +9723,22 @@
         <v>14</v>
       </c>
       <c r="E186" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F186" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G186" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H186" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I186" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J186" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K186" t="s">
         <v>710</v>
@@ -9758,22 +9758,22 @@
         <v>14</v>
       </c>
       <c r="E187" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F187" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G187" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H187" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I187" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J187" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K187" t="s">
         <v>710</v>
@@ -9793,22 +9793,22 @@
         <v>14</v>
       </c>
       <c r="E188" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F188" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G188" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H188" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I188" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J188" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K188" t="s">
         <v>710</v>
@@ -9828,22 +9828,22 @@
         <v>14</v>
       </c>
       <c r="E189" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F189" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G189" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H189" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I189" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J189" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K189" t="s">
         <v>710</v>
@@ -9863,22 +9863,22 @@
         <v>14</v>
       </c>
       <c r="E190" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F190" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G190" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H190" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I190" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J190" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K190" t="s">
         <v>710</v>
@@ -9898,22 +9898,22 @@
         <v>14</v>
       </c>
       <c r="E191" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F191" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G191" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H191" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I191" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J191" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K191" t="s">
         <v>710</v>
@@ -9930,22 +9930,22 @@
         <v>14</v>
       </c>
       <c r="E192" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F192" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G192" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H192" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I192" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J192" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K192" t="s">
         <v>710</v>
@@ -9965,25 +9965,25 @@
         <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>337</v>
+        <v>746</v>
       </c>
       <c r="F193" t="s">
-        <v>575</v>
+        <v>706</v>
       </c>
       <c r="G193" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H193" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I193" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J193" t="s">
-        <v>746</v>
+        <v>338</v>
       </c>
       <c r="K193" t="s">
-        <v>710</v>
+        <v>576</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -10000,22 +10000,22 @@
         <v>14</v>
       </c>
       <c r="E194" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F194" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G194" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H194" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I194" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J194" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K194" t="s">
         <v>710</v>
@@ -10035,22 +10035,22 @@
         <v>14</v>
       </c>
       <c r="E195" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F195" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G195" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H195" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I195" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J195" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K195" t="s">
         <v>710</v>
@@ -10070,22 +10070,22 @@
         <v>14</v>
       </c>
       <c r="E196" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F196" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G196" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H196" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I196" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J196" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K196" t="s">
         <v>710</v>
@@ -10105,22 +10105,22 @@
         <v>14</v>
       </c>
       <c r="E197" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F197" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G197" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H197" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I197" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J197" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K197" t="s">
         <v>710</v>
@@ -10140,22 +10140,22 @@
         <v>14</v>
       </c>
       <c r="E198" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F198" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G198" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H198" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I198" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J198" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K198" t="s">
         <v>710</v>
@@ -10175,22 +10175,22 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
-        <v>337</v>
+        <v>765</v>
       </c>
       <c r="F199" t="s">
-        <v>705</v>
+        <v>766</v>
       </c>
       <c r="G199" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H199" t="s">
-        <v>766</v>
+        <v>708</v>
       </c>
       <c r="I199" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J199" t="s">
-        <v>767</v>
+        <v>338</v>
       </c>
       <c r="K199" t="s">
         <v>710</v>
@@ -10210,22 +10210,22 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
-        <v>337</v>
+        <v>765</v>
       </c>
       <c r="F200" t="s">
-        <v>705</v>
+        <v>766</v>
       </c>
       <c r="G200" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H200" t="s">
-        <v>766</v>
+        <v>708</v>
       </c>
       <c r="I200" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J200" t="s">
-        <v>767</v>
+        <v>338</v>
       </c>
       <c r="K200" t="s">
         <v>710</v>
@@ -10245,22 +10245,22 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>337</v>
+        <v>765</v>
       </c>
       <c r="F201" t="s">
-        <v>705</v>
+        <v>766</v>
       </c>
       <c r="G201" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H201" t="s">
-        <v>766</v>
+        <v>708</v>
       </c>
       <c r="I201" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J201" t="s">
-        <v>767</v>
+        <v>338</v>
       </c>
       <c r="K201" t="s">
         <v>710</v>
@@ -10277,22 +10277,22 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
-        <v>337</v>
+        <v>765</v>
       </c>
       <c r="F202" t="s">
-        <v>705</v>
+        <v>766</v>
       </c>
       <c r="G202" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H202" t="s">
-        <v>766</v>
+        <v>708</v>
       </c>
       <c r="I202" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J202" t="s">
-        <v>767</v>
+        <v>338</v>
       </c>
       <c r="K202" t="s">
         <v>710</v>
@@ -10312,25 +10312,25 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
-        <v>337</v>
+        <v>746</v>
       </c>
       <c r="F203" t="s">
-        <v>575</v>
+        <v>766</v>
       </c>
       <c r="G203" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H203" t="s">
-        <v>766</v>
+        <v>708</v>
       </c>
       <c r="I203" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J203" t="s">
-        <v>746</v>
+        <v>338</v>
       </c>
       <c r="K203" t="s">
-        <v>710</v>
+        <v>576</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10344,22 +10344,22 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
-        <v>337</v>
+        <v>765</v>
       </c>
       <c r="F204" t="s">
-        <v>705</v>
+        <v>766</v>
       </c>
       <c r="G204" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H204" t="s">
-        <v>766</v>
+        <v>708</v>
       </c>
       <c r="I204" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J204" t="s">
-        <v>767</v>
+        <v>338</v>
       </c>
       <c r="K204" t="s">
         <v>710</v>
@@ -10379,22 +10379,22 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
-        <v>337</v>
+        <v>784</v>
       </c>
       <c r="F205" t="s">
-        <v>705</v>
+        <v>785</v>
       </c>
       <c r="G205" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="H205" t="s">
-        <v>785</v>
+        <v>708</v>
       </c>
       <c r="I205" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J205" t="s">
-        <v>786</v>
+        <v>338</v>
       </c>
       <c r="K205" t="s">
         <v>710</v>
@@ -10414,22 +10414,22 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
-        <v>337</v>
+        <v>784</v>
       </c>
       <c r="F206" t="s">
-        <v>705</v>
+        <v>785</v>
       </c>
       <c r="G206" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="H206" t="s">
-        <v>785</v>
+        <v>708</v>
       </c>
       <c r="I206" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J206" t="s">
-        <v>786</v>
+        <v>338</v>
       </c>
       <c r="K206" t="s">
         <v>710</v>
@@ -10446,22 +10446,22 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>337</v>
+        <v>784</v>
       </c>
       <c r="F207" t="s">
-        <v>705</v>
+        <v>785</v>
       </c>
       <c r="G207" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="H207" t="s">
-        <v>785</v>
+        <v>708</v>
       </c>
       <c r="I207" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J207" t="s">
-        <v>786</v>
+        <v>338</v>
       </c>
       <c r="K207" t="s">
         <v>710</v>
@@ -10481,25 +10481,25 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
-        <v>337</v>
+        <v>746</v>
       </c>
       <c r="F208" t="s">
-        <v>575</v>
+        <v>785</v>
       </c>
       <c r="G208" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="H208" t="s">
-        <v>785</v>
+        <v>708</v>
       </c>
       <c r="I208" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J208" t="s">
-        <v>746</v>
+        <v>338</v>
       </c>
       <c r="K208" t="s">
-        <v>710</v>
+        <v>576</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10516,22 +10516,22 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
-        <v>337</v>
+        <v>784</v>
       </c>
       <c r="F209" t="s">
-        <v>705</v>
+        <v>785</v>
       </c>
       <c r="G209" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="H209" t="s">
-        <v>785</v>
+        <v>708</v>
       </c>
       <c r="I209" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J209" t="s">
-        <v>786</v>
+        <v>338</v>
       </c>
       <c r="K209" t="s">
         <v>710</v>
@@ -10551,22 +10551,22 @@
         <v>14</v>
       </c>
       <c r="E210" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F210" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G210" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H210" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I210" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J210" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K210" t="s">
         <v>806</v>
@@ -10583,22 +10583,22 @@
         <v>14</v>
       </c>
       <c r="E211" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F211" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G211" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H211" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I211" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J211" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K211" t="s">
         <v>806</v>
@@ -10618,22 +10618,22 @@
         <v>14</v>
       </c>
       <c r="E212" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F212" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G212" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H212" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I212" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J212" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K212" t="s">
         <v>806</v>
@@ -10650,22 +10650,22 @@
         <v>14</v>
       </c>
       <c r="E213" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F213" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G213" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H213" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I213" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J213" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K213" t="s">
         <v>806</v>
@@ -10685,22 +10685,22 @@
         <v>14</v>
       </c>
       <c r="E214" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F214" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G214" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H214" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I214" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J214" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K214" t="s">
         <v>806</v>
@@ -10720,25 +10720,25 @@
         <v>14</v>
       </c>
       <c r="E215" t="s">
-        <v>337</v>
+        <v>765</v>
       </c>
       <c r="F215" t="s">
-        <v>705</v>
+        <v>802</v>
       </c>
       <c r="G215" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H215" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I215" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J215" t="s">
-        <v>767</v>
+        <v>338</v>
       </c>
       <c r="K215" t="s">
-        <v>806</v>
+        <v>710</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -10755,22 +10755,22 @@
         <v>14</v>
       </c>
       <c r="E216" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F216" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G216" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H216" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I216" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J216" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K216" t="s">
         <v>806</v>
@@ -10790,22 +10790,22 @@
         <v>14</v>
       </c>
       <c r="E217" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F217" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G217" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H217" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I217" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J217" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K217" t="s">
         <v>806</v>
@@ -10822,22 +10822,22 @@
         <v>14</v>
       </c>
       <c r="E218" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F218" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G218" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H218" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I218" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J218" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K218" t="s">
         <v>806</v>
@@ -10854,22 +10854,22 @@
         <v>14</v>
       </c>
       <c r="E219" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F219" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G219" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H219" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I219" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J219" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K219" t="s">
         <v>806</v>
@@ -10889,25 +10889,25 @@
         <v>14</v>
       </c>
       <c r="E220" t="s">
-        <v>337</v>
+        <v>663</v>
       </c>
       <c r="F220" t="s">
-        <v>564</v>
+        <v>802</v>
       </c>
       <c r="G220" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H220" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I220" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J220" t="s">
-        <v>663</v>
+        <v>338</v>
       </c>
       <c r="K220" t="s">
-        <v>806</v>
+        <v>569</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -10924,22 +10924,22 @@
         <v>14</v>
       </c>
       <c r="E221" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F221" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G221" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H221" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I221" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J221" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K221" t="s">
         <v>806</v>
@@ -10959,22 +10959,22 @@
         <v>14</v>
       </c>
       <c r="E222" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F222" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G222" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H222" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I222" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J222" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K222" t="s">
         <v>806</v>
@@ -10991,22 +10991,22 @@
         <v>14</v>
       </c>
       <c r="E223" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F223" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G223" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H223" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I223" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J223" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K223" t="s">
         <v>806</v>
@@ -11026,22 +11026,22 @@
         <v>14</v>
       </c>
       <c r="E224" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F224" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G224" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H224" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I224" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J224" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K224" t="s">
         <v>806</v>
@@ -11061,22 +11061,22 @@
         <v>14</v>
       </c>
       <c r="E225" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F225" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G225" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H225" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I225" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J225" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K225" t="s">
         <v>806</v>
@@ -11096,25 +11096,25 @@
         <v>14</v>
       </c>
       <c r="E226" t="s">
-        <v>337</v>
+        <v>575</v>
       </c>
       <c r="F226" t="s">
-        <v>575</v>
+        <v>802</v>
       </c>
       <c r="G226" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H226" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I226" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J226" t="s">
+        <v>338</v>
+      </c>
+      <c r="K226" t="s">
         <v>576</v>
-      </c>
-      <c r="K226" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -11131,22 +11131,22 @@
         <v>14</v>
       </c>
       <c r="E227" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F227" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G227" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H227" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I227" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J227" t="s">
-        <v>805</v>
+        <v>338</v>
       </c>
       <c r="K227" t="s">
         <v>806</v>
@@ -11169,22 +11169,22 @@
         <v>337</v>
       </c>
       <c r="F228" t="s">
+        <v>802</v>
+      </c>
+      <c r="G228" t="s">
+        <v>803</v>
+      </c>
+      <c r="H228" t="s">
+        <v>804</v>
+      </c>
+      <c r="I228" t="s">
+        <v>805</v>
+      </c>
+      <c r="J228" t="s">
         <v>338</v>
       </c>
-      <c r="G228" t="s">
-        <v>802</v>
-      </c>
-      <c r="H228" t="s">
-        <v>803</v>
-      </c>
-      <c r="I228" t="s">
-        <v>804</v>
-      </c>
-      <c r="J228" t="s">
+      <c r="K228" t="s">
         <v>339</v>
-      </c>
-      <c r="K228" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -11201,22 +11201,22 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
-        <v>337</v>
+        <v>859</v>
       </c>
       <c r="F229" t="s">
-        <v>801</v>
+        <v>860</v>
       </c>
       <c r="G229" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="H229" t="s">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="I229" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J229" t="s">
-        <v>861</v>
+        <v>338</v>
       </c>
       <c r="K229" t="s">
         <v>806</v>
@@ -11236,22 +11236,22 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
-        <v>337</v>
+        <v>859</v>
       </c>
       <c r="F230" t="s">
-        <v>801</v>
+        <v>860</v>
       </c>
       <c r="G230" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="H230" t="s">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="I230" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J230" t="s">
-        <v>861</v>
+        <v>338</v>
       </c>
       <c r="K230" t="s">
         <v>806</v>
@@ -11271,25 +11271,25 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
-        <v>337</v>
+        <v>623</v>
       </c>
       <c r="F231" t="s">
-        <v>564</v>
+        <v>860</v>
       </c>
       <c r="G231" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="H231" t="s">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="I231" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J231" t="s">
-        <v>623</v>
+        <v>338</v>
       </c>
       <c r="K231" t="s">
-        <v>806</v>
+        <v>569</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11306,25 +11306,25 @@
         <v>14</v>
       </c>
       <c r="E232" t="s">
-        <v>337</v>
+        <v>663</v>
       </c>
       <c r="F232" t="s">
-        <v>564</v>
+        <v>860</v>
       </c>
       <c r="G232" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="H232" t="s">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="I232" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J232" t="s">
-        <v>663</v>
+        <v>338</v>
       </c>
       <c r="K232" t="s">
-        <v>806</v>
+        <v>569</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11341,22 +11341,22 @@
         <v>14</v>
       </c>
       <c r="E233" t="s">
-        <v>337</v>
+        <v>859</v>
       </c>
       <c r="F233" t="s">
-        <v>801</v>
+        <v>860</v>
       </c>
       <c r="G233" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="H233" t="s">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="I233" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J233" t="s">
-        <v>861</v>
+        <v>338</v>
       </c>
       <c r="K233" t="s">
         <v>806</v>
@@ -11376,22 +11376,22 @@
         <v>14</v>
       </c>
       <c r="E234" t="s">
-        <v>337</v>
+        <v>859</v>
       </c>
       <c r="F234" t="s">
-        <v>801</v>
+        <v>860</v>
       </c>
       <c r="G234" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="H234" t="s">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="I234" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J234" t="s">
-        <v>861</v>
+        <v>338</v>
       </c>
       <c r="K234" t="s">
         <v>806</v>
@@ -11411,22 +11411,22 @@
         <v>14</v>
       </c>
       <c r="E235" t="s">
-        <v>337</v>
+        <v>859</v>
       </c>
       <c r="F235" t="s">
-        <v>801</v>
+        <v>860</v>
       </c>
       <c r="G235" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="H235" t="s">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="I235" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J235" t="s">
-        <v>861</v>
+        <v>338</v>
       </c>
       <c r="K235" t="s">
         <v>806</v>
@@ -11446,22 +11446,22 @@
         <v>14</v>
       </c>
       <c r="E236" t="s">
-        <v>337</v>
+        <v>859</v>
       </c>
       <c r="F236" t="s">
-        <v>801</v>
+        <v>860</v>
       </c>
       <c r="G236" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="H236" t="s">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="I236" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J236" t="s">
-        <v>861</v>
+        <v>338</v>
       </c>
       <c r="K236" t="s">
         <v>806</v>
@@ -11481,22 +11481,22 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
-        <v>337</v>
+        <v>859</v>
       </c>
       <c r="F237" t="s">
-        <v>801</v>
+        <v>860</v>
       </c>
       <c r="G237" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="H237" t="s">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="I237" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J237" t="s">
-        <v>861</v>
+        <v>338</v>
       </c>
       <c r="K237" t="s">
         <v>806</v>
@@ -11516,22 +11516,22 @@
         <v>14</v>
       </c>
       <c r="E238" t="s">
-        <v>337</v>
+        <v>859</v>
       </c>
       <c r="F238" t="s">
-        <v>801</v>
+        <v>860</v>
       </c>
       <c r="G238" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="H238" t="s">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="I238" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J238" t="s">
-        <v>861</v>
+        <v>338</v>
       </c>
       <c r="K238" t="s">
         <v>806</v>
@@ -11551,22 +11551,22 @@
         <v>14</v>
       </c>
       <c r="E239" t="s">
-        <v>337</v>
+        <v>892</v>
       </c>
       <c r="F239" t="s">
-        <v>801</v>
+        <v>893</v>
       </c>
       <c r="G239" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="H239" t="s">
-        <v>893</v>
+        <v>804</v>
       </c>
       <c r="I239" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J239" t="s">
-        <v>894</v>
+        <v>338</v>
       </c>
       <c r="K239" t="s">
         <v>806</v>
@@ -11589,22 +11589,22 @@
         <v>337</v>
       </c>
       <c r="F240" t="s">
-        <v>338</v>
+        <v>898</v>
       </c>
       <c r="G240" t="s">
+        <v>899</v>
+      </c>
+      <c r="H240" t="s">
         <v>898</v>
-      </c>
-      <c r="H240" t="s">
-        <v>899</v>
       </c>
       <c r="I240" t="s">
         <v>900</v>
       </c>
       <c r="J240" t="s">
+        <v>338</v>
+      </c>
+      <c r="K240" t="s">
         <v>339</v>
-      </c>
-      <c r="K240" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -11624,22 +11624,22 @@
         <v>337</v>
       </c>
       <c r="F241" t="s">
-        <v>338</v>
+        <v>898</v>
       </c>
       <c r="G241" t="s">
+        <v>899</v>
+      </c>
+      <c r="H241" t="s">
         <v>898</v>
-      </c>
-      <c r="H241" t="s">
-        <v>899</v>
       </c>
       <c r="I241" t="s">
         <v>900</v>
       </c>
       <c r="J241" t="s">
+        <v>338</v>
+      </c>
+      <c r="K241" t="s">
         <v>339</v>
-      </c>
-      <c r="K241" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -11659,22 +11659,22 @@
         <v>337</v>
       </c>
       <c r="F242" t="s">
-        <v>338</v>
+        <v>898</v>
       </c>
       <c r="G242" t="s">
+        <v>899</v>
+      </c>
+      <c r="H242" t="s">
         <v>898</v>
-      </c>
-      <c r="H242" t="s">
-        <v>899</v>
       </c>
       <c r="I242" t="s">
         <v>900</v>
       </c>
       <c r="J242" t="s">
+        <v>338</v>
+      </c>
+      <c r="K242" t="s">
         <v>339</v>
-      </c>
-      <c r="K242" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -11694,22 +11694,22 @@
         <v>337</v>
       </c>
       <c r="F243" t="s">
-        <v>338</v>
+        <v>898</v>
       </c>
       <c r="G243" t="s">
+        <v>899</v>
+      </c>
+      <c r="H243" t="s">
         <v>898</v>
-      </c>
-      <c r="H243" t="s">
-        <v>899</v>
       </c>
       <c r="I243" t="s">
         <v>900</v>
       </c>
       <c r="J243" t="s">
+        <v>338</v>
+      </c>
+      <c r="K243" t="s">
         <v>339</v>
-      </c>
-      <c r="K243" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -11729,22 +11729,22 @@
         <v>337</v>
       </c>
       <c r="F244" t="s">
-        <v>338</v>
+        <v>898</v>
       </c>
       <c r="G244" t="s">
+        <v>899</v>
+      </c>
+      <c r="H244" t="s">
         <v>898</v>
-      </c>
-      <c r="H244" t="s">
-        <v>899</v>
       </c>
       <c r="I244" t="s">
         <v>900</v>
       </c>
       <c r="J244" t="s">
+        <v>338</v>
+      </c>
+      <c r="K244" t="s">
         <v>339</v>
-      </c>
-      <c r="K244" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -11764,22 +11764,22 @@
         <v>337</v>
       </c>
       <c r="F245" t="s">
-        <v>338</v>
+        <v>898</v>
       </c>
       <c r="G245" t="s">
+        <v>899</v>
+      </c>
+      <c r="H245" t="s">
         <v>898</v>
-      </c>
-      <c r="H245" t="s">
-        <v>899</v>
       </c>
       <c r="I245" t="s">
         <v>900</v>
       </c>
       <c r="J245" t="s">
+        <v>338</v>
+      </c>
+      <c r="K245" t="s">
         <v>339</v>
-      </c>
-      <c r="K245" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -11793,25 +11793,25 @@
         <v>14</v>
       </c>
       <c r="E246" t="s">
-        <v>337</v>
+        <v>918</v>
       </c>
       <c r="F246" t="s">
-        <v>533</v>
+        <v>919</v>
       </c>
       <c r="G246" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="H246" t="s">
-        <v>919</v>
+        <v>898</v>
       </c>
       <c r="I246" t="s">
         <v>900</v>
       </c>
       <c r="J246" t="s">
-        <v>920</v>
+        <v>338</v>
       </c>
       <c r="K246" t="s">
-        <v>899</v>
+        <v>534</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11830,17 +11830,17 @@
       <c r="E247" t="s">
         <v>196</v>
       </c>
-      <c r="F247" t="s">
+      <c r="H247" t="s">
+        <v>924</v>
+      </c>
+      <c r="I247" t="s">
+        <v>925</v>
+      </c>
+      <c r="J247" t="s">
         <v>197</v>
       </c>
-      <c r="I247" t="s">
-        <v>924</v>
-      </c>
-      <c r="J247" t="s">
+      <c r="K247" t="s">
         <v>198</v>
-      </c>
-      <c r="K247" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -11859,17 +11859,17 @@
       <c r="E248" t="s">
         <v>196</v>
       </c>
-      <c r="F248" t="s">
+      <c r="H248" t="s">
+        <v>924</v>
+      </c>
+      <c r="I248" t="s">
+        <v>925</v>
+      </c>
+      <c r="J248" t="s">
         <v>197</v>
       </c>
-      <c r="I248" t="s">
-        <v>924</v>
-      </c>
-      <c r="J248" t="s">
+      <c r="K248" t="s">
         <v>198</v>
-      </c>
-      <c r="K248" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -11886,19 +11886,19 @@
         <v>14</v>
       </c>
       <c r="E249" t="s">
-        <v>196</v>
-      </c>
-      <c r="F249" t="s">
         <v>932</v>
       </c>
+      <c r="H249" t="s">
+        <v>924</v>
+      </c>
       <c r="I249" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="J249" t="s">
+        <v>197</v>
+      </c>
+      <c r="K249" t="s">
         <v>933</v>
-      </c>
-      <c r="K249" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -11917,17 +11917,17 @@
       <c r="E250" t="s">
         <v>196</v>
       </c>
-      <c r="F250" t="s">
+      <c r="H250" t="s">
+        <v>924</v>
+      </c>
+      <c r="I250" t="s">
+        <v>925</v>
+      </c>
+      <c r="J250" t="s">
         <v>197</v>
       </c>
-      <c r="I250" t="s">
-        <v>924</v>
-      </c>
-      <c r="J250" t="s">
+      <c r="K250" t="s">
         <v>198</v>
-      </c>
-      <c r="K250" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -11943,17 +11943,17 @@
       <c r="E251" t="s">
         <v>196</v>
       </c>
-      <c r="F251" t="s">
+      <c r="H251" t="s">
+        <v>924</v>
+      </c>
+      <c r="I251" t="s">
+        <v>925</v>
+      </c>
+      <c r="J251" t="s">
         <v>197</v>
       </c>
-      <c r="I251" t="s">
-        <v>924</v>
-      </c>
-      <c r="J251" t="s">
+      <c r="K251" t="s">
         <v>198</v>
-      </c>
-      <c r="K251" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -11972,17 +11972,17 @@
       <c r="E252" t="s">
         <v>196</v>
       </c>
-      <c r="F252" t="s">
+      <c r="H252" t="s">
+        <v>924</v>
+      </c>
+      <c r="I252" t="s">
+        <v>925</v>
+      </c>
+      <c r="J252" t="s">
         <v>197</v>
       </c>
-      <c r="I252" t="s">
-        <v>924</v>
-      </c>
-      <c r="J252" t="s">
+      <c r="K252" t="s">
         <v>198</v>
-      </c>
-      <c r="K252" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -11996,16 +11996,16 @@
         <v>14</v>
       </c>
       <c r="E253" t="s">
-        <v>337</v>
-      </c>
-      <c r="F253" t="s">
         <v>944</v>
       </c>
+      <c r="H253" t="s">
+        <v>945</v>
+      </c>
       <c r="I253" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J253" t="s">
-        <v>946</v>
+        <v>338</v>
       </c>
       <c r="K253" t="s">
         <v>947</v>
@@ -12025,19 +12025,19 @@
         <v>14</v>
       </c>
       <c r="E254" t="s">
-        <v>188</v>
-      </c>
-      <c r="F254" t="s">
         <v>454</v>
       </c>
+      <c r="H254" t="s">
+        <v>945</v>
+      </c>
       <c r="I254" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J254" t="s">
+        <v>191</v>
+      </c>
+      <c r="K254" t="s">
         <v>455</v>
-      </c>
-      <c r="K254" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -12054,19 +12054,19 @@
         <v>14</v>
       </c>
       <c r="E255" t="s">
-        <v>188</v>
-      </c>
-      <c r="F255" t="s">
         <v>954</v>
       </c>
+      <c r="H255" t="s">
+        <v>945</v>
+      </c>
       <c r="I255" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J255" t="s">
+        <v>191</v>
+      </c>
+      <c r="K255" t="s">
         <v>955</v>
-      </c>
-      <c r="K255" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -12083,19 +12083,19 @@
         <v>14</v>
       </c>
       <c r="E256" t="s">
-        <v>188</v>
-      </c>
-      <c r="F256" t="s">
         <v>954</v>
       </c>
+      <c r="H256" t="s">
+        <v>945</v>
+      </c>
       <c r="I256" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J256" t="s">
+        <v>191</v>
+      </c>
+      <c r="K256" t="s">
         <v>955</v>
-      </c>
-      <c r="K256" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -12112,19 +12112,19 @@
         <v>14</v>
       </c>
       <c r="E257" t="s">
-        <v>188</v>
-      </c>
-      <c r="F257" t="s">
         <v>954</v>
       </c>
+      <c r="H257" t="s">
+        <v>945</v>
+      </c>
       <c r="I257" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J257" t="s">
+        <v>191</v>
+      </c>
+      <c r="K257" t="s">
         <v>955</v>
-      </c>
-      <c r="K257" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -12141,19 +12141,19 @@
         <v>14</v>
       </c>
       <c r="E258" t="s">
-        <v>337</v>
-      </c>
-      <c r="F258" t="s">
         <v>705</v>
       </c>
+      <c r="H258" t="s">
+        <v>945</v>
+      </c>
       <c r="I258" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J258" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="K258" t="s">
-        <v>947</v>
+        <v>710</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -12170,19 +12170,19 @@
         <v>14</v>
       </c>
       <c r="E259" t="s">
-        <v>188</v>
-      </c>
-      <c r="F259" t="s">
         <v>954</v>
       </c>
+      <c r="H259" t="s">
+        <v>945</v>
+      </c>
       <c r="I259" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J259" t="s">
+        <v>191</v>
+      </c>
+      <c r="K259" t="s">
         <v>955</v>
-      </c>
-      <c r="K259" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -12201,17 +12201,17 @@
       <c r="E260" t="s">
         <v>337</v>
       </c>
-      <c r="F260" t="s">
+      <c r="H260" t="s">
+        <v>945</v>
+      </c>
+      <c r="I260" t="s">
+        <v>946</v>
+      </c>
+      <c r="J260" t="s">
         <v>338</v>
       </c>
-      <c r="I260" t="s">
-        <v>945</v>
-      </c>
-      <c r="J260" t="s">
+      <c r="K260" t="s">
         <v>339</v>
-      </c>
-      <c r="K260" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -12228,19 +12228,19 @@
         <v>14</v>
       </c>
       <c r="E261" t="s">
-        <v>405</v>
-      </c>
-      <c r="F261" t="s">
         <v>973</v>
       </c>
+      <c r="H261" t="s">
+        <v>945</v>
+      </c>
       <c r="I261" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J261" t="s">
+        <v>406</v>
+      </c>
+      <c r="K261" t="s">
         <v>974</v>
-      </c>
-      <c r="K261" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -12259,17 +12259,17 @@
       <c r="E262" t="s">
         <v>337</v>
       </c>
-      <c r="F262" t="s">
+      <c r="H262" t="s">
+        <v>945</v>
+      </c>
+      <c r="I262" t="s">
+        <v>946</v>
+      </c>
+      <c r="J262" t="s">
         <v>338</v>
       </c>
-      <c r="I262" t="s">
-        <v>945</v>
-      </c>
-      <c r="J262" t="s">
+      <c r="K262" t="s">
         <v>339</v>
-      </c>
-      <c r="K262" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -12286,19 +12286,19 @@
         <v>14</v>
       </c>
       <c r="E263" t="s">
-        <v>377</v>
-      </c>
-      <c r="F263" t="s">
         <v>981</v>
       </c>
+      <c r="H263" t="s">
+        <v>945</v>
+      </c>
       <c r="I263" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J263" t="s">
+        <v>378</v>
+      </c>
+      <c r="K263" t="s">
         <v>982</v>
-      </c>
-      <c r="K263" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="264" spans="1:11">
@@ -12317,17 +12317,17 @@
       <c r="E264" t="s">
         <v>58</v>
       </c>
-      <c r="F264" t="s">
+      <c r="H264" t="s">
+        <v>945</v>
+      </c>
+      <c r="I264" t="s">
+        <v>946</v>
+      </c>
+      <c r="J264" t="s">
         <v>59</v>
       </c>
-      <c r="I264" t="s">
-        <v>945</v>
-      </c>
-      <c r="J264" t="s">
+      <c r="K264" t="s">
         <v>60</v>
-      </c>
-      <c r="K264" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -12346,17 +12346,17 @@
       <c r="E265" t="s">
         <v>15</v>
       </c>
-      <c r="F265" t="s">
-        <v>16</v>
+      <c r="H265" t="s">
+        <v>945</v>
       </c>
       <c r="I265" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J265" t="s">
         <v>20</v>
       </c>
       <c r="K265" t="s">
-        <v>947</v>
+        <v>21</v>
       </c>
     </row>
     <row r="266" spans="1:11">
@@ -12373,19 +12373,19 @@
         <v>14</v>
       </c>
       <c r="E266" t="s">
-        <v>233</v>
-      </c>
-      <c r="F266" t="s">
         <v>992</v>
       </c>
+      <c r="H266" t="s">
+        <v>945</v>
+      </c>
       <c r="I266" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J266" t="s">
+        <v>238</v>
+      </c>
+      <c r="K266" t="s">
         <v>993</v>
-      </c>
-      <c r="K266" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="267" spans="1:11">
@@ -12402,19 +12402,19 @@
         <v>14</v>
       </c>
       <c r="E267" t="s">
-        <v>233</v>
-      </c>
-      <c r="F267" t="s">
         <v>243</v>
       </c>
+      <c r="H267" t="s">
+        <v>997</v>
+      </c>
       <c r="I267" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="J267" t="s">
+        <v>238</v>
+      </c>
+      <c r="K267" t="s">
         <v>244</v>
-      </c>
-      <c r="K267" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -12431,19 +12431,19 @@
         <v>14</v>
       </c>
       <c r="E268" t="s">
-        <v>377</v>
-      </c>
-      <c r="F268" t="s">
         <v>420</v>
       </c>
+      <c r="H268" t="s">
+        <v>1002</v>
+      </c>
       <c r="I268" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="J268" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K268" t="s">
-        <v>1003</v>
+        <v>423</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -12460,19 +12460,19 @@
         <v>14</v>
       </c>
       <c r="E269" t="s">
-        <v>233</v>
-      </c>
-      <c r="F269" t="s">
         <v>243</v>
       </c>
+      <c r="H269" t="s">
+        <v>1007</v>
+      </c>
       <c r="I269" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="J269" t="s">
+        <v>238</v>
+      </c>
+      <c r="K269" t="s">
         <v>244</v>
-      </c>
-      <c r="K269" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -12489,19 +12489,19 @@
         <v>14</v>
       </c>
       <c r="E270" t="s">
-        <v>233</v>
-      </c>
-      <c r="F270" t="s">
         <v>243</v>
       </c>
+      <c r="H270" t="s">
+        <v>1007</v>
+      </c>
       <c r="I270" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="J270" t="s">
+        <v>238</v>
+      </c>
+      <c r="K270" t="s">
         <v>244</v>
-      </c>
-      <c r="K270" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -12518,16 +12518,16 @@
         <v>14</v>
       </c>
       <c r="E271" t="s">
-        <v>233</v>
-      </c>
-      <c r="F271" t="s">
         <v>1015</v>
       </c>
+      <c r="H271" t="s">
+        <v>1016</v>
+      </c>
       <c r="I271" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="J271" t="s">
-        <v>1017</v>
+        <v>238</v>
       </c>
       <c r="K271" t="s">
         <v>1018</v>
@@ -12544,16 +12544,16 @@
         <v>14</v>
       </c>
       <c r="E272" t="s">
-        <v>233</v>
-      </c>
-      <c r="F272" t="s">
         <v>1015</v>
       </c>
+      <c r="H272" t="s">
+        <v>1016</v>
+      </c>
       <c r="I272" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="J272" t="s">
-        <v>1017</v>
+        <v>238</v>
       </c>
       <c r="K272" t="s">
         <v>1018</v>
@@ -12573,16 +12573,16 @@
         <v>14</v>
       </c>
       <c r="E273" t="s">
-        <v>233</v>
-      </c>
-      <c r="F273" t="s">
         <v>1015</v>
       </c>
+      <c r="H273" t="s">
+        <v>1016</v>
+      </c>
       <c r="I273" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="J273" t="s">
-        <v>1017</v>
+        <v>238</v>
       </c>
       <c r="K273" t="s">
         <v>1018</v>
@@ -12599,16 +12599,16 @@
         <v>14</v>
       </c>
       <c r="E274" t="s">
-        <v>233</v>
-      </c>
-      <c r="F274" t="s">
         <v>1015</v>
       </c>
+      <c r="H274" t="s">
+        <v>1016</v>
+      </c>
       <c r="I274" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="J274" t="s">
-        <v>1017</v>
+        <v>238</v>
       </c>
       <c r="K274" t="s">
         <v>1018</v>
@@ -12628,16 +12628,16 @@
         <v>14</v>
       </c>
       <c r="E275" t="s">
-        <v>233</v>
-      </c>
-      <c r="F275" t="s">
         <v>1015</v>
       </c>
+      <c r="H275" t="s">
+        <v>1016</v>
+      </c>
       <c r="I275" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="J275" t="s">
-        <v>1017</v>
+        <v>238</v>
       </c>
       <c r="K275" t="s">
         <v>1018</v>
@@ -12657,16 +12657,16 @@
         <v>14</v>
       </c>
       <c r="E276" t="s">
-        <v>233</v>
-      </c>
-      <c r="F276" t="s">
         <v>1015</v>
       </c>
+      <c r="H276" t="s">
+        <v>1016</v>
+      </c>
       <c r="I276" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="J276" t="s">
-        <v>1017</v>
+        <v>238</v>
       </c>
       <c r="K276" t="s">
         <v>1018</v>
@@ -12686,16 +12686,16 @@
         <v>14</v>
       </c>
       <c r="E277" t="s">
-        <v>233</v>
-      </c>
-      <c r="F277" t="s">
         <v>1015</v>
       </c>
+      <c r="H277" t="s">
+        <v>1016</v>
+      </c>
       <c r="I277" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="J277" t="s">
-        <v>1017</v>
+        <v>238</v>
       </c>
       <c r="K277" t="s">
         <v>1018</v>
@@ -12715,19 +12715,19 @@
         <v>14</v>
       </c>
       <c r="E278" t="s">
-        <v>377</v>
-      </c>
-      <c r="F278" t="s">
         <v>420</v>
       </c>
+      <c r="H278" t="s">
+        <v>1038</v>
+      </c>
       <c r="I278" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="J278" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="K278" t="s">
-        <v>1039</v>
+        <v>423</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -12744,19 +12744,19 @@
         <v>14</v>
       </c>
       <c r="E279" t="s">
-        <v>58</v>
-      </c>
-      <c r="F279" t="s">
         <v>92</v>
       </c>
+      <c r="H279" t="s">
+        <v>1038</v>
+      </c>
       <c r="I279" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="J279" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="K279" t="s">
-        <v>1039</v>
+        <v>97</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -12775,17 +12775,17 @@
       <c r="E280" t="s">
         <v>15</v>
       </c>
-      <c r="F280" t="s">
-        <v>16</v>
+      <c r="H280" t="s">
+        <v>1038</v>
       </c>
       <c r="I280" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="J280" t="s">
         <v>20</v>
       </c>
       <c r="K280" t="s">
-        <v>1039</v>
+        <v>21</v>
       </c>
     </row>
     <row r="281" spans="1:11">
@@ -12802,19 +12802,19 @@
         <v>14</v>
       </c>
       <c r="E281" t="s">
-        <v>233</v>
-      </c>
-      <c r="F281" t="s">
         <v>352</v>
       </c>
+      <c r="H281" t="s">
+        <v>1038</v>
+      </c>
       <c r="I281" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="J281" t="s">
+        <v>238</v>
+      </c>
+      <c r="K281" t="s">
         <v>353</v>
-      </c>
-      <c r="K281" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -12833,17 +12833,17 @@
       <c r="E282" t="s">
         <v>253</v>
       </c>
-      <c r="F282" t="s">
+      <c r="H282" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I282" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J282" t="s">
         <v>254</v>
       </c>
-      <c r="I282" t="s">
-        <v>1038</v>
-      </c>
-      <c r="J282" t="s">
+      <c r="K282" t="s">
         <v>255</v>
-      </c>
-      <c r="K282" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -12860,19 +12860,19 @@
         <v>14</v>
       </c>
       <c r="E283" t="s">
-        <v>337</v>
-      </c>
-      <c r="F283" t="s">
-        <v>801</v>
+        <v>892</v>
+      </c>
+      <c r="H283" t="s">
+        <v>1055</v>
       </c>
       <c r="I283" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="J283" t="s">
-        <v>894</v>
+        <v>338</v>
       </c>
       <c r="K283" t="s">
-        <v>1056</v>
+        <v>806</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -12891,17 +12891,17 @@
       <c r="E284" t="s">
         <v>253</v>
       </c>
-      <c r="F284" t="s">
+      <c r="H284" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I284" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J284" t="s">
         <v>254</v>
       </c>
-      <c r="I284" t="s">
-        <v>1060</v>
-      </c>
-      <c r="J284" t="s">
+      <c r="K284" t="s">
         <v>255</v>
-      </c>
-      <c r="K284" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -12915,19 +12915,19 @@
         <v>14</v>
       </c>
       <c r="E285" t="s">
-        <v>233</v>
-      </c>
-      <c r="F285" t="s">
         <v>352</v>
       </c>
+      <c r="H285" t="s">
+        <v>1064</v>
+      </c>
       <c r="I285" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J285" t="s">
+        <v>238</v>
+      </c>
+      <c r="K285" t="s">
         <v>353</v>
-      </c>
-      <c r="K285" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -12944,19 +12944,19 @@
         <v>14</v>
       </c>
       <c r="E286" t="s">
-        <v>377</v>
-      </c>
-      <c r="F286" t="s">
         <v>981</v>
       </c>
+      <c r="H286" t="s">
+        <v>1069</v>
+      </c>
       <c r="I286" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J286" t="s">
+        <v>378</v>
+      </c>
+      <c r="K286" t="s">
         <v>982</v>
-      </c>
-      <c r="K286" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -12973,19 +12973,19 @@
         <v>14</v>
       </c>
       <c r="E287" t="s">
-        <v>377</v>
-      </c>
-      <c r="F287" t="s">
         <v>981</v>
       </c>
+      <c r="H287" t="s">
+        <v>1069</v>
+      </c>
       <c r="I287" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J287" t="s">
+        <v>378</v>
+      </c>
+      <c r="K287" t="s">
         <v>982</v>
-      </c>
-      <c r="K287" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -13002,19 +13002,19 @@
         <v>14</v>
       </c>
       <c r="E288" t="s">
-        <v>15</v>
-      </c>
-      <c r="F288" t="s">
         <v>75</v>
       </c>
+      <c r="H288" t="s">
+        <v>1069</v>
+      </c>
       <c r="I288" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J288" t="s">
+        <v>20</v>
+      </c>
+      <c r="K288" t="s">
         <v>76</v>
-      </c>
-      <c r="K288" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -13033,17 +13033,17 @@
       <c r="E289" t="s">
         <v>58</v>
       </c>
-      <c r="F289" t="s">
+      <c r="H289" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I289" t="s">
+        <v>1070</v>
+      </c>
+      <c r="J289" t="s">
         <v>59</v>
       </c>
-      <c r="I289" t="s">
-        <v>1069</v>
-      </c>
-      <c r="J289" t="s">
+      <c r="K289" t="s">
         <v>60</v>
-      </c>
-      <c r="K289" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="290" spans="1:11">
@@ -13062,17 +13062,17 @@
       <c r="E290" t="s">
         <v>58</v>
       </c>
-      <c r="F290" t="s">
+      <c r="H290" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I290" t="s">
+        <v>1070</v>
+      </c>
+      <c r="J290" t="s">
         <v>59</v>
       </c>
-      <c r="I290" t="s">
-        <v>1069</v>
-      </c>
-      <c r="J290" t="s">
+      <c r="K290" t="s">
         <v>60</v>
-      </c>
-      <c r="K290" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -13089,19 +13089,19 @@
         <v>14</v>
       </c>
       <c r="E291" t="s">
-        <v>233</v>
-      </c>
-      <c r="F291" t="s">
         <v>352</v>
       </c>
+      <c r="H291" t="s">
+        <v>1069</v>
+      </c>
       <c r="I291" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J291" t="s">
+        <v>238</v>
+      </c>
+      <c r="K291" t="s">
         <v>353</v>
-      </c>
-      <c r="K291" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -13118,19 +13118,19 @@
         <v>14</v>
       </c>
       <c r="E292" t="s">
-        <v>233</v>
-      </c>
-      <c r="F292" t="s">
         <v>352</v>
       </c>
+      <c r="H292" t="s">
+        <v>1069</v>
+      </c>
       <c r="I292" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J292" t="s">
+        <v>238</v>
+      </c>
+      <c r="K292" t="s">
         <v>353</v>
-      </c>
-      <c r="K292" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -13147,19 +13147,19 @@
         <v>14</v>
       </c>
       <c r="E293" t="s">
-        <v>233</v>
-      </c>
-      <c r="F293" t="s">
         <v>352</v>
       </c>
+      <c r="H293" t="s">
+        <v>1069</v>
+      </c>
       <c r="I293" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J293" t="s">
+        <v>238</v>
+      </c>
+      <c r="K293" t="s">
         <v>353</v>
-      </c>
-      <c r="K293" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -13176,19 +13176,19 @@
         <v>14</v>
       </c>
       <c r="E294" t="s">
-        <v>233</v>
-      </c>
-      <c r="F294" t="s">
         <v>352</v>
       </c>
+      <c r="H294" t="s">
+        <v>1069</v>
+      </c>
       <c r="I294" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J294" t="s">
+        <v>238</v>
+      </c>
+      <c r="K294" t="s">
         <v>353</v>
-      </c>
-      <c r="K294" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -13205,19 +13205,19 @@
         <v>14</v>
       </c>
       <c r="E295" t="s">
-        <v>233</v>
-      </c>
-      <c r="F295" t="s">
         <v>352</v>
       </c>
+      <c r="H295" t="s">
+        <v>1098</v>
+      </c>
       <c r="I295" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J295" t="s">
+        <v>238</v>
+      </c>
+      <c r="K295" t="s">
         <v>353</v>
-      </c>
-      <c r="K295" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="296" spans="1:11">
@@ -13234,19 +13234,19 @@
         <v>14</v>
       </c>
       <c r="E296" t="s">
-        <v>233</v>
-      </c>
-      <c r="F296" t="s">
         <v>352</v>
       </c>
+      <c r="H296" t="s">
+        <v>1098</v>
+      </c>
       <c r="I296" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J296" t="s">
+        <v>238</v>
+      </c>
+      <c r="K296" t="s">
         <v>353</v>
-      </c>
-      <c r="K296" t="s">
-        <v>1099</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -28,27 +28,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -61,27 +61,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
     <t>Education</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -133,15 +133,15 @@
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>Basic Education</t>
   </si>
   <si>
     <t>112</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -190,12 +190,12 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
@@ -259,15 +259,15 @@
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
     <t>114</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -295,21 +295,21 @@
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
     <t>Health</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -520,12 +520,12 @@
     <t>Population/development policies; demographic research/analysis; reproductive health research; unspecified population activities. (Use purpose code 15190 for data on migration and refugees. Use code 13096 for census work, vital registration and migration data collection.)</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -580,21 +580,21 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
@@ -715,27 +715,27 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -775,12 +775,12 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
@@ -1027,12 +1027,12 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
@@ -1147,12 +1147,12 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
@@ -1231,12 +1231,12 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
@@ -1279,15 +1279,15 @@
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1402,12 +1402,12 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
@@ -1486,12 +1486,12 @@
     <t>Transport sector policy, planning and programmes; aid to transport ministries; institution capacity building and advice; unspecified transport; activities that combine road, rail, water and/or air transport. Includes prevention of road accidents. Whenever possible, report transport of goods under the sector of the good being transported.</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21011</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>Communications sector policy, planning and programmes; institution capacity building and advice; including postal services development; unspecified communications activities.</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22011</t>
   </si>
   <si>
@@ -1711,21 +1711,21 @@
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -2032,12 +2032,12 @@
     <t>Finance sector policy, planning and programmes; institution capacity building and advice; financial markets and systems.</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -2089,12 +2089,12 @@
     <t>Public sector policies and institution support to the business environment and investment climate, including business regulations, property rights, non-discrimination, investment promotion, competition policy, enterprises law, private-public partnerships.</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -2134,21 +2134,21 @@
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2422,21 +2422,21 @@
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2713,12 +2713,12 @@
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -2788,12 +2788,12 @@
     <t>Environmental policy, laws, regulations and economic instruments; administrational institutions and practices; environmental and land use planning and decision-making procedures; seminars, meetings; miscellaneous conservation and protection measures not specified below.</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -2851,15 +2851,15 @@
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -3007,12 +3007,12 @@
     <t>Unearmarked contributions to the government budget; support for the implementation of macroeconomic reforms (structural adjustment programmes, poverty reduction strategies); general programme assistance (when not allocable by sector).</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
@@ -3022,12 +3022,12 @@
     <t>Supply of edible human food under national or international programmes including transport costs, cash payments made for food supplies; project food assistance aid and food assistance aid for market sales when benefiting sector not specified. Excludes food security policy and administrative management (43071), household food security programmes (43072) and emergency food assistance aid (72040). Report as multilateral: i) food assistance aid by EU financed out of its budget and allocated pro rata to EU member countries; and ii) core contributions to the World Food Programme.</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
@@ -3037,12 +3037,12 @@
     <t>Capital goods and services; lines of credit.</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -3064,15 +3064,15 @@
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -3130,12 +3130,12 @@
     <t>Shelter, water, sanitation, education, health services including supply of medicines and malnutrition management, including medical nutrition management; supply of other nonfood relief items (including cash and voucher delivery modalities) for the benefit of crisisaffected people, including refugees and internally displaced people in developing countries, Includes assistance delivered by or coordinated by international civil protection units in the immediate aftermath of a disaster (in-kind assistance, deployment of specially-equipped teams, logistics and transportation, or assessment and coordination by experts sent to the field). Also includes measures to promote and protect the safety, well-being, dignity and integrity of crisis-affected people including refugees and internally displaced persons in developing countries. (Activities designed to protect the security of persons or properties through the use or display of force are not reportable as ODA.)</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72011</t>
   </si>
   <si>
@@ -3181,12 +3181,12 @@
     <t>Social and economic rehabilitation in the aftermath of emergencies to facilitate recovery and resilience building and enable populations to restore their livelihoods in the wake of an emergency situation (e.g. trauma counselling and treatment, employment programmes). Includes infrastructure necessary for the delivery of humanitarian aid; restoring pre-existing essential infrastructure and facilities (e.g. water and sanitation, shelter, health care services, education); rehabilitation of basic agricultural inputs and livestock. Excludes longer-term reconstruction ('build back better') which is reportable against relevant sectors.</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
@@ -3196,24 +3196,24 @@
     <t>Building the responsiveness, capability and capacity of international, regional and national humanitarian actors to disasters. Support to the institutional capacities of national and local government, specialised humanitarian bodies, and civil society organisations to anticipate, respond and recover from the impact of potential, imminent and current hazardous events and emergency situations that pose humanitarian threats and could call for a humanitarian response. This includes risk analysis and assessment, mitigation, preparedness, such as stockpiling of emergency items and training and capacity building aimed to increase the speed and effectiveness of lifesaving assistance delivered in the occurrence of crisis.</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
@@ -3223,12 +3223,12 @@
     <t>Costs incurred in donor countries for basic assistance to asylum seekers and refugees from developing countries, up to 12 months, when costs cannot be disaggregated. See section II.6 and Annex 17.</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>93011</t>
   </si>
   <si>
@@ -3310,10 +3310,10 @@
     <t>Contributions to general development of the recipient should be included under programme assistance (51010).</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -3741,13 +3741,13 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -3759,7 +3759,7 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3811,13 +3811,13 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
         <v>33</v>
       </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
@@ -3829,7 +3829,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3846,25 +3846,25 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>39</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>40</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
       </c>
       <c r="I6" t="s">
         <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3884,19 +3884,19 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
         <v>40</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
       </c>
       <c r="I7" t="s">
         <v>19</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -3916,25 +3916,25 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>39</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>40</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3951,25 +3951,25 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
         <v>38</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>39</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>40</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3986,25 +3986,25 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
         <v>54</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>39</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>40</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K10" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4024,22 +4024,22 @@
         <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" t="s">
         <v>40</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="K11" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4056,25 +4056,25 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
         <v>64</v>
       </c>
-      <c r="F12" t="s">
-        <v>39</v>
-      </c>
       <c r="G12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" t="s">
         <v>40</v>
-      </c>
-      <c r="H12" t="s">
-        <v>18</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K12" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4091,25 +4091,25 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
         <v>69</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" t="s">
         <v>70</v>
-      </c>
-      <c r="G13" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" t="s">
-        <v>18</v>
       </c>
       <c r="I13" t="s">
         <v>19</v>
       </c>
       <c r="J13" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="K13" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4126,25 +4126,25 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
         <v>75</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" t="s">
         <v>70</v>
-      </c>
-      <c r="G14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" t="s">
-        <v>18</v>
       </c>
       <c r="I14" t="s">
         <v>19</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="K14" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4161,25 +4161,25 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
         <v>80</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>81</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>82</v>
-      </c>
-      <c r="H15" t="s">
-        <v>18</v>
       </c>
       <c r="I15" t="s">
         <v>19</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="K15" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4196,25 +4196,25 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
         <v>87</v>
       </c>
-      <c r="F16" t="s">
-        <v>81</v>
-      </c>
       <c r="G16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" t="s">
         <v>82</v>
-      </c>
-      <c r="H16" t="s">
-        <v>18</v>
       </c>
       <c r="I16" t="s">
         <v>19</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4231,22 +4231,22 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" t="s">
         <v>92</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>93</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>94</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>95</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>96</v>
-      </c>
-      <c r="J17" t="s">
-        <v>59</v>
       </c>
       <c r="K17" t="s">
         <v>97</v>
@@ -4266,22 +4266,22 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" t="s">
         <v>92</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>93</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>94</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>95</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>96</v>
-      </c>
-      <c r="J18" t="s">
-        <v>59</v>
       </c>
       <c r="K18" t="s">
         <v>97</v>
@@ -4301,25 +4301,25 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" t="s">
         <v>104</v>
       </c>
-      <c r="F19" t="s">
-        <v>93</v>
-      </c>
       <c r="G19" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" t="s">
         <v>94</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>95</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>96</v>
       </c>
-      <c r="J19" t="s">
-        <v>59</v>
-      </c>
       <c r="K19" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4336,25 +4336,25 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" t="s">
         <v>109</v>
       </c>
-      <c r="F20" t="s">
-        <v>93</v>
-      </c>
       <c r="G20" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" t="s">
         <v>94</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>95</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>96</v>
       </c>
-      <c r="J20" t="s">
-        <v>59</v>
-      </c>
       <c r="K20" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4371,22 +4371,22 @@
         <v>14</v>
       </c>
       <c r="E21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" t="s">
         <v>92</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>93</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>94</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>95</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>96</v>
-      </c>
-      <c r="J21" t="s">
-        <v>59</v>
       </c>
       <c r="K21" t="s">
         <v>97</v>
@@ -4409,22 +4409,22 @@
         <v>58</v>
       </c>
       <c r="F22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" t="s">
         <v>117</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
+        <v>95</v>
+      </c>
+      <c r="J22" t="s">
         <v>118</v>
       </c>
-      <c r="H22" t="s">
-        <v>95</v>
-      </c>
-      <c r="I22" t="s">
-        <v>96</v>
-      </c>
-      <c r="J22" t="s">
-        <v>59</v>
-      </c>
       <c r="K22" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4441,25 +4441,25 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" t="s">
         <v>122</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" t="s">
         <v>117</v>
       </c>
-      <c r="G23" t="s">
+      <c r="I23" t="s">
+        <v>95</v>
+      </c>
+      <c r="J23" t="s">
         <v>118</v>
       </c>
-      <c r="H23" t="s">
-        <v>95</v>
-      </c>
-      <c r="I23" t="s">
-        <v>96</v>
-      </c>
-      <c r="J23" t="s">
-        <v>59</v>
-      </c>
       <c r="K23" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4479,22 +4479,22 @@
         <v>58</v>
       </c>
       <c r="F24" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
         <v>117</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" t="s">
+        <v>95</v>
+      </c>
+      <c r="J24" t="s">
         <v>118</v>
       </c>
-      <c r="H24" t="s">
-        <v>95</v>
-      </c>
-      <c r="I24" t="s">
-        <v>96</v>
-      </c>
-      <c r="J24" t="s">
-        <v>59</v>
-      </c>
       <c r="K24" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4514,22 +4514,22 @@
         <v>58</v>
       </c>
       <c r="F25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" t="s">
+        <v>60</v>
+      </c>
+      <c r="H25" t="s">
         <v>117</v>
       </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
+        <v>95</v>
+      </c>
+      <c r="J25" t="s">
         <v>118</v>
       </c>
-      <c r="H25" t="s">
-        <v>95</v>
-      </c>
-      <c r="I25" t="s">
-        <v>96</v>
-      </c>
-      <c r="J25" t="s">
-        <v>59</v>
-      </c>
       <c r="K25" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4549,22 +4549,22 @@
         <v>58</v>
       </c>
       <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" t="s">
+        <v>60</v>
+      </c>
+      <c r="H26" t="s">
         <v>117</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
+        <v>95</v>
+      </c>
+      <c r="J26" t="s">
         <v>118</v>
       </c>
-      <c r="H26" t="s">
-        <v>95</v>
-      </c>
-      <c r="I26" t="s">
-        <v>96</v>
-      </c>
-      <c r="J26" t="s">
-        <v>59</v>
-      </c>
       <c r="K26" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4584,22 +4584,22 @@
         <v>58</v>
       </c>
       <c r="F27" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" t="s">
+        <v>60</v>
+      </c>
+      <c r="H27" t="s">
         <v>117</v>
       </c>
-      <c r="G27" t="s">
+      <c r="I27" t="s">
+        <v>95</v>
+      </c>
+      <c r="J27" t="s">
         <v>118</v>
       </c>
-      <c r="H27" t="s">
-        <v>95</v>
-      </c>
-      <c r="I27" t="s">
-        <v>96</v>
-      </c>
-      <c r="J27" t="s">
-        <v>59</v>
-      </c>
       <c r="K27" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4619,22 +4619,22 @@
         <v>58</v>
       </c>
       <c r="F28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" t="s">
         <v>117</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
+        <v>95</v>
+      </c>
+      <c r="J28" t="s">
         <v>118</v>
       </c>
-      <c r="H28" t="s">
-        <v>95</v>
-      </c>
-      <c r="I28" t="s">
-        <v>96</v>
-      </c>
-      <c r="J28" t="s">
-        <v>59</v>
-      </c>
       <c r="K28" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4654,22 +4654,22 @@
         <v>58</v>
       </c>
       <c r="F29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" t="s">
+        <v>60</v>
+      </c>
+      <c r="H29" t="s">
         <v>117</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" t="s">
+        <v>95</v>
+      </c>
+      <c r="J29" t="s">
         <v>118</v>
       </c>
-      <c r="H29" t="s">
-        <v>95</v>
-      </c>
-      <c r="I29" t="s">
-        <v>96</v>
-      </c>
-      <c r="J29" t="s">
-        <v>59</v>
-      </c>
       <c r="K29" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4686,22 +4686,22 @@
         <v>14</v>
       </c>
       <c r="E30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" t="s">
         <v>92</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
+        <v>93</v>
+      </c>
+      <c r="H30" t="s">
         <v>117</v>
       </c>
-      <c r="G30" t="s">
+      <c r="I30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J30" t="s">
         <v>118</v>
-      </c>
-      <c r="H30" t="s">
-        <v>95</v>
-      </c>
-      <c r="I30" t="s">
-        <v>96</v>
-      </c>
-      <c r="J30" t="s">
-        <v>59</v>
       </c>
       <c r="K30" t="s">
         <v>97</v>
@@ -4724,22 +4724,22 @@
         <v>58</v>
       </c>
       <c r="F31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" t="s">
+        <v>60</v>
+      </c>
+      <c r="H31" t="s">
         <v>148</v>
       </c>
-      <c r="G31" t="s">
+      <c r="I31" t="s">
+        <v>95</v>
+      </c>
+      <c r="J31" t="s">
         <v>149</v>
       </c>
-      <c r="H31" t="s">
-        <v>95</v>
-      </c>
-      <c r="I31" t="s">
-        <v>96</v>
-      </c>
-      <c r="J31" t="s">
-        <v>59</v>
-      </c>
       <c r="K31" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4759,22 +4759,22 @@
         <v>58</v>
       </c>
       <c r="F32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H32" t="s">
         <v>148</v>
       </c>
-      <c r="G32" t="s">
+      <c r="I32" t="s">
+        <v>95</v>
+      </c>
+      <c r="J32" t="s">
         <v>149</v>
       </c>
-      <c r="H32" t="s">
-        <v>95</v>
-      </c>
-      <c r="I32" t="s">
-        <v>96</v>
-      </c>
-      <c r="J32" t="s">
-        <v>59</v>
-      </c>
       <c r="K32" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4794,22 +4794,22 @@
         <v>58</v>
       </c>
       <c r="F33" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" t="s">
+        <v>60</v>
+      </c>
+      <c r="H33" t="s">
         <v>148</v>
       </c>
-      <c r="G33" t="s">
+      <c r="I33" t="s">
+        <v>95</v>
+      </c>
+      <c r="J33" t="s">
         <v>149</v>
       </c>
-      <c r="H33" t="s">
-        <v>95</v>
-      </c>
-      <c r="I33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J33" t="s">
-        <v>59</v>
-      </c>
       <c r="K33" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4829,22 +4829,22 @@
         <v>58</v>
       </c>
       <c r="F34" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" t="s">
+        <v>60</v>
+      </c>
+      <c r="H34" t="s">
         <v>148</v>
       </c>
-      <c r="G34" t="s">
+      <c r="I34" t="s">
+        <v>95</v>
+      </c>
+      <c r="J34" t="s">
         <v>149</v>
       </c>
-      <c r="H34" t="s">
-        <v>95</v>
-      </c>
-      <c r="I34" t="s">
-        <v>96</v>
-      </c>
-      <c r="J34" t="s">
-        <v>59</v>
-      </c>
       <c r="K34" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4864,22 +4864,22 @@
         <v>58</v>
       </c>
       <c r="F35" t="s">
+        <v>59</v>
+      </c>
+      <c r="G35" t="s">
+        <v>60</v>
+      </c>
+      <c r="H35" t="s">
         <v>148</v>
       </c>
-      <c r="G35" t="s">
+      <c r="I35" t="s">
+        <v>95</v>
+      </c>
+      <c r="J35" t="s">
         <v>149</v>
       </c>
-      <c r="H35" t="s">
-        <v>95</v>
-      </c>
-      <c r="I35" t="s">
-        <v>96</v>
-      </c>
-      <c r="J35" t="s">
-        <v>59</v>
-      </c>
       <c r="K35" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4896,25 +4896,25 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" t="s">
         <v>104</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
+        <v>105</v>
+      </c>
+      <c r="H36" t="s">
         <v>148</v>
       </c>
-      <c r="G36" t="s">
+      <c r="I36" t="s">
+        <v>95</v>
+      </c>
+      <c r="J36" t="s">
         <v>149</v>
       </c>
-      <c r="H36" t="s">
-        <v>95</v>
-      </c>
-      <c r="I36" t="s">
-        <v>96</v>
-      </c>
-      <c r="J36" t="s">
-        <v>59</v>
-      </c>
       <c r="K36" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4933,17 +4933,17 @@
       <c r="E37" t="s">
         <v>58</v>
       </c>
-      <c r="H37" t="s">
+      <c r="F37" t="s">
+        <v>59</v>
+      </c>
+      <c r="G37" t="s">
+        <v>60</v>
+      </c>
+      <c r="I37" t="s">
         <v>168</v>
       </c>
-      <c r="I37" t="s">
+      <c r="K37" t="s">
         <v>169</v>
-      </c>
-      <c r="J37" t="s">
-        <v>59</v>
-      </c>
-      <c r="K37" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4962,17 +4962,17 @@
       <c r="E38" t="s">
         <v>58</v>
       </c>
-      <c r="H38" t="s">
+      <c r="F38" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" t="s">
+        <v>60</v>
+      </c>
+      <c r="I38" t="s">
         <v>168</v>
       </c>
-      <c r="I38" t="s">
+      <c r="K38" t="s">
         <v>169</v>
-      </c>
-      <c r="J38" t="s">
-        <v>59</v>
-      </c>
-      <c r="K38" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4991,17 +4991,17 @@
       <c r="E39" t="s">
         <v>58</v>
       </c>
-      <c r="H39" t="s">
+      <c r="F39" t="s">
+        <v>59</v>
+      </c>
+      <c r="G39" t="s">
+        <v>60</v>
+      </c>
+      <c r="I39" t="s">
         <v>168</v>
       </c>
-      <c r="I39" t="s">
+      <c r="K39" t="s">
         <v>169</v>
-      </c>
-      <c r="J39" t="s">
-        <v>59</v>
-      </c>
-      <c r="K39" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5020,17 +5020,17 @@
       <c r="E40" t="s">
         <v>58</v>
       </c>
-      <c r="H40" t="s">
+      <c r="F40" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40" t="s">
+        <v>60</v>
+      </c>
+      <c r="I40" t="s">
         <v>168</v>
       </c>
-      <c r="I40" t="s">
+      <c r="K40" t="s">
         <v>169</v>
-      </c>
-      <c r="J40" t="s">
-        <v>59</v>
-      </c>
-      <c r="K40" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5047,19 +5047,19 @@
         <v>14</v>
       </c>
       <c r="E41" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" t="s">
         <v>92</v>
       </c>
-      <c r="H41" t="s">
+      <c r="G41" t="s">
+        <v>93</v>
+      </c>
+      <c r="I41" t="s">
         <v>168</v>
       </c>
-      <c r="I41" t="s">
+      <c r="K41" t="s">
         <v>169</v>
-      </c>
-      <c r="J41" t="s">
-        <v>59</v>
-      </c>
-      <c r="K41" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5076,19 +5076,19 @@
         <v>14</v>
       </c>
       <c r="E42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42" t="s">
         <v>104</v>
       </c>
-      <c r="H42" t="s">
+      <c r="G42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I42" t="s">
         <v>168</v>
       </c>
-      <c r="I42" t="s">
+      <c r="K42" t="s">
         <v>169</v>
-      </c>
-      <c r="J42" t="s">
-        <v>59</v>
-      </c>
-      <c r="K42" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5107,13 +5107,13 @@
       <c r="E43" t="s">
         <v>188</v>
       </c>
-      <c r="H43" t="s">
+      <c r="F43" t="s">
         <v>189</v>
       </c>
+      <c r="G43" t="s">
+        <v>190</v>
+      </c>
       <c r="I43" t="s">
-        <v>190</v>
-      </c>
-      <c r="J43" t="s">
         <v>191</v>
       </c>
       <c r="K43" t="s">
@@ -5136,17 +5136,17 @@
       <c r="E44" t="s">
         <v>196</v>
       </c>
-      <c r="H44" t="s">
-        <v>189</v>
+      <c r="F44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G44" t="s">
+        <v>198</v>
       </c>
       <c r="I44" t="s">
-        <v>190</v>
-      </c>
-      <c r="J44" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K44" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5165,13 +5165,13 @@
       <c r="E45" t="s">
         <v>188</v>
       </c>
-      <c r="H45" t="s">
+      <c r="F45" t="s">
         <v>189</v>
       </c>
+      <c r="G45" t="s">
+        <v>190</v>
+      </c>
       <c r="I45" t="s">
-        <v>190</v>
-      </c>
-      <c r="J45" t="s">
         <v>191</v>
       </c>
       <c r="K45" t="s">
@@ -5194,13 +5194,13 @@
       <c r="E46" t="s">
         <v>188</v>
       </c>
-      <c r="H46" t="s">
+      <c r="F46" t="s">
         <v>189</v>
       </c>
+      <c r="G46" t="s">
+        <v>190</v>
+      </c>
       <c r="I46" t="s">
-        <v>190</v>
-      </c>
-      <c r="J46" t="s">
         <v>191</v>
       </c>
       <c r="K46" t="s">
@@ -5221,19 +5221,19 @@
         <v>14</v>
       </c>
       <c r="E47" t="s">
+        <v>196</v>
+      </c>
+      <c r="F47" t="s">
         <v>208</v>
       </c>
-      <c r="H47" t="s">
-        <v>189</v>
+      <c r="G47" t="s">
+        <v>209</v>
       </c>
       <c r="I47" t="s">
-        <v>190</v>
-      </c>
-      <c r="J47" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K47" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5252,13 +5252,13 @@
       <c r="E48" t="s">
         <v>188</v>
       </c>
-      <c r="H48" t="s">
+      <c r="F48" t="s">
         <v>189</v>
       </c>
+      <c r="G48" t="s">
+        <v>190</v>
+      </c>
       <c r="I48" t="s">
-        <v>190</v>
-      </c>
-      <c r="J48" t="s">
         <v>191</v>
       </c>
       <c r="K48" t="s">
@@ -5281,13 +5281,13 @@
       <c r="E49" t="s">
         <v>188</v>
       </c>
-      <c r="H49" t="s">
+      <c r="F49" t="s">
         <v>189</v>
       </c>
+      <c r="G49" t="s">
+        <v>190</v>
+      </c>
       <c r="I49" t="s">
-        <v>190</v>
-      </c>
-      <c r="J49" t="s">
         <v>191</v>
       </c>
       <c r="K49" t="s">
@@ -5308,19 +5308,19 @@
         <v>14</v>
       </c>
       <c r="E50" t="s">
+        <v>196</v>
+      </c>
+      <c r="F50" t="s">
         <v>208</v>
       </c>
-      <c r="H50" t="s">
-        <v>189</v>
+      <c r="G50" t="s">
+        <v>209</v>
       </c>
       <c r="I50" t="s">
-        <v>190</v>
-      </c>
-      <c r="J50" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K50" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5339,13 +5339,13 @@
       <c r="E51" t="s">
         <v>188</v>
       </c>
-      <c r="H51" t="s">
+      <c r="F51" t="s">
         <v>189</v>
       </c>
+      <c r="G51" t="s">
+        <v>190</v>
+      </c>
       <c r="I51" t="s">
-        <v>190</v>
-      </c>
-      <c r="J51" t="s">
         <v>191</v>
       </c>
       <c r="K51" t="s">
@@ -5366,19 +5366,19 @@
         <v>14</v>
       </c>
       <c r="E52" t="s">
+        <v>196</v>
+      </c>
+      <c r="F52" t="s">
         <v>225</v>
       </c>
-      <c r="H52" t="s">
-        <v>189</v>
+      <c r="G52" t="s">
+        <v>226</v>
       </c>
       <c r="I52" t="s">
-        <v>190</v>
-      </c>
-      <c r="J52" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K52" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5397,17 +5397,17 @@
       <c r="E53" t="s">
         <v>15</v>
       </c>
-      <c r="H53" t="s">
-        <v>189</v>
+      <c r="F53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" t="s">
+        <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>190</v>
-      </c>
-      <c r="J53" t="s">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="K53" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5459,13 +5459,13 @@
         <v>14</v>
       </c>
       <c r="E55" t="s">
+        <v>233</v>
+      </c>
+      <c r="F55" t="s">
         <v>243</v>
       </c>
-      <c r="F55" t="s">
-        <v>234</v>
-      </c>
       <c r="G55" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H55" t="s">
         <v>236</v>
@@ -5477,7 +5477,7 @@
         <v>238</v>
       </c>
       <c r="K55" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -5494,13 +5494,13 @@
         <v>14</v>
       </c>
       <c r="E56" t="s">
+        <v>233</v>
+      </c>
+      <c r="F56" t="s">
         <v>248</v>
       </c>
-      <c r="F56" t="s">
-        <v>234</v>
-      </c>
       <c r="G56" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="H56" t="s">
         <v>236</v>
@@ -5512,7 +5512,7 @@
         <v>238</v>
       </c>
       <c r="K56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -5532,10 +5532,10 @@
         <v>253</v>
       </c>
       <c r="F57" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="G57" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="H57" t="s">
         <v>236</v>
@@ -5544,10 +5544,10 @@
         <v>237</v>
       </c>
       <c r="J57" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K57" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5564,13 +5564,13 @@
         <v>14</v>
       </c>
       <c r="E58" t="s">
+        <v>233</v>
+      </c>
+      <c r="F58" t="s">
         <v>243</v>
       </c>
-      <c r="F58" t="s">
-        <v>234</v>
-      </c>
       <c r="G58" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H58" t="s">
         <v>236</v>
@@ -5582,7 +5582,7 @@
         <v>238</v>
       </c>
       <c r="K58" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5599,13 +5599,13 @@
         <v>14</v>
       </c>
       <c r="E59" t="s">
+        <v>233</v>
+      </c>
+      <c r="F59" t="s">
         <v>243</v>
       </c>
-      <c r="F59" t="s">
-        <v>234</v>
-      </c>
       <c r="G59" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H59" t="s">
         <v>236</v>
@@ -5617,7 +5617,7 @@
         <v>238</v>
       </c>
       <c r="K59" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5634,13 +5634,13 @@
         <v>14</v>
       </c>
       <c r="E60" t="s">
+        <v>233</v>
+      </c>
+      <c r="F60" t="s">
         <v>243</v>
       </c>
-      <c r="F60" t="s">
-        <v>234</v>
-      </c>
       <c r="G60" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H60" t="s">
         <v>236</v>
@@ -5652,7 +5652,7 @@
         <v>238</v>
       </c>
       <c r="K60" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -5669,13 +5669,13 @@
         <v>14</v>
       </c>
       <c r="E61" t="s">
+        <v>233</v>
+      </c>
+      <c r="F61" t="s">
         <v>243</v>
       </c>
-      <c r="F61" t="s">
-        <v>234</v>
-      </c>
       <c r="G61" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H61" t="s">
         <v>236</v>
@@ -5687,7 +5687,7 @@
         <v>238</v>
       </c>
       <c r="K61" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -5704,13 +5704,13 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
+        <v>233</v>
+      </c>
+      <c r="F62" t="s">
         <v>243</v>
       </c>
-      <c r="F62" t="s">
-        <v>234</v>
-      </c>
       <c r="G62" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H62" t="s">
         <v>236</v>
@@ -5722,7 +5722,7 @@
         <v>238</v>
       </c>
       <c r="K62" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -5739,13 +5739,13 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
+        <v>233</v>
+      </c>
+      <c r="F63" t="s">
         <v>274</v>
       </c>
-      <c r="F63" t="s">
-        <v>234</v>
-      </c>
       <c r="G63" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H63" t="s">
         <v>236</v>
@@ -5757,7 +5757,7 @@
         <v>238</v>
       </c>
       <c r="K63" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -5774,13 +5774,13 @@
         <v>14</v>
       </c>
       <c r="E64" t="s">
+        <v>233</v>
+      </c>
+      <c r="F64" t="s">
         <v>274</v>
       </c>
-      <c r="F64" t="s">
-        <v>234</v>
-      </c>
       <c r="G64" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H64" t="s">
         <v>236</v>
@@ -5792,7 +5792,7 @@
         <v>238</v>
       </c>
       <c r="K64" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -5809,13 +5809,13 @@
         <v>14</v>
       </c>
       <c r="E65" t="s">
+        <v>233</v>
+      </c>
+      <c r="F65" t="s">
         <v>281</v>
       </c>
-      <c r="F65" t="s">
-        <v>234</v>
-      </c>
       <c r="G65" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="H65" t="s">
         <v>236</v>
@@ -5827,7 +5827,7 @@
         <v>238</v>
       </c>
       <c r="K65" t="s">
-        <v>282</v>
+        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5879,13 +5879,13 @@
         <v>14</v>
       </c>
       <c r="E67" t="s">
+        <v>233</v>
+      </c>
+      <c r="F67" t="s">
         <v>243</v>
       </c>
-      <c r="F67" t="s">
-        <v>234</v>
-      </c>
       <c r="G67" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H67" t="s">
         <v>236</v>
@@ -5897,7 +5897,7 @@
         <v>238</v>
       </c>
       <c r="K67" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5914,10 +5914,10 @@
         <v>14</v>
       </c>
       <c r="E68" t="s">
+        <v>233</v>
+      </c>
+      <c r="F68" t="s">
         <v>292</v>
-      </c>
-      <c r="F68" t="s">
-        <v>234</v>
       </c>
       <c r="G68" t="s">
         <v>235</v>
@@ -5949,10 +5949,10 @@
         <v>14</v>
       </c>
       <c r="E69" t="s">
+        <v>233</v>
+      </c>
+      <c r="F69" t="s">
         <v>296</v>
-      </c>
-      <c r="F69" t="s">
-        <v>234</v>
       </c>
       <c r="G69" t="s">
         <v>235</v>
@@ -5984,13 +5984,13 @@
         <v>14</v>
       </c>
       <c r="E70" t="s">
+        <v>233</v>
+      </c>
+      <c r="F70" t="s">
         <v>248</v>
       </c>
-      <c r="F70" t="s">
-        <v>234</v>
-      </c>
       <c r="G70" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="H70" t="s">
         <v>236</v>
@@ -6002,7 +6002,7 @@
         <v>238</v>
       </c>
       <c r="K70" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -6019,13 +6019,13 @@
         <v>14</v>
       </c>
       <c r="E71" t="s">
+        <v>233</v>
+      </c>
+      <c r="F71" t="s">
         <v>248</v>
       </c>
-      <c r="F71" t="s">
-        <v>234</v>
-      </c>
       <c r="G71" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="H71" t="s">
         <v>236</v>
@@ -6037,7 +6037,7 @@
         <v>238</v>
       </c>
       <c r="K71" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6089,13 +6089,13 @@
         <v>14</v>
       </c>
       <c r="E73" t="s">
+        <v>253</v>
+      </c>
+      <c r="F73" t="s">
         <v>309</v>
       </c>
-      <c r="F73" t="s">
-        <v>234</v>
-      </c>
       <c r="G73" t="s">
-        <v>235</v>
+        <v>310</v>
       </c>
       <c r="H73" t="s">
         <v>236</v>
@@ -6104,10 +6104,10 @@
         <v>237</v>
       </c>
       <c r="J73" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K73" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6124,13 +6124,13 @@
         <v>14</v>
       </c>
       <c r="E74" t="s">
+        <v>253</v>
+      </c>
+      <c r="F74" t="s">
         <v>314</v>
       </c>
-      <c r="F74" t="s">
-        <v>234</v>
-      </c>
       <c r="G74" t="s">
-        <v>235</v>
+        <v>315</v>
       </c>
       <c r="H74" t="s">
         <v>236</v>
@@ -6139,10 +6139,10 @@
         <v>237</v>
       </c>
       <c r="J74" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K74" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6159,13 +6159,13 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
+        <v>253</v>
+      </c>
+      <c r="F75" t="s">
         <v>319</v>
       </c>
-      <c r="F75" t="s">
-        <v>234</v>
-      </c>
       <c r="G75" t="s">
-        <v>235</v>
+        <v>320</v>
       </c>
       <c r="H75" t="s">
         <v>236</v>
@@ -6174,10 +6174,10 @@
         <v>237</v>
       </c>
       <c r="J75" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K75" t="s">
-        <v>320</v>
+        <v>239</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6194,13 +6194,13 @@
         <v>14</v>
       </c>
       <c r="E76" t="s">
+        <v>253</v>
+      </c>
+      <c r="F76" t="s">
         <v>309</v>
       </c>
-      <c r="F76" t="s">
-        <v>234</v>
-      </c>
       <c r="G76" t="s">
-        <v>235</v>
+        <v>310</v>
       </c>
       <c r="H76" t="s">
         <v>236</v>
@@ -6209,10 +6209,10 @@
         <v>237</v>
       </c>
       <c r="J76" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K76" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -6229,13 +6229,13 @@
         <v>14</v>
       </c>
       <c r="E77" t="s">
+        <v>253</v>
+      </c>
+      <c r="F77" t="s">
         <v>309</v>
       </c>
-      <c r="F77" t="s">
-        <v>234</v>
-      </c>
       <c r="G77" t="s">
-        <v>235</v>
+        <v>310</v>
       </c>
       <c r="H77" t="s">
         <v>236</v>
@@ -6244,10 +6244,10 @@
         <v>237</v>
       </c>
       <c r="J77" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K77" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -6264,13 +6264,13 @@
         <v>14</v>
       </c>
       <c r="E78" t="s">
+        <v>253</v>
+      </c>
+      <c r="F78" t="s">
         <v>314</v>
       </c>
-      <c r="F78" t="s">
-        <v>234</v>
-      </c>
       <c r="G78" t="s">
-        <v>235</v>
+        <v>315</v>
       </c>
       <c r="H78" t="s">
         <v>236</v>
@@ -6279,10 +6279,10 @@
         <v>237</v>
       </c>
       <c r="J78" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K78" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -6296,13 +6296,13 @@
         <v>14</v>
       </c>
       <c r="E79" t="s">
+        <v>253</v>
+      </c>
+      <c r="F79" t="s">
         <v>332</v>
       </c>
-      <c r="F79" t="s">
-        <v>234</v>
-      </c>
       <c r="G79" t="s">
-        <v>235</v>
+        <v>333</v>
       </c>
       <c r="H79" t="s">
         <v>236</v>
@@ -6311,10 +6311,10 @@
         <v>237</v>
       </c>
       <c r="J79" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K79" t="s">
-        <v>333</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -6334,10 +6334,10 @@
         <v>337</v>
       </c>
       <c r="F80" t="s">
-        <v>234</v>
+        <v>338</v>
       </c>
       <c r="G80" t="s">
-        <v>235</v>
+        <v>339</v>
       </c>
       <c r="H80" t="s">
         <v>236</v>
@@ -6346,10 +6346,10 @@
         <v>237</v>
       </c>
       <c r="J80" t="s">
-        <v>338</v>
+        <v>238</v>
       </c>
       <c r="K80" t="s">
-        <v>339</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -6369,10 +6369,10 @@
         <v>337</v>
       </c>
       <c r="F81" t="s">
-        <v>234</v>
+        <v>338</v>
       </c>
       <c r="G81" t="s">
-        <v>235</v>
+        <v>339</v>
       </c>
       <c r="H81" t="s">
         <v>236</v>
@@ -6381,10 +6381,10 @@
         <v>237</v>
       </c>
       <c r="J81" t="s">
-        <v>338</v>
+        <v>238</v>
       </c>
       <c r="K81" t="s">
-        <v>339</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -6404,10 +6404,10 @@
         <v>337</v>
       </c>
       <c r="F82" t="s">
-        <v>234</v>
+        <v>338</v>
       </c>
       <c r="G82" t="s">
-        <v>235</v>
+        <v>339</v>
       </c>
       <c r="H82" t="s">
         <v>236</v>
@@ -6416,10 +6416,10 @@
         <v>237</v>
       </c>
       <c r="J82" t="s">
-        <v>338</v>
+        <v>238</v>
       </c>
       <c r="K82" t="s">
-        <v>339</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -6436,10 +6436,10 @@
         <v>14</v>
       </c>
       <c r="E83" t="s">
+        <v>233</v>
+      </c>
+      <c r="F83" t="s">
         <v>296</v>
-      </c>
-      <c r="F83" t="s">
-        <v>234</v>
       </c>
       <c r="G83" t="s">
         <v>235</v>
@@ -6471,13 +6471,13 @@
         <v>14</v>
       </c>
       <c r="E84" t="s">
+        <v>233</v>
+      </c>
+      <c r="F84" t="s">
         <v>352</v>
       </c>
-      <c r="F84" t="s">
-        <v>234</v>
-      </c>
       <c r="G84" t="s">
-        <v>235</v>
+        <v>353</v>
       </c>
       <c r="H84" t="s">
         <v>236</v>
@@ -6489,7 +6489,7 @@
         <v>238</v>
       </c>
       <c r="K84" t="s">
-        <v>353</v>
+        <v>239</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -6506,13 +6506,13 @@
         <v>14</v>
       </c>
       <c r="E85" t="s">
+        <v>233</v>
+      </c>
+      <c r="F85" t="s">
         <v>357</v>
       </c>
-      <c r="F85" t="s">
-        <v>234</v>
-      </c>
       <c r="G85" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H85" t="s">
         <v>236</v>
@@ -6524,7 +6524,7 @@
         <v>238</v>
       </c>
       <c r="K85" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -6541,13 +6541,13 @@
         <v>14</v>
       </c>
       <c r="E86" t="s">
+        <v>337</v>
+      </c>
+      <c r="F86" t="s">
         <v>361</v>
       </c>
-      <c r="F86" t="s">
-        <v>234</v>
-      </c>
       <c r="G86" t="s">
-        <v>235</v>
+        <v>362</v>
       </c>
       <c r="H86" t="s">
         <v>236</v>
@@ -6556,10 +6556,10 @@
         <v>237</v>
       </c>
       <c r="J86" t="s">
-        <v>338</v>
+        <v>238</v>
       </c>
       <c r="K86" t="s">
-        <v>362</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -6576,13 +6576,13 @@
         <v>14</v>
       </c>
       <c r="E87" t="s">
+        <v>233</v>
+      </c>
+      <c r="F87" t="s">
         <v>357</v>
       </c>
-      <c r="F87" t="s">
-        <v>234</v>
-      </c>
       <c r="G87" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H87" t="s">
         <v>236</v>
@@ -6594,7 +6594,7 @@
         <v>238</v>
       </c>
       <c r="K87" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -6608,13 +6608,13 @@
         <v>14</v>
       </c>
       <c r="E88" t="s">
+        <v>233</v>
+      </c>
+      <c r="F88" t="s">
         <v>243</v>
       </c>
-      <c r="F88" t="s">
-        <v>234</v>
-      </c>
       <c r="G88" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H88" t="s">
         <v>236</v>
@@ -6626,7 +6626,7 @@
         <v>238</v>
       </c>
       <c r="K88" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -6643,13 +6643,13 @@
         <v>14</v>
       </c>
       <c r="E89" t="s">
+        <v>233</v>
+      </c>
+      <c r="F89" t="s">
         <v>243</v>
       </c>
-      <c r="F89" t="s">
-        <v>234</v>
-      </c>
       <c r="G89" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H89" t="s">
         <v>236</v>
@@ -6661,7 +6661,7 @@
         <v>238</v>
       </c>
       <c r="K89" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -6681,10 +6681,10 @@
         <v>253</v>
       </c>
       <c r="F90" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="G90" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="H90" t="s">
         <v>236</v>
@@ -6693,10 +6693,10 @@
         <v>237</v>
       </c>
       <c r="J90" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K90" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -6716,10 +6716,10 @@
         <v>377</v>
       </c>
       <c r="F91" t="s">
-        <v>234</v>
+        <v>378</v>
       </c>
       <c r="G91" t="s">
-        <v>235</v>
+        <v>379</v>
       </c>
       <c r="H91" t="s">
         <v>236</v>
@@ -6728,10 +6728,10 @@
         <v>237</v>
       </c>
       <c r="J91" t="s">
-        <v>378</v>
+        <v>238</v>
       </c>
       <c r="K91" t="s">
-        <v>379</v>
+        <v>239</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -6751,10 +6751,10 @@
         <v>253</v>
       </c>
       <c r="F92" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="G92" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="H92" t="s">
         <v>236</v>
@@ -6763,10 +6763,10 @@
         <v>237</v>
       </c>
       <c r="J92" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K92" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -6783,13 +6783,13 @@
         <v>14</v>
       </c>
       <c r="E93" t="s">
+        <v>233</v>
+      </c>
+      <c r="F93" t="s">
         <v>248</v>
       </c>
-      <c r="F93" t="s">
-        <v>234</v>
-      </c>
       <c r="G93" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="H93" t="s">
         <v>236</v>
@@ -6801,7 +6801,7 @@
         <v>238</v>
       </c>
       <c r="K93" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -6821,10 +6821,10 @@
         <v>253</v>
       </c>
       <c r="F94" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="G94" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="H94" t="s">
         <v>236</v>
@@ -6833,10 +6833,10 @@
         <v>237</v>
       </c>
       <c r="J94" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K94" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -6853,13 +6853,13 @@
         <v>14</v>
       </c>
       <c r="E95" t="s">
+        <v>233</v>
+      </c>
+      <c r="F95" t="s">
         <v>392</v>
       </c>
-      <c r="F95" t="s">
-        <v>234</v>
-      </c>
       <c r="G95" t="s">
-        <v>235</v>
+        <v>393</v>
       </c>
       <c r="H95" t="s">
         <v>236</v>
@@ -6871,7 +6871,7 @@
         <v>238</v>
       </c>
       <c r="K95" t="s">
-        <v>393</v>
+        <v>239</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -6891,22 +6891,22 @@
         <v>253</v>
       </c>
       <c r="F96" t="s">
+        <v>254</v>
+      </c>
+      <c r="G96" t="s">
+        <v>255</v>
+      </c>
+      <c r="H96" t="s">
         <v>397</v>
-      </c>
-      <c r="G96" t="s">
-        <v>398</v>
-      </c>
-      <c r="H96" t="s">
-        <v>236</v>
       </c>
       <c r="I96" t="s">
         <v>237</v>
       </c>
       <c r="J96" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="K96" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -6926,22 +6926,22 @@
         <v>253</v>
       </c>
       <c r="F97" t="s">
+        <v>254</v>
+      </c>
+      <c r="G97" t="s">
+        <v>255</v>
+      </c>
+      <c r="H97" t="s">
         <v>397</v>
-      </c>
-      <c r="G97" t="s">
-        <v>398</v>
-      </c>
-      <c r="H97" t="s">
-        <v>236</v>
       </c>
       <c r="I97" t="s">
         <v>237</v>
       </c>
       <c r="J97" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="K97" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -6961,22 +6961,22 @@
         <v>405</v>
       </c>
       <c r="F98" t="s">
+        <v>406</v>
+      </c>
+      <c r="G98" t="s">
+        <v>407</v>
+      </c>
+      <c r="H98" t="s">
         <v>397</v>
-      </c>
-      <c r="G98" t="s">
-        <v>398</v>
-      </c>
-      <c r="H98" t="s">
-        <v>236</v>
       </c>
       <c r="I98" t="s">
         <v>237</v>
       </c>
       <c r="J98" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="K98" t="s">
-        <v>407</v>
+        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -6996,22 +6996,22 @@
         <v>253</v>
       </c>
       <c r="F99" t="s">
+        <v>254</v>
+      </c>
+      <c r="G99" t="s">
+        <v>255</v>
+      </c>
+      <c r="H99" t="s">
         <v>397</v>
-      </c>
-      <c r="G99" t="s">
-        <v>398</v>
-      </c>
-      <c r="H99" t="s">
-        <v>236</v>
       </c>
       <c r="I99" t="s">
         <v>237</v>
       </c>
       <c r="J99" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="K99" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -7028,25 +7028,25 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
+        <v>253</v>
+      </c>
+      <c r="F100" t="s">
         <v>319</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
+        <v>320</v>
+      </c>
+      <c r="H100" t="s">
         <v>397</v>
-      </c>
-      <c r="G100" t="s">
-        <v>398</v>
-      </c>
-      <c r="H100" t="s">
-        <v>236</v>
       </c>
       <c r="I100" t="s">
         <v>237</v>
       </c>
       <c r="J100" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="K100" t="s">
-        <v>320</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -7066,22 +7066,22 @@
         <v>253</v>
       </c>
       <c r="F101" t="s">
+        <v>254</v>
+      </c>
+      <c r="G101" t="s">
+        <v>255</v>
+      </c>
+      <c r="H101" t="s">
         <v>397</v>
-      </c>
-      <c r="G101" t="s">
-        <v>398</v>
-      </c>
-      <c r="H101" t="s">
-        <v>236</v>
       </c>
       <c r="I101" t="s">
         <v>237</v>
       </c>
       <c r="J101" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="K101" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -7098,16 +7098,16 @@
         <v>14</v>
       </c>
       <c r="E102" t="s">
+        <v>377</v>
+      </c>
+      <c r="F102" t="s">
         <v>420</v>
       </c>
-      <c r="H102" t="s">
+      <c r="G102" t="s">
         <v>421</v>
       </c>
       <c r="I102" t="s">
         <v>422</v>
-      </c>
-      <c r="J102" t="s">
-        <v>378</v>
       </c>
       <c r="K102" t="s">
         <v>423</v>
@@ -7127,16 +7127,16 @@
         <v>14</v>
       </c>
       <c r="E103" t="s">
+        <v>377</v>
+      </c>
+      <c r="F103" t="s">
         <v>420</v>
       </c>
-      <c r="H103" t="s">
+      <c r="G103" t="s">
         <v>421</v>
       </c>
       <c r="I103" t="s">
         <v>422</v>
-      </c>
-      <c r="J103" t="s">
-        <v>378</v>
       </c>
       <c r="K103" t="s">
         <v>423</v>
@@ -7156,16 +7156,16 @@
         <v>14</v>
       </c>
       <c r="E104" t="s">
+        <v>377</v>
+      </c>
+      <c r="F104" t="s">
         <v>420</v>
       </c>
-      <c r="H104" t="s">
+      <c r="G104" t="s">
         <v>421</v>
       </c>
       <c r="I104" t="s">
         <v>422</v>
-      </c>
-      <c r="J104" t="s">
-        <v>378</v>
       </c>
       <c r="K104" t="s">
         <v>423</v>
@@ -7185,19 +7185,19 @@
         <v>14</v>
       </c>
       <c r="E105" t="s">
+        <v>377</v>
+      </c>
+      <c r="F105" t="s">
         <v>433</v>
       </c>
-      <c r="H105" t="s">
-        <v>421</v>
+      <c r="G105" t="s">
+        <v>434</v>
       </c>
       <c r="I105" t="s">
         <v>422</v>
       </c>
-      <c r="J105" t="s">
-        <v>378</v>
-      </c>
       <c r="K105" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7214,16 +7214,16 @@
         <v>14</v>
       </c>
       <c r="E106" t="s">
+        <v>377</v>
+      </c>
+      <c r="F106" t="s">
         <v>420</v>
       </c>
-      <c r="H106" t="s">
+      <c r="G106" t="s">
         <v>421</v>
       </c>
       <c r="I106" t="s">
         <v>422</v>
-      </c>
-      <c r="J106" t="s">
-        <v>378</v>
       </c>
       <c r="K106" t="s">
         <v>423</v>
@@ -7245,17 +7245,17 @@
       <c r="E107" t="s">
         <v>377</v>
       </c>
-      <c r="H107" t="s">
-        <v>421</v>
+      <c r="F107" t="s">
+        <v>378</v>
+      </c>
+      <c r="G107" t="s">
+        <v>379</v>
       </c>
       <c r="I107" t="s">
         <v>422</v>
       </c>
-      <c r="J107" t="s">
-        <v>378</v>
-      </c>
       <c r="K107" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -7272,19 +7272,19 @@
         <v>14</v>
       </c>
       <c r="E108" t="s">
+        <v>377</v>
+      </c>
+      <c r="F108" t="s">
         <v>444</v>
       </c>
-      <c r="H108" t="s">
-        <v>421</v>
+      <c r="G108" t="s">
+        <v>445</v>
       </c>
       <c r="I108" t="s">
         <v>422</v>
       </c>
-      <c r="J108" t="s">
-        <v>378</v>
-      </c>
       <c r="K108" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7301,19 +7301,19 @@
         <v>14</v>
       </c>
       <c r="E109" t="s">
+        <v>188</v>
+      </c>
+      <c r="F109" t="s">
         <v>449</v>
       </c>
-      <c r="H109" t="s">
-        <v>421</v>
+      <c r="G109" t="s">
+        <v>450</v>
       </c>
       <c r="I109" t="s">
         <v>422</v>
       </c>
-      <c r="J109" t="s">
-        <v>191</v>
-      </c>
       <c r="K109" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -7330,19 +7330,19 @@
         <v>14</v>
       </c>
       <c r="E110" t="s">
+        <v>188</v>
+      </c>
+      <c r="F110" t="s">
         <v>454</v>
       </c>
-      <c r="H110" t="s">
-        <v>421</v>
+      <c r="G110" t="s">
+        <v>455</v>
       </c>
       <c r="I110" t="s">
         <v>422</v>
       </c>
-      <c r="J110" t="s">
-        <v>191</v>
-      </c>
       <c r="K110" t="s">
-        <v>455</v>
+        <v>423</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -7359,16 +7359,16 @@
         <v>14</v>
       </c>
       <c r="E111" t="s">
+        <v>377</v>
+      </c>
+      <c r="F111" t="s">
         <v>420</v>
       </c>
-      <c r="H111" t="s">
+      <c r="G111" t="s">
         <v>421</v>
       </c>
       <c r="I111" t="s">
         <v>422</v>
-      </c>
-      <c r="J111" t="s">
-        <v>378</v>
       </c>
       <c r="K111" t="s">
         <v>423</v>
@@ -7390,17 +7390,17 @@
       <c r="E112" t="s">
         <v>462</v>
       </c>
-      <c r="H112" t="s">
-        <v>421</v>
+      <c r="F112" t="s">
+        <v>463</v>
+      </c>
+      <c r="G112" t="s">
+        <v>464</v>
       </c>
       <c r="I112" t="s">
         <v>422</v>
       </c>
-      <c r="J112" t="s">
-        <v>463</v>
-      </c>
       <c r="K112" t="s">
-        <v>464</v>
+        <v>423</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -7417,19 +7417,19 @@
         <v>14</v>
       </c>
       <c r="E113" t="s">
+        <v>233</v>
+      </c>
+      <c r="F113" t="s">
         <v>296</v>
       </c>
-      <c r="H113" t="s">
-        <v>421</v>
+      <c r="G113" t="s">
+        <v>235</v>
       </c>
       <c r="I113" t="s">
         <v>422</v>
       </c>
-      <c r="J113" t="s">
-        <v>238</v>
-      </c>
       <c r="K113" t="s">
-        <v>239</v>
+        <v>423</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -7446,19 +7446,19 @@
         <v>14</v>
       </c>
       <c r="E114" t="s">
+        <v>253</v>
+      </c>
+      <c r="F114" t="s">
         <v>314</v>
       </c>
-      <c r="H114" t="s">
-        <v>421</v>
+      <c r="G114" t="s">
+        <v>315</v>
       </c>
       <c r="I114" t="s">
         <v>422</v>
       </c>
-      <c r="J114" t="s">
-        <v>254</v>
-      </c>
       <c r="K114" t="s">
-        <v>315</v>
+        <v>423</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -7477,17 +7477,17 @@
       <c r="E115" t="s">
         <v>377</v>
       </c>
-      <c r="H115" t="s">
-        <v>421</v>
+      <c r="F115" t="s">
+        <v>378</v>
+      </c>
+      <c r="G115" t="s">
+        <v>379</v>
       </c>
       <c r="I115" t="s">
         <v>422</v>
       </c>
-      <c r="J115" t="s">
-        <v>378</v>
-      </c>
       <c r="K115" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -7501,19 +7501,19 @@
         <v>14</v>
       </c>
       <c r="E116" t="s">
+        <v>462</v>
+      </c>
+      <c r="F116" t="s">
         <v>476</v>
       </c>
-      <c r="H116" t="s">
-        <v>421</v>
+      <c r="G116" t="s">
+        <v>477</v>
       </c>
       <c r="I116" t="s">
         <v>422</v>
       </c>
-      <c r="J116" t="s">
-        <v>463</v>
-      </c>
       <c r="K116" t="s">
-        <v>477</v>
+        <v>423</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -7529,17 +7529,17 @@
       <c r="E117" t="s">
         <v>462</v>
       </c>
-      <c r="H117" t="s">
-        <v>421</v>
+      <c r="F117" t="s">
+        <v>463</v>
+      </c>
+      <c r="G117" t="s">
+        <v>464</v>
       </c>
       <c r="I117" t="s">
         <v>422</v>
       </c>
-      <c r="J117" t="s">
-        <v>463</v>
-      </c>
       <c r="K117" t="s">
-        <v>464</v>
+        <v>423</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -7556,19 +7556,19 @@
         <v>14</v>
       </c>
       <c r="E118" t="s">
+        <v>337</v>
+      </c>
+      <c r="F118" t="s">
         <v>483</v>
       </c>
-      <c r="H118" t="s">
-        <v>421</v>
+      <c r="G118" t="s">
+        <v>339</v>
       </c>
       <c r="I118" t="s">
         <v>422</v>
       </c>
-      <c r="J118" t="s">
-        <v>338</v>
-      </c>
       <c r="K118" t="s">
-        <v>339</v>
+        <v>423</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -7587,17 +7587,17 @@
       <c r="E119" t="s">
         <v>377</v>
       </c>
-      <c r="H119" t="s">
-        <v>421</v>
+      <c r="F119" t="s">
+        <v>378</v>
+      </c>
+      <c r="G119" t="s">
+        <v>379</v>
       </c>
       <c r="I119" t="s">
         <v>422</v>
       </c>
-      <c r="J119" t="s">
-        <v>378</v>
-      </c>
       <c r="K119" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -7614,19 +7614,19 @@
         <v>14</v>
       </c>
       <c r="E120" t="s">
+        <v>233</v>
+      </c>
+      <c r="F120" t="s">
         <v>352</v>
       </c>
-      <c r="H120" t="s">
+      <c r="G120" t="s">
+        <v>353</v>
+      </c>
+      <c r="I120" t="s">
         <v>490</v>
       </c>
-      <c r="I120" t="s">
+      <c r="K120" t="s">
         <v>491</v>
-      </c>
-      <c r="J120" t="s">
-        <v>238</v>
-      </c>
-      <c r="K120" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -7643,19 +7643,19 @@
         <v>14</v>
       </c>
       <c r="E121" t="s">
+        <v>233</v>
+      </c>
+      <c r="F121" t="s">
         <v>296</v>
       </c>
-      <c r="H121" t="s">
+      <c r="G121" t="s">
+        <v>235</v>
+      </c>
+      <c r="I121" t="s">
         <v>490</v>
       </c>
-      <c r="I121" t="s">
+      <c r="K121" t="s">
         <v>491</v>
-      </c>
-      <c r="J121" t="s">
-        <v>238</v>
-      </c>
-      <c r="K121" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -7672,19 +7672,19 @@
         <v>14</v>
       </c>
       <c r="E122" t="s">
+        <v>233</v>
+      </c>
+      <c r="F122" t="s">
         <v>352</v>
       </c>
-      <c r="H122" t="s">
+      <c r="G122" t="s">
+        <v>353</v>
+      </c>
+      <c r="I122" t="s">
         <v>490</v>
       </c>
-      <c r="I122" t="s">
+      <c r="K122" t="s">
         <v>491</v>
-      </c>
-      <c r="J122" t="s">
-        <v>238</v>
-      </c>
-      <c r="K122" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -7701,19 +7701,19 @@
         <v>14</v>
       </c>
       <c r="E123" t="s">
+        <v>233</v>
+      </c>
+      <c r="F123" t="s">
         <v>352</v>
       </c>
-      <c r="H123" t="s">
+      <c r="G123" t="s">
+        <v>353</v>
+      </c>
+      <c r="I123" t="s">
         <v>490</v>
       </c>
-      <c r="I123" t="s">
+      <c r="K123" t="s">
         <v>491</v>
-      </c>
-      <c r="J123" t="s">
-        <v>238</v>
-      </c>
-      <c r="K123" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -7730,19 +7730,19 @@
         <v>14</v>
       </c>
       <c r="E124" t="s">
+        <v>337</v>
+      </c>
+      <c r="F124" t="s">
         <v>504</v>
       </c>
-      <c r="H124" t="s">
+      <c r="G124" t="s">
+        <v>505</v>
+      </c>
+      <c r="I124" t="s">
         <v>490</v>
       </c>
-      <c r="I124" t="s">
+      <c r="K124" t="s">
         <v>491</v>
-      </c>
-      <c r="J124" t="s">
-        <v>338</v>
-      </c>
-      <c r="K124" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -7759,19 +7759,19 @@
         <v>14</v>
       </c>
       <c r="E125" t="s">
+        <v>337</v>
+      </c>
+      <c r="F125" t="s">
         <v>504</v>
       </c>
-      <c r="H125" t="s">
+      <c r="G125" t="s">
+        <v>505</v>
+      </c>
+      <c r="I125" t="s">
         <v>490</v>
       </c>
-      <c r="I125" t="s">
+      <c r="K125" t="s">
         <v>491</v>
-      </c>
-      <c r="J125" t="s">
-        <v>338</v>
-      </c>
-      <c r="K125" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -7788,19 +7788,19 @@
         <v>14</v>
       </c>
       <c r="E126" t="s">
+        <v>337</v>
+      </c>
+      <c r="F126" t="s">
         <v>504</v>
       </c>
-      <c r="H126" t="s">
+      <c r="G126" t="s">
+        <v>505</v>
+      </c>
+      <c r="I126" t="s">
         <v>490</v>
       </c>
-      <c r="I126" t="s">
+      <c r="K126" t="s">
         <v>491</v>
-      </c>
-      <c r="J126" t="s">
-        <v>338</v>
-      </c>
-      <c r="K126" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -7817,19 +7817,19 @@
         <v>14</v>
       </c>
       <c r="E127" t="s">
+        <v>337</v>
+      </c>
+      <c r="F127" t="s">
         <v>504</v>
       </c>
-      <c r="H127" t="s">
+      <c r="G127" t="s">
+        <v>505</v>
+      </c>
+      <c r="I127" t="s">
         <v>490</v>
       </c>
-      <c r="I127" t="s">
+      <c r="K127" t="s">
         <v>491</v>
-      </c>
-      <c r="J127" t="s">
-        <v>338</v>
-      </c>
-      <c r="K127" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -7846,19 +7846,19 @@
         <v>14</v>
       </c>
       <c r="E128" t="s">
+        <v>337</v>
+      </c>
+      <c r="F128" t="s">
         <v>504</v>
       </c>
-      <c r="H128" t="s">
+      <c r="G128" t="s">
+        <v>505</v>
+      </c>
+      <c r="I128" t="s">
         <v>490</v>
       </c>
-      <c r="I128" t="s">
+      <c r="K128" t="s">
         <v>491</v>
-      </c>
-      <c r="J128" t="s">
-        <v>338</v>
-      </c>
-      <c r="K128" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -7875,19 +7875,19 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
+        <v>337</v>
+      </c>
+      <c r="F129" t="s">
         <v>521</v>
       </c>
-      <c r="H129" t="s">
+      <c r="G129" t="s">
+        <v>505</v>
+      </c>
+      <c r="I129" t="s">
         <v>490</v>
       </c>
-      <c r="I129" t="s">
+      <c r="K129" t="s">
         <v>491</v>
-      </c>
-      <c r="J129" t="s">
-        <v>338</v>
-      </c>
-      <c r="K129" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7904,19 +7904,19 @@
         <v>14</v>
       </c>
       <c r="E130" t="s">
+        <v>337</v>
+      </c>
+      <c r="F130" t="s">
         <v>525</v>
       </c>
-      <c r="H130" t="s">
+      <c r="G130" t="s">
+        <v>505</v>
+      </c>
+      <c r="I130" t="s">
         <v>490</v>
       </c>
-      <c r="I130" t="s">
+      <c r="K130" t="s">
         <v>491</v>
-      </c>
-      <c r="J130" t="s">
-        <v>338</v>
-      </c>
-      <c r="K130" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7933,19 +7933,19 @@
         <v>14</v>
       </c>
       <c r="E131" t="s">
+        <v>337</v>
+      </c>
+      <c r="F131" t="s">
         <v>529</v>
       </c>
-      <c r="H131" t="s">
+      <c r="G131" t="s">
+        <v>505</v>
+      </c>
+      <c r="I131" t="s">
         <v>490</v>
       </c>
-      <c r="I131" t="s">
+      <c r="K131" t="s">
         <v>491</v>
-      </c>
-      <c r="J131" t="s">
-        <v>338</v>
-      </c>
-      <c r="K131" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7962,19 +7962,19 @@
         <v>14</v>
       </c>
       <c r="E132" t="s">
+        <v>337</v>
+      </c>
+      <c r="F132" t="s">
         <v>533</v>
       </c>
-      <c r="H132" t="s">
+      <c r="G132" t="s">
+        <v>534</v>
+      </c>
+      <c r="I132" t="s">
         <v>490</v>
       </c>
-      <c r="I132" t="s">
+      <c r="K132" t="s">
         <v>491</v>
-      </c>
-      <c r="J132" t="s">
-        <v>338</v>
-      </c>
-      <c r="K132" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -7988,19 +7988,19 @@
         <v>14</v>
       </c>
       <c r="E133" t="s">
+        <v>233</v>
+      </c>
+      <c r="F133" t="s">
         <v>392</v>
       </c>
-      <c r="H133" t="s">
+      <c r="G133" t="s">
+        <v>393</v>
+      </c>
+      <c r="I133" t="s">
         <v>490</v>
       </c>
-      <c r="I133" t="s">
+      <c r="K133" t="s">
         <v>491</v>
-      </c>
-      <c r="J133" t="s">
-        <v>238</v>
-      </c>
-      <c r="K133" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -8017,19 +8017,19 @@
         <v>14</v>
       </c>
       <c r="E134" t="s">
+        <v>337</v>
+      </c>
+      <c r="F134" t="s">
         <v>361</v>
       </c>
-      <c r="H134" t="s">
+      <c r="G134" t="s">
+        <v>362</v>
+      </c>
+      <c r="I134" t="s">
         <v>540</v>
       </c>
-      <c r="I134" t="s">
+      <c r="K134" t="s">
         <v>541</v>
-      </c>
-      <c r="J134" t="s">
-        <v>338</v>
-      </c>
-      <c r="K134" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -8043,19 +8043,19 @@
         <v>14</v>
       </c>
       <c r="E135" t="s">
+        <v>337</v>
+      </c>
+      <c r="F135" t="s">
         <v>361</v>
       </c>
-      <c r="H135" t="s">
+      <c r="G135" t="s">
+        <v>362</v>
+      </c>
+      <c r="I135" t="s">
         <v>540</v>
       </c>
-      <c r="I135" t="s">
+      <c r="K135" t="s">
         <v>541</v>
-      </c>
-      <c r="J135" t="s">
-        <v>338</v>
-      </c>
-      <c r="K135" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -8072,19 +8072,19 @@
         <v>14</v>
       </c>
       <c r="E136" t="s">
+        <v>337</v>
+      </c>
+      <c r="F136" t="s">
         <v>361</v>
       </c>
-      <c r="H136" t="s">
+      <c r="G136" t="s">
+        <v>362</v>
+      </c>
+      <c r="I136" t="s">
         <v>540</v>
       </c>
-      <c r="I136" t="s">
+      <c r="K136" t="s">
         <v>541</v>
-      </c>
-      <c r="J136" t="s">
-        <v>338</v>
-      </c>
-      <c r="K136" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -8101,19 +8101,19 @@
         <v>14</v>
       </c>
       <c r="E137" t="s">
+        <v>337</v>
+      </c>
+      <c r="F137" t="s">
         <v>361</v>
       </c>
-      <c r="H137" t="s">
+      <c r="G137" t="s">
+        <v>362</v>
+      </c>
+      <c r="I137" t="s">
         <v>540</v>
       </c>
-      <c r="I137" t="s">
+      <c r="K137" t="s">
         <v>541</v>
-      </c>
-      <c r="J137" t="s">
-        <v>338</v>
-      </c>
-      <c r="K137" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -8130,19 +8130,19 @@
         <v>14</v>
       </c>
       <c r="E138" t="s">
+        <v>337</v>
+      </c>
+      <c r="F138" t="s">
         <v>361</v>
       </c>
-      <c r="H138" t="s">
+      <c r="G138" t="s">
+        <v>362</v>
+      </c>
+      <c r="I138" t="s">
         <v>540</v>
       </c>
-      <c r="I138" t="s">
+      <c r="K138" t="s">
         <v>541</v>
-      </c>
-      <c r="J138" t="s">
-        <v>338</v>
-      </c>
-      <c r="K138" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -8159,19 +8159,19 @@
         <v>14</v>
       </c>
       <c r="E139" t="s">
+        <v>462</v>
+      </c>
+      <c r="F139" t="s">
         <v>556</v>
       </c>
-      <c r="H139" t="s">
+      <c r="G139" t="s">
+        <v>557</v>
+      </c>
+      <c r="I139" t="s">
         <v>540</v>
       </c>
-      <c r="I139" t="s">
+      <c r="K139" t="s">
         <v>541</v>
-      </c>
-      <c r="J139" t="s">
-        <v>463</v>
-      </c>
-      <c r="K139" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -8188,19 +8188,19 @@
         <v>14</v>
       </c>
       <c r="E140" t="s">
+        <v>337</v>
+      </c>
+      <c r="F140" t="s">
         <v>361</v>
       </c>
-      <c r="H140" t="s">
+      <c r="G140" t="s">
+        <v>362</v>
+      </c>
+      <c r="I140" t="s">
         <v>540</v>
       </c>
-      <c r="I140" t="s">
+      <c r="K140" t="s">
         <v>541</v>
-      </c>
-      <c r="J140" t="s">
-        <v>338</v>
-      </c>
-      <c r="K140" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -8217,22 +8217,22 @@
         <v>14</v>
       </c>
       <c r="E141" t="s">
+        <v>337</v>
+      </c>
+      <c r="F141" t="s">
         <v>564</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>565</v>
       </c>
-      <c r="G141" t="s">
+      <c r="H141" t="s">
         <v>566</v>
       </c>
-      <c r="H141" t="s">
+      <c r="I141" t="s">
         <v>567</v>
       </c>
-      <c r="I141" t="s">
+      <c r="J141" t="s">
         <v>568</v>
-      </c>
-      <c r="J141" t="s">
-        <v>338</v>
       </c>
       <c r="K141" t="s">
         <v>569</v>
@@ -8249,22 +8249,22 @@
         <v>14</v>
       </c>
       <c r="E142" t="s">
+        <v>337</v>
+      </c>
+      <c r="F142" t="s">
         <v>564</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>565</v>
       </c>
-      <c r="G142" t="s">
+      <c r="H142" t="s">
         <v>566</v>
       </c>
-      <c r="H142" t="s">
+      <c r="I142" t="s">
         <v>567</v>
       </c>
-      <c r="I142" t="s">
+      <c r="J142" t="s">
         <v>568</v>
-      </c>
-      <c r="J142" t="s">
-        <v>338</v>
       </c>
       <c r="K142" t="s">
         <v>569</v>
@@ -8284,25 +8284,25 @@
         <v>14</v>
       </c>
       <c r="E143" t="s">
+        <v>337</v>
+      </c>
+      <c r="F143" t="s">
         <v>575</v>
       </c>
-      <c r="F143" t="s">
-        <v>565</v>
-      </c>
       <c r="G143" t="s">
+        <v>576</v>
+      </c>
+      <c r="H143" t="s">
         <v>566</v>
       </c>
-      <c r="H143" t="s">
+      <c r="I143" t="s">
         <v>567</v>
       </c>
-      <c r="I143" t="s">
+      <c r="J143" t="s">
         <v>568</v>
       </c>
-      <c r="J143" t="s">
-        <v>338</v>
-      </c>
       <c r="K143" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -8319,25 +8319,25 @@
         <v>14</v>
       </c>
       <c r="E144" t="s">
+        <v>337</v>
+      </c>
+      <c r="F144" t="s">
         <v>575</v>
       </c>
-      <c r="F144" t="s">
-        <v>565</v>
-      </c>
       <c r="G144" t="s">
+        <v>576</v>
+      </c>
+      <c r="H144" t="s">
         <v>566</v>
       </c>
-      <c r="H144" t="s">
+      <c r="I144" t="s">
         <v>567</v>
       </c>
-      <c r="I144" t="s">
+      <c r="J144" t="s">
         <v>568</v>
       </c>
-      <c r="J144" t="s">
-        <v>338</v>
-      </c>
       <c r="K144" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -8354,25 +8354,25 @@
         <v>14</v>
       </c>
       <c r="E145" t="s">
+        <v>337</v>
+      </c>
+      <c r="F145" t="s">
         <v>575</v>
       </c>
-      <c r="F145" t="s">
-        <v>565</v>
-      </c>
       <c r="G145" t="s">
+        <v>576</v>
+      </c>
+      <c r="H145" t="s">
         <v>566</v>
       </c>
-      <c r="H145" t="s">
+      <c r="I145" t="s">
         <v>567</v>
       </c>
-      <c r="I145" t="s">
+      <c r="J145" t="s">
         <v>568</v>
       </c>
-      <c r="J145" t="s">
-        <v>338</v>
-      </c>
       <c r="K145" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -8389,22 +8389,22 @@
         <v>14</v>
       </c>
       <c r="E146" t="s">
+        <v>337</v>
+      </c>
+      <c r="F146" t="s">
         <v>564</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>565</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" t="s">
         <v>566</v>
       </c>
-      <c r="H146" t="s">
+      <c r="I146" t="s">
         <v>567</v>
       </c>
-      <c r="I146" t="s">
+      <c r="J146" t="s">
         <v>568</v>
-      </c>
-      <c r="J146" t="s">
-        <v>338</v>
       </c>
       <c r="K146" t="s">
         <v>569</v>
@@ -8424,22 +8424,22 @@
         <v>14</v>
       </c>
       <c r="E147" t="s">
+        <v>337</v>
+      </c>
+      <c r="F147" t="s">
         <v>564</v>
       </c>
-      <c r="F147" t="s">
+      <c r="G147" t="s">
+        <v>565</v>
+      </c>
+      <c r="H147" t="s">
         <v>589</v>
       </c>
-      <c r="G147" t="s">
+      <c r="I147" t="s">
+        <v>567</v>
+      </c>
+      <c r="J147" t="s">
         <v>590</v>
-      </c>
-      <c r="H147" t="s">
-        <v>567</v>
-      </c>
-      <c r="I147" t="s">
-        <v>568</v>
-      </c>
-      <c r="J147" t="s">
-        <v>338</v>
       </c>
       <c r="K147" t="s">
         <v>569</v>
@@ -8459,22 +8459,22 @@
         <v>14</v>
       </c>
       <c r="E148" t="s">
+        <v>337</v>
+      </c>
+      <c r="F148" t="s">
         <v>564</v>
       </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
+        <v>565</v>
+      </c>
+      <c r="H148" t="s">
         <v>589</v>
       </c>
-      <c r="G148" t="s">
+      <c r="I148" t="s">
+        <v>567</v>
+      </c>
+      <c r="J148" t="s">
         <v>590</v>
-      </c>
-      <c r="H148" t="s">
-        <v>567</v>
-      </c>
-      <c r="I148" t="s">
-        <v>568</v>
-      </c>
-      <c r="J148" t="s">
-        <v>338</v>
       </c>
       <c r="K148" t="s">
         <v>569</v>
@@ -8494,22 +8494,22 @@
         <v>14</v>
       </c>
       <c r="E149" t="s">
+        <v>337</v>
+      </c>
+      <c r="F149" t="s">
         <v>564</v>
       </c>
-      <c r="F149" t="s">
+      <c r="G149" t="s">
+        <v>565</v>
+      </c>
+      <c r="H149" t="s">
         <v>589</v>
       </c>
-      <c r="G149" t="s">
+      <c r="I149" t="s">
+        <v>567</v>
+      </c>
+      <c r="J149" t="s">
         <v>590</v>
-      </c>
-      <c r="H149" t="s">
-        <v>567</v>
-      </c>
-      <c r="I149" t="s">
-        <v>568</v>
-      </c>
-      <c r="J149" t="s">
-        <v>338</v>
       </c>
       <c r="K149" t="s">
         <v>569</v>
@@ -8529,22 +8529,22 @@
         <v>14</v>
       </c>
       <c r="E150" t="s">
+        <v>337</v>
+      </c>
+      <c r="F150" t="s">
         <v>564</v>
       </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
+        <v>565</v>
+      </c>
+      <c r="H150" t="s">
         <v>589</v>
       </c>
-      <c r="G150" t="s">
+      <c r="I150" t="s">
+        <v>567</v>
+      </c>
+      <c r="J150" t="s">
         <v>590</v>
-      </c>
-      <c r="H150" t="s">
-        <v>567</v>
-      </c>
-      <c r="I150" t="s">
-        <v>568</v>
-      </c>
-      <c r="J150" t="s">
-        <v>338</v>
       </c>
       <c r="K150" t="s">
         <v>569</v>
@@ -8564,22 +8564,22 @@
         <v>14</v>
       </c>
       <c r="E151" t="s">
+        <v>337</v>
+      </c>
+      <c r="F151" t="s">
         <v>564</v>
       </c>
-      <c r="F151" t="s">
+      <c r="G151" t="s">
+        <v>565</v>
+      </c>
+      <c r="H151" t="s">
         <v>589</v>
       </c>
-      <c r="G151" t="s">
+      <c r="I151" t="s">
+        <v>567</v>
+      </c>
+      <c r="J151" t="s">
         <v>590</v>
-      </c>
-      <c r="H151" t="s">
-        <v>567</v>
-      </c>
-      <c r="I151" t="s">
-        <v>568</v>
-      </c>
-      <c r="J151" t="s">
-        <v>338</v>
       </c>
       <c r="K151" t="s">
         <v>569</v>
@@ -8599,22 +8599,22 @@
         <v>14</v>
       </c>
       <c r="E152" t="s">
+        <v>337</v>
+      </c>
+      <c r="F152" t="s">
         <v>564</v>
       </c>
-      <c r="F152" t="s">
+      <c r="G152" t="s">
+        <v>565</v>
+      </c>
+      <c r="H152" t="s">
         <v>589</v>
       </c>
-      <c r="G152" t="s">
+      <c r="I152" t="s">
+        <v>567</v>
+      </c>
+      <c r="J152" t="s">
         <v>590</v>
-      </c>
-      <c r="H152" t="s">
-        <v>567</v>
-      </c>
-      <c r="I152" t="s">
-        <v>568</v>
-      </c>
-      <c r="J152" t="s">
-        <v>338</v>
       </c>
       <c r="K152" t="s">
         <v>569</v>
@@ -8634,22 +8634,22 @@
         <v>14</v>
       </c>
       <c r="E153" t="s">
+        <v>337</v>
+      </c>
+      <c r="F153" t="s">
         <v>564</v>
       </c>
-      <c r="F153" t="s">
+      <c r="G153" t="s">
+        <v>565</v>
+      </c>
+      <c r="H153" t="s">
         <v>589</v>
       </c>
-      <c r="G153" t="s">
+      <c r="I153" t="s">
+        <v>567</v>
+      </c>
+      <c r="J153" t="s">
         <v>590</v>
-      </c>
-      <c r="H153" t="s">
-        <v>567</v>
-      </c>
-      <c r="I153" t="s">
-        <v>568</v>
-      </c>
-      <c r="J153" t="s">
-        <v>338</v>
       </c>
       <c r="K153" t="s">
         <v>569</v>
@@ -8669,22 +8669,22 @@
         <v>14</v>
       </c>
       <c r="E154" t="s">
+        <v>337</v>
+      </c>
+      <c r="F154" t="s">
         <v>564</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
+        <v>565</v>
+      </c>
+      <c r="H154" t="s">
         <v>589</v>
       </c>
-      <c r="G154" t="s">
+      <c r="I154" t="s">
+        <v>567</v>
+      </c>
+      <c r="J154" t="s">
         <v>590</v>
-      </c>
-      <c r="H154" t="s">
-        <v>567</v>
-      </c>
-      <c r="I154" t="s">
-        <v>568</v>
-      </c>
-      <c r="J154" t="s">
-        <v>338</v>
       </c>
       <c r="K154" t="s">
         <v>569</v>
@@ -8704,22 +8704,22 @@
         <v>14</v>
       </c>
       <c r="E155" t="s">
+        <v>337</v>
+      </c>
+      <c r="F155" t="s">
         <v>564</v>
       </c>
-      <c r="F155" t="s">
+      <c r="G155" t="s">
+        <v>565</v>
+      </c>
+      <c r="H155" t="s">
         <v>589</v>
       </c>
-      <c r="G155" t="s">
+      <c r="I155" t="s">
+        <v>567</v>
+      </c>
+      <c r="J155" t="s">
         <v>590</v>
-      </c>
-      <c r="H155" t="s">
-        <v>567</v>
-      </c>
-      <c r="I155" t="s">
-        <v>568</v>
-      </c>
-      <c r="J155" t="s">
-        <v>338</v>
       </c>
       <c r="K155" t="s">
         <v>569</v>
@@ -8739,22 +8739,22 @@
         <v>14</v>
       </c>
       <c r="E156" t="s">
+        <v>337</v>
+      </c>
+      <c r="F156" t="s">
         <v>564</v>
       </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
+        <v>565</v>
+      </c>
+      <c r="H156" t="s">
         <v>618</v>
       </c>
-      <c r="G156" t="s">
+      <c r="I156" t="s">
+        <v>567</v>
+      </c>
+      <c r="J156" t="s">
         <v>619</v>
-      </c>
-      <c r="H156" t="s">
-        <v>567</v>
-      </c>
-      <c r="I156" t="s">
-        <v>568</v>
-      </c>
-      <c r="J156" t="s">
-        <v>338</v>
       </c>
       <c r="K156" t="s">
         <v>569</v>
@@ -8774,22 +8774,22 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
+        <v>337</v>
+      </c>
+      <c r="F157" t="s">
         <v>623</v>
       </c>
-      <c r="F157" t="s">
+      <c r="G157" t="s">
+        <v>565</v>
+      </c>
+      <c r="H157" t="s">
         <v>618</v>
       </c>
-      <c r="G157" t="s">
+      <c r="I157" t="s">
+        <v>567</v>
+      </c>
+      <c r="J157" t="s">
         <v>619</v>
-      </c>
-      <c r="H157" t="s">
-        <v>567</v>
-      </c>
-      <c r="I157" t="s">
-        <v>568</v>
-      </c>
-      <c r="J157" t="s">
-        <v>338</v>
       </c>
       <c r="K157" t="s">
         <v>569</v>
@@ -8809,22 +8809,22 @@
         <v>14</v>
       </c>
       <c r="E158" t="s">
+        <v>337</v>
+      </c>
+      <c r="F158" t="s">
         <v>564</v>
       </c>
-      <c r="F158" t="s">
+      <c r="G158" t="s">
+        <v>565</v>
+      </c>
+      <c r="H158" t="s">
         <v>618</v>
       </c>
-      <c r="G158" t="s">
+      <c r="I158" t="s">
+        <v>567</v>
+      </c>
+      <c r="J158" t="s">
         <v>619</v>
-      </c>
-      <c r="H158" t="s">
-        <v>567</v>
-      </c>
-      <c r="I158" t="s">
-        <v>568</v>
-      </c>
-      <c r="J158" t="s">
-        <v>338</v>
       </c>
       <c r="K158" t="s">
         <v>569</v>
@@ -8844,22 +8844,22 @@
         <v>14</v>
       </c>
       <c r="E159" t="s">
+        <v>337</v>
+      </c>
+      <c r="F159" t="s">
         <v>564</v>
       </c>
-      <c r="F159" t="s">
+      <c r="G159" t="s">
+        <v>565</v>
+      </c>
+      <c r="H159" t="s">
         <v>618</v>
       </c>
-      <c r="G159" t="s">
+      <c r="I159" t="s">
+        <v>567</v>
+      </c>
+      <c r="J159" t="s">
         <v>619</v>
-      </c>
-      <c r="H159" t="s">
-        <v>567</v>
-      </c>
-      <c r="I159" t="s">
-        <v>568</v>
-      </c>
-      <c r="J159" t="s">
-        <v>338</v>
       </c>
       <c r="K159" t="s">
         <v>569</v>
@@ -8879,22 +8879,22 @@
         <v>14</v>
       </c>
       <c r="E160" t="s">
+        <v>337</v>
+      </c>
+      <c r="F160" t="s">
         <v>564</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
+        <v>565</v>
+      </c>
+      <c r="H160" t="s">
         <v>618</v>
       </c>
-      <c r="G160" t="s">
+      <c r="I160" t="s">
+        <v>567</v>
+      </c>
+      <c r="J160" t="s">
         <v>619</v>
-      </c>
-      <c r="H160" t="s">
-        <v>567</v>
-      </c>
-      <c r="I160" t="s">
-        <v>568</v>
-      </c>
-      <c r="J160" t="s">
-        <v>338</v>
       </c>
       <c r="K160" t="s">
         <v>569</v>
@@ -8914,22 +8914,22 @@
         <v>14</v>
       </c>
       <c r="E161" t="s">
+        <v>337</v>
+      </c>
+      <c r="F161" t="s">
         <v>564</v>
       </c>
-      <c r="F161" t="s">
+      <c r="G161" t="s">
+        <v>565</v>
+      </c>
+      <c r="H161" t="s">
         <v>618</v>
       </c>
-      <c r="G161" t="s">
+      <c r="I161" t="s">
+        <v>567</v>
+      </c>
+      <c r="J161" t="s">
         <v>619</v>
-      </c>
-      <c r="H161" t="s">
-        <v>567</v>
-      </c>
-      <c r="I161" t="s">
-        <v>568</v>
-      </c>
-      <c r="J161" t="s">
-        <v>338</v>
       </c>
       <c r="K161" t="s">
         <v>569</v>
@@ -8949,22 +8949,22 @@
         <v>14</v>
       </c>
       <c r="E162" t="s">
+        <v>337</v>
+      </c>
+      <c r="F162" t="s">
         <v>564</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
+        <v>565</v>
+      </c>
+      <c r="H162" t="s">
         <v>639</v>
       </c>
-      <c r="G162" t="s">
+      <c r="I162" t="s">
+        <v>567</v>
+      </c>
+      <c r="J162" t="s">
         <v>640</v>
-      </c>
-      <c r="H162" t="s">
-        <v>567</v>
-      </c>
-      <c r="I162" t="s">
-        <v>568</v>
-      </c>
-      <c r="J162" t="s">
-        <v>338</v>
       </c>
       <c r="K162" t="s">
         <v>569</v>
@@ -8984,22 +8984,22 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
+        <v>337</v>
+      </c>
+      <c r="F163" t="s">
         <v>644</v>
       </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
+        <v>565</v>
+      </c>
+      <c r="H163" t="s">
         <v>642</v>
       </c>
-      <c r="G163" t="s">
+      <c r="I163" t="s">
+        <v>567</v>
+      </c>
+      <c r="J163" t="s">
         <v>645</v>
-      </c>
-      <c r="H163" t="s">
-        <v>567</v>
-      </c>
-      <c r="I163" t="s">
-        <v>568</v>
-      </c>
-      <c r="J163" t="s">
-        <v>338</v>
       </c>
       <c r="K163" t="s">
         <v>569</v>
@@ -9019,22 +9019,22 @@
         <v>14</v>
       </c>
       <c r="E164" t="s">
+        <v>337</v>
+      </c>
+      <c r="F164" t="s">
         <v>564</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
+        <v>565</v>
+      </c>
+      <c r="H164" t="s">
         <v>649</v>
       </c>
-      <c r="G164" t="s">
+      <c r="I164" t="s">
+        <v>567</v>
+      </c>
+      <c r="J164" t="s">
         <v>650</v>
-      </c>
-      <c r="H164" t="s">
-        <v>567</v>
-      </c>
-      <c r="I164" t="s">
-        <v>568</v>
-      </c>
-      <c r="J164" t="s">
-        <v>338</v>
       </c>
       <c r="K164" t="s">
         <v>569</v>
@@ -9054,22 +9054,22 @@
         <v>14</v>
       </c>
       <c r="E165" t="s">
+        <v>337</v>
+      </c>
+      <c r="F165" t="s">
         <v>564</v>
       </c>
-      <c r="F165" t="s">
+      <c r="G165" t="s">
+        <v>565</v>
+      </c>
+      <c r="H165" t="s">
         <v>649</v>
       </c>
-      <c r="G165" t="s">
+      <c r="I165" t="s">
+        <v>567</v>
+      </c>
+      <c r="J165" t="s">
         <v>650</v>
-      </c>
-      <c r="H165" t="s">
-        <v>567</v>
-      </c>
-      <c r="I165" t="s">
-        <v>568</v>
-      </c>
-      <c r="J165" t="s">
-        <v>338</v>
       </c>
       <c r="K165" t="s">
         <v>569</v>
@@ -9089,22 +9089,22 @@
         <v>14</v>
       </c>
       <c r="E166" t="s">
+        <v>337</v>
+      </c>
+      <c r="F166" t="s">
         <v>564</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
+        <v>565</v>
+      </c>
+      <c r="H166" t="s">
         <v>649</v>
       </c>
-      <c r="G166" t="s">
+      <c r="I166" t="s">
+        <v>567</v>
+      </c>
+      <c r="J166" t="s">
         <v>650</v>
-      </c>
-      <c r="H166" t="s">
-        <v>567</v>
-      </c>
-      <c r="I166" t="s">
-        <v>568</v>
-      </c>
-      <c r="J166" t="s">
-        <v>338</v>
       </c>
       <c r="K166" t="s">
         <v>569</v>
@@ -9124,22 +9124,22 @@
         <v>14</v>
       </c>
       <c r="E167" t="s">
+        <v>337</v>
+      </c>
+      <c r="F167" t="s">
         <v>564</v>
       </c>
-      <c r="F167" t="s">
+      <c r="G167" t="s">
+        <v>565</v>
+      </c>
+      <c r="H167" t="s">
         <v>649</v>
       </c>
-      <c r="G167" t="s">
+      <c r="I167" t="s">
+        <v>567</v>
+      </c>
+      <c r="J167" t="s">
         <v>650</v>
-      </c>
-      <c r="H167" t="s">
-        <v>567</v>
-      </c>
-      <c r="I167" t="s">
-        <v>568</v>
-      </c>
-      <c r="J167" t="s">
-        <v>338</v>
       </c>
       <c r="K167" t="s">
         <v>569</v>
@@ -9159,22 +9159,22 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
+        <v>337</v>
+      </c>
+      <c r="F168" t="s">
         <v>663</v>
       </c>
-      <c r="F168" t="s">
+      <c r="G168" t="s">
+        <v>565</v>
+      </c>
+      <c r="H168" t="s">
         <v>649</v>
       </c>
-      <c r="G168" t="s">
+      <c r="I168" t="s">
+        <v>567</v>
+      </c>
+      <c r="J168" t="s">
         <v>650</v>
-      </c>
-      <c r="H168" t="s">
-        <v>567</v>
-      </c>
-      <c r="I168" t="s">
-        <v>568</v>
-      </c>
-      <c r="J168" t="s">
-        <v>338</v>
       </c>
       <c r="K168" t="s">
         <v>569</v>
@@ -9191,22 +9191,22 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
+        <v>337</v>
+      </c>
+      <c r="F169" t="s">
         <v>663</v>
       </c>
-      <c r="F169" t="s">
+      <c r="G169" t="s">
+        <v>565</v>
+      </c>
+      <c r="H169" t="s">
         <v>649</v>
       </c>
-      <c r="G169" t="s">
+      <c r="I169" t="s">
+        <v>567</v>
+      </c>
+      <c r="J169" t="s">
         <v>650</v>
-      </c>
-      <c r="H169" t="s">
-        <v>567</v>
-      </c>
-      <c r="I169" t="s">
-        <v>568</v>
-      </c>
-      <c r="J169" t="s">
-        <v>338</v>
       </c>
       <c r="K169" t="s">
         <v>569</v>
@@ -9226,22 +9226,22 @@
         <v>14</v>
       </c>
       <c r="E170" t="s">
+        <v>337</v>
+      </c>
+      <c r="F170" t="s">
         <v>564</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
+        <v>565</v>
+      </c>
+      <c r="H170" t="s">
         <v>649</v>
       </c>
-      <c r="G170" t="s">
+      <c r="I170" t="s">
+        <v>567</v>
+      </c>
+      <c r="J170" t="s">
         <v>650</v>
-      </c>
-      <c r="H170" t="s">
-        <v>567</v>
-      </c>
-      <c r="I170" t="s">
-        <v>568</v>
-      </c>
-      <c r="J170" t="s">
-        <v>338</v>
       </c>
       <c r="K170" t="s">
         <v>569</v>
@@ -9263,17 +9263,17 @@
       <c r="E171" t="s">
         <v>337</v>
       </c>
-      <c r="H171" t="s">
+      <c r="F171" t="s">
+        <v>338</v>
+      </c>
+      <c r="G171" t="s">
+        <v>339</v>
+      </c>
+      <c r="I171" t="s">
         <v>672</v>
       </c>
-      <c r="I171" t="s">
+      <c r="K171" t="s">
         <v>673</v>
-      </c>
-      <c r="J171" t="s">
-        <v>338</v>
-      </c>
-      <c r="K171" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -9290,19 +9290,19 @@
         <v>14</v>
       </c>
       <c r="E172" t="s">
+        <v>233</v>
+      </c>
+      <c r="F172" t="s">
         <v>243</v>
       </c>
-      <c r="H172" t="s">
+      <c r="G172" t="s">
+        <v>244</v>
+      </c>
+      <c r="I172" t="s">
         <v>672</v>
       </c>
-      <c r="I172" t="s">
+      <c r="K172" t="s">
         <v>673</v>
-      </c>
-      <c r="J172" t="s">
-        <v>238</v>
-      </c>
-      <c r="K172" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -9321,17 +9321,17 @@
       <c r="E173" t="s">
         <v>337</v>
       </c>
-      <c r="H173" t="s">
+      <c r="F173" t="s">
+        <v>338</v>
+      </c>
+      <c r="G173" t="s">
+        <v>339</v>
+      </c>
+      <c r="I173" t="s">
         <v>672</v>
       </c>
-      <c r="I173" t="s">
+      <c r="K173" t="s">
         <v>673</v>
-      </c>
-      <c r="J173" t="s">
-        <v>338</v>
-      </c>
-      <c r="K173" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -9350,17 +9350,17 @@
       <c r="E174" t="s">
         <v>337</v>
       </c>
-      <c r="H174" t="s">
+      <c r="F174" t="s">
+        <v>338</v>
+      </c>
+      <c r="G174" t="s">
+        <v>339</v>
+      </c>
+      <c r="I174" t="s">
         <v>672</v>
       </c>
-      <c r="I174" t="s">
+      <c r="K174" t="s">
         <v>673</v>
-      </c>
-      <c r="J174" t="s">
-        <v>338</v>
-      </c>
-      <c r="K174" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -9379,17 +9379,17 @@
       <c r="E175" t="s">
         <v>337</v>
       </c>
-      <c r="H175" t="s">
+      <c r="F175" t="s">
+        <v>338</v>
+      </c>
+      <c r="G175" t="s">
+        <v>339</v>
+      </c>
+      <c r="I175" t="s">
         <v>672</v>
       </c>
-      <c r="I175" t="s">
+      <c r="K175" t="s">
         <v>673</v>
-      </c>
-      <c r="J175" t="s">
-        <v>338</v>
-      </c>
-      <c r="K175" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -9405,17 +9405,17 @@
       <c r="E176" t="s">
         <v>337</v>
       </c>
-      <c r="H176" t="s">
+      <c r="F176" t="s">
+        <v>338</v>
+      </c>
+      <c r="G176" t="s">
+        <v>339</v>
+      </c>
+      <c r="I176" t="s">
         <v>672</v>
       </c>
-      <c r="I176" t="s">
+      <c r="K176" t="s">
         <v>673</v>
-      </c>
-      <c r="J176" t="s">
-        <v>338</v>
-      </c>
-      <c r="K176" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -9434,17 +9434,17 @@
       <c r="E177" t="s">
         <v>337</v>
       </c>
-      <c r="H177" t="s">
+      <c r="F177" t="s">
+        <v>338</v>
+      </c>
+      <c r="G177" t="s">
+        <v>339</v>
+      </c>
+      <c r="I177" t="s">
         <v>691</v>
       </c>
-      <c r="I177" t="s">
+      <c r="K177" t="s">
         <v>692</v>
-      </c>
-      <c r="J177" t="s">
-        <v>338</v>
-      </c>
-      <c r="K177" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -9463,17 +9463,17 @@
       <c r="E178" t="s">
         <v>337</v>
       </c>
-      <c r="H178" t="s">
+      <c r="F178" t="s">
+        <v>338</v>
+      </c>
+      <c r="G178" t="s">
+        <v>339</v>
+      </c>
+      <c r="I178" t="s">
         <v>691</v>
       </c>
-      <c r="I178" t="s">
+      <c r="K178" t="s">
         <v>692</v>
-      </c>
-      <c r="J178" t="s">
-        <v>338</v>
-      </c>
-      <c r="K178" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -9492,17 +9492,17 @@
       <c r="E179" t="s">
         <v>337</v>
       </c>
-      <c r="H179" t="s">
+      <c r="F179" t="s">
+        <v>338</v>
+      </c>
+      <c r="G179" t="s">
+        <v>339</v>
+      </c>
+      <c r="I179" t="s">
         <v>691</v>
       </c>
-      <c r="I179" t="s">
+      <c r="K179" t="s">
         <v>692</v>
-      </c>
-      <c r="J179" t="s">
-        <v>338</v>
-      </c>
-      <c r="K179" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -9521,17 +9521,17 @@
       <c r="E180" t="s">
         <v>337</v>
       </c>
-      <c r="H180" t="s">
+      <c r="F180" t="s">
+        <v>338</v>
+      </c>
+      <c r="G180" t="s">
+        <v>339</v>
+      </c>
+      <c r="I180" t="s">
         <v>691</v>
       </c>
-      <c r="I180" t="s">
+      <c r="K180" t="s">
         <v>692</v>
-      </c>
-      <c r="J180" t="s">
-        <v>338</v>
-      </c>
-      <c r="K180" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -9548,22 +9548,22 @@
         <v>14</v>
       </c>
       <c r="E181" t="s">
+        <v>337</v>
+      </c>
+      <c r="F181" t="s">
         <v>705</v>
       </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
         <v>706</v>
       </c>
-      <c r="G181" t="s">
+      <c r="H181" t="s">
         <v>707</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>708</v>
       </c>
-      <c r="I181" t="s">
+      <c r="J181" t="s">
         <v>709</v>
-      </c>
-      <c r="J181" t="s">
-        <v>338</v>
       </c>
       <c r="K181" t="s">
         <v>710</v>
@@ -9583,22 +9583,22 @@
         <v>14</v>
       </c>
       <c r="E182" t="s">
+        <v>337</v>
+      </c>
+      <c r="F182" t="s">
         <v>705</v>
       </c>
-      <c r="F182" t="s">
+      <c r="G182" t="s">
         <v>706</v>
       </c>
-      <c r="G182" t="s">
+      <c r="H182" t="s">
         <v>707</v>
       </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>708</v>
       </c>
-      <c r="I182" t="s">
+      <c r="J182" t="s">
         <v>709</v>
-      </c>
-      <c r="J182" t="s">
-        <v>338</v>
       </c>
       <c r="K182" t="s">
         <v>710</v>
@@ -9618,22 +9618,22 @@
         <v>14</v>
       </c>
       <c r="E183" t="s">
+        <v>337</v>
+      </c>
+      <c r="F183" t="s">
         <v>705</v>
       </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
         <v>706</v>
       </c>
-      <c r="G183" t="s">
+      <c r="H183" t="s">
         <v>707</v>
       </c>
-      <c r="H183" t="s">
+      <c r="I183" t="s">
         <v>708</v>
       </c>
-      <c r="I183" t="s">
+      <c r="J183" t="s">
         <v>709</v>
-      </c>
-      <c r="J183" t="s">
-        <v>338</v>
       </c>
       <c r="K183" t="s">
         <v>710</v>
@@ -9653,22 +9653,22 @@
         <v>14</v>
       </c>
       <c r="E184" t="s">
+        <v>337</v>
+      </c>
+      <c r="F184" t="s">
         <v>705</v>
       </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
         <v>706</v>
       </c>
-      <c r="G184" t="s">
+      <c r="H184" t="s">
         <v>707</v>
       </c>
-      <c r="H184" t="s">
+      <c r="I184" t="s">
         <v>708</v>
       </c>
-      <c r="I184" t="s">
+      <c r="J184" t="s">
         <v>709</v>
-      </c>
-      <c r="J184" t="s">
-        <v>338</v>
       </c>
       <c r="K184" t="s">
         <v>710</v>
@@ -9688,22 +9688,22 @@
         <v>14</v>
       </c>
       <c r="E185" t="s">
+        <v>337</v>
+      </c>
+      <c r="F185" t="s">
         <v>705</v>
       </c>
-      <c r="F185" t="s">
+      <c r="G185" t="s">
         <v>706</v>
       </c>
-      <c r="G185" t="s">
+      <c r="H185" t="s">
         <v>707</v>
       </c>
-      <c r="H185" t="s">
+      <c r="I185" t="s">
         <v>708</v>
       </c>
-      <c r="I185" t="s">
+      <c r="J185" t="s">
         <v>709</v>
-      </c>
-      <c r="J185" t="s">
-        <v>338</v>
       </c>
       <c r="K185" t="s">
         <v>710</v>
@@ -9723,22 +9723,22 @@
         <v>14</v>
       </c>
       <c r="E186" t="s">
+        <v>337</v>
+      </c>
+      <c r="F186" t="s">
         <v>705</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>706</v>
       </c>
-      <c r="G186" t="s">
+      <c r="H186" t="s">
         <v>707</v>
       </c>
-      <c r="H186" t="s">
+      <c r="I186" t="s">
         <v>708</v>
       </c>
-      <c r="I186" t="s">
+      <c r="J186" t="s">
         <v>709</v>
-      </c>
-      <c r="J186" t="s">
-        <v>338</v>
       </c>
       <c r="K186" t="s">
         <v>710</v>
@@ -9758,22 +9758,22 @@
         <v>14</v>
       </c>
       <c r="E187" t="s">
+        <v>337</v>
+      </c>
+      <c r="F187" t="s">
         <v>705</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>706</v>
       </c>
-      <c r="G187" t="s">
+      <c r="H187" t="s">
         <v>707</v>
       </c>
-      <c r="H187" t="s">
+      <c r="I187" t="s">
         <v>708</v>
       </c>
-      <c r="I187" t="s">
+      <c r="J187" t="s">
         <v>709</v>
-      </c>
-      <c r="J187" t="s">
-        <v>338</v>
       </c>
       <c r="K187" t="s">
         <v>710</v>
@@ -9793,22 +9793,22 @@
         <v>14</v>
       </c>
       <c r="E188" t="s">
+        <v>337</v>
+      </c>
+      <c r="F188" t="s">
         <v>705</v>
       </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>706</v>
       </c>
-      <c r="G188" t="s">
+      <c r="H188" t="s">
         <v>707</v>
       </c>
-      <c r="H188" t="s">
+      <c r="I188" t="s">
         <v>708</v>
       </c>
-      <c r="I188" t="s">
+      <c r="J188" t="s">
         <v>709</v>
-      </c>
-      <c r="J188" t="s">
-        <v>338</v>
       </c>
       <c r="K188" t="s">
         <v>710</v>
@@ -9828,22 +9828,22 @@
         <v>14</v>
       </c>
       <c r="E189" t="s">
+        <v>337</v>
+      </c>
+      <c r="F189" t="s">
         <v>705</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>706</v>
       </c>
-      <c r="G189" t="s">
+      <c r="H189" t="s">
         <v>707</v>
       </c>
-      <c r="H189" t="s">
+      <c r="I189" t="s">
         <v>708</v>
       </c>
-      <c r="I189" t="s">
+      <c r="J189" t="s">
         <v>709</v>
-      </c>
-      <c r="J189" t="s">
-        <v>338</v>
       </c>
       <c r="K189" t="s">
         <v>710</v>
@@ -9863,22 +9863,22 @@
         <v>14</v>
       </c>
       <c r="E190" t="s">
+        <v>337</v>
+      </c>
+      <c r="F190" t="s">
         <v>705</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>706</v>
       </c>
-      <c r="G190" t="s">
+      <c r="H190" t="s">
         <v>707</v>
       </c>
-      <c r="H190" t="s">
+      <c r="I190" t="s">
         <v>708</v>
       </c>
-      <c r="I190" t="s">
+      <c r="J190" t="s">
         <v>709</v>
-      </c>
-      <c r="J190" t="s">
-        <v>338</v>
       </c>
       <c r="K190" t="s">
         <v>710</v>
@@ -9898,22 +9898,22 @@
         <v>14</v>
       </c>
       <c r="E191" t="s">
+        <v>337</v>
+      </c>
+      <c r="F191" t="s">
         <v>705</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>706</v>
       </c>
-      <c r="G191" t="s">
+      <c r="H191" t="s">
         <v>707</v>
       </c>
-      <c r="H191" t="s">
+      <c r="I191" t="s">
         <v>708</v>
       </c>
-      <c r="I191" t="s">
+      <c r="J191" t="s">
         <v>709</v>
-      </c>
-      <c r="J191" t="s">
-        <v>338</v>
       </c>
       <c r="K191" t="s">
         <v>710</v>
@@ -9930,22 +9930,22 @@
         <v>14</v>
       </c>
       <c r="E192" t="s">
+        <v>337</v>
+      </c>
+      <c r="F192" t="s">
         <v>705</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>706</v>
       </c>
-      <c r="G192" t="s">
+      <c r="H192" t="s">
         <v>707</v>
       </c>
-      <c r="H192" t="s">
+      <c r="I192" t="s">
         <v>708</v>
       </c>
-      <c r="I192" t="s">
+      <c r="J192" t="s">
         <v>709</v>
-      </c>
-      <c r="J192" t="s">
-        <v>338</v>
       </c>
       <c r="K192" t="s">
         <v>710</v>
@@ -9965,25 +9965,25 @@
         <v>14</v>
       </c>
       <c r="E193" t="s">
+        <v>337</v>
+      </c>
+      <c r="F193" t="s">
         <v>746</v>
       </c>
-      <c r="F193" t="s">
-        <v>706</v>
-      </c>
       <c r="G193" t="s">
+        <v>576</v>
+      </c>
+      <c r="H193" t="s">
         <v>707</v>
       </c>
-      <c r="H193" t="s">
+      <c r="I193" t="s">
         <v>708</v>
       </c>
-      <c r="I193" t="s">
+      <c r="J193" t="s">
         <v>709</v>
       </c>
-      <c r="J193" t="s">
-        <v>338</v>
-      </c>
       <c r="K193" t="s">
-        <v>576</v>
+        <v>710</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -10000,22 +10000,22 @@
         <v>14</v>
       </c>
       <c r="E194" t="s">
+        <v>337</v>
+      </c>
+      <c r="F194" t="s">
         <v>705</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>706</v>
       </c>
-      <c r="G194" t="s">
+      <c r="H194" t="s">
         <v>707</v>
       </c>
-      <c r="H194" t="s">
+      <c r="I194" t="s">
         <v>708</v>
       </c>
-      <c r="I194" t="s">
+      <c r="J194" t="s">
         <v>709</v>
-      </c>
-      <c r="J194" t="s">
-        <v>338</v>
       </c>
       <c r="K194" t="s">
         <v>710</v>
@@ -10035,22 +10035,22 @@
         <v>14</v>
       </c>
       <c r="E195" t="s">
+        <v>337</v>
+      </c>
+      <c r="F195" t="s">
         <v>705</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>706</v>
       </c>
-      <c r="G195" t="s">
+      <c r="H195" t="s">
         <v>707</v>
       </c>
-      <c r="H195" t="s">
+      <c r="I195" t="s">
         <v>708</v>
       </c>
-      <c r="I195" t="s">
+      <c r="J195" t="s">
         <v>709</v>
-      </c>
-      <c r="J195" t="s">
-        <v>338</v>
       </c>
       <c r="K195" t="s">
         <v>710</v>
@@ -10070,22 +10070,22 @@
         <v>14</v>
       </c>
       <c r="E196" t="s">
+        <v>337</v>
+      </c>
+      <c r="F196" t="s">
         <v>705</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>706</v>
       </c>
-      <c r="G196" t="s">
+      <c r="H196" t="s">
         <v>707</v>
       </c>
-      <c r="H196" t="s">
+      <c r="I196" t="s">
         <v>708</v>
       </c>
-      <c r="I196" t="s">
+      <c r="J196" t="s">
         <v>709</v>
-      </c>
-      <c r="J196" t="s">
-        <v>338</v>
       </c>
       <c r="K196" t="s">
         <v>710</v>
@@ -10105,22 +10105,22 @@
         <v>14</v>
       </c>
       <c r="E197" t="s">
+        <v>337</v>
+      </c>
+      <c r="F197" t="s">
         <v>705</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
         <v>706</v>
       </c>
-      <c r="G197" t="s">
+      <c r="H197" t="s">
         <v>707</v>
       </c>
-      <c r="H197" t="s">
+      <c r="I197" t="s">
         <v>708</v>
       </c>
-      <c r="I197" t="s">
+      <c r="J197" t="s">
         <v>709</v>
-      </c>
-      <c r="J197" t="s">
-        <v>338</v>
       </c>
       <c r="K197" t="s">
         <v>710</v>
@@ -10140,22 +10140,22 @@
         <v>14</v>
       </c>
       <c r="E198" t="s">
+        <v>337</v>
+      </c>
+      <c r="F198" t="s">
         <v>705</v>
       </c>
-      <c r="F198" t="s">
+      <c r="G198" t="s">
         <v>706</v>
       </c>
-      <c r="G198" t="s">
+      <c r="H198" t="s">
         <v>707</v>
       </c>
-      <c r="H198" t="s">
+      <c r="I198" t="s">
         <v>708</v>
       </c>
-      <c r="I198" t="s">
+      <c r="J198" t="s">
         <v>709</v>
-      </c>
-      <c r="J198" t="s">
-        <v>338</v>
       </c>
       <c r="K198" t="s">
         <v>710</v>
@@ -10175,22 +10175,22 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
+        <v>337</v>
+      </c>
+      <c r="F199" t="s">
         <v>765</v>
       </c>
-      <c r="F199" t="s">
+      <c r="G199" t="s">
+        <v>706</v>
+      </c>
+      <c r="H199" t="s">
         <v>766</v>
       </c>
-      <c r="G199" t="s">
+      <c r="I199" t="s">
+        <v>708</v>
+      </c>
+      <c r="J199" t="s">
         <v>767</v>
-      </c>
-      <c r="H199" t="s">
-        <v>708</v>
-      </c>
-      <c r="I199" t="s">
-        <v>709</v>
-      </c>
-      <c r="J199" t="s">
-        <v>338</v>
       </c>
       <c r="K199" t="s">
         <v>710</v>
@@ -10210,22 +10210,22 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
+        <v>337</v>
+      </c>
+      <c r="F200" t="s">
         <v>765</v>
       </c>
-      <c r="F200" t="s">
+      <c r="G200" t="s">
+        <v>706</v>
+      </c>
+      <c r="H200" t="s">
         <v>766</v>
       </c>
-      <c r="G200" t="s">
+      <c r="I200" t="s">
+        <v>708</v>
+      </c>
+      <c r="J200" t="s">
         <v>767</v>
-      </c>
-      <c r="H200" t="s">
-        <v>708</v>
-      </c>
-      <c r="I200" t="s">
-        <v>709</v>
-      </c>
-      <c r="J200" t="s">
-        <v>338</v>
       </c>
       <c r="K200" t="s">
         <v>710</v>
@@ -10245,22 +10245,22 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
+        <v>337</v>
+      </c>
+      <c r="F201" t="s">
         <v>765</v>
       </c>
-      <c r="F201" t="s">
+      <c r="G201" t="s">
+        <v>706</v>
+      </c>
+      <c r="H201" t="s">
         <v>766</v>
       </c>
-      <c r="G201" t="s">
+      <c r="I201" t="s">
+        <v>708</v>
+      </c>
+      <c r="J201" t="s">
         <v>767</v>
-      </c>
-      <c r="H201" t="s">
-        <v>708</v>
-      </c>
-      <c r="I201" t="s">
-        <v>709</v>
-      </c>
-      <c r="J201" t="s">
-        <v>338</v>
       </c>
       <c r="K201" t="s">
         <v>710</v>
@@ -10277,22 +10277,22 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
+        <v>337</v>
+      </c>
+      <c r="F202" t="s">
         <v>765</v>
       </c>
-      <c r="F202" t="s">
+      <c r="G202" t="s">
+        <v>706</v>
+      </c>
+      <c r="H202" t="s">
         <v>766</v>
       </c>
-      <c r="G202" t="s">
+      <c r="I202" t="s">
+        <v>708</v>
+      </c>
+      <c r="J202" t="s">
         <v>767</v>
-      </c>
-      <c r="H202" t="s">
-        <v>708</v>
-      </c>
-      <c r="I202" t="s">
-        <v>709</v>
-      </c>
-      <c r="J202" t="s">
-        <v>338</v>
       </c>
       <c r="K202" t="s">
         <v>710</v>
@@ -10312,25 +10312,25 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
+        <v>337</v>
+      </c>
+      <c r="F203" t="s">
         <v>746</v>
       </c>
-      <c r="F203" t="s">
+      <c r="G203" t="s">
+        <v>576</v>
+      </c>
+      <c r="H203" t="s">
         <v>766</v>
       </c>
-      <c r="G203" t="s">
+      <c r="I203" t="s">
+        <v>708</v>
+      </c>
+      <c r="J203" t="s">
         <v>767</v>
       </c>
-      <c r="H203" t="s">
-        <v>708</v>
-      </c>
-      <c r="I203" t="s">
-        <v>709</v>
-      </c>
-      <c r="J203" t="s">
-        <v>338</v>
-      </c>
       <c r="K203" t="s">
-        <v>576</v>
+        <v>710</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10344,22 +10344,22 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
+        <v>337</v>
+      </c>
+      <c r="F204" t="s">
         <v>765</v>
       </c>
-      <c r="F204" t="s">
+      <c r="G204" t="s">
+        <v>706</v>
+      </c>
+      <c r="H204" t="s">
         <v>766</v>
       </c>
-      <c r="G204" t="s">
+      <c r="I204" t="s">
+        <v>708</v>
+      </c>
+      <c r="J204" t="s">
         <v>767</v>
-      </c>
-      <c r="H204" t="s">
-        <v>708</v>
-      </c>
-      <c r="I204" t="s">
-        <v>709</v>
-      </c>
-      <c r="J204" t="s">
-        <v>338</v>
       </c>
       <c r="K204" t="s">
         <v>710</v>
@@ -10379,22 +10379,22 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
+        <v>337</v>
+      </c>
+      <c r="F205" t="s">
         <v>784</v>
       </c>
-      <c r="F205" t="s">
+      <c r="G205" t="s">
+        <v>706</v>
+      </c>
+      <c r="H205" t="s">
         <v>785</v>
       </c>
-      <c r="G205" t="s">
+      <c r="I205" t="s">
+        <v>708</v>
+      </c>
+      <c r="J205" t="s">
         <v>786</v>
-      </c>
-      <c r="H205" t="s">
-        <v>708</v>
-      </c>
-      <c r="I205" t="s">
-        <v>709</v>
-      </c>
-      <c r="J205" t="s">
-        <v>338</v>
       </c>
       <c r="K205" t="s">
         <v>710</v>
@@ -10414,22 +10414,22 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
+        <v>337</v>
+      </c>
+      <c r="F206" t="s">
         <v>784</v>
       </c>
-      <c r="F206" t="s">
+      <c r="G206" t="s">
+        <v>706</v>
+      </c>
+      <c r="H206" t="s">
         <v>785</v>
       </c>
-      <c r="G206" t="s">
+      <c r="I206" t="s">
+        <v>708</v>
+      </c>
+      <c r="J206" t="s">
         <v>786</v>
-      </c>
-      <c r="H206" t="s">
-        <v>708</v>
-      </c>
-      <c r="I206" t="s">
-        <v>709</v>
-      </c>
-      <c r="J206" t="s">
-        <v>338</v>
       </c>
       <c r="K206" t="s">
         <v>710</v>
@@ -10446,22 +10446,22 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
+        <v>337</v>
+      </c>
+      <c r="F207" t="s">
         <v>784</v>
       </c>
-      <c r="F207" t="s">
+      <c r="G207" t="s">
+        <v>706</v>
+      </c>
+      <c r="H207" t="s">
         <v>785</v>
       </c>
-      <c r="G207" t="s">
+      <c r="I207" t="s">
+        <v>708</v>
+      </c>
+      <c r="J207" t="s">
         <v>786</v>
-      </c>
-      <c r="H207" t="s">
-        <v>708</v>
-      </c>
-      <c r="I207" t="s">
-        <v>709</v>
-      </c>
-      <c r="J207" t="s">
-        <v>338</v>
       </c>
       <c r="K207" t="s">
         <v>710</v>
@@ -10481,25 +10481,25 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
+        <v>337</v>
+      </c>
+      <c r="F208" t="s">
         <v>746</v>
       </c>
-      <c r="F208" t="s">
+      <c r="G208" t="s">
+        <v>576</v>
+      </c>
+      <c r="H208" t="s">
         <v>785</v>
       </c>
-      <c r="G208" t="s">
+      <c r="I208" t="s">
+        <v>708</v>
+      </c>
+      <c r="J208" t="s">
         <v>786</v>
       </c>
-      <c r="H208" t="s">
-        <v>708</v>
-      </c>
-      <c r="I208" t="s">
-        <v>709</v>
-      </c>
-      <c r="J208" t="s">
-        <v>338</v>
-      </c>
       <c r="K208" t="s">
-        <v>576</v>
+        <v>710</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10516,22 +10516,22 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
+        <v>337</v>
+      </c>
+      <c r="F209" t="s">
         <v>784</v>
       </c>
-      <c r="F209" t="s">
+      <c r="G209" t="s">
+        <v>706</v>
+      </c>
+      <c r="H209" t="s">
         <v>785</v>
       </c>
-      <c r="G209" t="s">
+      <c r="I209" t="s">
+        <v>708</v>
+      </c>
+      <c r="J209" t="s">
         <v>786</v>
-      </c>
-      <c r="H209" t="s">
-        <v>708</v>
-      </c>
-      <c r="I209" t="s">
-        <v>709</v>
-      </c>
-      <c r="J209" t="s">
-        <v>338</v>
       </c>
       <c r="K209" t="s">
         <v>710</v>
@@ -10551,22 +10551,22 @@
         <v>14</v>
       </c>
       <c r="E210" t="s">
+        <v>337</v>
+      </c>
+      <c r="F210" t="s">
         <v>801</v>
       </c>
-      <c r="F210" t="s">
+      <c r="G210" t="s">
         <v>802</v>
       </c>
-      <c r="G210" t="s">
+      <c r="H210" t="s">
         <v>803</v>
       </c>
-      <c r="H210" t="s">
+      <c r="I210" t="s">
         <v>804</v>
       </c>
-      <c r="I210" t="s">
+      <c r="J210" t="s">
         <v>805</v>
-      </c>
-      <c r="J210" t="s">
-        <v>338</v>
       </c>
       <c r="K210" t="s">
         <v>806</v>
@@ -10583,22 +10583,22 @@
         <v>14</v>
       </c>
       <c r="E211" t="s">
+        <v>337</v>
+      </c>
+      <c r="F211" t="s">
         <v>801</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>802</v>
       </c>
-      <c r="G211" t="s">
+      <c r="H211" t="s">
         <v>803</v>
       </c>
-      <c r="H211" t="s">
+      <c r="I211" t="s">
         <v>804</v>
       </c>
-      <c r="I211" t="s">
+      <c r="J211" t="s">
         <v>805</v>
-      </c>
-      <c r="J211" t="s">
-        <v>338</v>
       </c>
       <c r="K211" t="s">
         <v>806</v>
@@ -10618,22 +10618,22 @@
         <v>14</v>
       </c>
       <c r="E212" t="s">
+        <v>337</v>
+      </c>
+      <c r="F212" t="s">
         <v>801</v>
       </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>802</v>
       </c>
-      <c r="G212" t="s">
+      <c r="H212" t="s">
         <v>803</v>
       </c>
-      <c r="H212" t="s">
+      <c r="I212" t="s">
         <v>804</v>
       </c>
-      <c r="I212" t="s">
+      <c r="J212" t="s">
         <v>805</v>
-      </c>
-      <c r="J212" t="s">
-        <v>338</v>
       </c>
       <c r="K212" t="s">
         <v>806</v>
@@ -10650,22 +10650,22 @@
         <v>14</v>
       </c>
       <c r="E213" t="s">
+        <v>337</v>
+      </c>
+      <c r="F213" t="s">
         <v>801</v>
       </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>802</v>
       </c>
-      <c r="G213" t="s">
+      <c r="H213" t="s">
         <v>803</v>
       </c>
-      <c r="H213" t="s">
+      <c r="I213" t="s">
         <v>804</v>
       </c>
-      <c r="I213" t="s">
+      <c r="J213" t="s">
         <v>805</v>
-      </c>
-      <c r="J213" t="s">
-        <v>338</v>
       </c>
       <c r="K213" t="s">
         <v>806</v>
@@ -10685,22 +10685,22 @@
         <v>14</v>
       </c>
       <c r="E214" t="s">
+        <v>337</v>
+      </c>
+      <c r="F214" t="s">
         <v>801</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>802</v>
       </c>
-      <c r="G214" t="s">
+      <c r="H214" t="s">
         <v>803</v>
       </c>
-      <c r="H214" t="s">
+      <c r="I214" t="s">
         <v>804</v>
       </c>
-      <c r="I214" t="s">
+      <c r="J214" t="s">
         <v>805</v>
-      </c>
-      <c r="J214" t="s">
-        <v>338</v>
       </c>
       <c r="K214" t="s">
         <v>806</v>
@@ -10720,25 +10720,25 @@
         <v>14</v>
       </c>
       <c r="E215" t="s">
+        <v>337</v>
+      </c>
+      <c r="F215" t="s">
         <v>765</v>
       </c>
-      <c r="F215" t="s">
-        <v>802</v>
-      </c>
       <c r="G215" t="s">
+        <v>706</v>
+      </c>
+      <c r="H215" t="s">
         <v>803</v>
       </c>
-      <c r="H215" t="s">
+      <c r="I215" t="s">
         <v>804</v>
       </c>
-      <c r="I215" t="s">
+      <c r="J215" t="s">
         <v>805</v>
       </c>
-      <c r="J215" t="s">
-        <v>338</v>
-      </c>
       <c r="K215" t="s">
-        <v>710</v>
+        <v>806</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -10755,22 +10755,22 @@
         <v>14</v>
       </c>
       <c r="E216" t="s">
+        <v>337</v>
+      </c>
+      <c r="F216" t="s">
         <v>801</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>802</v>
       </c>
-      <c r="G216" t="s">
+      <c r="H216" t="s">
         <v>803</v>
       </c>
-      <c r="H216" t="s">
+      <c r="I216" t="s">
         <v>804</v>
       </c>
-      <c r="I216" t="s">
+      <c r="J216" t="s">
         <v>805</v>
-      </c>
-      <c r="J216" t="s">
-        <v>338</v>
       </c>
       <c r="K216" t="s">
         <v>806</v>
@@ -10790,22 +10790,22 @@
         <v>14</v>
       </c>
       <c r="E217" t="s">
+        <v>337</v>
+      </c>
+      <c r="F217" t="s">
         <v>801</v>
       </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
         <v>802</v>
       </c>
-      <c r="G217" t="s">
+      <c r="H217" t="s">
         <v>803</v>
       </c>
-      <c r="H217" t="s">
+      <c r="I217" t="s">
         <v>804</v>
       </c>
-      <c r="I217" t="s">
+      <c r="J217" t="s">
         <v>805</v>
-      </c>
-      <c r="J217" t="s">
-        <v>338</v>
       </c>
       <c r="K217" t="s">
         <v>806</v>
@@ -10822,22 +10822,22 @@
         <v>14</v>
       </c>
       <c r="E218" t="s">
+        <v>337</v>
+      </c>
+      <c r="F218" t="s">
         <v>801</v>
       </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>802</v>
       </c>
-      <c r="G218" t="s">
+      <c r="H218" t="s">
         <v>803</v>
       </c>
-      <c r="H218" t="s">
+      <c r="I218" t="s">
         <v>804</v>
       </c>
-      <c r="I218" t="s">
+      <c r="J218" t="s">
         <v>805</v>
-      </c>
-      <c r="J218" t="s">
-        <v>338</v>
       </c>
       <c r="K218" t="s">
         <v>806</v>
@@ -10854,22 +10854,22 @@
         <v>14</v>
       </c>
       <c r="E219" t="s">
+        <v>337</v>
+      </c>
+      <c r="F219" t="s">
         <v>801</v>
       </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>802</v>
       </c>
-      <c r="G219" t="s">
+      <c r="H219" t="s">
         <v>803</v>
       </c>
-      <c r="H219" t="s">
+      <c r="I219" t="s">
         <v>804</v>
       </c>
-      <c r="I219" t="s">
+      <c r="J219" t="s">
         <v>805</v>
-      </c>
-      <c r="J219" t="s">
-        <v>338</v>
       </c>
       <c r="K219" t="s">
         <v>806</v>
@@ -10889,25 +10889,25 @@
         <v>14</v>
       </c>
       <c r="E220" t="s">
+        <v>337</v>
+      </c>
+      <c r="F220" t="s">
         <v>663</v>
       </c>
-      <c r="F220" t="s">
-        <v>802</v>
-      </c>
       <c r="G220" t="s">
+        <v>565</v>
+      </c>
+      <c r="H220" t="s">
         <v>803</v>
       </c>
-      <c r="H220" t="s">
+      <c r="I220" t="s">
         <v>804</v>
       </c>
-      <c r="I220" t="s">
+      <c r="J220" t="s">
         <v>805</v>
       </c>
-      <c r="J220" t="s">
-        <v>338</v>
-      </c>
       <c r="K220" t="s">
-        <v>569</v>
+        <v>806</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -10924,22 +10924,22 @@
         <v>14</v>
       </c>
       <c r="E221" t="s">
+        <v>337</v>
+      </c>
+      <c r="F221" t="s">
         <v>801</v>
       </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>802</v>
       </c>
-      <c r="G221" t="s">
+      <c r="H221" t="s">
         <v>803</v>
       </c>
-      <c r="H221" t="s">
+      <c r="I221" t="s">
         <v>804</v>
       </c>
-      <c r="I221" t="s">
+      <c r="J221" t="s">
         <v>805</v>
-      </c>
-      <c r="J221" t="s">
-        <v>338</v>
       </c>
       <c r="K221" t="s">
         <v>806</v>
@@ -10959,22 +10959,22 @@
         <v>14</v>
       </c>
       <c r="E222" t="s">
+        <v>337</v>
+      </c>
+      <c r="F222" t="s">
         <v>801</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>802</v>
       </c>
-      <c r="G222" t="s">
+      <c r="H222" t="s">
         <v>803</v>
       </c>
-      <c r="H222" t="s">
+      <c r="I222" t="s">
         <v>804</v>
       </c>
-      <c r="I222" t="s">
+      <c r="J222" t="s">
         <v>805</v>
-      </c>
-      <c r="J222" t="s">
-        <v>338</v>
       </c>
       <c r="K222" t="s">
         <v>806</v>
@@ -10991,22 +10991,22 @@
         <v>14</v>
       </c>
       <c r="E223" t="s">
+        <v>337</v>
+      </c>
+      <c r="F223" t="s">
         <v>801</v>
       </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>802</v>
       </c>
-      <c r="G223" t="s">
+      <c r="H223" t="s">
         <v>803</v>
       </c>
-      <c r="H223" t="s">
+      <c r="I223" t="s">
         <v>804</v>
       </c>
-      <c r="I223" t="s">
+      <c r="J223" t="s">
         <v>805</v>
-      </c>
-      <c r="J223" t="s">
-        <v>338</v>
       </c>
       <c r="K223" t="s">
         <v>806</v>
@@ -11026,22 +11026,22 @@
         <v>14</v>
       </c>
       <c r="E224" t="s">
+        <v>337</v>
+      </c>
+      <c r="F224" t="s">
         <v>801</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>802</v>
       </c>
-      <c r="G224" t="s">
+      <c r="H224" t="s">
         <v>803</v>
       </c>
-      <c r="H224" t="s">
+      <c r="I224" t="s">
         <v>804</v>
       </c>
-      <c r="I224" t="s">
+      <c r="J224" t="s">
         <v>805</v>
-      </c>
-      <c r="J224" t="s">
-        <v>338</v>
       </c>
       <c r="K224" t="s">
         <v>806</v>
@@ -11061,22 +11061,22 @@
         <v>14</v>
       </c>
       <c r="E225" t="s">
+        <v>337</v>
+      </c>
+      <c r="F225" t="s">
         <v>801</v>
       </c>
-      <c r="F225" t="s">
+      <c r="G225" t="s">
         <v>802</v>
       </c>
-      <c r="G225" t="s">
+      <c r="H225" t="s">
         <v>803</v>
       </c>
-      <c r="H225" t="s">
+      <c r="I225" t="s">
         <v>804</v>
       </c>
-      <c r="I225" t="s">
+      <c r="J225" t="s">
         <v>805</v>
-      </c>
-      <c r="J225" t="s">
-        <v>338</v>
       </c>
       <c r="K225" t="s">
         <v>806</v>
@@ -11096,25 +11096,25 @@
         <v>14</v>
       </c>
       <c r="E226" t="s">
+        <v>337</v>
+      </c>
+      <c r="F226" t="s">
         <v>575</v>
       </c>
-      <c r="F226" t="s">
-        <v>802</v>
-      </c>
       <c r="G226" t="s">
+        <v>576</v>
+      </c>
+      <c r="H226" t="s">
         <v>803</v>
       </c>
-      <c r="H226" t="s">
+      <c r="I226" t="s">
         <v>804</v>
       </c>
-      <c r="I226" t="s">
+      <c r="J226" t="s">
         <v>805</v>
       </c>
-      <c r="J226" t="s">
-        <v>338</v>
-      </c>
       <c r="K226" t="s">
-        <v>576</v>
+        <v>806</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -11131,22 +11131,22 @@
         <v>14</v>
       </c>
       <c r="E227" t="s">
+        <v>337</v>
+      </c>
+      <c r="F227" t="s">
         <v>801</v>
       </c>
-      <c r="F227" t="s">
+      <c r="G227" t="s">
         <v>802</v>
       </c>
-      <c r="G227" t="s">
+      <c r="H227" t="s">
         <v>803</v>
       </c>
-      <c r="H227" t="s">
+      <c r="I227" t="s">
         <v>804</v>
       </c>
-      <c r="I227" t="s">
+      <c r="J227" t="s">
         <v>805</v>
-      </c>
-      <c r="J227" t="s">
-        <v>338</v>
       </c>
       <c r="K227" t="s">
         <v>806</v>
@@ -11169,22 +11169,22 @@
         <v>337</v>
       </c>
       <c r="F228" t="s">
-        <v>802</v>
+        <v>338</v>
       </c>
       <c r="G228" t="s">
+        <v>339</v>
+      </c>
+      <c r="H228" t="s">
         <v>803</v>
       </c>
-      <c r="H228" t="s">
+      <c r="I228" t="s">
         <v>804</v>
       </c>
-      <c r="I228" t="s">
+      <c r="J228" t="s">
         <v>805</v>
       </c>
-      <c r="J228" t="s">
-        <v>338</v>
-      </c>
       <c r="K228" t="s">
-        <v>339</v>
+        <v>806</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -11201,22 +11201,22 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
+        <v>337</v>
+      </c>
+      <c r="F229" t="s">
         <v>859</v>
       </c>
-      <c r="F229" t="s">
+      <c r="G229" t="s">
+        <v>802</v>
+      </c>
+      <c r="H229" t="s">
         <v>860</v>
       </c>
-      <c r="G229" t="s">
+      <c r="I229" t="s">
+        <v>804</v>
+      </c>
+      <c r="J229" t="s">
         <v>861</v>
-      </c>
-      <c r="H229" t="s">
-        <v>804</v>
-      </c>
-      <c r="I229" t="s">
-        <v>805</v>
-      </c>
-      <c r="J229" t="s">
-        <v>338</v>
       </c>
       <c r="K229" t="s">
         <v>806</v>
@@ -11236,22 +11236,22 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
+        <v>337</v>
+      </c>
+      <c r="F230" t="s">
         <v>859</v>
       </c>
-      <c r="F230" t="s">
+      <c r="G230" t="s">
+        <v>802</v>
+      </c>
+      <c r="H230" t="s">
         <v>860</v>
       </c>
-      <c r="G230" t="s">
+      <c r="I230" t="s">
+        <v>804</v>
+      </c>
+      <c r="J230" t="s">
         <v>861</v>
-      </c>
-      <c r="H230" t="s">
-        <v>804</v>
-      </c>
-      <c r="I230" t="s">
-        <v>805</v>
-      </c>
-      <c r="J230" t="s">
-        <v>338</v>
       </c>
       <c r="K230" t="s">
         <v>806</v>
@@ -11271,25 +11271,25 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
+        <v>337</v>
+      </c>
+      <c r="F231" t="s">
         <v>623</v>
       </c>
-      <c r="F231" t="s">
+      <c r="G231" t="s">
+        <v>565</v>
+      </c>
+      <c r="H231" t="s">
         <v>860</v>
       </c>
-      <c r="G231" t="s">
+      <c r="I231" t="s">
+        <v>804</v>
+      </c>
+      <c r="J231" t="s">
         <v>861</v>
       </c>
-      <c r="H231" t="s">
-        <v>804</v>
-      </c>
-      <c r="I231" t="s">
-        <v>805</v>
-      </c>
-      <c r="J231" t="s">
-        <v>338</v>
-      </c>
       <c r="K231" t="s">
-        <v>569</v>
+        <v>806</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11306,25 +11306,25 @@
         <v>14</v>
       </c>
       <c r="E232" t="s">
+        <v>337</v>
+      </c>
+      <c r="F232" t="s">
         <v>663</v>
       </c>
-      <c r="F232" t="s">
+      <c r="G232" t="s">
+        <v>565</v>
+      </c>
+      <c r="H232" t="s">
         <v>860</v>
       </c>
-      <c r="G232" t="s">
+      <c r="I232" t="s">
+        <v>804</v>
+      </c>
+      <c r="J232" t="s">
         <v>861</v>
       </c>
-      <c r="H232" t="s">
-        <v>804</v>
-      </c>
-      <c r="I232" t="s">
-        <v>805</v>
-      </c>
-      <c r="J232" t="s">
-        <v>338</v>
-      </c>
       <c r="K232" t="s">
-        <v>569</v>
+        <v>806</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11341,22 +11341,22 @@
         <v>14</v>
       </c>
       <c r="E233" t="s">
+        <v>337</v>
+      </c>
+      <c r="F233" t="s">
         <v>859</v>
       </c>
-      <c r="F233" t="s">
+      <c r="G233" t="s">
+        <v>802</v>
+      </c>
+      <c r="H233" t="s">
         <v>860</v>
       </c>
-      <c r="G233" t="s">
+      <c r="I233" t="s">
+        <v>804</v>
+      </c>
+      <c r="J233" t="s">
         <v>861</v>
-      </c>
-      <c r="H233" t="s">
-        <v>804</v>
-      </c>
-      <c r="I233" t="s">
-        <v>805</v>
-      </c>
-      <c r="J233" t="s">
-        <v>338</v>
       </c>
       <c r="K233" t="s">
         <v>806</v>
@@ -11376,22 +11376,22 @@
         <v>14</v>
       </c>
       <c r="E234" t="s">
+        <v>337</v>
+      </c>
+      <c r="F234" t="s">
         <v>859</v>
       </c>
-      <c r="F234" t="s">
+      <c r="G234" t="s">
+        <v>802</v>
+      </c>
+      <c r="H234" t="s">
         <v>860</v>
       </c>
-      <c r="G234" t="s">
+      <c r="I234" t="s">
+        <v>804</v>
+      </c>
+      <c r="J234" t="s">
         <v>861</v>
-      </c>
-      <c r="H234" t="s">
-        <v>804</v>
-      </c>
-      <c r="I234" t="s">
-        <v>805</v>
-      </c>
-      <c r="J234" t="s">
-        <v>338</v>
       </c>
       <c r="K234" t="s">
         <v>806</v>
@@ -11411,22 +11411,22 @@
         <v>14</v>
       </c>
       <c r="E235" t="s">
+        <v>337</v>
+      </c>
+      <c r="F235" t="s">
         <v>859</v>
       </c>
-      <c r="F235" t="s">
+      <c r="G235" t="s">
+        <v>802</v>
+      </c>
+      <c r="H235" t="s">
         <v>860</v>
       </c>
-      <c r="G235" t="s">
+      <c r="I235" t="s">
+        <v>804</v>
+      </c>
+      <c r="J235" t="s">
         <v>861</v>
-      </c>
-      <c r="H235" t="s">
-        <v>804</v>
-      </c>
-      <c r="I235" t="s">
-        <v>805</v>
-      </c>
-      <c r="J235" t="s">
-        <v>338</v>
       </c>
       <c r="K235" t="s">
         <v>806</v>
@@ -11446,22 +11446,22 @@
         <v>14</v>
       </c>
       <c r="E236" t="s">
+        <v>337</v>
+      </c>
+      <c r="F236" t="s">
         <v>859</v>
       </c>
-      <c r="F236" t="s">
+      <c r="G236" t="s">
+        <v>802</v>
+      </c>
+      <c r="H236" t="s">
         <v>860</v>
       </c>
-      <c r="G236" t="s">
+      <c r="I236" t="s">
+        <v>804</v>
+      </c>
+      <c r="J236" t="s">
         <v>861</v>
-      </c>
-      <c r="H236" t="s">
-        <v>804</v>
-      </c>
-      <c r="I236" t="s">
-        <v>805</v>
-      </c>
-      <c r="J236" t="s">
-        <v>338</v>
       </c>
       <c r="K236" t="s">
         <v>806</v>
@@ -11481,22 +11481,22 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
+        <v>337</v>
+      </c>
+      <c r="F237" t="s">
         <v>859</v>
       </c>
-      <c r="F237" t="s">
+      <c r="G237" t="s">
+        <v>802</v>
+      </c>
+      <c r="H237" t="s">
         <v>860</v>
       </c>
-      <c r="G237" t="s">
+      <c r="I237" t="s">
+        <v>804</v>
+      </c>
+      <c r="J237" t="s">
         <v>861</v>
-      </c>
-      <c r="H237" t="s">
-        <v>804</v>
-      </c>
-      <c r="I237" t="s">
-        <v>805</v>
-      </c>
-      <c r="J237" t="s">
-        <v>338</v>
       </c>
       <c r="K237" t="s">
         <v>806</v>
@@ -11516,22 +11516,22 @@
         <v>14</v>
       </c>
       <c r="E238" t="s">
+        <v>337</v>
+      </c>
+      <c r="F238" t="s">
         <v>859</v>
       </c>
-      <c r="F238" t="s">
+      <c r="G238" t="s">
+        <v>802</v>
+      </c>
+      <c r="H238" t="s">
         <v>860</v>
       </c>
-      <c r="G238" t="s">
+      <c r="I238" t="s">
+        <v>804</v>
+      </c>
+      <c r="J238" t="s">
         <v>861</v>
-      </c>
-      <c r="H238" t="s">
-        <v>804</v>
-      </c>
-      <c r="I238" t="s">
-        <v>805</v>
-      </c>
-      <c r="J238" t="s">
-        <v>338</v>
       </c>
       <c r="K238" t="s">
         <v>806</v>
@@ -11551,22 +11551,22 @@
         <v>14</v>
       </c>
       <c r="E239" t="s">
+        <v>337</v>
+      </c>
+      <c r="F239" t="s">
         <v>892</v>
       </c>
-      <c r="F239" t="s">
+      <c r="G239" t="s">
+        <v>802</v>
+      </c>
+      <c r="H239" t="s">
         <v>893</v>
       </c>
-      <c r="G239" t="s">
+      <c r="I239" t="s">
+        <v>804</v>
+      </c>
+      <c r="J239" t="s">
         <v>894</v>
-      </c>
-      <c r="H239" t="s">
-        <v>804</v>
-      </c>
-      <c r="I239" t="s">
-        <v>805</v>
-      </c>
-      <c r="J239" t="s">
-        <v>338</v>
       </c>
       <c r="K239" t="s">
         <v>806</v>
@@ -11589,22 +11589,22 @@
         <v>337</v>
       </c>
       <c r="F240" t="s">
-        <v>898</v>
+        <v>338</v>
       </c>
       <c r="G240" t="s">
-        <v>899</v>
+        <v>339</v>
       </c>
       <c r="H240" t="s">
         <v>898</v>
       </c>
       <c r="I240" t="s">
+        <v>899</v>
+      </c>
+      <c r="J240" t="s">
         <v>900</v>
       </c>
-      <c r="J240" t="s">
-        <v>338</v>
-      </c>
       <c r="K240" t="s">
-        <v>339</v>
+        <v>898</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -11624,22 +11624,22 @@
         <v>337</v>
       </c>
       <c r="F241" t="s">
-        <v>898</v>
+        <v>338</v>
       </c>
       <c r="G241" t="s">
-        <v>899</v>
+        <v>339</v>
       </c>
       <c r="H241" t="s">
         <v>898</v>
       </c>
       <c r="I241" t="s">
+        <v>899</v>
+      </c>
+      <c r="J241" t="s">
         <v>900</v>
       </c>
-      <c r="J241" t="s">
-        <v>338</v>
-      </c>
       <c r="K241" t="s">
-        <v>339</v>
+        <v>898</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -11659,22 +11659,22 @@
         <v>337</v>
       </c>
       <c r="F242" t="s">
-        <v>898</v>
+        <v>338</v>
       </c>
       <c r="G242" t="s">
-        <v>899</v>
+        <v>339</v>
       </c>
       <c r="H242" t="s">
         <v>898</v>
       </c>
       <c r="I242" t="s">
+        <v>899</v>
+      </c>
+      <c r="J242" t="s">
         <v>900</v>
       </c>
-      <c r="J242" t="s">
-        <v>338</v>
-      </c>
       <c r="K242" t="s">
-        <v>339</v>
+        <v>898</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -11694,22 +11694,22 @@
         <v>337</v>
       </c>
       <c r="F243" t="s">
-        <v>898</v>
+        <v>338</v>
       </c>
       <c r="G243" t="s">
-        <v>899</v>
+        <v>339</v>
       </c>
       <c r="H243" t="s">
         <v>898</v>
       </c>
       <c r="I243" t="s">
+        <v>899</v>
+      </c>
+      <c r="J243" t="s">
         <v>900</v>
       </c>
-      <c r="J243" t="s">
-        <v>338</v>
-      </c>
       <c r="K243" t="s">
-        <v>339</v>
+        <v>898</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -11729,22 +11729,22 @@
         <v>337</v>
       </c>
       <c r="F244" t="s">
-        <v>898</v>
+        <v>338</v>
       </c>
       <c r="G244" t="s">
-        <v>899</v>
+        <v>339</v>
       </c>
       <c r="H244" t="s">
         <v>898</v>
       </c>
       <c r="I244" t="s">
+        <v>899</v>
+      </c>
+      <c r="J244" t="s">
         <v>900</v>
       </c>
-      <c r="J244" t="s">
-        <v>338</v>
-      </c>
       <c r="K244" t="s">
-        <v>339</v>
+        <v>898</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -11764,22 +11764,22 @@
         <v>337</v>
       </c>
       <c r="F245" t="s">
-        <v>898</v>
+        <v>338</v>
       </c>
       <c r="G245" t="s">
-        <v>899</v>
+        <v>339</v>
       </c>
       <c r="H245" t="s">
         <v>898</v>
       </c>
       <c r="I245" t="s">
+        <v>899</v>
+      </c>
+      <c r="J245" t="s">
         <v>900</v>
       </c>
-      <c r="J245" t="s">
-        <v>338</v>
-      </c>
       <c r="K245" t="s">
-        <v>339</v>
+        <v>898</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -11793,25 +11793,25 @@
         <v>14</v>
       </c>
       <c r="E246" t="s">
+        <v>337</v>
+      </c>
+      <c r="F246" t="s">
         <v>918</v>
       </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
+        <v>534</v>
+      </c>
+      <c r="H246" t="s">
         <v>919</v>
       </c>
-      <c r="G246" t="s">
+      <c r="I246" t="s">
+        <v>899</v>
+      </c>
+      <c r="J246" t="s">
         <v>920</v>
       </c>
-      <c r="H246" t="s">
+      <c r="K246" t="s">
         <v>898</v>
-      </c>
-      <c r="I246" t="s">
-        <v>900</v>
-      </c>
-      <c r="J246" t="s">
-        <v>338</v>
-      </c>
-      <c r="K246" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11830,17 +11830,17 @@
       <c r="E247" t="s">
         <v>196</v>
       </c>
-      <c r="H247" t="s">
+      <c r="F247" t="s">
+        <v>197</v>
+      </c>
+      <c r="G247" t="s">
+        <v>198</v>
+      </c>
+      <c r="I247" t="s">
         <v>924</v>
       </c>
-      <c r="I247" t="s">
+      <c r="K247" t="s">
         <v>925</v>
-      </c>
-      <c r="J247" t="s">
-        <v>197</v>
-      </c>
-      <c r="K247" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -11859,17 +11859,17 @@
       <c r="E248" t="s">
         <v>196</v>
       </c>
-      <c r="H248" t="s">
+      <c r="F248" t="s">
+        <v>197</v>
+      </c>
+      <c r="G248" t="s">
+        <v>198</v>
+      </c>
+      <c r="I248" t="s">
         <v>924</v>
       </c>
-      <c r="I248" t="s">
+      <c r="K248" t="s">
         <v>925</v>
-      </c>
-      <c r="J248" t="s">
-        <v>197</v>
-      </c>
-      <c r="K248" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -11886,19 +11886,19 @@
         <v>14</v>
       </c>
       <c r="E249" t="s">
+        <v>196</v>
+      </c>
+      <c r="F249" t="s">
         <v>932</v>
       </c>
-      <c r="H249" t="s">
+      <c r="G249" t="s">
+        <v>933</v>
+      </c>
+      <c r="I249" t="s">
         <v>924</v>
       </c>
-      <c r="I249" t="s">
+      <c r="K249" t="s">
         <v>925</v>
-      </c>
-      <c r="J249" t="s">
-        <v>197</v>
-      </c>
-      <c r="K249" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -11917,17 +11917,17 @@
       <c r="E250" t="s">
         <v>196</v>
       </c>
-      <c r="H250" t="s">
+      <c r="F250" t="s">
+        <v>197</v>
+      </c>
+      <c r="G250" t="s">
+        <v>198</v>
+      </c>
+      <c r="I250" t="s">
         <v>924</v>
       </c>
-      <c r="I250" t="s">
+      <c r="K250" t="s">
         <v>925</v>
-      </c>
-      <c r="J250" t="s">
-        <v>197</v>
-      </c>
-      <c r="K250" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -11943,17 +11943,17 @@
       <c r="E251" t="s">
         <v>196</v>
       </c>
-      <c r="H251" t="s">
+      <c r="F251" t="s">
+        <v>197</v>
+      </c>
+      <c r="G251" t="s">
+        <v>198</v>
+      </c>
+      <c r="I251" t="s">
         <v>924</v>
       </c>
-      <c r="I251" t="s">
+      <c r="K251" t="s">
         <v>925</v>
-      </c>
-      <c r="J251" t="s">
-        <v>197</v>
-      </c>
-      <c r="K251" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -11972,17 +11972,17 @@
       <c r="E252" t="s">
         <v>196</v>
       </c>
-      <c r="H252" t="s">
+      <c r="F252" t="s">
+        <v>197</v>
+      </c>
+      <c r="G252" t="s">
+        <v>198</v>
+      </c>
+      <c r="I252" t="s">
         <v>924</v>
       </c>
-      <c r="I252" t="s">
+      <c r="K252" t="s">
         <v>925</v>
-      </c>
-      <c r="J252" t="s">
-        <v>197</v>
-      </c>
-      <c r="K252" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -11996,16 +11996,16 @@
         <v>14</v>
       </c>
       <c r="E253" t="s">
+        <v>337</v>
+      </c>
+      <c r="F253" t="s">
         <v>944</v>
       </c>
-      <c r="H253" t="s">
+      <c r="G253" t="s">
         <v>945</v>
       </c>
       <c r="I253" t="s">
         <v>946</v>
-      </c>
-      <c r="J253" t="s">
-        <v>338</v>
       </c>
       <c r="K253" t="s">
         <v>947</v>
@@ -12025,19 +12025,19 @@
         <v>14</v>
       </c>
       <c r="E254" t="s">
+        <v>188</v>
+      </c>
+      <c r="F254" t="s">
         <v>454</v>
       </c>
-      <c r="H254" t="s">
-        <v>945</v>
+      <c r="G254" t="s">
+        <v>455</v>
       </c>
       <c r="I254" t="s">
         <v>946</v>
       </c>
-      <c r="J254" t="s">
-        <v>191</v>
-      </c>
       <c r="K254" t="s">
-        <v>455</v>
+        <v>947</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -12054,19 +12054,19 @@
         <v>14</v>
       </c>
       <c r="E255" t="s">
+        <v>188</v>
+      </c>
+      <c r="F255" t="s">
         <v>954</v>
       </c>
-      <c r="H255" t="s">
-        <v>945</v>
+      <c r="G255" t="s">
+        <v>955</v>
       </c>
       <c r="I255" t="s">
         <v>946</v>
       </c>
-      <c r="J255" t="s">
-        <v>191</v>
-      </c>
       <c r="K255" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -12083,19 +12083,19 @@
         <v>14</v>
       </c>
       <c r="E256" t="s">
+        <v>188</v>
+      </c>
+      <c r="F256" t="s">
         <v>954</v>
       </c>
-      <c r="H256" t="s">
-        <v>945</v>
+      <c r="G256" t="s">
+        <v>955</v>
       </c>
       <c r="I256" t="s">
         <v>946</v>
       </c>
-      <c r="J256" t="s">
-        <v>191</v>
-      </c>
       <c r="K256" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -12112,19 +12112,19 @@
         <v>14</v>
       </c>
       <c r="E257" t="s">
+        <v>188</v>
+      </c>
+      <c r="F257" t="s">
         <v>954</v>
       </c>
-      <c r="H257" t="s">
-        <v>945</v>
+      <c r="G257" t="s">
+        <v>955</v>
       </c>
       <c r="I257" t="s">
         <v>946</v>
       </c>
-      <c r="J257" t="s">
-        <v>191</v>
-      </c>
       <c r="K257" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -12141,19 +12141,19 @@
         <v>14</v>
       </c>
       <c r="E258" t="s">
+        <v>337</v>
+      </c>
+      <c r="F258" t="s">
         <v>705</v>
       </c>
-      <c r="H258" t="s">
-        <v>945</v>
+      <c r="G258" t="s">
+        <v>706</v>
       </c>
       <c r="I258" t="s">
         <v>946</v>
       </c>
-      <c r="J258" t="s">
-        <v>338</v>
-      </c>
       <c r="K258" t="s">
-        <v>710</v>
+        <v>947</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -12170,19 +12170,19 @@
         <v>14</v>
       </c>
       <c r="E259" t="s">
+        <v>188</v>
+      </c>
+      <c r="F259" t="s">
         <v>954</v>
       </c>
-      <c r="H259" t="s">
-        <v>945</v>
+      <c r="G259" t="s">
+        <v>955</v>
       </c>
       <c r="I259" t="s">
         <v>946</v>
       </c>
-      <c r="J259" t="s">
-        <v>191</v>
-      </c>
       <c r="K259" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -12201,17 +12201,17 @@
       <c r="E260" t="s">
         <v>337</v>
       </c>
-      <c r="H260" t="s">
-        <v>945</v>
+      <c r="F260" t="s">
+        <v>338</v>
+      </c>
+      <c r="G260" t="s">
+        <v>339</v>
       </c>
       <c r="I260" t="s">
         <v>946</v>
       </c>
-      <c r="J260" t="s">
-        <v>338</v>
-      </c>
       <c r="K260" t="s">
-        <v>339</v>
+        <v>947</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -12228,19 +12228,19 @@
         <v>14</v>
       </c>
       <c r="E261" t="s">
+        <v>405</v>
+      </c>
+      <c r="F261" t="s">
         <v>973</v>
       </c>
-      <c r="H261" t="s">
-        <v>945</v>
+      <c r="G261" t="s">
+        <v>974</v>
       </c>
       <c r="I261" t="s">
         <v>946</v>
       </c>
-      <c r="J261" t="s">
-        <v>406</v>
-      </c>
       <c r="K261" t="s">
-        <v>974</v>
+        <v>947</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -12259,17 +12259,17 @@
       <c r="E262" t="s">
         <v>337</v>
       </c>
-      <c r="H262" t="s">
-        <v>945</v>
+      <c r="F262" t="s">
+        <v>338</v>
+      </c>
+      <c r="G262" t="s">
+        <v>339</v>
       </c>
       <c r="I262" t="s">
         <v>946</v>
       </c>
-      <c r="J262" t="s">
-        <v>338</v>
-      </c>
       <c r="K262" t="s">
-        <v>339</v>
+        <v>947</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -12286,19 +12286,19 @@
         <v>14</v>
       </c>
       <c r="E263" t="s">
+        <v>377</v>
+      </c>
+      <c r="F263" t="s">
         <v>981</v>
       </c>
-      <c r="H263" t="s">
-        <v>945</v>
+      <c r="G263" t="s">
+        <v>982</v>
       </c>
       <c r="I263" t="s">
         <v>946</v>
       </c>
-      <c r="J263" t="s">
-        <v>378</v>
-      </c>
       <c r="K263" t="s">
-        <v>982</v>
+        <v>947</v>
       </c>
     </row>
     <row r="264" spans="1:11">
@@ -12317,17 +12317,17 @@
       <c r="E264" t="s">
         <v>58</v>
       </c>
-      <c r="H264" t="s">
-        <v>945</v>
+      <c r="F264" t="s">
+        <v>59</v>
+      </c>
+      <c r="G264" t="s">
+        <v>60</v>
       </c>
       <c r="I264" t="s">
         <v>946</v>
       </c>
-      <c r="J264" t="s">
-        <v>59</v>
-      </c>
       <c r="K264" t="s">
-        <v>60</v>
+        <v>947</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -12346,17 +12346,17 @@
       <c r="E265" t="s">
         <v>15</v>
       </c>
-      <c r="H265" t="s">
-        <v>945</v>
+      <c r="F265" t="s">
+        <v>16</v>
+      </c>
+      <c r="G265" t="s">
+        <v>17</v>
       </c>
       <c r="I265" t="s">
         <v>946</v>
       </c>
-      <c r="J265" t="s">
-        <v>20</v>
-      </c>
       <c r="K265" t="s">
-        <v>21</v>
+        <v>947</v>
       </c>
     </row>
     <row r="266" spans="1:11">
@@ -12373,19 +12373,19 @@
         <v>14</v>
       </c>
       <c r="E266" t="s">
+        <v>233</v>
+      </c>
+      <c r="F266" t="s">
         <v>992</v>
       </c>
-      <c r="H266" t="s">
-        <v>945</v>
+      <c r="G266" t="s">
+        <v>993</v>
       </c>
       <c r="I266" t="s">
         <v>946</v>
       </c>
-      <c r="J266" t="s">
-        <v>238</v>
-      </c>
       <c r="K266" t="s">
-        <v>993</v>
+        <v>947</v>
       </c>
     </row>
     <row r="267" spans="1:11">
@@ -12402,19 +12402,19 @@
         <v>14</v>
       </c>
       <c r="E267" t="s">
+        <v>233</v>
+      </c>
+      <c r="F267" t="s">
         <v>243</v>
       </c>
-      <c r="H267" t="s">
+      <c r="G267" t="s">
+        <v>244</v>
+      </c>
+      <c r="I267" t="s">
         <v>997</v>
       </c>
-      <c r="I267" t="s">
+      <c r="K267" t="s">
         <v>998</v>
-      </c>
-      <c r="J267" t="s">
-        <v>238</v>
-      </c>
-      <c r="K267" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -12431,19 +12431,19 @@
         <v>14</v>
       </c>
       <c r="E268" t="s">
+        <v>377</v>
+      </c>
+      <c r="F268" t="s">
         <v>420</v>
       </c>
-      <c r="H268" t="s">
+      <c r="G268" t="s">
+        <v>421</v>
+      </c>
+      <c r="I268" t="s">
         <v>1002</v>
       </c>
-      <c r="I268" t="s">
+      <c r="K268" t="s">
         <v>1003</v>
-      </c>
-      <c r="J268" t="s">
-        <v>378</v>
-      </c>
-      <c r="K268" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -12460,19 +12460,19 @@
         <v>14</v>
       </c>
       <c r="E269" t="s">
+        <v>233</v>
+      </c>
+      <c r="F269" t="s">
         <v>243</v>
       </c>
-      <c r="H269" t="s">
+      <c r="G269" t="s">
+        <v>244</v>
+      </c>
+      <c r="I269" t="s">
         <v>1007</v>
       </c>
-      <c r="I269" t="s">
+      <c r="K269" t="s">
         <v>1008</v>
-      </c>
-      <c r="J269" t="s">
-        <v>238</v>
-      </c>
-      <c r="K269" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -12489,19 +12489,19 @@
         <v>14</v>
       </c>
       <c r="E270" t="s">
+        <v>233</v>
+      </c>
+      <c r="F270" t="s">
         <v>243</v>
       </c>
-      <c r="H270" t="s">
+      <c r="G270" t="s">
+        <v>244</v>
+      </c>
+      <c r="I270" t="s">
         <v>1007</v>
       </c>
-      <c r="I270" t="s">
+      <c r="K270" t="s">
         <v>1008</v>
-      </c>
-      <c r="J270" t="s">
-        <v>238</v>
-      </c>
-      <c r="K270" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -12518,16 +12518,16 @@
         <v>14</v>
       </c>
       <c r="E271" t="s">
+        <v>233</v>
+      </c>
+      <c r="F271" t="s">
         <v>1015</v>
       </c>
-      <c r="H271" t="s">
+      <c r="G271" t="s">
         <v>1016</v>
       </c>
       <c r="I271" t="s">
         <v>1017</v>
-      </c>
-      <c r="J271" t="s">
-        <v>238</v>
       </c>
       <c r="K271" t="s">
         <v>1018</v>
@@ -12544,16 +12544,16 @@
         <v>14</v>
       </c>
       <c r="E272" t="s">
+        <v>233</v>
+      </c>
+      <c r="F272" t="s">
         <v>1015</v>
       </c>
-      <c r="H272" t="s">
+      <c r="G272" t="s">
         <v>1016</v>
       </c>
       <c r="I272" t="s">
         <v>1017</v>
-      </c>
-      <c r="J272" t="s">
-        <v>238</v>
       </c>
       <c r="K272" t="s">
         <v>1018</v>
@@ -12573,16 +12573,16 @@
         <v>14</v>
       </c>
       <c r="E273" t="s">
+        <v>233</v>
+      </c>
+      <c r="F273" t="s">
         <v>1015</v>
       </c>
-      <c r="H273" t="s">
+      <c r="G273" t="s">
         <v>1016</v>
       </c>
       <c r="I273" t="s">
         <v>1017</v>
-      </c>
-      <c r="J273" t="s">
-        <v>238</v>
       </c>
       <c r="K273" t="s">
         <v>1018</v>
@@ -12599,16 +12599,16 @@
         <v>14</v>
       </c>
       <c r="E274" t="s">
+        <v>233</v>
+      </c>
+      <c r="F274" t="s">
         <v>1015</v>
       </c>
-      <c r="H274" t="s">
+      <c r="G274" t="s">
         <v>1016</v>
       </c>
       <c r="I274" t="s">
         <v>1017</v>
-      </c>
-      <c r="J274" t="s">
-        <v>238</v>
       </c>
       <c r="K274" t="s">
         <v>1018</v>
@@ -12628,16 +12628,16 @@
         <v>14</v>
       </c>
       <c r="E275" t="s">
+        <v>233</v>
+      </c>
+      <c r="F275" t="s">
         <v>1015</v>
       </c>
-      <c r="H275" t="s">
+      <c r="G275" t="s">
         <v>1016</v>
       </c>
       <c r="I275" t="s">
         <v>1017</v>
-      </c>
-      <c r="J275" t="s">
-        <v>238</v>
       </c>
       <c r="K275" t="s">
         <v>1018</v>
@@ -12657,16 +12657,16 @@
         <v>14</v>
       </c>
       <c r="E276" t="s">
+        <v>233</v>
+      </c>
+      <c r="F276" t="s">
         <v>1015</v>
       </c>
-      <c r="H276" t="s">
+      <c r="G276" t="s">
         <v>1016</v>
       </c>
       <c r="I276" t="s">
         <v>1017</v>
-      </c>
-      <c r="J276" t="s">
-        <v>238</v>
       </c>
       <c r="K276" t="s">
         <v>1018</v>
@@ -12686,16 +12686,16 @@
         <v>14</v>
       </c>
       <c r="E277" t="s">
+        <v>233</v>
+      </c>
+      <c r="F277" t="s">
         <v>1015</v>
       </c>
-      <c r="H277" t="s">
+      <c r="G277" t="s">
         <v>1016</v>
       </c>
       <c r="I277" t="s">
         <v>1017</v>
-      </c>
-      <c r="J277" t="s">
-        <v>238</v>
       </c>
       <c r="K277" t="s">
         <v>1018</v>
@@ -12715,19 +12715,19 @@
         <v>14</v>
       </c>
       <c r="E278" t="s">
+        <v>377</v>
+      </c>
+      <c r="F278" t="s">
         <v>420</v>
       </c>
-      <c r="H278" t="s">
+      <c r="G278" t="s">
+        <v>421</v>
+      </c>
+      <c r="I278" t="s">
         <v>1038</v>
       </c>
-      <c r="I278" t="s">
+      <c r="K278" t="s">
         <v>1039</v>
-      </c>
-      <c r="J278" t="s">
-        <v>378</v>
-      </c>
-      <c r="K278" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -12744,19 +12744,19 @@
         <v>14</v>
       </c>
       <c r="E279" t="s">
+        <v>58</v>
+      </c>
+      <c r="F279" t="s">
         <v>92</v>
       </c>
-      <c r="H279" t="s">
+      <c r="G279" t="s">
+        <v>93</v>
+      </c>
+      <c r="I279" t="s">
         <v>1038</v>
       </c>
-      <c r="I279" t="s">
+      <c r="K279" t="s">
         <v>1039</v>
-      </c>
-      <c r="J279" t="s">
-        <v>59</v>
-      </c>
-      <c r="K279" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -12775,17 +12775,17 @@
       <c r="E280" t="s">
         <v>15</v>
       </c>
-      <c r="H280" t="s">
+      <c r="F280" t="s">
+        <v>16</v>
+      </c>
+      <c r="G280" t="s">
+        <v>17</v>
+      </c>
+      <c r="I280" t="s">
         <v>1038</v>
       </c>
-      <c r="I280" t="s">
+      <c r="K280" t="s">
         <v>1039</v>
-      </c>
-      <c r="J280" t="s">
-        <v>20</v>
-      </c>
-      <c r="K280" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="281" spans="1:11">
@@ -12802,19 +12802,19 @@
         <v>14</v>
       </c>
       <c r="E281" t="s">
+        <v>233</v>
+      </c>
+      <c r="F281" t="s">
         <v>352</v>
       </c>
-      <c r="H281" t="s">
+      <c r="G281" t="s">
+        <v>353</v>
+      </c>
+      <c r="I281" t="s">
         <v>1038</v>
       </c>
-      <c r="I281" t="s">
+      <c r="K281" t="s">
         <v>1039</v>
-      </c>
-      <c r="J281" t="s">
-        <v>238</v>
-      </c>
-      <c r="K281" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -12833,17 +12833,17 @@
       <c r="E282" t="s">
         <v>253</v>
       </c>
-      <c r="H282" t="s">
+      <c r="F282" t="s">
+        <v>254</v>
+      </c>
+      <c r="G282" t="s">
+        <v>255</v>
+      </c>
+      <c r="I282" t="s">
         <v>1038</v>
       </c>
-      <c r="I282" t="s">
+      <c r="K282" t="s">
         <v>1039</v>
-      </c>
-      <c r="J282" t="s">
-        <v>254</v>
-      </c>
-      <c r="K282" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -12860,19 +12860,19 @@
         <v>14</v>
       </c>
       <c r="E283" t="s">
+        <v>337</v>
+      </c>
+      <c r="F283" t="s">
         <v>892</v>
       </c>
-      <c r="H283" t="s">
+      <c r="G283" t="s">
+        <v>802</v>
+      </c>
+      <c r="I283" t="s">
         <v>1055</v>
       </c>
-      <c r="I283" t="s">
+      <c r="K283" t="s">
         <v>1056</v>
-      </c>
-      <c r="J283" t="s">
-        <v>338</v>
-      </c>
-      <c r="K283" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -12891,17 +12891,17 @@
       <c r="E284" t="s">
         <v>253</v>
       </c>
-      <c r="H284" t="s">
+      <c r="F284" t="s">
+        <v>254</v>
+      </c>
+      <c r="G284" t="s">
+        <v>255</v>
+      </c>
+      <c r="I284" t="s">
         <v>1060</v>
       </c>
-      <c r="I284" t="s">
+      <c r="K284" t="s">
         <v>1061</v>
-      </c>
-      <c r="J284" t="s">
-        <v>254</v>
-      </c>
-      <c r="K284" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -12915,19 +12915,19 @@
         <v>14</v>
       </c>
       <c r="E285" t="s">
+        <v>233</v>
+      </c>
+      <c r="F285" t="s">
         <v>352</v>
       </c>
-      <c r="H285" t="s">
+      <c r="G285" t="s">
+        <v>353</v>
+      </c>
+      <c r="I285" t="s">
         <v>1064</v>
       </c>
-      <c r="I285" t="s">
+      <c r="K285" t="s">
         <v>1065</v>
-      </c>
-      <c r="J285" t="s">
-        <v>238</v>
-      </c>
-      <c r="K285" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -12944,19 +12944,19 @@
         <v>14</v>
       </c>
       <c r="E286" t="s">
+        <v>377</v>
+      </c>
+      <c r="F286" t="s">
         <v>981</v>
       </c>
-      <c r="H286" t="s">
+      <c r="G286" t="s">
+        <v>982</v>
+      </c>
+      <c r="I286" t="s">
         <v>1069</v>
       </c>
-      <c r="I286" t="s">
+      <c r="K286" t="s">
         <v>1070</v>
-      </c>
-      <c r="J286" t="s">
-        <v>378</v>
-      </c>
-      <c r="K286" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -12973,19 +12973,19 @@
         <v>14</v>
       </c>
       <c r="E287" t="s">
+        <v>377</v>
+      </c>
+      <c r="F287" t="s">
         <v>981</v>
       </c>
-      <c r="H287" t="s">
+      <c r="G287" t="s">
+        <v>982</v>
+      </c>
+      <c r="I287" t="s">
         <v>1069</v>
       </c>
-      <c r="I287" t="s">
+      <c r="K287" t="s">
         <v>1070</v>
-      </c>
-      <c r="J287" t="s">
-        <v>378</v>
-      </c>
-      <c r="K287" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -13002,19 +13002,19 @@
         <v>14</v>
       </c>
       <c r="E288" t="s">
+        <v>15</v>
+      </c>
+      <c r="F288" t="s">
         <v>75</v>
       </c>
-      <c r="H288" t="s">
+      <c r="G288" t="s">
+        <v>76</v>
+      </c>
+      <c r="I288" t="s">
         <v>1069</v>
       </c>
-      <c r="I288" t="s">
+      <c r="K288" t="s">
         <v>1070</v>
-      </c>
-      <c r="J288" t="s">
-        <v>20</v>
-      </c>
-      <c r="K288" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -13033,17 +13033,17 @@
       <c r="E289" t="s">
         <v>58</v>
       </c>
-      <c r="H289" t="s">
+      <c r="F289" t="s">
+        <v>59</v>
+      </c>
+      <c r="G289" t="s">
+        <v>60</v>
+      </c>
+      <c r="I289" t="s">
         <v>1069</v>
       </c>
-      <c r="I289" t="s">
+      <c r="K289" t="s">
         <v>1070</v>
-      </c>
-      <c r="J289" t="s">
-        <v>59</v>
-      </c>
-      <c r="K289" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="290" spans="1:11">
@@ -13062,17 +13062,17 @@
       <c r="E290" t="s">
         <v>58</v>
       </c>
-      <c r="H290" t="s">
+      <c r="F290" t="s">
+        <v>59</v>
+      </c>
+      <c r="G290" t="s">
+        <v>60</v>
+      </c>
+      <c r="I290" t="s">
         <v>1069</v>
       </c>
-      <c r="I290" t="s">
+      <c r="K290" t="s">
         <v>1070</v>
-      </c>
-      <c r="J290" t="s">
-        <v>59</v>
-      </c>
-      <c r="K290" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -13089,19 +13089,19 @@
         <v>14</v>
       </c>
       <c r="E291" t="s">
+        <v>233</v>
+      </c>
+      <c r="F291" t="s">
         <v>352</v>
       </c>
-      <c r="H291" t="s">
+      <c r="G291" t="s">
+        <v>353</v>
+      </c>
+      <c r="I291" t="s">
         <v>1069</v>
       </c>
-      <c r="I291" t="s">
+      <c r="K291" t="s">
         <v>1070</v>
-      </c>
-      <c r="J291" t="s">
-        <v>238</v>
-      </c>
-      <c r="K291" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -13118,19 +13118,19 @@
         <v>14</v>
       </c>
       <c r="E292" t="s">
+        <v>233</v>
+      </c>
+      <c r="F292" t="s">
         <v>352</v>
       </c>
-      <c r="H292" t="s">
+      <c r="G292" t="s">
+        <v>353</v>
+      </c>
+      <c r="I292" t="s">
         <v>1069</v>
       </c>
-      <c r="I292" t="s">
+      <c r="K292" t="s">
         <v>1070</v>
-      </c>
-      <c r="J292" t="s">
-        <v>238</v>
-      </c>
-      <c r="K292" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -13147,19 +13147,19 @@
         <v>14</v>
       </c>
       <c r="E293" t="s">
+        <v>233</v>
+      </c>
+      <c r="F293" t="s">
         <v>352</v>
       </c>
-      <c r="H293" t="s">
+      <c r="G293" t="s">
+        <v>353</v>
+      </c>
+      <c r="I293" t="s">
         <v>1069</v>
       </c>
-      <c r="I293" t="s">
+      <c r="K293" t="s">
         <v>1070</v>
-      </c>
-      <c r="J293" t="s">
-        <v>238</v>
-      </c>
-      <c r="K293" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -13176,19 +13176,19 @@
         <v>14</v>
       </c>
       <c r="E294" t="s">
+        <v>233</v>
+      </c>
+      <c r="F294" t="s">
         <v>352</v>
       </c>
-      <c r="H294" t="s">
+      <c r="G294" t="s">
+        <v>353</v>
+      </c>
+      <c r="I294" t="s">
         <v>1069</v>
       </c>
-      <c r="I294" t="s">
+      <c r="K294" t="s">
         <v>1070</v>
-      </c>
-      <c r="J294" t="s">
-        <v>238</v>
-      </c>
-      <c r="K294" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -13205,19 +13205,19 @@
         <v>14</v>
       </c>
       <c r="E295" t="s">
+        <v>233</v>
+      </c>
+      <c r="F295" t="s">
         <v>352</v>
       </c>
-      <c r="H295" t="s">
+      <c r="G295" t="s">
+        <v>353</v>
+      </c>
+      <c r="I295" t="s">
         <v>1098</v>
       </c>
-      <c r="I295" t="s">
+      <c r="K295" t="s">
         <v>1099</v>
-      </c>
-      <c r="J295" t="s">
-        <v>238</v>
-      </c>
-      <c r="K295" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="296" spans="1:11">
@@ -13234,19 +13234,19 @@
         <v>14</v>
       </c>
       <c r="E296" t="s">
+        <v>233</v>
+      </c>
+      <c r="F296" t="s">
         <v>352</v>
       </c>
-      <c r="H296" t="s">
+      <c r="G296" t="s">
+        <v>353</v>
+      </c>
+      <c r="I296" t="s">
         <v>1098</v>
       </c>
-      <c r="I296" t="s">
+      <c r="K296" t="s">
         <v>1099</v>
-      </c>
-      <c r="J296" t="s">
-        <v>238</v>
-      </c>
-      <c r="K296" t="s">
-        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -28,27 +28,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -61,27 +61,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -133,12 +133,12 @@
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>112</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -259,12 +259,12 @@
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>114</t>
   </si>
   <si>
@@ -292,24 +292,24 @@
     <t>Health sector policy, planning and programmes; aid to health ministries, public health administration; institution capacity building and advice; medical insurance programmes; including health system strengthening and health governance; unspecified health activities.</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -580,21 +580,21 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -604,15 +604,15 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -715,27 +715,27 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -775,15 +775,15 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -1027,15 +1027,15 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -1147,15 +1147,15 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -1231,15 +1231,15 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -1276,18 +1276,18 @@
     <t>Social protection or social security strategies, legislation and administration; institution capacity building and advice; social security and other social schemes; support programmes, cash benefits, pensions and special programmes for older persons, orphans, persons with disabilities, children, mothers with newborns, those living in poverty, without jobs and other vulnerable groups; social dimensions of structural adjustment.</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1402,15 +1402,15 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -1708,24 +1708,24 @@
     <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -2131,24 +2131,24 @@
     <t>Agricultural sector policy, planning and programmes; aid to agricultural ministries; institution capacity building and advice; unspecified agriculture.</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2419,24 +2419,24 @@
     <t>Industrial sector policy, planning and programmes; institution capacity building and advice; unspecified industrial activities; manufacturing of goods not specified below.</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2710,12 +2710,12 @@
     <t>Trade policy and planning; support to ministries and departments responsible for trade policy; trade-related legislation and regulatory reforms; policy analysis and implementation of multilateral trade agreements e.g. technical barriers to trade and sanitary and phytosanitary measures (TBT/SPS) except at regional level (see 33130); mainstreaming trade in national development strategies (e.g. poverty reduction strategy papers); wholesale/retail trade; unspecified trade and trade promotion activities.</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>331</t>
   </si>
   <si>
@@ -2848,18 +2848,18 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -3061,16 +3061,16 @@
     <t>Actions falling outside the code headings below.</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>Action Relating to Debt</t>
   </si>
   <si>
     <t>60020</t>
@@ -3747,13 +3747,13 @@
         <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
         <v>20</v>
@@ -3817,13 +3817,13 @@
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
@@ -3852,19 +3852,19 @@
         <v>38</v>
       </c>
       <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
         <v>39</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>40</v>
       </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
       <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
         <v>41</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3890,16 +3890,16 @@
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" t="s">
         <v>19</v>
       </c>
       <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
         <v>41</v>
-      </c>
-      <c r="K7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3922,19 +3922,19 @@
         <v>38</v>
       </c>
       <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" t="s">
         <v>39</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>40</v>
       </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
       <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
         <v>41</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3957,19 +3957,19 @@
         <v>38</v>
       </c>
       <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
         <v>39</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>40</v>
       </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
       <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s">
         <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3992,19 +3992,19 @@
         <v>54</v>
       </c>
       <c r="G10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" t="s">
         <v>39</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>40</v>
       </c>
-      <c r="I10" t="s">
-        <v>19</v>
-      </c>
       <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s">
         <v>41</v>
-      </c>
-      <c r="K10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4021,25 +4021,25 @@
         <v>14</v>
       </c>
       <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
         <v>58</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" t="s">
         <v>59</v>
       </c>
-      <c r="G11" t="s">
+      <c r="J11" t="s">
         <v>60</v>
       </c>
-      <c r="H11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>41</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4062,19 +4062,19 @@
         <v>64</v>
       </c>
       <c r="G12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" t="s">
         <v>65</v>
       </c>
-      <c r="H12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" t="s">
-        <v>19</v>
-      </c>
       <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
         <v>41</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4097,19 +4097,19 @@
         <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
         <v>70</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="J13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" t="s">
         <v>71</v>
-      </c>
-      <c r="K13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4132,19 +4132,19 @@
         <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
         <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" t="s">
         <v>71</v>
-      </c>
-      <c r="K14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4167,19 +4167,19 @@
         <v>80</v>
       </c>
       <c r="G15" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" t="s">
         <v>81</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>82</v>
       </c>
-      <c r="I15" t="s">
-        <v>19</v>
-      </c>
       <c r="J15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" t="s">
         <v>83</v>
-      </c>
-      <c r="K15" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4202,19 +4202,19 @@
         <v>87</v>
       </c>
       <c r="G16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s">
         <v>88</v>
       </c>
-      <c r="H16" t="s">
-        <v>82</v>
-      </c>
-      <c r="I16" t="s">
-        <v>19</v>
-      </c>
       <c r="J16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" t="s">
         <v>83</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4231,22 +4231,22 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="K17" t="s">
         <v>97</v>
@@ -4266,22 +4266,22 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J18" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="K18" t="s">
         <v>97</v>
@@ -4301,22 +4301,22 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F19" t="s">
         <v>104</v>
       </c>
       <c r="G19" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" t="s">
         <v>105</v>
       </c>
-      <c r="H19" t="s">
-        <v>94</v>
-      </c>
-      <c r="I19" t="s">
-        <v>95</v>
-      </c>
       <c r="J19" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="K19" t="s">
         <v>97</v>
@@ -4336,22 +4336,22 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s">
         <v>109</v>
       </c>
       <c r="G20" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" t="s">
+        <v>95</v>
+      </c>
+      <c r="I20" t="s">
         <v>110</v>
       </c>
-      <c r="H20" t="s">
-        <v>94</v>
-      </c>
-      <c r="I20" t="s">
-        <v>95</v>
-      </c>
       <c r="J20" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="K20" t="s">
         <v>97</v>
@@ -4371,22 +4371,22 @@
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J21" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="K21" t="s">
         <v>97</v>
@@ -4406,25 +4406,25 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" t="s">
         <v>58</v>
       </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s">
         <v>117</v>
       </c>
       <c r="I22" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J22" t="s">
+        <v>60</v>
+      </c>
+      <c r="K22" t="s">
         <v>118</v>
-      </c>
-      <c r="K22" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4441,25 +4441,25 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F23" t="s">
         <v>122</v>
       </c>
       <c r="G23" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s">
         <v>117</v>
       </c>
       <c r="I23" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="J23" t="s">
+        <v>60</v>
+      </c>
+      <c r="K23" t="s">
         <v>118</v>
-      </c>
-      <c r="K23" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4476,25 +4476,25 @@
         <v>14</v>
       </c>
       <c r="E24" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" t="s">
         <v>58</v>
       </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s">
         <v>117</v>
       </c>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J24" t="s">
+        <v>60</v>
+      </c>
+      <c r="K24" t="s">
         <v>118</v>
-      </c>
-      <c r="K24" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4511,25 +4511,25 @@
         <v>14</v>
       </c>
       <c r="E25" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" t="s">
         <v>58</v>
       </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
       <c r="G25" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s">
         <v>117</v>
       </c>
       <c r="I25" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J25" t="s">
+        <v>60</v>
+      </c>
+      <c r="K25" t="s">
         <v>118</v>
-      </c>
-      <c r="K25" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4546,25 +4546,25 @@
         <v>14</v>
       </c>
       <c r="E26" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" t="s">
         <v>58</v>
       </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s">
         <v>117</v>
       </c>
       <c r="I26" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K26" t="s">
         <v>118</v>
-      </c>
-      <c r="K26" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4581,25 +4581,25 @@
         <v>14</v>
       </c>
       <c r="E27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F27" t="s">
         <v>58</v>
       </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
       <c r="G27" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
         <v>117</v>
       </c>
       <c r="I27" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J27" t="s">
+        <v>60</v>
+      </c>
+      <c r="K27" t="s">
         <v>118</v>
-      </c>
-      <c r="K27" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4616,25 +4616,25 @@
         <v>14</v>
       </c>
       <c r="E28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" t="s">
         <v>58</v>
       </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
       <c r="G28" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s">
         <v>117</v>
       </c>
       <c r="I28" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J28" t="s">
+        <v>60</v>
+      </c>
+      <c r="K28" t="s">
         <v>118</v>
-      </c>
-      <c r="K28" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4651,25 +4651,25 @@
         <v>14</v>
       </c>
       <c r="E29" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" t="s">
         <v>58</v>
       </c>
-      <c r="F29" t="s">
-        <v>59</v>
-      </c>
       <c r="G29" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s">
         <v>117</v>
       </c>
       <c r="I29" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J29" t="s">
+        <v>60</v>
+      </c>
+      <c r="K29" t="s">
         <v>118</v>
-      </c>
-      <c r="K29" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4686,25 +4686,25 @@
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s">
         <v>117</v>
       </c>
       <c r="I30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J30" t="s">
+        <v>60</v>
+      </c>
+      <c r="K30" t="s">
         <v>118</v>
-      </c>
-      <c r="K30" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4721,25 +4721,25 @@
         <v>14</v>
       </c>
       <c r="E31" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" t="s">
         <v>58</v>
       </c>
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
       <c r="G31" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s">
         <v>148</v>
       </c>
       <c r="I31" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J31" t="s">
+        <v>60</v>
+      </c>
+      <c r="K31" t="s">
         <v>149</v>
-      </c>
-      <c r="K31" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4756,25 +4756,25 @@
         <v>14</v>
       </c>
       <c r="E32" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" t="s">
         <v>58</v>
       </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
       <c r="G32" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s">
         <v>148</v>
       </c>
       <c r="I32" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J32" t="s">
+        <v>60</v>
+      </c>
+      <c r="K32" t="s">
         <v>149</v>
-      </c>
-      <c r="K32" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4791,25 +4791,25 @@
         <v>14</v>
       </c>
       <c r="E33" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" t="s">
         <v>58</v>
       </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
       <c r="G33" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s">
         <v>148</v>
       </c>
       <c r="I33" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J33" t="s">
+        <v>60</v>
+      </c>
+      <c r="K33" t="s">
         <v>149</v>
-      </c>
-      <c r="K33" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4826,25 +4826,25 @@
         <v>14</v>
       </c>
       <c r="E34" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" t="s">
         <v>58</v>
       </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
       <c r="G34" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s">
         <v>148</v>
       </c>
       <c r="I34" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J34" t="s">
+        <v>60</v>
+      </c>
+      <c r="K34" t="s">
         <v>149</v>
-      </c>
-      <c r="K34" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4861,25 +4861,25 @@
         <v>14</v>
       </c>
       <c r="E35" t="s">
+        <v>92</v>
+      </c>
+      <c r="F35" t="s">
         <v>58</v>
       </c>
-      <c r="F35" t="s">
-        <v>59</v>
-      </c>
       <c r="G35" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s">
         <v>148</v>
       </c>
       <c r="I35" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="J35" t="s">
+        <v>60</v>
+      </c>
+      <c r="K35" t="s">
         <v>149</v>
-      </c>
-      <c r="K35" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4896,25 +4896,25 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F36" t="s">
         <v>104</v>
       </c>
       <c r="G36" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s">
         <v>148</v>
       </c>
       <c r="I36" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="J36" t="s">
+        <v>60</v>
+      </c>
+      <c r="K36" t="s">
         <v>149</v>
-      </c>
-      <c r="K36" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4931,19 +4931,19 @@
         <v>14</v>
       </c>
       <c r="E37" t="s">
+        <v>168</v>
+      </c>
+      <c r="F37" t="s">
         <v>58</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
+        <v>169</v>
+      </c>
+      <c r="I37" t="s">
         <v>59</v>
       </c>
-      <c r="G37" t="s">
+      <c r="J37" t="s">
         <v>60</v>
-      </c>
-      <c r="I37" t="s">
-        <v>168</v>
-      </c>
-      <c r="K37" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4960,19 +4960,19 @@
         <v>14</v>
       </c>
       <c r="E38" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38" t="s">
         <v>58</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
+        <v>169</v>
+      </c>
+      <c r="I38" t="s">
         <v>59</v>
       </c>
-      <c r="G38" t="s">
+      <c r="J38" t="s">
         <v>60</v>
-      </c>
-      <c r="I38" t="s">
-        <v>168</v>
-      </c>
-      <c r="K38" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4989,19 +4989,19 @@
         <v>14</v>
       </c>
       <c r="E39" t="s">
+        <v>168</v>
+      </c>
+      <c r="F39" t="s">
         <v>58</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
+        <v>169</v>
+      </c>
+      <c r="I39" t="s">
         <v>59</v>
       </c>
-      <c r="G39" t="s">
+      <c r="J39" t="s">
         <v>60</v>
-      </c>
-      <c r="I39" t="s">
-        <v>168</v>
-      </c>
-      <c r="K39" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5018,19 +5018,19 @@
         <v>14</v>
       </c>
       <c r="E40" t="s">
+        <v>168</v>
+      </c>
+      <c r="F40" t="s">
         <v>58</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
+        <v>169</v>
+      </c>
+      <c r="I40" t="s">
         <v>59</v>
       </c>
-      <c r="G40" t="s">
+      <c r="J40" t="s">
         <v>60</v>
-      </c>
-      <c r="I40" t="s">
-        <v>168</v>
-      </c>
-      <c r="K40" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5047,19 +5047,19 @@
         <v>14</v>
       </c>
       <c r="E41" t="s">
-        <v>58</v>
+        <v>168</v>
       </c>
       <c r="F41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="I41" t="s">
-        <v>168</v>
-      </c>
-      <c r="K41" t="s">
-        <v>169</v>
+        <v>96</v>
+      </c>
+      <c r="J41" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5076,19 +5076,19 @@
         <v>14</v>
       </c>
       <c r="E42" t="s">
-        <v>58</v>
+        <v>168</v>
       </c>
       <c r="F42" t="s">
         <v>104</v>
       </c>
       <c r="G42" t="s">
+        <v>169</v>
+      </c>
+      <c r="I42" t="s">
         <v>105</v>
       </c>
-      <c r="I42" t="s">
-        <v>168</v>
-      </c>
-      <c r="K42" t="s">
-        <v>169</v>
+      <c r="J42" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5116,7 +5116,7 @@
       <c r="I43" t="s">
         <v>191</v>
       </c>
-      <c r="K43" t="s">
+      <c r="J43" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5134,19 +5134,19 @@
         <v>14</v>
       </c>
       <c r="E44" t="s">
+        <v>188</v>
+      </c>
+      <c r="F44" t="s">
         <v>196</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
+        <v>190</v>
+      </c>
+      <c r="I44" t="s">
         <v>197</v>
       </c>
-      <c r="G44" t="s">
+      <c r="J44" t="s">
         <v>198</v>
-      </c>
-      <c r="I44" t="s">
-        <v>191</v>
-      </c>
-      <c r="K44" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5174,7 +5174,7 @@
       <c r="I45" t="s">
         <v>191</v>
       </c>
-      <c r="K45" t="s">
+      <c r="J45" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       <c r="I46" t="s">
         <v>191</v>
       </c>
-      <c r="K46" t="s">
+      <c r="J46" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5221,19 +5221,19 @@
         <v>14</v>
       </c>
       <c r="E47" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F47" t="s">
         <v>208</v>
       </c>
       <c r="G47" t="s">
+        <v>190</v>
+      </c>
+      <c r="I47" t="s">
         <v>209</v>
       </c>
-      <c r="I47" t="s">
-        <v>191</v>
-      </c>
-      <c r="K47" t="s">
-        <v>192</v>
+      <c r="J47" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5261,7 +5261,7 @@
       <c r="I48" t="s">
         <v>191</v>
       </c>
-      <c r="K48" t="s">
+      <c r="J48" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       <c r="I49" t="s">
         <v>191</v>
       </c>
-      <c r="K49" t="s">
+      <c r="J49" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5308,19 +5308,19 @@
         <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F50" t="s">
         <v>208</v>
       </c>
       <c r="G50" t="s">
+        <v>190</v>
+      </c>
+      <c r="I50" t="s">
         <v>209</v>
       </c>
-      <c r="I50" t="s">
-        <v>191</v>
-      </c>
-      <c r="K50" t="s">
-        <v>192</v>
+      <c r="J50" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5348,7 +5348,7 @@
       <c r="I51" t="s">
         <v>191</v>
       </c>
-      <c r="K51" t="s">
+      <c r="J51" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5366,19 +5366,19 @@
         <v>14</v>
       </c>
       <c r="E52" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F52" t="s">
         <v>225</v>
       </c>
       <c r="G52" t="s">
+        <v>190</v>
+      </c>
+      <c r="I52" t="s">
         <v>226</v>
       </c>
-      <c r="I52" t="s">
-        <v>191</v>
-      </c>
-      <c r="K52" t="s">
-        <v>192</v>
+      <c r="J52" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5395,19 +5395,19 @@
         <v>14</v>
       </c>
       <c r="E53" t="s">
-        <v>15</v>
+        <v>188</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>17</v>
+        <v>190</v>
       </c>
       <c r="I53" t="s">
-        <v>191</v>
-      </c>
-      <c r="K53" t="s">
-        <v>192</v>
+        <v>19</v>
+      </c>
+      <c r="J53" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5465,13 +5465,13 @@
         <v>243</v>
       </c>
       <c r="G55" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H55" t="s">
         <v>236</v>
       </c>
       <c r="I55" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J55" t="s">
         <v>238</v>
@@ -5500,13 +5500,13 @@
         <v>248</v>
       </c>
       <c r="G56" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="H56" t="s">
         <v>236</v>
       </c>
       <c r="I56" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J56" t="s">
         <v>238</v>
@@ -5529,22 +5529,22 @@
         <v>14</v>
       </c>
       <c r="E57" t="s">
+        <v>233</v>
+      </c>
+      <c r="F57" t="s">
         <v>253</v>
       </c>
-      <c r="F57" t="s">
-        <v>254</v>
-      </c>
       <c r="G57" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="H57" t="s">
         <v>236</v>
       </c>
       <c r="I57" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="J57" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K57" t="s">
         <v>239</v>
@@ -5570,13 +5570,13 @@
         <v>243</v>
       </c>
       <c r="G58" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H58" t="s">
         <v>236</v>
       </c>
       <c r="I58" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J58" t="s">
         <v>238</v>
@@ -5605,13 +5605,13 @@
         <v>243</v>
       </c>
       <c r="G59" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H59" t="s">
         <v>236</v>
       </c>
       <c r="I59" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J59" t="s">
         <v>238</v>
@@ -5640,13 +5640,13 @@
         <v>243</v>
       </c>
       <c r="G60" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H60" t="s">
         <v>236</v>
       </c>
       <c r="I60" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J60" t="s">
         <v>238</v>
@@ -5675,13 +5675,13 @@
         <v>243</v>
       </c>
       <c r="G61" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H61" t="s">
         <v>236</v>
       </c>
       <c r="I61" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J61" t="s">
         <v>238</v>
@@ -5710,13 +5710,13 @@
         <v>243</v>
       </c>
       <c r="G62" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H62" t="s">
         <v>236</v>
       </c>
       <c r="I62" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J62" t="s">
         <v>238</v>
@@ -5745,13 +5745,13 @@
         <v>274</v>
       </c>
       <c r="G63" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H63" t="s">
         <v>236</v>
       </c>
       <c r="I63" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J63" t="s">
         <v>238</v>
@@ -5780,13 +5780,13 @@
         <v>274</v>
       </c>
       <c r="G64" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H64" t="s">
         <v>236</v>
       </c>
       <c r="I64" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J64" t="s">
         <v>238</v>
@@ -5815,13 +5815,13 @@
         <v>281</v>
       </c>
       <c r="G65" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="H65" t="s">
         <v>236</v>
       </c>
       <c r="I65" t="s">
-        <v>237</v>
+        <v>282</v>
       </c>
       <c r="J65" t="s">
         <v>238</v>
@@ -5885,13 +5885,13 @@
         <v>243</v>
       </c>
       <c r="G67" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H67" t="s">
         <v>236</v>
       </c>
       <c r="I67" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J67" t="s">
         <v>238</v>
@@ -5990,13 +5990,13 @@
         <v>248</v>
       </c>
       <c r="G70" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="H70" t="s">
         <v>236</v>
       </c>
       <c r="I70" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J70" t="s">
         <v>238</v>
@@ -6025,13 +6025,13 @@
         <v>248</v>
       </c>
       <c r="G71" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="H71" t="s">
         <v>236</v>
       </c>
       <c r="I71" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J71" t="s">
         <v>238</v>
@@ -6089,22 +6089,22 @@
         <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F73" t="s">
         <v>309</v>
       </c>
       <c r="G73" t="s">
-        <v>310</v>
+        <v>235</v>
       </c>
       <c r="H73" t="s">
         <v>236</v>
       </c>
       <c r="I73" t="s">
-        <v>237</v>
+        <v>310</v>
       </c>
       <c r="J73" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K73" t="s">
         <v>239</v>
@@ -6124,22 +6124,22 @@
         <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F74" t="s">
         <v>314</v>
       </c>
       <c r="G74" t="s">
-        <v>315</v>
+        <v>235</v>
       </c>
       <c r="H74" t="s">
         <v>236</v>
       </c>
       <c r="I74" t="s">
-        <v>237</v>
+        <v>315</v>
       </c>
       <c r="J74" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K74" t="s">
         <v>239</v>
@@ -6159,22 +6159,22 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F75" t="s">
         <v>319</v>
       </c>
       <c r="G75" t="s">
-        <v>320</v>
+        <v>235</v>
       </c>
       <c r="H75" t="s">
         <v>236</v>
       </c>
       <c r="I75" t="s">
-        <v>237</v>
+        <v>320</v>
       </c>
       <c r="J75" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K75" t="s">
         <v>239</v>
@@ -6194,22 +6194,22 @@
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F76" t="s">
         <v>309</v>
       </c>
       <c r="G76" t="s">
-        <v>310</v>
+        <v>235</v>
       </c>
       <c r="H76" t="s">
         <v>236</v>
       </c>
       <c r="I76" t="s">
-        <v>237</v>
+        <v>310</v>
       </c>
       <c r="J76" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K76" t="s">
         <v>239</v>
@@ -6229,22 +6229,22 @@
         <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F77" t="s">
         <v>309</v>
       </c>
       <c r="G77" t="s">
-        <v>310</v>
+        <v>235</v>
       </c>
       <c r="H77" t="s">
         <v>236</v>
       </c>
       <c r="I77" t="s">
-        <v>237</v>
+        <v>310</v>
       </c>
       <c r="J77" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K77" t="s">
         <v>239</v>
@@ -6264,22 +6264,22 @@
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F78" t="s">
         <v>314</v>
       </c>
       <c r="G78" t="s">
-        <v>315</v>
+        <v>235</v>
       </c>
       <c r="H78" t="s">
         <v>236</v>
       </c>
       <c r="I78" t="s">
-        <v>237</v>
+        <v>315</v>
       </c>
       <c r="J78" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K78" t="s">
         <v>239</v>
@@ -6296,22 +6296,22 @@
         <v>14</v>
       </c>
       <c r="E79" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F79" t="s">
         <v>332</v>
       </c>
       <c r="G79" t="s">
-        <v>333</v>
+        <v>235</v>
       </c>
       <c r="H79" t="s">
         <v>236</v>
       </c>
       <c r="I79" t="s">
-        <v>237</v>
+        <v>333</v>
       </c>
       <c r="J79" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K79" t="s">
         <v>239</v>
@@ -6331,22 +6331,22 @@
         <v>14</v>
       </c>
       <c r="E80" t="s">
+        <v>233</v>
+      </c>
+      <c r="F80" t="s">
         <v>337</v>
       </c>
-      <c r="F80" t="s">
-        <v>338</v>
-      </c>
       <c r="G80" t="s">
-        <v>339</v>
+        <v>235</v>
       </c>
       <c r="H80" t="s">
         <v>236</v>
       </c>
       <c r="I80" t="s">
-        <v>237</v>
+        <v>338</v>
       </c>
       <c r="J80" t="s">
-        <v>238</v>
+        <v>339</v>
       </c>
       <c r="K80" t="s">
         <v>239</v>
@@ -6366,22 +6366,22 @@
         <v>14</v>
       </c>
       <c r="E81" t="s">
+        <v>233</v>
+      </c>
+      <c r="F81" t="s">
         <v>337</v>
       </c>
-      <c r="F81" t="s">
-        <v>338</v>
-      </c>
       <c r="G81" t="s">
-        <v>339</v>
+        <v>235</v>
       </c>
       <c r="H81" t="s">
         <v>236</v>
       </c>
       <c r="I81" t="s">
-        <v>237</v>
+        <v>338</v>
       </c>
       <c r="J81" t="s">
-        <v>238</v>
+        <v>339</v>
       </c>
       <c r="K81" t="s">
         <v>239</v>
@@ -6401,22 +6401,22 @@
         <v>14</v>
       </c>
       <c r="E82" t="s">
+        <v>233</v>
+      </c>
+      <c r="F82" t="s">
         <v>337</v>
       </c>
-      <c r="F82" t="s">
-        <v>338</v>
-      </c>
       <c r="G82" t="s">
-        <v>339</v>
+        <v>235</v>
       </c>
       <c r="H82" t="s">
         <v>236</v>
       </c>
       <c r="I82" t="s">
-        <v>237</v>
+        <v>338</v>
       </c>
       <c r="J82" t="s">
-        <v>238</v>
+        <v>339</v>
       </c>
       <c r="K82" t="s">
         <v>239</v>
@@ -6477,13 +6477,13 @@
         <v>352</v>
       </c>
       <c r="G84" t="s">
-        <v>353</v>
+        <v>235</v>
       </c>
       <c r="H84" t="s">
         <v>236</v>
       </c>
       <c r="I84" t="s">
-        <v>237</v>
+        <v>353</v>
       </c>
       <c r="J84" t="s">
         <v>238</v>
@@ -6512,13 +6512,13 @@
         <v>357</v>
       </c>
       <c r="G85" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H85" t="s">
         <v>236</v>
       </c>
       <c r="I85" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J85" t="s">
         <v>238</v>
@@ -6541,22 +6541,22 @@
         <v>14</v>
       </c>
       <c r="E86" t="s">
-        <v>337</v>
+        <v>233</v>
       </c>
       <c r="F86" t="s">
         <v>361</v>
       </c>
       <c r="G86" t="s">
-        <v>362</v>
+        <v>235</v>
       </c>
       <c r="H86" t="s">
         <v>236</v>
       </c>
       <c r="I86" t="s">
-        <v>237</v>
+        <v>362</v>
       </c>
       <c r="J86" t="s">
-        <v>238</v>
+        <v>339</v>
       </c>
       <c r="K86" t="s">
         <v>239</v>
@@ -6582,13 +6582,13 @@
         <v>357</v>
       </c>
       <c r="G87" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H87" t="s">
         <v>236</v>
       </c>
       <c r="I87" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J87" t="s">
         <v>238</v>
@@ -6614,13 +6614,13 @@
         <v>243</v>
       </c>
       <c r="G88" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H88" t="s">
         <v>236</v>
       </c>
       <c r="I88" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J88" t="s">
         <v>238</v>
@@ -6649,13 +6649,13 @@
         <v>243</v>
       </c>
       <c r="G89" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H89" t="s">
         <v>236</v>
       </c>
       <c r="I89" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J89" t="s">
         <v>238</v>
@@ -6678,22 +6678,22 @@
         <v>14</v>
       </c>
       <c r="E90" t="s">
+        <v>233</v>
+      </c>
+      <c r="F90" t="s">
         <v>253</v>
       </c>
-      <c r="F90" t="s">
-        <v>254</v>
-      </c>
       <c r="G90" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="H90" t="s">
         <v>236</v>
       </c>
       <c r="I90" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="J90" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K90" t="s">
         <v>239</v>
@@ -6713,22 +6713,22 @@
         <v>14</v>
       </c>
       <c r="E91" t="s">
+        <v>233</v>
+      </c>
+      <c r="F91" t="s">
         <v>377</v>
       </c>
-      <c r="F91" t="s">
-        <v>378</v>
-      </c>
       <c r="G91" t="s">
-        <v>379</v>
+        <v>235</v>
       </c>
       <c r="H91" t="s">
         <v>236</v>
       </c>
       <c r="I91" t="s">
-        <v>237</v>
+        <v>378</v>
       </c>
       <c r="J91" t="s">
-        <v>238</v>
+        <v>379</v>
       </c>
       <c r="K91" t="s">
         <v>239</v>
@@ -6748,22 +6748,22 @@
         <v>14</v>
       </c>
       <c r="E92" t="s">
+        <v>233</v>
+      </c>
+      <c r="F92" t="s">
         <v>253</v>
       </c>
-      <c r="F92" t="s">
-        <v>254</v>
-      </c>
       <c r="G92" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="H92" t="s">
         <v>236</v>
       </c>
       <c r="I92" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="J92" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K92" t="s">
         <v>239</v>
@@ -6789,13 +6789,13 @@
         <v>248</v>
       </c>
       <c r="G93" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="H93" t="s">
         <v>236</v>
       </c>
       <c r="I93" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J93" t="s">
         <v>238</v>
@@ -6818,22 +6818,22 @@
         <v>14</v>
       </c>
       <c r="E94" t="s">
+        <v>233</v>
+      </c>
+      <c r="F94" t="s">
         <v>253</v>
       </c>
-      <c r="F94" t="s">
-        <v>254</v>
-      </c>
       <c r="G94" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="H94" t="s">
         <v>236</v>
       </c>
       <c r="I94" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="J94" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K94" t="s">
         <v>239</v>
@@ -6859,13 +6859,13 @@
         <v>392</v>
       </c>
       <c r="G95" t="s">
-        <v>393</v>
+        <v>235</v>
       </c>
       <c r="H95" t="s">
         <v>236</v>
       </c>
       <c r="I95" t="s">
-        <v>237</v>
+        <v>393</v>
       </c>
       <c r="J95" t="s">
         <v>238</v>
@@ -6888,25 +6888,25 @@
         <v>14</v>
       </c>
       <c r="E96" t="s">
+        <v>233</v>
+      </c>
+      <c r="F96" t="s">
         <v>253</v>
       </c>
-      <c r="F96" t="s">
-        <v>254</v>
-      </c>
       <c r="G96" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="H96" t="s">
         <v>397</v>
       </c>
       <c r="I96" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="J96" t="s">
+        <v>255</v>
+      </c>
+      <c r="K96" t="s">
         <v>398</v>
-      </c>
-      <c r="K96" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -6923,25 +6923,25 @@
         <v>14</v>
       </c>
       <c r="E97" t="s">
+        <v>233</v>
+      </c>
+      <c r="F97" t="s">
         <v>253</v>
       </c>
-      <c r="F97" t="s">
-        <v>254</v>
-      </c>
       <c r="G97" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="H97" t="s">
         <v>397</v>
       </c>
       <c r="I97" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="J97" t="s">
+        <v>255</v>
+      </c>
+      <c r="K97" t="s">
         <v>398</v>
-      </c>
-      <c r="K97" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -6958,25 +6958,25 @@
         <v>14</v>
       </c>
       <c r="E98" t="s">
+        <v>233</v>
+      </c>
+      <c r="F98" t="s">
         <v>405</v>
       </c>
-      <c r="F98" t="s">
-        <v>406</v>
-      </c>
       <c r="G98" t="s">
-        <v>407</v>
+        <v>235</v>
       </c>
       <c r="H98" t="s">
         <v>397</v>
       </c>
       <c r="I98" t="s">
-        <v>237</v>
+        <v>406</v>
       </c>
       <c r="J98" t="s">
+        <v>407</v>
+      </c>
+      <c r="K98" t="s">
         <v>398</v>
-      </c>
-      <c r="K98" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -6993,25 +6993,25 @@
         <v>14</v>
       </c>
       <c r="E99" t="s">
+        <v>233</v>
+      </c>
+      <c r="F99" t="s">
         <v>253</v>
       </c>
-      <c r="F99" t="s">
-        <v>254</v>
-      </c>
       <c r="G99" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="H99" t="s">
         <v>397</v>
       </c>
       <c r="I99" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="J99" t="s">
+        <v>255</v>
+      </c>
+      <c r="K99" t="s">
         <v>398</v>
-      </c>
-      <c r="K99" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -7028,25 +7028,25 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F100" t="s">
         <v>319</v>
       </c>
       <c r="G100" t="s">
-        <v>320</v>
+        <v>235</v>
       </c>
       <c r="H100" t="s">
         <v>397</v>
       </c>
       <c r="I100" t="s">
-        <v>237</v>
+        <v>320</v>
       </c>
       <c r="J100" t="s">
+        <v>255</v>
+      </c>
+      <c r="K100" t="s">
         <v>398</v>
-      </c>
-      <c r="K100" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -7063,25 +7063,25 @@
         <v>14</v>
       </c>
       <c r="E101" t="s">
+        <v>233</v>
+      </c>
+      <c r="F101" t="s">
         <v>253</v>
       </c>
-      <c r="F101" t="s">
-        <v>254</v>
-      </c>
       <c r="G101" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="H101" t="s">
         <v>397</v>
       </c>
       <c r="I101" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="J101" t="s">
+        <v>255</v>
+      </c>
+      <c r="K101" t="s">
         <v>398</v>
-      </c>
-      <c r="K101" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -7098,19 +7098,19 @@
         <v>14</v>
       </c>
       <c r="E102" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="F102" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G102" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I102" t="s">
-        <v>422</v>
-      </c>
-      <c r="K102" t="s">
         <v>423</v>
+      </c>
+      <c r="J102" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -7127,19 +7127,19 @@
         <v>14</v>
       </c>
       <c r="E103" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="F103" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G103" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I103" t="s">
-        <v>422</v>
-      </c>
-      <c r="K103" t="s">
         <v>423</v>
+      </c>
+      <c r="J103" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -7156,19 +7156,19 @@
         <v>14</v>
       </c>
       <c r="E104" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="F104" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G104" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I104" t="s">
-        <v>422</v>
-      </c>
-      <c r="K104" t="s">
         <v>423</v>
+      </c>
+      <c r="J104" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -7185,19 +7185,19 @@
         <v>14</v>
       </c>
       <c r="E105" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="F105" t="s">
         <v>433</v>
       </c>
       <c r="G105" t="s">
+        <v>422</v>
+      </c>
+      <c r="I105" t="s">
         <v>434</v>
       </c>
-      <c r="I105" t="s">
-        <v>422</v>
-      </c>
-      <c r="K105" t="s">
-        <v>423</v>
+      <c r="J105" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7214,19 +7214,19 @@
         <v>14</v>
       </c>
       <c r="E106" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="F106" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G106" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I106" t="s">
-        <v>422</v>
-      </c>
-      <c r="K106" t="s">
         <v>423</v>
+      </c>
+      <c r="J106" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -7243,19 +7243,19 @@
         <v>14</v>
       </c>
       <c r="E107" t="s">
+        <v>420</v>
+      </c>
+      <c r="F107" t="s">
         <v>377</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
+        <v>422</v>
+      </c>
+      <c r="I107" t="s">
         <v>378</v>
       </c>
-      <c r="G107" t="s">
+      <c r="J107" t="s">
         <v>379</v>
-      </c>
-      <c r="I107" t="s">
-        <v>422</v>
-      </c>
-      <c r="K107" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -7272,19 +7272,19 @@
         <v>14</v>
       </c>
       <c r="E108" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="F108" t="s">
         <v>444</v>
       </c>
       <c r="G108" t="s">
+        <v>422</v>
+      </c>
+      <c r="I108" t="s">
         <v>445</v>
       </c>
-      <c r="I108" t="s">
-        <v>422</v>
-      </c>
-      <c r="K108" t="s">
-        <v>423</v>
+      <c r="J108" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7301,19 +7301,19 @@
         <v>14</v>
       </c>
       <c r="E109" t="s">
-        <v>188</v>
+        <v>420</v>
       </c>
       <c r="F109" t="s">
         <v>449</v>
       </c>
       <c r="G109" t="s">
+        <v>422</v>
+      </c>
+      <c r="I109" t="s">
         <v>450</v>
       </c>
-      <c r="I109" t="s">
-        <v>422</v>
-      </c>
-      <c r="K109" t="s">
-        <v>423</v>
+      <c r="J109" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -7330,19 +7330,19 @@
         <v>14</v>
       </c>
       <c r="E110" t="s">
-        <v>188</v>
+        <v>420</v>
       </c>
       <c r="F110" t="s">
         <v>454</v>
       </c>
       <c r="G110" t="s">
+        <v>422</v>
+      </c>
+      <c r="I110" t="s">
         <v>455</v>
       </c>
-      <c r="I110" t="s">
-        <v>422</v>
-      </c>
-      <c r="K110" t="s">
-        <v>423</v>
+      <c r="J110" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -7359,19 +7359,19 @@
         <v>14</v>
       </c>
       <c r="E111" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="F111" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G111" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I111" t="s">
-        <v>422</v>
-      </c>
-      <c r="K111" t="s">
         <v>423</v>
+      </c>
+      <c r="J111" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -7388,22 +7388,22 @@
         <v>14</v>
       </c>
       <c r="E112" t="s">
+        <v>420</v>
+      </c>
+      <c r="F112" t="s">
         <v>462</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
+        <v>422</v>
+      </c>
+      <c r="I112" t="s">
         <v>463</v>
       </c>
-      <c r="G112" t="s">
+      <c r="J112" t="s">
         <v>464</v>
       </c>
-      <c r="I112" t="s">
-        <v>422</v>
-      </c>
-      <c r="K112" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11">
+    </row>
+    <row r="113" spans="1:10">
       <c r="A113" t="s">
         <v>465</v>
       </c>
@@ -7417,22 +7417,22 @@
         <v>14</v>
       </c>
       <c r="E113" t="s">
-        <v>233</v>
+        <v>420</v>
       </c>
       <c r="F113" t="s">
         <v>296</v>
       </c>
       <c r="G113" t="s">
-        <v>235</v>
+        <v>422</v>
       </c>
       <c r="I113" t="s">
-        <v>422</v>
-      </c>
-      <c r="K113" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11">
+        <v>237</v>
+      </c>
+      <c r="J113" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
       <c r="A114" t="s">
         <v>468</v>
       </c>
@@ -7446,22 +7446,22 @@
         <v>14</v>
       </c>
       <c r="E114" t="s">
-        <v>253</v>
+        <v>420</v>
       </c>
       <c r="F114" t="s">
         <v>314</v>
       </c>
       <c r="G114" t="s">
+        <v>422</v>
+      </c>
+      <c r="I114" t="s">
         <v>315</v>
       </c>
-      <c r="I114" t="s">
-        <v>422</v>
-      </c>
-      <c r="K114" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
+      <c r="J114" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
       <c r="A115" t="s">
         <v>471</v>
       </c>
@@ -7475,22 +7475,22 @@
         <v>14</v>
       </c>
       <c r="E115" t="s">
+        <v>420</v>
+      </c>
+      <c r="F115" t="s">
         <v>377</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
+        <v>422</v>
+      </c>
+      <c r="I115" t="s">
         <v>378</v>
       </c>
-      <c r="G115" t="s">
+      <c r="J115" t="s">
         <v>379</v>
       </c>
-      <c r="I115" t="s">
-        <v>422</v>
-      </c>
-      <c r="K115" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
+    </row>
+    <row r="116" spans="1:10">
       <c r="A116" t="s">
         <v>474</v>
       </c>
@@ -7501,22 +7501,22 @@
         <v>14</v>
       </c>
       <c r="E116" t="s">
-        <v>462</v>
+        <v>420</v>
       </c>
       <c r="F116" t="s">
         <v>476</v>
       </c>
       <c r="G116" t="s">
+        <v>422</v>
+      </c>
+      <c r="I116" t="s">
         <v>477</v>
       </c>
-      <c r="I116" t="s">
-        <v>422</v>
-      </c>
-      <c r="K116" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11">
+      <c r="J116" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
       <c r="A117" t="s">
         <v>478</v>
       </c>
@@ -7527,22 +7527,22 @@
         <v>14</v>
       </c>
       <c r="E117" t="s">
+        <v>420</v>
+      </c>
+      <c r="F117" t="s">
         <v>462</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
+        <v>422</v>
+      </c>
+      <c r="I117" t="s">
         <v>463</v>
       </c>
-      <c r="G117" t="s">
+      <c r="J117" t="s">
         <v>464</v>
       </c>
-      <c r="I117" t="s">
-        <v>422</v>
-      </c>
-      <c r="K117" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
+    </row>
+    <row r="118" spans="1:10">
       <c r="A118" t="s">
         <v>480</v>
       </c>
@@ -7556,22 +7556,22 @@
         <v>14</v>
       </c>
       <c r="E118" t="s">
-        <v>337</v>
+        <v>420</v>
       </c>
       <c r="F118" t="s">
         <v>483</v>
       </c>
       <c r="G118" t="s">
+        <v>422</v>
+      </c>
+      <c r="I118" t="s">
+        <v>338</v>
+      </c>
+      <c r="J118" t="s">
         <v>339</v>
       </c>
-      <c r="I118" t="s">
-        <v>422</v>
-      </c>
-      <c r="K118" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
+    </row>
+    <row r="119" spans="1:10">
       <c r="A119" t="s">
         <v>484</v>
       </c>
@@ -7585,22 +7585,22 @@
         <v>14</v>
       </c>
       <c r="E119" t="s">
+        <v>420</v>
+      </c>
+      <c r="F119" t="s">
         <v>377</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
+        <v>422</v>
+      </c>
+      <c r="I119" t="s">
         <v>378</v>
       </c>
-      <c r="G119" t="s">
+      <c r="J119" t="s">
         <v>379</v>
       </c>
-      <c r="I119" t="s">
-        <v>422</v>
-      </c>
-      <c r="K119" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11">
+    </row>
+    <row r="120" spans="1:10">
       <c r="A120" t="s">
         <v>487</v>
       </c>
@@ -7614,22 +7614,22 @@
         <v>14</v>
       </c>
       <c r="E120" t="s">
-        <v>233</v>
+        <v>490</v>
       </c>
       <c r="F120" t="s">
         <v>352</v>
       </c>
       <c r="G120" t="s">
+        <v>491</v>
+      </c>
+      <c r="I120" t="s">
         <v>353</v>
       </c>
-      <c r="I120" t="s">
-        <v>490</v>
-      </c>
-      <c r="K120" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11">
+      <c r="J120" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
       <c r="A121" t="s">
         <v>492</v>
       </c>
@@ -7643,22 +7643,22 @@
         <v>14</v>
       </c>
       <c r="E121" t="s">
-        <v>233</v>
+        <v>490</v>
       </c>
       <c r="F121" t="s">
         <v>296</v>
       </c>
       <c r="G121" t="s">
-        <v>235</v>
+        <v>491</v>
       </c>
       <c r="I121" t="s">
-        <v>490</v>
-      </c>
-      <c r="K121" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11">
+        <v>237</v>
+      </c>
+      <c r="J121" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
       <c r="A122" t="s">
         <v>495</v>
       </c>
@@ -7672,22 +7672,22 @@
         <v>14</v>
       </c>
       <c r="E122" t="s">
-        <v>233</v>
+        <v>490</v>
       </c>
       <c r="F122" t="s">
         <v>352</v>
       </c>
       <c r="G122" t="s">
+        <v>491</v>
+      </c>
+      <c r="I122" t="s">
         <v>353</v>
       </c>
-      <c r="I122" t="s">
-        <v>490</v>
-      </c>
-      <c r="K122" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11">
+      <c r="J122" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
       <c r="A123" t="s">
         <v>498</v>
       </c>
@@ -7701,22 +7701,22 @@
         <v>14</v>
       </c>
       <c r="E123" t="s">
-        <v>233</v>
+        <v>490</v>
       </c>
       <c r="F123" t="s">
         <v>352</v>
       </c>
       <c r="G123" t="s">
+        <v>491</v>
+      </c>
+      <c r="I123" t="s">
         <v>353</v>
       </c>
-      <c r="I123" t="s">
-        <v>490</v>
-      </c>
-      <c r="K123" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
+      <c r="J123" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
       <c r="A124" t="s">
         <v>501</v>
       </c>
@@ -7730,22 +7730,22 @@
         <v>14</v>
       </c>
       <c r="E124" t="s">
-        <v>337</v>
+        <v>490</v>
       </c>
       <c r="F124" t="s">
         <v>504</v>
       </c>
       <c r="G124" t="s">
+        <v>491</v>
+      </c>
+      <c r="I124" t="s">
         <v>505</v>
       </c>
-      <c r="I124" t="s">
-        <v>490</v>
-      </c>
-      <c r="K124" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
+      <c r="J124" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
       <c r="A125" t="s">
         <v>506</v>
       </c>
@@ -7759,22 +7759,22 @@
         <v>14</v>
       </c>
       <c r="E125" t="s">
-        <v>337</v>
+        <v>490</v>
       </c>
       <c r="F125" t="s">
         <v>504</v>
       </c>
       <c r="G125" t="s">
+        <v>491</v>
+      </c>
+      <c r="I125" t="s">
         <v>505</v>
       </c>
-      <c r="I125" t="s">
-        <v>490</v>
-      </c>
-      <c r="K125" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11">
+      <c r="J125" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
       <c r="A126" t="s">
         <v>509</v>
       </c>
@@ -7788,22 +7788,22 @@
         <v>14</v>
       </c>
       <c r="E126" t="s">
-        <v>337</v>
+        <v>490</v>
       </c>
       <c r="F126" t="s">
         <v>504</v>
       </c>
       <c r="G126" t="s">
+        <v>491</v>
+      </c>
+      <c r="I126" t="s">
         <v>505</v>
       </c>
-      <c r="I126" t="s">
-        <v>490</v>
-      </c>
-      <c r="K126" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11">
+      <c r="J126" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
       <c r="A127" t="s">
         <v>512</v>
       </c>
@@ -7817,22 +7817,22 @@
         <v>14</v>
       </c>
       <c r="E127" t="s">
-        <v>337</v>
+        <v>490</v>
       </c>
       <c r="F127" t="s">
         <v>504</v>
       </c>
       <c r="G127" t="s">
+        <v>491</v>
+      </c>
+      <c r="I127" t="s">
         <v>505</v>
       </c>
-      <c r="I127" t="s">
-        <v>490</v>
-      </c>
-      <c r="K127" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11">
+      <c r="J127" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
       <c r="A128" t="s">
         <v>515</v>
       </c>
@@ -7846,19 +7846,19 @@
         <v>14</v>
       </c>
       <c r="E128" t="s">
-        <v>337</v>
+        <v>490</v>
       </c>
       <c r="F128" t="s">
         <v>504</v>
       </c>
       <c r="G128" t="s">
+        <v>491</v>
+      </c>
+      <c r="I128" t="s">
         <v>505</v>
       </c>
-      <c r="I128" t="s">
-        <v>490</v>
-      </c>
-      <c r="K128" t="s">
-        <v>491</v>
+      <c r="J128" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -7875,19 +7875,19 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>337</v>
+        <v>490</v>
       </c>
       <c r="F129" t="s">
         <v>521</v>
       </c>
       <c r="G129" t="s">
+        <v>491</v>
+      </c>
+      <c r="I129" t="s">
         <v>505</v>
       </c>
-      <c r="I129" t="s">
-        <v>490</v>
-      </c>
-      <c r="K129" t="s">
-        <v>491</v>
+      <c r="J129" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7904,19 +7904,19 @@
         <v>14</v>
       </c>
       <c r="E130" t="s">
-        <v>337</v>
+        <v>490</v>
       </c>
       <c r="F130" t="s">
         <v>525</v>
       </c>
       <c r="G130" t="s">
+        <v>491</v>
+      </c>
+      <c r="I130" t="s">
         <v>505</v>
       </c>
-      <c r="I130" t="s">
-        <v>490</v>
-      </c>
-      <c r="K130" t="s">
-        <v>491</v>
+      <c r="J130" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7933,19 +7933,19 @@
         <v>14</v>
       </c>
       <c r="E131" t="s">
-        <v>337</v>
+        <v>490</v>
       </c>
       <c r="F131" t="s">
         <v>529</v>
       </c>
       <c r="G131" t="s">
+        <v>491</v>
+      </c>
+      <c r="I131" t="s">
         <v>505</v>
       </c>
-      <c r="I131" t="s">
-        <v>490</v>
-      </c>
-      <c r="K131" t="s">
-        <v>491</v>
+      <c r="J131" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7962,19 +7962,19 @@
         <v>14</v>
       </c>
       <c r="E132" t="s">
-        <v>337</v>
+        <v>490</v>
       </c>
       <c r="F132" t="s">
         <v>533</v>
       </c>
       <c r="G132" t="s">
+        <v>491</v>
+      </c>
+      <c r="I132" t="s">
         <v>534</v>
       </c>
-      <c r="I132" t="s">
-        <v>490</v>
-      </c>
-      <c r="K132" t="s">
-        <v>491</v>
+      <c r="J132" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -7988,19 +7988,19 @@
         <v>14</v>
       </c>
       <c r="E133" t="s">
-        <v>233</v>
+        <v>490</v>
       </c>
       <c r="F133" t="s">
         <v>392</v>
       </c>
       <c r="G133" t="s">
+        <v>491</v>
+      </c>
+      <c r="I133" t="s">
         <v>393</v>
       </c>
-      <c r="I133" t="s">
-        <v>490</v>
-      </c>
-      <c r="K133" t="s">
-        <v>491</v>
+      <c r="J133" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -8017,19 +8017,19 @@
         <v>14</v>
       </c>
       <c r="E134" t="s">
-        <v>337</v>
+        <v>540</v>
       </c>
       <c r="F134" t="s">
         <v>361</v>
       </c>
       <c r="G134" t="s">
+        <v>541</v>
+      </c>
+      <c r="I134" t="s">
         <v>362</v>
       </c>
-      <c r="I134" t="s">
-        <v>540</v>
-      </c>
-      <c r="K134" t="s">
-        <v>541</v>
+      <c r="J134" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -8043,19 +8043,19 @@
         <v>14</v>
       </c>
       <c r="E135" t="s">
-        <v>337</v>
+        <v>540</v>
       </c>
       <c r="F135" t="s">
         <v>361</v>
       </c>
       <c r="G135" t="s">
+        <v>541</v>
+      </c>
+      <c r="I135" t="s">
         <v>362</v>
       </c>
-      <c r="I135" t="s">
-        <v>540</v>
-      </c>
-      <c r="K135" t="s">
-        <v>541</v>
+      <c r="J135" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -8072,19 +8072,19 @@
         <v>14</v>
       </c>
       <c r="E136" t="s">
-        <v>337</v>
+        <v>540</v>
       </c>
       <c r="F136" t="s">
         <v>361</v>
       </c>
       <c r="G136" t="s">
+        <v>541</v>
+      </c>
+      <c r="I136" t="s">
         <v>362</v>
       </c>
-      <c r="I136" t="s">
-        <v>540</v>
-      </c>
-      <c r="K136" t="s">
-        <v>541</v>
+      <c r="J136" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -8101,19 +8101,19 @@
         <v>14</v>
       </c>
       <c r="E137" t="s">
-        <v>337</v>
+        <v>540</v>
       </c>
       <c r="F137" t="s">
         <v>361</v>
       </c>
       <c r="G137" t="s">
+        <v>541</v>
+      </c>
+      <c r="I137" t="s">
         <v>362</v>
       </c>
-      <c r="I137" t="s">
-        <v>540</v>
-      </c>
-      <c r="K137" t="s">
-        <v>541</v>
+      <c r="J137" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -8130,19 +8130,19 @@
         <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>337</v>
+        <v>540</v>
       </c>
       <c r="F138" t="s">
         <v>361</v>
       </c>
       <c r="G138" t="s">
+        <v>541</v>
+      </c>
+      <c r="I138" t="s">
         <v>362</v>
       </c>
-      <c r="I138" t="s">
-        <v>540</v>
-      </c>
-      <c r="K138" t="s">
-        <v>541</v>
+      <c r="J138" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -8159,19 +8159,19 @@
         <v>14</v>
       </c>
       <c r="E139" t="s">
-        <v>462</v>
+        <v>540</v>
       </c>
       <c r="F139" t="s">
         <v>556</v>
       </c>
       <c r="G139" t="s">
+        <v>541</v>
+      </c>
+      <c r="I139" t="s">
         <v>557</v>
       </c>
-      <c r="I139" t="s">
-        <v>540</v>
-      </c>
-      <c r="K139" t="s">
-        <v>541</v>
+      <c r="J139" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -8188,19 +8188,19 @@
         <v>14</v>
       </c>
       <c r="E140" t="s">
-        <v>337</v>
+        <v>540</v>
       </c>
       <c r="F140" t="s">
         <v>361</v>
       </c>
       <c r="G140" t="s">
+        <v>541</v>
+      </c>
+      <c r="I140" t="s">
         <v>362</v>
       </c>
-      <c r="I140" t="s">
-        <v>540</v>
-      </c>
-      <c r="K140" t="s">
-        <v>541</v>
+      <c r="J140" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -8217,22 +8217,22 @@
         <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F141" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G141" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H141" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I141" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J141" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K141" t="s">
         <v>569</v>
@@ -8249,22 +8249,22 @@
         <v>14</v>
       </c>
       <c r="E142" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F142" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G142" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H142" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I142" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J142" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K142" t="s">
         <v>569</v>
@@ -8284,22 +8284,22 @@
         <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F143" t="s">
         <v>575</v>
       </c>
       <c r="G143" t="s">
+        <v>566</v>
+      </c>
+      <c r="H143" t="s">
+        <v>567</v>
+      </c>
+      <c r="I143" t="s">
         <v>576</v>
       </c>
-      <c r="H143" t="s">
-        <v>566</v>
-      </c>
-      <c r="I143" t="s">
-        <v>567</v>
-      </c>
       <c r="J143" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K143" t="s">
         <v>569</v>
@@ -8319,22 +8319,22 @@
         <v>14</v>
       </c>
       <c r="E144" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F144" t="s">
         <v>575</v>
       </c>
       <c r="G144" t="s">
+        <v>566</v>
+      </c>
+      <c r="H144" t="s">
+        <v>567</v>
+      </c>
+      <c r="I144" t="s">
         <v>576</v>
       </c>
-      <c r="H144" t="s">
-        <v>566</v>
-      </c>
-      <c r="I144" t="s">
-        <v>567</v>
-      </c>
       <c r="J144" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K144" t="s">
         <v>569</v>
@@ -8354,22 +8354,22 @@
         <v>14</v>
       </c>
       <c r="E145" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F145" t="s">
         <v>575</v>
       </c>
       <c r="G145" t="s">
+        <v>566</v>
+      </c>
+      <c r="H145" t="s">
+        <v>567</v>
+      </c>
+      <c r="I145" t="s">
         <v>576</v>
       </c>
-      <c r="H145" t="s">
-        <v>566</v>
-      </c>
-      <c r="I145" t="s">
-        <v>567</v>
-      </c>
       <c r="J145" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K145" t="s">
         <v>569</v>
@@ -8389,22 +8389,22 @@
         <v>14</v>
       </c>
       <c r="E146" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F146" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G146" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H146" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I146" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J146" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K146" t="s">
         <v>569</v>
@@ -8424,25 +8424,25 @@
         <v>14</v>
       </c>
       <c r="E147" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F147" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G147" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H147" t="s">
         <v>589</v>
       </c>
       <c r="I147" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J147" t="s">
+        <v>339</v>
+      </c>
+      <c r="K147" t="s">
         <v>590</v>
-      </c>
-      <c r="K147" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -8459,25 +8459,25 @@
         <v>14</v>
       </c>
       <c r="E148" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F148" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G148" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H148" t="s">
         <v>589</v>
       </c>
       <c r="I148" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J148" t="s">
+        <v>339</v>
+      </c>
+      <c r="K148" t="s">
         <v>590</v>
-      </c>
-      <c r="K148" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -8494,25 +8494,25 @@
         <v>14</v>
       </c>
       <c r="E149" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F149" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G149" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H149" t="s">
         <v>589</v>
       </c>
       <c r="I149" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J149" t="s">
+        <v>339</v>
+      </c>
+      <c r="K149" t="s">
         <v>590</v>
-      </c>
-      <c r="K149" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -8529,25 +8529,25 @@
         <v>14</v>
       </c>
       <c r="E150" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F150" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G150" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H150" t="s">
         <v>589</v>
       </c>
       <c r="I150" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J150" t="s">
+        <v>339</v>
+      </c>
+      <c r="K150" t="s">
         <v>590</v>
-      </c>
-      <c r="K150" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -8564,25 +8564,25 @@
         <v>14</v>
       </c>
       <c r="E151" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F151" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G151" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H151" t="s">
         <v>589</v>
       </c>
       <c r="I151" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J151" t="s">
+        <v>339</v>
+      </c>
+      <c r="K151" t="s">
         <v>590</v>
-      </c>
-      <c r="K151" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -8599,25 +8599,25 @@
         <v>14</v>
       </c>
       <c r="E152" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F152" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G152" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H152" t="s">
         <v>589</v>
       </c>
       <c r="I152" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J152" t="s">
+        <v>339</v>
+      </c>
+      <c r="K152" t="s">
         <v>590</v>
-      </c>
-      <c r="K152" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -8634,25 +8634,25 @@
         <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F153" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G153" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H153" t="s">
         <v>589</v>
       </c>
       <c r="I153" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J153" t="s">
+        <v>339</v>
+      </c>
+      <c r="K153" t="s">
         <v>590</v>
-      </c>
-      <c r="K153" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -8669,25 +8669,25 @@
         <v>14</v>
       </c>
       <c r="E154" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F154" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G154" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H154" t="s">
         <v>589</v>
       </c>
       <c r="I154" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J154" t="s">
+        <v>339</v>
+      </c>
+      <c r="K154" t="s">
         <v>590</v>
-      </c>
-      <c r="K154" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -8704,25 +8704,25 @@
         <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F155" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G155" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H155" t="s">
         <v>589</v>
       </c>
       <c r="I155" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J155" t="s">
+        <v>339</v>
+      </c>
+      <c r="K155" t="s">
         <v>590</v>
-      </c>
-      <c r="K155" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -8739,25 +8739,25 @@
         <v>14</v>
       </c>
       <c r="E156" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F156" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G156" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H156" t="s">
         <v>618</v>
       </c>
       <c r="I156" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J156" t="s">
+        <v>339</v>
+      </c>
+      <c r="K156" t="s">
         <v>619</v>
-      </c>
-      <c r="K156" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -8774,25 +8774,25 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F157" t="s">
         <v>623</v>
       </c>
       <c r="G157" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H157" t="s">
         <v>618</v>
       </c>
       <c r="I157" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J157" t="s">
+        <v>339</v>
+      </c>
+      <c r="K157" t="s">
         <v>619</v>
-      </c>
-      <c r="K157" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -8809,25 +8809,25 @@
         <v>14</v>
       </c>
       <c r="E158" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F158" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G158" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H158" t="s">
         <v>618</v>
       </c>
       <c r="I158" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J158" t="s">
+        <v>339</v>
+      </c>
+      <c r="K158" t="s">
         <v>619</v>
-      </c>
-      <c r="K158" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -8844,25 +8844,25 @@
         <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F159" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G159" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H159" t="s">
         <v>618</v>
       </c>
       <c r="I159" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J159" t="s">
+        <v>339</v>
+      </c>
+      <c r="K159" t="s">
         <v>619</v>
-      </c>
-      <c r="K159" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -8879,25 +8879,25 @@
         <v>14</v>
       </c>
       <c r="E160" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F160" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G160" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H160" t="s">
         <v>618</v>
       </c>
       <c r="I160" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J160" t="s">
+        <v>339</v>
+      </c>
+      <c r="K160" t="s">
         <v>619</v>
-      </c>
-      <c r="K160" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -8914,25 +8914,25 @@
         <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F161" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G161" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H161" t="s">
         <v>618</v>
       </c>
       <c r="I161" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J161" t="s">
+        <v>339</v>
+      </c>
+      <c r="K161" t="s">
         <v>619</v>
-      </c>
-      <c r="K161" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -8949,25 +8949,25 @@
         <v>14</v>
       </c>
       <c r="E162" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F162" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G162" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H162" t="s">
         <v>639</v>
       </c>
       <c r="I162" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J162" t="s">
+        <v>339</v>
+      </c>
+      <c r="K162" t="s">
         <v>640</v>
-      </c>
-      <c r="K162" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -8984,25 +8984,25 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F163" t="s">
         <v>644</v>
       </c>
       <c r="G163" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H163" t="s">
         <v>642</v>
       </c>
       <c r="I163" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J163" t="s">
+        <v>339</v>
+      </c>
+      <c r="K163" t="s">
         <v>645</v>
-      </c>
-      <c r="K163" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -9019,25 +9019,25 @@
         <v>14</v>
       </c>
       <c r="E164" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F164" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G164" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H164" t="s">
         <v>649</v>
       </c>
       <c r="I164" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J164" t="s">
+        <v>339</v>
+      </c>
+      <c r="K164" t="s">
         <v>650</v>
-      </c>
-      <c r="K164" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -9054,25 +9054,25 @@
         <v>14</v>
       </c>
       <c r="E165" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F165" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G165" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H165" t="s">
         <v>649</v>
       </c>
       <c r="I165" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J165" t="s">
+        <v>339</v>
+      </c>
+      <c r="K165" t="s">
         <v>650</v>
-      </c>
-      <c r="K165" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -9089,25 +9089,25 @@
         <v>14</v>
       </c>
       <c r="E166" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F166" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G166" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H166" t="s">
         <v>649</v>
       </c>
       <c r="I166" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J166" t="s">
+        <v>339</v>
+      </c>
+      <c r="K166" t="s">
         <v>650</v>
-      </c>
-      <c r="K166" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -9124,25 +9124,25 @@
         <v>14</v>
       </c>
       <c r="E167" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F167" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G167" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H167" t="s">
         <v>649</v>
       </c>
       <c r="I167" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J167" t="s">
+        <v>339</v>
+      </c>
+      <c r="K167" t="s">
         <v>650</v>
-      </c>
-      <c r="K167" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -9159,25 +9159,25 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F168" t="s">
         <v>663</v>
       </c>
       <c r="G168" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H168" t="s">
         <v>649</v>
       </c>
       <c r="I168" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J168" t="s">
+        <v>339</v>
+      </c>
+      <c r="K168" t="s">
         <v>650</v>
-      </c>
-      <c r="K168" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -9191,25 +9191,25 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F169" t="s">
         <v>663</v>
       </c>
       <c r="G169" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H169" t="s">
         <v>649</v>
       </c>
       <c r="I169" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J169" t="s">
+        <v>339</v>
+      </c>
+      <c r="K169" t="s">
         <v>650</v>
-      </c>
-      <c r="K169" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -9226,25 +9226,25 @@
         <v>14</v>
       </c>
       <c r="E170" t="s">
-        <v>337</v>
+        <v>564</v>
       </c>
       <c r="F170" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G170" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H170" t="s">
         <v>649</v>
       </c>
       <c r="I170" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J170" t="s">
+        <v>339</v>
+      </c>
+      <c r="K170" t="s">
         <v>650</v>
-      </c>
-      <c r="K170" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -9261,19 +9261,19 @@
         <v>14</v>
       </c>
       <c r="E171" t="s">
+        <v>672</v>
+      </c>
+      <c r="F171" t="s">
         <v>337</v>
       </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
+        <v>673</v>
+      </c>
+      <c r="I171" t="s">
         <v>338</v>
       </c>
-      <c r="G171" t="s">
+      <c r="J171" t="s">
         <v>339</v>
-      </c>
-      <c r="I171" t="s">
-        <v>672</v>
-      </c>
-      <c r="K171" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -9290,19 +9290,19 @@
         <v>14</v>
       </c>
       <c r="E172" t="s">
-        <v>233</v>
+        <v>672</v>
       </c>
       <c r="F172" t="s">
         <v>243</v>
       </c>
       <c r="G172" t="s">
+        <v>673</v>
+      </c>
+      <c r="I172" t="s">
         <v>244</v>
       </c>
-      <c r="I172" t="s">
-        <v>672</v>
-      </c>
-      <c r="K172" t="s">
-        <v>673</v>
+      <c r="J172" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -9319,19 +9319,19 @@
         <v>14</v>
       </c>
       <c r="E173" t="s">
+        <v>672</v>
+      </c>
+      <c r="F173" t="s">
         <v>337</v>
       </c>
-      <c r="F173" t="s">
+      <c r="G173" t="s">
+        <v>673</v>
+      </c>
+      <c r="I173" t="s">
         <v>338</v>
       </c>
-      <c r="G173" t="s">
+      <c r="J173" t="s">
         <v>339</v>
-      </c>
-      <c r="I173" t="s">
-        <v>672</v>
-      </c>
-      <c r="K173" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -9348,19 +9348,19 @@
         <v>14</v>
       </c>
       <c r="E174" t="s">
+        <v>672</v>
+      </c>
+      <c r="F174" t="s">
         <v>337</v>
       </c>
-      <c r="F174" t="s">
+      <c r="G174" t="s">
+        <v>673</v>
+      </c>
+      <c r="I174" t="s">
         <v>338</v>
       </c>
-      <c r="G174" t="s">
+      <c r="J174" t="s">
         <v>339</v>
-      </c>
-      <c r="I174" t="s">
-        <v>672</v>
-      </c>
-      <c r="K174" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -9377,19 +9377,19 @@
         <v>14</v>
       </c>
       <c r="E175" t="s">
+        <v>672</v>
+      </c>
+      <c r="F175" t="s">
         <v>337</v>
       </c>
-      <c r="F175" t="s">
+      <c r="G175" t="s">
+        <v>673</v>
+      </c>
+      <c r="I175" t="s">
         <v>338</v>
       </c>
-      <c r="G175" t="s">
+      <c r="J175" t="s">
         <v>339</v>
-      </c>
-      <c r="I175" t="s">
-        <v>672</v>
-      </c>
-      <c r="K175" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -9403,19 +9403,19 @@
         <v>14</v>
       </c>
       <c r="E176" t="s">
+        <v>672</v>
+      </c>
+      <c r="F176" t="s">
         <v>337</v>
       </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
+        <v>673</v>
+      </c>
+      <c r="I176" t="s">
         <v>338</v>
       </c>
-      <c r="G176" t="s">
+      <c r="J176" t="s">
         <v>339</v>
-      </c>
-      <c r="I176" t="s">
-        <v>672</v>
-      </c>
-      <c r="K176" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -9432,19 +9432,19 @@
         <v>14</v>
       </c>
       <c r="E177" t="s">
+        <v>691</v>
+      </c>
+      <c r="F177" t="s">
         <v>337</v>
       </c>
-      <c r="F177" t="s">
+      <c r="G177" t="s">
+        <v>692</v>
+      </c>
+      <c r="I177" t="s">
         <v>338</v>
       </c>
-      <c r="G177" t="s">
+      <c r="J177" t="s">
         <v>339</v>
-      </c>
-      <c r="I177" t="s">
-        <v>691</v>
-      </c>
-      <c r="K177" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -9461,19 +9461,19 @@
         <v>14</v>
       </c>
       <c r="E178" t="s">
+        <v>691</v>
+      </c>
+      <c r="F178" t="s">
         <v>337</v>
       </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
+        <v>692</v>
+      </c>
+      <c r="I178" t="s">
         <v>338</v>
       </c>
-      <c r="G178" t="s">
+      <c r="J178" t="s">
         <v>339</v>
-      </c>
-      <c r="I178" t="s">
-        <v>691</v>
-      </c>
-      <c r="K178" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -9490,19 +9490,19 @@
         <v>14</v>
       </c>
       <c r="E179" t="s">
+        <v>691</v>
+      </c>
+      <c r="F179" t="s">
         <v>337</v>
       </c>
-      <c r="F179" t="s">
+      <c r="G179" t="s">
+        <v>692</v>
+      </c>
+      <c r="I179" t="s">
         <v>338</v>
       </c>
-      <c r="G179" t="s">
+      <c r="J179" t="s">
         <v>339</v>
-      </c>
-      <c r="I179" t="s">
-        <v>691</v>
-      </c>
-      <c r="K179" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -9519,19 +9519,19 @@
         <v>14</v>
       </c>
       <c r="E180" t="s">
+        <v>691</v>
+      </c>
+      <c r="F180" t="s">
         <v>337</v>
       </c>
-      <c r="F180" t="s">
+      <c r="G180" t="s">
+        <v>692</v>
+      </c>
+      <c r="I180" t="s">
         <v>338</v>
       </c>
-      <c r="G180" t="s">
+      <c r="J180" t="s">
         <v>339</v>
-      </c>
-      <c r="I180" t="s">
-        <v>691</v>
-      </c>
-      <c r="K180" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -9548,22 +9548,22 @@
         <v>14</v>
       </c>
       <c r="E181" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F181" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G181" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H181" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I181" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J181" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K181" t="s">
         <v>710</v>
@@ -9583,22 +9583,22 @@
         <v>14</v>
       </c>
       <c r="E182" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F182" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G182" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H182" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I182" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J182" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K182" t="s">
         <v>710</v>
@@ -9618,22 +9618,22 @@
         <v>14</v>
       </c>
       <c r="E183" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F183" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G183" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H183" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I183" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J183" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K183" t="s">
         <v>710</v>
@@ -9653,22 +9653,22 @@
         <v>14</v>
       </c>
       <c r="E184" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F184" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G184" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H184" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I184" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J184" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K184" t="s">
         <v>710</v>
@@ -9688,22 +9688,22 @@
         <v>14</v>
       </c>
       <c r="E185" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F185" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G185" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H185" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I185" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J185" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K185" t="s">
         <v>710</v>
@@ -9723,22 +9723,22 @@
         <v>14</v>
       </c>
       <c r="E186" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F186" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G186" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H186" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I186" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J186" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K186" t="s">
         <v>710</v>
@@ -9758,22 +9758,22 @@
         <v>14</v>
       </c>
       <c r="E187" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F187" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G187" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H187" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I187" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J187" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K187" t="s">
         <v>710</v>
@@ -9793,22 +9793,22 @@
         <v>14</v>
       </c>
       <c r="E188" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F188" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G188" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H188" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I188" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J188" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K188" t="s">
         <v>710</v>
@@ -9828,22 +9828,22 @@
         <v>14</v>
       </c>
       <c r="E189" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F189" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G189" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H189" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I189" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J189" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K189" t="s">
         <v>710</v>
@@ -9863,22 +9863,22 @@
         <v>14</v>
       </c>
       <c r="E190" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F190" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G190" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H190" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I190" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J190" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K190" t="s">
         <v>710</v>
@@ -9898,22 +9898,22 @@
         <v>14</v>
       </c>
       <c r="E191" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F191" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G191" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H191" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I191" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J191" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K191" t="s">
         <v>710</v>
@@ -9930,22 +9930,22 @@
         <v>14</v>
       </c>
       <c r="E192" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F192" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G192" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H192" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I192" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J192" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K192" t="s">
         <v>710</v>
@@ -9965,22 +9965,22 @@
         <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F193" t="s">
         <v>746</v>
       </c>
       <c r="G193" t="s">
+        <v>707</v>
+      </c>
+      <c r="H193" t="s">
+        <v>708</v>
+      </c>
+      <c r="I193" t="s">
         <v>576</v>
       </c>
-      <c r="H193" t="s">
-        <v>707</v>
-      </c>
-      <c r="I193" t="s">
-        <v>708</v>
-      </c>
       <c r="J193" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K193" t="s">
         <v>710</v>
@@ -10000,22 +10000,22 @@
         <v>14</v>
       </c>
       <c r="E194" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F194" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G194" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H194" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I194" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J194" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K194" t="s">
         <v>710</v>
@@ -10035,22 +10035,22 @@
         <v>14</v>
       </c>
       <c r="E195" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F195" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G195" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H195" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I195" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J195" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K195" t="s">
         <v>710</v>
@@ -10070,22 +10070,22 @@
         <v>14</v>
       </c>
       <c r="E196" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F196" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G196" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H196" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I196" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J196" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K196" t="s">
         <v>710</v>
@@ -10105,22 +10105,22 @@
         <v>14</v>
       </c>
       <c r="E197" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F197" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G197" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H197" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I197" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J197" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K197" t="s">
         <v>710</v>
@@ -10140,22 +10140,22 @@
         <v>14</v>
       </c>
       <c r="E198" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F198" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G198" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H198" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I198" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J198" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K198" t="s">
         <v>710</v>
@@ -10175,25 +10175,25 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F199" t="s">
         <v>765</v>
       </c>
       <c r="G199" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H199" t="s">
         <v>766</v>
       </c>
       <c r="I199" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J199" t="s">
+        <v>339</v>
+      </c>
+      <c r="K199" t="s">
         <v>767</v>
-      </c>
-      <c r="K199" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -10210,25 +10210,25 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F200" t="s">
         <v>765</v>
       </c>
       <c r="G200" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H200" t="s">
         <v>766</v>
       </c>
       <c r="I200" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J200" t="s">
+        <v>339</v>
+      </c>
+      <c r="K200" t="s">
         <v>767</v>
-      </c>
-      <c r="K200" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -10245,25 +10245,25 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F201" t="s">
         <v>765</v>
       </c>
       <c r="G201" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H201" t="s">
         <v>766</v>
       </c>
       <c r="I201" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J201" t="s">
+        <v>339</v>
+      </c>
+      <c r="K201" t="s">
         <v>767</v>
-      </c>
-      <c r="K201" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -10277,25 +10277,25 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F202" t="s">
         <v>765</v>
       </c>
       <c r="G202" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H202" t="s">
         <v>766</v>
       </c>
       <c r="I202" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J202" t="s">
+        <v>339</v>
+      </c>
+      <c r="K202" t="s">
         <v>767</v>
-      </c>
-      <c r="K202" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -10312,25 +10312,25 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F203" t="s">
         <v>746</v>
       </c>
       <c r="G203" t="s">
-        <v>576</v>
+        <v>707</v>
       </c>
       <c r="H203" t="s">
         <v>766</v>
       </c>
       <c r="I203" t="s">
-        <v>708</v>
+        <v>576</v>
       </c>
       <c r="J203" t="s">
+        <v>339</v>
+      </c>
+      <c r="K203" t="s">
         <v>767</v>
-      </c>
-      <c r="K203" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10344,25 +10344,25 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F204" t="s">
         <v>765</v>
       </c>
       <c r="G204" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H204" t="s">
         <v>766</v>
       </c>
       <c r="I204" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J204" t="s">
+        <v>339</v>
+      </c>
+      <c r="K204" t="s">
         <v>767</v>
-      </c>
-      <c r="K204" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -10379,25 +10379,25 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F205" t="s">
         <v>784</v>
       </c>
       <c r="G205" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H205" t="s">
         <v>785</v>
       </c>
       <c r="I205" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J205" t="s">
+        <v>339</v>
+      </c>
+      <c r="K205" t="s">
         <v>786</v>
-      </c>
-      <c r="K205" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -10414,25 +10414,25 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F206" t="s">
         <v>784</v>
       </c>
       <c r="G206" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H206" t="s">
         <v>785</v>
       </c>
       <c r="I206" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J206" t="s">
+        <v>339</v>
+      </c>
+      <c r="K206" t="s">
         <v>786</v>
-      </c>
-      <c r="K206" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -10446,25 +10446,25 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F207" t="s">
         <v>784</v>
       </c>
       <c r="G207" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H207" t="s">
         <v>785</v>
       </c>
       <c r="I207" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J207" t="s">
+        <v>339</v>
+      </c>
+      <c r="K207" t="s">
         <v>786</v>
-      </c>
-      <c r="K207" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -10481,25 +10481,25 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F208" t="s">
         <v>746</v>
       </c>
       <c r="G208" t="s">
-        <v>576</v>
+        <v>707</v>
       </c>
       <c r="H208" t="s">
         <v>785</v>
       </c>
       <c r="I208" t="s">
-        <v>708</v>
+        <v>576</v>
       </c>
       <c r="J208" t="s">
+        <v>339</v>
+      </c>
+      <c r="K208" t="s">
         <v>786</v>
-      </c>
-      <c r="K208" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10516,25 +10516,25 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
-        <v>337</v>
+        <v>705</v>
       </c>
       <c r="F209" t="s">
         <v>784</v>
       </c>
       <c r="G209" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H209" t="s">
         <v>785</v>
       </c>
       <c r="I209" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J209" t="s">
+        <v>339</v>
+      </c>
+      <c r="K209" t="s">
         <v>786</v>
-      </c>
-      <c r="K209" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -10551,22 +10551,22 @@
         <v>14</v>
       </c>
       <c r="E210" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F210" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G210" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H210" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I210" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J210" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K210" t="s">
         <v>806</v>
@@ -10583,22 +10583,22 @@
         <v>14</v>
       </c>
       <c r="E211" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F211" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G211" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H211" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I211" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J211" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K211" t="s">
         <v>806</v>
@@ -10618,22 +10618,22 @@
         <v>14</v>
       </c>
       <c r="E212" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F212" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G212" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H212" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I212" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J212" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K212" t="s">
         <v>806</v>
@@ -10650,22 +10650,22 @@
         <v>14</v>
       </c>
       <c r="E213" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F213" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G213" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H213" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I213" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J213" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K213" t="s">
         <v>806</v>
@@ -10685,22 +10685,22 @@
         <v>14</v>
       </c>
       <c r="E214" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F214" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G214" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H214" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I214" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J214" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K214" t="s">
         <v>806</v>
@@ -10720,22 +10720,22 @@
         <v>14</v>
       </c>
       <c r="E215" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F215" t="s">
         <v>765</v>
       </c>
       <c r="G215" t="s">
-        <v>706</v>
+        <v>803</v>
       </c>
       <c r="H215" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I215" t="s">
-        <v>804</v>
+        <v>709</v>
       </c>
       <c r="J215" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K215" t="s">
         <v>806</v>
@@ -10755,22 +10755,22 @@
         <v>14</v>
       </c>
       <c r="E216" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F216" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G216" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H216" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I216" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J216" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K216" t="s">
         <v>806</v>
@@ -10790,22 +10790,22 @@
         <v>14</v>
       </c>
       <c r="E217" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F217" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G217" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H217" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I217" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J217" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K217" t="s">
         <v>806</v>
@@ -10822,22 +10822,22 @@
         <v>14</v>
       </c>
       <c r="E218" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F218" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G218" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H218" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I218" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J218" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K218" t="s">
         <v>806</v>
@@ -10854,22 +10854,22 @@
         <v>14</v>
       </c>
       <c r="E219" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F219" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G219" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H219" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I219" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J219" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K219" t="s">
         <v>806</v>
@@ -10889,22 +10889,22 @@
         <v>14</v>
       </c>
       <c r="E220" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F220" t="s">
         <v>663</v>
       </c>
       <c r="G220" t="s">
-        <v>565</v>
+        <v>803</v>
       </c>
       <c r="H220" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I220" t="s">
-        <v>804</v>
+        <v>568</v>
       </c>
       <c r="J220" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K220" t="s">
         <v>806</v>
@@ -10924,22 +10924,22 @@
         <v>14</v>
       </c>
       <c r="E221" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F221" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G221" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H221" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I221" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J221" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K221" t="s">
         <v>806</v>
@@ -10959,22 +10959,22 @@
         <v>14</v>
       </c>
       <c r="E222" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F222" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G222" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H222" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I222" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J222" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K222" t="s">
         <v>806</v>
@@ -10991,22 +10991,22 @@
         <v>14</v>
       </c>
       <c r="E223" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F223" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G223" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H223" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I223" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J223" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K223" t="s">
         <v>806</v>
@@ -11026,22 +11026,22 @@
         <v>14</v>
       </c>
       <c r="E224" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F224" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G224" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H224" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I224" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J224" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K224" t="s">
         <v>806</v>
@@ -11061,22 +11061,22 @@
         <v>14</v>
       </c>
       <c r="E225" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F225" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G225" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H225" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I225" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J225" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K225" t="s">
         <v>806</v>
@@ -11096,22 +11096,22 @@
         <v>14</v>
       </c>
       <c r="E226" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F226" t="s">
         <v>575</v>
       </c>
       <c r="G226" t="s">
+        <v>803</v>
+      </c>
+      <c r="H226" t="s">
+        <v>804</v>
+      </c>
+      <c r="I226" t="s">
         <v>576</v>
       </c>
-      <c r="H226" t="s">
-        <v>803</v>
-      </c>
-      <c r="I226" t="s">
-        <v>804</v>
-      </c>
       <c r="J226" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K226" t="s">
         <v>806</v>
@@ -11131,22 +11131,22 @@
         <v>14</v>
       </c>
       <c r="E227" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F227" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G227" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H227" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I227" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J227" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K227" t="s">
         <v>806</v>
@@ -11166,22 +11166,22 @@
         <v>14</v>
       </c>
       <c r="E228" t="s">
+        <v>801</v>
+      </c>
+      <c r="F228" t="s">
         <v>337</v>
       </c>
-      <c r="F228" t="s">
+      <c r="G228" t="s">
+        <v>803</v>
+      </c>
+      <c r="H228" t="s">
+        <v>804</v>
+      </c>
+      <c r="I228" t="s">
         <v>338</v>
       </c>
-      <c r="G228" t="s">
+      <c r="J228" t="s">
         <v>339</v>
-      </c>
-      <c r="H228" t="s">
-        <v>803</v>
-      </c>
-      <c r="I228" t="s">
-        <v>804</v>
-      </c>
-      <c r="J228" t="s">
-        <v>805</v>
       </c>
       <c r="K228" t="s">
         <v>806</v>
@@ -11201,25 +11201,25 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F229" t="s">
         <v>859</v>
       </c>
       <c r="G229" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H229" t="s">
         <v>860</v>
       </c>
       <c r="I229" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J229" t="s">
+        <v>339</v>
+      </c>
+      <c r="K229" t="s">
         <v>861</v>
-      </c>
-      <c r="K229" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -11236,25 +11236,25 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F230" t="s">
         <v>859</v>
       </c>
       <c r="G230" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H230" t="s">
         <v>860</v>
       </c>
       <c r="I230" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J230" t="s">
+        <v>339</v>
+      </c>
+      <c r="K230" t="s">
         <v>861</v>
-      </c>
-      <c r="K230" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -11271,25 +11271,25 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F231" t="s">
         <v>623</v>
       </c>
       <c r="G231" t="s">
-        <v>565</v>
+        <v>803</v>
       </c>
       <c r="H231" t="s">
         <v>860</v>
       </c>
       <c r="I231" t="s">
-        <v>804</v>
+        <v>568</v>
       </c>
       <c r="J231" t="s">
+        <v>339</v>
+      </c>
+      <c r="K231" t="s">
         <v>861</v>
-      </c>
-      <c r="K231" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11306,25 +11306,25 @@
         <v>14</v>
       </c>
       <c r="E232" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F232" t="s">
         <v>663</v>
       </c>
       <c r="G232" t="s">
-        <v>565</v>
+        <v>803</v>
       </c>
       <c r="H232" t="s">
         <v>860</v>
       </c>
       <c r="I232" t="s">
-        <v>804</v>
+        <v>568</v>
       </c>
       <c r="J232" t="s">
+        <v>339</v>
+      </c>
+      <c r="K232" t="s">
         <v>861</v>
-      </c>
-      <c r="K232" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11341,25 +11341,25 @@
         <v>14</v>
       </c>
       <c r="E233" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F233" t="s">
         <v>859</v>
       </c>
       <c r="G233" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H233" t="s">
         <v>860</v>
       </c>
       <c r="I233" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J233" t="s">
+        <v>339</v>
+      </c>
+      <c r="K233" t="s">
         <v>861</v>
-      </c>
-      <c r="K233" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -11376,25 +11376,25 @@
         <v>14</v>
       </c>
       <c r="E234" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F234" t="s">
         <v>859</v>
       </c>
       <c r="G234" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H234" t="s">
         <v>860</v>
       </c>
       <c r="I234" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J234" t="s">
+        <v>339</v>
+      </c>
+      <c r="K234" t="s">
         <v>861</v>
-      </c>
-      <c r="K234" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -11411,25 +11411,25 @@
         <v>14</v>
       </c>
       <c r="E235" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F235" t="s">
         <v>859</v>
       </c>
       <c r="G235" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H235" t="s">
         <v>860</v>
       </c>
       <c r="I235" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J235" t="s">
+        <v>339</v>
+      </c>
+      <c r="K235" t="s">
         <v>861</v>
-      </c>
-      <c r="K235" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -11446,25 +11446,25 @@
         <v>14</v>
       </c>
       <c r="E236" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F236" t="s">
         <v>859</v>
       </c>
       <c r="G236" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H236" t="s">
         <v>860</v>
       </c>
       <c r="I236" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J236" t="s">
+        <v>339</v>
+      </c>
+      <c r="K236" t="s">
         <v>861</v>
-      </c>
-      <c r="K236" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -11481,25 +11481,25 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F237" t="s">
         <v>859</v>
       </c>
       <c r="G237" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H237" t="s">
         <v>860</v>
       </c>
       <c r="I237" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J237" t="s">
+        <v>339</v>
+      </c>
+      <c r="K237" t="s">
         <v>861</v>
-      </c>
-      <c r="K237" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -11516,25 +11516,25 @@
         <v>14</v>
       </c>
       <c r="E238" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F238" t="s">
         <v>859</v>
       </c>
       <c r="G238" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H238" t="s">
         <v>860</v>
       </c>
       <c r="I238" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J238" t="s">
+        <v>339</v>
+      </c>
+      <c r="K238" t="s">
         <v>861</v>
-      </c>
-      <c r="K238" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -11551,25 +11551,25 @@
         <v>14</v>
       </c>
       <c r="E239" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F239" t="s">
         <v>892</v>
       </c>
       <c r="G239" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H239" t="s">
         <v>893</v>
       </c>
       <c r="I239" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J239" t="s">
+        <v>339</v>
+      </c>
+      <c r="K239" t="s">
         <v>894</v>
-      </c>
-      <c r="K239" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -11586,25 +11586,25 @@
         <v>14</v>
       </c>
       <c r="E240" t="s">
+        <v>898</v>
+      </c>
+      <c r="F240" t="s">
         <v>337</v>
       </c>
-      <c r="F240" t="s">
+      <c r="G240" t="s">
+        <v>899</v>
+      </c>
+      <c r="H240" t="s">
+        <v>899</v>
+      </c>
+      <c r="I240" t="s">
         <v>338</v>
       </c>
-      <c r="G240" t="s">
+      <c r="J240" t="s">
         <v>339</v>
       </c>
-      <c r="H240" t="s">
-        <v>898</v>
-      </c>
-      <c r="I240" t="s">
-        <v>899</v>
-      </c>
-      <c r="J240" t="s">
+      <c r="K240" t="s">
         <v>900</v>
-      </c>
-      <c r="K240" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -11621,25 +11621,25 @@
         <v>14</v>
       </c>
       <c r="E241" t="s">
+        <v>898</v>
+      </c>
+      <c r="F241" t="s">
         <v>337</v>
       </c>
-      <c r="F241" t="s">
+      <c r="G241" t="s">
+        <v>899</v>
+      </c>
+      <c r="H241" t="s">
+        <v>899</v>
+      </c>
+      <c r="I241" t="s">
         <v>338</v>
       </c>
-      <c r="G241" t="s">
+      <c r="J241" t="s">
         <v>339</v>
       </c>
-      <c r="H241" t="s">
-        <v>898</v>
-      </c>
-      <c r="I241" t="s">
-        <v>899</v>
-      </c>
-      <c r="J241" t="s">
+      <c r="K241" t="s">
         <v>900</v>
-      </c>
-      <c r="K241" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -11656,25 +11656,25 @@
         <v>14</v>
       </c>
       <c r="E242" t="s">
+        <v>898</v>
+      </c>
+      <c r="F242" t="s">
         <v>337</v>
       </c>
-      <c r="F242" t="s">
+      <c r="G242" t="s">
+        <v>899</v>
+      </c>
+      <c r="H242" t="s">
+        <v>899</v>
+      </c>
+      <c r="I242" t="s">
         <v>338</v>
       </c>
-      <c r="G242" t="s">
+      <c r="J242" t="s">
         <v>339</v>
       </c>
-      <c r="H242" t="s">
-        <v>898</v>
-      </c>
-      <c r="I242" t="s">
-        <v>899</v>
-      </c>
-      <c r="J242" t="s">
+      <c r="K242" t="s">
         <v>900</v>
-      </c>
-      <c r="K242" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -11691,25 +11691,25 @@
         <v>14</v>
       </c>
       <c r="E243" t="s">
+        <v>898</v>
+      </c>
+      <c r="F243" t="s">
         <v>337</v>
       </c>
-      <c r="F243" t="s">
+      <c r="G243" t="s">
+        <v>899</v>
+      </c>
+      <c r="H243" t="s">
+        <v>899</v>
+      </c>
+      <c r="I243" t="s">
         <v>338</v>
       </c>
-      <c r="G243" t="s">
+      <c r="J243" t="s">
         <v>339</v>
       </c>
-      <c r="H243" t="s">
-        <v>898</v>
-      </c>
-      <c r="I243" t="s">
-        <v>899</v>
-      </c>
-      <c r="J243" t="s">
+      <c r="K243" t="s">
         <v>900</v>
-      </c>
-      <c r="K243" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -11726,25 +11726,25 @@
         <v>14</v>
       </c>
       <c r="E244" t="s">
+        <v>898</v>
+      </c>
+      <c r="F244" t="s">
         <v>337</v>
       </c>
-      <c r="F244" t="s">
+      <c r="G244" t="s">
+        <v>899</v>
+      </c>
+      <c r="H244" t="s">
+        <v>899</v>
+      </c>
+      <c r="I244" t="s">
         <v>338</v>
       </c>
-      <c r="G244" t="s">
+      <c r="J244" t="s">
         <v>339</v>
       </c>
-      <c r="H244" t="s">
-        <v>898</v>
-      </c>
-      <c r="I244" t="s">
-        <v>899</v>
-      </c>
-      <c r="J244" t="s">
+      <c r="K244" t="s">
         <v>900</v>
-      </c>
-      <c r="K244" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -11761,25 +11761,25 @@
         <v>14</v>
       </c>
       <c r="E245" t="s">
+        <v>898</v>
+      </c>
+      <c r="F245" t="s">
         <v>337</v>
       </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
+        <v>899</v>
+      </c>
+      <c r="H245" t="s">
+        <v>899</v>
+      </c>
+      <c r="I245" t="s">
         <v>338</v>
       </c>
-      <c r="G245" t="s">
+      <c r="J245" t="s">
         <v>339</v>
       </c>
-      <c r="H245" t="s">
-        <v>898</v>
-      </c>
-      <c r="I245" t="s">
-        <v>899</v>
-      </c>
-      <c r="J245" t="s">
+      <c r="K245" t="s">
         <v>900</v>
-      </c>
-      <c r="K245" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -11793,25 +11793,25 @@
         <v>14</v>
       </c>
       <c r="E246" t="s">
-        <v>337</v>
+        <v>898</v>
       </c>
       <c r="F246" t="s">
         <v>918</v>
       </c>
       <c r="G246" t="s">
-        <v>534</v>
+        <v>899</v>
       </c>
       <c r="H246" t="s">
         <v>919</v>
       </c>
       <c r="I246" t="s">
-        <v>899</v>
+        <v>534</v>
       </c>
       <c r="J246" t="s">
+        <v>339</v>
+      </c>
+      <c r="K246" t="s">
         <v>920</v>
-      </c>
-      <c r="K246" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11828,19 +11828,19 @@
         <v>14</v>
       </c>
       <c r="E247" t="s">
+        <v>924</v>
+      </c>
+      <c r="F247" t="s">
         <v>196</v>
       </c>
-      <c r="F247" t="s">
+      <c r="G247" t="s">
+        <v>925</v>
+      </c>
+      <c r="I247" t="s">
         <v>197</v>
       </c>
-      <c r="G247" t="s">
+      <c r="J247" t="s">
         <v>198</v>
-      </c>
-      <c r="I247" t="s">
-        <v>924</v>
-      </c>
-      <c r="K247" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -11857,19 +11857,19 @@
         <v>14</v>
       </c>
       <c r="E248" t="s">
+        <v>924</v>
+      </c>
+      <c r="F248" t="s">
         <v>196</v>
       </c>
-      <c r="F248" t="s">
+      <c r="G248" t="s">
+        <v>925</v>
+      </c>
+      <c r="I248" t="s">
         <v>197</v>
       </c>
-      <c r="G248" t="s">
+      <c r="J248" t="s">
         <v>198</v>
-      </c>
-      <c r="I248" t="s">
-        <v>924</v>
-      </c>
-      <c r="K248" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -11886,19 +11886,19 @@
         <v>14</v>
       </c>
       <c r="E249" t="s">
-        <v>196</v>
+        <v>924</v>
       </c>
       <c r="F249" t="s">
         <v>932</v>
       </c>
       <c r="G249" t="s">
+        <v>925</v>
+      </c>
+      <c r="I249" t="s">
         <v>933</v>
       </c>
-      <c r="I249" t="s">
-        <v>924</v>
-      </c>
-      <c r="K249" t="s">
-        <v>925</v>
+      <c r="J249" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -11915,19 +11915,19 @@
         <v>14</v>
       </c>
       <c r="E250" t="s">
+        <v>924</v>
+      </c>
+      <c r="F250" t="s">
         <v>196</v>
       </c>
-      <c r="F250" t="s">
+      <c r="G250" t="s">
+        <v>925</v>
+      </c>
+      <c r="I250" t="s">
         <v>197</v>
       </c>
-      <c r="G250" t="s">
+      <c r="J250" t="s">
         <v>198</v>
-      </c>
-      <c r="I250" t="s">
-        <v>924</v>
-      </c>
-      <c r="K250" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -11941,19 +11941,19 @@
         <v>14</v>
       </c>
       <c r="E251" t="s">
+        <v>924</v>
+      </c>
+      <c r="F251" t="s">
         <v>196</v>
       </c>
-      <c r="F251" t="s">
+      <c r="G251" t="s">
+        <v>925</v>
+      </c>
+      <c r="I251" t="s">
         <v>197</v>
       </c>
-      <c r="G251" t="s">
+      <c r="J251" t="s">
         <v>198</v>
-      </c>
-      <c r="I251" t="s">
-        <v>924</v>
-      </c>
-      <c r="K251" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -11970,19 +11970,19 @@
         <v>14</v>
       </c>
       <c r="E252" t="s">
+        <v>924</v>
+      </c>
+      <c r="F252" t="s">
         <v>196</v>
       </c>
-      <c r="F252" t="s">
+      <c r="G252" t="s">
+        <v>925</v>
+      </c>
+      <c r="I252" t="s">
         <v>197</v>
       </c>
-      <c r="G252" t="s">
+      <c r="J252" t="s">
         <v>198</v>
-      </c>
-      <c r="I252" t="s">
-        <v>924</v>
-      </c>
-      <c r="K252" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -11996,19 +11996,19 @@
         <v>14</v>
       </c>
       <c r="E253" t="s">
-        <v>337</v>
+        <v>944</v>
       </c>
       <c r="F253" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="G253" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="I253" t="s">
-        <v>946</v>
-      </c>
-      <c r="K253" t="s">
         <v>947</v>
+      </c>
+      <c r="J253" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="254" spans="1:11">
@@ -12025,19 +12025,19 @@
         <v>14</v>
       </c>
       <c r="E254" t="s">
-        <v>188</v>
+        <v>944</v>
       </c>
       <c r="F254" t="s">
         <v>454</v>
       </c>
       <c r="G254" t="s">
+        <v>946</v>
+      </c>
+      <c r="I254" t="s">
         <v>455</v>
       </c>
-      <c r="I254" t="s">
-        <v>946</v>
-      </c>
-      <c r="K254" t="s">
-        <v>947</v>
+      <c r="J254" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -12054,19 +12054,19 @@
         <v>14</v>
       </c>
       <c r="E255" t="s">
-        <v>188</v>
+        <v>944</v>
       </c>
       <c r="F255" t="s">
         <v>954</v>
       </c>
       <c r="G255" t="s">
+        <v>946</v>
+      </c>
+      <c r="I255" t="s">
         <v>955</v>
       </c>
-      <c r="I255" t="s">
-        <v>946</v>
-      </c>
-      <c r="K255" t="s">
-        <v>947</v>
+      <c r="J255" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -12083,22 +12083,22 @@
         <v>14</v>
       </c>
       <c r="E256" t="s">
-        <v>188</v>
+        <v>944</v>
       </c>
       <c r="F256" t="s">
         <v>954</v>
       </c>
       <c r="G256" t="s">
+        <v>946</v>
+      </c>
+      <c r="I256" t="s">
         <v>955</v>
       </c>
-      <c r="I256" t="s">
-        <v>946</v>
-      </c>
-      <c r="K256" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="257" spans="1:11">
+      <c r="J256" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10">
       <c r="A257" t="s">
         <v>959</v>
       </c>
@@ -12112,22 +12112,22 @@
         <v>14</v>
       </c>
       <c r="E257" t="s">
-        <v>188</v>
+        <v>944</v>
       </c>
       <c r="F257" t="s">
         <v>954</v>
       </c>
       <c r="G257" t="s">
+        <v>946</v>
+      </c>
+      <c r="I257" t="s">
         <v>955</v>
       </c>
-      <c r="I257" t="s">
-        <v>946</v>
-      </c>
-      <c r="K257" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="258" spans="1:11">
+      <c r="J257" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10">
       <c r="A258" t="s">
         <v>962</v>
       </c>
@@ -12141,22 +12141,22 @@
         <v>14</v>
       </c>
       <c r="E258" t="s">
-        <v>337</v>
+        <v>944</v>
       </c>
       <c r="F258" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G258" t="s">
-        <v>706</v>
+        <v>946</v>
       </c>
       <c r="I258" t="s">
-        <v>946</v>
-      </c>
-      <c r="K258" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="259" spans="1:11">
+        <v>709</v>
+      </c>
+      <c r="J258" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10">
       <c r="A259" t="s">
         <v>965</v>
       </c>
@@ -12170,22 +12170,22 @@
         <v>14</v>
       </c>
       <c r="E259" t="s">
-        <v>188</v>
+        <v>944</v>
       </c>
       <c r="F259" t="s">
         <v>954</v>
       </c>
       <c r="G259" t="s">
+        <v>946</v>
+      </c>
+      <c r="I259" t="s">
         <v>955</v>
       </c>
-      <c r="I259" t="s">
-        <v>946</v>
-      </c>
-      <c r="K259" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="260" spans="1:11">
+      <c r="J259" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10">
       <c r="A260" t="s">
         <v>967</v>
       </c>
@@ -12199,22 +12199,22 @@
         <v>14</v>
       </c>
       <c r="E260" t="s">
+        <v>944</v>
+      </c>
+      <c r="F260" t="s">
         <v>337</v>
       </c>
-      <c r="F260" t="s">
+      <c r="G260" t="s">
+        <v>946</v>
+      </c>
+      <c r="I260" t="s">
         <v>338</v>
       </c>
-      <c r="G260" t="s">
+      <c r="J260" t="s">
         <v>339</v>
       </c>
-      <c r="I260" t="s">
-        <v>946</v>
-      </c>
-      <c r="K260" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="261" spans="1:11">
+    </row>
+    <row r="261" spans="1:10">
       <c r="A261" t="s">
         <v>970</v>
       </c>
@@ -12228,22 +12228,22 @@
         <v>14</v>
       </c>
       <c r="E261" t="s">
-        <v>405</v>
+        <v>944</v>
       </c>
       <c r="F261" t="s">
         <v>973</v>
       </c>
       <c r="G261" t="s">
+        <v>946</v>
+      </c>
+      <c r="I261" t="s">
         <v>974</v>
       </c>
-      <c r="I261" t="s">
-        <v>946</v>
-      </c>
-      <c r="K261" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="262" spans="1:11">
+      <c r="J261" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10">
       <c r="A262" t="s">
         <v>975</v>
       </c>
@@ -12257,22 +12257,22 @@
         <v>14</v>
       </c>
       <c r="E262" t="s">
+        <v>944</v>
+      </c>
+      <c r="F262" t="s">
         <v>337</v>
       </c>
-      <c r="F262" t="s">
+      <c r="G262" t="s">
+        <v>946</v>
+      </c>
+      <c r="I262" t="s">
         <v>338</v>
       </c>
-      <c r="G262" t="s">
+      <c r="J262" t="s">
         <v>339</v>
       </c>
-      <c r="I262" t="s">
-        <v>946</v>
-      </c>
-      <c r="K262" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="263" spans="1:11">
+    </row>
+    <row r="263" spans="1:10">
       <c r="A263" t="s">
         <v>978</v>
       </c>
@@ -12286,22 +12286,22 @@
         <v>14</v>
       </c>
       <c r="E263" t="s">
-        <v>377</v>
+        <v>944</v>
       </c>
       <c r="F263" t="s">
         <v>981</v>
       </c>
       <c r="G263" t="s">
+        <v>946</v>
+      </c>
+      <c r="I263" t="s">
         <v>982</v>
       </c>
-      <c r="I263" t="s">
-        <v>946</v>
-      </c>
-      <c r="K263" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="264" spans="1:11">
+      <c r="J263" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10">
       <c r="A264" t="s">
         <v>983</v>
       </c>
@@ -12315,22 +12315,22 @@
         <v>14</v>
       </c>
       <c r="E264" t="s">
+        <v>944</v>
+      </c>
+      <c r="F264" t="s">
         <v>58</v>
       </c>
-      <c r="F264" t="s">
+      <c r="G264" t="s">
+        <v>946</v>
+      </c>
+      <c r="I264" t="s">
         <v>59</v>
       </c>
-      <c r="G264" t="s">
+      <c r="J264" t="s">
         <v>60</v>
       </c>
-      <c r="I264" t="s">
-        <v>946</v>
-      </c>
-      <c r="K264" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="265" spans="1:11">
+    </row>
+    <row r="265" spans="1:10">
       <c r="A265" t="s">
         <v>986</v>
       </c>
@@ -12344,22 +12344,22 @@
         <v>14</v>
       </c>
       <c r="E265" t="s">
-        <v>15</v>
+        <v>944</v>
       </c>
       <c r="F265" t="s">
         <v>16</v>
       </c>
       <c r="G265" t="s">
-        <v>17</v>
+        <v>946</v>
       </c>
       <c r="I265" t="s">
-        <v>946</v>
-      </c>
-      <c r="K265" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="266" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="J265" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10">
       <c r="A266" t="s">
         <v>989</v>
       </c>
@@ -12373,22 +12373,22 @@
         <v>14</v>
       </c>
       <c r="E266" t="s">
-        <v>233</v>
+        <v>944</v>
       </c>
       <c r="F266" t="s">
         <v>992</v>
       </c>
       <c r="G266" t="s">
+        <v>946</v>
+      </c>
+      <c r="I266" t="s">
         <v>993</v>
       </c>
-      <c r="I266" t="s">
-        <v>946</v>
-      </c>
-      <c r="K266" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="267" spans="1:11">
+      <c r="J266" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10">
       <c r="A267" t="s">
         <v>994</v>
       </c>
@@ -12402,22 +12402,22 @@
         <v>14</v>
       </c>
       <c r="E267" t="s">
-        <v>233</v>
+        <v>997</v>
       </c>
       <c r="F267" t="s">
         <v>243</v>
       </c>
       <c r="G267" t="s">
+        <v>998</v>
+      </c>
+      <c r="I267" t="s">
         <v>244</v>
       </c>
-      <c r="I267" t="s">
-        <v>997</v>
-      </c>
-      <c r="K267" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="268" spans="1:11">
+      <c r="J267" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10">
       <c r="A268" t="s">
         <v>999</v>
       </c>
@@ -12431,22 +12431,22 @@
         <v>14</v>
       </c>
       <c r="E268" t="s">
-        <v>377</v>
+        <v>1002</v>
       </c>
       <c r="F268" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G268" t="s">
-        <v>421</v>
+        <v>1003</v>
       </c>
       <c r="I268" t="s">
-        <v>1002</v>
-      </c>
-      <c r="K268" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="269" spans="1:11">
+        <v>423</v>
+      </c>
+      <c r="J268" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10">
       <c r="A269" t="s">
         <v>1004</v>
       </c>
@@ -12460,22 +12460,22 @@
         <v>14</v>
       </c>
       <c r="E269" t="s">
-        <v>233</v>
+        <v>1007</v>
       </c>
       <c r="F269" t="s">
         <v>243</v>
       </c>
       <c r="G269" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I269" t="s">
         <v>244</v>
       </c>
-      <c r="I269" t="s">
-        <v>1007</v>
-      </c>
-      <c r="K269" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="270" spans="1:11">
+      <c r="J269" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10">
       <c r="A270" t="s">
         <v>1009</v>
       </c>
@@ -12489,22 +12489,22 @@
         <v>14</v>
       </c>
       <c r="E270" t="s">
-        <v>233</v>
+        <v>1007</v>
       </c>
       <c r="F270" t="s">
         <v>243</v>
       </c>
       <c r="G270" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I270" t="s">
         <v>244</v>
       </c>
-      <c r="I270" t="s">
-        <v>1007</v>
-      </c>
-      <c r="K270" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="271" spans="1:11">
+      <c r="J270" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10">
       <c r="A271" t="s">
         <v>1012</v>
       </c>
@@ -12518,22 +12518,22 @@
         <v>14</v>
       </c>
       <c r="E271" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="F271" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G271" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I271" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K271" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="272" spans="1:11">
+      <c r="J271" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10">
       <c r="A272" t="s">
         <v>1019</v>
       </c>
@@ -12544,22 +12544,22 @@
         <v>14</v>
       </c>
       <c r="E272" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="F272" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G272" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I272" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K272" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="273" spans="1:11">
+      <c r="J272" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10">
       <c r="A273" t="s">
         <v>1021</v>
       </c>
@@ -12573,22 +12573,22 @@
         <v>14</v>
       </c>
       <c r="E273" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="F273" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G273" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I273" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K273" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="274" spans="1:11">
+      <c r="J273" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10">
       <c r="A274" t="s">
         <v>1024</v>
       </c>
@@ -12599,22 +12599,22 @@
         <v>14</v>
       </c>
       <c r="E274" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="F274" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G274" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I274" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K274" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="275" spans="1:11">
+      <c r="J274" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10">
       <c r="A275" t="s">
         <v>1026</v>
       </c>
@@ -12628,22 +12628,22 @@
         <v>14</v>
       </c>
       <c r="E275" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="F275" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G275" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I275" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K275" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="276" spans="1:11">
+      <c r="J275" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10">
       <c r="A276" t="s">
         <v>1029</v>
       </c>
@@ -12657,22 +12657,22 @@
         <v>14</v>
       </c>
       <c r="E276" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="F276" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G276" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I276" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K276" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="277" spans="1:11">
+      <c r="J276" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10">
       <c r="A277" t="s">
         <v>1032</v>
       </c>
@@ -12686,22 +12686,22 @@
         <v>14</v>
       </c>
       <c r="E277" t="s">
-        <v>233</v>
+        <v>1015</v>
       </c>
       <c r="F277" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G277" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="I277" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K277" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="278" spans="1:11">
+      <c r="J277" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10">
       <c r="A278" t="s">
         <v>1035</v>
       </c>
@@ -12715,22 +12715,22 @@
         <v>14</v>
       </c>
       <c r="E278" t="s">
-        <v>377</v>
+        <v>1038</v>
       </c>
       <c r="F278" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G278" t="s">
-        <v>421</v>
+        <v>1039</v>
       </c>
       <c r="I278" t="s">
-        <v>1038</v>
-      </c>
-      <c r="K278" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="279" spans="1:11">
+        <v>423</v>
+      </c>
+      <c r="J278" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10">
       <c r="A279" t="s">
         <v>1040</v>
       </c>
@@ -12744,22 +12744,22 @@
         <v>14</v>
       </c>
       <c r="E279" t="s">
-        <v>58</v>
+        <v>1038</v>
       </c>
       <c r="F279" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G279" t="s">
-        <v>93</v>
+        <v>1039</v>
       </c>
       <c r="I279" t="s">
-        <v>1038</v>
-      </c>
-      <c r="K279" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="280" spans="1:11">
+        <v>96</v>
+      </c>
+      <c r="J279" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10">
       <c r="A280" t="s">
         <v>1043</v>
       </c>
@@ -12773,22 +12773,22 @@
         <v>14</v>
       </c>
       <c r="E280" t="s">
-        <v>15</v>
+        <v>1038</v>
       </c>
       <c r="F280" t="s">
         <v>16</v>
       </c>
       <c r="G280" t="s">
-        <v>17</v>
+        <v>1039</v>
       </c>
       <c r="I280" t="s">
-        <v>1038</v>
-      </c>
-      <c r="K280" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="281" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="J280" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10">
       <c r="A281" t="s">
         <v>1046</v>
       </c>
@@ -12802,22 +12802,22 @@
         <v>14</v>
       </c>
       <c r="E281" t="s">
-        <v>233</v>
+        <v>1038</v>
       </c>
       <c r="F281" t="s">
         <v>352</v>
       </c>
       <c r="G281" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I281" t="s">
         <v>353</v>
       </c>
-      <c r="I281" t="s">
-        <v>1038</v>
-      </c>
-      <c r="K281" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="282" spans="1:11">
+      <c r="J281" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10">
       <c r="A282" t="s">
         <v>1049</v>
       </c>
@@ -12831,22 +12831,22 @@
         <v>14</v>
       </c>
       <c r="E282" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F282" t="s">
         <v>253</v>
       </c>
-      <c r="F282" t="s">
+      <c r="G282" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I282" t="s">
         <v>254</v>
       </c>
-      <c r="G282" t="s">
+      <c r="J282" t="s">
         <v>255</v>
       </c>
-      <c r="I282" t="s">
-        <v>1038</v>
-      </c>
-      <c r="K282" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="283" spans="1:11">
+    </row>
+    <row r="283" spans="1:10">
       <c r="A283" t="s">
         <v>1052</v>
       </c>
@@ -12860,22 +12860,22 @@
         <v>14</v>
       </c>
       <c r="E283" t="s">
-        <v>337</v>
+        <v>1055</v>
       </c>
       <c r="F283" t="s">
         <v>892</v>
       </c>
       <c r="G283" t="s">
-        <v>802</v>
+        <v>1056</v>
       </c>
       <c r="I283" t="s">
-        <v>1055</v>
-      </c>
-      <c r="K283" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="284" spans="1:11">
+        <v>805</v>
+      </c>
+      <c r="J283" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10">
       <c r="A284" t="s">
         <v>1057</v>
       </c>
@@ -12889,22 +12889,22 @@
         <v>14</v>
       </c>
       <c r="E284" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F284" t="s">
         <v>253</v>
       </c>
-      <c r="F284" t="s">
+      <c r="G284" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I284" t="s">
         <v>254</v>
       </c>
-      <c r="G284" t="s">
+      <c r="J284" t="s">
         <v>255</v>
       </c>
-      <c r="I284" t="s">
-        <v>1060</v>
-      </c>
-      <c r="K284" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="285" spans="1:11">
+    </row>
+    <row r="285" spans="1:10">
       <c r="A285" t="s">
         <v>1062</v>
       </c>
@@ -12915,22 +12915,22 @@
         <v>14</v>
       </c>
       <c r="E285" t="s">
-        <v>233</v>
+        <v>1064</v>
       </c>
       <c r="F285" t="s">
         <v>352</v>
       </c>
       <c r="G285" t="s">
+        <v>1065</v>
+      </c>
+      <c r="I285" t="s">
         <v>353</v>
       </c>
-      <c r="I285" t="s">
-        <v>1064</v>
-      </c>
-      <c r="K285" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="286" spans="1:11">
+      <c r="J285" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10">
       <c r="A286" t="s">
         <v>1066</v>
       </c>
@@ -12944,22 +12944,22 @@
         <v>14</v>
       </c>
       <c r="E286" t="s">
-        <v>377</v>
+        <v>1069</v>
       </c>
       <c r="F286" t="s">
         <v>981</v>
       </c>
       <c r="G286" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I286" t="s">
         <v>982</v>
       </c>
-      <c r="I286" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K286" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="287" spans="1:11">
+      <c r="J286" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10">
       <c r="A287" t="s">
         <v>1071</v>
       </c>
@@ -12973,22 +12973,22 @@
         <v>14</v>
       </c>
       <c r="E287" t="s">
-        <v>377</v>
+        <v>1069</v>
       </c>
       <c r="F287" t="s">
         <v>981</v>
       </c>
       <c r="G287" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I287" t="s">
         <v>982</v>
       </c>
-      <c r="I287" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K287" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="288" spans="1:11">
+      <c r="J287" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10">
       <c r="A288" t="s">
         <v>1074</v>
       </c>
@@ -13002,22 +13002,22 @@
         <v>14</v>
       </c>
       <c r="E288" t="s">
-        <v>15</v>
+        <v>1069</v>
       </c>
       <c r="F288" t="s">
         <v>75</v>
       </c>
       <c r="G288" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I288" t="s">
         <v>76</v>
       </c>
-      <c r="I288" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K288" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="289" spans="1:11">
+      <c r="J288" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10">
       <c r="A289" t="s">
         <v>1077</v>
       </c>
@@ -13031,22 +13031,22 @@
         <v>14</v>
       </c>
       <c r="E289" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F289" t="s">
         <v>58</v>
       </c>
-      <c r="F289" t="s">
+      <c r="G289" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I289" t="s">
         <v>59</v>
       </c>
-      <c r="G289" t="s">
+      <c r="J289" t="s">
         <v>60</v>
       </c>
-      <c r="I289" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K289" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="290" spans="1:11">
+    </row>
+    <row r="290" spans="1:10">
       <c r="A290" t="s">
         <v>1080</v>
       </c>
@@ -13060,22 +13060,22 @@
         <v>14</v>
       </c>
       <c r="E290" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F290" t="s">
         <v>58</v>
       </c>
-      <c r="F290" t="s">
+      <c r="G290" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I290" t="s">
         <v>59</v>
       </c>
-      <c r="G290" t="s">
+      <c r="J290" t="s">
         <v>60</v>
       </c>
-      <c r="I290" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K290" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="291" spans="1:11">
+    </row>
+    <row r="291" spans="1:10">
       <c r="A291" t="s">
         <v>1083</v>
       </c>
@@ -13089,22 +13089,22 @@
         <v>14</v>
       </c>
       <c r="E291" t="s">
-        <v>233</v>
+        <v>1069</v>
       </c>
       <c r="F291" t="s">
         <v>352</v>
       </c>
       <c r="G291" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I291" t="s">
         <v>353</v>
       </c>
-      <c r="I291" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K291" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="292" spans="1:11">
+      <c r="J291" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10">
       <c r="A292" t="s">
         <v>1086</v>
       </c>
@@ -13118,22 +13118,22 @@
         <v>14</v>
       </c>
       <c r="E292" t="s">
-        <v>233</v>
+        <v>1069</v>
       </c>
       <c r="F292" t="s">
         <v>352</v>
       </c>
       <c r="G292" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I292" t="s">
         <v>353</v>
       </c>
-      <c r="I292" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K292" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="293" spans="1:11">
+      <c r="J292" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10">
       <c r="A293" t="s">
         <v>1089</v>
       </c>
@@ -13147,22 +13147,22 @@
         <v>14</v>
       </c>
       <c r="E293" t="s">
-        <v>233</v>
+        <v>1069</v>
       </c>
       <c r="F293" t="s">
         <v>352</v>
       </c>
       <c r="G293" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I293" t="s">
         <v>353</v>
       </c>
-      <c r="I293" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K293" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="294" spans="1:11">
+      <c r="J293" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10">
       <c r="A294" t="s">
         <v>1092</v>
       </c>
@@ -13176,22 +13176,22 @@
         <v>14</v>
       </c>
       <c r="E294" t="s">
-        <v>233</v>
+        <v>1069</v>
       </c>
       <c r="F294" t="s">
         <v>352</v>
       </c>
       <c r="G294" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I294" t="s">
         <v>353</v>
       </c>
-      <c r="I294" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K294" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="295" spans="1:11">
+      <c r="J294" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10">
       <c r="A295" t="s">
         <v>1095</v>
       </c>
@@ -13205,22 +13205,22 @@
         <v>14</v>
       </c>
       <c r="E295" t="s">
-        <v>233</v>
+        <v>1098</v>
       </c>
       <c r="F295" t="s">
         <v>352</v>
       </c>
       <c r="G295" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I295" t="s">
         <v>353</v>
       </c>
-      <c r="I295" t="s">
-        <v>1098</v>
-      </c>
-      <c r="K295" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="296" spans="1:11">
+      <c r="J295" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10">
       <c r="A296" t="s">
         <v>1100</v>
       </c>
@@ -13234,19 +13234,19 @@
         <v>14</v>
       </c>
       <c r="E296" t="s">
-        <v>233</v>
+        <v>1098</v>
       </c>
       <c r="F296" t="s">
         <v>352</v>
       </c>
       <c r="G296" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I296" t="s">
         <v>353</v>
       </c>
-      <c r="I296" t="s">
-        <v>1098</v>
-      </c>
-      <c r="K296" t="s">
-        <v>1099</v>
+      <c r="J296" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -28,27 +28,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -61,27 +61,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -91,12 +91,12 @@
     <t>Educational buildings, equipment, materials; subsidiary services to education (boarding facilities, staff housing); language training; colloquia, seminars, lectures, etc.</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Research and studies on education effectiveness, relevance and quality; systematic evaluation and monitoring.</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
@@ -130,15 +130,15 @@
     <t>Formal and non-formal primary education for children; all elementary and first cycle systematic instruction; provision of learning materials.</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>112</t>
   </si>
   <si>
@@ -190,12 +190,12 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>07 - Health</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>Second cycle systematic instruction at junior level.</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Elementary vocational training and secondary level technical education; on-the job training; apprenticeships; including informal vocational training.</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
@@ -256,15 +256,15 @@
     <t>Degree and diploma programmes at universities, colleges and polytechnics; scholarships.</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>114</t>
   </si>
   <si>
@@ -277,12 +277,12 @@
     <t>Professional-level vocational training programmes and in-service training.</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
@@ -292,24 +292,24 @@
     <t>Health sector policy, planning and programmes; aid to health ministries, public health administration; institution capacity building and advice; medical insurance programmes; including health system strengthening and health governance; unspecified health activities.</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -328,12 +328,12 @@
     <t>General medical research (excluding basic health research and research for prevention and control of NCDs (12382)).</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>Laboratories, specialised clinics and hospitals (including equipment and supplies); ambulances; dental services; medical rehabilitation. Excludes noncommunicable diseases (123xx).</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -382,12 +382,12 @@
     <t>District-level hospitals, clinics and dispensaries and related medical equipment; excluding specialised hospitals and clinics (12191).</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -520,12 +520,12 @@
     <t>Population/development policies; demographic research/analysis; reproductive health research; unspecified population activities. (Use purpose code 15190 for data on migration and refugees. Use code 13096 for census work, vital registration and migration data collection.)</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -580,21 +580,21 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>Large scale sewerage including trunk sewers and sewage pumping stations; domestic and industrial waste water treatment plants.</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>Municipal and industrial solid waste management, including hazardous and toxic waste; collection, disposal and treatment; landfill areas; composting and reuse.</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -715,27 +715,27 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Fiscal policy and planning; support to ministries of finance; strengthening financial and managerial accountability; public expenditure management; improving financial management systems; budget drafting; inter-governmental fiscal relations, public audit, public debt. (Use code 15114 for domestic revenue mobilisation and code 33120 for customs).</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
@@ -760,12 +760,12 @@
     <t>Decentralisation processes (including political, administrative and fiscal dimensions); intergovernmental relations and federalism; strengthening departments of regional and local government, regional and local authorities and their national associations. (Use specific sector codes for decentralisation of sector management and services.)</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
@@ -775,12 +775,12 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
@@ -859,12 +859,12 @@
     <t>Support to administration of developing countries' foreign aid (including triangular and south-south cooperation).</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -943,12 +943,12 @@
     <t>Judicial law and order sectors; policy development within ministries of justice or equivalents.</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
@@ -958,12 +958,12 @@
     <t>Police affairs and services.</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Fire-prevention and fire-fighting affairs and services.</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>Prisons</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
@@ -1027,12 +1027,12 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
@@ -1072,12 +1072,12 @@
     <t>Electoral management bodies and processes, election observation, voters' education. (Use code 15230 when in the context of an international peacekeeping operation.)</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -1099,12 +1099,12 @@
     <t>Activities that support free and uncensored flow of information on public issues; activities that increase the editorial and technical skills and the integrity of the print and broadcast media, e.g. training of journalists. (Use codes 22010-22040 for provision of equipment and capital assistance to media.)</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -1147,12 +1147,12 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
@@ -1192,12 +1192,12 @@
     <t>Collection, production, management and dissemination of statistics and data related to Government &amp; Civil Society. Includes macroeconomic statistics, government finance, fiscal and public sector statistics, support to development of administrative data infrastructure, civil society surveys.</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -1231,12 +1231,12 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>02 - Defence</t>
   </si>
   <si>
@@ -1276,18 +1276,18 @@
     <t>Social protection or social security strategies, legislation and administration; institution capacity building and advice; social security and other social schemes; support programmes, cash benefits, pensions and special programmes for older persons, orphans, persons with disabilities, children, mothers with newborns, those living in poverty, without jobs and other vulnerable groups; social dimensions of structural adjustment.</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Social protection schemes in the form of cash or in-kind benefits, including pensions, against the risks linked to old age.</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -1348,12 +1348,12 @@
     <t>Employment policy and planning; institution capacity building and advice; employment creation and income generation programmes; including activities specifically designed for the needs of vulnerable groups.</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
@@ -1363,12 +1363,12 @@
     <t>Housing sector policy, planning and programmes; excluding low-cost housing and slum clearance (16040).</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
@@ -1378,12 +1378,12 @@
     <t>Including slum clearance.</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -1402,12 +1402,12 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
@@ -1444,12 +1444,12 @@
     <t>Recreation and sport</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -1486,12 +1486,12 @@
     <t>Transport sector policy, planning and programmes; aid to transport ministries; institution capacity building and advice; unspecified transport; activities that combine road, rail, water and/or air transport. Includes prevention of road accidents. Whenever possible, report transport of goods under the sector of the good being transported.</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21011</t>
   </si>
   <si>
@@ -1528,12 +1528,12 @@
     <t>Road infrastructure, road vehicles; passenger road transport, motor passenger cars.</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -1615,12 +1615,12 @@
     <t>Whether or not related to transportation. Whenever possible, report storage projects under the sector of the resource being stored.</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>Communications sector policy, planning and programmes; institution capacity building and advice; including postal services development; unspecified communications activities.</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22011</t>
   </si>
   <si>
@@ -1684,12 +1684,12 @@
     <t>Radio and TV links, equipment; newspapers; printing and publishing.</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -1708,24 +1708,24 @@
     <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -1741,12 +1741,12 @@
     <t>Regulation of the energy sector, including wholesale and retail electricity provision.</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -2032,12 +2032,12 @@
     <t>Finance sector policy, planning and programmes; institution capacity building and advice; financial markets and systems.</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -2089,12 +2089,12 @@
     <t>Public sector policies and institution support to the business environment and investment climate, including business regulations, property rights, non-discrimination, investment promotion, competition policy, enterprises law, private-public partnerships.</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -2131,24 +2131,24 @@
     <t>Agricultural sector policy, planning and programmes; aid to agricultural ministries; institution capacity building and advice; unspecified agriculture.</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2419,24 +2419,24 @@
     <t>Industrial sector policy, planning and programmes; institution capacity building and advice; unspecified industrial activities; manufacturing of goods not specified below.</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2710,15 +2710,15 @@
     <t>Trade policy and planning; support to ministries and departments responsible for trade policy; trade-related legislation and regulatory reforms; policy analysis and implementation of multilateral trade agreements e.g. technical barriers to trade and sanitary and phytosanitary measures (TBT/SPS) except at regional level (see 33130); mainstreaming trade in national development strategies (e.g. poverty reduction strategy papers); wholesale/retail trade; unspecified trade and trade promotion activities.</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -2788,12 +2788,12 @@
     <t>Environmental policy, laws, regulations and economic instruments; administrational institutions and practices; environmental and land use planning and decision-making procedures; seminars, meetings; miscellaneous conservation and protection measures not specified below.</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -2812,12 +2812,12 @@
     <t>Including natural reserves and actions in the surrounding areas; other measures to protect endangered or vulnerable species and their habitats (e.g. wetlands preservation).</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -2848,18 +2848,18 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -2878,12 +2878,12 @@
     <t>Urban development and planning; urban management, land information systems.</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -2935,12 +2935,12 @@
     <t>Disaster risk reduction activities if not sector specific. Comprises risk assessments, structural prevention measures (e.g. flood prevention infrastructure), preparedness measures (e.g. early warning systems) normative prevention measures (e.g. building codes, land-use planning), and risk transfer systems (e.g. insurance schemes, risk funds). Also includes building local and national capacities and supporting the establishment of efficient and sustainable national structures able to promote disaster risk reduction.</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
@@ -2959,12 +2959,12 @@
     <t>Short or longer term household food security programmes and activities that improve the access of households to nutritionally adequate diets (excluding any cash transfers within broader social welfare programmes that do not have a specific food security, food acquisition or nutrition focus which should be reported under code 16010).</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -2992,12 +2992,12 @@
     <t>When sector cannot be identified.</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -3007,12 +3007,12 @@
     <t>Unearmarked contributions to the government budget; support for the implementation of macroeconomic reforms (structural adjustment programmes, poverty reduction strategies); general programme assistance (when not allocable by sector).</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
@@ -3022,12 +3022,12 @@
     <t>Supply of edible human food under national or international programmes including transport costs, cash payments made for food supplies; project food assistance aid and food assistance aid for market sales when benefiting sector not specified. Excludes food security policy and administrative management (43071), household food security programmes (43072) and emergency food assistance aid (72040). Report as multilateral: i) food assistance aid by EU financed out of its budget and allocated pro rata to EU member countries; and ii) core contributions to the World Food Programme.</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
@@ -3037,12 +3037,12 @@
     <t>Capital goods and services; lines of credit.</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -3061,18 +3061,18 @@
     <t>Actions falling outside the code headings below.</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -3130,12 +3130,12 @@
     <t>Shelter, water, sanitation, education, health services including supply of medicines and malnutrition management, including medical nutrition management; supply of other nonfood relief items (including cash and voucher delivery modalities) for the benefit of crisisaffected people, including refugees and internally displaced people in developing countries, Includes assistance delivered by or coordinated by international civil protection units in the immediate aftermath of a disaster (in-kind assistance, deployment of specially-equipped teams, logistics and transportation, or assessment and coordination by experts sent to the field). Also includes measures to promote and protect the safety, well-being, dignity and integrity of crisis-affected people including refugees and internally displaced persons in developing countries. (Activities designed to protect the security of persons or properties through the use or display of force are not reportable as ODA.)</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72011</t>
   </si>
   <si>
@@ -3181,12 +3181,12 @@
     <t>Social and economic rehabilitation in the aftermath of emergencies to facilitate recovery and resilience building and enable populations to restore their livelihoods in the wake of an emergency situation (e.g. trauma counselling and treatment, employment programmes). Includes infrastructure necessary for the delivery of humanitarian aid; restoring pre-existing essential infrastructure and facilities (e.g. water and sanitation, shelter, health care services, education); rehabilitation of basic agricultural inputs and livestock. Excludes longer-term reconstruction ('build back better') which is reportable against relevant sectors.</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
@@ -3196,24 +3196,24 @@
     <t>Building the responsiveness, capability and capacity of international, regional and national humanitarian actors to disasters. Support to the institutional capacities of national and local government, specialised humanitarian bodies, and civil society organisations to anticipate, respond and recover from the impact of potential, imminent and current hazardous events and emergency situations that pose humanitarian threats and could call for a humanitarian response. This includes risk analysis and assessment, mitigation, preparedness, such as stockpiling of emergency items and training and capacity building aimed to increase the speed and effectiveness of lifesaving assistance delivered in the occurrence of crisis.</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
@@ -3223,12 +3223,12 @@
     <t>Costs incurred in donor countries for basic assistance to asylum seekers and refugees from developing countries, up to 12 months, when costs cannot be disaggregated. See section II.6 and Annex 17.</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>93011</t>
   </si>
   <si>
@@ -3310,10 +3310,10 @@
     <t>Contributions to general development of the recipient should be included under programme assistance (51010).</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -3747,13 +3747,13 @@
         <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
         <v>20</v>
@@ -3817,13 +3817,13 @@
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
@@ -3852,19 +3852,19 @@
         <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
         <v>40</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3890,16 +3890,16 @@
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3922,19 +3922,19 @@
         <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3957,19 +3957,19 @@
         <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
         <v>40</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3989,22 +3989,22 @@
         <v>15</v>
       </c>
       <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
         <v>54</v>
       </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
         <v>40</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K10" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4027,19 +4027,19 @@
         <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="H11" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="I11" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="J11" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="K11" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4062,19 +4062,19 @@
         <v>64</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="H12" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K12" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4094,22 +4094,22 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" t="s">
         <v>69</v>
       </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
       <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
         <v>70</v>
       </c>
-      <c r="I13" t="s">
-        <v>65</v>
-      </c>
       <c r="J13" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="K13" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4132,19 +4132,19 @@
         <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" t="s">
         <v>70</v>
       </c>
-      <c r="I14" t="s">
-        <v>76</v>
-      </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="K14" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4167,19 +4167,19 @@
         <v>80</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
         <v>82</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="K15" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4202,19 +4202,19 @@
         <v>87</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4240,13 +4240,13 @@
         <v>94</v>
       </c>
       <c r="H17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" t="s">
         <v>95</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>96</v>
-      </c>
-      <c r="J17" t="s">
-        <v>60</v>
       </c>
       <c r="K17" t="s">
         <v>97</v>
@@ -4275,13 +4275,13 @@
         <v>94</v>
       </c>
       <c r="H18" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" t="s">
         <v>95</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>96</v>
-      </c>
-      <c r="J18" t="s">
-        <v>60</v>
       </c>
       <c r="K18" t="s">
         <v>97</v>
@@ -4307,16 +4307,16 @@
         <v>104</v>
       </c>
       <c r="G19" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H19" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" t="s">
         <v>95</v>
       </c>
-      <c r="I19" t="s">
-        <v>105</v>
-      </c>
       <c r="J19" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="K19" t="s">
         <v>97</v>
@@ -4342,16 +4342,16 @@
         <v>109</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20" t="s">
         <v>95</v>
       </c>
-      <c r="I20" t="s">
-        <v>110</v>
-      </c>
       <c r="J20" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="K20" t="s">
         <v>97</v>
@@ -4380,13 +4380,13 @@
         <v>94</v>
       </c>
       <c r="H21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21" t="s">
         <v>95</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>96</v>
-      </c>
-      <c r="J21" t="s">
-        <v>60</v>
       </c>
       <c r="K21" t="s">
         <v>97</v>
@@ -4412,19 +4412,19 @@
         <v>58</v>
       </c>
       <c r="G22" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H22" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" t="s">
         <v>117</v>
       </c>
-      <c r="I22" t="s">
-        <v>59</v>
-      </c>
       <c r="J22" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="K22" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4447,19 +4447,19 @@
         <v>122</v>
       </c>
       <c r="G23" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="H23" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" t="s">
         <v>117</v>
       </c>
-      <c r="I23" t="s">
-        <v>123</v>
-      </c>
       <c r="J23" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="K23" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4482,19 +4482,19 @@
         <v>58</v>
       </c>
       <c r="G24" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" t="s">
         <v>117</v>
       </c>
-      <c r="I24" t="s">
-        <v>59</v>
-      </c>
       <c r="J24" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="K24" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4517,19 +4517,19 @@
         <v>58</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" t="s">
         <v>117</v>
       </c>
-      <c r="I25" t="s">
-        <v>59</v>
-      </c>
       <c r="J25" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="K25" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4552,19 +4552,19 @@
         <v>58</v>
       </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H26" t="s">
+        <v>60</v>
+      </c>
+      <c r="I26" t="s">
         <v>117</v>
       </c>
-      <c r="I26" t="s">
-        <v>59</v>
-      </c>
       <c r="J26" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="K26" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4587,19 +4587,19 @@
         <v>58</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H27" t="s">
+        <v>60</v>
+      </c>
+      <c r="I27" t="s">
         <v>117</v>
       </c>
-      <c r="I27" t="s">
-        <v>59</v>
-      </c>
       <c r="J27" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="K27" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4622,19 +4622,19 @@
         <v>58</v>
       </c>
       <c r="G28" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I28" t="s">
         <v>117</v>
       </c>
-      <c r="I28" t="s">
-        <v>59</v>
-      </c>
       <c r="J28" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="K28" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4657,19 +4657,19 @@
         <v>58</v>
       </c>
       <c r="G29" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H29" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" t="s">
         <v>117</v>
       </c>
-      <c r="I29" t="s">
-        <v>59</v>
-      </c>
       <c r="J29" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="K29" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4695,16 +4695,16 @@
         <v>94</v>
       </c>
       <c r="H30" t="s">
+        <v>60</v>
+      </c>
+      <c r="I30" t="s">
         <v>117</v>
       </c>
-      <c r="I30" t="s">
-        <v>96</v>
-      </c>
       <c r="J30" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="K30" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4727,19 +4727,19 @@
         <v>58</v>
       </c>
       <c r="G31" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H31" t="s">
+        <v>60</v>
+      </c>
+      <c r="I31" t="s">
         <v>148</v>
       </c>
-      <c r="I31" t="s">
-        <v>59</v>
-      </c>
       <c r="J31" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="K31" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4762,19 +4762,19 @@
         <v>58</v>
       </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H32" t="s">
+        <v>60</v>
+      </c>
+      <c r="I32" t="s">
         <v>148</v>
       </c>
-      <c r="I32" t="s">
-        <v>59</v>
-      </c>
       <c r="J32" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="K32" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4797,19 +4797,19 @@
         <v>58</v>
       </c>
       <c r="G33" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H33" t="s">
+        <v>60</v>
+      </c>
+      <c r="I33" t="s">
         <v>148</v>
       </c>
-      <c r="I33" t="s">
-        <v>59</v>
-      </c>
       <c r="J33" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="K33" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4832,19 +4832,19 @@
         <v>58</v>
       </c>
       <c r="G34" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H34" t="s">
+        <v>60</v>
+      </c>
+      <c r="I34" t="s">
         <v>148</v>
       </c>
-      <c r="I34" t="s">
-        <v>59</v>
-      </c>
       <c r="J34" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="K34" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4867,19 +4867,19 @@
         <v>58</v>
       </c>
       <c r="G35" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H35" t="s">
+        <v>60</v>
+      </c>
+      <c r="I35" t="s">
         <v>148</v>
       </c>
-      <c r="I35" t="s">
-        <v>59</v>
-      </c>
       <c r="J35" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="K35" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4902,19 +4902,19 @@
         <v>104</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H36" t="s">
+        <v>60</v>
+      </c>
+      <c r="I36" t="s">
         <v>148</v>
       </c>
-      <c r="I36" t="s">
-        <v>105</v>
-      </c>
       <c r="J36" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="K36" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4937,13 +4937,13 @@
         <v>58</v>
       </c>
       <c r="G37" t="s">
+        <v>59</v>
+      </c>
+      <c r="H37" t="s">
+        <v>60</v>
+      </c>
+      <c r="K37" t="s">
         <v>169</v>
-      </c>
-      <c r="I37" t="s">
-        <v>59</v>
-      </c>
-      <c r="J37" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4966,13 +4966,13 @@
         <v>58</v>
       </c>
       <c r="G38" t="s">
+        <v>59</v>
+      </c>
+      <c r="H38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K38" t="s">
         <v>169</v>
-      </c>
-      <c r="I38" t="s">
-        <v>59</v>
-      </c>
-      <c r="J38" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4995,13 +4995,13 @@
         <v>58</v>
       </c>
       <c r="G39" t="s">
+        <v>59</v>
+      </c>
+      <c r="H39" t="s">
+        <v>60</v>
+      </c>
+      <c r="K39" t="s">
         <v>169</v>
-      </c>
-      <c r="I39" t="s">
-        <v>59</v>
-      </c>
-      <c r="J39" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5024,13 +5024,13 @@
         <v>58</v>
       </c>
       <c r="G40" t="s">
+        <v>59</v>
+      </c>
+      <c r="H40" t="s">
+        <v>60</v>
+      </c>
+      <c r="K40" t="s">
         <v>169</v>
-      </c>
-      <c r="I40" t="s">
-        <v>59</v>
-      </c>
-      <c r="J40" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5053,13 +5053,13 @@
         <v>93</v>
       </c>
       <c r="G41" t="s">
+        <v>94</v>
+      </c>
+      <c r="H41" t="s">
+        <v>60</v>
+      </c>
+      <c r="K41" t="s">
         <v>169</v>
-      </c>
-      <c r="I41" t="s">
-        <v>96</v>
-      </c>
-      <c r="J41" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5082,13 +5082,13 @@
         <v>104</v>
       </c>
       <c r="G42" t="s">
+        <v>105</v>
+      </c>
+      <c r="H42" t="s">
+        <v>60</v>
+      </c>
+      <c r="K42" t="s">
         <v>169</v>
-      </c>
-      <c r="I42" t="s">
-        <v>105</v>
-      </c>
-      <c r="J42" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5113,10 +5113,10 @@
       <c r="G43" t="s">
         <v>190</v>
       </c>
-      <c r="I43" t="s">
+      <c r="H43" t="s">
         <v>191</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5140,13 +5140,13 @@
         <v>196</v>
       </c>
       <c r="G44" t="s">
-        <v>190</v>
-      </c>
-      <c r="I44" t="s">
         <v>197</v>
       </c>
-      <c r="J44" t="s">
+      <c r="H44" t="s">
         <v>198</v>
+      </c>
+      <c r="K44" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5171,10 +5171,10 @@
       <c r="G45" t="s">
         <v>190</v>
       </c>
-      <c r="I45" t="s">
+      <c r="H45" t="s">
         <v>191</v>
       </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5200,10 +5200,10 @@
       <c r="G46" t="s">
         <v>190</v>
       </c>
-      <c r="I46" t="s">
+      <c r="H46" t="s">
         <v>191</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5227,13 +5227,13 @@
         <v>208</v>
       </c>
       <c r="G47" t="s">
-        <v>190</v>
-      </c>
-      <c r="I47" t="s">
         <v>209</v>
       </c>
-      <c r="J47" t="s">
+      <c r="H47" t="s">
         <v>198</v>
+      </c>
+      <c r="K47" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5258,10 +5258,10 @@
       <c r="G48" t="s">
         <v>190</v>
       </c>
-      <c r="I48" t="s">
+      <c r="H48" t="s">
         <v>191</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5287,10 +5287,10 @@
       <c r="G49" t="s">
         <v>190</v>
       </c>
-      <c r="I49" t="s">
+      <c r="H49" t="s">
         <v>191</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5314,13 +5314,13 @@
         <v>208</v>
       </c>
       <c r="G50" t="s">
-        <v>190</v>
-      </c>
-      <c r="I50" t="s">
         <v>209</v>
       </c>
-      <c r="J50" t="s">
+      <c r="H50" t="s">
         <v>198</v>
+      </c>
+      <c r="K50" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5345,10 +5345,10 @@
       <c r="G51" t="s">
         <v>190</v>
       </c>
-      <c r="I51" t="s">
+      <c r="H51" t="s">
         <v>191</v>
       </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5372,13 +5372,13 @@
         <v>225</v>
       </c>
       <c r="G52" t="s">
-        <v>190</v>
-      </c>
-      <c r="I52" t="s">
         <v>226</v>
       </c>
-      <c r="J52" t="s">
+      <c r="H52" t="s">
         <v>198</v>
+      </c>
+      <c r="K52" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5401,13 +5401,13 @@
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>190</v>
-      </c>
-      <c r="I53" t="s">
-        <v>19</v>
-      </c>
-      <c r="J53" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="H53" t="s">
+        <v>18</v>
+      </c>
+      <c r="K53" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5465,13 +5465,13 @@
         <v>243</v>
       </c>
       <c r="G55" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H55" t="s">
         <v>236</v>
       </c>
       <c r="I55" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J55" t="s">
         <v>238</v>
@@ -5500,13 +5500,13 @@
         <v>248</v>
       </c>
       <c r="G56" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="H56" t="s">
         <v>236</v>
       </c>
       <c r="I56" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="J56" t="s">
         <v>238</v>
@@ -5535,16 +5535,16 @@
         <v>253</v>
       </c>
       <c r="G57" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="H57" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I57" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J57" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="K57" t="s">
         <v>239</v>
@@ -5570,13 +5570,13 @@
         <v>243</v>
       </c>
       <c r="G58" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H58" t="s">
         <v>236</v>
       </c>
       <c r="I58" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J58" t="s">
         <v>238</v>
@@ -5605,13 +5605,13 @@
         <v>243</v>
       </c>
       <c r="G59" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H59" t="s">
         <v>236</v>
       </c>
       <c r="I59" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J59" t="s">
         <v>238</v>
@@ -5640,13 +5640,13 @@
         <v>243</v>
       </c>
       <c r="G60" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H60" t="s">
         <v>236</v>
       </c>
       <c r="I60" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J60" t="s">
         <v>238</v>
@@ -5675,13 +5675,13 @@
         <v>243</v>
       </c>
       <c r="G61" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H61" t="s">
         <v>236</v>
       </c>
       <c r="I61" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J61" t="s">
         <v>238</v>
@@ -5710,13 +5710,13 @@
         <v>243</v>
       </c>
       <c r="G62" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H62" t="s">
         <v>236</v>
       </c>
       <c r="I62" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J62" t="s">
         <v>238</v>
@@ -5742,16 +5742,16 @@
         <v>233</v>
       </c>
       <c r="F63" t="s">
+        <v>243</v>
+      </c>
+      <c r="G63" t="s">
         <v>274</v>
-      </c>
-      <c r="G63" t="s">
-        <v>235</v>
       </c>
       <c r="H63" t="s">
         <v>236</v>
       </c>
       <c r="I63" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J63" t="s">
         <v>238</v>
@@ -5777,16 +5777,16 @@
         <v>233</v>
       </c>
       <c r="F64" t="s">
+        <v>243</v>
+      </c>
+      <c r="G64" t="s">
         <v>274</v>
-      </c>
-      <c r="G64" t="s">
-        <v>235</v>
       </c>
       <c r="H64" t="s">
         <v>236</v>
       </c>
       <c r="I64" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J64" t="s">
         <v>238</v>
@@ -5815,13 +5815,13 @@
         <v>281</v>
       </c>
       <c r="G65" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="H65" t="s">
         <v>236</v>
       </c>
       <c r="I65" t="s">
-        <v>282</v>
+        <v>237</v>
       </c>
       <c r="J65" t="s">
         <v>238</v>
@@ -5885,13 +5885,13 @@
         <v>243</v>
       </c>
       <c r="G67" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H67" t="s">
         <v>236</v>
       </c>
       <c r="I67" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J67" t="s">
         <v>238</v>
@@ -5917,10 +5917,10 @@
         <v>233</v>
       </c>
       <c r="F68" t="s">
+        <v>234</v>
+      </c>
+      <c r="G68" t="s">
         <v>292</v>
-      </c>
-      <c r="G68" t="s">
-        <v>235</v>
       </c>
       <c r="H68" t="s">
         <v>236</v>
@@ -5952,10 +5952,10 @@
         <v>233</v>
       </c>
       <c r="F69" t="s">
+        <v>234</v>
+      </c>
+      <c r="G69" t="s">
         <v>296</v>
-      </c>
-      <c r="G69" t="s">
-        <v>235</v>
       </c>
       <c r="H69" t="s">
         <v>236</v>
@@ -5990,13 +5990,13 @@
         <v>248</v>
       </c>
       <c r="G70" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="H70" t="s">
         <v>236</v>
       </c>
       <c r="I70" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="J70" t="s">
         <v>238</v>
@@ -6025,13 +6025,13 @@
         <v>248</v>
       </c>
       <c r="G71" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="H71" t="s">
         <v>236</v>
       </c>
       <c r="I71" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="J71" t="s">
         <v>238</v>
@@ -6095,16 +6095,16 @@
         <v>309</v>
       </c>
       <c r="G73" t="s">
-        <v>235</v>
+        <v>310</v>
       </c>
       <c r="H73" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I73" t="s">
-        <v>310</v>
+        <v>237</v>
       </c>
       <c r="J73" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="K73" t="s">
         <v>239</v>
@@ -6130,16 +6130,16 @@
         <v>314</v>
       </c>
       <c r="G74" t="s">
-        <v>235</v>
+        <v>315</v>
       </c>
       <c r="H74" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I74" t="s">
-        <v>315</v>
+        <v>237</v>
       </c>
       <c r="J74" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="K74" t="s">
         <v>239</v>
@@ -6165,16 +6165,16 @@
         <v>319</v>
       </c>
       <c r="G75" t="s">
-        <v>235</v>
+        <v>320</v>
       </c>
       <c r="H75" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I75" t="s">
-        <v>320</v>
+        <v>237</v>
       </c>
       <c r="J75" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="K75" t="s">
         <v>239</v>
@@ -6200,16 +6200,16 @@
         <v>309</v>
       </c>
       <c r="G76" t="s">
-        <v>235</v>
+        <v>310</v>
       </c>
       <c r="H76" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I76" t="s">
-        <v>310</v>
+        <v>237</v>
       </c>
       <c r="J76" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="K76" t="s">
         <v>239</v>
@@ -6235,16 +6235,16 @@
         <v>309</v>
       </c>
       <c r="G77" t="s">
-        <v>235</v>
+        <v>310</v>
       </c>
       <c r="H77" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I77" t="s">
-        <v>310</v>
+        <v>237</v>
       </c>
       <c r="J77" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="K77" t="s">
         <v>239</v>
@@ -6270,16 +6270,16 @@
         <v>314</v>
       </c>
       <c r="G78" t="s">
-        <v>235</v>
+        <v>315</v>
       </c>
       <c r="H78" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I78" t="s">
-        <v>315</v>
+        <v>237</v>
       </c>
       <c r="J78" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="K78" t="s">
         <v>239</v>
@@ -6302,16 +6302,16 @@
         <v>332</v>
       </c>
       <c r="G79" t="s">
-        <v>235</v>
+        <v>333</v>
       </c>
       <c r="H79" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I79" t="s">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="J79" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="K79" t="s">
         <v>239</v>
@@ -6337,16 +6337,16 @@
         <v>337</v>
       </c>
       <c r="G80" t="s">
-        <v>235</v>
+        <v>338</v>
       </c>
       <c r="H80" t="s">
-        <v>236</v>
+        <v>339</v>
       </c>
       <c r="I80" t="s">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="J80" t="s">
-        <v>339</v>
+        <v>238</v>
       </c>
       <c r="K80" t="s">
         <v>239</v>
@@ -6372,16 +6372,16 @@
         <v>337</v>
       </c>
       <c r="G81" t="s">
-        <v>235</v>
+        <v>338</v>
       </c>
       <c r="H81" t="s">
-        <v>236</v>
+        <v>339</v>
       </c>
       <c r="I81" t="s">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="J81" t="s">
-        <v>339</v>
+        <v>238</v>
       </c>
       <c r="K81" t="s">
         <v>239</v>
@@ -6407,16 +6407,16 @@
         <v>337</v>
       </c>
       <c r="G82" t="s">
-        <v>235</v>
+        <v>338</v>
       </c>
       <c r="H82" t="s">
-        <v>236</v>
+        <v>339</v>
       </c>
       <c r="I82" t="s">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="J82" t="s">
-        <v>339</v>
+        <v>238</v>
       </c>
       <c r="K82" t="s">
         <v>239</v>
@@ -6439,10 +6439,10 @@
         <v>233</v>
       </c>
       <c r="F83" t="s">
+        <v>234</v>
+      </c>
+      <c r="G83" t="s">
         <v>296</v>
-      </c>
-      <c r="G83" t="s">
-        <v>235</v>
       </c>
       <c r="H83" t="s">
         <v>236</v>
@@ -6477,13 +6477,13 @@
         <v>352</v>
       </c>
       <c r="G84" t="s">
-        <v>235</v>
+        <v>353</v>
       </c>
       <c r="H84" t="s">
         <v>236</v>
       </c>
       <c r="I84" t="s">
-        <v>353</v>
+        <v>237</v>
       </c>
       <c r="J84" t="s">
         <v>238</v>
@@ -6509,16 +6509,16 @@
         <v>233</v>
       </c>
       <c r="F85" t="s">
+        <v>243</v>
+      </c>
+      <c r="G85" t="s">
         <v>357</v>
-      </c>
-      <c r="G85" t="s">
-        <v>235</v>
       </c>
       <c r="H85" t="s">
         <v>236</v>
       </c>
       <c r="I85" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J85" t="s">
         <v>238</v>
@@ -6547,16 +6547,16 @@
         <v>361</v>
       </c>
       <c r="G86" t="s">
-        <v>235</v>
+        <v>362</v>
       </c>
       <c r="H86" t="s">
-        <v>236</v>
+        <v>339</v>
       </c>
       <c r="I86" t="s">
-        <v>362</v>
+        <v>237</v>
       </c>
       <c r="J86" t="s">
-        <v>339</v>
+        <v>238</v>
       </c>
       <c r="K86" t="s">
         <v>239</v>
@@ -6579,16 +6579,16 @@
         <v>233</v>
       </c>
       <c r="F87" t="s">
+        <v>243</v>
+      </c>
+      <c r="G87" t="s">
         <v>357</v>
-      </c>
-      <c r="G87" t="s">
-        <v>235</v>
       </c>
       <c r="H87" t="s">
         <v>236</v>
       </c>
       <c r="I87" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J87" t="s">
         <v>238</v>
@@ -6614,13 +6614,13 @@
         <v>243</v>
       </c>
       <c r="G88" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H88" t="s">
         <v>236</v>
       </c>
       <c r="I88" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J88" t="s">
         <v>238</v>
@@ -6649,13 +6649,13 @@
         <v>243</v>
       </c>
       <c r="G89" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H89" t="s">
         <v>236</v>
       </c>
       <c r="I89" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J89" t="s">
         <v>238</v>
@@ -6684,16 +6684,16 @@
         <v>253</v>
       </c>
       <c r="G90" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="H90" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I90" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J90" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="K90" t="s">
         <v>239</v>
@@ -6719,16 +6719,16 @@
         <v>377</v>
       </c>
       <c r="G91" t="s">
-        <v>235</v>
+        <v>378</v>
       </c>
       <c r="H91" t="s">
-        <v>236</v>
+        <v>379</v>
       </c>
       <c r="I91" t="s">
-        <v>378</v>
+        <v>237</v>
       </c>
       <c r="J91" t="s">
-        <v>379</v>
+        <v>238</v>
       </c>
       <c r="K91" t="s">
         <v>239</v>
@@ -6754,16 +6754,16 @@
         <v>253</v>
       </c>
       <c r="G92" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="H92" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I92" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J92" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="K92" t="s">
         <v>239</v>
@@ -6789,13 +6789,13 @@
         <v>248</v>
       </c>
       <c r="G93" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="H93" t="s">
         <v>236</v>
       </c>
       <c r="I93" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="J93" t="s">
         <v>238</v>
@@ -6824,16 +6824,16 @@
         <v>253</v>
       </c>
       <c r="G94" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="H94" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I94" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J94" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="K94" t="s">
         <v>239</v>
@@ -6859,13 +6859,13 @@
         <v>392</v>
       </c>
       <c r="G95" t="s">
-        <v>235</v>
+        <v>393</v>
       </c>
       <c r="H95" t="s">
         <v>236</v>
       </c>
       <c r="I95" t="s">
-        <v>393</v>
+        <v>237</v>
       </c>
       <c r="J95" t="s">
         <v>238</v>
@@ -6894,19 +6894,19 @@
         <v>253</v>
       </c>
       <c r="G96" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="H96" t="s">
+        <v>255</v>
+      </c>
+      <c r="I96" t="s">
         <v>397</v>
       </c>
-      <c r="I96" t="s">
-        <v>254</v>
-      </c>
       <c r="J96" t="s">
-        <v>255</v>
+        <v>398</v>
       </c>
       <c r="K96" t="s">
-        <v>398</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -6929,19 +6929,19 @@
         <v>253</v>
       </c>
       <c r="G97" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="H97" t="s">
+        <v>255</v>
+      </c>
+      <c r="I97" t="s">
         <v>397</v>
       </c>
-      <c r="I97" t="s">
-        <v>254</v>
-      </c>
       <c r="J97" t="s">
-        <v>255</v>
+        <v>398</v>
       </c>
       <c r="K97" t="s">
-        <v>398</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -6964,19 +6964,19 @@
         <v>405</v>
       </c>
       <c r="G98" t="s">
-        <v>235</v>
+        <v>406</v>
       </c>
       <c r="H98" t="s">
+        <v>407</v>
+      </c>
+      <c r="I98" t="s">
         <v>397</v>
       </c>
-      <c r="I98" t="s">
-        <v>406</v>
-      </c>
       <c r="J98" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="K98" t="s">
-        <v>398</v>
+        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -6999,19 +6999,19 @@
         <v>253</v>
       </c>
       <c r="G99" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="H99" t="s">
+        <v>255</v>
+      </c>
+      <c r="I99" t="s">
         <v>397</v>
       </c>
-      <c r="I99" t="s">
-        <v>254</v>
-      </c>
       <c r="J99" t="s">
-        <v>255</v>
+        <v>398</v>
       </c>
       <c r="K99" t="s">
-        <v>398</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -7034,19 +7034,19 @@
         <v>319</v>
       </c>
       <c r="G100" t="s">
-        <v>235</v>
+        <v>320</v>
       </c>
       <c r="H100" t="s">
+        <v>255</v>
+      </c>
+      <c r="I100" t="s">
         <v>397</v>
       </c>
-      <c r="I100" t="s">
-        <v>320</v>
-      </c>
       <c r="J100" t="s">
-        <v>255</v>
+        <v>398</v>
       </c>
       <c r="K100" t="s">
-        <v>398</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -7069,19 +7069,19 @@
         <v>253</v>
       </c>
       <c r="G101" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="H101" t="s">
+        <v>255</v>
+      </c>
+      <c r="I101" t="s">
         <v>397</v>
       </c>
-      <c r="I101" t="s">
-        <v>254</v>
-      </c>
       <c r="J101" t="s">
-        <v>255</v>
+        <v>398</v>
       </c>
       <c r="K101" t="s">
-        <v>398</v>
+        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -7106,11 +7106,11 @@
       <c r="G102" t="s">
         <v>422</v>
       </c>
-      <c r="I102" t="s">
+      <c r="H102" t="s">
+        <v>379</v>
+      </c>
+      <c r="K102" t="s">
         <v>423</v>
-      </c>
-      <c r="J102" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -7135,11 +7135,11 @@
       <c r="G103" t="s">
         <v>422</v>
       </c>
-      <c r="I103" t="s">
+      <c r="H103" t="s">
+        <v>379</v>
+      </c>
+      <c r="K103" t="s">
         <v>423</v>
-      </c>
-      <c r="J103" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -7164,11 +7164,11 @@
       <c r="G104" t="s">
         <v>422</v>
       </c>
-      <c r="I104" t="s">
+      <c r="H104" t="s">
+        <v>379</v>
+      </c>
+      <c r="K104" t="s">
         <v>423</v>
-      </c>
-      <c r="J104" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -7191,13 +7191,13 @@
         <v>433</v>
       </c>
       <c r="G105" t="s">
-        <v>422</v>
-      </c>
-      <c r="I105" t="s">
         <v>434</v>
       </c>
-      <c r="J105" t="s">
+      <c r="H105" t="s">
         <v>379</v>
+      </c>
+      <c r="K105" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7222,11 +7222,11 @@
       <c r="G106" t="s">
         <v>422</v>
       </c>
-      <c r="I106" t="s">
+      <c r="H106" t="s">
+        <v>379</v>
+      </c>
+      <c r="K106" t="s">
         <v>423</v>
-      </c>
-      <c r="J106" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -7249,13 +7249,13 @@
         <v>377</v>
       </c>
       <c r="G107" t="s">
-        <v>422</v>
-      </c>
-      <c r="I107" t="s">
         <v>378</v>
       </c>
-      <c r="J107" t="s">
+      <c r="H107" t="s">
         <v>379</v>
+      </c>
+      <c r="K107" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -7278,13 +7278,13 @@
         <v>444</v>
       </c>
       <c r="G108" t="s">
-        <v>422</v>
-      </c>
-      <c r="I108" t="s">
         <v>445</v>
       </c>
-      <c r="J108" t="s">
+      <c r="H108" t="s">
         <v>379</v>
+      </c>
+      <c r="K108" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7307,13 +7307,13 @@
         <v>449</v>
       </c>
       <c r="G109" t="s">
-        <v>422</v>
-      </c>
-      <c r="I109" t="s">
         <v>450</v>
       </c>
-      <c r="J109" t="s">
-        <v>192</v>
+      <c r="H109" t="s">
+        <v>191</v>
+      </c>
+      <c r="K109" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -7336,13 +7336,13 @@
         <v>454</v>
       </c>
       <c r="G110" t="s">
-        <v>422</v>
-      </c>
-      <c r="I110" t="s">
         <v>455</v>
       </c>
-      <c r="J110" t="s">
-        <v>192</v>
+      <c r="H110" t="s">
+        <v>191</v>
+      </c>
+      <c r="K110" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -7367,11 +7367,11 @@
       <c r="G111" t="s">
         <v>422</v>
       </c>
-      <c r="I111" t="s">
+      <c r="H111" t="s">
+        <v>379</v>
+      </c>
+      <c r="K111" t="s">
         <v>423</v>
-      </c>
-      <c r="J111" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -7394,16 +7394,16 @@
         <v>462</v>
       </c>
       <c r="G112" t="s">
-        <v>422</v>
-      </c>
-      <c r="I112" t="s">
         <v>463</v>
       </c>
-      <c r="J112" t="s">
+      <c r="H112" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="113" spans="1:10">
+      <c r="K112" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
       <c r="A113" t="s">
         <v>465</v>
       </c>
@@ -7420,19 +7420,19 @@
         <v>420</v>
       </c>
       <c r="F113" t="s">
+        <v>234</v>
+      </c>
+      <c r="G113" t="s">
         <v>296</v>
       </c>
-      <c r="G113" t="s">
-        <v>422</v>
-      </c>
-      <c r="I113" t="s">
-        <v>237</v>
-      </c>
-      <c r="J113" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
+      <c r="H113" t="s">
+        <v>236</v>
+      </c>
+      <c r="K113" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
       <c r="A114" t="s">
         <v>468</v>
       </c>
@@ -7452,16 +7452,16 @@
         <v>314</v>
       </c>
       <c r="G114" t="s">
-        <v>422</v>
-      </c>
-      <c r="I114" t="s">
         <v>315</v>
       </c>
-      <c r="J114" t="s">
+      <c r="H114" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="115" spans="1:10">
+      <c r="K114" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
       <c r="A115" t="s">
         <v>471</v>
       </c>
@@ -7481,16 +7481,16 @@
         <v>377</v>
       </c>
       <c r="G115" t="s">
-        <v>422</v>
-      </c>
-      <c r="I115" t="s">
         <v>378</v>
       </c>
-      <c r="J115" t="s">
+      <c r="H115" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="116" spans="1:10">
+      <c r="K115" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
       <c r="A116" t="s">
         <v>474</v>
       </c>
@@ -7507,16 +7507,16 @@
         <v>476</v>
       </c>
       <c r="G116" t="s">
-        <v>422</v>
-      </c>
-      <c r="I116" t="s">
         <v>477</v>
       </c>
-      <c r="J116" t="s">
+      <c r="H116" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="117" spans="1:10">
+      <c r="K116" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
       <c r="A117" t="s">
         <v>478</v>
       </c>
@@ -7533,16 +7533,16 @@
         <v>462</v>
       </c>
       <c r="G117" t="s">
-        <v>422</v>
-      </c>
-      <c r="I117" t="s">
         <v>463</v>
       </c>
-      <c r="J117" t="s">
+      <c r="H117" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="118" spans="1:10">
+      <c r="K117" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
       <c r="A118" t="s">
         <v>480</v>
       </c>
@@ -7559,19 +7559,19 @@
         <v>420</v>
       </c>
       <c r="F118" t="s">
+        <v>337</v>
+      </c>
+      <c r="G118" t="s">
         <v>483</v>
       </c>
-      <c r="G118" t="s">
-        <v>422</v>
-      </c>
-      <c r="I118" t="s">
-        <v>338</v>
-      </c>
-      <c r="J118" t="s">
+      <c r="H118" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="119" spans="1:10">
+      <c r="K118" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
       <c r="A119" t="s">
         <v>484</v>
       </c>
@@ -7591,16 +7591,16 @@
         <v>377</v>
       </c>
       <c r="G119" t="s">
-        <v>422</v>
-      </c>
-      <c r="I119" t="s">
         <v>378</v>
       </c>
-      <c r="J119" t="s">
+      <c r="H119" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="120" spans="1:10">
+      <c r="K119" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
       <c r="A120" t="s">
         <v>487</v>
       </c>
@@ -7620,16 +7620,16 @@
         <v>352</v>
       </c>
       <c r="G120" t="s">
+        <v>353</v>
+      </c>
+      <c r="H120" t="s">
+        <v>236</v>
+      </c>
+      <c r="K120" t="s">
         <v>491</v>
       </c>
-      <c r="I120" t="s">
-        <v>353</v>
-      </c>
-      <c r="J120" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10">
+    </row>
+    <row r="121" spans="1:11">
       <c r="A121" t="s">
         <v>492</v>
       </c>
@@ -7646,19 +7646,19 @@
         <v>490</v>
       </c>
       <c r="F121" t="s">
+        <v>234</v>
+      </c>
+      <c r="G121" t="s">
         <v>296</v>
       </c>
-      <c r="G121" t="s">
+      <c r="H121" t="s">
+        <v>236</v>
+      </c>
+      <c r="K121" t="s">
         <v>491</v>
       </c>
-      <c r="I121" t="s">
-        <v>237</v>
-      </c>
-      <c r="J121" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
+    </row>
+    <row r="122" spans="1:11">
       <c r="A122" t="s">
         <v>495</v>
       </c>
@@ -7678,16 +7678,16 @@
         <v>352</v>
       </c>
       <c r="G122" t="s">
+        <v>353</v>
+      </c>
+      <c r="H122" t="s">
+        <v>236</v>
+      </c>
+      <c r="K122" t="s">
         <v>491</v>
       </c>
-      <c r="I122" t="s">
-        <v>353</v>
-      </c>
-      <c r="J122" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
+    </row>
+    <row r="123" spans="1:11">
       <c r="A123" t="s">
         <v>498</v>
       </c>
@@ -7707,16 +7707,16 @@
         <v>352</v>
       </c>
       <c r="G123" t="s">
+        <v>353</v>
+      </c>
+      <c r="H123" t="s">
+        <v>236</v>
+      </c>
+      <c r="K123" t="s">
         <v>491</v>
       </c>
-      <c r="I123" t="s">
-        <v>353</v>
-      </c>
-      <c r="J123" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
+    </row>
+    <row r="124" spans="1:11">
       <c r="A124" t="s">
         <v>501</v>
       </c>
@@ -7736,16 +7736,16 @@
         <v>504</v>
       </c>
       <c r="G124" t="s">
+        <v>505</v>
+      </c>
+      <c r="H124" t="s">
+        <v>339</v>
+      </c>
+      <c r="K124" t="s">
         <v>491</v>
       </c>
-      <c r="I124" t="s">
-        <v>505</v>
-      </c>
-      <c r="J124" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10">
+    </row>
+    <row r="125" spans="1:11">
       <c r="A125" t="s">
         <v>506</v>
       </c>
@@ -7765,16 +7765,16 @@
         <v>504</v>
       </c>
       <c r="G125" t="s">
+        <v>505</v>
+      </c>
+      <c r="H125" t="s">
+        <v>339</v>
+      </c>
+      <c r="K125" t="s">
         <v>491</v>
       </c>
-      <c r="I125" t="s">
-        <v>505</v>
-      </c>
-      <c r="J125" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10">
+    </row>
+    <row r="126" spans="1:11">
       <c r="A126" t="s">
         <v>509</v>
       </c>
@@ -7794,16 +7794,16 @@
         <v>504</v>
       </c>
       <c r="G126" t="s">
+        <v>505</v>
+      </c>
+      <c r="H126" t="s">
+        <v>339</v>
+      </c>
+      <c r="K126" t="s">
         <v>491</v>
       </c>
-      <c r="I126" t="s">
-        <v>505</v>
-      </c>
-      <c r="J126" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10">
+    </row>
+    <row r="127" spans="1:11">
       <c r="A127" t="s">
         <v>512</v>
       </c>
@@ -7823,16 +7823,16 @@
         <v>504</v>
       </c>
       <c r="G127" t="s">
+        <v>505</v>
+      </c>
+      <c r="H127" t="s">
+        <v>339</v>
+      </c>
+      <c r="K127" t="s">
         <v>491</v>
       </c>
-      <c r="I127" t="s">
-        <v>505</v>
-      </c>
-      <c r="J127" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10">
+    </row>
+    <row r="128" spans="1:11">
       <c r="A128" t="s">
         <v>515</v>
       </c>
@@ -7852,13 +7852,13 @@
         <v>504</v>
       </c>
       <c r="G128" t="s">
+        <v>505</v>
+      </c>
+      <c r="H128" t="s">
+        <v>339</v>
+      </c>
+      <c r="K128" t="s">
         <v>491</v>
-      </c>
-      <c r="I128" t="s">
-        <v>505</v>
-      </c>
-      <c r="J128" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -7878,16 +7878,16 @@
         <v>490</v>
       </c>
       <c r="F129" t="s">
+        <v>504</v>
+      </c>
+      <c r="G129" t="s">
         <v>521</v>
       </c>
-      <c r="G129" t="s">
+      <c r="H129" t="s">
+        <v>339</v>
+      </c>
+      <c r="K129" t="s">
         <v>491</v>
-      </c>
-      <c r="I129" t="s">
-        <v>505</v>
-      </c>
-      <c r="J129" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7907,16 +7907,16 @@
         <v>490</v>
       </c>
       <c r="F130" t="s">
+        <v>504</v>
+      </c>
+      <c r="G130" t="s">
         <v>525</v>
       </c>
-      <c r="G130" t="s">
+      <c r="H130" t="s">
+        <v>339</v>
+      </c>
+      <c r="K130" t="s">
         <v>491</v>
-      </c>
-      <c r="I130" t="s">
-        <v>505</v>
-      </c>
-      <c r="J130" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7936,16 +7936,16 @@
         <v>490</v>
       </c>
       <c r="F131" t="s">
+        <v>504</v>
+      </c>
+      <c r="G131" t="s">
         <v>529</v>
       </c>
-      <c r="G131" t="s">
+      <c r="H131" t="s">
+        <v>339</v>
+      </c>
+      <c r="K131" t="s">
         <v>491</v>
-      </c>
-      <c r="I131" t="s">
-        <v>505</v>
-      </c>
-      <c r="J131" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7968,13 +7968,13 @@
         <v>533</v>
       </c>
       <c r="G132" t="s">
+        <v>534</v>
+      </c>
+      <c r="H132" t="s">
+        <v>339</v>
+      </c>
+      <c r="K132" t="s">
         <v>491</v>
-      </c>
-      <c r="I132" t="s">
-        <v>534</v>
-      </c>
-      <c r="J132" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -7994,13 +7994,13 @@
         <v>392</v>
       </c>
       <c r="G133" t="s">
+        <v>393</v>
+      </c>
+      <c r="H133" t="s">
+        <v>236</v>
+      </c>
+      <c r="K133" t="s">
         <v>491</v>
-      </c>
-      <c r="I133" t="s">
-        <v>393</v>
-      </c>
-      <c r="J133" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -8023,13 +8023,13 @@
         <v>361</v>
       </c>
       <c r="G134" t="s">
+        <v>362</v>
+      </c>
+      <c r="H134" t="s">
+        <v>339</v>
+      </c>
+      <c r="K134" t="s">
         <v>541</v>
-      </c>
-      <c r="I134" t="s">
-        <v>362</v>
-      </c>
-      <c r="J134" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -8049,13 +8049,13 @@
         <v>361</v>
       </c>
       <c r="G135" t="s">
+        <v>362</v>
+      </c>
+      <c r="H135" t="s">
+        <v>339</v>
+      </c>
+      <c r="K135" t="s">
         <v>541</v>
-      </c>
-      <c r="I135" t="s">
-        <v>362</v>
-      </c>
-      <c r="J135" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -8078,13 +8078,13 @@
         <v>361</v>
       </c>
       <c r="G136" t="s">
+        <v>362</v>
+      </c>
+      <c r="H136" t="s">
+        <v>339</v>
+      </c>
+      <c r="K136" t="s">
         <v>541</v>
-      </c>
-      <c r="I136" t="s">
-        <v>362</v>
-      </c>
-      <c r="J136" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -8107,13 +8107,13 @@
         <v>361</v>
       </c>
       <c r="G137" t="s">
+        <v>362</v>
+      </c>
+      <c r="H137" t="s">
+        <v>339</v>
+      </c>
+      <c r="K137" t="s">
         <v>541</v>
-      </c>
-      <c r="I137" t="s">
-        <v>362</v>
-      </c>
-      <c r="J137" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -8136,13 +8136,13 @@
         <v>361</v>
       </c>
       <c r="G138" t="s">
+        <v>362</v>
+      </c>
+      <c r="H138" t="s">
+        <v>339</v>
+      </c>
+      <c r="K138" t="s">
         <v>541</v>
-      </c>
-      <c r="I138" t="s">
-        <v>362</v>
-      </c>
-      <c r="J138" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -8165,13 +8165,13 @@
         <v>556</v>
       </c>
       <c r="G139" t="s">
+        <v>557</v>
+      </c>
+      <c r="H139" t="s">
+        <v>464</v>
+      </c>
+      <c r="K139" t="s">
         <v>541</v>
-      </c>
-      <c r="I139" t="s">
-        <v>557</v>
-      </c>
-      <c r="J139" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -8194,13 +8194,13 @@
         <v>361</v>
       </c>
       <c r="G140" t="s">
+        <v>362</v>
+      </c>
+      <c r="H140" t="s">
+        <v>339</v>
+      </c>
+      <c r="K140" t="s">
         <v>541</v>
-      </c>
-      <c r="I140" t="s">
-        <v>362</v>
-      </c>
-      <c r="J140" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -8226,13 +8226,13 @@
         <v>566</v>
       </c>
       <c r="H141" t="s">
+        <v>339</v>
+      </c>
+      <c r="I141" t="s">
         <v>567</v>
       </c>
-      <c r="I141" t="s">
+      <c r="J141" t="s">
         <v>568</v>
-      </c>
-      <c r="J141" t="s">
-        <v>339</v>
       </c>
       <c r="K141" t="s">
         <v>569</v>
@@ -8258,13 +8258,13 @@
         <v>566</v>
       </c>
       <c r="H142" t="s">
+        <v>339</v>
+      </c>
+      <c r="I142" t="s">
         <v>567</v>
       </c>
-      <c r="I142" t="s">
+      <c r="J142" t="s">
         <v>568</v>
-      </c>
-      <c r="J142" t="s">
-        <v>339</v>
       </c>
       <c r="K142" t="s">
         <v>569</v>
@@ -8290,16 +8290,16 @@
         <v>575</v>
       </c>
       <c r="G143" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="H143" t="s">
+        <v>339</v>
+      </c>
+      <c r="I143" t="s">
         <v>567</v>
       </c>
-      <c r="I143" t="s">
-        <v>576</v>
-      </c>
       <c r="J143" t="s">
-        <v>339</v>
+        <v>568</v>
       </c>
       <c r="K143" t="s">
         <v>569</v>
@@ -8325,16 +8325,16 @@
         <v>575</v>
       </c>
       <c r="G144" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="H144" t="s">
+        <v>339</v>
+      </c>
+      <c r="I144" t="s">
         <v>567</v>
       </c>
-      <c r="I144" t="s">
-        <v>576</v>
-      </c>
       <c r="J144" t="s">
-        <v>339</v>
+        <v>568</v>
       </c>
       <c r="K144" t="s">
         <v>569</v>
@@ -8360,16 +8360,16 @@
         <v>575</v>
       </c>
       <c r="G145" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="H145" t="s">
+        <v>339</v>
+      </c>
+      <c r="I145" t="s">
         <v>567</v>
       </c>
-      <c r="I145" t="s">
-        <v>576</v>
-      </c>
       <c r="J145" t="s">
-        <v>339</v>
+        <v>568</v>
       </c>
       <c r="K145" t="s">
         <v>569</v>
@@ -8398,13 +8398,13 @@
         <v>566</v>
       </c>
       <c r="H146" t="s">
+        <v>339</v>
+      </c>
+      <c r="I146" t="s">
         <v>567</v>
       </c>
-      <c r="I146" t="s">
+      <c r="J146" t="s">
         <v>568</v>
-      </c>
-      <c r="J146" t="s">
-        <v>339</v>
       </c>
       <c r="K146" t="s">
         <v>569</v>
@@ -8433,16 +8433,16 @@
         <v>566</v>
       </c>
       <c r="H147" t="s">
+        <v>339</v>
+      </c>
+      <c r="I147" t="s">
         <v>589</v>
       </c>
-      <c r="I147" t="s">
-        <v>568</v>
-      </c>
       <c r="J147" t="s">
-        <v>339</v>
+        <v>590</v>
       </c>
       <c r="K147" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -8468,16 +8468,16 @@
         <v>566</v>
       </c>
       <c r="H148" t="s">
+        <v>339</v>
+      </c>
+      <c r="I148" t="s">
         <v>589</v>
       </c>
-      <c r="I148" t="s">
-        <v>568</v>
-      </c>
       <c r="J148" t="s">
-        <v>339</v>
+        <v>590</v>
       </c>
       <c r="K148" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -8503,16 +8503,16 @@
         <v>566</v>
       </c>
       <c r="H149" t="s">
+        <v>339</v>
+      </c>
+      <c r="I149" t="s">
         <v>589</v>
       </c>
-      <c r="I149" t="s">
-        <v>568</v>
-      </c>
       <c r="J149" t="s">
-        <v>339</v>
+        <v>590</v>
       </c>
       <c r="K149" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -8538,16 +8538,16 @@
         <v>566</v>
       </c>
       <c r="H150" t="s">
+        <v>339</v>
+      </c>
+      <c r="I150" t="s">
         <v>589</v>
       </c>
-      <c r="I150" t="s">
-        <v>568</v>
-      </c>
       <c r="J150" t="s">
-        <v>339</v>
+        <v>590</v>
       </c>
       <c r="K150" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -8573,16 +8573,16 @@
         <v>566</v>
       </c>
       <c r="H151" t="s">
+        <v>339</v>
+      </c>
+      <c r="I151" t="s">
         <v>589</v>
       </c>
-      <c r="I151" t="s">
-        <v>568</v>
-      </c>
       <c r="J151" t="s">
-        <v>339</v>
+        <v>590</v>
       </c>
       <c r="K151" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -8608,16 +8608,16 @@
         <v>566</v>
       </c>
       <c r="H152" t="s">
+        <v>339</v>
+      </c>
+      <c r="I152" t="s">
         <v>589</v>
       </c>
-      <c r="I152" t="s">
-        <v>568</v>
-      </c>
       <c r="J152" t="s">
-        <v>339</v>
+        <v>590</v>
       </c>
       <c r="K152" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -8643,16 +8643,16 @@
         <v>566</v>
       </c>
       <c r="H153" t="s">
+        <v>339</v>
+      </c>
+      <c r="I153" t="s">
         <v>589</v>
       </c>
-      <c r="I153" t="s">
-        <v>568</v>
-      </c>
       <c r="J153" t="s">
-        <v>339</v>
+        <v>590</v>
       </c>
       <c r="K153" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -8678,16 +8678,16 @@
         <v>566</v>
       </c>
       <c r="H154" t="s">
+        <v>339</v>
+      </c>
+      <c r="I154" t="s">
         <v>589</v>
       </c>
-      <c r="I154" t="s">
-        <v>568</v>
-      </c>
       <c r="J154" t="s">
-        <v>339</v>
+        <v>590</v>
       </c>
       <c r="K154" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -8713,16 +8713,16 @@
         <v>566</v>
       </c>
       <c r="H155" t="s">
+        <v>339</v>
+      </c>
+      <c r="I155" t="s">
         <v>589</v>
       </c>
-      <c r="I155" t="s">
-        <v>568</v>
-      </c>
       <c r="J155" t="s">
-        <v>339</v>
+        <v>590</v>
       </c>
       <c r="K155" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -8748,16 +8748,16 @@
         <v>566</v>
       </c>
       <c r="H156" t="s">
+        <v>339</v>
+      </c>
+      <c r="I156" t="s">
         <v>618</v>
       </c>
-      <c r="I156" t="s">
-        <v>568</v>
-      </c>
       <c r="J156" t="s">
-        <v>339</v>
+        <v>619</v>
       </c>
       <c r="K156" t="s">
-        <v>619</v>
+        <v>569</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -8777,22 +8777,22 @@
         <v>564</v>
       </c>
       <c r="F157" t="s">
+        <v>565</v>
+      </c>
+      <c r="G157" t="s">
         <v>623</v>
       </c>
-      <c r="G157" t="s">
-        <v>566</v>
-      </c>
       <c r="H157" t="s">
+        <v>339</v>
+      </c>
+      <c r="I157" t="s">
         <v>618</v>
       </c>
-      <c r="I157" t="s">
-        <v>568</v>
-      </c>
       <c r="J157" t="s">
-        <v>339</v>
+        <v>619</v>
       </c>
       <c r="K157" t="s">
-        <v>619</v>
+        <v>569</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -8818,16 +8818,16 @@
         <v>566</v>
       </c>
       <c r="H158" t="s">
+        <v>339</v>
+      </c>
+      <c r="I158" t="s">
         <v>618</v>
       </c>
-      <c r="I158" t="s">
-        <v>568</v>
-      </c>
       <c r="J158" t="s">
-        <v>339</v>
+        <v>619</v>
       </c>
       <c r="K158" t="s">
-        <v>619</v>
+        <v>569</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -8853,16 +8853,16 @@
         <v>566</v>
       </c>
       <c r="H159" t="s">
+        <v>339</v>
+      </c>
+      <c r="I159" t="s">
         <v>618</v>
       </c>
-      <c r="I159" t="s">
-        <v>568</v>
-      </c>
       <c r="J159" t="s">
-        <v>339</v>
+        <v>619</v>
       </c>
       <c r="K159" t="s">
-        <v>619</v>
+        <v>569</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -8888,16 +8888,16 @@
         <v>566</v>
       </c>
       <c r="H160" t="s">
+        <v>339</v>
+      </c>
+      <c r="I160" t="s">
         <v>618</v>
       </c>
-      <c r="I160" t="s">
-        <v>568</v>
-      </c>
       <c r="J160" t="s">
-        <v>339</v>
+        <v>619</v>
       </c>
       <c r="K160" t="s">
-        <v>619</v>
+        <v>569</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -8923,16 +8923,16 @@
         <v>566</v>
       </c>
       <c r="H161" t="s">
+        <v>339</v>
+      </c>
+      <c r="I161" t="s">
         <v>618</v>
       </c>
-      <c r="I161" t="s">
-        <v>568</v>
-      </c>
       <c r="J161" t="s">
-        <v>339</v>
+        <v>619</v>
       </c>
       <c r="K161" t="s">
-        <v>619</v>
+        <v>569</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -8958,16 +8958,16 @@
         <v>566</v>
       </c>
       <c r="H162" t="s">
+        <v>339</v>
+      </c>
+      <c r="I162" t="s">
         <v>639</v>
       </c>
-      <c r="I162" t="s">
-        <v>568</v>
-      </c>
       <c r="J162" t="s">
-        <v>339</v>
+        <v>640</v>
       </c>
       <c r="K162" t="s">
-        <v>640</v>
+        <v>569</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -8987,22 +8987,22 @@
         <v>564</v>
       </c>
       <c r="F163" t="s">
+        <v>565</v>
+      </c>
+      <c r="G163" t="s">
         <v>644</v>
       </c>
-      <c r="G163" t="s">
-        <v>566</v>
-      </c>
       <c r="H163" t="s">
+        <v>339</v>
+      </c>
+      <c r="I163" t="s">
         <v>642</v>
       </c>
-      <c r="I163" t="s">
-        <v>568</v>
-      </c>
       <c r="J163" t="s">
-        <v>339</v>
+        <v>645</v>
       </c>
       <c r="K163" t="s">
-        <v>645</v>
+        <v>569</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -9028,16 +9028,16 @@
         <v>566</v>
       </c>
       <c r="H164" t="s">
+        <v>339</v>
+      </c>
+      <c r="I164" t="s">
         <v>649</v>
       </c>
-      <c r="I164" t="s">
-        <v>568</v>
-      </c>
       <c r="J164" t="s">
-        <v>339</v>
+        <v>650</v>
       </c>
       <c r="K164" t="s">
-        <v>650</v>
+        <v>569</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -9063,16 +9063,16 @@
         <v>566</v>
       </c>
       <c r="H165" t="s">
+        <v>339</v>
+      </c>
+      <c r="I165" t="s">
         <v>649</v>
       </c>
-      <c r="I165" t="s">
-        <v>568</v>
-      </c>
       <c r="J165" t="s">
-        <v>339</v>
+        <v>650</v>
       </c>
       <c r="K165" t="s">
-        <v>650</v>
+        <v>569</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -9098,16 +9098,16 @@
         <v>566</v>
       </c>
       <c r="H166" t="s">
+        <v>339</v>
+      </c>
+      <c r="I166" t="s">
         <v>649</v>
       </c>
-      <c r="I166" t="s">
-        <v>568</v>
-      </c>
       <c r="J166" t="s">
-        <v>339</v>
+        <v>650</v>
       </c>
       <c r="K166" t="s">
-        <v>650</v>
+        <v>569</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -9133,16 +9133,16 @@
         <v>566</v>
       </c>
       <c r="H167" t="s">
+        <v>339</v>
+      </c>
+      <c r="I167" t="s">
         <v>649</v>
       </c>
-      <c r="I167" t="s">
-        <v>568</v>
-      </c>
       <c r="J167" t="s">
-        <v>339</v>
+        <v>650</v>
       </c>
       <c r="K167" t="s">
-        <v>650</v>
+        <v>569</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -9162,22 +9162,22 @@
         <v>564</v>
       </c>
       <c r="F168" t="s">
+        <v>565</v>
+      </c>
+      <c r="G168" t="s">
         <v>663</v>
       </c>
-      <c r="G168" t="s">
-        <v>566</v>
-      </c>
       <c r="H168" t="s">
+        <v>339</v>
+      </c>
+      <c r="I168" t="s">
         <v>649</v>
       </c>
-      <c r="I168" t="s">
-        <v>568</v>
-      </c>
       <c r="J168" t="s">
-        <v>339</v>
+        <v>650</v>
       </c>
       <c r="K168" t="s">
-        <v>650</v>
+        <v>569</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -9194,22 +9194,22 @@
         <v>564</v>
       </c>
       <c r="F169" t="s">
+        <v>565</v>
+      </c>
+      <c r="G169" t="s">
         <v>663</v>
       </c>
-      <c r="G169" t="s">
-        <v>566</v>
-      </c>
       <c r="H169" t="s">
+        <v>339</v>
+      </c>
+      <c r="I169" t="s">
         <v>649</v>
       </c>
-      <c r="I169" t="s">
-        <v>568</v>
-      </c>
       <c r="J169" t="s">
-        <v>339</v>
+        <v>650</v>
       </c>
       <c r="K169" t="s">
-        <v>650</v>
+        <v>569</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -9235,16 +9235,16 @@
         <v>566</v>
       </c>
       <c r="H170" t="s">
+        <v>339</v>
+      </c>
+      <c r="I170" t="s">
         <v>649</v>
       </c>
-      <c r="I170" t="s">
-        <v>568</v>
-      </c>
       <c r="J170" t="s">
-        <v>339</v>
+        <v>650</v>
       </c>
       <c r="K170" t="s">
-        <v>650</v>
+        <v>569</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -9267,13 +9267,13 @@
         <v>337</v>
       </c>
       <c r="G171" t="s">
+        <v>338</v>
+      </c>
+      <c r="H171" t="s">
+        <v>339</v>
+      </c>
+      <c r="K171" t="s">
         <v>673</v>
-      </c>
-      <c r="I171" t="s">
-        <v>338</v>
-      </c>
-      <c r="J171" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -9296,13 +9296,13 @@
         <v>243</v>
       </c>
       <c r="G172" t="s">
+        <v>244</v>
+      </c>
+      <c r="H172" t="s">
+        <v>236</v>
+      </c>
+      <c r="K172" t="s">
         <v>673</v>
-      </c>
-      <c r="I172" t="s">
-        <v>244</v>
-      </c>
-      <c r="J172" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -9325,13 +9325,13 @@
         <v>337</v>
       </c>
       <c r="G173" t="s">
+        <v>338</v>
+      </c>
+      <c r="H173" t="s">
+        <v>339</v>
+      </c>
+      <c r="K173" t="s">
         <v>673</v>
-      </c>
-      <c r="I173" t="s">
-        <v>338</v>
-      </c>
-      <c r="J173" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -9354,13 +9354,13 @@
         <v>337</v>
       </c>
       <c r="G174" t="s">
+        <v>338</v>
+      </c>
+      <c r="H174" t="s">
+        <v>339</v>
+      </c>
+      <c r="K174" t="s">
         <v>673</v>
-      </c>
-      <c r="I174" t="s">
-        <v>338</v>
-      </c>
-      <c r="J174" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -9383,13 +9383,13 @@
         <v>337</v>
       </c>
       <c r="G175" t="s">
+        <v>338</v>
+      </c>
+      <c r="H175" t="s">
+        <v>339</v>
+      </c>
+      <c r="K175" t="s">
         <v>673</v>
-      </c>
-      <c r="I175" t="s">
-        <v>338</v>
-      </c>
-      <c r="J175" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -9409,13 +9409,13 @@
         <v>337</v>
       </c>
       <c r="G176" t="s">
+        <v>338</v>
+      </c>
+      <c r="H176" t="s">
+        <v>339</v>
+      </c>
+      <c r="K176" t="s">
         <v>673</v>
-      </c>
-      <c r="I176" t="s">
-        <v>338</v>
-      </c>
-      <c r="J176" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -9438,13 +9438,13 @@
         <v>337</v>
       </c>
       <c r="G177" t="s">
+        <v>338</v>
+      </c>
+      <c r="H177" t="s">
+        <v>339</v>
+      </c>
+      <c r="K177" t="s">
         <v>692</v>
-      </c>
-      <c r="I177" t="s">
-        <v>338</v>
-      </c>
-      <c r="J177" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -9467,13 +9467,13 @@
         <v>337</v>
       </c>
       <c r="G178" t="s">
+        <v>338</v>
+      </c>
+      <c r="H178" t="s">
+        <v>339</v>
+      </c>
+      <c r="K178" t="s">
         <v>692</v>
-      </c>
-      <c r="I178" t="s">
-        <v>338</v>
-      </c>
-      <c r="J178" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -9496,13 +9496,13 @@
         <v>337</v>
       </c>
       <c r="G179" t="s">
+        <v>338</v>
+      </c>
+      <c r="H179" t="s">
+        <v>339</v>
+      </c>
+      <c r="K179" t="s">
         <v>692</v>
-      </c>
-      <c r="I179" t="s">
-        <v>338</v>
-      </c>
-      <c r="J179" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -9525,13 +9525,13 @@
         <v>337</v>
       </c>
       <c r="G180" t="s">
+        <v>338</v>
+      </c>
+      <c r="H180" t="s">
+        <v>339</v>
+      </c>
+      <c r="K180" t="s">
         <v>692</v>
-      </c>
-      <c r="I180" t="s">
-        <v>338</v>
-      </c>
-      <c r="J180" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -9557,13 +9557,13 @@
         <v>707</v>
       </c>
       <c r="H181" t="s">
+        <v>339</v>
+      </c>
+      <c r="I181" t="s">
         <v>708</v>
       </c>
-      <c r="I181" t="s">
+      <c r="J181" t="s">
         <v>709</v>
-      </c>
-      <c r="J181" t="s">
-        <v>339</v>
       </c>
       <c r="K181" t="s">
         <v>710</v>
@@ -9592,13 +9592,13 @@
         <v>707</v>
       </c>
       <c r="H182" t="s">
+        <v>339</v>
+      </c>
+      <c r="I182" t="s">
         <v>708</v>
       </c>
-      <c r="I182" t="s">
+      <c r="J182" t="s">
         <v>709</v>
-      </c>
-      <c r="J182" t="s">
-        <v>339</v>
       </c>
       <c r="K182" t="s">
         <v>710</v>
@@ -9627,13 +9627,13 @@
         <v>707</v>
       </c>
       <c r="H183" t="s">
+        <v>339</v>
+      </c>
+      <c r="I183" t="s">
         <v>708</v>
       </c>
-      <c r="I183" t="s">
+      <c r="J183" t="s">
         <v>709</v>
-      </c>
-      <c r="J183" t="s">
-        <v>339</v>
       </c>
       <c r="K183" t="s">
         <v>710</v>
@@ -9662,13 +9662,13 @@
         <v>707</v>
       </c>
       <c r="H184" t="s">
+        <v>339</v>
+      </c>
+      <c r="I184" t="s">
         <v>708</v>
       </c>
-      <c r="I184" t="s">
+      <c r="J184" t="s">
         <v>709</v>
-      </c>
-      <c r="J184" t="s">
-        <v>339</v>
       </c>
       <c r="K184" t="s">
         <v>710</v>
@@ -9697,13 +9697,13 @@
         <v>707</v>
       </c>
       <c r="H185" t="s">
+        <v>339</v>
+      </c>
+      <c r="I185" t="s">
         <v>708</v>
       </c>
-      <c r="I185" t="s">
+      <c r="J185" t="s">
         <v>709</v>
-      </c>
-      <c r="J185" t="s">
-        <v>339</v>
       </c>
       <c r="K185" t="s">
         <v>710</v>
@@ -9732,13 +9732,13 @@
         <v>707</v>
       </c>
       <c r="H186" t="s">
+        <v>339</v>
+      </c>
+      <c r="I186" t="s">
         <v>708</v>
       </c>
-      <c r="I186" t="s">
+      <c r="J186" t="s">
         <v>709</v>
-      </c>
-      <c r="J186" t="s">
-        <v>339</v>
       </c>
       <c r="K186" t="s">
         <v>710</v>
@@ -9767,13 +9767,13 @@
         <v>707</v>
       </c>
       <c r="H187" t="s">
+        <v>339</v>
+      </c>
+      <c r="I187" t="s">
         <v>708</v>
       </c>
-      <c r="I187" t="s">
+      <c r="J187" t="s">
         <v>709</v>
-      </c>
-      <c r="J187" t="s">
-        <v>339</v>
       </c>
       <c r="K187" t="s">
         <v>710</v>
@@ -9802,13 +9802,13 @@
         <v>707</v>
       </c>
       <c r="H188" t="s">
+        <v>339</v>
+      </c>
+      <c r="I188" t="s">
         <v>708</v>
       </c>
-      <c r="I188" t="s">
+      <c r="J188" t="s">
         <v>709</v>
-      </c>
-      <c r="J188" t="s">
-        <v>339</v>
       </c>
       <c r="K188" t="s">
         <v>710</v>
@@ -9837,13 +9837,13 @@
         <v>707</v>
       </c>
       <c r="H189" t="s">
+        <v>339</v>
+      </c>
+      <c r="I189" t="s">
         <v>708</v>
       </c>
-      <c r="I189" t="s">
+      <c r="J189" t="s">
         <v>709</v>
-      </c>
-      <c r="J189" t="s">
-        <v>339</v>
       </c>
       <c r="K189" t="s">
         <v>710</v>
@@ -9872,13 +9872,13 @@
         <v>707</v>
       </c>
       <c r="H190" t="s">
+        <v>339</v>
+      </c>
+      <c r="I190" t="s">
         <v>708</v>
       </c>
-      <c r="I190" t="s">
+      <c r="J190" t="s">
         <v>709</v>
-      </c>
-      <c r="J190" t="s">
-        <v>339</v>
       </c>
       <c r="K190" t="s">
         <v>710</v>
@@ -9907,13 +9907,13 @@
         <v>707</v>
       </c>
       <c r="H191" t="s">
+        <v>339</v>
+      </c>
+      <c r="I191" t="s">
         <v>708</v>
       </c>
-      <c r="I191" t="s">
+      <c r="J191" t="s">
         <v>709</v>
-      </c>
-      <c r="J191" t="s">
-        <v>339</v>
       </c>
       <c r="K191" t="s">
         <v>710</v>
@@ -9939,13 +9939,13 @@
         <v>707</v>
       </c>
       <c r="H192" t="s">
+        <v>339</v>
+      </c>
+      <c r="I192" t="s">
         <v>708</v>
       </c>
-      <c r="I192" t="s">
+      <c r="J192" t="s">
         <v>709</v>
-      </c>
-      <c r="J192" t="s">
-        <v>339</v>
       </c>
       <c r="K192" t="s">
         <v>710</v>
@@ -9968,19 +9968,19 @@
         <v>705</v>
       </c>
       <c r="F193" t="s">
+        <v>575</v>
+      </c>
+      <c r="G193" t="s">
         <v>746</v>
       </c>
-      <c r="G193" t="s">
-        <v>707</v>
-      </c>
       <c r="H193" t="s">
+        <v>339</v>
+      </c>
+      <c r="I193" t="s">
         <v>708</v>
       </c>
-      <c r="I193" t="s">
-        <v>576</v>
-      </c>
       <c r="J193" t="s">
-        <v>339</v>
+        <v>709</v>
       </c>
       <c r="K193" t="s">
         <v>710</v>
@@ -10009,13 +10009,13 @@
         <v>707</v>
       </c>
       <c r="H194" t="s">
+        <v>339</v>
+      </c>
+      <c r="I194" t="s">
         <v>708</v>
       </c>
-      <c r="I194" t="s">
+      <c r="J194" t="s">
         <v>709</v>
-      </c>
-      <c r="J194" t="s">
-        <v>339</v>
       </c>
       <c r="K194" t="s">
         <v>710</v>
@@ -10044,13 +10044,13 @@
         <v>707</v>
       </c>
       <c r="H195" t="s">
+        <v>339</v>
+      </c>
+      <c r="I195" t="s">
         <v>708</v>
       </c>
-      <c r="I195" t="s">
+      <c r="J195" t="s">
         <v>709</v>
-      </c>
-      <c r="J195" t="s">
-        <v>339</v>
       </c>
       <c r="K195" t="s">
         <v>710</v>
@@ -10079,13 +10079,13 @@
         <v>707</v>
       </c>
       <c r="H196" t="s">
+        <v>339</v>
+      </c>
+      <c r="I196" t="s">
         <v>708</v>
       </c>
-      <c r="I196" t="s">
+      <c r="J196" t="s">
         <v>709</v>
-      </c>
-      <c r="J196" t="s">
-        <v>339</v>
       </c>
       <c r="K196" t="s">
         <v>710</v>
@@ -10114,13 +10114,13 @@
         <v>707</v>
       </c>
       <c r="H197" t="s">
+        <v>339</v>
+      </c>
+      <c r="I197" t="s">
         <v>708</v>
       </c>
-      <c r="I197" t="s">
+      <c r="J197" t="s">
         <v>709</v>
-      </c>
-      <c r="J197" t="s">
-        <v>339</v>
       </c>
       <c r="K197" t="s">
         <v>710</v>
@@ -10149,13 +10149,13 @@
         <v>707</v>
       </c>
       <c r="H198" t="s">
+        <v>339</v>
+      </c>
+      <c r="I198" t="s">
         <v>708</v>
       </c>
-      <c r="I198" t="s">
+      <c r="J198" t="s">
         <v>709</v>
-      </c>
-      <c r="J198" t="s">
-        <v>339</v>
       </c>
       <c r="K198" t="s">
         <v>710</v>
@@ -10178,22 +10178,22 @@
         <v>705</v>
       </c>
       <c r="F199" t="s">
+        <v>706</v>
+      </c>
+      <c r="G199" t="s">
         <v>765</v>
       </c>
-      <c r="G199" t="s">
-        <v>707</v>
-      </c>
       <c r="H199" t="s">
+        <v>339</v>
+      </c>
+      <c r="I199" t="s">
         <v>766</v>
       </c>
-      <c r="I199" t="s">
-        <v>709</v>
-      </c>
       <c r="J199" t="s">
-        <v>339</v>
+        <v>767</v>
       </c>
       <c r="K199" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -10213,22 +10213,22 @@
         <v>705</v>
       </c>
       <c r="F200" t="s">
+        <v>706</v>
+      </c>
+      <c r="G200" t="s">
         <v>765</v>
       </c>
-      <c r="G200" t="s">
-        <v>707</v>
-      </c>
       <c r="H200" t="s">
+        <v>339</v>
+      </c>
+      <c r="I200" t="s">
         <v>766</v>
       </c>
-      <c r="I200" t="s">
-        <v>709</v>
-      </c>
       <c r="J200" t="s">
-        <v>339</v>
+        <v>767</v>
       </c>
       <c r="K200" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -10248,22 +10248,22 @@
         <v>705</v>
       </c>
       <c r="F201" t="s">
+        <v>706</v>
+      </c>
+      <c r="G201" t="s">
         <v>765</v>
       </c>
-      <c r="G201" t="s">
-        <v>707</v>
-      </c>
       <c r="H201" t="s">
+        <v>339</v>
+      </c>
+      <c r="I201" t="s">
         <v>766</v>
       </c>
-      <c r="I201" t="s">
-        <v>709</v>
-      </c>
       <c r="J201" t="s">
-        <v>339</v>
+        <v>767</v>
       </c>
       <c r="K201" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -10280,22 +10280,22 @@
         <v>705</v>
       </c>
       <c r="F202" t="s">
+        <v>706</v>
+      </c>
+      <c r="G202" t="s">
         <v>765</v>
       </c>
-      <c r="G202" t="s">
-        <v>707</v>
-      </c>
       <c r="H202" t="s">
+        <v>339</v>
+      </c>
+      <c r="I202" t="s">
         <v>766</v>
       </c>
-      <c r="I202" t="s">
-        <v>709</v>
-      </c>
       <c r="J202" t="s">
-        <v>339</v>
+        <v>767</v>
       </c>
       <c r="K202" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -10315,22 +10315,22 @@
         <v>705</v>
       </c>
       <c r="F203" t="s">
+        <v>575</v>
+      </c>
+      <c r="G203" t="s">
         <v>746</v>
       </c>
-      <c r="G203" t="s">
-        <v>707</v>
-      </c>
       <c r="H203" t="s">
+        <v>339</v>
+      </c>
+      <c r="I203" t="s">
         <v>766</v>
       </c>
-      <c r="I203" t="s">
-        <v>576</v>
-      </c>
       <c r="J203" t="s">
-        <v>339</v>
+        <v>767</v>
       </c>
       <c r="K203" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10347,22 +10347,22 @@
         <v>705</v>
       </c>
       <c r="F204" t="s">
+        <v>706</v>
+      </c>
+      <c r="G204" t="s">
         <v>765</v>
       </c>
-      <c r="G204" t="s">
-        <v>707</v>
-      </c>
       <c r="H204" t="s">
+        <v>339</v>
+      </c>
+      <c r="I204" t="s">
         <v>766</v>
       </c>
-      <c r="I204" t="s">
-        <v>709</v>
-      </c>
       <c r="J204" t="s">
-        <v>339</v>
+        <v>767</v>
       </c>
       <c r="K204" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -10382,22 +10382,22 @@
         <v>705</v>
       </c>
       <c r="F205" t="s">
+        <v>706</v>
+      </c>
+      <c r="G205" t="s">
         <v>784</v>
       </c>
-      <c r="G205" t="s">
-        <v>707</v>
-      </c>
       <c r="H205" t="s">
+        <v>339</v>
+      </c>
+      <c r="I205" t="s">
         <v>785</v>
       </c>
-      <c r="I205" t="s">
-        <v>709</v>
-      </c>
       <c r="J205" t="s">
-        <v>339</v>
+        <v>786</v>
       </c>
       <c r="K205" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -10417,22 +10417,22 @@
         <v>705</v>
       </c>
       <c r="F206" t="s">
+        <v>706</v>
+      </c>
+      <c r="G206" t="s">
         <v>784</v>
       </c>
-      <c r="G206" t="s">
-        <v>707</v>
-      </c>
       <c r="H206" t="s">
+        <v>339</v>
+      </c>
+      <c r="I206" t="s">
         <v>785</v>
       </c>
-      <c r="I206" t="s">
-        <v>709</v>
-      </c>
       <c r="J206" t="s">
-        <v>339</v>
+        <v>786</v>
       </c>
       <c r="K206" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -10449,22 +10449,22 @@
         <v>705</v>
       </c>
       <c r="F207" t="s">
+        <v>706</v>
+      </c>
+      <c r="G207" t="s">
         <v>784</v>
       </c>
-      <c r="G207" t="s">
-        <v>707</v>
-      </c>
       <c r="H207" t="s">
+        <v>339</v>
+      </c>
+      <c r="I207" t="s">
         <v>785</v>
       </c>
-      <c r="I207" t="s">
-        <v>709</v>
-      </c>
       <c r="J207" t="s">
-        <v>339</v>
+        <v>786</v>
       </c>
       <c r="K207" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -10484,22 +10484,22 @@
         <v>705</v>
       </c>
       <c r="F208" t="s">
+        <v>575</v>
+      </c>
+      <c r="G208" t="s">
         <v>746</v>
       </c>
-      <c r="G208" t="s">
-        <v>707</v>
-      </c>
       <c r="H208" t="s">
+        <v>339</v>
+      </c>
+      <c r="I208" t="s">
         <v>785</v>
       </c>
-      <c r="I208" t="s">
-        <v>576</v>
-      </c>
       <c r="J208" t="s">
-        <v>339</v>
+        <v>786</v>
       </c>
       <c r="K208" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10519,22 +10519,22 @@
         <v>705</v>
       </c>
       <c r="F209" t="s">
+        <v>706</v>
+      </c>
+      <c r="G209" t="s">
         <v>784</v>
       </c>
-      <c r="G209" t="s">
-        <v>707</v>
-      </c>
       <c r="H209" t="s">
+        <v>339</v>
+      </c>
+      <c r="I209" t="s">
         <v>785</v>
       </c>
-      <c r="I209" t="s">
-        <v>709</v>
-      </c>
       <c r="J209" t="s">
-        <v>339</v>
+        <v>786</v>
       </c>
       <c r="K209" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -10560,13 +10560,13 @@
         <v>803</v>
       </c>
       <c r="H210" t="s">
+        <v>339</v>
+      </c>
+      <c r="I210" t="s">
         <v>804</v>
       </c>
-      <c r="I210" t="s">
+      <c r="J210" t="s">
         <v>805</v>
-      </c>
-      <c r="J210" t="s">
-        <v>339</v>
       </c>
       <c r="K210" t="s">
         <v>806</v>
@@ -10592,13 +10592,13 @@
         <v>803</v>
       </c>
       <c r="H211" t="s">
+        <v>339</v>
+      </c>
+      <c r="I211" t="s">
         <v>804</v>
       </c>
-      <c r="I211" t="s">
+      <c r="J211" t="s">
         <v>805</v>
-      </c>
-      <c r="J211" t="s">
-        <v>339</v>
       </c>
       <c r="K211" t="s">
         <v>806</v>
@@ -10627,13 +10627,13 @@
         <v>803</v>
       </c>
       <c r="H212" t="s">
+        <v>339</v>
+      </c>
+      <c r="I212" t="s">
         <v>804</v>
       </c>
-      <c r="I212" t="s">
+      <c r="J212" t="s">
         <v>805</v>
-      </c>
-      <c r="J212" t="s">
-        <v>339</v>
       </c>
       <c r="K212" t="s">
         <v>806</v>
@@ -10659,13 +10659,13 @@
         <v>803</v>
       </c>
       <c r="H213" t="s">
+        <v>339</v>
+      </c>
+      <c r="I213" t="s">
         <v>804</v>
       </c>
-      <c r="I213" t="s">
+      <c r="J213" t="s">
         <v>805</v>
-      </c>
-      <c r="J213" t="s">
-        <v>339</v>
       </c>
       <c r="K213" t="s">
         <v>806</v>
@@ -10694,13 +10694,13 @@
         <v>803</v>
       </c>
       <c r="H214" t="s">
+        <v>339</v>
+      </c>
+      <c r="I214" t="s">
         <v>804</v>
       </c>
-      <c r="I214" t="s">
+      <c r="J214" t="s">
         <v>805</v>
-      </c>
-      <c r="J214" t="s">
-        <v>339</v>
       </c>
       <c r="K214" t="s">
         <v>806</v>
@@ -10723,19 +10723,19 @@
         <v>801</v>
       </c>
       <c r="F215" t="s">
+        <v>706</v>
+      </c>
+      <c r="G215" t="s">
         <v>765</v>
       </c>
-      <c r="G215" t="s">
-        <v>803</v>
-      </c>
       <c r="H215" t="s">
+        <v>339</v>
+      </c>
+      <c r="I215" t="s">
         <v>804</v>
       </c>
-      <c r="I215" t="s">
-        <v>709</v>
-      </c>
       <c r="J215" t="s">
-        <v>339</v>
+        <v>805</v>
       </c>
       <c r="K215" t="s">
         <v>806</v>
@@ -10764,13 +10764,13 @@
         <v>803</v>
       </c>
       <c r="H216" t="s">
+        <v>339</v>
+      </c>
+      <c r="I216" t="s">
         <v>804</v>
       </c>
-      <c r="I216" t="s">
+      <c r="J216" t="s">
         <v>805</v>
-      </c>
-      <c r="J216" t="s">
-        <v>339</v>
       </c>
       <c r="K216" t="s">
         <v>806</v>
@@ -10799,13 +10799,13 @@
         <v>803</v>
       </c>
       <c r="H217" t="s">
+        <v>339</v>
+      </c>
+      <c r="I217" t="s">
         <v>804</v>
       </c>
-      <c r="I217" t="s">
+      <c r="J217" t="s">
         <v>805</v>
-      </c>
-      <c r="J217" t="s">
-        <v>339</v>
       </c>
       <c r="K217" t="s">
         <v>806</v>
@@ -10831,13 +10831,13 @@
         <v>803</v>
       </c>
       <c r="H218" t="s">
+        <v>339</v>
+      </c>
+      <c r="I218" t="s">
         <v>804</v>
       </c>
-      <c r="I218" t="s">
+      <c r="J218" t="s">
         <v>805</v>
-      </c>
-      <c r="J218" t="s">
-        <v>339</v>
       </c>
       <c r="K218" t="s">
         <v>806</v>
@@ -10863,13 +10863,13 @@
         <v>803</v>
       </c>
       <c r="H219" t="s">
+        <v>339</v>
+      </c>
+      <c r="I219" t="s">
         <v>804</v>
       </c>
-      <c r="I219" t="s">
+      <c r="J219" t="s">
         <v>805</v>
-      </c>
-      <c r="J219" t="s">
-        <v>339</v>
       </c>
       <c r="K219" t="s">
         <v>806</v>
@@ -10892,19 +10892,19 @@
         <v>801</v>
       </c>
       <c r="F220" t="s">
+        <v>565</v>
+      </c>
+      <c r="G220" t="s">
         <v>663</v>
       </c>
-      <c r="G220" t="s">
-        <v>803</v>
-      </c>
       <c r="H220" t="s">
+        <v>339</v>
+      </c>
+      <c r="I220" t="s">
         <v>804</v>
       </c>
-      <c r="I220" t="s">
-        <v>568</v>
-      </c>
       <c r="J220" t="s">
-        <v>339</v>
+        <v>805</v>
       </c>
       <c r="K220" t="s">
         <v>806</v>
@@ -10933,13 +10933,13 @@
         <v>803</v>
       </c>
       <c r="H221" t="s">
+        <v>339</v>
+      </c>
+      <c r="I221" t="s">
         <v>804</v>
       </c>
-      <c r="I221" t="s">
+      <c r="J221" t="s">
         <v>805</v>
-      </c>
-      <c r="J221" t="s">
-        <v>339</v>
       </c>
       <c r="K221" t="s">
         <v>806</v>
@@ -10968,13 +10968,13 @@
         <v>803</v>
       </c>
       <c r="H222" t="s">
+        <v>339</v>
+      </c>
+      <c r="I222" t="s">
         <v>804</v>
       </c>
-      <c r="I222" t="s">
+      <c r="J222" t="s">
         <v>805</v>
-      </c>
-      <c r="J222" t="s">
-        <v>339</v>
       </c>
       <c r="K222" t="s">
         <v>806</v>
@@ -11000,13 +11000,13 @@
         <v>803</v>
       </c>
       <c r="H223" t="s">
+        <v>339</v>
+      </c>
+      <c r="I223" t="s">
         <v>804</v>
       </c>
-      <c r="I223" t="s">
+      <c r="J223" t="s">
         <v>805</v>
-      </c>
-      <c r="J223" t="s">
-        <v>339</v>
       </c>
       <c r="K223" t="s">
         <v>806</v>
@@ -11035,13 +11035,13 @@
         <v>803</v>
       </c>
       <c r="H224" t="s">
+        <v>339</v>
+      </c>
+      <c r="I224" t="s">
         <v>804</v>
       </c>
-      <c r="I224" t="s">
+      <c r="J224" t="s">
         <v>805</v>
-      </c>
-      <c r="J224" t="s">
-        <v>339</v>
       </c>
       <c r="K224" t="s">
         <v>806</v>
@@ -11070,13 +11070,13 @@
         <v>803</v>
       </c>
       <c r="H225" t="s">
+        <v>339</v>
+      </c>
+      <c r="I225" t="s">
         <v>804</v>
       </c>
-      <c r="I225" t="s">
+      <c r="J225" t="s">
         <v>805</v>
-      </c>
-      <c r="J225" t="s">
-        <v>339</v>
       </c>
       <c r="K225" t="s">
         <v>806</v>
@@ -11102,16 +11102,16 @@
         <v>575</v>
       </c>
       <c r="G226" t="s">
-        <v>803</v>
+        <v>576</v>
       </c>
       <c r="H226" t="s">
+        <v>339</v>
+      </c>
+      <c r="I226" t="s">
         <v>804</v>
       </c>
-      <c r="I226" t="s">
-        <v>576</v>
-      </c>
       <c r="J226" t="s">
-        <v>339</v>
+        <v>805</v>
       </c>
       <c r="K226" t="s">
         <v>806</v>
@@ -11140,13 +11140,13 @@
         <v>803</v>
       </c>
       <c r="H227" t="s">
+        <v>339</v>
+      </c>
+      <c r="I227" t="s">
         <v>804</v>
       </c>
-      <c r="I227" t="s">
+      <c r="J227" t="s">
         <v>805</v>
-      </c>
-      <c r="J227" t="s">
-        <v>339</v>
       </c>
       <c r="K227" t="s">
         <v>806</v>
@@ -11172,16 +11172,16 @@
         <v>337</v>
       </c>
       <c r="G228" t="s">
-        <v>803</v>
+        <v>338</v>
       </c>
       <c r="H228" t="s">
+        <v>339</v>
+      </c>
+      <c r="I228" t="s">
         <v>804</v>
       </c>
-      <c r="I228" t="s">
-        <v>338</v>
-      </c>
       <c r="J228" t="s">
-        <v>339</v>
+        <v>805</v>
       </c>
       <c r="K228" t="s">
         <v>806</v>
@@ -11204,22 +11204,22 @@
         <v>801</v>
       </c>
       <c r="F229" t="s">
+        <v>802</v>
+      </c>
+      <c r="G229" t="s">
         <v>859</v>
       </c>
-      <c r="G229" t="s">
-        <v>803</v>
-      </c>
       <c r="H229" t="s">
+        <v>339</v>
+      </c>
+      <c r="I229" t="s">
         <v>860</v>
       </c>
-      <c r="I229" t="s">
-        <v>805</v>
-      </c>
       <c r="J229" t="s">
-        <v>339</v>
+        <v>861</v>
       </c>
       <c r="K229" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -11239,22 +11239,22 @@
         <v>801</v>
       </c>
       <c r="F230" t="s">
+        <v>802</v>
+      </c>
+      <c r="G230" t="s">
         <v>859</v>
       </c>
-      <c r="G230" t="s">
-        <v>803</v>
-      </c>
       <c r="H230" t="s">
+        <v>339</v>
+      </c>
+      <c r="I230" t="s">
         <v>860</v>
       </c>
-      <c r="I230" t="s">
-        <v>805</v>
-      </c>
       <c r="J230" t="s">
-        <v>339</v>
+        <v>861</v>
       </c>
       <c r="K230" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -11274,22 +11274,22 @@
         <v>801</v>
       </c>
       <c r="F231" t="s">
+        <v>565</v>
+      </c>
+      <c r="G231" t="s">
         <v>623</v>
       </c>
-      <c r="G231" t="s">
-        <v>803</v>
-      </c>
       <c r="H231" t="s">
+        <v>339</v>
+      </c>
+      <c r="I231" t="s">
         <v>860</v>
       </c>
-      <c r="I231" t="s">
-        <v>568</v>
-      </c>
       <c r="J231" t="s">
-        <v>339</v>
+        <v>861</v>
       </c>
       <c r="K231" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11309,22 +11309,22 @@
         <v>801</v>
       </c>
       <c r="F232" t="s">
+        <v>565</v>
+      </c>
+      <c r="G232" t="s">
         <v>663</v>
       </c>
-      <c r="G232" t="s">
-        <v>803</v>
-      </c>
       <c r="H232" t="s">
+        <v>339</v>
+      </c>
+      <c r="I232" t="s">
         <v>860</v>
       </c>
-      <c r="I232" t="s">
-        <v>568</v>
-      </c>
       <c r="J232" t="s">
-        <v>339</v>
+        <v>861</v>
       </c>
       <c r="K232" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11344,22 +11344,22 @@
         <v>801</v>
       </c>
       <c r="F233" t="s">
+        <v>802</v>
+      </c>
+      <c r="G233" t="s">
         <v>859</v>
       </c>
-      <c r="G233" t="s">
-        <v>803</v>
-      </c>
       <c r="H233" t="s">
+        <v>339</v>
+      </c>
+      <c r="I233" t="s">
         <v>860</v>
       </c>
-      <c r="I233" t="s">
-        <v>805</v>
-      </c>
       <c r="J233" t="s">
-        <v>339</v>
+        <v>861</v>
       </c>
       <c r="K233" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -11379,22 +11379,22 @@
         <v>801</v>
       </c>
       <c r="F234" t="s">
+        <v>802</v>
+      </c>
+      <c r="G234" t="s">
         <v>859</v>
       </c>
-      <c r="G234" t="s">
-        <v>803</v>
-      </c>
       <c r="H234" t="s">
+        <v>339</v>
+      </c>
+      <c r="I234" t="s">
         <v>860</v>
       </c>
-      <c r="I234" t="s">
-        <v>805</v>
-      </c>
       <c r="J234" t="s">
-        <v>339</v>
+        <v>861</v>
       </c>
       <c r="K234" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -11414,22 +11414,22 @@
         <v>801</v>
       </c>
       <c r="F235" t="s">
+        <v>802</v>
+      </c>
+      <c r="G235" t="s">
         <v>859</v>
       </c>
-      <c r="G235" t="s">
-        <v>803</v>
-      </c>
       <c r="H235" t="s">
+        <v>339</v>
+      </c>
+      <c r="I235" t="s">
         <v>860</v>
       </c>
-      <c r="I235" t="s">
-        <v>805</v>
-      </c>
       <c r="J235" t="s">
-        <v>339</v>
+        <v>861</v>
       </c>
       <c r="K235" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -11449,22 +11449,22 @@
         <v>801</v>
       </c>
       <c r="F236" t="s">
+        <v>802</v>
+      </c>
+      <c r="G236" t="s">
         <v>859</v>
       </c>
-      <c r="G236" t="s">
-        <v>803</v>
-      </c>
       <c r="H236" t="s">
+        <v>339</v>
+      </c>
+      <c r="I236" t="s">
         <v>860</v>
       </c>
-      <c r="I236" t="s">
-        <v>805</v>
-      </c>
       <c r="J236" t="s">
-        <v>339</v>
+        <v>861</v>
       </c>
       <c r="K236" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -11484,22 +11484,22 @@
         <v>801</v>
       </c>
       <c r="F237" t="s">
+        <v>802</v>
+      </c>
+      <c r="G237" t="s">
         <v>859</v>
       </c>
-      <c r="G237" t="s">
-        <v>803</v>
-      </c>
       <c r="H237" t="s">
+        <v>339</v>
+      </c>
+      <c r="I237" t="s">
         <v>860</v>
       </c>
-      <c r="I237" t="s">
-        <v>805</v>
-      </c>
       <c r="J237" t="s">
-        <v>339</v>
+        <v>861</v>
       </c>
       <c r="K237" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -11519,22 +11519,22 @@
         <v>801</v>
       </c>
       <c r="F238" t="s">
+        <v>802</v>
+      </c>
+      <c r="G238" t="s">
         <v>859</v>
       </c>
-      <c r="G238" t="s">
-        <v>803</v>
-      </c>
       <c r="H238" t="s">
+        <v>339</v>
+      </c>
+      <c r="I238" t="s">
         <v>860</v>
       </c>
-      <c r="I238" t="s">
-        <v>805</v>
-      </c>
       <c r="J238" t="s">
-        <v>339</v>
+        <v>861</v>
       </c>
       <c r="K238" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -11554,22 +11554,22 @@
         <v>801</v>
       </c>
       <c r="F239" t="s">
+        <v>802</v>
+      </c>
+      <c r="G239" t="s">
         <v>892</v>
       </c>
-      <c r="G239" t="s">
-        <v>803</v>
-      </c>
       <c r="H239" t="s">
+        <v>339</v>
+      </c>
+      <c r="I239" t="s">
         <v>893</v>
       </c>
-      <c r="I239" t="s">
-        <v>805</v>
-      </c>
       <c r="J239" t="s">
-        <v>339</v>
+        <v>894</v>
       </c>
       <c r="K239" t="s">
-        <v>894</v>
+        <v>806</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -11592,16 +11592,16 @@
         <v>337</v>
       </c>
       <c r="G240" t="s">
+        <v>338</v>
+      </c>
+      <c r="H240" t="s">
+        <v>339</v>
+      </c>
+      <c r="I240" t="s">
+        <v>898</v>
+      </c>
+      <c r="J240" t="s">
         <v>899</v>
-      </c>
-      <c r="H240" t="s">
-        <v>899</v>
-      </c>
-      <c r="I240" t="s">
-        <v>338</v>
-      </c>
-      <c r="J240" t="s">
-        <v>339</v>
       </c>
       <c r="K240" t="s">
         <v>900</v>
@@ -11627,16 +11627,16 @@
         <v>337</v>
       </c>
       <c r="G241" t="s">
+        <v>338</v>
+      </c>
+      <c r="H241" t="s">
+        <v>339</v>
+      </c>
+      <c r="I241" t="s">
+        <v>898</v>
+      </c>
+      <c r="J241" t="s">
         <v>899</v>
-      </c>
-      <c r="H241" t="s">
-        <v>899</v>
-      </c>
-      <c r="I241" t="s">
-        <v>338</v>
-      </c>
-      <c r="J241" t="s">
-        <v>339</v>
       </c>
       <c r="K241" t="s">
         <v>900</v>
@@ -11662,16 +11662,16 @@
         <v>337</v>
       </c>
       <c r="G242" t="s">
+        <v>338</v>
+      </c>
+      <c r="H242" t="s">
+        <v>339</v>
+      </c>
+      <c r="I242" t="s">
+        <v>898</v>
+      </c>
+      <c r="J242" t="s">
         <v>899</v>
-      </c>
-      <c r="H242" t="s">
-        <v>899</v>
-      </c>
-      <c r="I242" t="s">
-        <v>338</v>
-      </c>
-      <c r="J242" t="s">
-        <v>339</v>
       </c>
       <c r="K242" t="s">
         <v>900</v>
@@ -11697,16 +11697,16 @@
         <v>337</v>
       </c>
       <c r="G243" t="s">
+        <v>338</v>
+      </c>
+      <c r="H243" t="s">
+        <v>339</v>
+      </c>
+      <c r="I243" t="s">
+        <v>898</v>
+      </c>
+      <c r="J243" t="s">
         <v>899</v>
-      </c>
-      <c r="H243" t="s">
-        <v>899</v>
-      </c>
-      <c r="I243" t="s">
-        <v>338</v>
-      </c>
-      <c r="J243" t="s">
-        <v>339</v>
       </c>
       <c r="K243" t="s">
         <v>900</v>
@@ -11732,16 +11732,16 @@
         <v>337</v>
       </c>
       <c r="G244" t="s">
+        <v>338</v>
+      </c>
+      <c r="H244" t="s">
+        <v>339</v>
+      </c>
+      <c r="I244" t="s">
+        <v>898</v>
+      </c>
+      <c r="J244" t="s">
         <v>899</v>
-      </c>
-      <c r="H244" t="s">
-        <v>899</v>
-      </c>
-      <c r="I244" t="s">
-        <v>338</v>
-      </c>
-      <c r="J244" t="s">
-        <v>339</v>
       </c>
       <c r="K244" t="s">
         <v>900</v>
@@ -11767,16 +11767,16 @@
         <v>337</v>
       </c>
       <c r="G245" t="s">
+        <v>338</v>
+      </c>
+      <c r="H245" t="s">
+        <v>339</v>
+      </c>
+      <c r="I245" t="s">
+        <v>898</v>
+      </c>
+      <c r="J245" t="s">
         <v>899</v>
-      </c>
-      <c r="H245" t="s">
-        <v>899</v>
-      </c>
-      <c r="I245" t="s">
-        <v>338</v>
-      </c>
-      <c r="J245" t="s">
-        <v>339</v>
       </c>
       <c r="K245" t="s">
         <v>900</v>
@@ -11796,22 +11796,22 @@
         <v>898</v>
       </c>
       <c r="F246" t="s">
+        <v>533</v>
+      </c>
+      <c r="G246" t="s">
         <v>918</v>
       </c>
-      <c r="G246" t="s">
-        <v>899</v>
-      </c>
       <c r="H246" t="s">
+        <v>339</v>
+      </c>
+      <c r="I246" t="s">
         <v>919</v>
       </c>
-      <c r="I246" t="s">
-        <v>534</v>
-      </c>
       <c r="J246" t="s">
-        <v>339</v>
+        <v>920</v>
       </c>
       <c r="K246" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11834,13 +11834,13 @@
         <v>196</v>
       </c>
       <c r="G247" t="s">
+        <v>197</v>
+      </c>
+      <c r="H247" t="s">
+        <v>198</v>
+      </c>
+      <c r="K247" t="s">
         <v>925</v>
-      </c>
-      <c r="I247" t="s">
-        <v>197</v>
-      </c>
-      <c r="J247" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -11863,13 +11863,13 @@
         <v>196</v>
       </c>
       <c r="G248" t="s">
+        <v>197</v>
+      </c>
+      <c r="H248" t="s">
+        <v>198</v>
+      </c>
+      <c r="K248" t="s">
         <v>925</v>
-      </c>
-      <c r="I248" t="s">
-        <v>197</v>
-      </c>
-      <c r="J248" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -11892,13 +11892,13 @@
         <v>932</v>
       </c>
       <c r="G249" t="s">
+        <v>933</v>
+      </c>
+      <c r="H249" t="s">
+        <v>198</v>
+      </c>
+      <c r="K249" t="s">
         <v>925</v>
-      </c>
-      <c r="I249" t="s">
-        <v>933</v>
-      </c>
-      <c r="J249" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -11921,13 +11921,13 @@
         <v>196</v>
       </c>
       <c r="G250" t="s">
+        <v>197</v>
+      </c>
+      <c r="H250" t="s">
+        <v>198</v>
+      </c>
+      <c r="K250" t="s">
         <v>925</v>
-      </c>
-      <c r="I250" t="s">
-        <v>197</v>
-      </c>
-      <c r="J250" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -11947,13 +11947,13 @@
         <v>196</v>
       </c>
       <c r="G251" t="s">
+        <v>197</v>
+      </c>
+      <c r="H251" t="s">
+        <v>198</v>
+      </c>
+      <c r="K251" t="s">
         <v>925</v>
-      </c>
-      <c r="I251" t="s">
-        <v>197</v>
-      </c>
-      <c r="J251" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -11976,13 +11976,13 @@
         <v>196</v>
       </c>
       <c r="G252" t="s">
+        <v>197</v>
+      </c>
+      <c r="H252" t="s">
+        <v>198</v>
+      </c>
+      <c r="K252" t="s">
         <v>925</v>
-      </c>
-      <c r="I252" t="s">
-        <v>197</v>
-      </c>
-      <c r="J252" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -12004,11 +12004,11 @@
       <c r="G253" t="s">
         <v>946</v>
       </c>
-      <c r="I253" t="s">
+      <c r="H253" t="s">
+        <v>339</v>
+      </c>
+      <c r="K253" t="s">
         <v>947</v>
-      </c>
-      <c r="J253" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="254" spans="1:11">
@@ -12031,13 +12031,13 @@
         <v>454</v>
       </c>
       <c r="G254" t="s">
-        <v>946</v>
-      </c>
-      <c r="I254" t="s">
         <v>455</v>
       </c>
-      <c r="J254" t="s">
-        <v>192</v>
+      <c r="H254" t="s">
+        <v>191</v>
+      </c>
+      <c r="K254" t="s">
+        <v>947</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -12060,13 +12060,13 @@
         <v>954</v>
       </c>
       <c r="G255" t="s">
-        <v>946</v>
-      </c>
-      <c r="I255" t="s">
         <v>955</v>
       </c>
-      <c r="J255" t="s">
-        <v>192</v>
+      <c r="H255" t="s">
+        <v>191</v>
+      </c>
+      <c r="K255" t="s">
+        <v>947</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -12089,16 +12089,16 @@
         <v>954</v>
       </c>
       <c r="G256" t="s">
-        <v>946</v>
-      </c>
-      <c r="I256" t="s">
         <v>955</v>
       </c>
-      <c r="J256" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10">
+      <c r="H256" t="s">
+        <v>191</v>
+      </c>
+      <c r="K256" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11">
       <c r="A257" t="s">
         <v>959</v>
       </c>
@@ -12118,16 +12118,16 @@
         <v>954</v>
       </c>
       <c r="G257" t="s">
-        <v>946</v>
-      </c>
-      <c r="I257" t="s">
         <v>955</v>
       </c>
-      <c r="J257" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="258" spans="1:10">
+      <c r="H257" t="s">
+        <v>191</v>
+      </c>
+      <c r="K257" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11">
       <c r="A258" t="s">
         <v>962</v>
       </c>
@@ -12147,16 +12147,16 @@
         <v>706</v>
       </c>
       <c r="G258" t="s">
-        <v>946</v>
-      </c>
-      <c r="I258" t="s">
-        <v>709</v>
-      </c>
-      <c r="J258" t="s">
+        <v>707</v>
+      </c>
+      <c r="H258" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="259" spans="1:10">
+      <c r="K258" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11">
       <c r="A259" t="s">
         <v>965</v>
       </c>
@@ -12176,16 +12176,16 @@
         <v>954</v>
       </c>
       <c r="G259" t="s">
-        <v>946</v>
-      </c>
-      <c r="I259" t="s">
         <v>955</v>
       </c>
-      <c r="J259" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="260" spans="1:10">
+      <c r="H259" t="s">
+        <v>191</v>
+      </c>
+      <c r="K259" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11">
       <c r="A260" t="s">
         <v>967</v>
       </c>
@@ -12205,16 +12205,16 @@
         <v>337</v>
       </c>
       <c r="G260" t="s">
-        <v>946</v>
-      </c>
-      <c r="I260" t="s">
         <v>338</v>
       </c>
-      <c r="J260" t="s">
+      <c r="H260" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="261" spans="1:10">
+      <c r="K260" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11">
       <c r="A261" t="s">
         <v>970</v>
       </c>
@@ -12234,16 +12234,16 @@
         <v>973</v>
       </c>
       <c r="G261" t="s">
-        <v>946</v>
-      </c>
-      <c r="I261" t="s">
         <v>974</v>
       </c>
-      <c r="J261" t="s">
+      <c r="H261" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="262" spans="1:10">
+      <c r="K261" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11">
       <c r="A262" t="s">
         <v>975</v>
       </c>
@@ -12263,16 +12263,16 @@
         <v>337</v>
       </c>
       <c r="G262" t="s">
-        <v>946</v>
-      </c>
-      <c r="I262" t="s">
         <v>338</v>
       </c>
-      <c r="J262" t="s">
+      <c r="H262" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="263" spans="1:10">
+      <c r="K262" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11">
       <c r="A263" t="s">
         <v>978</v>
       </c>
@@ -12292,16 +12292,16 @@
         <v>981</v>
       </c>
       <c r="G263" t="s">
-        <v>946</v>
-      </c>
-      <c r="I263" t="s">
         <v>982</v>
       </c>
-      <c r="J263" t="s">
+      <c r="H263" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="264" spans="1:10">
+      <c r="K263" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11">
       <c r="A264" t="s">
         <v>983</v>
       </c>
@@ -12321,16 +12321,16 @@
         <v>58</v>
       </c>
       <c r="G264" t="s">
-        <v>946</v>
-      </c>
-      <c r="I264" t="s">
         <v>59</v>
       </c>
-      <c r="J264" t="s">
+      <c r="H264" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="265" spans="1:10">
+      <c r="K264" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11">
       <c r="A265" t="s">
         <v>986</v>
       </c>
@@ -12350,16 +12350,16 @@
         <v>16</v>
       </c>
       <c r="G265" t="s">
-        <v>946</v>
-      </c>
-      <c r="I265" t="s">
-        <v>19</v>
-      </c>
-      <c r="J265" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="266" spans="1:10">
+        <v>17</v>
+      </c>
+      <c r="H265" t="s">
+        <v>18</v>
+      </c>
+      <c r="K265" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11">
       <c r="A266" t="s">
         <v>989</v>
       </c>
@@ -12379,16 +12379,16 @@
         <v>992</v>
       </c>
       <c r="G266" t="s">
-        <v>946</v>
-      </c>
-      <c r="I266" t="s">
         <v>993</v>
       </c>
-      <c r="J266" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="267" spans="1:10">
+      <c r="H266" t="s">
+        <v>236</v>
+      </c>
+      <c r="K266" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11">
       <c r="A267" t="s">
         <v>994</v>
       </c>
@@ -12408,16 +12408,16 @@
         <v>243</v>
       </c>
       <c r="G267" t="s">
+        <v>244</v>
+      </c>
+      <c r="H267" t="s">
+        <v>236</v>
+      </c>
+      <c r="K267" t="s">
         <v>998</v>
       </c>
-      <c r="I267" t="s">
-        <v>244</v>
-      </c>
-      <c r="J267" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="268" spans="1:10">
+    </row>
+    <row r="268" spans="1:11">
       <c r="A268" t="s">
         <v>999</v>
       </c>
@@ -12437,16 +12437,16 @@
         <v>421</v>
       </c>
       <c r="G268" t="s">
+        <v>422</v>
+      </c>
+      <c r="H268" t="s">
+        <v>379</v>
+      </c>
+      <c r="K268" t="s">
         <v>1003</v>
       </c>
-      <c r="I268" t="s">
-        <v>423</v>
-      </c>
-      <c r="J268" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="269" spans="1:10">
+    </row>
+    <row r="269" spans="1:11">
       <c r="A269" t="s">
         <v>1004</v>
       </c>
@@ -12466,16 +12466,16 @@
         <v>243</v>
       </c>
       <c r="G269" t="s">
+        <v>244</v>
+      </c>
+      <c r="H269" t="s">
+        <v>236</v>
+      </c>
+      <c r="K269" t="s">
         <v>1008</v>
       </c>
-      <c r="I269" t="s">
-        <v>244</v>
-      </c>
-      <c r="J269" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10">
+    </row>
+    <row r="270" spans="1:11">
       <c r="A270" t="s">
         <v>1009</v>
       </c>
@@ -12495,16 +12495,16 @@
         <v>243</v>
       </c>
       <c r="G270" t="s">
+        <v>244</v>
+      </c>
+      <c r="H270" t="s">
+        <v>236</v>
+      </c>
+      <c r="K270" t="s">
         <v>1008</v>
       </c>
-      <c r="I270" t="s">
-        <v>244</v>
-      </c>
-      <c r="J270" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="271" spans="1:10">
+    </row>
+    <row r="271" spans="1:11">
       <c r="A271" t="s">
         <v>1012</v>
       </c>
@@ -12526,14 +12526,14 @@
       <c r="G271" t="s">
         <v>1017</v>
       </c>
-      <c r="I271" t="s">
+      <c r="H271" t="s">
+        <v>236</v>
+      </c>
+      <c r="K271" t="s">
         <v>1018</v>
       </c>
-      <c r="J271" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="272" spans="1:10">
+    </row>
+    <row r="272" spans="1:11">
       <c r="A272" t="s">
         <v>1019</v>
       </c>
@@ -12552,14 +12552,14 @@
       <c r="G272" t="s">
         <v>1017</v>
       </c>
-      <c r="I272" t="s">
+      <c r="H272" t="s">
+        <v>236</v>
+      </c>
+      <c r="K272" t="s">
         <v>1018</v>
       </c>
-      <c r="J272" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="273" spans="1:10">
+    </row>
+    <row r="273" spans="1:11">
       <c r="A273" t="s">
         <v>1021</v>
       </c>
@@ -12581,14 +12581,14 @@
       <c r="G273" t="s">
         <v>1017</v>
       </c>
-      <c r="I273" t="s">
+      <c r="H273" t="s">
+        <v>236</v>
+      </c>
+      <c r="K273" t="s">
         <v>1018</v>
       </c>
-      <c r="J273" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="274" spans="1:10">
+    </row>
+    <row r="274" spans="1:11">
       <c r="A274" t="s">
         <v>1024</v>
       </c>
@@ -12607,14 +12607,14 @@
       <c r="G274" t="s">
         <v>1017</v>
       </c>
-      <c r="I274" t="s">
+      <c r="H274" t="s">
+        <v>236</v>
+      </c>
+      <c r="K274" t="s">
         <v>1018</v>
       </c>
-      <c r="J274" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="275" spans="1:10">
+    </row>
+    <row r="275" spans="1:11">
       <c r="A275" t="s">
         <v>1026</v>
       </c>
@@ -12636,14 +12636,14 @@
       <c r="G275" t="s">
         <v>1017</v>
       </c>
-      <c r="I275" t="s">
+      <c r="H275" t="s">
+        <v>236</v>
+      </c>
+      <c r="K275" t="s">
         <v>1018</v>
       </c>
-      <c r="J275" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="276" spans="1:10">
+    </row>
+    <row r="276" spans="1:11">
       <c r="A276" t="s">
         <v>1029</v>
       </c>
@@ -12665,14 +12665,14 @@
       <c r="G276" t="s">
         <v>1017</v>
       </c>
-      <c r="I276" t="s">
+      <c r="H276" t="s">
+        <v>236</v>
+      </c>
+      <c r="K276" t="s">
         <v>1018</v>
       </c>
-      <c r="J276" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="277" spans="1:10">
+    </row>
+    <row r="277" spans="1:11">
       <c r="A277" t="s">
         <v>1032</v>
       </c>
@@ -12694,14 +12694,14 @@
       <c r="G277" t="s">
         <v>1017</v>
       </c>
-      <c r="I277" t="s">
+      <c r="H277" t="s">
+        <v>236</v>
+      </c>
+      <c r="K277" t="s">
         <v>1018</v>
       </c>
-      <c r="J277" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="278" spans="1:10">
+    </row>
+    <row r="278" spans="1:11">
       <c r="A278" t="s">
         <v>1035</v>
       </c>
@@ -12721,16 +12721,16 @@
         <v>421</v>
       </c>
       <c r="G278" t="s">
+        <v>422</v>
+      </c>
+      <c r="H278" t="s">
+        <v>379</v>
+      </c>
+      <c r="K278" t="s">
         <v>1039</v>
       </c>
-      <c r="I278" t="s">
-        <v>423</v>
-      </c>
-      <c r="J278" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="279" spans="1:10">
+    </row>
+    <row r="279" spans="1:11">
       <c r="A279" t="s">
         <v>1040</v>
       </c>
@@ -12750,16 +12750,16 @@
         <v>93</v>
       </c>
       <c r="G279" t="s">
+        <v>94</v>
+      </c>
+      <c r="H279" t="s">
+        <v>60</v>
+      </c>
+      <c r="K279" t="s">
         <v>1039</v>
       </c>
-      <c r="I279" t="s">
-        <v>96</v>
-      </c>
-      <c r="J279" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="280" spans="1:10">
+    </row>
+    <row r="280" spans="1:11">
       <c r="A280" t="s">
         <v>1043</v>
       </c>
@@ -12779,16 +12779,16 @@
         <v>16</v>
       </c>
       <c r="G280" t="s">
+        <v>17</v>
+      </c>
+      <c r="H280" t="s">
+        <v>18</v>
+      </c>
+      <c r="K280" t="s">
         <v>1039</v>
       </c>
-      <c r="I280" t="s">
-        <v>19</v>
-      </c>
-      <c r="J280" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="281" spans="1:10">
+    </row>
+    <row r="281" spans="1:11">
       <c r="A281" t="s">
         <v>1046</v>
       </c>
@@ -12808,16 +12808,16 @@
         <v>352</v>
       </c>
       <c r="G281" t="s">
+        <v>353</v>
+      </c>
+      <c r="H281" t="s">
+        <v>236</v>
+      </c>
+      <c r="K281" t="s">
         <v>1039</v>
       </c>
-      <c r="I281" t="s">
-        <v>353</v>
-      </c>
-      <c r="J281" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="282" spans="1:10">
+    </row>
+    <row r="282" spans="1:11">
       <c r="A282" t="s">
         <v>1049</v>
       </c>
@@ -12837,16 +12837,16 @@
         <v>253</v>
       </c>
       <c r="G282" t="s">
+        <v>254</v>
+      </c>
+      <c r="H282" t="s">
+        <v>255</v>
+      </c>
+      <c r="K282" t="s">
         <v>1039</v>
       </c>
-      <c r="I282" t="s">
-        <v>254</v>
-      </c>
-      <c r="J282" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="283" spans="1:10">
+    </row>
+    <row r="283" spans="1:11">
       <c r="A283" t="s">
         <v>1052</v>
       </c>
@@ -12863,19 +12863,19 @@
         <v>1055</v>
       </c>
       <c r="F283" t="s">
+        <v>802</v>
+      </c>
+      <c r="G283" t="s">
         <v>892</v>
       </c>
-      <c r="G283" t="s">
+      <c r="H283" t="s">
+        <v>339</v>
+      </c>
+      <c r="K283" t="s">
         <v>1056</v>
       </c>
-      <c r="I283" t="s">
-        <v>805</v>
-      </c>
-      <c r="J283" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10">
+    </row>
+    <row r="284" spans="1:11">
       <c r="A284" t="s">
         <v>1057</v>
       </c>
@@ -12895,16 +12895,16 @@
         <v>253</v>
       </c>
       <c r="G284" t="s">
+        <v>254</v>
+      </c>
+      <c r="H284" t="s">
+        <v>255</v>
+      </c>
+      <c r="K284" t="s">
         <v>1061</v>
       </c>
-      <c r="I284" t="s">
-        <v>254</v>
-      </c>
-      <c r="J284" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="285" spans="1:10">
+    </row>
+    <row r="285" spans="1:11">
       <c r="A285" t="s">
         <v>1062</v>
       </c>
@@ -12921,16 +12921,16 @@
         <v>352</v>
       </c>
       <c r="G285" t="s">
+        <v>353</v>
+      </c>
+      <c r="H285" t="s">
+        <v>236</v>
+      </c>
+      <c r="K285" t="s">
         <v>1065</v>
       </c>
-      <c r="I285" t="s">
-        <v>353</v>
-      </c>
-      <c r="J285" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="286" spans="1:10">
+    </row>
+    <row r="286" spans="1:11">
       <c r="A286" t="s">
         <v>1066</v>
       </c>
@@ -12950,16 +12950,16 @@
         <v>981</v>
       </c>
       <c r="G286" t="s">
+        <v>982</v>
+      </c>
+      <c r="H286" t="s">
+        <v>379</v>
+      </c>
+      <c r="K286" t="s">
         <v>1070</v>
       </c>
-      <c r="I286" t="s">
-        <v>982</v>
-      </c>
-      <c r="J286" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="287" spans="1:10">
+    </row>
+    <row r="287" spans="1:11">
       <c r="A287" t="s">
         <v>1071</v>
       </c>
@@ -12979,16 +12979,16 @@
         <v>981</v>
       </c>
       <c r="G287" t="s">
+        <v>982</v>
+      </c>
+      <c r="H287" t="s">
+        <v>379</v>
+      </c>
+      <c r="K287" t="s">
         <v>1070</v>
       </c>
-      <c r="I287" t="s">
-        <v>982</v>
-      </c>
-      <c r="J287" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="288" spans="1:10">
+    </row>
+    <row r="288" spans="1:11">
       <c r="A288" t="s">
         <v>1074</v>
       </c>
@@ -13008,16 +13008,16 @@
         <v>75</v>
       </c>
       <c r="G288" t="s">
+        <v>76</v>
+      </c>
+      <c r="H288" t="s">
+        <v>18</v>
+      </c>
+      <c r="K288" t="s">
         <v>1070</v>
       </c>
-      <c r="I288" t="s">
-        <v>76</v>
-      </c>
-      <c r="J288" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="289" spans="1:10">
+    </row>
+    <row r="289" spans="1:11">
       <c r="A289" t="s">
         <v>1077</v>
       </c>
@@ -13037,16 +13037,16 @@
         <v>58</v>
       </c>
       <c r="G289" t="s">
+        <v>59</v>
+      </c>
+      <c r="H289" t="s">
+        <v>60</v>
+      </c>
+      <c r="K289" t="s">
         <v>1070</v>
       </c>
-      <c r="I289" t="s">
-        <v>59</v>
-      </c>
-      <c r="J289" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="290" spans="1:10">
+    </row>
+    <row r="290" spans="1:11">
       <c r="A290" t="s">
         <v>1080</v>
       </c>
@@ -13066,16 +13066,16 @@
         <v>58</v>
       </c>
       <c r="G290" t="s">
+        <v>59</v>
+      </c>
+      <c r="H290" t="s">
+        <v>60</v>
+      </c>
+      <c r="K290" t="s">
         <v>1070</v>
       </c>
-      <c r="I290" t="s">
-        <v>59</v>
-      </c>
-      <c r="J290" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="291" spans="1:10">
+    </row>
+    <row r="291" spans="1:11">
       <c r="A291" t="s">
         <v>1083</v>
       </c>
@@ -13095,16 +13095,16 @@
         <v>352</v>
       </c>
       <c r="G291" t="s">
+        <v>353</v>
+      </c>
+      <c r="H291" t="s">
+        <v>236</v>
+      </c>
+      <c r="K291" t="s">
         <v>1070</v>
       </c>
-      <c r="I291" t="s">
-        <v>353</v>
-      </c>
-      <c r="J291" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="292" spans="1:10">
+    </row>
+    <row r="292" spans="1:11">
       <c r="A292" t="s">
         <v>1086</v>
       </c>
@@ -13124,16 +13124,16 @@
         <v>352</v>
       </c>
       <c r="G292" t="s">
+        <v>353</v>
+      </c>
+      <c r="H292" t="s">
+        <v>236</v>
+      </c>
+      <c r="K292" t="s">
         <v>1070</v>
       </c>
-      <c r="I292" t="s">
-        <v>353</v>
-      </c>
-      <c r="J292" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="293" spans="1:10">
+    </row>
+    <row r="293" spans="1:11">
       <c r="A293" t="s">
         <v>1089</v>
       </c>
@@ -13153,16 +13153,16 @@
         <v>352</v>
       </c>
       <c r="G293" t="s">
+        <v>353</v>
+      </c>
+      <c r="H293" t="s">
+        <v>236</v>
+      </c>
+      <c r="K293" t="s">
         <v>1070</v>
       </c>
-      <c r="I293" t="s">
-        <v>353</v>
-      </c>
-      <c r="J293" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="294" spans="1:10">
+    </row>
+    <row r="294" spans="1:11">
       <c r="A294" t="s">
         <v>1092</v>
       </c>
@@ -13182,16 +13182,16 @@
         <v>352</v>
       </c>
       <c r="G294" t="s">
+        <v>353</v>
+      </c>
+      <c r="H294" t="s">
+        <v>236</v>
+      </c>
+      <c r="K294" t="s">
         <v>1070</v>
       </c>
-      <c r="I294" t="s">
-        <v>353</v>
-      </c>
-      <c r="J294" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="295" spans="1:10">
+    </row>
+    <row r="295" spans="1:11">
       <c r="A295" t="s">
         <v>1095</v>
       </c>
@@ -13211,16 +13211,16 @@
         <v>352</v>
       </c>
       <c r="G295" t="s">
+        <v>353</v>
+      </c>
+      <c r="H295" t="s">
+        <v>236</v>
+      </c>
+      <c r="K295" t="s">
         <v>1099</v>
       </c>
-      <c r="I295" t="s">
-        <v>353</v>
-      </c>
-      <c r="J295" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="296" spans="1:10">
+    </row>
+    <row r="296" spans="1:11">
       <c r="A296" t="s">
         <v>1100</v>
       </c>
@@ -13240,13 +13240,13 @@
         <v>352</v>
       </c>
       <c r="G296" t="s">
+        <v>353</v>
+      </c>
+      <c r="H296" t="s">
+        <v>236</v>
+      </c>
+      <c r="K296" t="s">
         <v>1099</v>
-      </c>
-      <c r="I296" t="s">
-        <v>353</v>
-      </c>
-      <c r="J296" t="s">
-        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -28,27 +28,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
+    <t>codeforiati:group-code</t>
   </si>
   <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -61,27 +61,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
+    <t>110</t>
   </si>
   <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -91,12 +91,12 @@
     <t>Educational buildings, equipment, materials; subsidiary services to education (boarding facilities, staff housing); language training; colloquia, seminars, lectures, etc.</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Research and studies on education effectiveness, relevance and quality; systematic evaluation and monitoring.</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
@@ -130,18 +130,18 @@
     <t>Formal and non-formal primary education for children; all elementary and first cycle systematic instruction; provision of learning materials.</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -190,12 +190,12 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>07 - Health</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>Second cycle systematic instruction at junior level.</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>Second cycle systematic instruction at senior levels.</t>
   </si>
   <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>09.2.2 - Upper‐secondary education (IS)</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>113</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Elementary vocational training and secondary level technical education; on-the job training; apprenticeships; including informal vocational training.</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
@@ -256,18 +256,18 @@
     <t>Degree and diploma programmes at universities, colleges and polytechnics; scholarships.</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -277,12 +277,12 @@
     <t>Professional-level vocational training programmes and in-service training.</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
@@ -292,21 +292,21 @@
     <t>Health sector policy, planning and programmes; aid to health ministries, public health administration; institution capacity building and advice; medical insurance programmes; including health system strengthening and health governance; unspecified health activities.</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>Health</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -328,12 +328,12 @@
     <t>General medical research (excluding basic health research and research for prevention and control of NCDs (12382)).</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>Laboratories, specialised clinics and hospitals (including equipment and supplies); ambulances; dental services; medical rehabilitation. Excludes noncommunicable diseases (123xx).</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -382,12 +382,12 @@
     <t>District-level hospitals, clinics and dispensaries and related medical equipment; excluding specialised hospitals and clinics (12191).</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -580,21 +580,21 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
+    <t>140</t>
   </si>
   <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>Large scale sewerage including trunk sewers and sewage pumping stations; domestic and industrial waste water treatment plants.</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>Municipal and industrial solid waste management, including hazardous and toxic waste; collection, disposal and treatment; landfill areas; composting and reuse.</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -715,27 +715,27 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
+    <t>150</t>
   </si>
   <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Fiscal policy and planning; support to ministries of finance; strengthening financial and managerial accountability; public expenditure management; improving financial management systems; budget drafting; inter-governmental fiscal relations, public audit, public debt. (Use code 15114 for domestic revenue mobilisation and code 33120 for customs).</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
@@ -760,12 +760,12 @@
     <t>Decentralisation processes (including political, administrative and fiscal dimensions); intergovernmental relations and federalism; strengthening departments of regional and local government, regional and local authorities and their national associations. (Use specific sector codes for decentralisation of sector management and services.)</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
@@ -775,12 +775,12 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
@@ -859,12 +859,12 @@
     <t>Support to administration of developing countries' foreign aid (including triangular and south-south cooperation).</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -943,12 +943,12 @@
     <t>Judicial law and order sectors; policy development within ministries of justice or equivalents.</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
@@ -958,12 +958,12 @@
     <t>Police affairs and services.</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Fire-prevention and fire-fighting affairs and services.</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>Prisons</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
@@ -1027,12 +1027,12 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
@@ -1072,12 +1072,12 @@
     <t>Electoral management bodies and processes, election observation, voters' education. (Use code 15230 when in the context of an international peacekeeping operation.)</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -1099,12 +1099,12 @@
     <t>Activities that support free and uncensored flow of information on public issues; activities that increase the editorial and technical skills and the integrity of the print and broadcast media, e.g. training of journalists. (Use codes 22010-22040 for provision of equipment and capital assistance to media.)</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -1147,12 +1147,12 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
@@ -1192,12 +1192,12 @@
     <t>Collection, production, management and dissemination of statistics and data related to Government &amp; Civil Society. Includes macroeconomic statistics, government finance, fiscal and public sector statistics, support to development of administrative data infrastructure, civil society surveys.</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -1231,12 +1231,12 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>02 - Defence</t>
   </si>
   <si>
@@ -1276,15 +1276,15 @@
     <t>Social protection or social security strategies, legislation and administration; institution capacity building and advice; social security and other social schemes; support programmes, cash benefits, pensions and special programmes for older persons, orphans, persons with disabilities, children, mothers with newborns, those living in poverty, without jobs and other vulnerable groups; social dimensions of structural adjustment.</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>160</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Social protection schemes in the form of cash or in-kind benefits, including pensions, against the risks linked to old age.</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -1348,12 +1348,12 @@
     <t>Employment policy and planning; institution capacity building and advice; employment creation and income generation programmes; including activities specifically designed for the needs of vulnerable groups.</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
@@ -1363,12 +1363,12 @@
     <t>Housing sector policy, planning and programmes; excluding low-cost housing and slum clearance (16040).</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
@@ -1378,12 +1378,12 @@
     <t>Including slum clearance.</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -1402,12 +1402,12 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
@@ -1444,12 +1444,12 @@
     <t>Recreation and sport</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -1528,12 +1528,12 @@
     <t>Road infrastructure, road vehicles; passenger road transport, motor passenger cars.</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -1615,12 +1615,12 @@
     <t>Whether or not related to transportation. Whenever possible, report storage projects under the sector of the resource being stored.</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -1684,12 +1684,12 @@
     <t>Radio and TV links, equipment; newspapers; printing and publishing.</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -1708,21 +1708,21 @@
     <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>230</t>
   </si>
   <si>
@@ -1741,12 +1741,12 @@
     <t>Regulation of the energy sector, including wholesale and retail electricity provision.</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -2131,21 +2131,21 @@
     <t>Agricultural sector policy, planning and programmes; aid to agricultural ministries; institution capacity building and advice; unspecified agriculture.</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>310</t>
   </si>
   <si>
@@ -2311,12 +2311,12 @@
     <t>Forestry sector policy, planning and programmes; institution capacity building and advice; forest surveys; unspecified forestry and agro-forestry activities.</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>04.2.2 - Forestry (CS)</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>312</t>
   </si>
   <si>
@@ -2368,12 +2368,12 @@
     <t>Fishing sector policy, planning and programmes; institution capacity building and advice; ocean and coastal fishing; marine and freshwater fish surveys and prospecting; fishing boats/equipment; unspecified fishing activities.</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>04.2.3 - Fishing and hunting (CS)</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>313</t>
   </si>
   <si>
@@ -2419,21 +2419,21 @@
     <t>Industrial sector policy, planning and programmes; institution capacity building and advice; unspecified industrial activities; manufacturing of goods not specified below.</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -2593,12 +2593,12 @@
     <t>Mineral and mining sector policy, planning and programmes; mining legislation, mining cadastre, mineral resources inventory, information systems, institution capacity building and advice; unspecified mineral resources exploitation.</t>
   </si>
   <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>322</t>
   </si>
   <si>
@@ -2692,12 +2692,12 @@
     <t>Construction sector policy and planning; excluding construction activities within specific sectors (e.g., hospital or school construction).</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>04.4.3 - Construction (CS)</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>323</t>
   </si>
   <si>
@@ -2770,12 +2770,12 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>332</t>
   </si>
   <si>
@@ -2812,12 +2812,12 @@
     <t>Including natural reserves and actions in the surrounding areas; other measures to protect endangered or vulnerable species and their habitats (e.g. wetlands preservation).</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -2848,15 +2848,15 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>430</t>
   </si>
   <si>
@@ -2878,12 +2878,12 @@
     <t>Urban development and planning; urban management, land information systems.</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -2935,12 +2935,12 @@
     <t>Disaster risk reduction activities if not sector specific. Comprises risk assessments, structural prevention measures (e.g. flood prevention infrastructure), preparedness measures (e.g. early warning systems) normative prevention measures (e.g. building codes, land-use planning), and risk transfer systems (e.g. insurance schemes, risk funds). Also includes building local and national capacities and supporting the establishment of efficient and sustainable national structures able to promote disaster risk reduction.</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
@@ -2959,12 +2959,12 @@
     <t>Short or longer term household food security programmes and activities that improve the access of households to nutritionally adequate diets (excluding any cash transfers within broader social welfare programmes that do not have a specific food security, food acquisition or nutrition focus which should be reported under code 16010).</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -2992,12 +2992,12 @@
     <t>When sector cannot be identified.</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -3061,13 +3061,13 @@
     <t>Actions falling outside the code headings below.</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>600</t>
@@ -3747,13 +3747,13 @@
         <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
         <v>20</v>
@@ -3817,13 +3817,13 @@
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
@@ -3846,22 +3846,22 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -3881,7 +3881,7 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -3890,13 +3890,13 @@
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -3916,22 +3916,22 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J8" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
@@ -3951,22 +3951,22 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s">
         <v>21</v>
@@ -3986,22 +3986,22 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J10" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K10" t="s">
         <v>21</v>
@@ -4021,25 +4021,25 @@
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
         <v>58</v>
       </c>
       <c r="G11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" t="s">
         <v>59</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" t="s">
         <v>60</v>
-      </c>
-      <c r="I11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4056,22 +4056,22 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
         <v>64</v>
       </c>
       <c r="G12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" t="s">
         <v>65</v>
       </c>
-      <c r="H12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" t="s">
-        <v>40</v>
-      </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -4091,22 +4091,22 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J13" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s">
         <v>21</v>
@@ -4126,22 +4126,22 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="F14" t="s">
         <v>75</v>
       </c>
       <c r="G14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" t="s">
         <v>76</v>
       </c>
-      <c r="H14" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" t="s">
-        <v>70</v>
-      </c>
       <c r="J14" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s">
         <v>21</v>
@@ -4161,22 +4161,22 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J15" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="K15" t="s">
         <v>21</v>
@@ -4196,22 +4196,22 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
         <v>87</v>
       </c>
       <c r="G16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s">
         <v>88</v>
       </c>
-      <c r="H16" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" t="s">
-        <v>82</v>
-      </c>
       <c r="J16" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="K16" t="s">
         <v>21</v>
@@ -4240,16 +4240,16 @@
         <v>94</v>
       </c>
       <c r="H17" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" t="s">
+        <v>97</v>
+      </c>
+      <c r="K17" t="s">
         <v>60</v>
-      </c>
-      <c r="I17" t="s">
-        <v>95</v>
-      </c>
-      <c r="J17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K17" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4275,16 +4275,16 @@
         <v>94</v>
       </c>
       <c r="H18" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" t="s">
+        <v>97</v>
+      </c>
+      <c r="K18" t="s">
         <v>60</v>
-      </c>
-      <c r="I18" t="s">
-        <v>95</v>
-      </c>
-      <c r="J18" t="s">
-        <v>96</v>
-      </c>
-      <c r="K18" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -4307,19 +4307,19 @@
         <v>104</v>
       </c>
       <c r="G19" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" t="s">
         <v>105</v>
       </c>
-      <c r="H19" t="s">
+      <c r="J19" t="s">
+        <v>97</v>
+      </c>
+      <c r="K19" t="s">
         <v>60</v>
-      </c>
-      <c r="I19" t="s">
-        <v>95</v>
-      </c>
-      <c r="J19" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4342,19 +4342,19 @@
         <v>109</v>
       </c>
       <c r="G20" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" t="s">
+        <v>95</v>
+      </c>
+      <c r="I20" t="s">
         <v>110</v>
       </c>
-      <c r="H20" t="s">
+      <c r="J20" t="s">
+        <v>97</v>
+      </c>
+      <c r="K20" t="s">
         <v>60</v>
-      </c>
-      <c r="I20" t="s">
-        <v>95</v>
-      </c>
-      <c r="J20" t="s">
-        <v>96</v>
-      </c>
-      <c r="K20" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4380,16 +4380,16 @@
         <v>94</v>
       </c>
       <c r="H21" t="s">
+        <v>95</v>
+      </c>
+      <c r="I21" t="s">
+        <v>96</v>
+      </c>
+      <c r="J21" t="s">
+        <v>97</v>
+      </c>
+      <c r="K21" t="s">
         <v>60</v>
-      </c>
-      <c r="I21" t="s">
-        <v>95</v>
-      </c>
-      <c r="J21" t="s">
-        <v>96</v>
-      </c>
-      <c r="K21" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -4406,25 +4406,25 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="F22" t="s">
         <v>58</v>
       </c>
       <c r="G22" t="s">
+        <v>94</v>
+      </c>
+      <c r="H22" t="s">
+        <v>118</v>
+      </c>
+      <c r="I22" t="s">
         <v>59</v>
       </c>
-      <c r="H22" t="s">
+      <c r="J22" t="s">
+        <v>97</v>
+      </c>
+      <c r="K22" t="s">
         <v>60</v>
-      </c>
-      <c r="I22" t="s">
-        <v>117</v>
-      </c>
-      <c r="J22" t="s">
-        <v>118</v>
-      </c>
-      <c r="K22" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4441,25 +4441,25 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="F23" t="s">
         <v>122</v>
       </c>
       <c r="G23" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" t="s">
         <v>123</v>
       </c>
-      <c r="H23" t="s">
+      <c r="J23" t="s">
+        <v>97</v>
+      </c>
+      <c r="K23" t="s">
         <v>60</v>
-      </c>
-      <c r="I23" t="s">
-        <v>117</v>
-      </c>
-      <c r="J23" t="s">
-        <v>118</v>
-      </c>
-      <c r="K23" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4476,25 +4476,25 @@
         <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="F24" t="s">
         <v>58</v>
       </c>
       <c r="G24" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" t="s">
+        <v>118</v>
+      </c>
+      <c r="I24" t="s">
         <v>59</v>
       </c>
-      <c r="H24" t="s">
+      <c r="J24" t="s">
+        <v>97</v>
+      </c>
+      <c r="K24" t="s">
         <v>60</v>
-      </c>
-      <c r="I24" t="s">
-        <v>117</v>
-      </c>
-      <c r="J24" t="s">
-        <v>118</v>
-      </c>
-      <c r="K24" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4511,25 +4511,25 @@
         <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="F25" t="s">
         <v>58</v>
       </c>
       <c r="G25" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" t="s">
         <v>59</v>
       </c>
-      <c r="H25" t="s">
+      <c r="J25" t="s">
+        <v>97</v>
+      </c>
+      <c r="K25" t="s">
         <v>60</v>
-      </c>
-      <c r="I25" t="s">
-        <v>117</v>
-      </c>
-      <c r="J25" t="s">
-        <v>118</v>
-      </c>
-      <c r="K25" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4546,25 +4546,25 @@
         <v>14</v>
       </c>
       <c r="E26" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="F26" t="s">
         <v>58</v>
       </c>
       <c r="G26" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" t="s">
+        <v>118</v>
+      </c>
+      <c r="I26" t="s">
         <v>59</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J26" t="s">
+        <v>97</v>
+      </c>
+      <c r="K26" t="s">
         <v>60</v>
-      </c>
-      <c r="I26" t="s">
-        <v>117</v>
-      </c>
-      <c r="J26" t="s">
-        <v>118</v>
-      </c>
-      <c r="K26" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4581,25 +4581,25 @@
         <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="F27" t="s">
         <v>58</v>
       </c>
       <c r="G27" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" t="s">
+        <v>118</v>
+      </c>
+      <c r="I27" t="s">
         <v>59</v>
       </c>
-      <c r="H27" t="s">
+      <c r="J27" t="s">
+        <v>97</v>
+      </c>
+      <c r="K27" t="s">
         <v>60</v>
-      </c>
-      <c r="I27" t="s">
-        <v>117</v>
-      </c>
-      <c r="J27" t="s">
-        <v>118</v>
-      </c>
-      <c r="K27" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4616,25 +4616,25 @@
         <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="F28" t="s">
         <v>58</v>
       </c>
       <c r="G28" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" t="s">
+        <v>118</v>
+      </c>
+      <c r="I28" t="s">
         <v>59</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" t="s">
+        <v>97</v>
+      </c>
+      <c r="K28" t="s">
         <v>60</v>
-      </c>
-      <c r="I28" t="s">
-        <v>117</v>
-      </c>
-      <c r="J28" t="s">
-        <v>118</v>
-      </c>
-      <c r="K28" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4651,25 +4651,25 @@
         <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="F29" t="s">
         <v>58</v>
       </c>
       <c r="G29" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" t="s">
+        <v>118</v>
+      </c>
+      <c r="I29" t="s">
         <v>59</v>
       </c>
-      <c r="H29" t="s">
+      <c r="J29" t="s">
+        <v>97</v>
+      </c>
+      <c r="K29" t="s">
         <v>60</v>
-      </c>
-      <c r="I29" t="s">
-        <v>117</v>
-      </c>
-      <c r="J29" t="s">
-        <v>118</v>
-      </c>
-      <c r="K29" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4686,7 +4686,7 @@
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="F30" t="s">
         <v>93</v>
@@ -4695,16 +4695,16 @@
         <v>94</v>
       </c>
       <c r="H30" t="s">
+        <v>118</v>
+      </c>
+      <c r="I30" t="s">
+        <v>96</v>
+      </c>
+      <c r="J30" t="s">
+        <v>97</v>
+      </c>
+      <c r="K30" t="s">
         <v>60</v>
-      </c>
-      <c r="I30" t="s">
-        <v>117</v>
-      </c>
-      <c r="J30" t="s">
-        <v>118</v>
-      </c>
-      <c r="K30" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4721,25 +4721,25 @@
         <v>14</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="F31" t="s">
         <v>58</v>
       </c>
       <c r="G31" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31" t="s">
+        <v>149</v>
+      </c>
+      <c r="I31" t="s">
         <v>59</v>
       </c>
-      <c r="H31" t="s">
+      <c r="J31" t="s">
+        <v>97</v>
+      </c>
+      <c r="K31" t="s">
         <v>60</v>
-      </c>
-      <c r="I31" t="s">
-        <v>148</v>
-      </c>
-      <c r="J31" t="s">
-        <v>149</v>
-      </c>
-      <c r="K31" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4756,25 +4756,25 @@
         <v>14</v>
       </c>
       <c r="E32" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="F32" t="s">
         <v>58</v>
       </c>
       <c r="G32" t="s">
+        <v>94</v>
+      </c>
+      <c r="H32" t="s">
+        <v>149</v>
+      </c>
+      <c r="I32" t="s">
         <v>59</v>
       </c>
-      <c r="H32" t="s">
+      <c r="J32" t="s">
+        <v>97</v>
+      </c>
+      <c r="K32" t="s">
         <v>60</v>
-      </c>
-      <c r="I32" t="s">
-        <v>148</v>
-      </c>
-      <c r="J32" t="s">
-        <v>149</v>
-      </c>
-      <c r="K32" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4791,25 +4791,25 @@
         <v>14</v>
       </c>
       <c r="E33" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="F33" t="s">
         <v>58</v>
       </c>
       <c r="G33" t="s">
+        <v>94</v>
+      </c>
+      <c r="H33" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" t="s">
         <v>59</v>
       </c>
-      <c r="H33" t="s">
+      <c r="J33" t="s">
+        <v>97</v>
+      </c>
+      <c r="K33" t="s">
         <v>60</v>
-      </c>
-      <c r="I33" t="s">
-        <v>148</v>
-      </c>
-      <c r="J33" t="s">
-        <v>149</v>
-      </c>
-      <c r="K33" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4826,25 +4826,25 @@
         <v>14</v>
       </c>
       <c r="E34" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="F34" t="s">
         <v>58</v>
       </c>
       <c r="G34" t="s">
+        <v>94</v>
+      </c>
+      <c r="H34" t="s">
+        <v>149</v>
+      </c>
+      <c r="I34" t="s">
         <v>59</v>
       </c>
-      <c r="H34" t="s">
+      <c r="J34" t="s">
+        <v>97</v>
+      </c>
+      <c r="K34" t="s">
         <v>60</v>
-      </c>
-      <c r="I34" t="s">
-        <v>148</v>
-      </c>
-      <c r="J34" t="s">
-        <v>149</v>
-      </c>
-      <c r="K34" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4861,25 +4861,25 @@
         <v>14</v>
       </c>
       <c r="E35" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="F35" t="s">
         <v>58</v>
       </c>
       <c r="G35" t="s">
+        <v>94</v>
+      </c>
+      <c r="H35" t="s">
+        <v>149</v>
+      </c>
+      <c r="I35" t="s">
         <v>59</v>
       </c>
-      <c r="H35" t="s">
+      <c r="J35" t="s">
+        <v>97</v>
+      </c>
+      <c r="K35" t="s">
         <v>60</v>
-      </c>
-      <c r="I35" t="s">
-        <v>148</v>
-      </c>
-      <c r="J35" t="s">
-        <v>149</v>
-      </c>
-      <c r="K35" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4896,25 +4896,25 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="F36" t="s">
         <v>104</v>
       </c>
       <c r="G36" t="s">
+        <v>94</v>
+      </c>
+      <c r="H36" t="s">
+        <v>149</v>
+      </c>
+      <c r="I36" t="s">
         <v>105</v>
       </c>
-      <c r="H36" t="s">
+      <c r="J36" t="s">
+        <v>97</v>
+      </c>
+      <c r="K36" t="s">
         <v>60</v>
-      </c>
-      <c r="I36" t="s">
-        <v>148</v>
-      </c>
-      <c r="J36" t="s">
-        <v>149</v>
-      </c>
-      <c r="K36" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4930,20 +4930,20 @@
       <c r="D37" t="s">
         <v>14</v>
       </c>
-      <c r="E37" t="s">
-        <v>168</v>
-      </c>
       <c r="F37" t="s">
         <v>58</v>
       </c>
       <c r="G37" t="s">
+        <v>168</v>
+      </c>
+      <c r="I37" t="s">
         <v>59</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
+        <v>169</v>
+      </c>
+      <c r="K37" t="s">
         <v>60</v>
-      </c>
-      <c r="K37" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4959,20 +4959,20 @@
       <c r="D38" t="s">
         <v>14</v>
       </c>
-      <c r="E38" t="s">
-        <v>168</v>
-      </c>
       <c r="F38" t="s">
         <v>58</v>
       </c>
       <c r="G38" t="s">
+        <v>168</v>
+      </c>
+      <c r="I38" t="s">
         <v>59</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" t="s">
+        <v>169</v>
+      </c>
+      <c r="K38" t="s">
         <v>60</v>
-      </c>
-      <c r="K38" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4988,20 +4988,20 @@
       <c r="D39" t="s">
         <v>14</v>
       </c>
-      <c r="E39" t="s">
-        <v>168</v>
-      </c>
       <c r="F39" t="s">
         <v>58</v>
       </c>
       <c r="G39" t="s">
+        <v>168</v>
+      </c>
+      <c r="I39" t="s">
         <v>59</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" t="s">
+        <v>169</v>
+      </c>
+      <c r="K39" t="s">
         <v>60</v>
-      </c>
-      <c r="K39" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5017,20 +5017,20 @@
       <c r="D40" t="s">
         <v>14</v>
       </c>
-      <c r="E40" t="s">
-        <v>168</v>
-      </c>
       <c r="F40" t="s">
         <v>58</v>
       </c>
       <c r="G40" t="s">
+        <v>168</v>
+      </c>
+      <c r="I40" t="s">
         <v>59</v>
       </c>
-      <c r="H40" t="s">
+      <c r="J40" t="s">
+        <v>169</v>
+      </c>
+      <c r="K40" t="s">
         <v>60</v>
-      </c>
-      <c r="K40" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5046,20 +5046,20 @@
       <c r="D41" t="s">
         <v>14</v>
       </c>
-      <c r="E41" t="s">
-        <v>168</v>
-      </c>
       <c r="F41" t="s">
         <v>93</v>
       </c>
       <c r="G41" t="s">
-        <v>94</v>
-      </c>
-      <c r="H41" t="s">
+        <v>168</v>
+      </c>
+      <c r="I41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J41" t="s">
+        <v>169</v>
+      </c>
+      <c r="K41" t="s">
         <v>60</v>
-      </c>
-      <c r="K41" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5075,20 +5075,20 @@
       <c r="D42" t="s">
         <v>14</v>
       </c>
-      <c r="E42" t="s">
-        <v>168</v>
-      </c>
       <c r="F42" t="s">
         <v>104</v>
       </c>
       <c r="G42" t="s">
+        <v>168</v>
+      </c>
+      <c r="I42" t="s">
         <v>105</v>
       </c>
-      <c r="H42" t="s">
+      <c r="J42" t="s">
+        <v>169</v>
+      </c>
+      <c r="K42" t="s">
         <v>60</v>
-      </c>
-      <c r="K42" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5104,16 +5104,16 @@
       <c r="D43" t="s">
         <v>14</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>188</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>189</v>
       </c>
-      <c r="G43" t="s">
+      <c r="I43" t="s">
         <v>190</v>
       </c>
-      <c r="H43" t="s">
+      <c r="J43" t="s">
         <v>191</v>
       </c>
       <c r="K43" t="s">
@@ -5133,20 +5133,20 @@
       <c r="D44" t="s">
         <v>14</v>
       </c>
-      <c r="E44" t="s">
-        <v>188</v>
-      </c>
       <c r="F44" t="s">
         <v>196</v>
       </c>
       <c r="G44" t="s">
+        <v>189</v>
+      </c>
+      <c r="I44" t="s">
         <v>197</v>
       </c>
-      <c r="H44" t="s">
+      <c r="J44" t="s">
+        <v>191</v>
+      </c>
+      <c r="K44" t="s">
         <v>198</v>
-      </c>
-      <c r="K44" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5162,16 +5162,16 @@
       <c r="D45" t="s">
         <v>14</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>188</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>189</v>
       </c>
-      <c r="G45" t="s">
+      <c r="I45" t="s">
         <v>190</v>
       </c>
-      <c r="H45" t="s">
+      <c r="J45" t="s">
         <v>191</v>
       </c>
       <c r="K45" t="s">
@@ -5191,16 +5191,16 @@
       <c r="D46" t="s">
         <v>14</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>188</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>189</v>
       </c>
-      <c r="G46" t="s">
+      <c r="I46" t="s">
         <v>190</v>
       </c>
-      <c r="H46" t="s">
+      <c r="J46" t="s">
         <v>191</v>
       </c>
       <c r="K46" t="s">
@@ -5220,20 +5220,20 @@
       <c r="D47" t="s">
         <v>14</v>
       </c>
-      <c r="E47" t="s">
-        <v>188</v>
-      </c>
       <c r="F47" t="s">
         <v>208</v>
       </c>
       <c r="G47" t="s">
+        <v>189</v>
+      </c>
+      <c r="I47" t="s">
         <v>209</v>
       </c>
-      <c r="H47" t="s">
+      <c r="J47" t="s">
+        <v>191</v>
+      </c>
+      <c r="K47" t="s">
         <v>198</v>
-      </c>
-      <c r="K47" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5249,16 +5249,16 @@
       <c r="D48" t="s">
         <v>14</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>188</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>189</v>
       </c>
-      <c r="G48" t="s">
+      <c r="I48" t="s">
         <v>190</v>
       </c>
-      <c r="H48" t="s">
+      <c r="J48" t="s">
         <v>191</v>
       </c>
       <c r="K48" t="s">
@@ -5278,16 +5278,16 @@
       <c r="D49" t="s">
         <v>14</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>188</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>189</v>
       </c>
-      <c r="G49" t="s">
+      <c r="I49" t="s">
         <v>190</v>
       </c>
-      <c r="H49" t="s">
+      <c r="J49" t="s">
         <v>191</v>
       </c>
       <c r="K49" t="s">
@@ -5307,20 +5307,20 @@
       <c r="D50" t="s">
         <v>14</v>
       </c>
-      <c r="E50" t="s">
-        <v>188</v>
-      </c>
       <c r="F50" t="s">
         <v>208</v>
       </c>
       <c r="G50" t="s">
+        <v>189</v>
+      </c>
+      <c r="I50" t="s">
         <v>209</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
+        <v>191</v>
+      </c>
+      <c r="K50" t="s">
         <v>198</v>
-      </c>
-      <c r="K50" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5336,16 +5336,16 @@
       <c r="D51" t="s">
         <v>14</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>188</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>189</v>
       </c>
-      <c r="G51" t="s">
+      <c r="I51" t="s">
         <v>190</v>
       </c>
-      <c r="H51" t="s">
+      <c r="J51" t="s">
         <v>191</v>
       </c>
       <c r="K51" t="s">
@@ -5365,20 +5365,20 @@
       <c r="D52" t="s">
         <v>14</v>
       </c>
-      <c r="E52" t="s">
-        <v>188</v>
-      </c>
       <c r="F52" t="s">
         <v>225</v>
       </c>
       <c r="G52" t="s">
+        <v>189</v>
+      </c>
+      <c r="I52" t="s">
         <v>226</v>
       </c>
-      <c r="H52" t="s">
+      <c r="J52" t="s">
+        <v>191</v>
+      </c>
+      <c r="K52" t="s">
         <v>198</v>
-      </c>
-      <c r="K52" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5394,20 +5394,20 @@
       <c r="D53" t="s">
         <v>14</v>
       </c>
-      <c r="E53" t="s">
-        <v>188</v>
-      </c>
       <c r="F53" t="s">
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>17</v>
-      </c>
-      <c r="H53" t="s">
-        <v>18</v>
+        <v>189</v>
+      </c>
+      <c r="I53" t="s">
+        <v>19</v>
+      </c>
+      <c r="J53" t="s">
+        <v>191</v>
       </c>
       <c r="K53" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5465,13 +5465,13 @@
         <v>243</v>
       </c>
       <c r="G55" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H55" t="s">
         <v>236</v>
       </c>
       <c r="I55" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J55" t="s">
         <v>238</v>
@@ -5500,13 +5500,13 @@
         <v>248</v>
       </c>
       <c r="G56" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="H56" t="s">
         <v>236</v>
       </c>
       <c r="I56" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J56" t="s">
         <v>238</v>
@@ -5535,19 +5535,19 @@
         <v>253</v>
       </c>
       <c r="G57" t="s">
+        <v>235</v>
+      </c>
+      <c r="H57" t="s">
+        <v>236</v>
+      </c>
+      <c r="I57" t="s">
         <v>254</v>
-      </c>
-      <c r="H57" t="s">
-        <v>255</v>
-      </c>
-      <c r="I57" t="s">
-        <v>237</v>
       </c>
       <c r="J57" t="s">
         <v>238</v>
       </c>
       <c r="K57" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5570,13 +5570,13 @@
         <v>243</v>
       </c>
       <c r="G58" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H58" t="s">
         <v>236</v>
       </c>
       <c r="I58" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J58" t="s">
         <v>238</v>
@@ -5605,13 +5605,13 @@
         <v>243</v>
       </c>
       <c r="G59" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H59" t="s">
         <v>236</v>
       </c>
       <c r="I59" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J59" t="s">
         <v>238</v>
@@ -5640,13 +5640,13 @@
         <v>243</v>
       </c>
       <c r="G60" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H60" t="s">
         <v>236</v>
       </c>
       <c r="I60" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J60" t="s">
         <v>238</v>
@@ -5675,13 +5675,13 @@
         <v>243</v>
       </c>
       <c r="G61" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H61" t="s">
         <v>236</v>
       </c>
       <c r="I61" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J61" t="s">
         <v>238</v>
@@ -5710,13 +5710,13 @@
         <v>243</v>
       </c>
       <c r="G62" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H62" t="s">
         <v>236</v>
       </c>
       <c r="I62" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J62" t="s">
         <v>238</v>
@@ -5742,16 +5742,16 @@
         <v>233</v>
       </c>
       <c r="F63" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="G63" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="H63" t="s">
         <v>236</v>
       </c>
       <c r="I63" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J63" t="s">
         <v>238</v>
@@ -5777,16 +5777,16 @@
         <v>233</v>
       </c>
       <c r="F64" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="G64" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="H64" t="s">
         <v>236</v>
       </c>
       <c r="I64" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J64" t="s">
         <v>238</v>
@@ -5815,13 +5815,13 @@
         <v>281</v>
       </c>
       <c r="G65" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="H65" t="s">
         <v>236</v>
       </c>
       <c r="I65" t="s">
-        <v>237</v>
+        <v>282</v>
       </c>
       <c r="J65" t="s">
         <v>238</v>
@@ -5885,13 +5885,13 @@
         <v>243</v>
       </c>
       <c r="G67" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H67" t="s">
         <v>236</v>
       </c>
       <c r="I67" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J67" t="s">
         <v>238</v>
@@ -5917,10 +5917,10 @@
         <v>233</v>
       </c>
       <c r="F68" t="s">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="G68" t="s">
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="H68" t="s">
         <v>236</v>
@@ -5952,10 +5952,10 @@
         <v>233</v>
       </c>
       <c r="F69" t="s">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="G69" t="s">
-        <v>296</v>
+        <v>235</v>
       </c>
       <c r="H69" t="s">
         <v>236</v>
@@ -5990,13 +5990,13 @@
         <v>248</v>
       </c>
       <c r="G70" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="H70" t="s">
         <v>236</v>
       </c>
       <c r="I70" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J70" t="s">
         <v>238</v>
@@ -6025,13 +6025,13 @@
         <v>248</v>
       </c>
       <c r="G71" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="H71" t="s">
         <v>236</v>
       </c>
       <c r="I71" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J71" t="s">
         <v>238</v>
@@ -6095,19 +6095,19 @@
         <v>309</v>
       </c>
       <c r="G73" t="s">
+        <v>235</v>
+      </c>
+      <c r="H73" t="s">
+        <v>236</v>
+      </c>
+      <c r="I73" t="s">
         <v>310</v>
-      </c>
-      <c r="H73" t="s">
-        <v>255</v>
-      </c>
-      <c r="I73" t="s">
-        <v>237</v>
       </c>
       <c r="J73" t="s">
         <v>238</v>
       </c>
       <c r="K73" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6130,19 +6130,19 @@
         <v>314</v>
       </c>
       <c r="G74" t="s">
+        <v>235</v>
+      </c>
+      <c r="H74" t="s">
+        <v>236</v>
+      </c>
+      <c r="I74" t="s">
         <v>315</v>
-      </c>
-      <c r="H74" t="s">
-        <v>255</v>
-      </c>
-      <c r="I74" t="s">
-        <v>237</v>
       </c>
       <c r="J74" t="s">
         <v>238</v>
       </c>
       <c r="K74" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6165,19 +6165,19 @@
         <v>319</v>
       </c>
       <c r="G75" t="s">
+        <v>235</v>
+      </c>
+      <c r="H75" t="s">
+        <v>236</v>
+      </c>
+      <c r="I75" t="s">
         <v>320</v>
-      </c>
-      <c r="H75" t="s">
-        <v>255</v>
-      </c>
-      <c r="I75" t="s">
-        <v>237</v>
       </c>
       <c r="J75" t="s">
         <v>238</v>
       </c>
       <c r="K75" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6200,19 +6200,19 @@
         <v>309</v>
       </c>
       <c r="G76" t="s">
+        <v>235</v>
+      </c>
+      <c r="H76" t="s">
+        <v>236</v>
+      </c>
+      <c r="I76" t="s">
         <v>310</v>
-      </c>
-      <c r="H76" t="s">
-        <v>255</v>
-      </c>
-      <c r="I76" t="s">
-        <v>237</v>
       </c>
       <c r="J76" t="s">
         <v>238</v>
       </c>
       <c r="K76" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -6235,19 +6235,19 @@
         <v>309</v>
       </c>
       <c r="G77" t="s">
+        <v>235</v>
+      </c>
+      <c r="H77" t="s">
+        <v>236</v>
+      </c>
+      <c r="I77" t="s">
         <v>310</v>
-      </c>
-      <c r="H77" t="s">
-        <v>255</v>
-      </c>
-      <c r="I77" t="s">
-        <v>237</v>
       </c>
       <c r="J77" t="s">
         <v>238</v>
       </c>
       <c r="K77" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -6270,19 +6270,19 @@
         <v>314</v>
       </c>
       <c r="G78" t="s">
+        <v>235</v>
+      </c>
+      <c r="H78" t="s">
+        <v>236</v>
+      </c>
+      <c r="I78" t="s">
         <v>315</v>
-      </c>
-      <c r="H78" t="s">
-        <v>255</v>
-      </c>
-      <c r="I78" t="s">
-        <v>237</v>
       </c>
       <c r="J78" t="s">
         <v>238</v>
       </c>
       <c r="K78" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -6302,19 +6302,19 @@
         <v>332</v>
       </c>
       <c r="G79" t="s">
+        <v>235</v>
+      </c>
+      <c r="H79" t="s">
+        <v>236</v>
+      </c>
+      <c r="I79" t="s">
         <v>333</v>
-      </c>
-      <c r="H79" t="s">
-        <v>255</v>
-      </c>
-      <c r="I79" t="s">
-        <v>237</v>
       </c>
       <c r="J79" t="s">
         <v>238</v>
       </c>
       <c r="K79" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -6337,19 +6337,19 @@
         <v>337</v>
       </c>
       <c r="G80" t="s">
+        <v>235</v>
+      </c>
+      <c r="H80" t="s">
+        <v>236</v>
+      </c>
+      <c r="I80" t="s">
         <v>338</v>
-      </c>
-      <c r="H80" t="s">
-        <v>339</v>
-      </c>
-      <c r="I80" t="s">
-        <v>237</v>
       </c>
       <c r="J80" t="s">
         <v>238</v>
       </c>
       <c r="K80" t="s">
-        <v>239</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -6372,19 +6372,19 @@
         <v>337</v>
       </c>
       <c r="G81" t="s">
+        <v>235</v>
+      </c>
+      <c r="H81" t="s">
+        <v>236</v>
+      </c>
+      <c r="I81" t="s">
         <v>338</v>
-      </c>
-      <c r="H81" t="s">
-        <v>339</v>
-      </c>
-      <c r="I81" t="s">
-        <v>237</v>
       </c>
       <c r="J81" t="s">
         <v>238</v>
       </c>
       <c r="K81" t="s">
-        <v>239</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -6407,19 +6407,19 @@
         <v>337</v>
       </c>
       <c r="G82" t="s">
+        <v>235</v>
+      </c>
+      <c r="H82" t="s">
+        <v>236</v>
+      </c>
+      <c r="I82" t="s">
         <v>338</v>
-      </c>
-      <c r="H82" t="s">
-        <v>339</v>
-      </c>
-      <c r="I82" t="s">
-        <v>237</v>
       </c>
       <c r="J82" t="s">
         <v>238</v>
       </c>
       <c r="K82" t="s">
-        <v>239</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -6439,10 +6439,10 @@
         <v>233</v>
       </c>
       <c r="F83" t="s">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="G83" t="s">
-        <v>296</v>
+        <v>235</v>
       </c>
       <c r="H83" t="s">
         <v>236</v>
@@ -6477,13 +6477,13 @@
         <v>352</v>
       </c>
       <c r="G84" t="s">
-        <v>353</v>
+        <v>235</v>
       </c>
       <c r="H84" t="s">
         <v>236</v>
       </c>
       <c r="I84" t="s">
-        <v>237</v>
+        <v>353</v>
       </c>
       <c r="J84" t="s">
         <v>238</v>
@@ -6509,16 +6509,16 @@
         <v>233</v>
       </c>
       <c r="F85" t="s">
-        <v>243</v>
+        <v>357</v>
       </c>
       <c r="G85" t="s">
-        <v>357</v>
+        <v>235</v>
       </c>
       <c r="H85" t="s">
         <v>236</v>
       </c>
       <c r="I85" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J85" t="s">
         <v>238</v>
@@ -6547,19 +6547,19 @@
         <v>361</v>
       </c>
       <c r="G86" t="s">
+        <v>235</v>
+      </c>
+      <c r="H86" t="s">
+        <v>236</v>
+      </c>
+      <c r="I86" t="s">
         <v>362</v>
-      </c>
-      <c r="H86" t="s">
-        <v>339</v>
-      </c>
-      <c r="I86" t="s">
-        <v>237</v>
       </c>
       <c r="J86" t="s">
         <v>238</v>
       </c>
       <c r="K86" t="s">
-        <v>239</v>
+        <v>339</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -6579,16 +6579,16 @@
         <v>233</v>
       </c>
       <c r="F87" t="s">
-        <v>243</v>
+        <v>357</v>
       </c>
       <c r="G87" t="s">
-        <v>357</v>
+        <v>235</v>
       </c>
       <c r="H87" t="s">
         <v>236</v>
       </c>
       <c r="I87" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J87" t="s">
         <v>238</v>
@@ -6614,13 +6614,13 @@
         <v>243</v>
       </c>
       <c r="G88" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H88" t="s">
         <v>236</v>
       </c>
       <c r="I88" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J88" t="s">
         <v>238</v>
@@ -6649,13 +6649,13 @@
         <v>243</v>
       </c>
       <c r="G89" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H89" t="s">
         <v>236</v>
       </c>
       <c r="I89" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J89" t="s">
         <v>238</v>
@@ -6684,19 +6684,19 @@
         <v>253</v>
       </c>
       <c r="G90" t="s">
+        <v>235</v>
+      </c>
+      <c r="H90" t="s">
+        <v>236</v>
+      </c>
+      <c r="I90" t="s">
         <v>254</v>
-      </c>
-      <c r="H90" t="s">
-        <v>255</v>
-      </c>
-      <c r="I90" t="s">
-        <v>237</v>
       </c>
       <c r="J90" t="s">
         <v>238</v>
       </c>
       <c r="K90" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -6719,19 +6719,19 @@
         <v>377</v>
       </c>
       <c r="G91" t="s">
+        <v>235</v>
+      </c>
+      <c r="H91" t="s">
+        <v>236</v>
+      </c>
+      <c r="I91" t="s">
         <v>378</v>
-      </c>
-      <c r="H91" t="s">
-        <v>379</v>
-      </c>
-      <c r="I91" t="s">
-        <v>237</v>
       </c>
       <c r="J91" t="s">
         <v>238</v>
       </c>
       <c r="K91" t="s">
-        <v>239</v>
+        <v>379</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -6754,19 +6754,19 @@
         <v>253</v>
       </c>
       <c r="G92" t="s">
+        <v>235</v>
+      </c>
+      <c r="H92" t="s">
+        <v>236</v>
+      </c>
+      <c r="I92" t="s">
         <v>254</v>
-      </c>
-      <c r="H92" t="s">
-        <v>255</v>
-      </c>
-      <c r="I92" t="s">
-        <v>237</v>
       </c>
       <c r="J92" t="s">
         <v>238</v>
       </c>
       <c r="K92" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -6789,13 +6789,13 @@
         <v>248</v>
       </c>
       <c r="G93" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="H93" t="s">
         <v>236</v>
       </c>
       <c r="I93" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J93" t="s">
         <v>238</v>
@@ -6824,19 +6824,19 @@
         <v>253</v>
       </c>
       <c r="G94" t="s">
+        <v>235</v>
+      </c>
+      <c r="H94" t="s">
+        <v>236</v>
+      </c>
+      <c r="I94" t="s">
         <v>254</v>
-      </c>
-      <c r="H94" t="s">
-        <v>255</v>
-      </c>
-      <c r="I94" t="s">
-        <v>237</v>
       </c>
       <c r="J94" t="s">
         <v>238</v>
       </c>
       <c r="K94" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -6859,13 +6859,13 @@
         <v>392</v>
       </c>
       <c r="G95" t="s">
-        <v>393</v>
+        <v>235</v>
       </c>
       <c r="H95" t="s">
         <v>236</v>
       </c>
       <c r="I95" t="s">
-        <v>237</v>
+        <v>393</v>
       </c>
       <c r="J95" t="s">
         <v>238</v>
@@ -6888,25 +6888,25 @@
         <v>14</v>
       </c>
       <c r="E96" t="s">
-        <v>233</v>
+        <v>397</v>
       </c>
       <c r="F96" t="s">
         <v>253</v>
       </c>
       <c r="G96" t="s">
+        <v>235</v>
+      </c>
+      <c r="H96" t="s">
+        <v>398</v>
+      </c>
+      <c r="I96" t="s">
         <v>254</v>
       </c>
-      <c r="H96" t="s">
+      <c r="J96" t="s">
+        <v>238</v>
+      </c>
+      <c r="K96" t="s">
         <v>255</v>
-      </c>
-      <c r="I96" t="s">
-        <v>397</v>
-      </c>
-      <c r="J96" t="s">
-        <v>398</v>
-      </c>
-      <c r="K96" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -6923,25 +6923,25 @@
         <v>14</v>
       </c>
       <c r="E97" t="s">
-        <v>233</v>
+        <v>397</v>
       </c>
       <c r="F97" t="s">
         <v>253</v>
       </c>
       <c r="G97" t="s">
+        <v>235</v>
+      </c>
+      <c r="H97" t="s">
+        <v>398</v>
+      </c>
+      <c r="I97" t="s">
         <v>254</v>
       </c>
-      <c r="H97" t="s">
+      <c r="J97" t="s">
+        <v>238</v>
+      </c>
+      <c r="K97" t="s">
         <v>255</v>
-      </c>
-      <c r="I97" t="s">
-        <v>397</v>
-      </c>
-      <c r="J97" t="s">
-        <v>398</v>
-      </c>
-      <c r="K97" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -6958,25 +6958,25 @@
         <v>14</v>
       </c>
       <c r="E98" t="s">
-        <v>233</v>
+        <v>397</v>
       </c>
       <c r="F98" t="s">
         <v>405</v>
       </c>
       <c r="G98" t="s">
+        <v>235</v>
+      </c>
+      <c r="H98" t="s">
+        <v>398</v>
+      </c>
+      <c r="I98" t="s">
         <v>406</v>
       </c>
-      <c r="H98" t="s">
+      <c r="J98" t="s">
+        <v>238</v>
+      </c>
+      <c r="K98" t="s">
         <v>407</v>
-      </c>
-      <c r="I98" t="s">
-        <v>397</v>
-      </c>
-      <c r="J98" t="s">
-        <v>398</v>
-      </c>
-      <c r="K98" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -6993,25 +6993,25 @@
         <v>14</v>
       </c>
       <c r="E99" t="s">
-        <v>233</v>
+        <v>397</v>
       </c>
       <c r="F99" t="s">
         <v>253</v>
       </c>
       <c r="G99" t="s">
+        <v>235</v>
+      </c>
+      <c r="H99" t="s">
+        <v>398</v>
+      </c>
+      <c r="I99" t="s">
         <v>254</v>
       </c>
-      <c r="H99" t="s">
+      <c r="J99" t="s">
+        <v>238</v>
+      </c>
+      <c r="K99" t="s">
         <v>255</v>
-      </c>
-      <c r="I99" t="s">
-        <v>397</v>
-      </c>
-      <c r="J99" t="s">
-        <v>398</v>
-      </c>
-      <c r="K99" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -7028,25 +7028,25 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
-        <v>233</v>
+        <v>397</v>
       </c>
       <c r="F100" t="s">
         <v>319</v>
       </c>
       <c r="G100" t="s">
+        <v>235</v>
+      </c>
+      <c r="H100" t="s">
+        <v>398</v>
+      </c>
+      <c r="I100" t="s">
         <v>320</v>
       </c>
-      <c r="H100" t="s">
+      <c r="J100" t="s">
+        <v>238</v>
+      </c>
+      <c r="K100" t="s">
         <v>255</v>
-      </c>
-      <c r="I100" t="s">
-        <v>397</v>
-      </c>
-      <c r="J100" t="s">
-        <v>398</v>
-      </c>
-      <c r="K100" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -7063,25 +7063,25 @@
         <v>14</v>
       </c>
       <c r="E101" t="s">
-        <v>233</v>
+        <v>397</v>
       </c>
       <c r="F101" t="s">
         <v>253</v>
       </c>
       <c r="G101" t="s">
+        <v>235</v>
+      </c>
+      <c r="H101" t="s">
+        <v>398</v>
+      </c>
+      <c r="I101" t="s">
         <v>254</v>
       </c>
-      <c r="H101" t="s">
+      <c r="J101" t="s">
+        <v>238</v>
+      </c>
+      <c r="K101" t="s">
         <v>255</v>
-      </c>
-      <c r="I101" t="s">
-        <v>397</v>
-      </c>
-      <c r="J101" t="s">
-        <v>398</v>
-      </c>
-      <c r="K101" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -7097,20 +7097,20 @@
       <c r="D102" t="s">
         <v>14</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>420</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>421</v>
       </c>
-      <c r="G102" t="s">
+      <c r="I102" t="s">
         <v>422</v>
       </c>
-      <c r="H102" t="s">
+      <c r="J102" t="s">
+        <v>423</v>
+      </c>
+      <c r="K102" t="s">
         <v>379</v>
-      </c>
-      <c r="K102" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -7126,20 +7126,20 @@
       <c r="D103" t="s">
         <v>14</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>420</v>
       </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
         <v>421</v>
       </c>
-      <c r="G103" t="s">
+      <c r="I103" t="s">
         <v>422</v>
       </c>
-      <c r="H103" t="s">
+      <c r="J103" t="s">
+        <v>423</v>
+      </c>
+      <c r="K103" t="s">
         <v>379</v>
-      </c>
-      <c r="K103" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -7155,20 +7155,20 @@
       <c r="D104" t="s">
         <v>14</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>420</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>421</v>
       </c>
-      <c r="G104" t="s">
+      <c r="I104" t="s">
         <v>422</v>
       </c>
-      <c r="H104" t="s">
+      <c r="J104" t="s">
+        <v>423</v>
+      </c>
+      <c r="K104" t="s">
         <v>379</v>
-      </c>
-      <c r="K104" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -7184,20 +7184,20 @@
       <c r="D105" t="s">
         <v>14</v>
       </c>
-      <c r="E105" t="s">
-        <v>420</v>
-      </c>
       <c r="F105" t="s">
         <v>433</v>
       </c>
       <c r="G105" t="s">
+        <v>421</v>
+      </c>
+      <c r="I105" t="s">
         <v>434</v>
       </c>
-      <c r="H105" t="s">
+      <c r="J105" t="s">
+        <v>423</v>
+      </c>
+      <c r="K105" t="s">
         <v>379</v>
-      </c>
-      <c r="K105" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7213,20 +7213,20 @@
       <c r="D106" t="s">
         <v>14</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>420</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>421</v>
       </c>
-      <c r="G106" t="s">
+      <c r="I106" t="s">
         <v>422</v>
       </c>
-      <c r="H106" t="s">
+      <c r="J106" t="s">
+        <v>423</v>
+      </c>
+      <c r="K106" t="s">
         <v>379</v>
-      </c>
-      <c r="K106" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -7242,20 +7242,20 @@
       <c r="D107" t="s">
         <v>14</v>
       </c>
-      <c r="E107" t="s">
-        <v>420</v>
-      </c>
       <c r="F107" t="s">
         <v>377</v>
       </c>
       <c r="G107" t="s">
+        <v>421</v>
+      </c>
+      <c r="I107" t="s">
         <v>378</v>
       </c>
-      <c r="H107" t="s">
+      <c r="J107" t="s">
+        <v>423</v>
+      </c>
+      <c r="K107" t="s">
         <v>379</v>
-      </c>
-      <c r="K107" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -7271,20 +7271,20 @@
       <c r="D108" t="s">
         <v>14</v>
       </c>
-      <c r="E108" t="s">
-        <v>420</v>
-      </c>
       <c r="F108" t="s">
         <v>444</v>
       </c>
       <c r="G108" t="s">
+        <v>421</v>
+      </c>
+      <c r="I108" t="s">
         <v>445</v>
       </c>
-      <c r="H108" t="s">
+      <c r="J108" t="s">
+        <v>423</v>
+      </c>
+      <c r="K108" t="s">
         <v>379</v>
-      </c>
-      <c r="K108" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7300,20 +7300,20 @@
       <c r="D109" t="s">
         <v>14</v>
       </c>
-      <c r="E109" t="s">
-        <v>420</v>
-      </c>
       <c r="F109" t="s">
         <v>449</v>
       </c>
       <c r="G109" t="s">
+        <v>421</v>
+      </c>
+      <c r="I109" t="s">
         <v>450</v>
       </c>
-      <c r="H109" t="s">
-        <v>191</v>
+      <c r="J109" t="s">
+        <v>423</v>
       </c>
       <c r="K109" t="s">
-        <v>423</v>
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -7329,20 +7329,20 @@
       <c r="D110" t="s">
         <v>14</v>
       </c>
-      <c r="E110" t="s">
-        <v>420</v>
-      </c>
       <c r="F110" t="s">
         <v>454</v>
       </c>
       <c r="G110" t="s">
+        <v>421</v>
+      </c>
+      <c r="I110" t="s">
         <v>455</v>
       </c>
-      <c r="H110" t="s">
-        <v>191</v>
+      <c r="J110" t="s">
+        <v>423</v>
       </c>
       <c r="K110" t="s">
-        <v>423</v>
+        <v>192</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -7358,20 +7358,20 @@
       <c r="D111" t="s">
         <v>14</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>420</v>
       </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>421</v>
       </c>
-      <c r="G111" t="s">
+      <c r="I111" t="s">
         <v>422</v>
       </c>
-      <c r="H111" t="s">
+      <c r="J111" t="s">
+        <v>423</v>
+      </c>
+      <c r="K111" t="s">
         <v>379</v>
-      </c>
-      <c r="K111" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -7387,20 +7387,20 @@
       <c r="D112" t="s">
         <v>14</v>
       </c>
-      <c r="E112" t="s">
-        <v>420</v>
-      </c>
       <c r="F112" t="s">
         <v>462</v>
       </c>
       <c r="G112" t="s">
+        <v>421</v>
+      </c>
+      <c r="I112" t="s">
         <v>463</v>
       </c>
-      <c r="H112" t="s">
+      <c r="J112" t="s">
+        <v>423</v>
+      </c>
+      <c r="K112" t="s">
         <v>464</v>
-      </c>
-      <c r="K112" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -7416,20 +7416,20 @@
       <c r="D113" t="s">
         <v>14</v>
       </c>
-      <c r="E113" t="s">
-        <v>420</v>
-      </c>
       <c r="F113" t="s">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="G113" t="s">
-        <v>296</v>
-      </c>
-      <c r="H113" t="s">
-        <v>236</v>
+        <v>421</v>
+      </c>
+      <c r="I113" t="s">
+        <v>237</v>
+      </c>
+      <c r="J113" t="s">
+        <v>423</v>
       </c>
       <c r="K113" t="s">
-        <v>423</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -7445,20 +7445,20 @@
       <c r="D114" t="s">
         <v>14</v>
       </c>
-      <c r="E114" t="s">
-        <v>420</v>
-      </c>
       <c r="F114" t="s">
         <v>314</v>
       </c>
       <c r="G114" t="s">
+        <v>421</v>
+      </c>
+      <c r="I114" t="s">
         <v>315</v>
       </c>
-      <c r="H114" t="s">
+      <c r="J114" t="s">
+        <v>423</v>
+      </c>
+      <c r="K114" t="s">
         <v>255</v>
-      </c>
-      <c r="K114" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -7474,20 +7474,20 @@
       <c r="D115" t="s">
         <v>14</v>
       </c>
-      <c r="E115" t="s">
-        <v>420</v>
-      </c>
       <c r="F115" t="s">
         <v>377</v>
       </c>
       <c r="G115" t="s">
+        <v>421</v>
+      </c>
+      <c r="I115" t="s">
         <v>378</v>
       </c>
-      <c r="H115" t="s">
+      <c r="J115" t="s">
+        <v>423</v>
+      </c>
+      <c r="K115" t="s">
         <v>379</v>
-      </c>
-      <c r="K115" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -7500,20 +7500,20 @@
       <c r="D116" t="s">
         <v>14</v>
       </c>
-      <c r="E116" t="s">
-        <v>420</v>
-      </c>
       <c r="F116" t="s">
         <v>476</v>
       </c>
       <c r="G116" t="s">
+        <v>421</v>
+      </c>
+      <c r="I116" t="s">
         <v>477</v>
       </c>
-      <c r="H116" t="s">
+      <c r="J116" t="s">
+        <v>423</v>
+      </c>
+      <c r="K116" t="s">
         <v>464</v>
-      </c>
-      <c r="K116" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -7526,20 +7526,20 @@
       <c r="D117" t="s">
         <v>14</v>
       </c>
-      <c r="E117" t="s">
-        <v>420</v>
-      </c>
       <c r="F117" t="s">
         <v>462</v>
       </c>
       <c r="G117" t="s">
+        <v>421</v>
+      </c>
+      <c r="I117" t="s">
         <v>463</v>
       </c>
-      <c r="H117" t="s">
+      <c r="J117" t="s">
+        <v>423</v>
+      </c>
+      <c r="K117" t="s">
         <v>464</v>
-      </c>
-      <c r="K117" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -7555,20 +7555,20 @@
       <c r="D118" t="s">
         <v>14</v>
       </c>
-      <c r="E118" t="s">
-        <v>420</v>
-      </c>
       <c r="F118" t="s">
-        <v>337</v>
+        <v>483</v>
       </c>
       <c r="G118" t="s">
-        <v>483</v>
-      </c>
-      <c r="H118" t="s">
+        <v>421</v>
+      </c>
+      <c r="I118" t="s">
+        <v>338</v>
+      </c>
+      <c r="J118" t="s">
+        <v>423</v>
+      </c>
+      <c r="K118" t="s">
         <v>339</v>
-      </c>
-      <c r="K118" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -7584,20 +7584,20 @@
       <c r="D119" t="s">
         <v>14</v>
       </c>
-      <c r="E119" t="s">
-        <v>420</v>
-      </c>
       <c r="F119" t="s">
         <v>377</v>
       </c>
       <c r="G119" t="s">
+        <v>421</v>
+      </c>
+      <c r="I119" t="s">
         <v>378</v>
       </c>
-      <c r="H119" t="s">
+      <c r="J119" t="s">
+        <v>423</v>
+      </c>
+      <c r="K119" t="s">
         <v>379</v>
-      </c>
-      <c r="K119" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -7613,20 +7613,20 @@
       <c r="D120" t="s">
         <v>14</v>
       </c>
-      <c r="E120" t="s">
-        <v>490</v>
-      </c>
       <c r="F120" t="s">
         <v>352</v>
       </c>
       <c r="G120" t="s">
+        <v>490</v>
+      </c>
+      <c r="I120" t="s">
         <v>353</v>
       </c>
-      <c r="H120" t="s">
-        <v>236</v>
+      <c r="J120" t="s">
+        <v>491</v>
       </c>
       <c r="K120" t="s">
-        <v>491</v>
+        <v>239</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -7642,20 +7642,20 @@
       <c r="D121" t="s">
         <v>14</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
+        <v>296</v>
+      </c>
+      <c r="G121" t="s">
         <v>490</v>
       </c>
-      <c r="F121" t="s">
-        <v>234</v>
-      </c>
-      <c r="G121" t="s">
-        <v>296</v>
-      </c>
-      <c r="H121" t="s">
-        <v>236</v>
+      <c r="I121" t="s">
+        <v>237</v>
+      </c>
+      <c r="J121" t="s">
+        <v>491</v>
       </c>
       <c r="K121" t="s">
-        <v>491</v>
+        <v>239</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -7671,20 +7671,20 @@
       <c r="D122" t="s">
         <v>14</v>
       </c>
-      <c r="E122" t="s">
-        <v>490</v>
-      </c>
       <c r="F122" t="s">
         <v>352</v>
       </c>
       <c r="G122" t="s">
+        <v>490</v>
+      </c>
+      <c r="I122" t="s">
         <v>353</v>
       </c>
-      <c r="H122" t="s">
-        <v>236</v>
+      <c r="J122" t="s">
+        <v>491</v>
       </c>
       <c r="K122" t="s">
-        <v>491</v>
+        <v>239</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -7700,20 +7700,20 @@
       <c r="D123" t="s">
         <v>14</v>
       </c>
-      <c r="E123" t="s">
-        <v>490</v>
-      </c>
       <c r="F123" t="s">
         <v>352</v>
       </c>
       <c r="G123" t="s">
+        <v>490</v>
+      </c>
+      <c r="I123" t="s">
         <v>353</v>
       </c>
-      <c r="H123" t="s">
-        <v>236</v>
+      <c r="J123" t="s">
+        <v>491</v>
       </c>
       <c r="K123" t="s">
-        <v>491</v>
+        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -7729,20 +7729,20 @@
       <c r="D124" t="s">
         <v>14</v>
       </c>
-      <c r="E124" t="s">
-        <v>490</v>
-      </c>
       <c r="F124" t="s">
         <v>504</v>
       </c>
       <c r="G124" t="s">
+        <v>490</v>
+      </c>
+      <c r="I124" t="s">
         <v>505</v>
       </c>
-      <c r="H124" t="s">
+      <c r="J124" t="s">
+        <v>491</v>
+      </c>
+      <c r="K124" t="s">
         <v>339</v>
-      </c>
-      <c r="K124" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -7758,20 +7758,20 @@
       <c r="D125" t="s">
         <v>14</v>
       </c>
-      <c r="E125" t="s">
-        <v>490</v>
-      </c>
       <c r="F125" t="s">
         <v>504</v>
       </c>
       <c r="G125" t="s">
+        <v>490</v>
+      </c>
+      <c r="I125" t="s">
         <v>505</v>
       </c>
-      <c r="H125" t="s">
+      <c r="J125" t="s">
+        <v>491</v>
+      </c>
+      <c r="K125" t="s">
         <v>339</v>
-      </c>
-      <c r="K125" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -7787,20 +7787,20 @@
       <c r="D126" t="s">
         <v>14</v>
       </c>
-      <c r="E126" t="s">
-        <v>490</v>
-      </c>
       <c r="F126" t="s">
         <v>504</v>
       </c>
       <c r="G126" t="s">
+        <v>490</v>
+      </c>
+      <c r="I126" t="s">
         <v>505</v>
       </c>
-      <c r="H126" t="s">
+      <c r="J126" t="s">
+        <v>491</v>
+      </c>
+      <c r="K126" t="s">
         <v>339</v>
-      </c>
-      <c r="K126" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -7816,20 +7816,20 @@
       <c r="D127" t="s">
         <v>14</v>
       </c>
-      <c r="E127" t="s">
-        <v>490</v>
-      </c>
       <c r="F127" t="s">
         <v>504</v>
       </c>
       <c r="G127" t="s">
+        <v>490</v>
+      </c>
+      <c r="I127" t="s">
         <v>505</v>
       </c>
-      <c r="H127" t="s">
+      <c r="J127" t="s">
+        <v>491</v>
+      </c>
+      <c r="K127" t="s">
         <v>339</v>
-      </c>
-      <c r="K127" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -7845,20 +7845,20 @@
       <c r="D128" t="s">
         <v>14</v>
       </c>
-      <c r="E128" t="s">
-        <v>490</v>
-      </c>
       <c r="F128" t="s">
         <v>504</v>
       </c>
       <c r="G128" t="s">
+        <v>490</v>
+      </c>
+      <c r="I128" t="s">
         <v>505</v>
       </c>
-      <c r="H128" t="s">
+      <c r="J128" t="s">
+        <v>491</v>
+      </c>
+      <c r="K128" t="s">
         <v>339</v>
-      </c>
-      <c r="K128" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -7874,20 +7874,20 @@
       <c r="D129" t="s">
         <v>14</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
+        <v>521</v>
+      </c>
+      <c r="G129" t="s">
         <v>490</v>
       </c>
-      <c r="F129" t="s">
-        <v>504</v>
-      </c>
-      <c r="G129" t="s">
-        <v>521</v>
-      </c>
-      <c r="H129" t="s">
+      <c r="I129" t="s">
+        <v>505</v>
+      </c>
+      <c r="J129" t="s">
+        <v>491</v>
+      </c>
+      <c r="K129" t="s">
         <v>339</v>
-      </c>
-      <c r="K129" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7903,20 +7903,20 @@
       <c r="D130" t="s">
         <v>14</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
+        <v>525</v>
+      </c>
+      <c r="G130" t="s">
         <v>490</v>
       </c>
-      <c r="F130" t="s">
-        <v>504</v>
-      </c>
-      <c r="G130" t="s">
-        <v>525</v>
-      </c>
-      <c r="H130" t="s">
+      <c r="I130" t="s">
+        <v>505</v>
+      </c>
+      <c r="J130" t="s">
+        <v>491</v>
+      </c>
+      <c r="K130" t="s">
         <v>339</v>
-      </c>
-      <c r="K130" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7932,20 +7932,20 @@
       <c r="D131" t="s">
         <v>14</v>
       </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
+        <v>529</v>
+      </c>
+      <c r="G131" t="s">
         <v>490</v>
       </c>
-      <c r="F131" t="s">
-        <v>504</v>
-      </c>
-      <c r="G131" t="s">
-        <v>529</v>
-      </c>
-      <c r="H131" t="s">
+      <c r="I131" t="s">
+        <v>505</v>
+      </c>
+      <c r="J131" t="s">
+        <v>491</v>
+      </c>
+      <c r="K131" t="s">
         <v>339</v>
-      </c>
-      <c r="K131" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7961,20 +7961,20 @@
       <c r="D132" t="s">
         <v>14</v>
       </c>
-      <c r="E132" t="s">
-        <v>490</v>
-      </c>
       <c r="F132" t="s">
         <v>533</v>
       </c>
       <c r="G132" t="s">
+        <v>490</v>
+      </c>
+      <c r="I132" t="s">
         <v>534</v>
       </c>
-      <c r="H132" t="s">
+      <c r="J132" t="s">
+        <v>491</v>
+      </c>
+      <c r="K132" t="s">
         <v>339</v>
-      </c>
-      <c r="K132" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -7987,20 +7987,20 @@
       <c r="D133" t="s">
         <v>14</v>
       </c>
-      <c r="E133" t="s">
-        <v>490</v>
-      </c>
       <c r="F133" t="s">
         <v>392</v>
       </c>
       <c r="G133" t="s">
+        <v>490</v>
+      </c>
+      <c r="I133" t="s">
         <v>393</v>
       </c>
-      <c r="H133" t="s">
-        <v>236</v>
+      <c r="J133" t="s">
+        <v>491</v>
       </c>
       <c r="K133" t="s">
-        <v>491</v>
+        <v>239</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -8016,20 +8016,20 @@
       <c r="D134" t="s">
         <v>14</v>
       </c>
-      <c r="E134" t="s">
-        <v>540</v>
-      </c>
       <c r="F134" t="s">
         <v>361</v>
       </c>
       <c r="G134" t="s">
+        <v>540</v>
+      </c>
+      <c r="I134" t="s">
         <v>362</v>
       </c>
-      <c r="H134" t="s">
+      <c r="J134" t="s">
+        <v>541</v>
+      </c>
+      <c r="K134" t="s">
         <v>339</v>
-      </c>
-      <c r="K134" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -8042,20 +8042,20 @@
       <c r="D135" t="s">
         <v>14</v>
       </c>
-      <c r="E135" t="s">
-        <v>540</v>
-      </c>
       <c r="F135" t="s">
         <v>361</v>
       </c>
       <c r="G135" t="s">
+        <v>540</v>
+      </c>
+      <c r="I135" t="s">
         <v>362</v>
       </c>
-      <c r="H135" t="s">
+      <c r="J135" t="s">
+        <v>541</v>
+      </c>
+      <c r="K135" t="s">
         <v>339</v>
-      </c>
-      <c r="K135" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -8071,20 +8071,20 @@
       <c r="D136" t="s">
         <v>14</v>
       </c>
-      <c r="E136" t="s">
-        <v>540</v>
-      </c>
       <c r="F136" t="s">
         <v>361</v>
       </c>
       <c r="G136" t="s">
+        <v>540</v>
+      </c>
+      <c r="I136" t="s">
         <v>362</v>
       </c>
-      <c r="H136" t="s">
+      <c r="J136" t="s">
+        <v>541</v>
+      </c>
+      <c r="K136" t="s">
         <v>339</v>
-      </c>
-      <c r="K136" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -8100,20 +8100,20 @@
       <c r="D137" t="s">
         <v>14</v>
       </c>
-      <c r="E137" t="s">
-        <v>540</v>
-      </c>
       <c r="F137" t="s">
         <v>361</v>
       </c>
       <c r="G137" t="s">
+        <v>540</v>
+      </c>
+      <c r="I137" t="s">
         <v>362</v>
       </c>
-      <c r="H137" t="s">
+      <c r="J137" t="s">
+        <v>541</v>
+      </c>
+      <c r="K137" t="s">
         <v>339</v>
-      </c>
-      <c r="K137" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -8129,20 +8129,20 @@
       <c r="D138" t="s">
         <v>14</v>
       </c>
-      <c r="E138" t="s">
-        <v>540</v>
-      </c>
       <c r="F138" t="s">
         <v>361</v>
       </c>
       <c r="G138" t="s">
+        <v>540</v>
+      </c>
+      <c r="I138" t="s">
         <v>362</v>
       </c>
-      <c r="H138" t="s">
+      <c r="J138" t="s">
+        <v>541</v>
+      </c>
+      <c r="K138" t="s">
         <v>339</v>
-      </c>
-      <c r="K138" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -8158,20 +8158,20 @@
       <c r="D139" t="s">
         <v>14</v>
       </c>
-      <c r="E139" t="s">
-        <v>540</v>
-      </c>
       <c r="F139" t="s">
         <v>556</v>
       </c>
       <c r="G139" t="s">
+        <v>540</v>
+      </c>
+      <c r="I139" t="s">
         <v>557</v>
       </c>
-      <c r="H139" t="s">
+      <c r="J139" t="s">
+        <v>541</v>
+      </c>
+      <c r="K139" t="s">
         <v>464</v>
-      </c>
-      <c r="K139" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -8187,20 +8187,20 @@
       <c r="D140" t="s">
         <v>14</v>
       </c>
-      <c r="E140" t="s">
-        <v>540</v>
-      </c>
       <c r="F140" t="s">
         <v>361</v>
       </c>
       <c r="G140" t="s">
+        <v>540</v>
+      </c>
+      <c r="I140" t="s">
         <v>362</v>
       </c>
-      <c r="H140" t="s">
+      <c r="J140" t="s">
+        <v>541</v>
+      </c>
+      <c r="K140" t="s">
         <v>339</v>
-      </c>
-      <c r="K140" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -8226,16 +8226,16 @@
         <v>566</v>
       </c>
       <c r="H141" t="s">
+        <v>567</v>
+      </c>
+      <c r="I141" t="s">
+        <v>568</v>
+      </c>
+      <c r="J141" t="s">
+        <v>569</v>
+      </c>
+      <c r="K141" t="s">
         <v>339</v>
-      </c>
-      <c r="I141" t="s">
-        <v>567</v>
-      </c>
-      <c r="J141" t="s">
-        <v>568</v>
-      </c>
-      <c r="K141" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -8258,16 +8258,16 @@
         <v>566</v>
       </c>
       <c r="H142" t="s">
+        <v>567</v>
+      </c>
+      <c r="I142" t="s">
+        <v>568</v>
+      </c>
+      <c r="J142" t="s">
+        <v>569</v>
+      </c>
+      <c r="K142" t="s">
         <v>339</v>
-      </c>
-      <c r="I142" t="s">
-        <v>567</v>
-      </c>
-      <c r="J142" t="s">
-        <v>568</v>
-      </c>
-      <c r="K142" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -8290,19 +8290,19 @@
         <v>575</v>
       </c>
       <c r="G143" t="s">
+        <v>566</v>
+      </c>
+      <c r="H143" t="s">
+        <v>567</v>
+      </c>
+      <c r="I143" t="s">
         <v>576</v>
       </c>
-      <c r="H143" t="s">
+      <c r="J143" t="s">
+        <v>569</v>
+      </c>
+      <c r="K143" t="s">
         <v>339</v>
-      </c>
-      <c r="I143" t="s">
-        <v>567</v>
-      </c>
-      <c r="J143" t="s">
-        <v>568</v>
-      </c>
-      <c r="K143" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -8325,19 +8325,19 @@
         <v>575</v>
       </c>
       <c r="G144" t="s">
+        <v>566</v>
+      </c>
+      <c r="H144" t="s">
+        <v>567</v>
+      </c>
+      <c r="I144" t="s">
         <v>576</v>
       </c>
-      <c r="H144" t="s">
+      <c r="J144" t="s">
+        <v>569</v>
+      </c>
+      <c r="K144" t="s">
         <v>339</v>
-      </c>
-      <c r="I144" t="s">
-        <v>567</v>
-      </c>
-      <c r="J144" t="s">
-        <v>568</v>
-      </c>
-      <c r="K144" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -8360,19 +8360,19 @@
         <v>575</v>
       </c>
       <c r="G145" t="s">
+        <v>566</v>
+      </c>
+      <c r="H145" t="s">
+        <v>567</v>
+      </c>
+      <c r="I145" t="s">
         <v>576</v>
       </c>
-      <c r="H145" t="s">
+      <c r="J145" t="s">
+        <v>569</v>
+      </c>
+      <c r="K145" t="s">
         <v>339</v>
-      </c>
-      <c r="I145" t="s">
-        <v>567</v>
-      </c>
-      <c r="J145" t="s">
-        <v>568</v>
-      </c>
-      <c r="K145" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -8398,16 +8398,16 @@
         <v>566</v>
       </c>
       <c r="H146" t="s">
+        <v>567</v>
+      </c>
+      <c r="I146" t="s">
+        <v>568</v>
+      </c>
+      <c r="J146" t="s">
+        <v>569</v>
+      </c>
+      <c r="K146" t="s">
         <v>339</v>
-      </c>
-      <c r="I146" t="s">
-        <v>567</v>
-      </c>
-      <c r="J146" t="s">
-        <v>568</v>
-      </c>
-      <c r="K146" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -8424,7 +8424,7 @@
         <v>14</v>
       </c>
       <c r="E147" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="F147" t="s">
         <v>565</v>
@@ -8433,16 +8433,16 @@
         <v>566</v>
       </c>
       <c r="H147" t="s">
+        <v>590</v>
+      </c>
+      <c r="I147" t="s">
+        <v>568</v>
+      </c>
+      <c r="J147" t="s">
+        <v>569</v>
+      </c>
+      <c r="K147" t="s">
         <v>339</v>
-      </c>
-      <c r="I147" t="s">
-        <v>589</v>
-      </c>
-      <c r="J147" t="s">
-        <v>590</v>
-      </c>
-      <c r="K147" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -8459,7 +8459,7 @@
         <v>14</v>
       </c>
       <c r="E148" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="F148" t="s">
         <v>565</v>
@@ -8468,16 +8468,16 @@
         <v>566</v>
       </c>
       <c r="H148" t="s">
+        <v>590</v>
+      </c>
+      <c r="I148" t="s">
+        <v>568</v>
+      </c>
+      <c r="J148" t="s">
+        <v>569</v>
+      </c>
+      <c r="K148" t="s">
         <v>339</v>
-      </c>
-      <c r="I148" t="s">
-        <v>589</v>
-      </c>
-      <c r="J148" t="s">
-        <v>590</v>
-      </c>
-      <c r="K148" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -8494,7 +8494,7 @@
         <v>14</v>
       </c>
       <c r="E149" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="F149" t="s">
         <v>565</v>
@@ -8503,16 +8503,16 @@
         <v>566</v>
       </c>
       <c r="H149" t="s">
+        <v>590</v>
+      </c>
+      <c r="I149" t="s">
+        <v>568</v>
+      </c>
+      <c r="J149" t="s">
+        <v>569</v>
+      </c>
+      <c r="K149" t="s">
         <v>339</v>
-      </c>
-      <c r="I149" t="s">
-        <v>589</v>
-      </c>
-      <c r="J149" t="s">
-        <v>590</v>
-      </c>
-      <c r="K149" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -8529,7 +8529,7 @@
         <v>14</v>
       </c>
       <c r="E150" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="F150" t="s">
         <v>565</v>
@@ -8538,16 +8538,16 @@
         <v>566</v>
       </c>
       <c r="H150" t="s">
+        <v>590</v>
+      </c>
+      <c r="I150" t="s">
+        <v>568</v>
+      </c>
+      <c r="J150" t="s">
+        <v>569</v>
+      </c>
+      <c r="K150" t="s">
         <v>339</v>
-      </c>
-      <c r="I150" t="s">
-        <v>589</v>
-      </c>
-      <c r="J150" t="s">
-        <v>590</v>
-      </c>
-      <c r="K150" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -8564,7 +8564,7 @@
         <v>14</v>
       </c>
       <c r="E151" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="F151" t="s">
         <v>565</v>
@@ -8573,16 +8573,16 @@
         <v>566</v>
       </c>
       <c r="H151" t="s">
+        <v>590</v>
+      </c>
+      <c r="I151" t="s">
+        <v>568</v>
+      </c>
+      <c r="J151" t="s">
+        <v>569</v>
+      </c>
+      <c r="K151" t="s">
         <v>339</v>
-      </c>
-      <c r="I151" t="s">
-        <v>589</v>
-      </c>
-      <c r="J151" t="s">
-        <v>590</v>
-      </c>
-      <c r="K151" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -8599,7 +8599,7 @@
         <v>14</v>
       </c>
       <c r="E152" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="F152" t="s">
         <v>565</v>
@@ -8608,16 +8608,16 @@
         <v>566</v>
       </c>
       <c r="H152" t="s">
+        <v>590</v>
+      </c>
+      <c r="I152" t="s">
+        <v>568</v>
+      </c>
+      <c r="J152" t="s">
+        <v>569</v>
+      </c>
+      <c r="K152" t="s">
         <v>339</v>
-      </c>
-      <c r="I152" t="s">
-        <v>589</v>
-      </c>
-      <c r="J152" t="s">
-        <v>590</v>
-      </c>
-      <c r="K152" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -8634,7 +8634,7 @@
         <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="F153" t="s">
         <v>565</v>
@@ -8643,16 +8643,16 @@
         <v>566</v>
       </c>
       <c r="H153" t="s">
+        <v>590</v>
+      </c>
+      <c r="I153" t="s">
+        <v>568</v>
+      </c>
+      <c r="J153" t="s">
+        <v>569</v>
+      </c>
+      <c r="K153" t="s">
         <v>339</v>
-      </c>
-      <c r="I153" t="s">
-        <v>589</v>
-      </c>
-      <c r="J153" t="s">
-        <v>590</v>
-      </c>
-      <c r="K153" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -8669,7 +8669,7 @@
         <v>14</v>
       </c>
       <c r="E154" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="F154" t="s">
         <v>565</v>
@@ -8678,16 +8678,16 @@
         <v>566</v>
       </c>
       <c r="H154" t="s">
+        <v>590</v>
+      </c>
+      <c r="I154" t="s">
+        <v>568</v>
+      </c>
+      <c r="J154" t="s">
+        <v>569</v>
+      </c>
+      <c r="K154" t="s">
         <v>339</v>
-      </c>
-      <c r="I154" t="s">
-        <v>589</v>
-      </c>
-      <c r="J154" t="s">
-        <v>590</v>
-      </c>
-      <c r="K154" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -8704,7 +8704,7 @@
         <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="F155" t="s">
         <v>565</v>
@@ -8713,16 +8713,16 @@
         <v>566</v>
       </c>
       <c r="H155" t="s">
+        <v>590</v>
+      </c>
+      <c r="I155" t="s">
+        <v>568</v>
+      </c>
+      <c r="J155" t="s">
+        <v>569</v>
+      </c>
+      <c r="K155" t="s">
         <v>339</v>
-      </c>
-      <c r="I155" t="s">
-        <v>589</v>
-      </c>
-      <c r="J155" t="s">
-        <v>590</v>
-      </c>
-      <c r="K155" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -8739,7 +8739,7 @@
         <v>14</v>
       </c>
       <c r="E156" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="F156" t="s">
         <v>565</v>
@@ -8748,16 +8748,16 @@
         <v>566</v>
       </c>
       <c r="H156" t="s">
+        <v>619</v>
+      </c>
+      <c r="I156" t="s">
+        <v>568</v>
+      </c>
+      <c r="J156" t="s">
+        <v>569</v>
+      </c>
+      <c r="K156" t="s">
         <v>339</v>
-      </c>
-      <c r="I156" t="s">
-        <v>618</v>
-      </c>
-      <c r="J156" t="s">
-        <v>619</v>
-      </c>
-      <c r="K156" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -8774,25 +8774,25 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="F157" t="s">
-        <v>565</v>
+        <v>623</v>
       </c>
       <c r="G157" t="s">
-        <v>623</v>
+        <v>566</v>
       </c>
       <c r="H157" t="s">
+        <v>619</v>
+      </c>
+      <c r="I157" t="s">
+        <v>568</v>
+      </c>
+      <c r="J157" t="s">
+        <v>569</v>
+      </c>
+      <c r="K157" t="s">
         <v>339</v>
-      </c>
-      <c r="I157" t="s">
-        <v>618</v>
-      </c>
-      <c r="J157" t="s">
-        <v>619</v>
-      </c>
-      <c r="K157" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -8809,7 +8809,7 @@
         <v>14</v>
       </c>
       <c r="E158" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="F158" t="s">
         <v>565</v>
@@ -8818,16 +8818,16 @@
         <v>566</v>
       </c>
       <c r="H158" t="s">
+        <v>619</v>
+      </c>
+      <c r="I158" t="s">
+        <v>568</v>
+      </c>
+      <c r="J158" t="s">
+        <v>569</v>
+      </c>
+      <c r="K158" t="s">
         <v>339</v>
-      </c>
-      <c r="I158" t="s">
-        <v>618</v>
-      </c>
-      <c r="J158" t="s">
-        <v>619</v>
-      </c>
-      <c r="K158" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -8844,7 +8844,7 @@
         <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="F159" t="s">
         <v>565</v>
@@ -8853,16 +8853,16 @@
         <v>566</v>
       </c>
       <c r="H159" t="s">
+        <v>619</v>
+      </c>
+      <c r="I159" t="s">
+        <v>568</v>
+      </c>
+      <c r="J159" t="s">
+        <v>569</v>
+      </c>
+      <c r="K159" t="s">
         <v>339</v>
-      </c>
-      <c r="I159" t="s">
-        <v>618</v>
-      </c>
-      <c r="J159" t="s">
-        <v>619</v>
-      </c>
-      <c r="K159" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -8879,7 +8879,7 @@
         <v>14</v>
       </c>
       <c r="E160" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="F160" t="s">
         <v>565</v>
@@ -8888,16 +8888,16 @@
         <v>566</v>
       </c>
       <c r="H160" t="s">
+        <v>619</v>
+      </c>
+      <c r="I160" t="s">
+        <v>568</v>
+      </c>
+      <c r="J160" t="s">
+        <v>569</v>
+      </c>
+      <c r="K160" t="s">
         <v>339</v>
-      </c>
-      <c r="I160" t="s">
-        <v>618</v>
-      </c>
-      <c r="J160" t="s">
-        <v>619</v>
-      </c>
-      <c r="K160" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -8914,7 +8914,7 @@
         <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="F161" t="s">
         <v>565</v>
@@ -8923,16 +8923,16 @@
         <v>566</v>
       </c>
       <c r="H161" t="s">
+        <v>619</v>
+      </c>
+      <c r="I161" t="s">
+        <v>568</v>
+      </c>
+      <c r="J161" t="s">
+        <v>569</v>
+      </c>
+      <c r="K161" t="s">
         <v>339</v>
-      </c>
-      <c r="I161" t="s">
-        <v>618</v>
-      </c>
-      <c r="J161" t="s">
-        <v>619</v>
-      </c>
-      <c r="K161" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -8949,7 +8949,7 @@
         <v>14</v>
       </c>
       <c r="E162" t="s">
-        <v>564</v>
+        <v>639</v>
       </c>
       <c r="F162" t="s">
         <v>565</v>
@@ -8958,16 +8958,16 @@
         <v>566</v>
       </c>
       <c r="H162" t="s">
+        <v>640</v>
+      </c>
+      <c r="I162" t="s">
+        <v>568</v>
+      </c>
+      <c r="J162" t="s">
+        <v>569</v>
+      </c>
+      <c r="K162" t="s">
         <v>339</v>
-      </c>
-      <c r="I162" t="s">
-        <v>639</v>
-      </c>
-      <c r="J162" t="s">
-        <v>640</v>
-      </c>
-      <c r="K162" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -8984,25 +8984,25 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
       <c r="F163" t="s">
-        <v>565</v>
+        <v>644</v>
       </c>
       <c r="G163" t="s">
-        <v>644</v>
+        <v>566</v>
       </c>
       <c r="H163" t="s">
+        <v>645</v>
+      </c>
+      <c r="I163" t="s">
+        <v>568</v>
+      </c>
+      <c r="J163" t="s">
+        <v>569</v>
+      </c>
+      <c r="K163" t="s">
         <v>339</v>
-      </c>
-      <c r="I163" t="s">
-        <v>642</v>
-      </c>
-      <c r="J163" t="s">
-        <v>645</v>
-      </c>
-      <c r="K163" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -9019,7 +9019,7 @@
         <v>14</v>
       </c>
       <c r="E164" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="F164" t="s">
         <v>565</v>
@@ -9028,16 +9028,16 @@
         <v>566</v>
       </c>
       <c r="H164" t="s">
+        <v>650</v>
+      </c>
+      <c r="I164" t="s">
+        <v>568</v>
+      </c>
+      <c r="J164" t="s">
+        <v>569</v>
+      </c>
+      <c r="K164" t="s">
         <v>339</v>
-      </c>
-      <c r="I164" t="s">
-        <v>649</v>
-      </c>
-      <c r="J164" t="s">
-        <v>650</v>
-      </c>
-      <c r="K164" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -9054,7 +9054,7 @@
         <v>14</v>
       </c>
       <c r="E165" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="F165" t="s">
         <v>565</v>
@@ -9063,16 +9063,16 @@
         <v>566</v>
       </c>
       <c r="H165" t="s">
+        <v>650</v>
+      </c>
+      <c r="I165" t="s">
+        <v>568</v>
+      </c>
+      <c r="J165" t="s">
+        <v>569</v>
+      </c>
+      <c r="K165" t="s">
         <v>339</v>
-      </c>
-      <c r="I165" t="s">
-        <v>649</v>
-      </c>
-      <c r="J165" t="s">
-        <v>650</v>
-      </c>
-      <c r="K165" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -9089,7 +9089,7 @@
         <v>14</v>
       </c>
       <c r="E166" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="F166" t="s">
         <v>565</v>
@@ -9098,16 +9098,16 @@
         <v>566</v>
       </c>
       <c r="H166" t="s">
+        <v>650</v>
+      </c>
+      <c r="I166" t="s">
+        <v>568</v>
+      </c>
+      <c r="J166" t="s">
+        <v>569</v>
+      </c>
+      <c r="K166" t="s">
         <v>339</v>
-      </c>
-      <c r="I166" t="s">
-        <v>649</v>
-      </c>
-      <c r="J166" t="s">
-        <v>650</v>
-      </c>
-      <c r="K166" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -9124,7 +9124,7 @@
         <v>14</v>
       </c>
       <c r="E167" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="F167" t="s">
         <v>565</v>
@@ -9133,16 +9133,16 @@
         <v>566</v>
       </c>
       <c r="H167" t="s">
+        <v>650</v>
+      </c>
+      <c r="I167" t="s">
+        <v>568</v>
+      </c>
+      <c r="J167" t="s">
+        <v>569</v>
+      </c>
+      <c r="K167" t="s">
         <v>339</v>
-      </c>
-      <c r="I167" t="s">
-        <v>649</v>
-      </c>
-      <c r="J167" t="s">
-        <v>650</v>
-      </c>
-      <c r="K167" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -9159,25 +9159,25 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="F168" t="s">
-        <v>565</v>
+        <v>663</v>
       </c>
       <c r="G168" t="s">
-        <v>663</v>
+        <v>566</v>
       </c>
       <c r="H168" t="s">
+        <v>650</v>
+      </c>
+      <c r="I168" t="s">
+        <v>568</v>
+      </c>
+      <c r="J168" t="s">
+        <v>569</v>
+      </c>
+      <c r="K168" t="s">
         <v>339</v>
-      </c>
-      <c r="I168" t="s">
-        <v>649</v>
-      </c>
-      <c r="J168" t="s">
-        <v>650</v>
-      </c>
-      <c r="K168" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -9191,25 +9191,25 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="F169" t="s">
-        <v>565</v>
+        <v>663</v>
       </c>
       <c r="G169" t="s">
-        <v>663</v>
+        <v>566</v>
       </c>
       <c r="H169" t="s">
+        <v>650</v>
+      </c>
+      <c r="I169" t="s">
+        <v>568</v>
+      </c>
+      <c r="J169" t="s">
+        <v>569</v>
+      </c>
+      <c r="K169" t="s">
         <v>339</v>
-      </c>
-      <c r="I169" t="s">
-        <v>649</v>
-      </c>
-      <c r="J169" t="s">
-        <v>650</v>
-      </c>
-      <c r="K169" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -9226,7 +9226,7 @@
         <v>14</v>
       </c>
       <c r="E170" t="s">
-        <v>564</v>
+        <v>649</v>
       </c>
       <c r="F170" t="s">
         <v>565</v>
@@ -9235,16 +9235,16 @@
         <v>566</v>
       </c>
       <c r="H170" t="s">
+        <v>650</v>
+      </c>
+      <c r="I170" t="s">
+        <v>568</v>
+      </c>
+      <c r="J170" t="s">
+        <v>569</v>
+      </c>
+      <c r="K170" t="s">
         <v>339</v>
-      </c>
-      <c r="I170" t="s">
-        <v>649</v>
-      </c>
-      <c r="J170" t="s">
-        <v>650</v>
-      </c>
-      <c r="K170" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -9260,20 +9260,20 @@
       <c r="D171" t="s">
         <v>14</v>
       </c>
-      <c r="E171" t="s">
-        <v>672</v>
-      </c>
       <c r="F171" t="s">
         <v>337</v>
       </c>
       <c r="G171" t="s">
+        <v>672</v>
+      </c>
+      <c r="I171" t="s">
         <v>338</v>
       </c>
-      <c r="H171" t="s">
+      <c r="J171" t="s">
+        <v>673</v>
+      </c>
+      <c r="K171" t="s">
         <v>339</v>
-      </c>
-      <c r="K171" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -9289,20 +9289,20 @@
       <c r="D172" t="s">
         <v>14</v>
       </c>
-      <c r="E172" t="s">
-        <v>672</v>
-      </c>
       <c r="F172" t="s">
         <v>243</v>
       </c>
       <c r="G172" t="s">
+        <v>672</v>
+      </c>
+      <c r="I172" t="s">
         <v>244</v>
       </c>
-      <c r="H172" t="s">
-        <v>236</v>
+      <c r="J172" t="s">
+        <v>673</v>
       </c>
       <c r="K172" t="s">
-        <v>673</v>
+        <v>239</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -9318,20 +9318,20 @@
       <c r="D173" t="s">
         <v>14</v>
       </c>
-      <c r="E173" t="s">
-        <v>672</v>
-      </c>
       <c r="F173" t="s">
         <v>337</v>
       </c>
       <c r="G173" t="s">
+        <v>672</v>
+      </c>
+      <c r="I173" t="s">
         <v>338</v>
       </c>
-      <c r="H173" t="s">
+      <c r="J173" t="s">
+        <v>673</v>
+      </c>
+      <c r="K173" t="s">
         <v>339</v>
-      </c>
-      <c r="K173" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -9347,20 +9347,20 @@
       <c r="D174" t="s">
         <v>14</v>
       </c>
-      <c r="E174" t="s">
-        <v>672</v>
-      </c>
       <c r="F174" t="s">
         <v>337</v>
       </c>
       <c r="G174" t="s">
+        <v>672</v>
+      </c>
+      <c r="I174" t="s">
         <v>338</v>
       </c>
-      <c r="H174" t="s">
+      <c r="J174" t="s">
+        <v>673</v>
+      </c>
+      <c r="K174" t="s">
         <v>339</v>
-      </c>
-      <c r="K174" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -9376,20 +9376,20 @@
       <c r="D175" t="s">
         <v>14</v>
       </c>
-      <c r="E175" t="s">
-        <v>672</v>
-      </c>
       <c r="F175" t="s">
         <v>337</v>
       </c>
       <c r="G175" t="s">
+        <v>672</v>
+      </c>
+      <c r="I175" t="s">
         <v>338</v>
       </c>
-      <c r="H175" t="s">
+      <c r="J175" t="s">
+        <v>673</v>
+      </c>
+      <c r="K175" t="s">
         <v>339</v>
-      </c>
-      <c r="K175" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -9402,20 +9402,20 @@
       <c r="D176" t="s">
         <v>14</v>
       </c>
-      <c r="E176" t="s">
-        <v>672</v>
-      </c>
       <c r="F176" t="s">
         <v>337</v>
       </c>
       <c r="G176" t="s">
+        <v>672</v>
+      </c>
+      <c r="I176" t="s">
         <v>338</v>
       </c>
-      <c r="H176" t="s">
+      <c r="J176" t="s">
+        <v>673</v>
+      </c>
+      <c r="K176" t="s">
         <v>339</v>
-      </c>
-      <c r="K176" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -9431,20 +9431,20 @@
       <c r="D177" t="s">
         <v>14</v>
       </c>
-      <c r="E177" t="s">
-        <v>691</v>
-      </c>
       <c r="F177" t="s">
         <v>337</v>
       </c>
       <c r="G177" t="s">
+        <v>691</v>
+      </c>
+      <c r="I177" t="s">
         <v>338</v>
       </c>
-      <c r="H177" t="s">
+      <c r="J177" t="s">
+        <v>692</v>
+      </c>
+      <c r="K177" t="s">
         <v>339</v>
-      </c>
-      <c r="K177" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -9460,20 +9460,20 @@
       <c r="D178" t="s">
         <v>14</v>
       </c>
-      <c r="E178" t="s">
-        <v>691</v>
-      </c>
       <c r="F178" t="s">
         <v>337</v>
       </c>
       <c r="G178" t="s">
+        <v>691</v>
+      </c>
+      <c r="I178" t="s">
         <v>338</v>
       </c>
-      <c r="H178" t="s">
+      <c r="J178" t="s">
+        <v>692</v>
+      </c>
+      <c r="K178" t="s">
         <v>339</v>
-      </c>
-      <c r="K178" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -9489,20 +9489,20 @@
       <c r="D179" t="s">
         <v>14</v>
       </c>
-      <c r="E179" t="s">
-        <v>691</v>
-      </c>
       <c r="F179" t="s">
         <v>337</v>
       </c>
       <c r="G179" t="s">
+        <v>691</v>
+      </c>
+      <c r="I179" t="s">
         <v>338</v>
       </c>
-      <c r="H179" t="s">
+      <c r="J179" t="s">
+        <v>692</v>
+      </c>
+      <c r="K179" t="s">
         <v>339</v>
-      </c>
-      <c r="K179" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -9518,20 +9518,20 @@
       <c r="D180" t="s">
         <v>14</v>
       </c>
-      <c r="E180" t="s">
-        <v>691</v>
-      </c>
       <c r="F180" t="s">
         <v>337</v>
       </c>
       <c r="G180" t="s">
+        <v>691</v>
+      </c>
+      <c r="I180" t="s">
         <v>338</v>
       </c>
-      <c r="H180" t="s">
+      <c r="J180" t="s">
+        <v>692</v>
+      </c>
+      <c r="K180" t="s">
         <v>339</v>
-      </c>
-      <c r="K180" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -9557,16 +9557,16 @@
         <v>707</v>
       </c>
       <c r="H181" t="s">
+        <v>708</v>
+      </c>
+      <c r="I181" t="s">
+        <v>709</v>
+      </c>
+      <c r="J181" t="s">
+        <v>710</v>
+      </c>
+      <c r="K181" t="s">
         <v>339</v>
-      </c>
-      <c r="I181" t="s">
-        <v>708</v>
-      </c>
-      <c r="J181" t="s">
-        <v>709</v>
-      </c>
-      <c r="K181" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -9592,16 +9592,16 @@
         <v>707</v>
       </c>
       <c r="H182" t="s">
+        <v>708</v>
+      </c>
+      <c r="I182" t="s">
+        <v>709</v>
+      </c>
+      <c r="J182" t="s">
+        <v>710</v>
+      </c>
+      <c r="K182" t="s">
         <v>339</v>
-      </c>
-      <c r="I182" t="s">
-        <v>708</v>
-      </c>
-      <c r="J182" t="s">
-        <v>709</v>
-      </c>
-      <c r="K182" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -9627,16 +9627,16 @@
         <v>707</v>
       </c>
       <c r="H183" t="s">
+        <v>708</v>
+      </c>
+      <c r="I183" t="s">
+        <v>709</v>
+      </c>
+      <c r="J183" t="s">
+        <v>710</v>
+      </c>
+      <c r="K183" t="s">
         <v>339</v>
-      </c>
-      <c r="I183" t="s">
-        <v>708</v>
-      </c>
-      <c r="J183" t="s">
-        <v>709</v>
-      </c>
-      <c r="K183" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -9662,16 +9662,16 @@
         <v>707</v>
       </c>
       <c r="H184" t="s">
+        <v>708</v>
+      </c>
+      <c r="I184" t="s">
+        <v>709</v>
+      </c>
+      <c r="J184" t="s">
+        <v>710</v>
+      </c>
+      <c r="K184" t="s">
         <v>339</v>
-      </c>
-      <c r="I184" t="s">
-        <v>708</v>
-      </c>
-      <c r="J184" t="s">
-        <v>709</v>
-      </c>
-      <c r="K184" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -9697,16 +9697,16 @@
         <v>707</v>
       </c>
       <c r="H185" t="s">
+        <v>708</v>
+      </c>
+      <c r="I185" t="s">
+        <v>709</v>
+      </c>
+      <c r="J185" t="s">
+        <v>710</v>
+      </c>
+      <c r="K185" t="s">
         <v>339</v>
-      </c>
-      <c r="I185" t="s">
-        <v>708</v>
-      </c>
-      <c r="J185" t="s">
-        <v>709</v>
-      </c>
-      <c r="K185" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -9732,16 +9732,16 @@
         <v>707</v>
       </c>
       <c r="H186" t="s">
+        <v>708</v>
+      </c>
+      <c r="I186" t="s">
+        <v>709</v>
+      </c>
+      <c r="J186" t="s">
+        <v>710</v>
+      </c>
+      <c r="K186" t="s">
         <v>339</v>
-      </c>
-      <c r="I186" t="s">
-        <v>708</v>
-      </c>
-      <c r="J186" t="s">
-        <v>709</v>
-      </c>
-      <c r="K186" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -9767,16 +9767,16 @@
         <v>707</v>
       </c>
       <c r="H187" t="s">
+        <v>708</v>
+      </c>
+      <c r="I187" t="s">
+        <v>709</v>
+      </c>
+      <c r="J187" t="s">
+        <v>710</v>
+      </c>
+      <c r="K187" t="s">
         <v>339</v>
-      </c>
-      <c r="I187" t="s">
-        <v>708</v>
-      </c>
-      <c r="J187" t="s">
-        <v>709</v>
-      </c>
-      <c r="K187" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -9802,16 +9802,16 @@
         <v>707</v>
       </c>
       <c r="H188" t="s">
+        <v>708</v>
+      </c>
+      <c r="I188" t="s">
+        <v>709</v>
+      </c>
+      <c r="J188" t="s">
+        <v>710</v>
+      </c>
+      <c r="K188" t="s">
         <v>339</v>
-      </c>
-      <c r="I188" t="s">
-        <v>708</v>
-      </c>
-      <c r="J188" t="s">
-        <v>709</v>
-      </c>
-      <c r="K188" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -9837,16 +9837,16 @@
         <v>707</v>
       </c>
       <c r="H189" t="s">
+        <v>708</v>
+      </c>
+      <c r="I189" t="s">
+        <v>709</v>
+      </c>
+      <c r="J189" t="s">
+        <v>710</v>
+      </c>
+      <c r="K189" t="s">
         <v>339</v>
-      </c>
-      <c r="I189" t="s">
-        <v>708</v>
-      </c>
-      <c r="J189" t="s">
-        <v>709</v>
-      </c>
-      <c r="K189" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -9872,16 +9872,16 @@
         <v>707</v>
       </c>
       <c r="H190" t="s">
+        <v>708</v>
+      </c>
+      <c r="I190" t="s">
+        <v>709</v>
+      </c>
+      <c r="J190" t="s">
+        <v>710</v>
+      </c>
+      <c r="K190" t="s">
         <v>339</v>
-      </c>
-      <c r="I190" t="s">
-        <v>708</v>
-      </c>
-      <c r="J190" t="s">
-        <v>709</v>
-      </c>
-      <c r="K190" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -9907,16 +9907,16 @@
         <v>707</v>
       </c>
       <c r="H191" t="s">
+        <v>708</v>
+      </c>
+      <c r="I191" t="s">
+        <v>709</v>
+      </c>
+      <c r="J191" t="s">
+        <v>710</v>
+      </c>
+      <c r="K191" t="s">
         <v>339</v>
-      </c>
-      <c r="I191" t="s">
-        <v>708</v>
-      </c>
-      <c r="J191" t="s">
-        <v>709</v>
-      </c>
-      <c r="K191" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -9939,16 +9939,16 @@
         <v>707</v>
       </c>
       <c r="H192" t="s">
+        <v>708</v>
+      </c>
+      <c r="I192" t="s">
+        <v>709</v>
+      </c>
+      <c r="J192" t="s">
+        <v>710</v>
+      </c>
+      <c r="K192" t="s">
         <v>339</v>
-      </c>
-      <c r="I192" t="s">
-        <v>708</v>
-      </c>
-      <c r="J192" t="s">
-        <v>709</v>
-      </c>
-      <c r="K192" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -9968,22 +9968,22 @@
         <v>705</v>
       </c>
       <c r="F193" t="s">
-        <v>575</v>
+        <v>746</v>
       </c>
       <c r="G193" t="s">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="H193" t="s">
+        <v>708</v>
+      </c>
+      <c r="I193" t="s">
+        <v>576</v>
+      </c>
+      <c r="J193" t="s">
+        <v>710</v>
+      </c>
+      <c r="K193" t="s">
         <v>339</v>
-      </c>
-      <c r="I193" t="s">
-        <v>708</v>
-      </c>
-      <c r="J193" t="s">
-        <v>709</v>
-      </c>
-      <c r="K193" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -10009,16 +10009,16 @@
         <v>707</v>
       </c>
       <c r="H194" t="s">
+        <v>708</v>
+      </c>
+      <c r="I194" t="s">
+        <v>709</v>
+      </c>
+      <c r="J194" t="s">
+        <v>710</v>
+      </c>
+      <c r="K194" t="s">
         <v>339</v>
-      </c>
-      <c r="I194" t="s">
-        <v>708</v>
-      </c>
-      <c r="J194" t="s">
-        <v>709</v>
-      </c>
-      <c r="K194" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -10044,16 +10044,16 @@
         <v>707</v>
       </c>
       <c r="H195" t="s">
+        <v>708</v>
+      </c>
+      <c r="I195" t="s">
+        <v>709</v>
+      </c>
+      <c r="J195" t="s">
+        <v>710</v>
+      </c>
+      <c r="K195" t="s">
         <v>339</v>
-      </c>
-      <c r="I195" t="s">
-        <v>708</v>
-      </c>
-      <c r="J195" t="s">
-        <v>709</v>
-      </c>
-      <c r="K195" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -10079,16 +10079,16 @@
         <v>707</v>
       </c>
       <c r="H196" t="s">
+        <v>708</v>
+      </c>
+      <c r="I196" t="s">
+        <v>709</v>
+      </c>
+      <c r="J196" t="s">
+        <v>710</v>
+      </c>
+      <c r="K196" t="s">
         <v>339</v>
-      </c>
-      <c r="I196" t="s">
-        <v>708</v>
-      </c>
-      <c r="J196" t="s">
-        <v>709</v>
-      </c>
-      <c r="K196" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -10114,16 +10114,16 @@
         <v>707</v>
       </c>
       <c r="H197" t="s">
+        <v>708</v>
+      </c>
+      <c r="I197" t="s">
+        <v>709</v>
+      </c>
+      <c r="J197" t="s">
+        <v>710</v>
+      </c>
+      <c r="K197" t="s">
         <v>339</v>
-      </c>
-      <c r="I197" t="s">
-        <v>708</v>
-      </c>
-      <c r="J197" t="s">
-        <v>709</v>
-      </c>
-      <c r="K197" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -10149,16 +10149,16 @@
         <v>707</v>
       </c>
       <c r="H198" t="s">
+        <v>708</v>
+      </c>
+      <c r="I198" t="s">
+        <v>709</v>
+      </c>
+      <c r="J198" t="s">
+        <v>710</v>
+      </c>
+      <c r="K198" t="s">
         <v>339</v>
-      </c>
-      <c r="I198" t="s">
-        <v>708</v>
-      </c>
-      <c r="J198" t="s">
-        <v>709</v>
-      </c>
-      <c r="K198" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -10175,25 +10175,25 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F199" t="s">
-        <v>706</v>
+        <v>766</v>
       </c>
       <c r="G199" t="s">
-        <v>765</v>
+        <v>707</v>
       </c>
       <c r="H199" t="s">
+        <v>767</v>
+      </c>
+      <c r="I199" t="s">
+        <v>709</v>
+      </c>
+      <c r="J199" t="s">
+        <v>710</v>
+      </c>
+      <c r="K199" t="s">
         <v>339</v>
-      </c>
-      <c r="I199" t="s">
-        <v>766</v>
-      </c>
-      <c r="J199" t="s">
-        <v>767</v>
-      </c>
-      <c r="K199" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -10210,25 +10210,25 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F200" t="s">
-        <v>706</v>
+        <v>766</v>
       </c>
       <c r="G200" t="s">
-        <v>765</v>
+        <v>707</v>
       </c>
       <c r="H200" t="s">
+        <v>767</v>
+      </c>
+      <c r="I200" t="s">
+        <v>709</v>
+      </c>
+      <c r="J200" t="s">
+        <v>710</v>
+      </c>
+      <c r="K200" t="s">
         <v>339</v>
-      </c>
-      <c r="I200" t="s">
-        <v>766</v>
-      </c>
-      <c r="J200" t="s">
-        <v>767</v>
-      </c>
-      <c r="K200" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -10245,25 +10245,25 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F201" t="s">
-        <v>706</v>
+        <v>766</v>
       </c>
       <c r="G201" t="s">
-        <v>765</v>
+        <v>707</v>
       </c>
       <c r="H201" t="s">
+        <v>767</v>
+      </c>
+      <c r="I201" t="s">
+        <v>709</v>
+      </c>
+      <c r="J201" t="s">
+        <v>710</v>
+      </c>
+      <c r="K201" t="s">
         <v>339</v>
-      </c>
-      <c r="I201" t="s">
-        <v>766</v>
-      </c>
-      <c r="J201" t="s">
-        <v>767</v>
-      </c>
-      <c r="K201" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -10277,25 +10277,25 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F202" t="s">
-        <v>706</v>
+        <v>766</v>
       </c>
       <c r="G202" t="s">
-        <v>765</v>
+        <v>707</v>
       </c>
       <c r="H202" t="s">
+        <v>767</v>
+      </c>
+      <c r="I202" t="s">
+        <v>709</v>
+      </c>
+      <c r="J202" t="s">
+        <v>710</v>
+      </c>
+      <c r="K202" t="s">
         <v>339</v>
-      </c>
-      <c r="I202" t="s">
-        <v>766</v>
-      </c>
-      <c r="J202" t="s">
-        <v>767</v>
-      </c>
-      <c r="K202" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -10312,25 +10312,25 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F203" t="s">
-        <v>575</v>
+        <v>746</v>
       </c>
       <c r="G203" t="s">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="H203" t="s">
+        <v>767</v>
+      </c>
+      <c r="I203" t="s">
+        <v>576</v>
+      </c>
+      <c r="J203" t="s">
+        <v>710</v>
+      </c>
+      <c r="K203" t="s">
         <v>339</v>
-      </c>
-      <c r="I203" t="s">
-        <v>766</v>
-      </c>
-      <c r="J203" t="s">
-        <v>767</v>
-      </c>
-      <c r="K203" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10344,25 +10344,25 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F204" t="s">
-        <v>706</v>
+        <v>766</v>
       </c>
       <c r="G204" t="s">
-        <v>765</v>
+        <v>707</v>
       </c>
       <c r="H204" t="s">
+        <v>767</v>
+      </c>
+      <c r="I204" t="s">
+        <v>709</v>
+      </c>
+      <c r="J204" t="s">
+        <v>710</v>
+      </c>
+      <c r="K204" t="s">
         <v>339</v>
-      </c>
-      <c r="I204" t="s">
-        <v>766</v>
-      </c>
-      <c r="J204" t="s">
-        <v>767</v>
-      </c>
-      <c r="K204" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -10379,25 +10379,25 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F205" t="s">
-        <v>706</v>
+        <v>785</v>
       </c>
       <c r="G205" t="s">
-        <v>784</v>
+        <v>707</v>
       </c>
       <c r="H205" t="s">
+        <v>786</v>
+      </c>
+      <c r="I205" t="s">
+        <v>709</v>
+      </c>
+      <c r="J205" t="s">
+        <v>710</v>
+      </c>
+      <c r="K205" t="s">
         <v>339</v>
-      </c>
-      <c r="I205" t="s">
-        <v>785</v>
-      </c>
-      <c r="J205" t="s">
-        <v>786</v>
-      </c>
-      <c r="K205" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -10414,25 +10414,25 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F206" t="s">
-        <v>706</v>
+        <v>785</v>
       </c>
       <c r="G206" t="s">
-        <v>784</v>
+        <v>707</v>
       </c>
       <c r="H206" t="s">
+        <v>786</v>
+      </c>
+      <c r="I206" t="s">
+        <v>709</v>
+      </c>
+      <c r="J206" t="s">
+        <v>710</v>
+      </c>
+      <c r="K206" t="s">
         <v>339</v>
-      </c>
-      <c r="I206" t="s">
-        <v>785</v>
-      </c>
-      <c r="J206" t="s">
-        <v>786</v>
-      </c>
-      <c r="K206" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -10446,25 +10446,25 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F207" t="s">
-        <v>706</v>
+        <v>785</v>
       </c>
       <c r="G207" t="s">
-        <v>784</v>
+        <v>707</v>
       </c>
       <c r="H207" t="s">
+        <v>786</v>
+      </c>
+      <c r="I207" t="s">
+        <v>709</v>
+      </c>
+      <c r="J207" t="s">
+        <v>710</v>
+      </c>
+      <c r="K207" t="s">
         <v>339</v>
-      </c>
-      <c r="I207" t="s">
-        <v>785</v>
-      </c>
-      <c r="J207" t="s">
-        <v>786</v>
-      </c>
-      <c r="K207" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -10481,25 +10481,25 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F208" t="s">
-        <v>575</v>
+        <v>746</v>
       </c>
       <c r="G208" t="s">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="H208" t="s">
+        <v>786</v>
+      </c>
+      <c r="I208" t="s">
+        <v>576</v>
+      </c>
+      <c r="J208" t="s">
+        <v>710</v>
+      </c>
+      <c r="K208" t="s">
         <v>339</v>
-      </c>
-      <c r="I208" t="s">
-        <v>785</v>
-      </c>
-      <c r="J208" t="s">
-        <v>786</v>
-      </c>
-      <c r="K208" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10516,25 +10516,25 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F209" t="s">
-        <v>706</v>
+        <v>785</v>
       </c>
       <c r="G209" t="s">
-        <v>784</v>
+        <v>707</v>
       </c>
       <c r="H209" t="s">
+        <v>786</v>
+      </c>
+      <c r="I209" t="s">
+        <v>709</v>
+      </c>
+      <c r="J209" t="s">
+        <v>710</v>
+      </c>
+      <c r="K209" t="s">
         <v>339</v>
-      </c>
-      <c r="I209" t="s">
-        <v>785</v>
-      </c>
-      <c r="J209" t="s">
-        <v>786</v>
-      </c>
-      <c r="K209" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -10560,16 +10560,16 @@
         <v>803</v>
       </c>
       <c r="H210" t="s">
+        <v>804</v>
+      </c>
+      <c r="I210" t="s">
+        <v>805</v>
+      </c>
+      <c r="J210" t="s">
+        <v>806</v>
+      </c>
+      <c r="K210" t="s">
         <v>339</v>
-      </c>
-      <c r="I210" t="s">
-        <v>804</v>
-      </c>
-      <c r="J210" t="s">
-        <v>805</v>
-      </c>
-      <c r="K210" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="211" spans="1:11">
@@ -10592,16 +10592,16 @@
         <v>803</v>
       </c>
       <c r="H211" t="s">
+        <v>804</v>
+      </c>
+      <c r="I211" t="s">
+        <v>805</v>
+      </c>
+      <c r="J211" t="s">
+        <v>806</v>
+      </c>
+      <c r="K211" t="s">
         <v>339</v>
-      </c>
-      <c r="I211" t="s">
-        <v>804</v>
-      </c>
-      <c r="J211" t="s">
-        <v>805</v>
-      </c>
-      <c r="K211" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -10627,16 +10627,16 @@
         <v>803</v>
       </c>
       <c r="H212" t="s">
+        <v>804</v>
+      </c>
+      <c r="I212" t="s">
+        <v>805</v>
+      </c>
+      <c r="J212" t="s">
+        <v>806</v>
+      </c>
+      <c r="K212" t="s">
         <v>339</v>
-      </c>
-      <c r="I212" t="s">
-        <v>804</v>
-      </c>
-      <c r="J212" t="s">
-        <v>805</v>
-      </c>
-      <c r="K212" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="213" spans="1:11">
@@ -10659,16 +10659,16 @@
         <v>803</v>
       </c>
       <c r="H213" t="s">
+        <v>804</v>
+      </c>
+      <c r="I213" t="s">
+        <v>805</v>
+      </c>
+      <c r="J213" t="s">
+        <v>806</v>
+      </c>
+      <c r="K213" t="s">
         <v>339</v>
-      </c>
-      <c r="I213" t="s">
-        <v>804</v>
-      </c>
-      <c r="J213" t="s">
-        <v>805</v>
-      </c>
-      <c r="K213" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -10694,16 +10694,16 @@
         <v>803</v>
       </c>
       <c r="H214" t="s">
+        <v>804</v>
+      </c>
+      <c r="I214" t="s">
+        <v>805</v>
+      </c>
+      <c r="J214" t="s">
+        <v>806</v>
+      </c>
+      <c r="K214" t="s">
         <v>339</v>
-      </c>
-      <c r="I214" t="s">
-        <v>804</v>
-      </c>
-      <c r="J214" t="s">
-        <v>805</v>
-      </c>
-      <c r="K214" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="215" spans="1:11">
@@ -10723,22 +10723,22 @@
         <v>801</v>
       </c>
       <c r="F215" t="s">
-        <v>706</v>
+        <v>766</v>
       </c>
       <c r="G215" t="s">
-        <v>765</v>
+        <v>803</v>
       </c>
       <c r="H215" t="s">
+        <v>804</v>
+      </c>
+      <c r="I215" t="s">
+        <v>709</v>
+      </c>
+      <c r="J215" t="s">
+        <v>806</v>
+      </c>
+      <c r="K215" t="s">
         <v>339</v>
-      </c>
-      <c r="I215" t="s">
-        <v>804</v>
-      </c>
-      <c r="J215" t="s">
-        <v>805</v>
-      </c>
-      <c r="K215" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -10764,16 +10764,16 @@
         <v>803</v>
       </c>
       <c r="H216" t="s">
+        <v>804</v>
+      </c>
+      <c r="I216" t="s">
+        <v>805</v>
+      </c>
+      <c r="J216" t="s">
+        <v>806</v>
+      </c>
+      <c r="K216" t="s">
         <v>339</v>
-      </c>
-      <c r="I216" t="s">
-        <v>804</v>
-      </c>
-      <c r="J216" t="s">
-        <v>805</v>
-      </c>
-      <c r="K216" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -10799,16 +10799,16 @@
         <v>803</v>
       </c>
       <c r="H217" t="s">
+        <v>804</v>
+      </c>
+      <c r="I217" t="s">
+        <v>805</v>
+      </c>
+      <c r="J217" t="s">
+        <v>806</v>
+      </c>
+      <c r="K217" t="s">
         <v>339</v>
-      </c>
-      <c r="I217" t="s">
-        <v>804</v>
-      </c>
-      <c r="J217" t="s">
-        <v>805</v>
-      </c>
-      <c r="K217" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="218" spans="1:11">
@@ -10831,16 +10831,16 @@
         <v>803</v>
       </c>
       <c r="H218" t="s">
+        <v>804</v>
+      </c>
+      <c r="I218" t="s">
+        <v>805</v>
+      </c>
+      <c r="J218" t="s">
+        <v>806</v>
+      </c>
+      <c r="K218" t="s">
         <v>339</v>
-      </c>
-      <c r="I218" t="s">
-        <v>804</v>
-      </c>
-      <c r="J218" t="s">
-        <v>805</v>
-      </c>
-      <c r="K218" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="219" spans="1:11">
@@ -10863,16 +10863,16 @@
         <v>803</v>
       </c>
       <c r="H219" t="s">
+        <v>804</v>
+      </c>
+      <c r="I219" t="s">
+        <v>805</v>
+      </c>
+      <c r="J219" t="s">
+        <v>806</v>
+      </c>
+      <c r="K219" t="s">
         <v>339</v>
-      </c>
-      <c r="I219" t="s">
-        <v>804</v>
-      </c>
-      <c r="J219" t="s">
-        <v>805</v>
-      </c>
-      <c r="K219" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="220" spans="1:11">
@@ -10892,22 +10892,22 @@
         <v>801</v>
       </c>
       <c r="F220" t="s">
-        <v>565</v>
+        <v>663</v>
       </c>
       <c r="G220" t="s">
-        <v>663</v>
+        <v>803</v>
       </c>
       <c r="H220" t="s">
+        <v>804</v>
+      </c>
+      <c r="I220" t="s">
+        <v>568</v>
+      </c>
+      <c r="J220" t="s">
+        <v>806</v>
+      </c>
+      <c r="K220" t="s">
         <v>339</v>
-      </c>
-      <c r="I220" t="s">
-        <v>804</v>
-      </c>
-      <c r="J220" t="s">
-        <v>805</v>
-      </c>
-      <c r="K220" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -10933,16 +10933,16 @@
         <v>803</v>
       </c>
       <c r="H221" t="s">
+        <v>804</v>
+      </c>
+      <c r="I221" t="s">
+        <v>805</v>
+      </c>
+      <c r="J221" t="s">
+        <v>806</v>
+      </c>
+      <c r="K221" t="s">
         <v>339</v>
-      </c>
-      <c r="I221" t="s">
-        <v>804</v>
-      </c>
-      <c r="J221" t="s">
-        <v>805</v>
-      </c>
-      <c r="K221" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -10968,16 +10968,16 @@
         <v>803</v>
       </c>
       <c r="H222" t="s">
+        <v>804</v>
+      </c>
+      <c r="I222" t="s">
+        <v>805</v>
+      </c>
+      <c r="J222" t="s">
+        <v>806</v>
+      </c>
+      <c r="K222" t="s">
         <v>339</v>
-      </c>
-      <c r="I222" t="s">
-        <v>804</v>
-      </c>
-      <c r="J222" t="s">
-        <v>805</v>
-      </c>
-      <c r="K222" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="223" spans="1:11">
@@ -11000,16 +11000,16 @@
         <v>803</v>
       </c>
       <c r="H223" t="s">
+        <v>804</v>
+      </c>
+      <c r="I223" t="s">
+        <v>805</v>
+      </c>
+      <c r="J223" t="s">
+        <v>806</v>
+      </c>
+      <c r="K223" t="s">
         <v>339</v>
-      </c>
-      <c r="I223" t="s">
-        <v>804</v>
-      </c>
-      <c r="J223" t="s">
-        <v>805</v>
-      </c>
-      <c r="K223" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="224" spans="1:11">
@@ -11035,16 +11035,16 @@
         <v>803</v>
       </c>
       <c r="H224" t="s">
+        <v>804</v>
+      </c>
+      <c r="I224" t="s">
+        <v>805</v>
+      </c>
+      <c r="J224" t="s">
+        <v>806</v>
+      </c>
+      <c r="K224" t="s">
         <v>339</v>
-      </c>
-      <c r="I224" t="s">
-        <v>804</v>
-      </c>
-      <c r="J224" t="s">
-        <v>805</v>
-      </c>
-      <c r="K224" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="225" spans="1:11">
@@ -11070,16 +11070,16 @@
         <v>803</v>
       </c>
       <c r="H225" t="s">
+        <v>804</v>
+      </c>
+      <c r="I225" t="s">
+        <v>805</v>
+      </c>
+      <c r="J225" t="s">
+        <v>806</v>
+      </c>
+      <c r="K225" t="s">
         <v>339</v>
-      </c>
-      <c r="I225" t="s">
-        <v>804</v>
-      </c>
-      <c r="J225" t="s">
-        <v>805</v>
-      </c>
-      <c r="K225" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -11102,19 +11102,19 @@
         <v>575</v>
       </c>
       <c r="G226" t="s">
+        <v>803</v>
+      </c>
+      <c r="H226" t="s">
+        <v>804</v>
+      </c>
+      <c r="I226" t="s">
         <v>576</v>
       </c>
-      <c r="H226" t="s">
+      <c r="J226" t="s">
+        <v>806</v>
+      </c>
+      <c r="K226" t="s">
         <v>339</v>
-      </c>
-      <c r="I226" t="s">
-        <v>804</v>
-      </c>
-      <c r="J226" t="s">
-        <v>805</v>
-      </c>
-      <c r="K226" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -11140,16 +11140,16 @@
         <v>803</v>
       </c>
       <c r="H227" t="s">
+        <v>804</v>
+      </c>
+      <c r="I227" t="s">
+        <v>805</v>
+      </c>
+      <c r="J227" t="s">
+        <v>806</v>
+      </c>
+      <c r="K227" t="s">
         <v>339</v>
-      </c>
-      <c r="I227" t="s">
-        <v>804</v>
-      </c>
-      <c r="J227" t="s">
-        <v>805</v>
-      </c>
-      <c r="K227" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="228" spans="1:11">
@@ -11172,19 +11172,19 @@
         <v>337</v>
       </c>
       <c r="G228" t="s">
+        <v>803</v>
+      </c>
+      <c r="H228" t="s">
+        <v>804</v>
+      </c>
+      <c r="I228" t="s">
         <v>338</v>
       </c>
-      <c r="H228" t="s">
+      <c r="J228" t="s">
+        <v>806</v>
+      </c>
+      <c r="K228" t="s">
         <v>339</v>
-      </c>
-      <c r="I228" t="s">
-        <v>804</v>
-      </c>
-      <c r="J228" t="s">
-        <v>805</v>
-      </c>
-      <c r="K228" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -11201,25 +11201,25 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F229" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G229" t="s">
-        <v>859</v>
+        <v>803</v>
       </c>
       <c r="H229" t="s">
+        <v>861</v>
+      </c>
+      <c r="I229" t="s">
+        <v>805</v>
+      </c>
+      <c r="J229" t="s">
+        <v>806</v>
+      </c>
+      <c r="K229" t="s">
         <v>339</v>
-      </c>
-      <c r="I229" t="s">
-        <v>860</v>
-      </c>
-      <c r="J229" t="s">
-        <v>861</v>
-      </c>
-      <c r="K229" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -11236,25 +11236,25 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F230" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G230" t="s">
-        <v>859</v>
+        <v>803</v>
       </c>
       <c r="H230" t="s">
+        <v>861</v>
+      </c>
+      <c r="I230" t="s">
+        <v>805</v>
+      </c>
+      <c r="J230" t="s">
+        <v>806</v>
+      </c>
+      <c r="K230" t="s">
         <v>339</v>
-      </c>
-      <c r="I230" t="s">
-        <v>860</v>
-      </c>
-      <c r="J230" t="s">
-        <v>861</v>
-      </c>
-      <c r="K230" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -11271,25 +11271,25 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F231" t="s">
-        <v>565</v>
+        <v>623</v>
       </c>
       <c r="G231" t="s">
-        <v>623</v>
+        <v>803</v>
       </c>
       <c r="H231" t="s">
+        <v>861</v>
+      </c>
+      <c r="I231" t="s">
+        <v>568</v>
+      </c>
+      <c r="J231" t="s">
+        <v>806</v>
+      </c>
+      <c r="K231" t="s">
         <v>339</v>
-      </c>
-      <c r="I231" t="s">
-        <v>860</v>
-      </c>
-      <c r="J231" t="s">
-        <v>861</v>
-      </c>
-      <c r="K231" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11306,25 +11306,25 @@
         <v>14</v>
       </c>
       <c r="E232" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F232" t="s">
-        <v>565</v>
+        <v>663</v>
       </c>
       <c r="G232" t="s">
-        <v>663</v>
+        <v>803</v>
       </c>
       <c r="H232" t="s">
+        <v>861</v>
+      </c>
+      <c r="I232" t="s">
+        <v>568</v>
+      </c>
+      <c r="J232" t="s">
+        <v>806</v>
+      </c>
+      <c r="K232" t="s">
         <v>339</v>
-      </c>
-      <c r="I232" t="s">
-        <v>860</v>
-      </c>
-      <c r="J232" t="s">
-        <v>861</v>
-      </c>
-      <c r="K232" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11341,25 +11341,25 @@
         <v>14</v>
       </c>
       <c r="E233" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F233" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G233" t="s">
-        <v>859</v>
+        <v>803</v>
       </c>
       <c r="H233" t="s">
+        <v>861</v>
+      </c>
+      <c r="I233" t="s">
+        <v>805</v>
+      </c>
+      <c r="J233" t="s">
+        <v>806</v>
+      </c>
+      <c r="K233" t="s">
         <v>339</v>
-      </c>
-      <c r="I233" t="s">
-        <v>860</v>
-      </c>
-      <c r="J233" t="s">
-        <v>861</v>
-      </c>
-      <c r="K233" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -11376,25 +11376,25 @@
         <v>14</v>
       </c>
       <c r="E234" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F234" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G234" t="s">
-        <v>859</v>
+        <v>803</v>
       </c>
       <c r="H234" t="s">
+        <v>861</v>
+      </c>
+      <c r="I234" t="s">
+        <v>805</v>
+      </c>
+      <c r="J234" t="s">
+        <v>806</v>
+      </c>
+      <c r="K234" t="s">
         <v>339</v>
-      </c>
-      <c r="I234" t="s">
-        <v>860</v>
-      </c>
-      <c r="J234" t="s">
-        <v>861</v>
-      </c>
-      <c r="K234" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -11411,25 +11411,25 @@
         <v>14</v>
       </c>
       <c r="E235" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F235" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G235" t="s">
-        <v>859</v>
+        <v>803</v>
       </c>
       <c r="H235" t="s">
+        <v>861</v>
+      </c>
+      <c r="I235" t="s">
+        <v>805</v>
+      </c>
+      <c r="J235" t="s">
+        <v>806</v>
+      </c>
+      <c r="K235" t="s">
         <v>339</v>
-      </c>
-      <c r="I235" t="s">
-        <v>860</v>
-      </c>
-      <c r="J235" t="s">
-        <v>861</v>
-      </c>
-      <c r="K235" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -11446,25 +11446,25 @@
         <v>14</v>
       </c>
       <c r="E236" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F236" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G236" t="s">
-        <v>859</v>
+        <v>803</v>
       </c>
       <c r="H236" t="s">
+        <v>861</v>
+      </c>
+      <c r="I236" t="s">
+        <v>805</v>
+      </c>
+      <c r="J236" t="s">
+        <v>806</v>
+      </c>
+      <c r="K236" t="s">
         <v>339</v>
-      </c>
-      <c r="I236" t="s">
-        <v>860</v>
-      </c>
-      <c r="J236" t="s">
-        <v>861</v>
-      </c>
-      <c r="K236" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -11481,25 +11481,25 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F237" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G237" t="s">
-        <v>859</v>
+        <v>803</v>
       </c>
       <c r="H237" t="s">
+        <v>861</v>
+      </c>
+      <c r="I237" t="s">
+        <v>805</v>
+      </c>
+      <c r="J237" t="s">
+        <v>806</v>
+      </c>
+      <c r="K237" t="s">
         <v>339</v>
-      </c>
-      <c r="I237" t="s">
-        <v>860</v>
-      </c>
-      <c r="J237" t="s">
-        <v>861</v>
-      </c>
-      <c r="K237" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -11516,25 +11516,25 @@
         <v>14</v>
       </c>
       <c r="E238" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F238" t="s">
-        <v>802</v>
+        <v>860</v>
       </c>
       <c r="G238" t="s">
-        <v>859</v>
+        <v>803</v>
       </c>
       <c r="H238" t="s">
+        <v>861</v>
+      </c>
+      <c r="I238" t="s">
+        <v>805</v>
+      </c>
+      <c r="J238" t="s">
+        <v>806</v>
+      </c>
+      <c r="K238" t="s">
         <v>339</v>
-      </c>
-      <c r="I238" t="s">
-        <v>860</v>
-      </c>
-      <c r="J238" t="s">
-        <v>861</v>
-      </c>
-      <c r="K238" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -11551,25 +11551,25 @@
         <v>14</v>
       </c>
       <c r="E239" t="s">
-        <v>801</v>
+        <v>892</v>
       </c>
       <c r="F239" t="s">
-        <v>802</v>
+        <v>893</v>
       </c>
       <c r="G239" t="s">
-        <v>892</v>
+        <v>803</v>
       </c>
       <c r="H239" t="s">
+        <v>894</v>
+      </c>
+      <c r="I239" t="s">
+        <v>805</v>
+      </c>
+      <c r="J239" t="s">
+        <v>806</v>
+      </c>
+      <c r="K239" t="s">
         <v>339</v>
-      </c>
-      <c r="I239" t="s">
-        <v>893</v>
-      </c>
-      <c r="J239" t="s">
-        <v>894</v>
-      </c>
-      <c r="K239" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -11592,19 +11592,19 @@
         <v>337</v>
       </c>
       <c r="G240" t="s">
+        <v>898</v>
+      </c>
+      <c r="H240" t="s">
+        <v>899</v>
+      </c>
+      <c r="I240" t="s">
         <v>338</v>
       </c>
-      <c r="H240" t="s">
+      <c r="J240" t="s">
+        <v>900</v>
+      </c>
+      <c r="K240" t="s">
         <v>339</v>
-      </c>
-      <c r="I240" t="s">
-        <v>898</v>
-      </c>
-      <c r="J240" t="s">
-        <v>899</v>
-      </c>
-      <c r="K240" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -11627,19 +11627,19 @@
         <v>337</v>
       </c>
       <c r="G241" t="s">
+        <v>898</v>
+      </c>
+      <c r="H241" t="s">
+        <v>899</v>
+      </c>
+      <c r="I241" t="s">
         <v>338</v>
       </c>
-      <c r="H241" t="s">
+      <c r="J241" t="s">
+        <v>900</v>
+      </c>
+      <c r="K241" t="s">
         <v>339</v>
-      </c>
-      <c r="I241" t="s">
-        <v>898</v>
-      </c>
-      <c r="J241" t="s">
-        <v>899</v>
-      </c>
-      <c r="K241" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -11662,19 +11662,19 @@
         <v>337</v>
       </c>
       <c r="G242" t="s">
+        <v>898</v>
+      </c>
+      <c r="H242" t="s">
+        <v>899</v>
+      </c>
+      <c r="I242" t="s">
         <v>338</v>
       </c>
-      <c r="H242" t="s">
+      <c r="J242" t="s">
+        <v>900</v>
+      </c>
+      <c r="K242" t="s">
         <v>339</v>
-      </c>
-      <c r="I242" t="s">
-        <v>898</v>
-      </c>
-      <c r="J242" t="s">
-        <v>899</v>
-      </c>
-      <c r="K242" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -11697,19 +11697,19 @@
         <v>337</v>
       </c>
       <c r="G243" t="s">
+        <v>898</v>
+      </c>
+      <c r="H243" t="s">
+        <v>899</v>
+      </c>
+      <c r="I243" t="s">
         <v>338</v>
       </c>
-      <c r="H243" t="s">
+      <c r="J243" t="s">
+        <v>900</v>
+      </c>
+      <c r="K243" t="s">
         <v>339</v>
-      </c>
-      <c r="I243" t="s">
-        <v>898</v>
-      </c>
-      <c r="J243" t="s">
-        <v>899</v>
-      </c>
-      <c r="K243" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -11732,19 +11732,19 @@
         <v>337</v>
       </c>
       <c r="G244" t="s">
+        <v>898</v>
+      </c>
+      <c r="H244" t="s">
+        <v>899</v>
+      </c>
+      <c r="I244" t="s">
         <v>338</v>
       </c>
-      <c r="H244" t="s">
+      <c r="J244" t="s">
+        <v>900</v>
+      </c>
+      <c r="K244" t="s">
         <v>339</v>
-      </c>
-      <c r="I244" t="s">
-        <v>898</v>
-      </c>
-      <c r="J244" t="s">
-        <v>899</v>
-      </c>
-      <c r="K244" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -11767,19 +11767,19 @@
         <v>337</v>
       </c>
       <c r="G245" t="s">
+        <v>898</v>
+      </c>
+      <c r="H245" t="s">
+        <v>899</v>
+      </c>
+      <c r="I245" t="s">
         <v>338</v>
       </c>
-      <c r="H245" t="s">
+      <c r="J245" t="s">
+        <v>900</v>
+      </c>
+      <c r="K245" t="s">
         <v>339</v>
-      </c>
-      <c r="I245" t="s">
-        <v>898</v>
-      </c>
-      <c r="J245" t="s">
-        <v>899</v>
-      </c>
-      <c r="K245" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -11793,25 +11793,25 @@
         <v>14</v>
       </c>
       <c r="E246" t="s">
+        <v>918</v>
+      </c>
+      <c r="F246" t="s">
+        <v>919</v>
+      </c>
+      <c r="G246" t="s">
         <v>898</v>
       </c>
-      <c r="F246" t="s">
-        <v>533</v>
-      </c>
-      <c r="G246" t="s">
-        <v>918</v>
-      </c>
       <c r="H246" t="s">
+        <v>920</v>
+      </c>
+      <c r="I246" t="s">
+        <v>534</v>
+      </c>
+      <c r="J246" t="s">
+        <v>900</v>
+      </c>
+      <c r="K246" t="s">
         <v>339</v>
-      </c>
-      <c r="I246" t="s">
-        <v>919</v>
-      </c>
-      <c r="J246" t="s">
-        <v>920</v>
-      </c>
-      <c r="K246" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11827,20 +11827,20 @@
       <c r="D247" t="s">
         <v>14</v>
       </c>
-      <c r="E247" t="s">
-        <v>924</v>
-      </c>
       <c r="F247" t="s">
         <v>196</v>
       </c>
       <c r="G247" t="s">
+        <v>924</v>
+      </c>
+      <c r="I247" t="s">
         <v>197</v>
       </c>
-      <c r="H247" t="s">
+      <c r="J247" t="s">
+        <v>925</v>
+      </c>
+      <c r="K247" t="s">
         <v>198</v>
-      </c>
-      <c r="K247" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -11856,20 +11856,20 @@
       <c r="D248" t="s">
         <v>14</v>
       </c>
-      <c r="E248" t="s">
-        <v>924</v>
-      </c>
       <c r="F248" t="s">
         <v>196</v>
       </c>
       <c r="G248" t="s">
+        <v>924</v>
+      </c>
+      <c r="I248" t="s">
         <v>197</v>
       </c>
-      <c r="H248" t="s">
+      <c r="J248" t="s">
+        <v>925</v>
+      </c>
+      <c r="K248" t="s">
         <v>198</v>
-      </c>
-      <c r="K248" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -11885,20 +11885,20 @@
       <c r="D249" t="s">
         <v>14</v>
       </c>
-      <c r="E249" t="s">
-        <v>924</v>
-      </c>
       <c r="F249" t="s">
         <v>932</v>
       </c>
       <c r="G249" t="s">
+        <v>924</v>
+      </c>
+      <c r="I249" t="s">
         <v>933</v>
       </c>
-      <c r="H249" t="s">
+      <c r="J249" t="s">
+        <v>925</v>
+      </c>
+      <c r="K249" t="s">
         <v>198</v>
-      </c>
-      <c r="K249" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -11914,20 +11914,20 @@
       <c r="D250" t="s">
         <v>14</v>
       </c>
-      <c r="E250" t="s">
-        <v>924</v>
-      </c>
       <c r="F250" t="s">
         <v>196</v>
       </c>
       <c r="G250" t="s">
+        <v>924</v>
+      </c>
+      <c r="I250" t="s">
         <v>197</v>
       </c>
-      <c r="H250" t="s">
+      <c r="J250" t="s">
+        <v>925</v>
+      </c>
+      <c r="K250" t="s">
         <v>198</v>
-      </c>
-      <c r="K250" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -11940,20 +11940,20 @@
       <c r="D251" t="s">
         <v>14</v>
       </c>
-      <c r="E251" t="s">
-        <v>924</v>
-      </c>
       <c r="F251" t="s">
         <v>196</v>
       </c>
       <c r="G251" t="s">
+        <v>924</v>
+      </c>
+      <c r="I251" t="s">
         <v>197</v>
       </c>
-      <c r="H251" t="s">
+      <c r="J251" t="s">
+        <v>925</v>
+      </c>
+      <c r="K251" t="s">
         <v>198</v>
-      </c>
-      <c r="K251" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -11969,20 +11969,20 @@
       <c r="D252" t="s">
         <v>14</v>
       </c>
-      <c r="E252" t="s">
-        <v>924</v>
-      </c>
       <c r="F252" t="s">
         <v>196</v>
       </c>
       <c r="G252" t="s">
+        <v>924</v>
+      </c>
+      <c r="I252" t="s">
         <v>197</v>
       </c>
-      <c r="H252" t="s">
+      <c r="J252" t="s">
+        <v>925</v>
+      </c>
+      <c r="K252" t="s">
         <v>198</v>
-      </c>
-      <c r="K252" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -11995,20 +11995,20 @@
       <c r="D253" t="s">
         <v>14</v>
       </c>
-      <c r="E253" t="s">
+      <c r="F253" t="s">
         <v>944</v>
       </c>
-      <c r="F253" t="s">
+      <c r="G253" t="s">
         <v>945</v>
       </c>
-      <c r="G253" t="s">
+      <c r="I253" t="s">
         <v>946</v>
       </c>
-      <c r="H253" t="s">
+      <c r="J253" t="s">
+        <v>947</v>
+      </c>
+      <c r="K253" t="s">
         <v>339</v>
-      </c>
-      <c r="K253" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="254" spans="1:11">
@@ -12024,20 +12024,20 @@
       <c r="D254" t="s">
         <v>14</v>
       </c>
-      <c r="E254" t="s">
-        <v>944</v>
-      </c>
       <c r="F254" t="s">
         <v>454</v>
       </c>
       <c r="G254" t="s">
+        <v>945</v>
+      </c>
+      <c r="I254" t="s">
         <v>455</v>
       </c>
-      <c r="H254" t="s">
-        <v>191</v>
+      <c r="J254" t="s">
+        <v>947</v>
       </c>
       <c r="K254" t="s">
-        <v>947</v>
+        <v>192</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -12053,20 +12053,20 @@
       <c r="D255" t="s">
         <v>14</v>
       </c>
-      <c r="E255" t="s">
-        <v>944</v>
-      </c>
       <c r="F255" t="s">
         <v>954</v>
       </c>
       <c r="G255" t="s">
+        <v>945</v>
+      </c>
+      <c r="I255" t="s">
         <v>955</v>
       </c>
-      <c r="H255" t="s">
-        <v>191</v>
+      <c r="J255" t="s">
+        <v>947</v>
       </c>
       <c r="K255" t="s">
-        <v>947</v>
+        <v>192</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -12082,20 +12082,20 @@
       <c r="D256" t="s">
         <v>14</v>
       </c>
-      <c r="E256" t="s">
-        <v>944</v>
-      </c>
       <c r="F256" t="s">
         <v>954</v>
       </c>
       <c r="G256" t="s">
+        <v>945</v>
+      </c>
+      <c r="I256" t="s">
         <v>955</v>
       </c>
-      <c r="H256" t="s">
-        <v>191</v>
+      <c r="J256" t="s">
+        <v>947</v>
       </c>
       <c r="K256" t="s">
-        <v>947</v>
+        <v>192</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -12111,20 +12111,20 @@
       <c r="D257" t="s">
         <v>14</v>
       </c>
-      <c r="E257" t="s">
-        <v>944</v>
-      </c>
       <c r="F257" t="s">
         <v>954</v>
       </c>
       <c r="G257" t="s">
+        <v>945</v>
+      </c>
+      <c r="I257" t="s">
         <v>955</v>
       </c>
-      <c r="H257" t="s">
-        <v>191</v>
+      <c r="J257" t="s">
+        <v>947</v>
       </c>
       <c r="K257" t="s">
-        <v>947</v>
+        <v>192</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -12140,20 +12140,20 @@
       <c r="D258" t="s">
         <v>14</v>
       </c>
-      <c r="E258" t="s">
-        <v>944</v>
-      </c>
       <c r="F258" t="s">
         <v>706</v>
       </c>
       <c r="G258" t="s">
-        <v>707</v>
-      </c>
-      <c r="H258" t="s">
+        <v>945</v>
+      </c>
+      <c r="I258" t="s">
+        <v>709</v>
+      </c>
+      <c r="J258" t="s">
+        <v>947</v>
+      </c>
+      <c r="K258" t="s">
         <v>339</v>
-      </c>
-      <c r="K258" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -12169,20 +12169,20 @@
       <c r="D259" t="s">
         <v>14</v>
       </c>
-      <c r="E259" t="s">
-        <v>944</v>
-      </c>
       <c r="F259" t="s">
         <v>954</v>
       </c>
       <c r="G259" t="s">
+        <v>945</v>
+      </c>
+      <c r="I259" t="s">
         <v>955</v>
       </c>
-      <c r="H259" t="s">
-        <v>191</v>
+      <c r="J259" t="s">
+        <v>947</v>
       </c>
       <c r="K259" t="s">
-        <v>947</v>
+        <v>192</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -12198,20 +12198,20 @@
       <c r="D260" t="s">
         <v>14</v>
       </c>
-      <c r="E260" t="s">
-        <v>944</v>
-      </c>
       <c r="F260" t="s">
         <v>337</v>
       </c>
       <c r="G260" t="s">
+        <v>945</v>
+      </c>
+      <c r="I260" t="s">
         <v>338</v>
       </c>
-      <c r="H260" t="s">
+      <c r="J260" t="s">
+        <v>947</v>
+      </c>
+      <c r="K260" t="s">
         <v>339</v>
-      </c>
-      <c r="K260" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -12227,20 +12227,20 @@
       <c r="D261" t="s">
         <v>14</v>
       </c>
-      <c r="E261" t="s">
-        <v>944</v>
-      </c>
       <c r="F261" t="s">
         <v>973</v>
       </c>
       <c r="G261" t="s">
+        <v>945</v>
+      </c>
+      <c r="I261" t="s">
         <v>974</v>
       </c>
-      <c r="H261" t="s">
+      <c r="J261" t="s">
+        <v>947</v>
+      </c>
+      <c r="K261" t="s">
         <v>407</v>
-      </c>
-      <c r="K261" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -12256,20 +12256,20 @@
       <c r="D262" t="s">
         <v>14</v>
       </c>
-      <c r="E262" t="s">
-        <v>944</v>
-      </c>
       <c r="F262" t="s">
         <v>337</v>
       </c>
       <c r="G262" t="s">
+        <v>945</v>
+      </c>
+      <c r="I262" t="s">
         <v>338</v>
       </c>
-      <c r="H262" t="s">
+      <c r="J262" t="s">
+        <v>947</v>
+      </c>
+      <c r="K262" t="s">
         <v>339</v>
-      </c>
-      <c r="K262" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -12285,20 +12285,20 @@
       <c r="D263" t="s">
         <v>14</v>
       </c>
-      <c r="E263" t="s">
-        <v>944</v>
-      </c>
       <c r="F263" t="s">
         <v>981</v>
       </c>
       <c r="G263" t="s">
+        <v>945</v>
+      </c>
+      <c r="I263" t="s">
         <v>982</v>
       </c>
-      <c r="H263" t="s">
+      <c r="J263" t="s">
+        <v>947</v>
+      </c>
+      <c r="K263" t="s">
         <v>379</v>
-      </c>
-      <c r="K263" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="264" spans="1:11">
@@ -12314,20 +12314,20 @@
       <c r="D264" t="s">
         <v>14</v>
       </c>
-      <c r="E264" t="s">
-        <v>944</v>
-      </c>
       <c r="F264" t="s">
         <v>58</v>
       </c>
       <c r="G264" t="s">
+        <v>945</v>
+      </c>
+      <c r="I264" t="s">
         <v>59</v>
       </c>
-      <c r="H264" t="s">
+      <c r="J264" t="s">
+        <v>947</v>
+      </c>
+      <c r="K264" t="s">
         <v>60</v>
-      </c>
-      <c r="K264" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -12343,20 +12343,20 @@
       <c r="D265" t="s">
         <v>14</v>
       </c>
-      <c r="E265" t="s">
-        <v>944</v>
-      </c>
       <c r="F265" t="s">
         <v>16</v>
       </c>
       <c r="G265" t="s">
-        <v>17</v>
-      </c>
-      <c r="H265" t="s">
-        <v>18</v>
+        <v>945</v>
+      </c>
+      <c r="I265" t="s">
+        <v>19</v>
+      </c>
+      <c r="J265" t="s">
+        <v>947</v>
       </c>
       <c r="K265" t="s">
-        <v>947</v>
+        <v>21</v>
       </c>
     </row>
     <row r="266" spans="1:11">
@@ -12372,20 +12372,20 @@
       <c r="D266" t="s">
         <v>14</v>
       </c>
-      <c r="E266" t="s">
-        <v>944</v>
-      </c>
       <c r="F266" t="s">
         <v>992</v>
       </c>
       <c r="G266" t="s">
+        <v>945</v>
+      </c>
+      <c r="I266" t="s">
         <v>993</v>
       </c>
-      <c r="H266" t="s">
-        <v>236</v>
+      <c r="J266" t="s">
+        <v>947</v>
       </c>
       <c r="K266" t="s">
-        <v>947</v>
+        <v>239</v>
       </c>
     </row>
     <row r="267" spans="1:11">
@@ -12401,20 +12401,20 @@
       <c r="D267" t="s">
         <v>14</v>
       </c>
-      <c r="E267" t="s">
-        <v>997</v>
-      </c>
       <c r="F267" t="s">
         <v>243</v>
       </c>
       <c r="G267" t="s">
+        <v>997</v>
+      </c>
+      <c r="I267" t="s">
         <v>244</v>
       </c>
-      <c r="H267" t="s">
-        <v>236</v>
+      <c r="J267" t="s">
+        <v>998</v>
       </c>
       <c r="K267" t="s">
-        <v>998</v>
+        <v>239</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -12430,20 +12430,20 @@
       <c r="D268" t="s">
         <v>14</v>
       </c>
-      <c r="E268" t="s">
+      <c r="F268" t="s">
+        <v>420</v>
+      </c>
+      <c r="G268" t="s">
         <v>1002</v>
       </c>
-      <c r="F268" t="s">
-        <v>421</v>
-      </c>
-      <c r="G268" t="s">
+      <c r="I268" t="s">
         <v>422</v>
       </c>
-      <c r="H268" t="s">
+      <c r="J268" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K268" t="s">
         <v>379</v>
-      </c>
-      <c r="K268" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -12459,20 +12459,20 @@
       <c r="D269" t="s">
         <v>14</v>
       </c>
-      <c r="E269" t="s">
-        <v>1007</v>
-      </c>
       <c r="F269" t="s">
         <v>243</v>
       </c>
       <c r="G269" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I269" t="s">
         <v>244</v>
       </c>
-      <c r="H269" t="s">
-        <v>236</v>
+      <c r="J269" t="s">
+        <v>1008</v>
       </c>
       <c r="K269" t="s">
-        <v>1008</v>
+        <v>239</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -12488,20 +12488,20 @@
       <c r="D270" t="s">
         <v>14</v>
       </c>
-      <c r="E270" t="s">
-        <v>1007</v>
-      </c>
       <c r="F270" t="s">
         <v>243</v>
       </c>
       <c r="G270" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I270" t="s">
         <v>244</v>
       </c>
-      <c r="H270" t="s">
-        <v>236</v>
+      <c r="J270" t="s">
+        <v>1008</v>
       </c>
       <c r="K270" t="s">
-        <v>1008</v>
+        <v>239</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -12517,20 +12517,20 @@
       <c r="D271" t="s">
         <v>14</v>
       </c>
-      <c r="E271" t="s">
+      <c r="F271" t="s">
         <v>1015</v>
       </c>
-      <c r="F271" t="s">
+      <c r="G271" t="s">
         <v>1016</v>
       </c>
-      <c r="G271" t="s">
+      <c r="I271" t="s">
         <v>1017</v>
       </c>
-      <c r="H271" t="s">
-        <v>236</v>
+      <c r="J271" t="s">
+        <v>1018</v>
       </c>
       <c r="K271" t="s">
-        <v>1018</v>
+        <v>239</v>
       </c>
     </row>
     <row r="272" spans="1:11">
@@ -12543,20 +12543,20 @@
       <c r="D272" t="s">
         <v>14</v>
       </c>
-      <c r="E272" t="s">
+      <c r="F272" t="s">
         <v>1015</v>
       </c>
-      <c r="F272" t="s">
+      <c r="G272" t="s">
         <v>1016</v>
       </c>
-      <c r="G272" t="s">
+      <c r="I272" t="s">
         <v>1017</v>
       </c>
-      <c r="H272" t="s">
-        <v>236</v>
+      <c r="J272" t="s">
+        <v>1018</v>
       </c>
       <c r="K272" t="s">
-        <v>1018</v>
+        <v>239</v>
       </c>
     </row>
     <row r="273" spans="1:11">
@@ -12572,20 +12572,20 @@
       <c r="D273" t="s">
         <v>14</v>
       </c>
-      <c r="E273" t="s">
+      <c r="F273" t="s">
         <v>1015</v>
       </c>
-      <c r="F273" t="s">
+      <c r="G273" t="s">
         <v>1016</v>
       </c>
-      <c r="G273" t="s">
+      <c r="I273" t="s">
         <v>1017</v>
       </c>
-      <c r="H273" t="s">
-        <v>236</v>
+      <c r="J273" t="s">
+        <v>1018</v>
       </c>
       <c r="K273" t="s">
-        <v>1018</v>
+        <v>239</v>
       </c>
     </row>
     <row r="274" spans="1:11">
@@ -12598,20 +12598,20 @@
       <c r="D274" t="s">
         <v>14</v>
       </c>
-      <c r="E274" t="s">
+      <c r="F274" t="s">
         <v>1015</v>
       </c>
-      <c r="F274" t="s">
+      <c r="G274" t="s">
         <v>1016</v>
       </c>
-      <c r="G274" t="s">
+      <c r="I274" t="s">
         <v>1017</v>
       </c>
-      <c r="H274" t="s">
-        <v>236</v>
+      <c r="J274" t="s">
+        <v>1018</v>
       </c>
       <c r="K274" t="s">
-        <v>1018</v>
+        <v>239</v>
       </c>
     </row>
     <row r="275" spans="1:11">
@@ -12627,20 +12627,20 @@
       <c r="D275" t="s">
         <v>14</v>
       </c>
-      <c r="E275" t="s">
+      <c r="F275" t="s">
         <v>1015</v>
       </c>
-      <c r="F275" t="s">
+      <c r="G275" t="s">
         <v>1016</v>
       </c>
-      <c r="G275" t="s">
+      <c r="I275" t="s">
         <v>1017</v>
       </c>
-      <c r="H275" t="s">
-        <v>236</v>
+      <c r="J275" t="s">
+        <v>1018</v>
       </c>
       <c r="K275" t="s">
-        <v>1018</v>
+        <v>239</v>
       </c>
     </row>
     <row r="276" spans="1:11">
@@ -12656,20 +12656,20 @@
       <c r="D276" t="s">
         <v>14</v>
       </c>
-      <c r="E276" t="s">
+      <c r="F276" t="s">
         <v>1015</v>
       </c>
-      <c r="F276" t="s">
+      <c r="G276" t="s">
         <v>1016</v>
       </c>
-      <c r="G276" t="s">
+      <c r="I276" t="s">
         <v>1017</v>
       </c>
-      <c r="H276" t="s">
-        <v>236</v>
+      <c r="J276" t="s">
+        <v>1018</v>
       </c>
       <c r="K276" t="s">
-        <v>1018</v>
+        <v>239</v>
       </c>
     </row>
     <row r="277" spans="1:11">
@@ -12685,20 +12685,20 @@
       <c r="D277" t="s">
         <v>14</v>
       </c>
-      <c r="E277" t="s">
+      <c r="F277" t="s">
         <v>1015</v>
       </c>
-      <c r="F277" t="s">
+      <c r="G277" t="s">
         <v>1016</v>
       </c>
-      <c r="G277" t="s">
+      <c r="I277" t="s">
         <v>1017</v>
       </c>
-      <c r="H277" t="s">
-        <v>236</v>
+      <c r="J277" t="s">
+        <v>1018</v>
       </c>
       <c r="K277" t="s">
-        <v>1018</v>
+        <v>239</v>
       </c>
     </row>
     <row r="278" spans="1:11">
@@ -12714,20 +12714,20 @@
       <c r="D278" t="s">
         <v>14</v>
       </c>
-      <c r="E278" t="s">
+      <c r="F278" t="s">
+        <v>420</v>
+      </c>
+      <c r="G278" t="s">
         <v>1038</v>
       </c>
-      <c r="F278" t="s">
-        <v>421</v>
-      </c>
-      <c r="G278" t="s">
+      <c r="I278" t="s">
         <v>422</v>
       </c>
-      <c r="H278" t="s">
+      <c r="J278" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K278" t="s">
         <v>379</v>
-      </c>
-      <c r="K278" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -12743,20 +12743,20 @@
       <c r="D279" t="s">
         <v>14</v>
       </c>
-      <c r="E279" t="s">
-        <v>1038</v>
-      </c>
       <c r="F279" t="s">
         <v>93</v>
       </c>
       <c r="G279" t="s">
-        <v>94</v>
-      </c>
-      <c r="H279" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I279" t="s">
+        <v>96</v>
+      </c>
+      <c r="J279" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K279" t="s">
         <v>60</v>
-      </c>
-      <c r="K279" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -12772,20 +12772,20 @@
       <c r="D280" t="s">
         <v>14</v>
       </c>
-      <c r="E280" t="s">
-        <v>1038</v>
-      </c>
       <c r="F280" t="s">
         <v>16</v>
       </c>
       <c r="G280" t="s">
-        <v>17</v>
-      </c>
-      <c r="H280" t="s">
-        <v>18</v>
+        <v>1038</v>
+      </c>
+      <c r="I280" t="s">
+        <v>19</v>
+      </c>
+      <c r="J280" t="s">
+        <v>1039</v>
       </c>
       <c r="K280" t="s">
-        <v>1039</v>
+        <v>21</v>
       </c>
     </row>
     <row r="281" spans="1:11">
@@ -12801,20 +12801,20 @@
       <c r="D281" t="s">
         <v>14</v>
       </c>
-      <c r="E281" t="s">
-        <v>1038</v>
-      </c>
       <c r="F281" t="s">
         <v>352</v>
       </c>
       <c r="G281" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I281" t="s">
         <v>353</v>
       </c>
-      <c r="H281" t="s">
-        <v>236</v>
+      <c r="J281" t="s">
+        <v>1039</v>
       </c>
       <c r="K281" t="s">
-        <v>1039</v>
+        <v>239</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -12830,20 +12830,20 @@
       <c r="D282" t="s">
         <v>14</v>
       </c>
-      <c r="E282" t="s">
-        <v>1038</v>
-      </c>
       <c r="F282" t="s">
         <v>253</v>
       </c>
       <c r="G282" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I282" t="s">
         <v>254</v>
       </c>
-      <c r="H282" t="s">
+      <c r="J282" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K282" t="s">
         <v>255</v>
-      </c>
-      <c r="K282" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -12859,20 +12859,20 @@
       <c r="D283" t="s">
         <v>14</v>
       </c>
-      <c r="E283" t="s">
+      <c r="F283" t="s">
+        <v>893</v>
+      </c>
+      <c r="G283" t="s">
         <v>1055</v>
       </c>
-      <c r="F283" t="s">
-        <v>802</v>
-      </c>
-      <c r="G283" t="s">
-        <v>892</v>
-      </c>
-      <c r="H283" t="s">
+      <c r="I283" t="s">
+        <v>805</v>
+      </c>
+      <c r="J283" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K283" t="s">
         <v>339</v>
-      </c>
-      <c r="K283" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -12888,20 +12888,20 @@
       <c r="D284" t="s">
         <v>14</v>
       </c>
-      <c r="E284" t="s">
-        <v>1060</v>
-      </c>
       <c r="F284" t="s">
         <v>253</v>
       </c>
       <c r="G284" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I284" t="s">
         <v>254</v>
       </c>
-      <c r="H284" t="s">
+      <c r="J284" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K284" t="s">
         <v>255</v>
-      </c>
-      <c r="K284" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -12914,20 +12914,20 @@
       <c r="D285" t="s">
         <v>14</v>
       </c>
-      <c r="E285" t="s">
-        <v>1064</v>
-      </c>
       <c r="F285" t="s">
         <v>352</v>
       </c>
       <c r="G285" t="s">
+        <v>1064</v>
+      </c>
+      <c r="I285" t="s">
         <v>353</v>
       </c>
-      <c r="H285" t="s">
-        <v>236</v>
+      <c r="J285" t="s">
+        <v>1065</v>
       </c>
       <c r="K285" t="s">
-        <v>1065</v>
+        <v>239</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -12943,20 +12943,20 @@
       <c r="D286" t="s">
         <v>14</v>
       </c>
-      <c r="E286" t="s">
-        <v>1069</v>
-      </c>
       <c r="F286" t="s">
         <v>981</v>
       </c>
       <c r="G286" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I286" t="s">
         <v>982</v>
       </c>
-      <c r="H286" t="s">
+      <c r="J286" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K286" t="s">
         <v>379</v>
-      </c>
-      <c r="K286" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -12972,20 +12972,20 @@
       <c r="D287" t="s">
         <v>14</v>
       </c>
-      <c r="E287" t="s">
-        <v>1069</v>
-      </c>
       <c r="F287" t="s">
         <v>981</v>
       </c>
       <c r="G287" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I287" t="s">
         <v>982</v>
       </c>
-      <c r="H287" t="s">
+      <c r="J287" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K287" t="s">
         <v>379</v>
-      </c>
-      <c r="K287" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -13001,20 +13001,20 @@
       <c r="D288" t="s">
         <v>14</v>
       </c>
-      <c r="E288" t="s">
-        <v>1069</v>
-      </c>
       <c r="F288" t="s">
         <v>75</v>
       </c>
       <c r="G288" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I288" t="s">
         <v>76</v>
       </c>
-      <c r="H288" t="s">
-        <v>18</v>
+      <c r="J288" t="s">
+        <v>1070</v>
       </c>
       <c r="K288" t="s">
-        <v>1070</v>
+        <v>21</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -13030,20 +13030,20 @@
       <c r="D289" t="s">
         <v>14</v>
       </c>
-      <c r="E289" t="s">
-        <v>1069</v>
-      </c>
       <c r="F289" t="s">
         <v>58</v>
       </c>
       <c r="G289" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I289" t="s">
         <v>59</v>
       </c>
-      <c r="H289" t="s">
+      <c r="J289" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K289" t="s">
         <v>60</v>
-      </c>
-      <c r="K289" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="290" spans="1:11">
@@ -13059,20 +13059,20 @@
       <c r="D290" t="s">
         <v>14</v>
       </c>
-      <c r="E290" t="s">
-        <v>1069</v>
-      </c>
       <c r="F290" t="s">
         <v>58</v>
       </c>
       <c r="G290" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I290" t="s">
         <v>59</v>
       </c>
-      <c r="H290" t="s">
+      <c r="J290" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K290" t="s">
         <v>60</v>
-      </c>
-      <c r="K290" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -13088,20 +13088,20 @@
       <c r="D291" t="s">
         <v>14</v>
       </c>
-      <c r="E291" t="s">
-        <v>1069</v>
-      </c>
       <c r="F291" t="s">
         <v>352</v>
       </c>
       <c r="G291" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I291" t="s">
         <v>353</v>
       </c>
-      <c r="H291" t="s">
-        <v>236</v>
+      <c r="J291" t="s">
+        <v>1070</v>
       </c>
       <c r="K291" t="s">
-        <v>1070</v>
+        <v>239</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -13117,20 +13117,20 @@
       <c r="D292" t="s">
         <v>14</v>
       </c>
-      <c r="E292" t="s">
-        <v>1069</v>
-      </c>
       <c r="F292" t="s">
         <v>352</v>
       </c>
       <c r="G292" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I292" t="s">
         <v>353</v>
       </c>
-      <c r="H292" t="s">
-        <v>236</v>
+      <c r="J292" t="s">
+        <v>1070</v>
       </c>
       <c r="K292" t="s">
-        <v>1070</v>
+        <v>239</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -13146,20 +13146,20 @@
       <c r="D293" t="s">
         <v>14</v>
       </c>
-      <c r="E293" t="s">
-        <v>1069</v>
-      </c>
       <c r="F293" t="s">
         <v>352</v>
       </c>
       <c r="G293" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I293" t="s">
         <v>353</v>
       </c>
-      <c r="H293" t="s">
-        <v>236</v>
+      <c r="J293" t="s">
+        <v>1070</v>
       </c>
       <c r="K293" t="s">
-        <v>1070</v>
+        <v>239</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -13175,20 +13175,20 @@
       <c r="D294" t="s">
         <v>14</v>
       </c>
-      <c r="E294" t="s">
-        <v>1069</v>
-      </c>
       <c r="F294" t="s">
         <v>352</v>
       </c>
       <c r="G294" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I294" t="s">
         <v>353</v>
       </c>
-      <c r="H294" t="s">
-        <v>236</v>
+      <c r="J294" t="s">
+        <v>1070</v>
       </c>
       <c r="K294" t="s">
-        <v>1070</v>
+        <v>239</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -13204,20 +13204,20 @@
       <c r="D295" t="s">
         <v>14</v>
       </c>
-      <c r="E295" t="s">
-        <v>1098</v>
-      </c>
       <c r="F295" t="s">
         <v>352</v>
       </c>
       <c r="G295" t="s">
+        <v>1098</v>
+      </c>
+      <c r="I295" t="s">
         <v>353</v>
       </c>
-      <c r="H295" t="s">
-        <v>236</v>
+      <c r="J295" t="s">
+        <v>1099</v>
       </c>
       <c r="K295" t="s">
-        <v>1099</v>
+        <v>239</v>
       </c>
     </row>
     <row r="296" spans="1:11">
@@ -13233,20 +13233,20 @@
       <c r="D296" t="s">
         <v>14</v>
       </c>
-      <c r="E296" t="s">
-        <v>1098</v>
-      </c>
       <c r="F296" t="s">
         <v>352</v>
       </c>
       <c r="G296" t="s">
+        <v>1098</v>
+      </c>
+      <c r="I296" t="s">
         <v>353</v>
       </c>
-      <c r="H296" t="s">
-        <v>236</v>
+      <c r="J296" t="s">
+        <v>1099</v>
       </c>
       <c r="K296" t="s">
-        <v>1099</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -28,24 +28,24 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
@@ -61,24 +61,24 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>09 - Education</t>
   </si>
   <si>
@@ -130,15 +130,15 @@
     <t>Formal and non-formal primary education for children; all elementary and first cycle systematic instruction; provision of learning materials.</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
@@ -223,15 +223,15 @@
     <t>Second cycle systematic instruction at senior levels.</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>Secondary Education</t>
   </si>
   <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -256,15 +256,15 @@
     <t>Degree and diploma programmes at universities, colleges and polytechnics; scholarships.</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
@@ -292,24 +292,24 @@
     <t>Health sector policy, planning and programmes; aid to health ministries, public health administration; institution capacity building and advice; medical insurance programmes; including health system strengthening and health governance; unspecified health activities.</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -367,12 +367,12 @@
     <t>Basic and primary health care programmes; paramedical and nursing care programmes; supply of drugs, medicines and vaccines related to basic health care; activities aimed at achieving universal health coverage.</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Basic Health</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -460,12 +460,12 @@
     <t>Programmes for the prevention and control of NCDs which cannot be broken down into the codes below.</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Non-communicable diseases (NCDs)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -520,12 +520,12 @@
     <t>Population/development policies; demographic research/analysis; reproductive health research; unspecified population activities. (Use purpose code 15190 for data on migration and refugees. Use code 13096 for census work, vital registration and migration data collection.)</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
     <t>Population Policies/Programmes &amp; Reproductive Health</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -580,18 +580,18 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
@@ -715,24 +715,24 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>01 - General public services</t>
   </si>
   <si>
@@ -1207,12 +1207,12 @@
     <t>Technical co-operation provided to parliament, government ministries, law enforcement agencies and the judiciary to assist review and reform of the security system to improve democratic governance and civilian control; technical co-operation provided to government to improve civilian oversight and democratic control of budgeting, management, accountability and auditing of security expenditure, including military budgets, as part of a public expenditure management programme; assistance to civil society to enhance its competence and capacity to scrutinise the security system so that it is managed in accordance with democratic norms and principles of accountability, transparency and good governance. [Other than in the context of an international peacekeeping operation (15230)].</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflict, Peace &amp; Security</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -1276,18 +1276,18 @@
     <t>Social protection or social security strategies, legislation and administration; institution capacity building and advice; social security and other social schemes; support programmes, cash benefits, pensions and special programmes for older persons, orphans, persons with disabilities, children, mothers with newborns, those living in poverty, without jobs and other vulnerable groups; social dimensions of structural adjustment.</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1486,12 +1486,12 @@
     <t>Transport sector policy, planning and programmes; aid to transport ministries; institution capacity building and advice; unspecified transport; activities that combine road, rail, water and/or air transport. Includes prevention of road accidents. Whenever possible, report transport of goods under the sector of the good being transported.</t>
   </si>
   <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>Transport &amp; Storage</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
     <t>21011</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>Communications sector policy, planning and programmes; institution capacity building and advice; including postal services development; unspecified communications activities.</t>
   </si>
   <si>
+    <t>220</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>22011</t>
   </si>
   <si>
@@ -1708,24 +1708,24 @@
     <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>Renewable energy generation programmes that cannot be attributed to one single technology (codes 23220 through 23280 below). Fuelwood/charcoal production should be included under forestry 31261.</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Energy generation, renewable sources</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -1870,12 +1870,12 @@
     <t>Thermal power plants including when energy source cannot be determined; combined gas-coal power plants.</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Energy generation, non-renewable sources</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -1933,12 +1933,12 @@
     <t>Electric power plants that make use of both non-renewable and renewable energy sources.</t>
   </si>
   <si>
+    <t>234</t>
+  </si>
+  <si>
     <t>Hybrid energy plants</t>
   </si>
   <si>
-    <t>234</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
@@ -1948,12 +1948,12 @@
     <t>See note regarding ODA eligibility of nuclear energy.</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>04.3.3 - Nuclear fuel (CS)</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -1963,12 +1963,12 @@
     <t>Power plants which are designed to produce heat only.</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Energy distribution</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -2032,12 +2032,12 @@
     <t>Finance sector policy, planning and programmes; institution capacity building and advice; financial markets and systems.</t>
   </si>
   <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>Banking &amp; Financial Services</t>
   </si>
   <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -2089,12 +2089,12 @@
     <t>Public sector policies and institution support to the business environment and investment climate, including business regulations, property rights, non-discrimination, investment promotion, competition policy, enterprises law, private-public partnerships.</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
     <t>Business &amp; Other Services</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -2131,24 +2131,24 @@
     <t>Agricultural sector policy, planning and programmes; aid to agricultural ministries; institution capacity building and advice; unspecified agriculture.</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2311,15 +2311,15 @@
     <t>Forestry sector policy, planning and programmes; institution capacity building and advice; forest surveys; unspecified forestry and agro-forestry activities.</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
     <t>Forestry</t>
   </si>
   <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -2368,15 +2368,15 @@
     <t>Fishing sector policy, planning and programmes; institution capacity building and advice; ocean and coastal fishing; marine and freshwater fish surveys and prospecting; fishing boats/equipment; unspecified fishing activities.</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
     <t>Fishing</t>
   </si>
   <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -2419,24 +2419,24 @@
     <t>Industrial sector policy, planning and programmes; institution capacity building and advice; unspecified industrial activities; manufacturing of goods not specified below.</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
     <t>Industry</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2593,15 +2593,15 @@
     <t>Mineral and mining sector policy, planning and programmes; mining legislation, mining cadastre, mineral resources inventory, information systems, institution capacity building and advice; unspecified mineral resources exploitation.</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -2692,15 +2692,15 @@
     <t>Construction sector policy and planning; excluding construction activities within specific sectors (e.g., hospital or school construction).</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -2710,15 +2710,15 @@
     <t>Trade policy and planning; support to ministries and departments responsible for trade policy; trade-related legislation and regulatory reforms; policy analysis and implementation of multilateral trade agreements e.g. technical barriers to trade and sanitary and phytosanitary measures (TBT/SPS) except at regional level (see 33130); mainstreaming trade in national development strategies (e.g. poverty reduction strategy papers); wholesale/retail trade; unspecified trade and trade promotion activities.</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -2770,15 +2770,15 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>04.7.3 - Tourism (CS)</t>
-  </si>
-  <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -2788,12 +2788,12 @@
     <t>Environmental policy, laws, regulations and economic instruments; administrational institutions and practices; environmental and land use planning and decision-making procedures; seminars, meetings; miscellaneous conservation and protection measures not specified below.</t>
   </si>
   <si>
+    <t>410</t>
+  </si>
+  <si>
     <t>General Environment Protection</t>
   </si>
   <si>
-    <t>410</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -2848,18 +2848,18 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -3007,12 +3007,12 @@
     <t>Unearmarked contributions to the government budget; support for the implementation of macroeconomic reforms (structural adjustment programmes, poverty reduction strategies); general programme assistance (when not allocable by sector).</t>
   </si>
   <si>
+    <t>510</t>
+  </si>
+  <si>
     <t>General Budget Support</t>
   </si>
   <si>
-    <t>510</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
@@ -3022,12 +3022,12 @@
     <t>Supply of edible human food under national or international programmes including transport costs, cash payments made for food supplies; project food assistance aid and food assistance aid for market sales when benefiting sector not specified. Excludes food security policy and administrative management (43071), household food security programmes (43072) and emergency food assistance aid (72040). Report as multilateral: i) food assistance aid by EU financed out of its budget and allocated pro rata to EU member countries; and ii) core contributions to the World Food Programme.</t>
   </si>
   <si>
+    <t>520</t>
+  </si>
+  <si>
     <t>Development Food Assistance</t>
   </si>
   <si>
-    <t>520</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
@@ -3037,12 +3037,12 @@
     <t>Capital goods and services; lines of credit.</t>
   </si>
   <si>
+    <t>530</t>
+  </si>
+  <si>
     <t>Other Commodity Assistance</t>
   </si>
   <si>
-    <t>530</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -3061,18 +3061,18 @@
     <t>Actions falling outside the code headings below.</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>01.7 - Public debt transactions</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -3130,12 +3130,12 @@
     <t>Shelter, water, sanitation, education, health services including supply of medicines and malnutrition management, including medical nutrition management; supply of other nonfood relief items (including cash and voucher delivery modalities) for the benefit of crisisaffected people, including refugees and internally displaced people in developing countries, Includes assistance delivered by or coordinated by international civil protection units in the immediate aftermath of a disaster (in-kind assistance, deployment of specially-equipped teams, logistics and transportation, or assessment and coordination by experts sent to the field). Also includes measures to promote and protect the safety, well-being, dignity and integrity of crisis-affected people including refugees and internally displaced persons in developing countries. (Activities designed to protect the security of persons or properties through the use or display of force are not reportable as ODA.)</t>
   </si>
   <si>
+    <t>720</t>
+  </si>
+  <si>
     <t>Emergency Response</t>
   </si>
   <si>
-    <t>720</t>
-  </si>
-  <si>
     <t>72011</t>
   </si>
   <si>
@@ -3181,12 +3181,12 @@
     <t>Social and economic rehabilitation in the aftermath of emergencies to facilitate recovery and resilience building and enable populations to restore their livelihoods in the wake of an emergency situation (e.g. trauma counselling and treatment, employment programmes). Includes infrastructure necessary for the delivery of humanitarian aid; restoring pre-existing essential infrastructure and facilities (e.g. water and sanitation, shelter, health care services, education); rehabilitation of basic agricultural inputs and livestock. Excludes longer-term reconstruction ('build back better') which is reportable against relevant sectors.</t>
   </si>
   <si>
+    <t>730</t>
+  </si>
+  <si>
     <t>Reconstruction Relief &amp; Rehabilitation</t>
   </si>
   <si>
-    <t>730</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
@@ -3196,24 +3196,24 @@
     <t>Building the responsiveness, capability and capacity of international, regional and national humanitarian actors to disasters. Support to the institutional capacities of national and local government, specialised humanitarian bodies, and civil society organisations to anticipate, respond and recover from the impact of potential, imminent and current hazardous events and emergency situations that pose humanitarian threats and could call for a humanitarian response. This includes risk analysis and assessment, mitigation, preparedness, such as stockpiling of emergency items and training and capacity building aimed to increase the speed and effectiveness of lifesaving assistance delivered in the occurrence of crisis.</t>
   </si>
   <si>
+    <t>740</t>
+  </si>
+  <si>
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>740</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>910</t>
+  </si>
+  <si>
     <t>Administrative Costs of Donors</t>
   </si>
   <si>
-    <t>910</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
@@ -3223,12 +3223,12 @@
     <t>Costs incurred in donor countries for basic assistance to asylum seekers and refugees from developing countries, up to 12 months, when costs cannot be disaggregated. See section II.6 and Annex 17.</t>
   </si>
   <si>
+    <t>930</t>
+  </si>
+  <si>
     <t>Refugees in Donor Countries</t>
   </si>
   <si>
-    <t>930</t>
-  </si>
-  <si>
     <t>93011</t>
   </si>
   <si>
@@ -3310,10 +3310,10 @@
     <t>Contributions to general development of the recipient should be included under programme assistance (51010).</t>
   </si>
   <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>Unallocated / Unspecified</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
   <si>
     <t>99820</t>
@@ -3744,19 +3744,19 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
         <v>26</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
@@ -3814,19 +3814,19 @@
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="I5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" t="s">
         <v>34</v>
-      </c>
-      <c r="J5" t="s">
-        <v>20</v>
       </c>
       <c r="K5" t="s">
         <v>21</v>
@@ -3849,19 +3849,19 @@
         <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
       </c>
       <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" t="s">
         <v>40</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>41</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -3890,10 +3890,10 @@
         <v>17</v>
       </c>
       <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
         <v>40</v>
-      </c>
-      <c r="I7" t="s">
-        <v>19</v>
       </c>
       <c r="J7" t="s">
         <v>20</v>
@@ -3919,19 +3919,19 @@
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
       </c>
       <c r="H8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" t="s">
         <v>40</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>41</v>
-      </c>
-      <c r="J8" t="s">
-        <v>20</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
@@ -3954,19 +3954,19 @@
         <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
       </c>
       <c r="H9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" t="s">
         <v>40</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>41</v>
-      </c>
-      <c r="J9" t="s">
-        <v>20</v>
       </c>
       <c r="K9" t="s">
         <v>21</v>
@@ -3989,19 +3989,19 @@
         <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
       <c r="H10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" t="s">
         <v>40</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>41</v>
-      </c>
-      <c r="J10" t="s">
-        <v>20</v>
       </c>
       <c r="K10" t="s">
         <v>21</v>
@@ -4024,19 +4024,19 @@
         <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
         <v>17</v>
       </c>
       <c r="H11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" t="s">
         <v>40</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>59</v>
-      </c>
-      <c r="J11" t="s">
-        <v>20</v>
       </c>
       <c r="K11" t="s">
         <v>60</v>
@@ -4059,19 +4059,19 @@
         <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
         <v>17</v>
       </c>
       <c r="H12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" t="s">
         <v>40</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>65</v>
-      </c>
-      <c r="J12" t="s">
-        <v>20</v>
       </c>
       <c r="K12" t="s">
         <v>21</v>
@@ -4094,19 +4094,19 @@
         <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
       </c>
       <c r="H13" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" t="s">
         <v>71</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>65</v>
-      </c>
-      <c r="J13" t="s">
-        <v>20</v>
       </c>
       <c r="K13" t="s">
         <v>21</v>
@@ -4129,19 +4129,19 @@
         <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
       </c>
       <c r="H14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" t="s">
         <v>71</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>76</v>
-      </c>
-      <c r="J14" t="s">
-        <v>20</v>
       </c>
       <c r="K14" t="s">
         <v>21</v>
@@ -4164,19 +4164,19 @@
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="G15" t="s">
         <v>17</v>
       </c>
       <c r="H15" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" t="s">
         <v>82</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>83</v>
-      </c>
-      <c r="J15" t="s">
-        <v>20</v>
       </c>
       <c r="K15" t="s">
         <v>21</v>
@@ -4199,19 +4199,19 @@
         <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="G16" t="s">
         <v>17</v>
       </c>
       <c r="H16" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" t="s">
         <v>82</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>88</v>
-      </c>
-      <c r="J16" t="s">
-        <v>20</v>
       </c>
       <c r="K16" t="s">
         <v>21</v>
@@ -4304,19 +4304,19 @@
         <v>92</v>
       </c>
       <c r="F19" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s">
         <v>94</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="I19" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" t="s">
         <v>105</v>
-      </c>
-      <c r="J19" t="s">
-        <v>97</v>
       </c>
       <c r="K19" t="s">
         <v>60</v>
@@ -4339,19 +4339,19 @@
         <v>92</v>
       </c>
       <c r="F20" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s">
         <v>94</v>
       </c>
       <c r="H20" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I20" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" t="s">
         <v>110</v>
-      </c>
-      <c r="J20" t="s">
-        <v>97</v>
       </c>
       <c r="K20" t="s">
         <v>60</v>
@@ -4409,19 +4409,19 @@
         <v>117</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s">
         <v>94</v>
       </c>
       <c r="H22" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" t="s">
         <v>118</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>59</v>
-      </c>
-      <c r="J22" t="s">
-        <v>97</v>
       </c>
       <c r="K22" t="s">
         <v>60</v>
@@ -4444,19 +4444,19 @@
         <v>117</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s">
         <v>94</v>
       </c>
       <c r="H23" t="s">
+        <v>122</v>
+      </c>
+      <c r="I23" t="s">
         <v>118</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>123</v>
-      </c>
-      <c r="J23" t="s">
-        <v>97</v>
       </c>
       <c r="K23" t="s">
         <v>60</v>
@@ -4479,19 +4479,19 @@
         <v>117</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s">
         <v>94</v>
       </c>
       <c r="H24" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" t="s">
         <v>118</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>59</v>
-      </c>
-      <c r="J24" t="s">
-        <v>97</v>
       </c>
       <c r="K24" t="s">
         <v>60</v>
@@ -4514,19 +4514,19 @@
         <v>117</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s">
         <v>94</v>
       </c>
       <c r="H25" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" t="s">
         <v>118</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>59</v>
-      </c>
-      <c r="J25" t="s">
-        <v>97</v>
       </c>
       <c r="K25" t="s">
         <v>60</v>
@@ -4549,19 +4549,19 @@
         <v>117</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s">
         <v>94</v>
       </c>
       <c r="H26" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" t="s">
         <v>118</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>59</v>
-      </c>
-      <c r="J26" t="s">
-        <v>97</v>
       </c>
       <c r="K26" t="s">
         <v>60</v>
@@ -4584,19 +4584,19 @@
         <v>117</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s">
         <v>94</v>
       </c>
       <c r="H27" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" t="s">
         <v>118</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>59</v>
-      </c>
-      <c r="J27" t="s">
-        <v>97</v>
       </c>
       <c r="K27" t="s">
         <v>60</v>
@@ -4619,19 +4619,19 @@
         <v>117</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s">
         <v>94</v>
       </c>
       <c r="H28" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" t="s">
         <v>118</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>59</v>
-      </c>
-      <c r="J28" t="s">
-        <v>97</v>
       </c>
       <c r="K28" t="s">
         <v>60</v>
@@ -4654,19 +4654,19 @@
         <v>117</v>
       </c>
       <c r="F29" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s">
         <v>94</v>
       </c>
       <c r="H29" t="s">
+        <v>58</v>
+      </c>
+      <c r="I29" t="s">
         <v>118</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>59</v>
-      </c>
-      <c r="J29" t="s">
-        <v>97</v>
       </c>
       <c r="K29" t="s">
         <v>60</v>
@@ -4695,10 +4695,10 @@
         <v>94</v>
       </c>
       <c r="H30" t="s">
+        <v>95</v>
+      </c>
+      <c r="I30" t="s">
         <v>118</v>
-      </c>
-      <c r="I30" t="s">
-        <v>96</v>
       </c>
       <c r="J30" t="s">
         <v>97</v>
@@ -4724,19 +4724,19 @@
         <v>148</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s">
         <v>94</v>
       </c>
       <c r="H31" t="s">
+        <v>58</v>
+      </c>
+      <c r="I31" t="s">
         <v>149</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>59</v>
-      </c>
-      <c r="J31" t="s">
-        <v>97</v>
       </c>
       <c r="K31" t="s">
         <v>60</v>
@@ -4759,19 +4759,19 @@
         <v>148</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s">
         <v>94</v>
       </c>
       <c r="H32" t="s">
+        <v>58</v>
+      </c>
+      <c r="I32" t="s">
         <v>149</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>59</v>
-      </c>
-      <c r="J32" t="s">
-        <v>97</v>
       </c>
       <c r="K32" t="s">
         <v>60</v>
@@ -4794,19 +4794,19 @@
         <v>148</v>
       </c>
       <c r="F33" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s">
         <v>94</v>
       </c>
       <c r="H33" t="s">
+        <v>58</v>
+      </c>
+      <c r="I33" t="s">
         <v>149</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>59</v>
-      </c>
-      <c r="J33" t="s">
-        <v>97</v>
       </c>
       <c r="K33" t="s">
         <v>60</v>
@@ -4829,19 +4829,19 @@
         <v>148</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s">
         <v>94</v>
       </c>
       <c r="H34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I34" t="s">
         <v>149</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>59</v>
-      </c>
-      <c r="J34" t="s">
-        <v>97</v>
       </c>
       <c r="K34" t="s">
         <v>60</v>
@@ -4864,19 +4864,19 @@
         <v>148</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s">
         <v>94</v>
       </c>
       <c r="H35" t="s">
+        <v>58</v>
+      </c>
+      <c r="I35" t="s">
         <v>149</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>59</v>
-      </c>
-      <c r="J35" t="s">
-        <v>97</v>
       </c>
       <c r="K35" t="s">
         <v>60</v>
@@ -4899,19 +4899,19 @@
         <v>148</v>
       </c>
       <c r="F36" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s">
         <v>94</v>
       </c>
       <c r="H36" t="s">
+        <v>104</v>
+      </c>
+      <c r="I36" t="s">
         <v>149</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>105</v>
-      </c>
-      <c r="J36" t="s">
-        <v>97</v>
       </c>
       <c r="K36" t="s">
         <v>60</v>
@@ -4931,16 +4931,16 @@
         <v>14</v>
       </c>
       <c r="F37" t="s">
+        <v>168</v>
+      </c>
+      <c r="G37" t="s">
+        <v>169</v>
+      </c>
+      <c r="H37" t="s">
         <v>58</v>
       </c>
-      <c r="G37" t="s">
-        <v>168</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>59</v>
-      </c>
-      <c r="J37" t="s">
-        <v>169</v>
       </c>
       <c r="K37" t="s">
         <v>60</v>
@@ -4960,16 +4960,16 @@
         <v>14</v>
       </c>
       <c r="F38" t="s">
+        <v>168</v>
+      </c>
+      <c r="G38" t="s">
+        <v>169</v>
+      </c>
+      <c r="H38" t="s">
         <v>58</v>
       </c>
-      <c r="G38" t="s">
-        <v>168</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>59</v>
-      </c>
-      <c r="J38" t="s">
-        <v>169</v>
       </c>
       <c r="K38" t="s">
         <v>60</v>
@@ -4989,16 +4989,16 @@
         <v>14</v>
       </c>
       <c r="F39" t="s">
+        <v>168</v>
+      </c>
+      <c r="G39" t="s">
+        <v>169</v>
+      </c>
+      <c r="H39" t="s">
         <v>58</v>
       </c>
-      <c r="G39" t="s">
-        <v>168</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>59</v>
-      </c>
-      <c r="J39" t="s">
-        <v>169</v>
       </c>
       <c r="K39" t="s">
         <v>60</v>
@@ -5018,16 +5018,16 @@
         <v>14</v>
       </c>
       <c r="F40" t="s">
+        <v>168</v>
+      </c>
+      <c r="G40" t="s">
+        <v>169</v>
+      </c>
+      <c r="H40" t="s">
         <v>58</v>
       </c>
-      <c r="G40" t="s">
-        <v>168</v>
-      </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>59</v>
-      </c>
-      <c r="J40" t="s">
-        <v>169</v>
       </c>
       <c r="K40" t="s">
         <v>60</v>
@@ -5047,16 +5047,16 @@
         <v>14</v>
       </c>
       <c r="F41" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="G41" t="s">
-        <v>168</v>
-      </c>
-      <c r="I41" t="s">
-        <v>96</v>
+        <v>169</v>
+      </c>
+      <c r="H41" t="s">
+        <v>95</v>
       </c>
       <c r="J41" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
       <c r="K41" t="s">
         <v>60</v>
@@ -5076,16 +5076,16 @@
         <v>14</v>
       </c>
       <c r="F42" t="s">
+        <v>168</v>
+      </c>
+      <c r="G42" t="s">
+        <v>169</v>
+      </c>
+      <c r="H42" t="s">
         <v>104</v>
       </c>
-      <c r="G42" t="s">
-        <v>168</v>
-      </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>105</v>
-      </c>
-      <c r="J42" t="s">
-        <v>169</v>
       </c>
       <c r="K42" t="s">
         <v>60</v>
@@ -5110,7 +5110,7 @@
       <c r="G43" t="s">
         <v>189</v>
       </c>
-      <c r="I43" t="s">
+      <c r="H43" t="s">
         <v>190</v>
       </c>
       <c r="J43" t="s">
@@ -5134,16 +5134,16 @@
         <v>14</v>
       </c>
       <c r="F44" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="G44" t="s">
         <v>189</v>
       </c>
-      <c r="I44" t="s">
+      <c r="H44" t="s">
+        <v>196</v>
+      </c>
+      <c r="J44" t="s">
         <v>197</v>
-      </c>
-      <c r="J44" t="s">
-        <v>191</v>
       </c>
       <c r="K44" t="s">
         <v>198</v>
@@ -5168,7 +5168,7 @@
       <c r="G45" t="s">
         <v>189</v>
       </c>
-      <c r="I45" t="s">
+      <c r="H45" t="s">
         <v>190</v>
       </c>
       <c r="J45" t="s">
@@ -5197,7 +5197,7 @@
       <c r="G46" t="s">
         <v>189</v>
       </c>
-      <c r="I46" t="s">
+      <c r="H46" t="s">
         <v>190</v>
       </c>
       <c r="J46" t="s">
@@ -5221,16 +5221,16 @@
         <v>14</v>
       </c>
       <c r="F47" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="G47" t="s">
         <v>189</v>
       </c>
-      <c r="I47" t="s">
+      <c r="H47" t="s">
+        <v>208</v>
+      </c>
+      <c r="J47" t="s">
         <v>209</v>
-      </c>
-      <c r="J47" t="s">
-        <v>191</v>
       </c>
       <c r="K47" t="s">
         <v>198</v>
@@ -5255,7 +5255,7 @@
       <c r="G48" t="s">
         <v>189</v>
       </c>
-      <c r="I48" t="s">
+      <c r="H48" t="s">
         <v>190</v>
       </c>
       <c r="J48" t="s">
@@ -5284,7 +5284,7 @@
       <c r="G49" t="s">
         <v>189</v>
       </c>
-      <c r="I49" t="s">
+      <c r="H49" t="s">
         <v>190</v>
       </c>
       <c r="J49" t="s">
@@ -5308,16 +5308,16 @@
         <v>14</v>
       </c>
       <c r="F50" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="G50" t="s">
         <v>189</v>
       </c>
-      <c r="I50" t="s">
+      <c r="H50" t="s">
+        <v>208</v>
+      </c>
+      <c r="J50" t="s">
         <v>209</v>
-      </c>
-      <c r="J50" t="s">
-        <v>191</v>
       </c>
       <c r="K50" t="s">
         <v>198</v>
@@ -5342,7 +5342,7 @@
       <c r="G51" t="s">
         <v>189</v>
       </c>
-      <c r="I51" t="s">
+      <c r="H51" t="s">
         <v>190</v>
       </c>
       <c r="J51" t="s">
@@ -5366,16 +5366,16 @@
         <v>14</v>
       </c>
       <c r="F52" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="G52" t="s">
         <v>189</v>
       </c>
-      <c r="I52" t="s">
+      <c r="H52" t="s">
+        <v>225</v>
+      </c>
+      <c r="J52" t="s">
         <v>226</v>
-      </c>
-      <c r="J52" t="s">
-        <v>191</v>
       </c>
       <c r="K52" t="s">
         <v>198</v>
@@ -5395,16 +5395,16 @@
         <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="G53" t="s">
         <v>189</v>
       </c>
-      <c r="I53" t="s">
-        <v>19</v>
+      <c r="H53" t="s">
+        <v>18</v>
       </c>
       <c r="J53" t="s">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s">
         <v>21</v>
@@ -5462,19 +5462,19 @@
         <v>233</v>
       </c>
       <c r="F55" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G55" t="s">
         <v>235</v>
       </c>
       <c r="H55" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I55" t="s">
+        <v>237</v>
+      </c>
+      <c r="J55" t="s">
         <v>244</v>
-      </c>
-      <c r="J55" t="s">
-        <v>238</v>
       </c>
       <c r="K55" t="s">
         <v>239</v>
@@ -5497,19 +5497,19 @@
         <v>233</v>
       </c>
       <c r="F56" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G56" t="s">
         <v>235</v>
       </c>
       <c r="H56" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="I56" t="s">
+        <v>237</v>
+      </c>
+      <c r="J56" t="s">
         <v>249</v>
-      </c>
-      <c r="J56" t="s">
-        <v>238</v>
       </c>
       <c r="K56" t="s">
         <v>239</v>
@@ -5532,19 +5532,19 @@
         <v>233</v>
       </c>
       <c r="F57" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="G57" t="s">
         <v>235</v>
       </c>
       <c r="H57" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="I57" t="s">
+        <v>237</v>
+      </c>
+      <c r="J57" t="s">
         <v>254</v>
-      </c>
-      <c r="J57" t="s">
-        <v>238</v>
       </c>
       <c r="K57" t="s">
         <v>255</v>
@@ -5567,19 +5567,19 @@
         <v>233</v>
       </c>
       <c r="F58" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G58" t="s">
         <v>235</v>
       </c>
       <c r="H58" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I58" t="s">
+        <v>237</v>
+      </c>
+      <c r="J58" t="s">
         <v>244</v>
-      </c>
-      <c r="J58" t="s">
-        <v>238</v>
       </c>
       <c r="K58" t="s">
         <v>239</v>
@@ -5602,19 +5602,19 @@
         <v>233</v>
       </c>
       <c r="F59" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G59" t="s">
         <v>235</v>
       </c>
       <c r="H59" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I59" t="s">
+        <v>237</v>
+      </c>
+      <c r="J59" t="s">
         <v>244</v>
-      </c>
-      <c r="J59" t="s">
-        <v>238</v>
       </c>
       <c r="K59" t="s">
         <v>239</v>
@@ -5637,19 +5637,19 @@
         <v>233</v>
       </c>
       <c r="F60" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G60" t="s">
         <v>235</v>
       </c>
       <c r="H60" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I60" t="s">
+        <v>237</v>
+      </c>
+      <c r="J60" t="s">
         <v>244</v>
-      </c>
-      <c r="J60" t="s">
-        <v>238</v>
       </c>
       <c r="K60" t="s">
         <v>239</v>
@@ -5672,19 +5672,19 @@
         <v>233</v>
       </c>
       <c r="F61" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G61" t="s">
         <v>235</v>
       </c>
       <c r="H61" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I61" t="s">
+        <v>237</v>
+      </c>
+      <c r="J61" t="s">
         <v>244</v>
-      </c>
-      <c r="J61" t="s">
-        <v>238</v>
       </c>
       <c r="K61" t="s">
         <v>239</v>
@@ -5707,19 +5707,19 @@
         <v>233</v>
       </c>
       <c r="F62" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G62" t="s">
         <v>235</v>
       </c>
       <c r="H62" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I62" t="s">
+        <v>237</v>
+      </c>
+      <c r="J62" t="s">
         <v>244</v>
-      </c>
-      <c r="J62" t="s">
-        <v>238</v>
       </c>
       <c r="K62" t="s">
         <v>239</v>
@@ -5742,19 +5742,19 @@
         <v>233</v>
       </c>
       <c r="F63" t="s">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="G63" t="s">
         <v>235</v>
       </c>
       <c r="H63" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="I63" t="s">
+        <v>237</v>
+      </c>
+      <c r="J63" t="s">
         <v>244</v>
-      </c>
-      <c r="J63" t="s">
-        <v>238</v>
       </c>
       <c r="K63" t="s">
         <v>239</v>
@@ -5777,19 +5777,19 @@
         <v>233</v>
       </c>
       <c r="F64" t="s">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="G64" t="s">
         <v>235</v>
       </c>
       <c r="H64" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="I64" t="s">
+        <v>237</v>
+      </c>
+      <c r="J64" t="s">
         <v>244</v>
-      </c>
-      <c r="J64" t="s">
-        <v>238</v>
       </c>
       <c r="K64" t="s">
         <v>239</v>
@@ -5812,19 +5812,19 @@
         <v>233</v>
       </c>
       <c r="F65" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="G65" t="s">
         <v>235</v>
       </c>
       <c r="H65" t="s">
-        <v>236</v>
+        <v>281</v>
       </c>
       <c r="I65" t="s">
+        <v>237</v>
+      </c>
+      <c r="J65" t="s">
         <v>282</v>
-      </c>
-      <c r="J65" t="s">
-        <v>238</v>
       </c>
       <c r="K65" t="s">
         <v>239</v>
@@ -5882,19 +5882,19 @@
         <v>233</v>
       </c>
       <c r="F67" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G67" t="s">
         <v>235</v>
       </c>
       <c r="H67" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I67" t="s">
+        <v>237</v>
+      </c>
+      <c r="J67" t="s">
         <v>244</v>
-      </c>
-      <c r="J67" t="s">
-        <v>238</v>
       </c>
       <c r="K67" t="s">
         <v>239</v>
@@ -5917,13 +5917,13 @@
         <v>233</v>
       </c>
       <c r="F68" t="s">
-        <v>292</v>
+        <v>234</v>
       </c>
       <c r="G68" t="s">
         <v>235</v>
       </c>
       <c r="H68" t="s">
-        <v>236</v>
+        <v>292</v>
       </c>
       <c r="I68" t="s">
         <v>237</v>
@@ -5952,13 +5952,13 @@
         <v>233</v>
       </c>
       <c r="F69" t="s">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="G69" t="s">
         <v>235</v>
       </c>
       <c r="H69" t="s">
-        <v>236</v>
+        <v>296</v>
       </c>
       <c r="I69" t="s">
         <v>237</v>
@@ -5987,19 +5987,19 @@
         <v>233</v>
       </c>
       <c r="F70" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G70" t="s">
         <v>235</v>
       </c>
       <c r="H70" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="I70" t="s">
+        <v>237</v>
+      </c>
+      <c r="J70" t="s">
         <v>249</v>
-      </c>
-      <c r="J70" t="s">
-        <v>238</v>
       </c>
       <c r="K70" t="s">
         <v>239</v>
@@ -6022,19 +6022,19 @@
         <v>233</v>
       </c>
       <c r="F71" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G71" t="s">
         <v>235</v>
       </c>
       <c r="H71" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="I71" t="s">
+        <v>237</v>
+      </c>
+      <c r="J71" t="s">
         <v>249</v>
-      </c>
-      <c r="J71" t="s">
-        <v>238</v>
       </c>
       <c r="K71" t="s">
         <v>239</v>
@@ -6092,19 +6092,19 @@
         <v>233</v>
       </c>
       <c r="F73" t="s">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="G73" t="s">
         <v>235</v>
       </c>
       <c r="H73" t="s">
-        <v>236</v>
+        <v>309</v>
       </c>
       <c r="I73" t="s">
+        <v>237</v>
+      </c>
+      <c r="J73" t="s">
         <v>310</v>
-      </c>
-      <c r="J73" t="s">
-        <v>238</v>
       </c>
       <c r="K73" t="s">
         <v>255</v>
@@ -6127,19 +6127,19 @@
         <v>233</v>
       </c>
       <c r="F74" t="s">
-        <v>314</v>
+        <v>234</v>
       </c>
       <c r="G74" t="s">
         <v>235</v>
       </c>
       <c r="H74" t="s">
-        <v>236</v>
+        <v>314</v>
       </c>
       <c r="I74" t="s">
+        <v>237</v>
+      </c>
+      <c r="J74" t="s">
         <v>315</v>
-      </c>
-      <c r="J74" t="s">
-        <v>238</v>
       </c>
       <c r="K74" t="s">
         <v>255</v>
@@ -6162,19 +6162,19 @@
         <v>233</v>
       </c>
       <c r="F75" t="s">
-        <v>319</v>
+        <v>234</v>
       </c>
       <c r="G75" t="s">
         <v>235</v>
       </c>
       <c r="H75" t="s">
-        <v>236</v>
+        <v>319</v>
       </c>
       <c r="I75" t="s">
+        <v>237</v>
+      </c>
+      <c r="J75" t="s">
         <v>320</v>
-      </c>
-      <c r="J75" t="s">
-        <v>238</v>
       </c>
       <c r="K75" t="s">
         <v>255</v>
@@ -6197,19 +6197,19 @@
         <v>233</v>
       </c>
       <c r="F76" t="s">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="G76" t="s">
         <v>235</v>
       </c>
       <c r="H76" t="s">
-        <v>236</v>
+        <v>309</v>
       </c>
       <c r="I76" t="s">
+        <v>237</v>
+      </c>
+      <c r="J76" t="s">
         <v>310</v>
-      </c>
-      <c r="J76" t="s">
-        <v>238</v>
       </c>
       <c r="K76" t="s">
         <v>255</v>
@@ -6232,19 +6232,19 @@
         <v>233</v>
       </c>
       <c r="F77" t="s">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="G77" t="s">
         <v>235</v>
       </c>
       <c r="H77" t="s">
-        <v>236</v>
+        <v>309</v>
       </c>
       <c r="I77" t="s">
+        <v>237</v>
+      </c>
+      <c r="J77" t="s">
         <v>310</v>
-      </c>
-      <c r="J77" t="s">
-        <v>238</v>
       </c>
       <c r="K77" t="s">
         <v>255</v>
@@ -6267,19 +6267,19 @@
         <v>233</v>
       </c>
       <c r="F78" t="s">
-        <v>314</v>
+        <v>234</v>
       </c>
       <c r="G78" t="s">
         <v>235</v>
       </c>
       <c r="H78" t="s">
-        <v>236</v>
+        <v>314</v>
       </c>
       <c r="I78" t="s">
+        <v>237</v>
+      </c>
+      <c r="J78" t="s">
         <v>315</v>
-      </c>
-      <c r="J78" t="s">
-        <v>238</v>
       </c>
       <c r="K78" t="s">
         <v>255</v>
@@ -6299,19 +6299,19 @@
         <v>233</v>
       </c>
       <c r="F79" t="s">
-        <v>332</v>
+        <v>234</v>
       </c>
       <c r="G79" t="s">
         <v>235</v>
       </c>
       <c r="H79" t="s">
-        <v>236</v>
+        <v>332</v>
       </c>
       <c r="I79" t="s">
+        <v>237</v>
+      </c>
+      <c r="J79" t="s">
         <v>333</v>
-      </c>
-      <c r="J79" t="s">
-        <v>238</v>
       </c>
       <c r="K79" t="s">
         <v>255</v>
@@ -6334,19 +6334,19 @@
         <v>233</v>
       </c>
       <c r="F80" t="s">
-        <v>337</v>
+        <v>234</v>
       </c>
       <c r="G80" t="s">
         <v>235</v>
       </c>
       <c r="H80" t="s">
-        <v>236</v>
+        <v>337</v>
       </c>
       <c r="I80" t="s">
+        <v>237</v>
+      </c>
+      <c r="J80" t="s">
         <v>338</v>
-      </c>
-      <c r="J80" t="s">
-        <v>238</v>
       </c>
       <c r="K80" t="s">
         <v>339</v>
@@ -6369,19 +6369,19 @@
         <v>233</v>
       </c>
       <c r="F81" t="s">
-        <v>337</v>
+        <v>234</v>
       </c>
       <c r="G81" t="s">
         <v>235</v>
       </c>
       <c r="H81" t="s">
-        <v>236</v>
+        <v>337</v>
       </c>
       <c r="I81" t="s">
+        <v>237</v>
+      </c>
+      <c r="J81" t="s">
         <v>338</v>
-      </c>
-      <c r="J81" t="s">
-        <v>238</v>
       </c>
       <c r="K81" t="s">
         <v>339</v>
@@ -6404,19 +6404,19 @@
         <v>233</v>
       </c>
       <c r="F82" t="s">
-        <v>337</v>
+        <v>234</v>
       </c>
       <c r="G82" t="s">
         <v>235</v>
       </c>
       <c r="H82" t="s">
-        <v>236</v>
+        <v>337</v>
       </c>
       <c r="I82" t="s">
+        <v>237</v>
+      </c>
+      <c r="J82" t="s">
         <v>338</v>
-      </c>
-      <c r="J82" t="s">
-        <v>238</v>
       </c>
       <c r="K82" t="s">
         <v>339</v>
@@ -6439,13 +6439,13 @@
         <v>233</v>
       </c>
       <c r="F83" t="s">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="G83" t="s">
         <v>235</v>
       </c>
       <c r="H83" t="s">
-        <v>236</v>
+        <v>296</v>
       </c>
       <c r="I83" t="s">
         <v>237</v>
@@ -6474,19 +6474,19 @@
         <v>233</v>
       </c>
       <c r="F84" t="s">
-        <v>352</v>
+        <v>234</v>
       </c>
       <c r="G84" t="s">
         <v>235</v>
       </c>
       <c r="H84" t="s">
-        <v>236</v>
+        <v>352</v>
       </c>
       <c r="I84" t="s">
+        <v>237</v>
+      </c>
+      <c r="J84" t="s">
         <v>353</v>
-      </c>
-      <c r="J84" t="s">
-        <v>238</v>
       </c>
       <c r="K84" t="s">
         <v>239</v>
@@ -6509,19 +6509,19 @@
         <v>233</v>
       </c>
       <c r="F85" t="s">
-        <v>357</v>
+        <v>234</v>
       </c>
       <c r="G85" t="s">
         <v>235</v>
       </c>
       <c r="H85" t="s">
-        <v>236</v>
+        <v>357</v>
       </c>
       <c r="I85" t="s">
+        <v>237</v>
+      </c>
+      <c r="J85" t="s">
         <v>244</v>
-      </c>
-      <c r="J85" t="s">
-        <v>238</v>
       </c>
       <c r="K85" t="s">
         <v>239</v>
@@ -6544,19 +6544,19 @@
         <v>233</v>
       </c>
       <c r="F86" t="s">
-        <v>361</v>
+        <v>234</v>
       </c>
       <c r="G86" t="s">
         <v>235</v>
       </c>
       <c r="H86" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="I86" t="s">
+        <v>237</v>
+      </c>
+      <c r="J86" t="s">
         <v>362</v>
-      </c>
-      <c r="J86" t="s">
-        <v>238</v>
       </c>
       <c r="K86" t="s">
         <v>339</v>
@@ -6579,19 +6579,19 @@
         <v>233</v>
       </c>
       <c r="F87" t="s">
-        <v>357</v>
+        <v>234</v>
       </c>
       <c r="G87" t="s">
         <v>235</v>
       </c>
       <c r="H87" t="s">
-        <v>236</v>
+        <v>357</v>
       </c>
       <c r="I87" t="s">
+        <v>237</v>
+      </c>
+      <c r="J87" t="s">
         <v>244</v>
-      </c>
-      <c r="J87" t="s">
-        <v>238</v>
       </c>
       <c r="K87" t="s">
         <v>239</v>
@@ -6611,19 +6611,19 @@
         <v>233</v>
       </c>
       <c r="F88" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G88" t="s">
         <v>235</v>
       </c>
       <c r="H88" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I88" t="s">
+        <v>237</v>
+      </c>
+      <c r="J88" t="s">
         <v>244</v>
-      </c>
-      <c r="J88" t="s">
-        <v>238</v>
       </c>
       <c r="K88" t="s">
         <v>239</v>
@@ -6646,19 +6646,19 @@
         <v>233</v>
       </c>
       <c r="F89" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G89" t="s">
         <v>235</v>
       </c>
       <c r="H89" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I89" t="s">
+        <v>237</v>
+      </c>
+      <c r="J89" t="s">
         <v>244</v>
-      </c>
-      <c r="J89" t="s">
-        <v>238</v>
       </c>
       <c r="K89" t="s">
         <v>239</v>
@@ -6681,19 +6681,19 @@
         <v>233</v>
       </c>
       <c r="F90" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="G90" t="s">
         <v>235</v>
       </c>
       <c r="H90" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="I90" t="s">
+        <v>237</v>
+      </c>
+      <c r="J90" t="s">
         <v>254</v>
-      </c>
-      <c r="J90" t="s">
-        <v>238</v>
       </c>
       <c r="K90" t="s">
         <v>255</v>
@@ -6716,19 +6716,19 @@
         <v>233</v>
       </c>
       <c r="F91" t="s">
-        <v>377</v>
+        <v>234</v>
       </c>
       <c r="G91" t="s">
         <v>235</v>
       </c>
       <c r="H91" t="s">
-        <v>236</v>
+        <v>377</v>
       </c>
       <c r="I91" t="s">
+        <v>237</v>
+      </c>
+      <c r="J91" t="s">
         <v>378</v>
-      </c>
-      <c r="J91" t="s">
-        <v>238</v>
       </c>
       <c r="K91" t="s">
         <v>379</v>
@@ -6751,19 +6751,19 @@
         <v>233</v>
       </c>
       <c r="F92" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="G92" t="s">
         <v>235</v>
       </c>
       <c r="H92" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="I92" t="s">
+        <v>237</v>
+      </c>
+      <c r="J92" t="s">
         <v>254</v>
-      </c>
-      <c r="J92" t="s">
-        <v>238</v>
       </c>
       <c r="K92" t="s">
         <v>255</v>
@@ -6786,19 +6786,19 @@
         <v>233</v>
       </c>
       <c r="F93" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="G93" t="s">
         <v>235</v>
       </c>
       <c r="H93" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="I93" t="s">
+        <v>237</v>
+      </c>
+      <c r="J93" t="s">
         <v>249</v>
-      </c>
-      <c r="J93" t="s">
-        <v>238</v>
       </c>
       <c r="K93" t="s">
         <v>239</v>
@@ -6821,19 +6821,19 @@
         <v>233</v>
       </c>
       <c r="F94" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="G94" t="s">
         <v>235</v>
       </c>
       <c r="H94" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="I94" t="s">
+        <v>237</v>
+      </c>
+      <c r="J94" t="s">
         <v>254</v>
-      </c>
-      <c r="J94" t="s">
-        <v>238</v>
       </c>
       <c r="K94" t="s">
         <v>255</v>
@@ -6856,19 +6856,19 @@
         <v>233</v>
       </c>
       <c r="F95" t="s">
-        <v>392</v>
+        <v>234</v>
       </c>
       <c r="G95" t="s">
         <v>235</v>
       </c>
       <c r="H95" t="s">
-        <v>236</v>
+        <v>392</v>
       </c>
       <c r="I95" t="s">
+        <v>237</v>
+      </c>
+      <c r="J95" t="s">
         <v>393</v>
-      </c>
-      <c r="J95" t="s">
-        <v>238</v>
       </c>
       <c r="K95" t="s">
         <v>239</v>
@@ -6891,19 +6891,19 @@
         <v>397</v>
       </c>
       <c r="F96" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="G96" t="s">
         <v>235</v>
       </c>
       <c r="H96" t="s">
+        <v>253</v>
+      </c>
+      <c r="I96" t="s">
         <v>398</v>
       </c>
-      <c r="I96" t="s">
+      <c r="J96" t="s">
         <v>254</v>
-      </c>
-      <c r="J96" t="s">
-        <v>238</v>
       </c>
       <c r="K96" t="s">
         <v>255</v>
@@ -6926,19 +6926,19 @@
         <v>397</v>
       </c>
       <c r="F97" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="G97" t="s">
         <v>235</v>
       </c>
       <c r="H97" t="s">
+        <v>253</v>
+      </c>
+      <c r="I97" t="s">
         <v>398</v>
       </c>
-      <c r="I97" t="s">
+      <c r="J97" t="s">
         <v>254</v>
-      </c>
-      <c r="J97" t="s">
-        <v>238</v>
       </c>
       <c r="K97" t="s">
         <v>255</v>
@@ -6961,19 +6961,19 @@
         <v>397</v>
       </c>
       <c r="F98" t="s">
-        <v>405</v>
+        <v>234</v>
       </c>
       <c r="G98" t="s">
         <v>235</v>
       </c>
       <c r="H98" t="s">
+        <v>405</v>
+      </c>
+      <c r="I98" t="s">
         <v>398</v>
       </c>
-      <c r="I98" t="s">
+      <c r="J98" t="s">
         <v>406</v>
-      </c>
-      <c r="J98" t="s">
-        <v>238</v>
       </c>
       <c r="K98" t="s">
         <v>407</v>
@@ -6996,19 +6996,19 @@
         <v>397</v>
       </c>
       <c r="F99" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="G99" t="s">
         <v>235</v>
       </c>
       <c r="H99" t="s">
+        <v>253</v>
+      </c>
+      <c r="I99" t="s">
         <v>398</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>254</v>
-      </c>
-      <c r="J99" t="s">
-        <v>238</v>
       </c>
       <c r="K99" t="s">
         <v>255</v>
@@ -7031,19 +7031,19 @@
         <v>397</v>
       </c>
       <c r="F100" t="s">
-        <v>319</v>
+        <v>234</v>
       </c>
       <c r="G100" t="s">
         <v>235</v>
       </c>
       <c r="H100" t="s">
+        <v>319</v>
+      </c>
+      <c r="I100" t="s">
         <v>398</v>
       </c>
-      <c r="I100" t="s">
+      <c r="J100" t="s">
         <v>320</v>
-      </c>
-      <c r="J100" t="s">
-        <v>238</v>
       </c>
       <c r="K100" t="s">
         <v>255</v>
@@ -7066,19 +7066,19 @@
         <v>397</v>
       </c>
       <c r="F101" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="G101" t="s">
         <v>235</v>
       </c>
       <c r="H101" t="s">
+        <v>253</v>
+      </c>
+      <c r="I101" t="s">
         <v>398</v>
       </c>
-      <c r="I101" t="s">
+      <c r="J101" t="s">
         <v>254</v>
-      </c>
-      <c r="J101" t="s">
-        <v>238</v>
       </c>
       <c r="K101" t="s">
         <v>255</v>
@@ -7103,7 +7103,7 @@
       <c r="G102" t="s">
         <v>421</v>
       </c>
-      <c r="I102" t="s">
+      <c r="H102" t="s">
         <v>422</v>
       </c>
       <c r="J102" t="s">
@@ -7132,7 +7132,7 @@
       <c r="G103" t="s">
         <v>421</v>
       </c>
-      <c r="I103" t="s">
+      <c r="H103" t="s">
         <v>422</v>
       </c>
       <c r="J103" t="s">
@@ -7161,7 +7161,7 @@
       <c r="G104" t="s">
         <v>421</v>
       </c>
-      <c r="I104" t="s">
+      <c r="H104" t="s">
         <v>422</v>
       </c>
       <c r="J104" t="s">
@@ -7185,16 +7185,16 @@
         <v>14</v>
       </c>
       <c r="F105" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="G105" t="s">
         <v>421</v>
       </c>
-      <c r="I105" t="s">
+      <c r="H105" t="s">
+        <v>433</v>
+      </c>
+      <c r="J105" t="s">
         <v>434</v>
-      </c>
-      <c r="J105" t="s">
-        <v>423</v>
       </c>
       <c r="K105" t="s">
         <v>379</v>
@@ -7219,7 +7219,7 @@
       <c r="G106" t="s">
         <v>421</v>
       </c>
-      <c r="I106" t="s">
+      <c r="H106" t="s">
         <v>422</v>
       </c>
       <c r="J106" t="s">
@@ -7243,16 +7243,16 @@
         <v>14</v>
       </c>
       <c r="F107" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="G107" t="s">
         <v>421</v>
       </c>
-      <c r="I107" t="s">
+      <c r="H107" t="s">
+        <v>377</v>
+      </c>
+      <c r="J107" t="s">
         <v>378</v>
-      </c>
-      <c r="J107" t="s">
-        <v>423</v>
       </c>
       <c r="K107" t="s">
         <v>379</v>
@@ -7272,16 +7272,16 @@
         <v>14</v>
       </c>
       <c r="F108" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="G108" t="s">
         <v>421</v>
       </c>
-      <c r="I108" t="s">
+      <c r="H108" t="s">
+        <v>444</v>
+      </c>
+      <c r="J108" t="s">
         <v>445</v>
-      </c>
-      <c r="J108" t="s">
-        <v>423</v>
       </c>
       <c r="K108" t="s">
         <v>379</v>
@@ -7301,16 +7301,16 @@
         <v>14</v>
       </c>
       <c r="F109" t="s">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="G109" t="s">
         <v>421</v>
       </c>
-      <c r="I109" t="s">
+      <c r="H109" t="s">
+        <v>449</v>
+      </c>
+      <c r="J109" t="s">
         <v>450</v>
-      </c>
-      <c r="J109" t="s">
-        <v>423</v>
       </c>
       <c r="K109" t="s">
         <v>192</v>
@@ -7330,16 +7330,16 @@
         <v>14</v>
       </c>
       <c r="F110" t="s">
-        <v>454</v>
+        <v>420</v>
       </c>
       <c r="G110" t="s">
         <v>421</v>
       </c>
-      <c r="I110" t="s">
+      <c r="H110" t="s">
+        <v>454</v>
+      </c>
+      <c r="J110" t="s">
         <v>455</v>
-      </c>
-      <c r="J110" t="s">
-        <v>423</v>
       </c>
       <c r="K110" t="s">
         <v>192</v>
@@ -7364,7 +7364,7 @@
       <c r="G111" t="s">
         <v>421</v>
       </c>
-      <c r="I111" t="s">
+      <c r="H111" t="s">
         <v>422</v>
       </c>
       <c r="J111" t="s">
@@ -7388,16 +7388,16 @@
         <v>14</v>
       </c>
       <c r="F112" t="s">
-        <v>462</v>
+        <v>420</v>
       </c>
       <c r="G112" t="s">
         <v>421</v>
       </c>
-      <c r="I112" t="s">
+      <c r="H112" t="s">
+        <v>462</v>
+      </c>
+      <c r="J112" t="s">
         <v>463</v>
-      </c>
-      <c r="J112" t="s">
-        <v>423</v>
       </c>
       <c r="K112" t="s">
         <v>464</v>
@@ -7417,16 +7417,16 @@
         <v>14</v>
       </c>
       <c r="F113" t="s">
-        <v>296</v>
+        <v>420</v>
       </c>
       <c r="G113" t="s">
         <v>421</v>
       </c>
-      <c r="I113" t="s">
-        <v>237</v>
+      <c r="H113" t="s">
+        <v>296</v>
       </c>
       <c r="J113" t="s">
-        <v>423</v>
+        <v>238</v>
       </c>
       <c r="K113" t="s">
         <v>239</v>
@@ -7446,16 +7446,16 @@
         <v>14</v>
       </c>
       <c r="F114" t="s">
-        <v>314</v>
+        <v>420</v>
       </c>
       <c r="G114" t="s">
         <v>421</v>
       </c>
-      <c r="I114" t="s">
+      <c r="H114" t="s">
+        <v>314</v>
+      </c>
+      <c r="J114" t="s">
         <v>315</v>
-      </c>
-      <c r="J114" t="s">
-        <v>423</v>
       </c>
       <c r="K114" t="s">
         <v>255</v>
@@ -7475,16 +7475,16 @@
         <v>14</v>
       </c>
       <c r="F115" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="G115" t="s">
         <v>421</v>
       </c>
-      <c r="I115" t="s">
+      <c r="H115" t="s">
+        <v>377</v>
+      </c>
+      <c r="J115" t="s">
         <v>378</v>
-      </c>
-      <c r="J115" t="s">
-        <v>423</v>
       </c>
       <c r="K115" t="s">
         <v>379</v>
@@ -7501,16 +7501,16 @@
         <v>14</v>
       </c>
       <c r="F116" t="s">
-        <v>476</v>
+        <v>420</v>
       </c>
       <c r="G116" t="s">
         <v>421</v>
       </c>
-      <c r="I116" t="s">
+      <c r="H116" t="s">
+        <v>476</v>
+      </c>
+      <c r="J116" t="s">
         <v>477</v>
-      </c>
-      <c r="J116" t="s">
-        <v>423</v>
       </c>
       <c r="K116" t="s">
         <v>464</v>
@@ -7527,16 +7527,16 @@
         <v>14</v>
       </c>
       <c r="F117" t="s">
-        <v>462</v>
+        <v>420</v>
       </c>
       <c r="G117" t="s">
         <v>421</v>
       </c>
-      <c r="I117" t="s">
+      <c r="H117" t="s">
+        <v>462</v>
+      </c>
+      <c r="J117" t="s">
         <v>463</v>
-      </c>
-      <c r="J117" t="s">
-        <v>423</v>
       </c>
       <c r="K117" t="s">
         <v>464</v>
@@ -7556,16 +7556,16 @@
         <v>14</v>
       </c>
       <c r="F118" t="s">
-        <v>483</v>
+        <v>420</v>
       </c>
       <c r="G118" t="s">
         <v>421</v>
       </c>
-      <c r="I118" t="s">
+      <c r="H118" t="s">
+        <v>483</v>
+      </c>
+      <c r="J118" t="s">
         <v>338</v>
-      </c>
-      <c r="J118" t="s">
-        <v>423</v>
       </c>
       <c r="K118" t="s">
         <v>339</v>
@@ -7585,16 +7585,16 @@
         <v>14</v>
       </c>
       <c r="F119" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="G119" t="s">
         <v>421</v>
       </c>
-      <c r="I119" t="s">
+      <c r="H119" t="s">
+        <v>377</v>
+      </c>
+      <c r="J119" t="s">
         <v>378</v>
-      </c>
-      <c r="J119" t="s">
-        <v>423</v>
       </c>
       <c r="K119" t="s">
         <v>379</v>
@@ -7614,16 +7614,16 @@
         <v>14</v>
       </c>
       <c r="F120" t="s">
+        <v>490</v>
+      </c>
+      <c r="G120" t="s">
+        <v>491</v>
+      </c>
+      <c r="H120" t="s">
         <v>352</v>
       </c>
-      <c r="G120" t="s">
-        <v>490</v>
-      </c>
-      <c r="I120" t="s">
+      <c r="J120" t="s">
         <v>353</v>
-      </c>
-      <c r="J120" t="s">
-        <v>491</v>
       </c>
       <c r="K120" t="s">
         <v>239</v>
@@ -7643,16 +7643,16 @@
         <v>14</v>
       </c>
       <c r="F121" t="s">
+        <v>490</v>
+      </c>
+      <c r="G121" t="s">
+        <v>491</v>
+      </c>
+      <c r="H121" t="s">
         <v>296</v>
       </c>
-      <c r="G121" t="s">
-        <v>490</v>
-      </c>
-      <c r="I121" t="s">
-        <v>237</v>
-      </c>
       <c r="J121" t="s">
-        <v>491</v>
+        <v>238</v>
       </c>
       <c r="K121" t="s">
         <v>239</v>
@@ -7672,16 +7672,16 @@
         <v>14</v>
       </c>
       <c r="F122" t="s">
+        <v>490</v>
+      </c>
+      <c r="G122" t="s">
+        <v>491</v>
+      </c>
+      <c r="H122" t="s">
         <v>352</v>
       </c>
-      <c r="G122" t="s">
-        <v>490</v>
-      </c>
-      <c r="I122" t="s">
+      <c r="J122" t="s">
         <v>353</v>
-      </c>
-      <c r="J122" t="s">
-        <v>491</v>
       </c>
       <c r="K122" t="s">
         <v>239</v>
@@ -7701,16 +7701,16 @@
         <v>14</v>
       </c>
       <c r="F123" t="s">
+        <v>490</v>
+      </c>
+      <c r="G123" t="s">
+        <v>491</v>
+      </c>
+      <c r="H123" t="s">
         <v>352</v>
       </c>
-      <c r="G123" t="s">
-        <v>490</v>
-      </c>
-      <c r="I123" t="s">
+      <c r="J123" t="s">
         <v>353</v>
-      </c>
-      <c r="J123" t="s">
-        <v>491</v>
       </c>
       <c r="K123" t="s">
         <v>239</v>
@@ -7730,16 +7730,16 @@
         <v>14</v>
       </c>
       <c r="F124" t="s">
+        <v>490</v>
+      </c>
+      <c r="G124" t="s">
+        <v>491</v>
+      </c>
+      <c r="H124" t="s">
         <v>504</v>
       </c>
-      <c r="G124" t="s">
-        <v>490</v>
-      </c>
-      <c r="I124" t="s">
+      <c r="J124" t="s">
         <v>505</v>
-      </c>
-      <c r="J124" t="s">
-        <v>491</v>
       </c>
       <c r="K124" t="s">
         <v>339</v>
@@ -7759,16 +7759,16 @@
         <v>14</v>
       </c>
       <c r="F125" t="s">
+        <v>490</v>
+      </c>
+      <c r="G125" t="s">
+        <v>491</v>
+      </c>
+      <c r="H125" t="s">
         <v>504</v>
       </c>
-      <c r="G125" t="s">
-        <v>490</v>
-      </c>
-      <c r="I125" t="s">
+      <c r="J125" t="s">
         <v>505</v>
-      </c>
-      <c r="J125" t="s">
-        <v>491</v>
       </c>
       <c r="K125" t="s">
         <v>339</v>
@@ -7788,16 +7788,16 @@
         <v>14</v>
       </c>
       <c r="F126" t="s">
+        <v>490</v>
+      </c>
+      <c r="G126" t="s">
+        <v>491</v>
+      </c>
+      <c r="H126" t="s">
         <v>504</v>
       </c>
-      <c r="G126" t="s">
-        <v>490</v>
-      </c>
-      <c r="I126" t="s">
+      <c r="J126" t="s">
         <v>505</v>
-      </c>
-      <c r="J126" t="s">
-        <v>491</v>
       </c>
       <c r="K126" t="s">
         <v>339</v>
@@ -7817,16 +7817,16 @@
         <v>14</v>
       </c>
       <c r="F127" t="s">
+        <v>490</v>
+      </c>
+      <c r="G127" t="s">
+        <v>491</v>
+      </c>
+      <c r="H127" t="s">
         <v>504</v>
       </c>
-      <c r="G127" t="s">
-        <v>490</v>
-      </c>
-      <c r="I127" t="s">
+      <c r="J127" t="s">
         <v>505</v>
-      </c>
-      <c r="J127" t="s">
-        <v>491</v>
       </c>
       <c r="K127" t="s">
         <v>339</v>
@@ -7846,16 +7846,16 @@
         <v>14</v>
       </c>
       <c r="F128" t="s">
+        <v>490</v>
+      </c>
+      <c r="G128" t="s">
+        <v>491</v>
+      </c>
+      <c r="H128" t="s">
         <v>504</v>
       </c>
-      <c r="G128" t="s">
-        <v>490</v>
-      </c>
-      <c r="I128" t="s">
+      <c r="J128" t="s">
         <v>505</v>
-      </c>
-      <c r="J128" t="s">
-        <v>491</v>
       </c>
       <c r="K128" t="s">
         <v>339</v>
@@ -7875,16 +7875,16 @@
         <v>14</v>
       </c>
       <c r="F129" t="s">
+        <v>490</v>
+      </c>
+      <c r="G129" t="s">
+        <v>491</v>
+      </c>
+      <c r="H129" t="s">
         <v>521</v>
       </c>
-      <c r="G129" t="s">
-        <v>490</v>
-      </c>
-      <c r="I129" t="s">
+      <c r="J129" t="s">
         <v>505</v>
-      </c>
-      <c r="J129" t="s">
-        <v>491</v>
       </c>
       <c r="K129" t="s">
         <v>339</v>
@@ -7904,16 +7904,16 @@
         <v>14</v>
       </c>
       <c r="F130" t="s">
+        <v>490</v>
+      </c>
+      <c r="G130" t="s">
+        <v>491</v>
+      </c>
+      <c r="H130" t="s">
         <v>525</v>
       </c>
-      <c r="G130" t="s">
-        <v>490</v>
-      </c>
-      <c r="I130" t="s">
+      <c r="J130" t="s">
         <v>505</v>
-      </c>
-      <c r="J130" t="s">
-        <v>491</v>
       </c>
       <c r="K130" t="s">
         <v>339</v>
@@ -7933,16 +7933,16 @@
         <v>14</v>
       </c>
       <c r="F131" t="s">
+        <v>490</v>
+      </c>
+      <c r="G131" t="s">
+        <v>491</v>
+      </c>
+      <c r="H131" t="s">
         <v>529</v>
       </c>
-      <c r="G131" t="s">
-        <v>490</v>
-      </c>
-      <c r="I131" t="s">
+      <c r="J131" t="s">
         <v>505</v>
-      </c>
-      <c r="J131" t="s">
-        <v>491</v>
       </c>
       <c r="K131" t="s">
         <v>339</v>
@@ -7962,16 +7962,16 @@
         <v>14</v>
       </c>
       <c r="F132" t="s">
+        <v>490</v>
+      </c>
+      <c r="G132" t="s">
+        <v>491</v>
+      </c>
+      <c r="H132" t="s">
         <v>533</v>
       </c>
-      <c r="G132" t="s">
-        <v>490</v>
-      </c>
-      <c r="I132" t="s">
+      <c r="J132" t="s">
         <v>534</v>
-      </c>
-      <c r="J132" t="s">
-        <v>491</v>
       </c>
       <c r="K132" t="s">
         <v>339</v>
@@ -7988,16 +7988,16 @@
         <v>14</v>
       </c>
       <c r="F133" t="s">
+        <v>490</v>
+      </c>
+      <c r="G133" t="s">
+        <v>491</v>
+      </c>
+      <c r="H133" t="s">
         <v>392</v>
       </c>
-      <c r="G133" t="s">
-        <v>490</v>
-      </c>
-      <c r="I133" t="s">
+      <c r="J133" t="s">
         <v>393</v>
-      </c>
-      <c r="J133" t="s">
-        <v>491</v>
       </c>
       <c r="K133" t="s">
         <v>239</v>
@@ -8017,16 +8017,16 @@
         <v>14</v>
       </c>
       <c r="F134" t="s">
+        <v>540</v>
+      </c>
+      <c r="G134" t="s">
+        <v>541</v>
+      </c>
+      <c r="H134" t="s">
         <v>361</v>
       </c>
-      <c r="G134" t="s">
-        <v>540</v>
-      </c>
-      <c r="I134" t="s">
+      <c r="J134" t="s">
         <v>362</v>
-      </c>
-      <c r="J134" t="s">
-        <v>541</v>
       </c>
       <c r="K134" t="s">
         <v>339</v>
@@ -8043,16 +8043,16 @@
         <v>14</v>
       </c>
       <c r="F135" t="s">
+        <v>540</v>
+      </c>
+      <c r="G135" t="s">
+        <v>541</v>
+      </c>
+      <c r="H135" t="s">
         <v>361</v>
       </c>
-      <c r="G135" t="s">
-        <v>540</v>
-      </c>
-      <c r="I135" t="s">
+      <c r="J135" t="s">
         <v>362</v>
-      </c>
-      <c r="J135" t="s">
-        <v>541</v>
       </c>
       <c r="K135" t="s">
         <v>339</v>
@@ -8072,16 +8072,16 @@
         <v>14</v>
       </c>
       <c r="F136" t="s">
+        <v>540</v>
+      </c>
+      <c r="G136" t="s">
+        <v>541</v>
+      </c>
+      <c r="H136" t="s">
         <v>361</v>
       </c>
-      <c r="G136" t="s">
-        <v>540</v>
-      </c>
-      <c r="I136" t="s">
+      <c r="J136" t="s">
         <v>362</v>
-      </c>
-      <c r="J136" t="s">
-        <v>541</v>
       </c>
       <c r="K136" t="s">
         <v>339</v>
@@ -8101,16 +8101,16 @@
         <v>14</v>
       </c>
       <c r="F137" t="s">
+        <v>540</v>
+      </c>
+      <c r="G137" t="s">
+        <v>541</v>
+      </c>
+      <c r="H137" t="s">
         <v>361</v>
       </c>
-      <c r="G137" t="s">
-        <v>540</v>
-      </c>
-      <c r="I137" t="s">
+      <c r="J137" t="s">
         <v>362</v>
-      </c>
-      <c r="J137" t="s">
-        <v>541</v>
       </c>
       <c r="K137" t="s">
         <v>339</v>
@@ -8130,16 +8130,16 @@
         <v>14</v>
       </c>
       <c r="F138" t="s">
+        <v>540</v>
+      </c>
+      <c r="G138" t="s">
+        <v>541</v>
+      </c>
+      <c r="H138" t="s">
         <v>361</v>
       </c>
-      <c r="G138" t="s">
-        <v>540</v>
-      </c>
-      <c r="I138" t="s">
+      <c r="J138" t="s">
         <v>362</v>
-      </c>
-      <c r="J138" t="s">
-        <v>541</v>
       </c>
       <c r="K138" t="s">
         <v>339</v>
@@ -8159,16 +8159,16 @@
         <v>14</v>
       </c>
       <c r="F139" t="s">
+        <v>540</v>
+      </c>
+      <c r="G139" t="s">
+        <v>541</v>
+      </c>
+      <c r="H139" t="s">
         <v>556</v>
       </c>
-      <c r="G139" t="s">
-        <v>540</v>
-      </c>
-      <c r="I139" t="s">
+      <c r="J139" t="s">
         <v>557</v>
-      </c>
-      <c r="J139" t="s">
-        <v>541</v>
       </c>
       <c r="K139" t="s">
         <v>464</v>
@@ -8188,16 +8188,16 @@
         <v>14</v>
       </c>
       <c r="F140" t="s">
+        <v>540</v>
+      </c>
+      <c r="G140" t="s">
+        <v>541</v>
+      </c>
+      <c r="H140" t="s">
         <v>361</v>
       </c>
-      <c r="G140" t="s">
-        <v>540</v>
-      </c>
-      <c r="I140" t="s">
+      <c r="J140" t="s">
         <v>362</v>
-      </c>
-      <c r="J140" t="s">
-        <v>541</v>
       </c>
       <c r="K140" t="s">
         <v>339</v>
@@ -8287,19 +8287,19 @@
         <v>564</v>
       </c>
       <c r="F143" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="G143" t="s">
         <v>566</v>
       </c>
       <c r="H143" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="I143" t="s">
+        <v>568</v>
+      </c>
+      <c r="J143" t="s">
         <v>576</v>
-      </c>
-      <c r="J143" t="s">
-        <v>569</v>
       </c>
       <c r="K143" t="s">
         <v>339</v>
@@ -8322,19 +8322,19 @@
         <v>564</v>
       </c>
       <c r="F144" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="G144" t="s">
         <v>566</v>
       </c>
       <c r="H144" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="I144" t="s">
+        <v>568</v>
+      </c>
+      <c r="J144" t="s">
         <v>576</v>
-      </c>
-      <c r="J144" t="s">
-        <v>569</v>
       </c>
       <c r="K144" t="s">
         <v>339</v>
@@ -8357,19 +8357,19 @@
         <v>564</v>
       </c>
       <c r="F145" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="G145" t="s">
         <v>566</v>
       </c>
       <c r="H145" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="I145" t="s">
+        <v>568</v>
+      </c>
+      <c r="J145" t="s">
         <v>576</v>
-      </c>
-      <c r="J145" t="s">
-        <v>569</v>
       </c>
       <c r="K145" t="s">
         <v>339</v>
@@ -8433,10 +8433,10 @@
         <v>566</v>
       </c>
       <c r="H147" t="s">
+        <v>567</v>
+      </c>
+      <c r="I147" t="s">
         <v>590</v>
-      </c>
-      <c r="I147" t="s">
-        <v>568</v>
       </c>
       <c r="J147" t="s">
         <v>569</v>
@@ -8468,10 +8468,10 @@
         <v>566</v>
       </c>
       <c r="H148" t="s">
+        <v>567</v>
+      </c>
+      <c r="I148" t="s">
         <v>590</v>
-      </c>
-      <c r="I148" t="s">
-        <v>568</v>
       </c>
       <c r="J148" t="s">
         <v>569</v>
@@ -8503,10 +8503,10 @@
         <v>566</v>
       </c>
       <c r="H149" t="s">
+        <v>567</v>
+      </c>
+      <c r="I149" t="s">
         <v>590</v>
-      </c>
-      <c r="I149" t="s">
-        <v>568</v>
       </c>
       <c r="J149" t="s">
         <v>569</v>
@@ -8538,10 +8538,10 @@
         <v>566</v>
       </c>
       <c r="H150" t="s">
+        <v>567</v>
+      </c>
+      <c r="I150" t="s">
         <v>590</v>
-      </c>
-      <c r="I150" t="s">
-        <v>568</v>
       </c>
       <c r="J150" t="s">
         <v>569</v>
@@ -8573,10 +8573,10 @@
         <v>566</v>
       </c>
       <c r="H151" t="s">
+        <v>567</v>
+      </c>
+      <c r="I151" t="s">
         <v>590</v>
-      </c>
-      <c r="I151" t="s">
-        <v>568</v>
       </c>
       <c r="J151" t="s">
         <v>569</v>
@@ -8608,10 +8608,10 @@
         <v>566</v>
       </c>
       <c r="H152" t="s">
+        <v>567</v>
+      </c>
+      <c r="I152" t="s">
         <v>590</v>
-      </c>
-      <c r="I152" t="s">
-        <v>568</v>
       </c>
       <c r="J152" t="s">
         <v>569</v>
@@ -8643,10 +8643,10 @@
         <v>566</v>
       </c>
       <c r="H153" t="s">
+        <v>567</v>
+      </c>
+      <c r="I153" t="s">
         <v>590</v>
-      </c>
-      <c r="I153" t="s">
-        <v>568</v>
       </c>
       <c r="J153" t="s">
         <v>569</v>
@@ -8678,10 +8678,10 @@
         <v>566</v>
       </c>
       <c r="H154" t="s">
+        <v>567</v>
+      </c>
+      <c r="I154" t="s">
         <v>590</v>
-      </c>
-      <c r="I154" t="s">
-        <v>568</v>
       </c>
       <c r="J154" t="s">
         <v>569</v>
@@ -8713,10 +8713,10 @@
         <v>566</v>
       </c>
       <c r="H155" t="s">
+        <v>567</v>
+      </c>
+      <c r="I155" t="s">
         <v>590</v>
-      </c>
-      <c r="I155" t="s">
-        <v>568</v>
       </c>
       <c r="J155" t="s">
         <v>569</v>
@@ -8748,10 +8748,10 @@
         <v>566</v>
       </c>
       <c r="H156" t="s">
+        <v>567</v>
+      </c>
+      <c r="I156" t="s">
         <v>619</v>
-      </c>
-      <c r="I156" t="s">
-        <v>568</v>
       </c>
       <c r="J156" t="s">
         <v>569</v>
@@ -8777,16 +8777,16 @@
         <v>618</v>
       </c>
       <c r="F157" t="s">
-        <v>623</v>
+        <v>565</v>
       </c>
       <c r="G157" t="s">
         <v>566</v>
       </c>
       <c r="H157" t="s">
+        <v>623</v>
+      </c>
+      <c r="I157" t="s">
         <v>619</v>
-      </c>
-      <c r="I157" t="s">
-        <v>568</v>
       </c>
       <c r="J157" t="s">
         <v>569</v>
@@ -8818,10 +8818,10 @@
         <v>566</v>
       </c>
       <c r="H158" t="s">
+        <v>567</v>
+      </c>
+      <c r="I158" t="s">
         <v>619</v>
-      </c>
-      <c r="I158" t="s">
-        <v>568</v>
       </c>
       <c r="J158" t="s">
         <v>569</v>
@@ -8853,10 +8853,10 @@
         <v>566</v>
       </c>
       <c r="H159" t="s">
+        <v>567</v>
+      </c>
+      <c r="I159" t="s">
         <v>619</v>
-      </c>
-      <c r="I159" t="s">
-        <v>568</v>
       </c>
       <c r="J159" t="s">
         <v>569</v>
@@ -8888,10 +8888,10 @@
         <v>566</v>
       </c>
       <c r="H160" t="s">
+        <v>567</v>
+      </c>
+      <c r="I160" t="s">
         <v>619</v>
-      </c>
-      <c r="I160" t="s">
-        <v>568</v>
       </c>
       <c r="J160" t="s">
         <v>569</v>
@@ -8923,10 +8923,10 @@
         <v>566</v>
       </c>
       <c r="H161" t="s">
+        <v>567</v>
+      </c>
+      <c r="I161" t="s">
         <v>619</v>
-      </c>
-      <c r="I161" t="s">
-        <v>568</v>
       </c>
       <c r="J161" t="s">
         <v>569</v>
@@ -8958,10 +8958,10 @@
         <v>566</v>
       </c>
       <c r="H162" t="s">
+        <v>567</v>
+      </c>
+      <c r="I162" t="s">
         <v>640</v>
-      </c>
-      <c r="I162" t="s">
-        <v>568</v>
       </c>
       <c r="J162" t="s">
         <v>569</v>
@@ -8984,10 +8984,10 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F163" t="s">
-        <v>644</v>
+        <v>565</v>
       </c>
       <c r="G163" t="s">
         <v>566</v>
@@ -8996,7 +8996,7 @@
         <v>645</v>
       </c>
       <c r="I163" t="s">
-        <v>568</v>
+        <v>642</v>
       </c>
       <c r="J163" t="s">
         <v>569</v>
@@ -9028,10 +9028,10 @@
         <v>566</v>
       </c>
       <c r="H164" t="s">
+        <v>567</v>
+      </c>
+      <c r="I164" t="s">
         <v>650</v>
-      </c>
-      <c r="I164" t="s">
-        <v>568</v>
       </c>
       <c r="J164" t="s">
         <v>569</v>
@@ -9063,10 +9063,10 @@
         <v>566</v>
       </c>
       <c r="H165" t="s">
+        <v>567</v>
+      </c>
+      <c r="I165" t="s">
         <v>650</v>
-      </c>
-      <c r="I165" t="s">
-        <v>568</v>
       </c>
       <c r="J165" t="s">
         <v>569</v>
@@ -9098,10 +9098,10 @@
         <v>566</v>
       </c>
       <c r="H166" t="s">
+        <v>567</v>
+      </c>
+      <c r="I166" t="s">
         <v>650</v>
-      </c>
-      <c r="I166" t="s">
-        <v>568</v>
       </c>
       <c r="J166" t="s">
         <v>569</v>
@@ -9133,10 +9133,10 @@
         <v>566</v>
       </c>
       <c r="H167" t="s">
+        <v>567</v>
+      </c>
+      <c r="I167" t="s">
         <v>650</v>
-      </c>
-      <c r="I167" t="s">
-        <v>568</v>
       </c>
       <c r="J167" t="s">
         <v>569</v>
@@ -9162,16 +9162,16 @@
         <v>649</v>
       </c>
       <c r="F168" t="s">
-        <v>663</v>
+        <v>565</v>
       </c>
       <c r="G168" t="s">
         <v>566</v>
       </c>
       <c r="H168" t="s">
+        <v>663</v>
+      </c>
+      <c r="I168" t="s">
         <v>650</v>
-      </c>
-      <c r="I168" t="s">
-        <v>568</v>
       </c>
       <c r="J168" t="s">
         <v>569</v>
@@ -9194,16 +9194,16 @@
         <v>649</v>
       </c>
       <c r="F169" t="s">
-        <v>663</v>
+        <v>565</v>
       </c>
       <c r="G169" t="s">
         <v>566</v>
       </c>
       <c r="H169" t="s">
+        <v>663</v>
+      </c>
+      <c r="I169" t="s">
         <v>650</v>
-      </c>
-      <c r="I169" t="s">
-        <v>568</v>
       </c>
       <c r="J169" t="s">
         <v>569</v>
@@ -9235,10 +9235,10 @@
         <v>566</v>
       </c>
       <c r="H170" t="s">
+        <v>567</v>
+      </c>
+      <c r="I170" t="s">
         <v>650</v>
-      </c>
-      <c r="I170" t="s">
-        <v>568</v>
       </c>
       <c r="J170" t="s">
         <v>569</v>
@@ -9261,16 +9261,16 @@
         <v>14</v>
       </c>
       <c r="F171" t="s">
+        <v>672</v>
+      </c>
+      <c r="G171" t="s">
+        <v>673</v>
+      </c>
+      <c r="H171" t="s">
         <v>337</v>
       </c>
-      <c r="G171" t="s">
-        <v>672</v>
-      </c>
-      <c r="I171" t="s">
+      <c r="J171" t="s">
         <v>338</v>
-      </c>
-      <c r="J171" t="s">
-        <v>673</v>
       </c>
       <c r="K171" t="s">
         <v>339</v>
@@ -9290,16 +9290,16 @@
         <v>14</v>
       </c>
       <c r="F172" t="s">
+        <v>672</v>
+      </c>
+      <c r="G172" t="s">
+        <v>673</v>
+      </c>
+      <c r="H172" t="s">
         <v>243</v>
       </c>
-      <c r="G172" t="s">
-        <v>672</v>
-      </c>
-      <c r="I172" t="s">
+      <c r="J172" t="s">
         <v>244</v>
-      </c>
-      <c r="J172" t="s">
-        <v>673</v>
       </c>
       <c r="K172" t="s">
         <v>239</v>
@@ -9319,16 +9319,16 @@
         <v>14</v>
       </c>
       <c r="F173" t="s">
+        <v>672</v>
+      </c>
+      <c r="G173" t="s">
+        <v>673</v>
+      </c>
+      <c r="H173" t="s">
         <v>337</v>
       </c>
-      <c r="G173" t="s">
-        <v>672</v>
-      </c>
-      <c r="I173" t="s">
+      <c r="J173" t="s">
         <v>338</v>
-      </c>
-      <c r="J173" t="s">
-        <v>673</v>
       </c>
       <c r="K173" t="s">
         <v>339</v>
@@ -9348,16 +9348,16 @@
         <v>14</v>
       </c>
       <c r="F174" t="s">
+        <v>672</v>
+      </c>
+      <c r="G174" t="s">
+        <v>673</v>
+      </c>
+      <c r="H174" t="s">
         <v>337</v>
       </c>
-      <c r="G174" t="s">
-        <v>672</v>
-      </c>
-      <c r="I174" t="s">
+      <c r="J174" t="s">
         <v>338</v>
-      </c>
-      <c r="J174" t="s">
-        <v>673</v>
       </c>
       <c r="K174" t="s">
         <v>339</v>
@@ -9377,16 +9377,16 @@
         <v>14</v>
       </c>
       <c r="F175" t="s">
+        <v>672</v>
+      </c>
+      <c r="G175" t="s">
+        <v>673</v>
+      </c>
+      <c r="H175" t="s">
         <v>337</v>
       </c>
-      <c r="G175" t="s">
-        <v>672</v>
-      </c>
-      <c r="I175" t="s">
+      <c r="J175" t="s">
         <v>338</v>
-      </c>
-      <c r="J175" t="s">
-        <v>673</v>
       </c>
       <c r="K175" t="s">
         <v>339</v>
@@ -9403,16 +9403,16 @@
         <v>14</v>
       </c>
       <c r="F176" t="s">
+        <v>672</v>
+      </c>
+      <c r="G176" t="s">
+        <v>673</v>
+      </c>
+      <c r="H176" t="s">
         <v>337</v>
       </c>
-      <c r="G176" t="s">
-        <v>672</v>
-      </c>
-      <c r="I176" t="s">
+      <c r="J176" t="s">
         <v>338</v>
-      </c>
-      <c r="J176" t="s">
-        <v>673</v>
       </c>
       <c r="K176" t="s">
         <v>339</v>
@@ -9432,16 +9432,16 @@
         <v>14</v>
       </c>
       <c r="F177" t="s">
+        <v>691</v>
+      </c>
+      <c r="G177" t="s">
+        <v>692</v>
+      </c>
+      <c r="H177" t="s">
         <v>337</v>
       </c>
-      <c r="G177" t="s">
-        <v>691</v>
-      </c>
-      <c r="I177" t="s">
+      <c r="J177" t="s">
         <v>338</v>
-      </c>
-      <c r="J177" t="s">
-        <v>692</v>
       </c>
       <c r="K177" t="s">
         <v>339</v>
@@ -9461,16 +9461,16 @@
         <v>14</v>
       </c>
       <c r="F178" t="s">
+        <v>691</v>
+      </c>
+      <c r="G178" t="s">
+        <v>692</v>
+      </c>
+      <c r="H178" t="s">
         <v>337</v>
       </c>
-      <c r="G178" t="s">
-        <v>691</v>
-      </c>
-      <c r="I178" t="s">
+      <c r="J178" t="s">
         <v>338</v>
-      </c>
-      <c r="J178" t="s">
-        <v>692</v>
       </c>
       <c r="K178" t="s">
         <v>339</v>
@@ -9490,16 +9490,16 @@
         <v>14</v>
       </c>
       <c r="F179" t="s">
+        <v>691</v>
+      </c>
+      <c r="G179" t="s">
+        <v>692</v>
+      </c>
+      <c r="H179" t="s">
         <v>337</v>
       </c>
-      <c r="G179" t="s">
-        <v>691</v>
-      </c>
-      <c r="I179" t="s">
+      <c r="J179" t="s">
         <v>338</v>
-      </c>
-      <c r="J179" t="s">
-        <v>692</v>
       </c>
       <c r="K179" t="s">
         <v>339</v>
@@ -9519,16 +9519,16 @@
         <v>14</v>
       </c>
       <c r="F180" t="s">
+        <v>691</v>
+      </c>
+      <c r="G180" t="s">
+        <v>692</v>
+      </c>
+      <c r="H180" t="s">
         <v>337</v>
       </c>
-      <c r="G180" t="s">
-        <v>691</v>
-      </c>
-      <c r="I180" t="s">
+      <c r="J180" t="s">
         <v>338</v>
-      </c>
-      <c r="J180" t="s">
-        <v>692</v>
       </c>
       <c r="K180" t="s">
         <v>339</v>
@@ -9968,19 +9968,19 @@
         <v>705</v>
       </c>
       <c r="F193" t="s">
-        <v>746</v>
+        <v>706</v>
       </c>
       <c r="G193" t="s">
         <v>707</v>
       </c>
       <c r="H193" t="s">
-        <v>708</v>
+        <v>746</v>
       </c>
       <c r="I193" t="s">
+        <v>709</v>
+      </c>
+      <c r="J193" t="s">
         <v>576</v>
-      </c>
-      <c r="J193" t="s">
-        <v>710</v>
       </c>
       <c r="K193" t="s">
         <v>339</v>
@@ -10178,16 +10178,16 @@
         <v>765</v>
       </c>
       <c r="F199" t="s">
-        <v>766</v>
+        <v>706</v>
       </c>
       <c r="G199" t="s">
         <v>707</v>
       </c>
       <c r="H199" t="s">
+        <v>766</v>
+      </c>
+      <c r="I199" t="s">
         <v>767</v>
-      </c>
-      <c r="I199" t="s">
-        <v>709</v>
       </c>
       <c r="J199" t="s">
         <v>710</v>
@@ -10213,16 +10213,16 @@
         <v>765</v>
       </c>
       <c r="F200" t="s">
-        <v>766</v>
+        <v>706</v>
       </c>
       <c r="G200" t="s">
         <v>707</v>
       </c>
       <c r="H200" t="s">
+        <v>766</v>
+      </c>
+      <c r="I200" t="s">
         <v>767</v>
-      </c>
-      <c r="I200" t="s">
-        <v>709</v>
       </c>
       <c r="J200" t="s">
         <v>710</v>
@@ -10248,16 +10248,16 @@
         <v>765</v>
       </c>
       <c r="F201" t="s">
-        <v>766</v>
+        <v>706</v>
       </c>
       <c r="G201" t="s">
         <v>707</v>
       </c>
       <c r="H201" t="s">
+        <v>766</v>
+      </c>
+      <c r="I201" t="s">
         <v>767</v>
-      </c>
-      <c r="I201" t="s">
-        <v>709</v>
       </c>
       <c r="J201" t="s">
         <v>710</v>
@@ -10280,16 +10280,16 @@
         <v>765</v>
       </c>
       <c r="F202" t="s">
-        <v>766</v>
+        <v>706</v>
       </c>
       <c r="G202" t="s">
         <v>707</v>
       </c>
       <c r="H202" t="s">
+        <v>766</v>
+      </c>
+      <c r="I202" t="s">
         <v>767</v>
-      </c>
-      <c r="I202" t="s">
-        <v>709</v>
       </c>
       <c r="J202" t="s">
         <v>710</v>
@@ -10315,19 +10315,19 @@
         <v>765</v>
       </c>
       <c r="F203" t="s">
-        <v>746</v>
+        <v>706</v>
       </c>
       <c r="G203" t="s">
         <v>707</v>
       </c>
       <c r="H203" t="s">
+        <v>746</v>
+      </c>
+      <c r="I203" t="s">
         <v>767</v>
       </c>
-      <c r="I203" t="s">
+      <c r="J203" t="s">
         <v>576</v>
-      </c>
-      <c r="J203" t="s">
-        <v>710</v>
       </c>
       <c r="K203" t="s">
         <v>339</v>
@@ -10347,16 +10347,16 @@
         <v>765</v>
       </c>
       <c r="F204" t="s">
-        <v>766</v>
+        <v>706</v>
       </c>
       <c r="G204" t="s">
         <v>707</v>
       </c>
       <c r="H204" t="s">
+        <v>766</v>
+      </c>
+      <c r="I204" t="s">
         <v>767</v>
-      </c>
-      <c r="I204" t="s">
-        <v>709</v>
       </c>
       <c r="J204" t="s">
         <v>710</v>
@@ -10382,16 +10382,16 @@
         <v>784</v>
       </c>
       <c r="F205" t="s">
-        <v>785</v>
+        <v>706</v>
       </c>
       <c r="G205" t="s">
         <v>707</v>
       </c>
       <c r="H205" t="s">
+        <v>785</v>
+      </c>
+      <c r="I205" t="s">
         <v>786</v>
-      </c>
-      <c r="I205" t="s">
-        <v>709</v>
       </c>
       <c r="J205" t="s">
         <v>710</v>
@@ -10417,16 +10417,16 @@
         <v>784</v>
       </c>
       <c r="F206" t="s">
-        <v>785</v>
+        <v>706</v>
       </c>
       <c r="G206" t="s">
         <v>707</v>
       </c>
       <c r="H206" t="s">
+        <v>785</v>
+      </c>
+      <c r="I206" t="s">
         <v>786</v>
-      </c>
-      <c r="I206" t="s">
-        <v>709</v>
       </c>
       <c r="J206" t="s">
         <v>710</v>
@@ -10449,16 +10449,16 @@
         <v>784</v>
       </c>
       <c r="F207" t="s">
-        <v>785</v>
+        <v>706</v>
       </c>
       <c r="G207" t="s">
         <v>707</v>
       </c>
       <c r="H207" t="s">
+        <v>785</v>
+      </c>
+      <c r="I207" t="s">
         <v>786</v>
-      </c>
-      <c r="I207" t="s">
-        <v>709</v>
       </c>
       <c r="J207" t="s">
         <v>710</v>
@@ -10484,19 +10484,19 @@
         <v>784</v>
       </c>
       <c r="F208" t="s">
-        <v>746</v>
+        <v>706</v>
       </c>
       <c r="G208" t="s">
         <v>707</v>
       </c>
       <c r="H208" t="s">
+        <v>746</v>
+      </c>
+      <c r="I208" t="s">
         <v>786</v>
       </c>
-      <c r="I208" t="s">
+      <c r="J208" t="s">
         <v>576</v>
-      </c>
-      <c r="J208" t="s">
-        <v>710</v>
       </c>
       <c r="K208" t="s">
         <v>339</v>
@@ -10519,16 +10519,16 @@
         <v>784</v>
       </c>
       <c r="F209" t="s">
-        <v>785</v>
+        <v>706</v>
       </c>
       <c r="G209" t="s">
         <v>707</v>
       </c>
       <c r="H209" t="s">
+        <v>785</v>
+      </c>
+      <c r="I209" t="s">
         <v>786</v>
-      </c>
-      <c r="I209" t="s">
-        <v>709</v>
       </c>
       <c r="J209" t="s">
         <v>710</v>
@@ -10723,19 +10723,19 @@
         <v>801</v>
       </c>
       <c r="F215" t="s">
-        <v>766</v>
+        <v>802</v>
       </c>
       <c r="G215" t="s">
         <v>803</v>
       </c>
       <c r="H215" t="s">
-        <v>804</v>
+        <v>766</v>
       </c>
       <c r="I215" t="s">
-        <v>709</v>
+        <v>805</v>
       </c>
       <c r="J215" t="s">
-        <v>806</v>
+        <v>710</v>
       </c>
       <c r="K215" t="s">
         <v>339</v>
@@ -10892,19 +10892,19 @@
         <v>801</v>
       </c>
       <c r="F220" t="s">
-        <v>663</v>
+        <v>802</v>
       </c>
       <c r="G220" t="s">
         <v>803</v>
       </c>
       <c r="H220" t="s">
-        <v>804</v>
+        <v>663</v>
       </c>
       <c r="I220" t="s">
-        <v>568</v>
+        <v>805</v>
       </c>
       <c r="J220" t="s">
-        <v>806</v>
+        <v>569</v>
       </c>
       <c r="K220" t="s">
         <v>339</v>
@@ -11099,19 +11099,19 @@
         <v>801</v>
       </c>
       <c r="F226" t="s">
-        <v>575</v>
+        <v>802</v>
       </c>
       <c r="G226" t="s">
         <v>803</v>
       </c>
       <c r="H226" t="s">
-        <v>804</v>
+        <v>575</v>
       </c>
       <c r="I226" t="s">
+        <v>805</v>
+      </c>
+      <c r="J226" t="s">
         <v>576</v>
-      </c>
-      <c r="J226" t="s">
-        <v>806</v>
       </c>
       <c r="K226" t="s">
         <v>339</v>
@@ -11169,19 +11169,19 @@
         <v>801</v>
       </c>
       <c r="F228" t="s">
-        <v>337</v>
+        <v>802</v>
       </c>
       <c r="G228" t="s">
         <v>803</v>
       </c>
       <c r="H228" t="s">
-        <v>804</v>
+        <v>337</v>
       </c>
       <c r="I228" t="s">
+        <v>805</v>
+      </c>
+      <c r="J228" t="s">
         <v>338</v>
-      </c>
-      <c r="J228" t="s">
-        <v>806</v>
       </c>
       <c r="K228" t="s">
         <v>339</v>
@@ -11204,16 +11204,16 @@
         <v>859</v>
       </c>
       <c r="F229" t="s">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="G229" t="s">
         <v>803</v>
       </c>
       <c r="H229" t="s">
+        <v>860</v>
+      </c>
+      <c r="I229" t="s">
         <v>861</v>
-      </c>
-      <c r="I229" t="s">
-        <v>805</v>
       </c>
       <c r="J229" t="s">
         <v>806</v>
@@ -11239,16 +11239,16 @@
         <v>859</v>
       </c>
       <c r="F230" t="s">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="G230" t="s">
         <v>803</v>
       </c>
       <c r="H230" t="s">
+        <v>860</v>
+      </c>
+      <c r="I230" t="s">
         <v>861</v>
-      </c>
-      <c r="I230" t="s">
-        <v>805</v>
       </c>
       <c r="J230" t="s">
         <v>806</v>
@@ -11274,19 +11274,19 @@
         <v>859</v>
       </c>
       <c r="F231" t="s">
-        <v>623</v>
+        <v>802</v>
       </c>
       <c r="G231" t="s">
         <v>803</v>
       </c>
       <c r="H231" t="s">
+        <v>623</v>
+      </c>
+      <c r="I231" t="s">
         <v>861</v>
       </c>
-      <c r="I231" t="s">
-        <v>568</v>
-      </c>
       <c r="J231" t="s">
-        <v>806</v>
+        <v>569</v>
       </c>
       <c r="K231" t="s">
         <v>339</v>
@@ -11309,19 +11309,19 @@
         <v>859</v>
       </c>
       <c r="F232" t="s">
-        <v>663</v>
+        <v>802</v>
       </c>
       <c r="G232" t="s">
         <v>803</v>
       </c>
       <c r="H232" t="s">
+        <v>663</v>
+      </c>
+      <c r="I232" t="s">
         <v>861</v>
       </c>
-      <c r="I232" t="s">
-        <v>568</v>
-      </c>
       <c r="J232" t="s">
-        <v>806</v>
+        <v>569</v>
       </c>
       <c r="K232" t="s">
         <v>339</v>
@@ -11344,16 +11344,16 @@
         <v>859</v>
       </c>
       <c r="F233" t="s">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="G233" t="s">
         <v>803</v>
       </c>
       <c r="H233" t="s">
+        <v>860</v>
+      </c>
+      <c r="I233" t="s">
         <v>861</v>
-      </c>
-      <c r="I233" t="s">
-        <v>805</v>
       </c>
       <c r="J233" t="s">
         <v>806</v>
@@ -11379,16 +11379,16 @@
         <v>859</v>
       </c>
       <c r="F234" t="s">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="G234" t="s">
         <v>803</v>
       </c>
       <c r="H234" t="s">
+        <v>860</v>
+      </c>
+      <c r="I234" t="s">
         <v>861</v>
-      </c>
-      <c r="I234" t="s">
-        <v>805</v>
       </c>
       <c r="J234" t="s">
         <v>806</v>
@@ -11414,16 +11414,16 @@
         <v>859</v>
       </c>
       <c r="F235" t="s">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="G235" t="s">
         <v>803</v>
       </c>
       <c r="H235" t="s">
+        <v>860</v>
+      </c>
+      <c r="I235" t="s">
         <v>861</v>
-      </c>
-      <c r="I235" t="s">
-        <v>805</v>
       </c>
       <c r="J235" t="s">
         <v>806</v>
@@ -11449,16 +11449,16 @@
         <v>859</v>
       </c>
       <c r="F236" t="s">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="G236" t="s">
         <v>803</v>
       </c>
       <c r="H236" t="s">
+        <v>860</v>
+      </c>
+      <c r="I236" t="s">
         <v>861</v>
-      </c>
-      <c r="I236" t="s">
-        <v>805</v>
       </c>
       <c r="J236" t="s">
         <v>806</v>
@@ -11484,16 +11484,16 @@
         <v>859</v>
       </c>
       <c r="F237" t="s">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="G237" t="s">
         <v>803</v>
       </c>
       <c r="H237" t="s">
+        <v>860</v>
+      </c>
+      <c r="I237" t="s">
         <v>861</v>
-      </c>
-      <c r="I237" t="s">
-        <v>805</v>
       </c>
       <c r="J237" t="s">
         <v>806</v>
@@ -11519,16 +11519,16 @@
         <v>859</v>
       </c>
       <c r="F238" t="s">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="G238" t="s">
         <v>803</v>
       </c>
       <c r="H238" t="s">
+        <v>860</v>
+      </c>
+      <c r="I238" t="s">
         <v>861</v>
-      </c>
-      <c r="I238" t="s">
-        <v>805</v>
       </c>
       <c r="J238" t="s">
         <v>806</v>
@@ -11554,16 +11554,16 @@
         <v>892</v>
       </c>
       <c r="F239" t="s">
-        <v>893</v>
+        <v>802</v>
       </c>
       <c r="G239" t="s">
         <v>803</v>
       </c>
       <c r="H239" t="s">
+        <v>893</v>
+      </c>
+      <c r="I239" t="s">
         <v>894</v>
-      </c>
-      <c r="I239" t="s">
-        <v>805</v>
       </c>
       <c r="J239" t="s">
         <v>806</v>
@@ -11589,19 +11589,19 @@
         <v>898</v>
       </c>
       <c r="F240" t="s">
+        <v>899</v>
+      </c>
+      <c r="G240" t="s">
+        <v>900</v>
+      </c>
+      <c r="H240" t="s">
         <v>337</v>
       </c>
-      <c r="G240" t="s">
-        <v>898</v>
-      </c>
-      <c r="H240" t="s">
-        <v>899</v>
-      </c>
       <c r="I240" t="s">
+        <v>900</v>
+      </c>
+      <c r="J240" t="s">
         <v>338</v>
-      </c>
-      <c r="J240" t="s">
-        <v>900</v>
       </c>
       <c r="K240" t="s">
         <v>339</v>
@@ -11624,19 +11624,19 @@
         <v>898</v>
       </c>
       <c r="F241" t="s">
+        <v>899</v>
+      </c>
+      <c r="G241" t="s">
+        <v>900</v>
+      </c>
+      <c r="H241" t="s">
         <v>337</v>
       </c>
-      <c r="G241" t="s">
-        <v>898</v>
-      </c>
-      <c r="H241" t="s">
-        <v>899</v>
-      </c>
       <c r="I241" t="s">
+        <v>900</v>
+      </c>
+      <c r="J241" t="s">
         <v>338</v>
-      </c>
-      <c r="J241" t="s">
-        <v>900</v>
       </c>
       <c r="K241" t="s">
         <v>339</v>
@@ -11659,19 +11659,19 @@
         <v>898</v>
       </c>
       <c r="F242" t="s">
+        <v>899</v>
+      </c>
+      <c r="G242" t="s">
+        <v>900</v>
+      </c>
+      <c r="H242" t="s">
         <v>337</v>
       </c>
-      <c r="G242" t="s">
-        <v>898</v>
-      </c>
-      <c r="H242" t="s">
-        <v>899</v>
-      </c>
       <c r="I242" t="s">
+        <v>900</v>
+      </c>
+      <c r="J242" t="s">
         <v>338</v>
-      </c>
-      <c r="J242" t="s">
-        <v>900</v>
       </c>
       <c r="K242" t="s">
         <v>339</v>
@@ -11694,19 +11694,19 @@
         <v>898</v>
       </c>
       <c r="F243" t="s">
+        <v>899</v>
+      </c>
+      <c r="G243" t="s">
+        <v>900</v>
+      </c>
+      <c r="H243" t="s">
         <v>337</v>
       </c>
-      <c r="G243" t="s">
-        <v>898</v>
-      </c>
-      <c r="H243" t="s">
-        <v>899</v>
-      </c>
       <c r="I243" t="s">
+        <v>900</v>
+      </c>
+      <c r="J243" t="s">
         <v>338</v>
-      </c>
-      <c r="J243" t="s">
-        <v>900</v>
       </c>
       <c r="K243" t="s">
         <v>339</v>
@@ -11729,19 +11729,19 @@
         <v>898</v>
       </c>
       <c r="F244" t="s">
+        <v>899</v>
+      </c>
+      <c r="G244" t="s">
+        <v>900</v>
+      </c>
+      <c r="H244" t="s">
         <v>337</v>
       </c>
-      <c r="G244" t="s">
-        <v>898</v>
-      </c>
-      <c r="H244" t="s">
-        <v>899</v>
-      </c>
       <c r="I244" t="s">
+        <v>900</v>
+      </c>
+      <c r="J244" t="s">
         <v>338</v>
-      </c>
-      <c r="J244" t="s">
-        <v>900</v>
       </c>
       <c r="K244" t="s">
         <v>339</v>
@@ -11764,19 +11764,19 @@
         <v>898</v>
       </c>
       <c r="F245" t="s">
+        <v>899</v>
+      </c>
+      <c r="G245" t="s">
+        <v>900</v>
+      </c>
+      <c r="H245" t="s">
         <v>337</v>
       </c>
-      <c r="G245" t="s">
-        <v>898</v>
-      </c>
-      <c r="H245" t="s">
-        <v>899</v>
-      </c>
       <c r="I245" t="s">
+        <v>900</v>
+      </c>
+      <c r="J245" t="s">
         <v>338</v>
-      </c>
-      <c r="J245" t="s">
-        <v>900</v>
       </c>
       <c r="K245" t="s">
         <v>339</v>
@@ -11796,19 +11796,19 @@
         <v>918</v>
       </c>
       <c r="F246" t="s">
+        <v>899</v>
+      </c>
+      <c r="G246" t="s">
+        <v>900</v>
+      </c>
+      <c r="H246" t="s">
         <v>919</v>
       </c>
-      <c r="G246" t="s">
-        <v>898</v>
-      </c>
-      <c r="H246" t="s">
+      <c r="I246" t="s">
         <v>920</v>
       </c>
-      <c r="I246" t="s">
+      <c r="J246" t="s">
         <v>534</v>
-      </c>
-      <c r="J246" t="s">
-        <v>900</v>
       </c>
       <c r="K246" t="s">
         <v>339</v>
@@ -11828,16 +11828,16 @@
         <v>14</v>
       </c>
       <c r="F247" t="s">
+        <v>924</v>
+      </c>
+      <c r="G247" t="s">
+        <v>925</v>
+      </c>
+      <c r="H247" t="s">
         <v>196</v>
       </c>
-      <c r="G247" t="s">
-        <v>924</v>
-      </c>
-      <c r="I247" t="s">
+      <c r="J247" t="s">
         <v>197</v>
-      </c>
-      <c r="J247" t="s">
-        <v>925</v>
       </c>
       <c r="K247" t="s">
         <v>198</v>
@@ -11857,16 +11857,16 @@
         <v>14</v>
       </c>
       <c r="F248" t="s">
+        <v>924</v>
+      </c>
+      <c r="G248" t="s">
+        <v>925</v>
+      </c>
+      <c r="H248" t="s">
         <v>196</v>
       </c>
-      <c r="G248" t="s">
-        <v>924</v>
-      </c>
-      <c r="I248" t="s">
+      <c r="J248" t="s">
         <v>197</v>
-      </c>
-      <c r="J248" t="s">
-        <v>925</v>
       </c>
       <c r="K248" t="s">
         <v>198</v>
@@ -11886,16 +11886,16 @@
         <v>14</v>
       </c>
       <c r="F249" t="s">
+        <v>924</v>
+      </c>
+      <c r="G249" t="s">
+        <v>925</v>
+      </c>
+      <c r="H249" t="s">
         <v>932</v>
       </c>
-      <c r="G249" t="s">
-        <v>924</v>
-      </c>
-      <c r="I249" t="s">
+      <c r="J249" t="s">
         <v>933</v>
-      </c>
-      <c r="J249" t="s">
-        <v>925</v>
       </c>
       <c r="K249" t="s">
         <v>198</v>
@@ -11915,16 +11915,16 @@
         <v>14</v>
       </c>
       <c r="F250" t="s">
+        <v>924</v>
+      </c>
+      <c r="G250" t="s">
+        <v>925</v>
+      </c>
+      <c r="H250" t="s">
         <v>196</v>
       </c>
-      <c r="G250" t="s">
-        <v>924</v>
-      </c>
-      <c r="I250" t="s">
+      <c r="J250" t="s">
         <v>197</v>
-      </c>
-      <c r="J250" t="s">
-        <v>925</v>
       </c>
       <c r="K250" t="s">
         <v>198</v>
@@ -11941,16 +11941,16 @@
         <v>14</v>
       </c>
       <c r="F251" t="s">
+        <v>924</v>
+      </c>
+      <c r="G251" t="s">
+        <v>925</v>
+      </c>
+      <c r="H251" t="s">
         <v>196</v>
       </c>
-      <c r="G251" t="s">
-        <v>924</v>
-      </c>
-      <c r="I251" t="s">
+      <c r="J251" t="s">
         <v>197</v>
-      </c>
-      <c r="J251" t="s">
-        <v>925</v>
       </c>
       <c r="K251" t="s">
         <v>198</v>
@@ -11970,16 +11970,16 @@
         <v>14</v>
       </c>
       <c r="F252" t="s">
+        <v>924</v>
+      </c>
+      <c r="G252" t="s">
+        <v>925</v>
+      </c>
+      <c r="H252" t="s">
         <v>196</v>
       </c>
-      <c r="G252" t="s">
-        <v>924</v>
-      </c>
-      <c r="I252" t="s">
+      <c r="J252" t="s">
         <v>197</v>
-      </c>
-      <c r="J252" t="s">
-        <v>925</v>
       </c>
       <c r="K252" t="s">
         <v>198</v>
@@ -12001,7 +12001,7 @@
       <c r="G253" t="s">
         <v>945</v>
       </c>
-      <c r="I253" t="s">
+      <c r="H253" t="s">
         <v>946</v>
       </c>
       <c r="J253" t="s">
@@ -12025,16 +12025,16 @@
         <v>14</v>
       </c>
       <c r="F254" t="s">
-        <v>454</v>
+        <v>944</v>
       </c>
       <c r="G254" t="s">
         <v>945</v>
       </c>
-      <c r="I254" t="s">
+      <c r="H254" t="s">
+        <v>454</v>
+      </c>
+      <c r="J254" t="s">
         <v>455</v>
-      </c>
-      <c r="J254" t="s">
-        <v>947</v>
       </c>
       <c r="K254" t="s">
         <v>192</v>
@@ -12054,16 +12054,16 @@
         <v>14</v>
       </c>
       <c r="F255" t="s">
-        <v>954</v>
+        <v>944</v>
       </c>
       <c r="G255" t="s">
         <v>945</v>
       </c>
-      <c r="I255" t="s">
+      <c r="H255" t="s">
+        <v>954</v>
+      </c>
+      <c r="J255" t="s">
         <v>955</v>
-      </c>
-      <c r="J255" t="s">
-        <v>947</v>
       </c>
       <c r="K255" t="s">
         <v>192</v>
@@ -12083,16 +12083,16 @@
         <v>14</v>
       </c>
       <c r="F256" t="s">
-        <v>954</v>
+        <v>944</v>
       </c>
       <c r="G256" t="s">
         <v>945</v>
       </c>
-      <c r="I256" t="s">
+      <c r="H256" t="s">
+        <v>954</v>
+      </c>
+      <c r="J256" t="s">
         <v>955</v>
-      </c>
-      <c r="J256" t="s">
-        <v>947</v>
       </c>
       <c r="K256" t="s">
         <v>192</v>
@@ -12112,16 +12112,16 @@
         <v>14</v>
       </c>
       <c r="F257" t="s">
-        <v>954</v>
+        <v>944</v>
       </c>
       <c r="G257" t="s">
         <v>945</v>
       </c>
-      <c r="I257" t="s">
+      <c r="H257" t="s">
+        <v>954</v>
+      </c>
+      <c r="J257" t="s">
         <v>955</v>
-      </c>
-      <c r="J257" t="s">
-        <v>947</v>
       </c>
       <c r="K257" t="s">
         <v>192</v>
@@ -12141,16 +12141,16 @@
         <v>14</v>
       </c>
       <c r="F258" t="s">
-        <v>706</v>
+        <v>944</v>
       </c>
       <c r="G258" t="s">
         <v>945</v>
       </c>
-      <c r="I258" t="s">
-        <v>709</v>
+      <c r="H258" t="s">
+        <v>708</v>
       </c>
       <c r="J258" t="s">
-        <v>947</v>
+        <v>710</v>
       </c>
       <c r="K258" t="s">
         <v>339</v>
@@ -12170,16 +12170,16 @@
         <v>14</v>
       </c>
       <c r="F259" t="s">
-        <v>954</v>
+        <v>944</v>
       </c>
       <c r="G259" t="s">
         <v>945</v>
       </c>
-      <c r="I259" t="s">
+      <c r="H259" t="s">
+        <v>954</v>
+      </c>
+      <c r="J259" t="s">
         <v>955</v>
-      </c>
-      <c r="J259" t="s">
-        <v>947</v>
       </c>
       <c r="K259" t="s">
         <v>192</v>
@@ -12199,16 +12199,16 @@
         <v>14</v>
       </c>
       <c r="F260" t="s">
-        <v>337</v>
+        <v>944</v>
       </c>
       <c r="G260" t="s">
         <v>945</v>
       </c>
-      <c r="I260" t="s">
+      <c r="H260" t="s">
+        <v>337</v>
+      </c>
+      <c r="J260" t="s">
         <v>338</v>
-      </c>
-      <c r="J260" t="s">
-        <v>947</v>
       </c>
       <c r="K260" t="s">
         <v>339</v>
@@ -12228,16 +12228,16 @@
         <v>14</v>
       </c>
       <c r="F261" t="s">
-        <v>973</v>
+        <v>944</v>
       </c>
       <c r="G261" t="s">
         <v>945</v>
       </c>
-      <c r="I261" t="s">
+      <c r="H261" t="s">
+        <v>973</v>
+      </c>
+      <c r="J261" t="s">
         <v>974</v>
-      </c>
-      <c r="J261" t="s">
-        <v>947</v>
       </c>
       <c r="K261" t="s">
         <v>407</v>
@@ -12257,16 +12257,16 @@
         <v>14</v>
       </c>
       <c r="F262" t="s">
-        <v>337</v>
+        <v>944</v>
       </c>
       <c r="G262" t="s">
         <v>945</v>
       </c>
-      <c r="I262" t="s">
+      <c r="H262" t="s">
+        <v>337</v>
+      </c>
+      <c r="J262" t="s">
         <v>338</v>
-      </c>
-      <c r="J262" t="s">
-        <v>947</v>
       </c>
       <c r="K262" t="s">
         <v>339</v>
@@ -12286,16 +12286,16 @@
         <v>14</v>
       </c>
       <c r="F263" t="s">
-        <v>981</v>
+        <v>944</v>
       </c>
       <c r="G263" t="s">
         <v>945</v>
       </c>
-      <c r="I263" t="s">
+      <c r="H263" t="s">
+        <v>981</v>
+      </c>
+      <c r="J263" t="s">
         <v>982</v>
-      </c>
-      <c r="J263" t="s">
-        <v>947</v>
       </c>
       <c r="K263" t="s">
         <v>379</v>
@@ -12315,16 +12315,16 @@
         <v>14</v>
       </c>
       <c r="F264" t="s">
-        <v>58</v>
+        <v>944</v>
       </c>
       <c r="G264" t="s">
         <v>945</v>
       </c>
-      <c r="I264" t="s">
+      <c r="H264" t="s">
+        <v>58</v>
+      </c>
+      <c r="J264" t="s">
         <v>59</v>
-      </c>
-      <c r="J264" t="s">
-        <v>947</v>
       </c>
       <c r="K264" t="s">
         <v>60</v>
@@ -12344,16 +12344,16 @@
         <v>14</v>
       </c>
       <c r="F265" t="s">
-        <v>16</v>
+        <v>944</v>
       </c>
       <c r="G265" t="s">
         <v>945</v>
       </c>
-      <c r="I265" t="s">
-        <v>19</v>
+      <c r="H265" t="s">
+        <v>18</v>
       </c>
       <c r="J265" t="s">
-        <v>947</v>
+        <v>20</v>
       </c>
       <c r="K265" t="s">
         <v>21</v>
@@ -12373,16 +12373,16 @@
         <v>14</v>
       </c>
       <c r="F266" t="s">
-        <v>992</v>
+        <v>944</v>
       </c>
       <c r="G266" t="s">
         <v>945</v>
       </c>
-      <c r="I266" t="s">
+      <c r="H266" t="s">
+        <v>992</v>
+      </c>
+      <c r="J266" t="s">
         <v>993</v>
-      </c>
-      <c r="J266" t="s">
-        <v>947</v>
       </c>
       <c r="K266" t="s">
         <v>239</v>
@@ -12402,16 +12402,16 @@
         <v>14</v>
       </c>
       <c r="F267" t="s">
+        <v>997</v>
+      </c>
+      <c r="G267" t="s">
+        <v>998</v>
+      </c>
+      <c r="H267" t="s">
         <v>243</v>
       </c>
-      <c r="G267" t="s">
-        <v>997</v>
-      </c>
-      <c r="I267" t="s">
+      <c r="J267" t="s">
         <v>244</v>
-      </c>
-      <c r="J267" t="s">
-        <v>998</v>
       </c>
       <c r="K267" t="s">
         <v>239</v>
@@ -12431,16 +12431,16 @@
         <v>14</v>
       </c>
       <c r="F268" t="s">
-        <v>420</v>
+        <v>1002</v>
       </c>
       <c r="G268" t="s">
-        <v>1002</v>
-      </c>
-      <c r="I268" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H268" t="s">
         <v>422</v>
       </c>
       <c r="J268" t="s">
-        <v>1003</v>
+        <v>423</v>
       </c>
       <c r="K268" t="s">
         <v>379</v>
@@ -12460,16 +12460,16 @@
         <v>14</v>
       </c>
       <c r="F269" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G269" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H269" t="s">
         <v>243</v>
       </c>
-      <c r="G269" t="s">
-        <v>1007</v>
-      </c>
-      <c r="I269" t="s">
+      <c r="J269" t="s">
         <v>244</v>
-      </c>
-      <c r="J269" t="s">
-        <v>1008</v>
       </c>
       <c r="K269" t="s">
         <v>239</v>
@@ -12489,16 +12489,16 @@
         <v>14</v>
       </c>
       <c r="F270" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G270" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H270" t="s">
         <v>243</v>
       </c>
-      <c r="G270" t="s">
-        <v>1007</v>
-      </c>
-      <c r="I270" t="s">
+      <c r="J270" t="s">
         <v>244</v>
-      </c>
-      <c r="J270" t="s">
-        <v>1008</v>
       </c>
       <c r="K270" t="s">
         <v>239</v>
@@ -12523,7 +12523,7 @@
       <c r="G271" t="s">
         <v>1016</v>
       </c>
-      <c r="I271" t="s">
+      <c r="H271" t="s">
         <v>1017</v>
       </c>
       <c r="J271" t="s">
@@ -12549,7 +12549,7 @@
       <c r="G272" t="s">
         <v>1016</v>
       </c>
-      <c r="I272" t="s">
+      <c r="H272" t="s">
         <v>1017</v>
       </c>
       <c r="J272" t="s">
@@ -12578,7 +12578,7 @@
       <c r="G273" t="s">
         <v>1016</v>
       </c>
-      <c r="I273" t="s">
+      <c r="H273" t="s">
         <v>1017</v>
       </c>
       <c r="J273" t="s">
@@ -12604,7 +12604,7 @@
       <c r="G274" t="s">
         <v>1016</v>
       </c>
-      <c r="I274" t="s">
+      <c r="H274" t="s">
         <v>1017</v>
       </c>
       <c r="J274" t="s">
@@ -12633,7 +12633,7 @@
       <c r="G275" t="s">
         <v>1016</v>
       </c>
-      <c r="I275" t="s">
+      <c r="H275" t="s">
         <v>1017</v>
       </c>
       <c r="J275" t="s">
@@ -12662,7 +12662,7 @@
       <c r="G276" t="s">
         <v>1016</v>
       </c>
-      <c r="I276" t="s">
+      <c r="H276" t="s">
         <v>1017</v>
       </c>
       <c r="J276" t="s">
@@ -12691,7 +12691,7 @@
       <c r="G277" t="s">
         <v>1016</v>
       </c>
-      <c r="I277" t="s">
+      <c r="H277" t="s">
         <v>1017</v>
       </c>
       <c r="J277" t="s">
@@ -12715,16 +12715,16 @@
         <v>14</v>
       </c>
       <c r="F278" t="s">
-        <v>420</v>
+        <v>1038</v>
       </c>
       <c r="G278" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I278" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H278" t="s">
         <v>422</v>
       </c>
       <c r="J278" t="s">
-        <v>1039</v>
+        <v>423</v>
       </c>
       <c r="K278" t="s">
         <v>379</v>
@@ -12744,16 +12744,16 @@
         <v>14</v>
       </c>
       <c r="F279" t="s">
-        <v>93</v>
+        <v>1038</v>
       </c>
       <c r="G279" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I279" t="s">
-        <v>96</v>
+        <v>1039</v>
+      </c>
+      <c r="H279" t="s">
+        <v>95</v>
       </c>
       <c r="J279" t="s">
-        <v>1039</v>
+        <v>97</v>
       </c>
       <c r="K279" t="s">
         <v>60</v>
@@ -12773,16 +12773,16 @@
         <v>14</v>
       </c>
       <c r="F280" t="s">
-        <v>16</v>
+        <v>1038</v>
       </c>
       <c r="G280" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I280" t="s">
-        <v>19</v>
+        <v>1039</v>
+      </c>
+      <c r="H280" t="s">
+        <v>18</v>
       </c>
       <c r="J280" t="s">
-        <v>1039</v>
+        <v>20</v>
       </c>
       <c r="K280" t="s">
         <v>21</v>
@@ -12802,16 +12802,16 @@
         <v>14</v>
       </c>
       <c r="F281" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G281" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H281" t="s">
         <v>352</v>
       </c>
-      <c r="G281" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I281" t="s">
+      <c r="J281" t="s">
         <v>353</v>
-      </c>
-      <c r="J281" t="s">
-        <v>1039</v>
       </c>
       <c r="K281" t="s">
         <v>239</v>
@@ -12831,16 +12831,16 @@
         <v>14</v>
       </c>
       <c r="F282" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G282" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H282" t="s">
         <v>253</v>
       </c>
-      <c r="G282" t="s">
-        <v>1038</v>
-      </c>
-      <c r="I282" t="s">
+      <c r="J282" t="s">
         <v>254</v>
-      </c>
-      <c r="J282" t="s">
-        <v>1039</v>
       </c>
       <c r="K282" t="s">
         <v>255</v>
@@ -12860,16 +12860,16 @@
         <v>14</v>
       </c>
       <c r="F283" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G283" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H283" t="s">
         <v>893</v>
       </c>
-      <c r="G283" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I283" t="s">
-        <v>805</v>
-      </c>
       <c r="J283" t="s">
-        <v>1056</v>
+        <v>806</v>
       </c>
       <c r="K283" t="s">
         <v>339</v>
@@ -12889,16 +12889,16 @@
         <v>14</v>
       </c>
       <c r="F284" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G284" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H284" t="s">
         <v>253</v>
       </c>
-      <c r="G284" t="s">
-        <v>1060</v>
-      </c>
-      <c r="I284" t="s">
+      <c r="J284" t="s">
         <v>254</v>
-      </c>
-      <c r="J284" t="s">
-        <v>1061</v>
       </c>
       <c r="K284" t="s">
         <v>255</v>
@@ -12915,16 +12915,16 @@
         <v>14</v>
       </c>
       <c r="F285" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G285" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H285" t="s">
         <v>352</v>
       </c>
-      <c r="G285" t="s">
-        <v>1064</v>
-      </c>
-      <c r="I285" t="s">
+      <c r="J285" t="s">
         <v>353</v>
-      </c>
-      <c r="J285" t="s">
-        <v>1065</v>
       </c>
       <c r="K285" t="s">
         <v>239</v>
@@ -12944,16 +12944,16 @@
         <v>14</v>
       </c>
       <c r="F286" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G286" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H286" t="s">
         <v>981</v>
       </c>
-      <c r="G286" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I286" t="s">
+      <c r="J286" t="s">
         <v>982</v>
-      </c>
-      <c r="J286" t="s">
-        <v>1070</v>
       </c>
       <c r="K286" t="s">
         <v>379</v>
@@ -12973,16 +12973,16 @@
         <v>14</v>
       </c>
       <c r="F287" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G287" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H287" t="s">
         <v>981</v>
       </c>
-      <c r="G287" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I287" t="s">
+      <c r="J287" t="s">
         <v>982</v>
-      </c>
-      <c r="J287" t="s">
-        <v>1070</v>
       </c>
       <c r="K287" t="s">
         <v>379</v>
@@ -13002,16 +13002,16 @@
         <v>14</v>
       </c>
       <c r="F288" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G288" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H288" t="s">
         <v>75</v>
       </c>
-      <c r="G288" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I288" t="s">
+      <c r="J288" t="s">
         <v>76</v>
-      </c>
-      <c r="J288" t="s">
-        <v>1070</v>
       </c>
       <c r="K288" t="s">
         <v>21</v>
@@ -13031,16 +13031,16 @@
         <v>14</v>
       </c>
       <c r="F289" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G289" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H289" t="s">
         <v>58</v>
       </c>
-      <c r="G289" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I289" t="s">
+      <c r="J289" t="s">
         <v>59</v>
-      </c>
-      <c r="J289" t="s">
-        <v>1070</v>
       </c>
       <c r="K289" t="s">
         <v>60</v>
@@ -13060,16 +13060,16 @@
         <v>14</v>
       </c>
       <c r="F290" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G290" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H290" t="s">
         <v>58</v>
       </c>
-      <c r="G290" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I290" t="s">
+      <c r="J290" t="s">
         <v>59</v>
-      </c>
-      <c r="J290" t="s">
-        <v>1070</v>
       </c>
       <c r="K290" t="s">
         <v>60</v>
@@ -13089,16 +13089,16 @@
         <v>14</v>
       </c>
       <c r="F291" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G291" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H291" t="s">
         <v>352</v>
       </c>
-      <c r="G291" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I291" t="s">
+      <c r="J291" t="s">
         <v>353</v>
-      </c>
-      <c r="J291" t="s">
-        <v>1070</v>
       </c>
       <c r="K291" t="s">
         <v>239</v>
@@ -13118,16 +13118,16 @@
         <v>14</v>
       </c>
       <c r="F292" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G292" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H292" t="s">
         <v>352</v>
       </c>
-      <c r="G292" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I292" t="s">
+      <c r="J292" t="s">
         <v>353</v>
-      </c>
-      <c r="J292" t="s">
-        <v>1070</v>
       </c>
       <c r="K292" t="s">
         <v>239</v>
@@ -13147,16 +13147,16 @@
         <v>14</v>
       </c>
       <c r="F293" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G293" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H293" t="s">
         <v>352</v>
       </c>
-      <c r="G293" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I293" t="s">
+      <c r="J293" t="s">
         <v>353</v>
-      </c>
-      <c r="J293" t="s">
-        <v>1070</v>
       </c>
       <c r="K293" t="s">
         <v>239</v>
@@ -13176,16 +13176,16 @@
         <v>14</v>
       </c>
       <c r="F294" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G294" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H294" t="s">
         <v>352</v>
       </c>
-      <c r="G294" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I294" t="s">
+      <c r="J294" t="s">
         <v>353</v>
-      </c>
-      <c r="J294" t="s">
-        <v>1070</v>
       </c>
       <c r="K294" t="s">
         <v>239</v>
@@ -13205,16 +13205,16 @@
         <v>14</v>
       </c>
       <c r="F295" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G295" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H295" t="s">
         <v>352</v>
       </c>
-      <c r="G295" t="s">
-        <v>1098</v>
-      </c>
-      <c r="I295" t="s">
+      <c r="J295" t="s">
         <v>353</v>
-      </c>
-      <c r="J295" t="s">
-        <v>1099</v>
       </c>
       <c r="K295" t="s">
         <v>239</v>
@@ -13234,16 +13234,16 @@
         <v>14</v>
       </c>
       <c r="F296" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G296" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H296" t="s">
         <v>352</v>
       </c>
-      <c r="G296" t="s">
-        <v>1098</v>
-      </c>
-      <c r="I296" t="s">
+      <c r="J296" t="s">
         <v>353</v>
-      </c>
-      <c r="J296" t="s">
-        <v>1099</v>
       </c>
       <c r="K296" t="s">
         <v>239</v>

--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -28,27 +28,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -61,27 +61,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>Education</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -91,12 +91,12 @@
     <t>Educational buildings, equipment, materials; subsidiary services to education (boarding facilities, staff housing); language training; colloquia, seminars, lectures, etc.</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Research and studies on education effectiveness, relevance and quality; systematic evaluation and monitoring.</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
@@ -130,18 +130,18 @@
     <t>Formal and non-formal primary education for children; all elementary and first cycle systematic instruction; provision of learning materials.</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>Second cycle systematic instruction at junior level.</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -223,15 +223,15 @@
     <t>Second cycle systematic instruction at senior levels.</t>
   </si>
   <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
     <t>09.2.2 - Upper‐secondary education (IS)</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Elementary vocational training and secondary level technical education; on-the job training; apprenticeships; including informal vocational training.</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
@@ -256,18 +256,18 @@
     <t>Degree and diploma programmes at universities, colleges and polytechnics; scholarships.</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -277,12 +277,12 @@
     <t>Professional-level vocational training programmes and in-service training.</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
@@ -292,24 +292,24 @@
     <t>Health sector policy, planning and programmes; aid to health ministries, public health administration; institution capacity building and advice; medical insurance programmes; including health system strengthening and health governance; unspecified health activities.</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>Health</t>
   </si>
   <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -328,12 +328,12 @@
     <t>General medical research (excluding basic health research and research for prevention and control of NCDs (12382)).</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>Laboratories, specialised clinics and hospitals (including equipment and supplies); ambulances; dental services; medical rehabilitation. Excludes noncommunicable diseases (123xx).</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -367,12 +367,12 @@
     <t>Basic and primary health care programmes; paramedical and nursing care programmes; supply of drugs, medicines and vaccines related to basic health care; activities aimed at achieving universal health coverage.</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -382,12 +382,12 @@
     <t>District-level hospitals, clinics and dispensaries and related medical equipment; excluding specialised hospitals and clinics (12191).</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -460,12 +460,12 @@
     <t>Programmes for the prevention and control of NCDs which cannot be broken down into the codes below.</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -583,18 +583,18 @@
     <t>140</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -604,15 +604,15 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>Large scale sewerage including trunk sewers and sewage pumping stations; domestic and industrial waste water treatment plants.</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>Municipal and industrial solid waste management, including hazardous and toxic waste; collection, disposal and treatment; landfill areas; composting and reuse.</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -715,27 +715,27 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Fiscal policy and planning; support to ministries of finance; strengthening financial and managerial accountability; public expenditure management; improving financial management systems; budget drafting; inter-governmental fiscal relations, public audit, public debt. (Use code 15114 for domestic revenue mobilisation and code 33120 for customs).</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
@@ -760,12 +760,12 @@
     <t>Decentralisation processes (including political, administrative and fiscal dimensions); intergovernmental relations and federalism; strengthening departments of regional and local government, regional and local authorities and their national associations. (Use specific sector codes for decentralisation of sector management and services.)</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
@@ -775,15 +775,15 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -859,12 +859,12 @@
     <t>Support to administration of developing countries' foreign aid (including triangular and south-south cooperation).</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -943,12 +943,12 @@
     <t>Judicial law and order sectors; policy development within ministries of justice or equivalents.</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
@@ -958,12 +958,12 @@
     <t>Police affairs and services.</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Fire-prevention and fire-fighting affairs and services.</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>Prisons</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
@@ -1027,15 +1027,15 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -1072,12 +1072,12 @@
     <t>Electoral management bodies and processes, election observation, voters' education. (Use code 15230 when in the context of an international peacekeeping operation.)</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -1099,12 +1099,12 @@
     <t>Activities that support free and uncensored flow of information on public issues; activities that increase the editorial and technical skills and the integrity of the print and broadcast media, e.g. training of journalists. (Use codes 22010-22040 for provision of equipment and capital assistance to media.)</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -1147,15 +1147,15 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -1192,12 +1192,12 @@
     <t>Collection, production, management and dissemination of statistics and data related to Government &amp; Civil Society. Includes macroeconomic statistics, government finance, fiscal and public sector statistics, support to development of administrative data infrastructure, civil society surveys.</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -1207,12 +1207,12 @@
     <t>Technical co-operation provided to parliament, government ministries, law enforcement agencies and the judiciary to assist review and reform of the security system to improve democratic governance and civilian control; technical co-operation provided to government to improve civilian oversight and democratic control of budgeting, management, accountability and auditing of security expenditure, including military budgets, as part of a public expenditure management programme; assistance to civil society to enhance its competence and capacity to scrutinise the security system so that it is managed in accordance with democratic norms and principles of accountability, transparency and good governance. [Other than in the context of an international peacekeeping operation (15230)].</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -1231,15 +1231,15 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -1279,15 +1279,15 @@
     <t>160</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Social protection schemes in the form of cash or in-kind benefits, including pensions, against the risks linked to old age.</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -1348,12 +1348,12 @@
     <t>Employment policy and planning; institution capacity building and advice; employment creation and income generation programmes; including activities specifically designed for the needs of vulnerable groups.</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
@@ -1363,12 +1363,12 @@
     <t>Housing sector policy, planning and programmes; excluding low-cost housing and slum clearance (16040).</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
@@ -1378,12 +1378,12 @@
     <t>Including slum clearance.</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -1402,15 +1402,15 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -1444,12 +1444,12 @@
     <t>Recreation and sport</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -1528,12 +1528,12 @@
     <t>Road infrastructure, road vehicles; passenger road transport, motor passenger cars.</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -1615,12 +1615,12 @@
     <t>Whether or not related to transportation. Whenever possible, report storage projects under the sector of the resource being stored.</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -1684,12 +1684,12 @@
     <t>Radio and TV links, equipment; newspapers; printing and publishing.</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -1708,24 +1708,24 @@
     <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>Energy</t>
   </si>
   <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -1741,12 +1741,12 @@
     <t>Regulation of the energy sector, including wholesale and retail electricity provision.</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>Renewable energy generation programmes that cannot be attributed to one single technology (codes 23220 through 23280 below). Fuelwood/charcoal production should be included under forestry 31261.</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -1870,12 +1870,12 @@
     <t>Thermal power plants including when energy source cannot be determined; combined gas-coal power plants.</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -1933,12 +1933,12 @@
     <t>Electric power plants that make use of both non-renewable and renewable energy sources.</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
@@ -1963,12 +1963,12 @@
     <t>Power plants which are designed to produce heat only.</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -2131,24 +2131,24 @@
     <t>Agricultural sector policy, planning and programmes; aid to agricultural ministries; institution capacity building and advice; unspecified agriculture.</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2311,15 +2311,15 @@
     <t>Forestry sector policy, planning and programmes; institution capacity building and advice; forest surveys; unspecified forestry and agro-forestry activities.</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
     <t>04.2.2 - Forestry (CS)</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -2368,15 +2368,15 @@
     <t>Fishing sector policy, planning and programmes; institution capacity building and advice; ocean and coastal fishing; marine and freshwater fish surveys and prospecting; fishing boats/equipment; unspecified fishing activities.</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
     <t>04.2.3 - Fishing and hunting (CS)</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -2419,24 +2419,24 @@
     <t>Industrial sector policy, planning and programmes; institution capacity building and advice; unspecified industrial activities; manufacturing of goods not specified below.</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2593,15 +2593,15 @@
     <t>Mineral and mining sector policy, planning and programmes; mining legislation, mining cadastre, mineral resources inventory, information systems, institution capacity building and advice; unspecified mineral resources exploitation.</t>
   </si>
   <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
     <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -2692,15 +2692,15 @@
     <t>Construction sector policy and planning; excluding construction activities within specific sectors (e.g., hospital or school construction).</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
     <t>04.4.3 - Construction (CS)</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -2710,15 +2710,15 @@
     <t>Trade policy and planning; support to ministries and departments responsible for trade policy; trade-related legislation and regulatory reforms; policy analysis and implementation of multilateral trade agreements e.g. technical barriers to trade and sanitary and phytosanitary measures (TBT/SPS) except at regional level (see 33130); mainstreaming trade in national development strategies (e.g. poverty reduction strategy papers); wholesale/retail trade; unspecified trade and trade promotion activities.</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -2770,15 +2770,15 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
     <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -2812,12 +2812,12 @@
     <t>Including natural reserves and actions in the surrounding areas; other measures to protect endangered or vulnerable species and their habitats (e.g. wetlands preservation).</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -2851,15 +2851,15 @@
     <t>430</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>Other Multisector</t>
   </si>
   <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -2878,12 +2878,12 @@
     <t>Urban development and planning; urban management, land information systems.</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -2935,12 +2935,12 @@
     <t>Disaster risk reduction activities if not sector specific. Comprises risk assessments, structural prevention measures (e.g. flood prevention infrastructure), preparedness measures (e.g. early warning systems) normative prevention measures (e.g. building codes, land-use planning), and risk transfer systems (e.g. insurance schemes, risk funds). Also includes building local and national capacities and supporting the establishment of efficient and sustainable national structures able to promote disaster risk reduction.</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
@@ -2959,12 +2959,12 @@
     <t>Short or longer term household food security programmes and activities that improve the access of households to nutritionally adequate diets (excluding any cash transfers within broader social welfare programmes that do not have a specific food security, food acquisition or nutrition focus which should be reported under code 16010).</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -2992,12 +2992,12 @@
     <t>When sector cannot be identified.</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -3064,13 +3064,13 @@
     <t>600</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>Action Relating to Debt</t>
   </si>
   <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -3747,19 +3747,19 @@
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
       </c>
       <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
         <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3817,19 +3817,19 @@
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
       </c>
       <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
         <v>34</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3846,25 +3846,25 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
         <v>41</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3881,19 +3881,19 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
         <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s">
         <v>20</v>
@@ -3916,25 +3916,25 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
         <v>41</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3951,25 +3951,25 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
         <v>38</v>
       </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I9" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s">
         <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3986,25 +3986,25 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
         <v>38</v>
       </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s">
         <v>54</v>
-      </c>
-      <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4021,19 +4021,19 @@
         <v>14</v>
       </c>
       <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
         <v>38</v>
       </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J11" t="s">
         <v>59</v>
@@ -4056,25 +4056,25 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
         <v>38</v>
       </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="H12" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
         <v>65</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4091,25 +4091,25 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
         <v>69</v>
       </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="H13" t="s">
         <v>70</v>
       </c>
       <c r="I13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" t="s">
         <v>71</v>
-      </c>
-      <c r="J13" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4126,25 +4126,25 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
         <v>69</v>
       </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" t="s">
         <v>76</v>
-      </c>
-      <c r="K14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4161,25 +4161,25 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
         <v>80</v>
       </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="J15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" t="s">
         <v>83</v>
-      </c>
-      <c r="K15" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4196,25 +4196,25 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
         <v>80</v>
       </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" t="s">
         <v>88</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4246,10 +4246,10 @@
         <v>96</v>
       </c>
       <c r="J17" t="s">
+        <v>59</v>
+      </c>
+      <c r="K17" t="s">
         <v>97</v>
-      </c>
-      <c r="K17" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4281,10 +4281,10 @@
         <v>96</v>
       </c>
       <c r="J18" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18" t="s">
         <v>97</v>
-      </c>
-      <c r="K18" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -4307,19 +4307,19 @@
         <v>93</v>
       </c>
       <c r="G19" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="H19" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s">
         <v>96</v>
       </c>
       <c r="J19" t="s">
+        <v>59</v>
+      </c>
+      <c r="K19" t="s">
         <v>105</v>
-      </c>
-      <c r="K19" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4342,19 +4342,19 @@
         <v>93</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H20" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s">
         <v>96</v>
       </c>
       <c r="J20" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" t="s">
         <v>110</v>
-      </c>
-      <c r="K20" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4386,10 +4386,10 @@
         <v>96</v>
       </c>
       <c r="J21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K21" t="s">
         <v>97</v>
-      </c>
-      <c r="K21" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -4406,19 +4406,19 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" t="s">
         <v>117</v>
       </c>
-      <c r="F22" t="s">
-        <v>93</v>
-      </c>
       <c r="G22" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H22" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="I22" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="J22" t="s">
         <v>59</v>
@@ -4441,25 +4441,25 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" t="s">
         <v>117</v>
       </c>
-      <c r="F23" t="s">
-        <v>93</v>
-      </c>
       <c r="G23" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="H23" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I23" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="J23" t="s">
+        <v>59</v>
+      </c>
+      <c r="K23" t="s">
         <v>123</v>
-      </c>
-      <c r="K23" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4476,19 +4476,19 @@
         <v>14</v>
       </c>
       <c r="E24" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" t="s">
         <v>117</v>
       </c>
-      <c r="F24" t="s">
-        <v>93</v>
-      </c>
       <c r="G24" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H24" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="I24" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="J24" t="s">
         <v>59</v>
@@ -4511,19 +4511,19 @@
         <v>14</v>
       </c>
       <c r="E25" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" t="s">
         <v>117</v>
       </c>
-      <c r="F25" t="s">
-        <v>93</v>
-      </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H25" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="I25" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="J25" t="s">
         <v>59</v>
@@ -4546,19 +4546,19 @@
         <v>14</v>
       </c>
       <c r="E26" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" t="s">
         <v>117</v>
       </c>
-      <c r="F26" t="s">
-        <v>93</v>
-      </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="I26" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="J26" t="s">
         <v>59</v>
@@ -4581,19 +4581,19 @@
         <v>14</v>
       </c>
       <c r="E27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F27" t="s">
         <v>117</v>
       </c>
-      <c r="F27" t="s">
-        <v>93</v>
-      </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="I27" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="J27" t="s">
         <v>59</v>
@@ -4616,19 +4616,19 @@
         <v>14</v>
       </c>
       <c r="E28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" t="s">
         <v>117</v>
       </c>
-      <c r="F28" t="s">
-        <v>93</v>
-      </c>
       <c r="G28" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H28" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="I28" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="J28" t="s">
         <v>59</v>
@@ -4651,19 +4651,19 @@
         <v>14</v>
       </c>
       <c r="E29" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" t="s">
         <v>117</v>
       </c>
-      <c r="F29" t="s">
-        <v>93</v>
-      </c>
       <c r="G29" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="I29" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="J29" t="s">
         <v>59</v>
@@ -4686,25 +4686,25 @@
         <v>14</v>
       </c>
       <c r="E30" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" t="s">
         <v>117</v>
-      </c>
-      <c r="F30" t="s">
-        <v>93</v>
       </c>
       <c r="G30" t="s">
         <v>94</v>
       </c>
       <c r="H30" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="I30" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="J30" t="s">
+        <v>59</v>
+      </c>
+      <c r="K30" t="s">
         <v>97</v>
-      </c>
-      <c r="K30" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4721,19 +4721,19 @@
         <v>14</v>
       </c>
       <c r="E31" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" t="s">
         <v>148</v>
       </c>
-      <c r="F31" t="s">
-        <v>93</v>
-      </c>
       <c r="G31" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H31" t="s">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="I31" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="J31" t="s">
         <v>59</v>
@@ -4756,19 +4756,19 @@
         <v>14</v>
       </c>
       <c r="E32" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" t="s">
         <v>148</v>
       </c>
-      <c r="F32" t="s">
-        <v>93</v>
-      </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H32" t="s">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="I32" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="J32" t="s">
         <v>59</v>
@@ -4791,19 +4791,19 @@
         <v>14</v>
       </c>
       <c r="E33" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" t="s">
         <v>148</v>
       </c>
-      <c r="F33" t="s">
-        <v>93</v>
-      </c>
       <c r="G33" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="I33" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="J33" t="s">
         <v>59</v>
@@ -4826,19 +4826,19 @@
         <v>14</v>
       </c>
       <c r="E34" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" t="s">
         <v>148</v>
       </c>
-      <c r="F34" t="s">
-        <v>93</v>
-      </c>
       <c r="G34" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="I34" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="J34" t="s">
         <v>59</v>
@@ -4861,19 +4861,19 @@
         <v>14</v>
       </c>
       <c r="E35" t="s">
+        <v>92</v>
+      </c>
+      <c r="F35" t="s">
         <v>148</v>
       </c>
-      <c r="F35" t="s">
-        <v>93</v>
-      </c>
       <c r="G35" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="I35" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="J35" t="s">
         <v>59</v>
@@ -4896,25 +4896,25 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" t="s">
         <v>148</v>
       </c>
-      <c r="F36" t="s">
-        <v>93</v>
-      </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="H36" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="I36" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="J36" t="s">
+        <v>59</v>
+      </c>
+      <c r="K36" t="s">
         <v>105</v>
-      </c>
-      <c r="K36" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4930,14 +4930,14 @@
       <c r="D37" t="s">
         <v>14</v>
       </c>
-      <c r="F37" t="s">
+      <c r="E37" t="s">
         <v>168</v>
       </c>
       <c r="G37" t="s">
+        <v>58</v>
+      </c>
+      <c r="I37" t="s">
         <v>169</v>
-      </c>
-      <c r="H37" t="s">
-        <v>58</v>
       </c>
       <c r="J37" t="s">
         <v>59</v>
@@ -4959,14 +4959,14 @@
       <c r="D38" t="s">
         <v>14</v>
       </c>
-      <c r="F38" t="s">
+      <c r="E38" t="s">
         <v>168</v>
       </c>
       <c r="G38" t="s">
+        <v>58</v>
+      </c>
+      <c r="I38" t="s">
         <v>169</v>
-      </c>
-      <c r="H38" t="s">
-        <v>58</v>
       </c>
       <c r="J38" t="s">
         <v>59</v>
@@ -4988,14 +4988,14 @@
       <c r="D39" t="s">
         <v>14</v>
       </c>
-      <c r="F39" t="s">
+      <c r="E39" t="s">
         <v>168</v>
       </c>
       <c r="G39" t="s">
+        <v>58</v>
+      </c>
+      <c r="I39" t="s">
         <v>169</v>
-      </c>
-      <c r="H39" t="s">
-        <v>58</v>
       </c>
       <c r="J39" t="s">
         <v>59</v>
@@ -5017,14 +5017,14 @@
       <c r="D40" t="s">
         <v>14</v>
       </c>
-      <c r="F40" t="s">
+      <c r="E40" t="s">
         <v>168</v>
       </c>
       <c r="G40" t="s">
+        <v>58</v>
+      </c>
+      <c r="I40" t="s">
         <v>169</v>
-      </c>
-      <c r="H40" t="s">
-        <v>58</v>
       </c>
       <c r="J40" t="s">
         <v>59</v>
@@ -5046,20 +5046,20 @@
       <c r="D41" t="s">
         <v>14</v>
       </c>
-      <c r="F41" t="s">
+      <c r="E41" t="s">
         <v>168</v>
       </c>
       <c r="G41" t="s">
+        <v>94</v>
+      </c>
+      <c r="I41" t="s">
         <v>169</v>
       </c>
-      <c r="H41" t="s">
-        <v>95</v>
-      </c>
       <c r="J41" t="s">
+        <v>59</v>
+      </c>
+      <c r="K41" t="s">
         <v>97</v>
-      </c>
-      <c r="K41" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5075,20 +5075,20 @@
       <c r="D42" t="s">
         <v>14</v>
       </c>
-      <c r="F42" t="s">
+      <c r="E42" t="s">
         <v>168</v>
       </c>
       <c r="G42" t="s">
+        <v>104</v>
+      </c>
+      <c r="I42" t="s">
         <v>169</v>
       </c>
-      <c r="H42" t="s">
-        <v>104</v>
-      </c>
       <c r="J42" t="s">
+        <v>59</v>
+      </c>
+      <c r="K42" t="s">
         <v>105</v>
-      </c>
-      <c r="K42" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5104,13 +5104,13 @@
       <c r="D43" t="s">
         <v>14</v>
       </c>
-      <c r="F43" t="s">
+      <c r="E43" t="s">
         <v>188</v>
       </c>
       <c r="G43" t="s">
         <v>189</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>190</v>
       </c>
       <c r="J43" t="s">
@@ -5133,14 +5133,14 @@
       <c r="D44" t="s">
         <v>14</v>
       </c>
-      <c r="F44" t="s">
+      <c r="E44" t="s">
         <v>188</v>
       </c>
       <c r="G44" t="s">
-        <v>189</v>
-      </c>
-      <c r="H44" t="s">
         <v>196</v>
+      </c>
+      <c r="I44" t="s">
+        <v>190</v>
       </c>
       <c r="J44" t="s">
         <v>197</v>
@@ -5162,13 +5162,13 @@
       <c r="D45" t="s">
         <v>14</v>
       </c>
-      <c r="F45" t="s">
+      <c r="E45" t="s">
         <v>188</v>
       </c>
       <c r="G45" t="s">
         <v>189</v>
       </c>
-      <c r="H45" t="s">
+      <c r="I45" t="s">
         <v>190</v>
       </c>
       <c r="J45" t="s">
@@ -5191,13 +5191,13 @@
       <c r="D46" t="s">
         <v>14</v>
       </c>
-      <c r="F46" t="s">
+      <c r="E46" t="s">
         <v>188</v>
       </c>
       <c r="G46" t="s">
         <v>189</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>190</v>
       </c>
       <c r="J46" t="s">
@@ -5220,20 +5220,20 @@
       <c r="D47" t="s">
         <v>14</v>
       </c>
-      <c r="F47" t="s">
+      <c r="E47" t="s">
         <v>188</v>
       </c>
       <c r="G47" t="s">
-        <v>189</v>
-      </c>
-      <c r="H47" t="s">
         <v>208</v>
       </c>
+      <c r="I47" t="s">
+        <v>190</v>
+      </c>
       <c r="J47" t="s">
+        <v>197</v>
+      </c>
+      <c r="K47" t="s">
         <v>209</v>
-      </c>
-      <c r="K47" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5249,13 +5249,13 @@
       <c r="D48" t="s">
         <v>14</v>
       </c>
-      <c r="F48" t="s">
+      <c r="E48" t="s">
         <v>188</v>
       </c>
       <c r="G48" t="s">
         <v>189</v>
       </c>
-      <c r="H48" t="s">
+      <c r="I48" t="s">
         <v>190</v>
       </c>
       <c r="J48" t="s">
@@ -5278,13 +5278,13 @@
       <c r="D49" t="s">
         <v>14</v>
       </c>
-      <c r="F49" t="s">
+      <c r="E49" t="s">
         <v>188</v>
       </c>
       <c r="G49" t="s">
         <v>189</v>
       </c>
-      <c r="H49" t="s">
+      <c r="I49" t="s">
         <v>190</v>
       </c>
       <c r="J49" t="s">
@@ -5307,20 +5307,20 @@
       <c r="D50" t="s">
         <v>14</v>
       </c>
-      <c r="F50" t="s">
+      <c r="E50" t="s">
         <v>188</v>
       </c>
       <c r="G50" t="s">
-        <v>189</v>
-      </c>
-      <c r="H50" t="s">
         <v>208</v>
       </c>
+      <c r="I50" t="s">
+        <v>190</v>
+      </c>
       <c r="J50" t="s">
+        <v>197</v>
+      </c>
+      <c r="K50" t="s">
         <v>209</v>
-      </c>
-      <c r="K50" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5336,13 +5336,13 @@
       <c r="D51" t="s">
         <v>14</v>
       </c>
-      <c r="F51" t="s">
+      <c r="E51" t="s">
         <v>188</v>
       </c>
       <c r="G51" t="s">
         <v>189</v>
       </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>190</v>
       </c>
       <c r="J51" t="s">
@@ -5365,20 +5365,20 @@
       <c r="D52" t="s">
         <v>14</v>
       </c>
-      <c r="F52" t="s">
+      <c r="E52" t="s">
         <v>188</v>
       </c>
       <c r="G52" t="s">
-        <v>189</v>
-      </c>
-      <c r="H52" t="s">
         <v>225</v>
       </c>
+      <c r="I52" t="s">
+        <v>190</v>
+      </c>
       <c r="J52" t="s">
+        <v>197</v>
+      </c>
+      <c r="K52" t="s">
         <v>226</v>
-      </c>
-      <c r="K52" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5394,14 +5394,14 @@
       <c r="D53" t="s">
         <v>14</v>
       </c>
-      <c r="F53" t="s">
+      <c r="E53" t="s">
         <v>188</v>
       </c>
       <c r="G53" t="s">
-        <v>189</v>
-      </c>
-      <c r="H53" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="I53" t="s">
+        <v>190</v>
       </c>
       <c r="J53" t="s">
         <v>20</v>
@@ -5465,19 +5465,19 @@
         <v>234</v>
       </c>
       <c r="G55" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H55" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="I55" t="s">
         <v>237</v>
       </c>
       <c r="J55" t="s">
+        <v>238</v>
+      </c>
+      <c r="K55" t="s">
         <v>244</v>
-      </c>
-      <c r="K55" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -5500,19 +5500,19 @@
         <v>234</v>
       </c>
       <c r="G56" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="H56" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="I56" t="s">
         <v>237</v>
       </c>
       <c r="J56" t="s">
+        <v>238</v>
+      </c>
+      <c r="K56" t="s">
         <v>249</v>
-      </c>
-      <c r="K56" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -5535,10 +5535,10 @@
         <v>234</v>
       </c>
       <c r="G57" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H57" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="I57" t="s">
         <v>237</v>
@@ -5570,19 +5570,19 @@
         <v>234</v>
       </c>
       <c r="G58" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H58" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="I58" t="s">
         <v>237</v>
       </c>
       <c r="J58" t="s">
+        <v>238</v>
+      </c>
+      <c r="K58" t="s">
         <v>244</v>
-      </c>
-      <c r="K58" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5605,19 +5605,19 @@
         <v>234</v>
       </c>
       <c r="G59" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H59" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="I59" t="s">
         <v>237</v>
       </c>
       <c r="J59" t="s">
+        <v>238</v>
+      </c>
+      <c r="K59" t="s">
         <v>244</v>
-      </c>
-      <c r="K59" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5640,19 +5640,19 @@
         <v>234</v>
       </c>
       <c r="G60" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H60" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="I60" t="s">
         <v>237</v>
       </c>
       <c r="J60" t="s">
+        <v>238</v>
+      </c>
+      <c r="K60" t="s">
         <v>244</v>
-      </c>
-      <c r="K60" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -5675,19 +5675,19 @@
         <v>234</v>
       </c>
       <c r="G61" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H61" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="I61" t="s">
         <v>237</v>
       </c>
       <c r="J61" t="s">
+        <v>238</v>
+      </c>
+      <c r="K61" t="s">
         <v>244</v>
-      </c>
-      <c r="K61" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -5710,19 +5710,19 @@
         <v>234</v>
       </c>
       <c r="G62" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H62" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="I62" t="s">
         <v>237</v>
       </c>
       <c r="J62" t="s">
+        <v>238</v>
+      </c>
+      <c r="K62" t="s">
         <v>244</v>
-      </c>
-      <c r="K62" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -5745,19 +5745,19 @@
         <v>234</v>
       </c>
       <c r="G63" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H63" t="s">
-        <v>274</v>
+        <v>236</v>
       </c>
       <c r="I63" t="s">
         <v>237</v>
       </c>
       <c r="J63" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="K63" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -5780,19 +5780,19 @@
         <v>234</v>
       </c>
       <c r="G64" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H64" t="s">
-        <v>274</v>
+        <v>236</v>
       </c>
       <c r="I64" t="s">
         <v>237</v>
       </c>
       <c r="J64" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="K64" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -5815,19 +5815,19 @@
         <v>234</v>
       </c>
       <c r="G65" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="H65" t="s">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c r="I65" t="s">
         <v>237</v>
       </c>
       <c r="J65" t="s">
+        <v>238</v>
+      </c>
+      <c r="K65" t="s">
         <v>282</v>
-      </c>
-      <c r="K65" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5885,19 +5885,19 @@
         <v>234</v>
       </c>
       <c r="G67" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H67" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="I67" t="s">
         <v>237</v>
       </c>
       <c r="J67" t="s">
+        <v>238</v>
+      </c>
+      <c r="K67" t="s">
         <v>244</v>
-      </c>
-      <c r="K67" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5923,7 +5923,7 @@
         <v>235</v>
       </c>
       <c r="H68" t="s">
-        <v>292</v>
+        <v>236</v>
       </c>
       <c r="I68" t="s">
         <v>237</v>
@@ -5932,7 +5932,7 @@
         <v>238</v>
       </c>
       <c r="K68" t="s">
-        <v>239</v>
+        <v>292</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -5958,7 +5958,7 @@
         <v>235</v>
       </c>
       <c r="H69" t="s">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="I69" t="s">
         <v>237</v>
@@ -5967,7 +5967,7 @@
         <v>238</v>
       </c>
       <c r="K69" t="s">
-        <v>239</v>
+        <v>296</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -5990,19 +5990,19 @@
         <v>234</v>
       </c>
       <c r="G70" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="H70" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="I70" t="s">
         <v>237</v>
       </c>
       <c r="J70" t="s">
+        <v>238</v>
+      </c>
+      <c r="K70" t="s">
         <v>249</v>
-      </c>
-      <c r="K70" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -6025,19 +6025,19 @@
         <v>234</v>
       </c>
       <c r="G71" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="H71" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="I71" t="s">
         <v>237</v>
       </c>
       <c r="J71" t="s">
+        <v>238</v>
+      </c>
+      <c r="K71" t="s">
         <v>249</v>
-      </c>
-      <c r="K71" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6095,19 +6095,19 @@
         <v>234</v>
       </c>
       <c r="G73" t="s">
-        <v>235</v>
+        <v>309</v>
       </c>
       <c r="H73" t="s">
-        <v>309</v>
+        <v>236</v>
       </c>
       <c r="I73" t="s">
         <v>237</v>
       </c>
       <c r="J73" t="s">
+        <v>254</v>
+      </c>
+      <c r="K73" t="s">
         <v>310</v>
-      </c>
-      <c r="K73" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6130,19 +6130,19 @@
         <v>234</v>
       </c>
       <c r="G74" t="s">
-        <v>235</v>
+        <v>314</v>
       </c>
       <c r="H74" t="s">
-        <v>314</v>
+        <v>236</v>
       </c>
       <c r="I74" t="s">
         <v>237</v>
       </c>
       <c r="J74" t="s">
+        <v>254</v>
+      </c>
+      <c r="K74" t="s">
         <v>315</v>
-      </c>
-      <c r="K74" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6165,19 +6165,19 @@
         <v>234</v>
       </c>
       <c r="G75" t="s">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c r="H75" t="s">
-        <v>319</v>
+        <v>236</v>
       </c>
       <c r="I75" t="s">
         <v>237</v>
       </c>
       <c r="J75" t="s">
+        <v>254</v>
+      </c>
+      <c r="K75" t="s">
         <v>320</v>
-      </c>
-      <c r="K75" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6200,19 +6200,19 @@
         <v>234</v>
       </c>
       <c r="G76" t="s">
-        <v>235</v>
+        <v>309</v>
       </c>
       <c r="H76" t="s">
-        <v>309</v>
+        <v>236</v>
       </c>
       <c r="I76" t="s">
         <v>237</v>
       </c>
       <c r="J76" t="s">
+        <v>254</v>
+      </c>
+      <c r="K76" t="s">
         <v>310</v>
-      </c>
-      <c r="K76" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -6235,19 +6235,19 @@
         <v>234</v>
       </c>
       <c r="G77" t="s">
-        <v>235</v>
+        <v>309</v>
       </c>
       <c r="H77" t="s">
-        <v>309</v>
+        <v>236</v>
       </c>
       <c r="I77" t="s">
         <v>237</v>
       </c>
       <c r="J77" t="s">
+        <v>254</v>
+      </c>
+      <c r="K77" t="s">
         <v>310</v>
-      </c>
-      <c r="K77" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -6270,19 +6270,19 @@
         <v>234</v>
       </c>
       <c r="G78" t="s">
-        <v>235</v>
+        <v>314</v>
       </c>
       <c r="H78" t="s">
-        <v>314</v>
+        <v>236</v>
       </c>
       <c r="I78" t="s">
         <v>237</v>
       </c>
       <c r="J78" t="s">
+        <v>254</v>
+      </c>
+      <c r="K78" t="s">
         <v>315</v>
-      </c>
-      <c r="K78" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -6302,19 +6302,19 @@
         <v>234</v>
       </c>
       <c r="G79" t="s">
-        <v>235</v>
+        <v>332</v>
       </c>
       <c r="H79" t="s">
-        <v>332</v>
+        <v>236</v>
       </c>
       <c r="I79" t="s">
         <v>237</v>
       </c>
       <c r="J79" t="s">
+        <v>254</v>
+      </c>
+      <c r="K79" t="s">
         <v>333</v>
-      </c>
-      <c r="K79" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -6337,10 +6337,10 @@
         <v>234</v>
       </c>
       <c r="G80" t="s">
-        <v>235</v>
+        <v>337</v>
       </c>
       <c r="H80" t="s">
-        <v>337</v>
+        <v>236</v>
       </c>
       <c r="I80" t="s">
         <v>237</v>
@@ -6372,10 +6372,10 @@
         <v>234</v>
       </c>
       <c r="G81" t="s">
-        <v>235</v>
+        <v>337</v>
       </c>
       <c r="H81" t="s">
-        <v>337</v>
+        <v>236</v>
       </c>
       <c r="I81" t="s">
         <v>237</v>
@@ -6407,10 +6407,10 @@
         <v>234</v>
       </c>
       <c r="G82" t="s">
-        <v>235</v>
+        <v>337</v>
       </c>
       <c r="H82" t="s">
-        <v>337</v>
+        <v>236</v>
       </c>
       <c r="I82" t="s">
         <v>237</v>
@@ -6445,7 +6445,7 @@
         <v>235</v>
       </c>
       <c r="H83" t="s">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="I83" t="s">
         <v>237</v>
@@ -6454,7 +6454,7 @@
         <v>238</v>
       </c>
       <c r="K83" t="s">
-        <v>239</v>
+        <v>296</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -6477,19 +6477,19 @@
         <v>234</v>
       </c>
       <c r="G84" t="s">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="H84" t="s">
-        <v>352</v>
+        <v>236</v>
       </c>
       <c r="I84" t="s">
         <v>237</v>
       </c>
       <c r="J84" t="s">
+        <v>238</v>
+      </c>
+      <c r="K84" t="s">
         <v>353</v>
-      </c>
-      <c r="K84" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -6512,19 +6512,19 @@
         <v>234</v>
       </c>
       <c r="G85" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H85" t="s">
-        <v>357</v>
+        <v>236</v>
       </c>
       <c r="I85" t="s">
         <v>237</v>
       </c>
       <c r="J85" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="K85" t="s">
-        <v>239</v>
+        <v>357</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -6547,19 +6547,19 @@
         <v>234</v>
       </c>
       <c r="G86" t="s">
-        <v>235</v>
+        <v>361</v>
       </c>
       <c r="H86" t="s">
-        <v>361</v>
+        <v>236</v>
       </c>
       <c r="I86" t="s">
         <v>237</v>
       </c>
       <c r="J86" t="s">
+        <v>338</v>
+      </c>
+      <c r="K86" t="s">
         <v>362</v>
-      </c>
-      <c r="K86" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -6582,19 +6582,19 @@
         <v>234</v>
       </c>
       <c r="G87" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H87" t="s">
-        <v>357</v>
+        <v>236</v>
       </c>
       <c r="I87" t="s">
         <v>237</v>
       </c>
       <c r="J87" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="K87" t="s">
-        <v>239</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -6614,19 +6614,19 @@
         <v>234</v>
       </c>
       <c r="G88" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H88" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="I88" t="s">
         <v>237</v>
       </c>
       <c r="J88" t="s">
+        <v>238</v>
+      </c>
+      <c r="K88" t="s">
         <v>244</v>
-      </c>
-      <c r="K88" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -6649,19 +6649,19 @@
         <v>234</v>
       </c>
       <c r="G89" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H89" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="I89" t="s">
         <v>237</v>
       </c>
       <c r="J89" t="s">
+        <v>238</v>
+      </c>
+      <c r="K89" t="s">
         <v>244</v>
-      </c>
-      <c r="K89" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -6684,10 +6684,10 @@
         <v>234</v>
       </c>
       <c r="G90" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H90" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="I90" t="s">
         <v>237</v>
@@ -6719,10 +6719,10 @@
         <v>234</v>
       </c>
       <c r="G91" t="s">
-        <v>235</v>
+        <v>377</v>
       </c>
       <c r="H91" t="s">
-        <v>377</v>
+        <v>236</v>
       </c>
       <c r="I91" t="s">
         <v>237</v>
@@ -6754,10 +6754,10 @@
         <v>234</v>
       </c>
       <c r="G92" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H92" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="I92" t="s">
         <v>237</v>
@@ -6789,19 +6789,19 @@
         <v>234</v>
       </c>
       <c r="G93" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="H93" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="I93" t="s">
         <v>237</v>
       </c>
       <c r="J93" t="s">
+        <v>238</v>
+      </c>
+      <c r="K93" t="s">
         <v>249</v>
-      </c>
-      <c r="K93" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -6824,10 +6824,10 @@
         <v>234</v>
       </c>
       <c r="G94" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H94" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="I94" t="s">
         <v>237</v>
@@ -6859,19 +6859,19 @@
         <v>234</v>
       </c>
       <c r="G95" t="s">
-        <v>235</v>
+        <v>392</v>
       </c>
       <c r="H95" t="s">
-        <v>392</v>
+        <v>236</v>
       </c>
       <c r="I95" t="s">
         <v>237</v>
       </c>
       <c r="J95" t="s">
+        <v>238</v>
+      </c>
+      <c r="K95" t="s">
         <v>393</v>
-      </c>
-      <c r="K95" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -6888,19 +6888,19 @@
         <v>14</v>
       </c>
       <c r="E96" t="s">
+        <v>233</v>
+      </c>
+      <c r="F96" t="s">
         <v>397</v>
       </c>
-      <c r="F96" t="s">
-        <v>234</v>
-      </c>
       <c r="G96" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H96" t="s">
-        <v>253</v>
+        <v>398</v>
       </c>
       <c r="I96" t="s">
-        <v>398</v>
+        <v>237</v>
       </c>
       <c r="J96" t="s">
         <v>254</v>
@@ -6923,19 +6923,19 @@
         <v>14</v>
       </c>
       <c r="E97" t="s">
+        <v>233</v>
+      </c>
+      <c r="F97" t="s">
         <v>397</v>
       </c>
-      <c r="F97" t="s">
-        <v>234</v>
-      </c>
       <c r="G97" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H97" t="s">
-        <v>253</v>
+        <v>398</v>
       </c>
       <c r="I97" t="s">
-        <v>398</v>
+        <v>237</v>
       </c>
       <c r="J97" t="s">
         <v>254</v>
@@ -6958,19 +6958,19 @@
         <v>14</v>
       </c>
       <c r="E98" t="s">
+        <v>233</v>
+      </c>
+      <c r="F98" t="s">
         <v>397</v>
       </c>
-      <c r="F98" t="s">
-        <v>234</v>
-      </c>
       <c r="G98" t="s">
-        <v>235</v>
+        <v>405</v>
       </c>
       <c r="H98" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="I98" t="s">
-        <v>398</v>
+        <v>237</v>
       </c>
       <c r="J98" t="s">
         <v>406</v>
@@ -6993,19 +6993,19 @@
         <v>14</v>
       </c>
       <c r="E99" t="s">
+        <v>233</v>
+      </c>
+      <c r="F99" t="s">
         <v>397</v>
       </c>
-      <c r="F99" t="s">
-        <v>234</v>
-      </c>
       <c r="G99" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H99" t="s">
-        <v>253</v>
+        <v>398</v>
       </c>
       <c r="I99" t="s">
-        <v>398</v>
+        <v>237</v>
       </c>
       <c r="J99" t="s">
         <v>254</v>
@@ -7028,25 +7028,25 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
+        <v>233</v>
+      </c>
+      <c r="F100" t="s">
         <v>397</v>
       </c>
-      <c r="F100" t="s">
-        <v>234</v>
-      </c>
       <c r="G100" t="s">
-        <v>235</v>
+        <v>319</v>
       </c>
       <c r="H100" t="s">
-        <v>319</v>
+        <v>398</v>
       </c>
       <c r="I100" t="s">
-        <v>398</v>
+        <v>237</v>
       </c>
       <c r="J100" t="s">
+        <v>254</v>
+      </c>
+      <c r="K100" t="s">
         <v>320</v>
-      </c>
-      <c r="K100" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -7063,19 +7063,19 @@
         <v>14</v>
       </c>
       <c r="E101" t="s">
+        <v>233</v>
+      </c>
+      <c r="F101" t="s">
         <v>397</v>
       </c>
-      <c r="F101" t="s">
-        <v>234</v>
-      </c>
       <c r="G101" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H101" t="s">
-        <v>253</v>
+        <v>398</v>
       </c>
       <c r="I101" t="s">
-        <v>398</v>
+        <v>237</v>
       </c>
       <c r="J101" t="s">
         <v>254</v>
@@ -7097,20 +7097,20 @@
       <c r="D102" t="s">
         <v>14</v>
       </c>
-      <c r="F102" t="s">
+      <c r="E102" t="s">
         <v>420</v>
       </c>
       <c r="G102" t="s">
         <v>421</v>
       </c>
-      <c r="H102" t="s">
+      <c r="I102" t="s">
         <v>422</v>
       </c>
       <c r="J102" t="s">
+        <v>378</v>
+      </c>
+      <c r="K102" t="s">
         <v>423</v>
-      </c>
-      <c r="K102" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -7126,20 +7126,20 @@
       <c r="D103" t="s">
         <v>14</v>
       </c>
-      <c r="F103" t="s">
+      <c r="E103" t="s">
         <v>420</v>
       </c>
       <c r="G103" t="s">
         <v>421</v>
       </c>
-      <c r="H103" t="s">
+      <c r="I103" t="s">
         <v>422</v>
       </c>
       <c r="J103" t="s">
+        <v>378</v>
+      </c>
+      <c r="K103" t="s">
         <v>423</v>
-      </c>
-      <c r="K103" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -7155,20 +7155,20 @@
       <c r="D104" t="s">
         <v>14</v>
       </c>
-      <c r="F104" t="s">
+      <c r="E104" t="s">
         <v>420</v>
       </c>
       <c r="G104" t="s">
         <v>421</v>
       </c>
-      <c r="H104" t="s">
+      <c r="I104" t="s">
         <v>422</v>
       </c>
       <c r="J104" t="s">
+        <v>378</v>
+      </c>
+      <c r="K104" t="s">
         <v>423</v>
-      </c>
-      <c r="K104" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -7184,20 +7184,20 @@
       <c r="D105" t="s">
         <v>14</v>
       </c>
-      <c r="F105" t="s">
+      <c r="E105" t="s">
         <v>420</v>
       </c>
       <c r="G105" t="s">
-        <v>421</v>
-      </c>
-      <c r="H105" t="s">
         <v>433</v>
       </c>
+      <c r="I105" t="s">
+        <v>422</v>
+      </c>
       <c r="J105" t="s">
+        <v>378</v>
+      </c>
+      <c r="K105" t="s">
         <v>434</v>
-      </c>
-      <c r="K105" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7213,20 +7213,20 @@
       <c r="D106" t="s">
         <v>14</v>
       </c>
-      <c r="F106" t="s">
+      <c r="E106" t="s">
         <v>420</v>
       </c>
       <c r="G106" t="s">
         <v>421</v>
       </c>
-      <c r="H106" t="s">
+      <c r="I106" t="s">
         <v>422</v>
       </c>
       <c r="J106" t="s">
+        <v>378</v>
+      </c>
+      <c r="K106" t="s">
         <v>423</v>
-      </c>
-      <c r="K106" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -7242,14 +7242,14 @@
       <c r="D107" t="s">
         <v>14</v>
       </c>
-      <c r="F107" t="s">
+      <c r="E107" t="s">
         <v>420</v>
       </c>
       <c r="G107" t="s">
-        <v>421</v>
-      </c>
-      <c r="H107" t="s">
         <v>377</v>
+      </c>
+      <c r="I107" t="s">
+        <v>422</v>
       </c>
       <c r="J107" t="s">
         <v>378</v>
@@ -7271,20 +7271,20 @@
       <c r="D108" t="s">
         <v>14</v>
       </c>
-      <c r="F108" t="s">
+      <c r="E108" t="s">
         <v>420</v>
       </c>
       <c r="G108" t="s">
-        <v>421</v>
-      </c>
-      <c r="H108" t="s">
         <v>444</v>
       </c>
+      <c r="I108" t="s">
+        <v>422</v>
+      </c>
       <c r="J108" t="s">
+        <v>378</v>
+      </c>
+      <c r="K108" t="s">
         <v>445</v>
-      </c>
-      <c r="K108" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7300,20 +7300,20 @@
       <c r="D109" t="s">
         <v>14</v>
       </c>
-      <c r="F109" t="s">
+      <c r="E109" t="s">
         <v>420</v>
       </c>
       <c r="G109" t="s">
-        <v>421</v>
-      </c>
-      <c r="H109" t="s">
         <v>449</v>
       </c>
+      <c r="I109" t="s">
+        <v>422</v>
+      </c>
       <c r="J109" t="s">
+        <v>191</v>
+      </c>
+      <c r="K109" t="s">
         <v>450</v>
-      </c>
-      <c r="K109" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -7329,20 +7329,20 @@
       <c r="D110" t="s">
         <v>14</v>
       </c>
-      <c r="F110" t="s">
+      <c r="E110" t="s">
         <v>420</v>
       </c>
       <c r="G110" t="s">
-        <v>421</v>
-      </c>
-      <c r="H110" t="s">
         <v>454</v>
       </c>
+      <c r="I110" t="s">
+        <v>422</v>
+      </c>
       <c r="J110" t="s">
+        <v>191</v>
+      </c>
+      <c r="K110" t="s">
         <v>455</v>
-      </c>
-      <c r="K110" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -7358,20 +7358,20 @@
       <c r="D111" t="s">
         <v>14</v>
       </c>
-      <c r="F111" t="s">
+      <c r="E111" t="s">
         <v>420</v>
       </c>
       <c r="G111" t="s">
         <v>421</v>
       </c>
-      <c r="H111" t="s">
+      <c r="I111" t="s">
         <v>422</v>
       </c>
       <c r="J111" t="s">
+        <v>378</v>
+      </c>
+      <c r="K111" t="s">
         <v>423</v>
-      </c>
-      <c r="K111" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -7387,14 +7387,14 @@
       <c r="D112" t="s">
         <v>14</v>
       </c>
-      <c r="F112" t="s">
+      <c r="E112" t="s">
         <v>420</v>
       </c>
       <c r="G112" t="s">
-        <v>421</v>
-      </c>
-      <c r="H112" t="s">
         <v>462</v>
+      </c>
+      <c r="I112" t="s">
+        <v>422</v>
       </c>
       <c r="J112" t="s">
         <v>463</v>
@@ -7416,20 +7416,20 @@
       <c r="D113" t="s">
         <v>14</v>
       </c>
-      <c r="F113" t="s">
+      <c r="E113" t="s">
         <v>420</v>
       </c>
       <c r="G113" t="s">
-        <v>421</v>
-      </c>
-      <c r="H113" t="s">
-        <v>296</v>
+        <v>235</v>
+      </c>
+      <c r="I113" t="s">
+        <v>422</v>
       </c>
       <c r="J113" t="s">
         <v>238</v>
       </c>
       <c r="K113" t="s">
-        <v>239</v>
+        <v>296</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -7445,20 +7445,20 @@
       <c r="D114" t="s">
         <v>14</v>
       </c>
-      <c r="F114" t="s">
+      <c r="E114" t="s">
         <v>420</v>
       </c>
       <c r="G114" t="s">
-        <v>421</v>
-      </c>
-      <c r="H114" t="s">
         <v>314</v>
       </c>
+      <c r="I114" t="s">
+        <v>422</v>
+      </c>
       <c r="J114" t="s">
+        <v>254</v>
+      </c>
+      <c r="K114" t="s">
         <v>315</v>
-      </c>
-      <c r="K114" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -7474,14 +7474,14 @@
       <c r="D115" t="s">
         <v>14</v>
       </c>
-      <c r="F115" t="s">
+      <c r="E115" t="s">
         <v>420</v>
       </c>
       <c r="G115" t="s">
-        <v>421</v>
-      </c>
-      <c r="H115" t="s">
         <v>377</v>
+      </c>
+      <c r="I115" t="s">
+        <v>422</v>
       </c>
       <c r="J115" t="s">
         <v>378</v>
@@ -7500,20 +7500,20 @@
       <c r="D116" t="s">
         <v>14</v>
       </c>
-      <c r="F116" t="s">
+      <c r="E116" t="s">
         <v>420</v>
       </c>
       <c r="G116" t="s">
-        <v>421</v>
-      </c>
-      <c r="H116" t="s">
         <v>476</v>
       </c>
+      <c r="I116" t="s">
+        <v>422</v>
+      </c>
       <c r="J116" t="s">
+        <v>463</v>
+      </c>
+      <c r="K116" t="s">
         <v>477</v>
-      </c>
-      <c r="K116" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -7526,14 +7526,14 @@
       <c r="D117" t="s">
         <v>14</v>
       </c>
-      <c r="F117" t="s">
+      <c r="E117" t="s">
         <v>420</v>
       </c>
       <c r="G117" t="s">
-        <v>421</v>
-      </c>
-      <c r="H117" t="s">
         <v>462</v>
+      </c>
+      <c r="I117" t="s">
+        <v>422</v>
       </c>
       <c r="J117" t="s">
         <v>463</v>
@@ -7555,20 +7555,20 @@
       <c r="D118" t="s">
         <v>14</v>
       </c>
-      <c r="F118" t="s">
+      <c r="E118" t="s">
         <v>420</v>
       </c>
       <c r="G118" t="s">
-        <v>421</v>
-      </c>
-      <c r="H118" t="s">
-        <v>483</v>
+        <v>337</v>
+      </c>
+      <c r="I118" t="s">
+        <v>422</v>
       </c>
       <c r="J118" t="s">
         <v>338</v>
       </c>
       <c r="K118" t="s">
-        <v>339</v>
+        <v>483</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -7584,14 +7584,14 @@
       <c r="D119" t="s">
         <v>14</v>
       </c>
-      <c r="F119" t="s">
+      <c r="E119" t="s">
         <v>420</v>
       </c>
       <c r="G119" t="s">
-        <v>421</v>
-      </c>
-      <c r="H119" t="s">
         <v>377</v>
+      </c>
+      <c r="I119" t="s">
+        <v>422</v>
       </c>
       <c r="J119" t="s">
         <v>378</v>
@@ -7613,20 +7613,20 @@
       <c r="D120" t="s">
         <v>14</v>
       </c>
-      <c r="F120" t="s">
+      <c r="E120" t="s">
         <v>490</v>
       </c>
       <c r="G120" t="s">
+        <v>352</v>
+      </c>
+      <c r="I120" t="s">
         <v>491</v>
       </c>
-      <c r="H120" t="s">
-        <v>352</v>
-      </c>
       <c r="J120" t="s">
+        <v>238</v>
+      </c>
+      <c r="K120" t="s">
         <v>353</v>
-      </c>
-      <c r="K120" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -7642,20 +7642,20 @@
       <c r="D121" t="s">
         <v>14</v>
       </c>
-      <c r="F121" t="s">
+      <c r="E121" t="s">
         <v>490</v>
       </c>
       <c r="G121" t="s">
+        <v>235</v>
+      </c>
+      <c r="I121" t="s">
         <v>491</v>
-      </c>
-      <c r="H121" t="s">
-        <v>296</v>
       </c>
       <c r="J121" t="s">
         <v>238</v>
       </c>
       <c r="K121" t="s">
-        <v>239</v>
+        <v>296</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -7671,20 +7671,20 @@
       <c r="D122" t="s">
         <v>14</v>
       </c>
-      <c r="F122" t="s">
+      <c r="E122" t="s">
         <v>490</v>
       </c>
       <c r="G122" t="s">
+        <v>352</v>
+      </c>
+      <c r="I122" t="s">
         <v>491</v>
       </c>
-      <c r="H122" t="s">
-        <v>352</v>
-      </c>
       <c r="J122" t="s">
+        <v>238</v>
+      </c>
+      <c r="K122" t="s">
         <v>353</v>
-      </c>
-      <c r="K122" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -7700,20 +7700,20 @@
       <c r="D123" t="s">
         <v>14</v>
       </c>
-      <c r="F123" t="s">
+      <c r="E123" t="s">
         <v>490</v>
       </c>
       <c r="G123" t="s">
+        <v>352</v>
+      </c>
+      <c r="I123" t="s">
         <v>491</v>
       </c>
-      <c r="H123" t="s">
-        <v>352</v>
-      </c>
       <c r="J123" t="s">
+        <v>238</v>
+      </c>
+      <c r="K123" t="s">
         <v>353</v>
-      </c>
-      <c r="K123" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -7729,20 +7729,20 @@
       <c r="D124" t="s">
         <v>14</v>
       </c>
-      <c r="F124" t="s">
+      <c r="E124" t="s">
         <v>490</v>
       </c>
       <c r="G124" t="s">
+        <v>504</v>
+      </c>
+      <c r="I124" t="s">
         <v>491</v>
       </c>
-      <c r="H124" t="s">
-        <v>504</v>
-      </c>
       <c r="J124" t="s">
+        <v>338</v>
+      </c>
+      <c r="K124" t="s">
         <v>505</v>
-      </c>
-      <c r="K124" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -7758,20 +7758,20 @@
       <c r="D125" t="s">
         <v>14</v>
       </c>
-      <c r="F125" t="s">
+      <c r="E125" t="s">
         <v>490</v>
       </c>
       <c r="G125" t="s">
+        <v>504</v>
+      </c>
+      <c r="I125" t="s">
         <v>491</v>
       </c>
-      <c r="H125" t="s">
-        <v>504</v>
-      </c>
       <c r="J125" t="s">
+        <v>338</v>
+      </c>
+      <c r="K125" t="s">
         <v>505</v>
-      </c>
-      <c r="K125" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -7787,20 +7787,20 @@
       <c r="D126" t="s">
         <v>14</v>
       </c>
-      <c r="F126" t="s">
+      <c r="E126" t="s">
         <v>490</v>
       </c>
       <c r="G126" t="s">
+        <v>504</v>
+      </c>
+      <c r="I126" t="s">
         <v>491</v>
       </c>
-      <c r="H126" t="s">
-        <v>504</v>
-      </c>
       <c r="J126" t="s">
+        <v>338</v>
+      </c>
+      <c r="K126" t="s">
         <v>505</v>
-      </c>
-      <c r="K126" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -7816,20 +7816,20 @@
       <c r="D127" t="s">
         <v>14</v>
       </c>
-      <c r="F127" t="s">
+      <c r="E127" t="s">
         <v>490</v>
       </c>
       <c r="G127" t="s">
+        <v>504</v>
+      </c>
+      <c r="I127" t="s">
         <v>491</v>
       </c>
-      <c r="H127" t="s">
-        <v>504</v>
-      </c>
       <c r="J127" t="s">
+        <v>338</v>
+      </c>
+      <c r="K127" t="s">
         <v>505</v>
-      </c>
-      <c r="K127" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -7845,20 +7845,20 @@
       <c r="D128" t="s">
         <v>14</v>
       </c>
-      <c r="F128" t="s">
+      <c r="E128" t="s">
         <v>490</v>
       </c>
       <c r="G128" t="s">
+        <v>504</v>
+      </c>
+      <c r="I128" t="s">
         <v>491</v>
       </c>
-      <c r="H128" t="s">
-        <v>504</v>
-      </c>
       <c r="J128" t="s">
+        <v>338</v>
+      </c>
+      <c r="K128" t="s">
         <v>505</v>
-      </c>
-      <c r="K128" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -7874,20 +7874,20 @@
       <c r="D129" t="s">
         <v>14</v>
       </c>
-      <c r="F129" t="s">
+      <c r="E129" t="s">
         <v>490</v>
       </c>
       <c r="G129" t="s">
+        <v>504</v>
+      </c>
+      <c r="I129" t="s">
         <v>491</v>
       </c>
-      <c r="H129" t="s">
+      <c r="J129" t="s">
+        <v>338</v>
+      </c>
+      <c r="K129" t="s">
         <v>521</v>
-      </c>
-      <c r="J129" t="s">
-        <v>505</v>
-      </c>
-      <c r="K129" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7903,20 +7903,20 @@
       <c r="D130" t="s">
         <v>14</v>
       </c>
-      <c r="F130" t="s">
+      <c r="E130" t="s">
         <v>490</v>
       </c>
       <c r="G130" t="s">
+        <v>504</v>
+      </c>
+      <c r="I130" t="s">
         <v>491</v>
       </c>
-      <c r="H130" t="s">
+      <c r="J130" t="s">
+        <v>338</v>
+      </c>
+      <c r="K130" t="s">
         <v>525</v>
-      </c>
-      <c r="J130" t="s">
-        <v>505</v>
-      </c>
-      <c r="K130" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7932,20 +7932,20 @@
       <c r="D131" t="s">
         <v>14</v>
       </c>
-      <c r="F131" t="s">
+      <c r="E131" t="s">
         <v>490</v>
       </c>
       <c r="G131" t="s">
+        <v>504</v>
+      </c>
+      <c r="I131" t="s">
         <v>491</v>
       </c>
-      <c r="H131" t="s">
+      <c r="J131" t="s">
+        <v>338</v>
+      </c>
+      <c r="K131" t="s">
         <v>529</v>
-      </c>
-      <c r="J131" t="s">
-        <v>505</v>
-      </c>
-      <c r="K131" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7961,20 +7961,20 @@
       <c r="D132" t="s">
         <v>14</v>
       </c>
-      <c r="F132" t="s">
+      <c r="E132" t="s">
         <v>490</v>
       </c>
       <c r="G132" t="s">
+        <v>533</v>
+      </c>
+      <c r="I132" t="s">
         <v>491</v>
       </c>
-      <c r="H132" t="s">
-        <v>533</v>
-      </c>
       <c r="J132" t="s">
+        <v>338</v>
+      </c>
+      <c r="K132" t="s">
         <v>534</v>
-      </c>
-      <c r="K132" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -7987,20 +7987,20 @@
       <c r="D133" t="s">
         <v>14</v>
       </c>
-      <c r="F133" t="s">
+      <c r="E133" t="s">
         <v>490</v>
       </c>
       <c r="G133" t="s">
+        <v>392</v>
+      </c>
+      <c r="I133" t="s">
         <v>491</v>
       </c>
-      <c r="H133" t="s">
-        <v>392</v>
-      </c>
       <c r="J133" t="s">
+        <v>238</v>
+      </c>
+      <c r="K133" t="s">
         <v>393</v>
-      </c>
-      <c r="K133" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -8016,20 +8016,20 @@
       <c r="D134" t="s">
         <v>14</v>
       </c>
-      <c r="F134" t="s">
+      <c r="E134" t="s">
         <v>540</v>
       </c>
       <c r="G134" t="s">
+        <v>361</v>
+      </c>
+      <c r="I134" t="s">
         <v>541</v>
       </c>
-      <c r="H134" t="s">
-        <v>361</v>
-      </c>
       <c r="J134" t="s">
+        <v>338</v>
+      </c>
+      <c r="K134" t="s">
         <v>362</v>
-      </c>
-      <c r="K134" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -8042,20 +8042,20 @@
       <c r="D135" t="s">
         <v>14</v>
       </c>
-      <c r="F135" t="s">
+      <c r="E135" t="s">
         <v>540</v>
       </c>
       <c r="G135" t="s">
+        <v>361</v>
+      </c>
+      <c r="I135" t="s">
         <v>541</v>
       </c>
-      <c r="H135" t="s">
-        <v>361</v>
-      </c>
       <c r="J135" t="s">
+        <v>338</v>
+      </c>
+      <c r="K135" t="s">
         <v>362</v>
-      </c>
-      <c r="K135" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -8071,20 +8071,20 @@
       <c r="D136" t="s">
         <v>14</v>
       </c>
-      <c r="F136" t="s">
+      <c r="E136" t="s">
         <v>540</v>
       </c>
       <c r="G136" t="s">
+        <v>361</v>
+      </c>
+      <c r="I136" t="s">
         <v>541</v>
       </c>
-      <c r="H136" t="s">
-        <v>361</v>
-      </c>
       <c r="J136" t="s">
+        <v>338</v>
+      </c>
+      <c r="K136" t="s">
         <v>362</v>
-      </c>
-      <c r="K136" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -8100,20 +8100,20 @@
       <c r="D137" t="s">
         <v>14</v>
       </c>
-      <c r="F137" t="s">
+      <c r="E137" t="s">
         <v>540</v>
       </c>
       <c r="G137" t="s">
+        <v>361</v>
+      </c>
+      <c r="I137" t="s">
         <v>541</v>
       </c>
-      <c r="H137" t="s">
-        <v>361</v>
-      </c>
       <c r="J137" t="s">
+        <v>338</v>
+      </c>
+      <c r="K137" t="s">
         <v>362</v>
-      </c>
-      <c r="K137" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -8129,20 +8129,20 @@
       <c r="D138" t="s">
         <v>14</v>
       </c>
-      <c r="F138" t="s">
+      <c r="E138" t="s">
         <v>540</v>
       </c>
       <c r="G138" t="s">
+        <v>361</v>
+      </c>
+      <c r="I138" t="s">
         <v>541</v>
       </c>
-      <c r="H138" t="s">
-        <v>361</v>
-      </c>
       <c r="J138" t="s">
+        <v>338</v>
+      </c>
+      <c r="K138" t="s">
         <v>362</v>
-      </c>
-      <c r="K138" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -8158,20 +8158,20 @@
       <c r="D139" t="s">
         <v>14</v>
       </c>
-      <c r="F139" t="s">
+      <c r="E139" t="s">
         <v>540</v>
       </c>
       <c r="G139" t="s">
+        <v>556</v>
+      </c>
+      <c r="I139" t="s">
         <v>541</v>
       </c>
-      <c r="H139" t="s">
-        <v>556</v>
-      </c>
       <c r="J139" t="s">
+        <v>463</v>
+      </c>
+      <c r="K139" t="s">
         <v>557</v>
-      </c>
-      <c r="K139" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -8187,20 +8187,20 @@
       <c r="D140" t="s">
         <v>14</v>
       </c>
-      <c r="F140" t="s">
+      <c r="E140" t="s">
         <v>540</v>
       </c>
       <c r="G140" t="s">
+        <v>361</v>
+      </c>
+      <c r="I140" t="s">
         <v>541</v>
       </c>
-      <c r="H140" t="s">
-        <v>361</v>
-      </c>
       <c r="J140" t="s">
+        <v>338</v>
+      </c>
+      <c r="K140" t="s">
         <v>362</v>
-      </c>
-      <c r="K140" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -8232,10 +8232,10 @@
         <v>568</v>
       </c>
       <c r="J141" t="s">
+        <v>338</v>
+      </c>
+      <c r="K141" t="s">
         <v>569</v>
-      </c>
-      <c r="K141" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -8264,10 +8264,10 @@
         <v>568</v>
       </c>
       <c r="J142" t="s">
+        <v>338</v>
+      </c>
+      <c r="K142" t="s">
         <v>569</v>
-      </c>
-      <c r="K142" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -8290,19 +8290,19 @@
         <v>565</v>
       </c>
       <c r="G143" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="H143" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="I143" t="s">
         <v>568</v>
       </c>
       <c r="J143" t="s">
+        <v>338</v>
+      </c>
+      <c r="K143" t="s">
         <v>576</v>
-      </c>
-      <c r="K143" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -8325,19 +8325,19 @@
         <v>565</v>
       </c>
       <c r="G144" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="H144" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="I144" t="s">
         <v>568</v>
       </c>
       <c r="J144" t="s">
+        <v>338</v>
+      </c>
+      <c r="K144" t="s">
         <v>576</v>
-      </c>
-      <c r="K144" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -8360,19 +8360,19 @@
         <v>565</v>
       </c>
       <c r="G145" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="H145" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="I145" t="s">
         <v>568</v>
       </c>
       <c r="J145" t="s">
+        <v>338</v>
+      </c>
+      <c r="K145" t="s">
         <v>576</v>
-      </c>
-      <c r="K145" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -8404,10 +8404,10 @@
         <v>568</v>
       </c>
       <c r="J146" t="s">
+        <v>338</v>
+      </c>
+      <c r="K146" t="s">
         <v>569</v>
-      </c>
-      <c r="K146" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -8424,25 +8424,25 @@
         <v>14</v>
       </c>
       <c r="E147" t="s">
+        <v>564</v>
+      </c>
+      <c r="F147" t="s">
         <v>589</v>
-      </c>
-      <c r="F147" t="s">
-        <v>565</v>
       </c>
       <c r="G147" t="s">
         <v>566</v>
       </c>
       <c r="H147" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="I147" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="J147" t="s">
+        <v>338</v>
+      </c>
+      <c r="K147" t="s">
         <v>569</v>
-      </c>
-      <c r="K147" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -8459,25 +8459,25 @@
         <v>14</v>
       </c>
       <c r="E148" t="s">
+        <v>564</v>
+      </c>
+      <c r="F148" t="s">
         <v>589</v>
-      </c>
-      <c r="F148" t="s">
-        <v>565</v>
       </c>
       <c r="G148" t="s">
         <v>566</v>
       </c>
       <c r="H148" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="I148" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="J148" t="s">
+        <v>338</v>
+      </c>
+      <c r="K148" t="s">
         <v>569</v>
-      </c>
-      <c r="K148" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -8494,25 +8494,25 @@
         <v>14</v>
       </c>
       <c r="E149" t="s">
+        <v>564</v>
+      </c>
+      <c r="F149" t="s">
         <v>589</v>
-      </c>
-      <c r="F149" t="s">
-        <v>565</v>
       </c>
       <c r="G149" t="s">
         <v>566</v>
       </c>
       <c r="H149" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="I149" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="J149" t="s">
+        <v>338</v>
+      </c>
+      <c r="K149" t="s">
         <v>569</v>
-      </c>
-      <c r="K149" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -8529,25 +8529,25 @@
         <v>14</v>
       </c>
       <c r="E150" t="s">
+        <v>564</v>
+      </c>
+      <c r="F150" t="s">
         <v>589</v>
-      </c>
-      <c r="F150" t="s">
-        <v>565</v>
       </c>
       <c r="G150" t="s">
         <v>566</v>
       </c>
       <c r="H150" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="I150" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="J150" t="s">
+        <v>338</v>
+      </c>
+      <c r="K150" t="s">
         <v>569</v>
-      </c>
-      <c r="K150" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -8564,25 +8564,25 @@
         <v>14</v>
       </c>
       <c r="E151" t="s">
+        <v>564</v>
+      </c>
+      <c r="F151" t="s">
         <v>589</v>
-      </c>
-      <c r="F151" t="s">
-        <v>565</v>
       </c>
       <c r="G151" t="s">
         <v>566</v>
       </c>
       <c r="H151" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="I151" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="J151" t="s">
+        <v>338</v>
+      </c>
+      <c r="K151" t="s">
         <v>569</v>
-      </c>
-      <c r="K151" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -8599,25 +8599,25 @@
         <v>14</v>
       </c>
       <c r="E152" t="s">
+        <v>564</v>
+      </c>
+      <c r="F152" t="s">
         <v>589</v>
-      </c>
-      <c r="F152" t="s">
-        <v>565</v>
       </c>
       <c r="G152" t="s">
         <v>566</v>
       </c>
       <c r="H152" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="I152" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="J152" t="s">
+        <v>338</v>
+      </c>
+      <c r="K152" t="s">
         <v>569</v>
-      </c>
-      <c r="K152" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -8634,25 +8634,25 @@
         <v>14</v>
       </c>
       <c r="E153" t="s">
+        <v>564</v>
+      </c>
+      <c r="F153" t="s">
         <v>589</v>
-      </c>
-      <c r="F153" t="s">
-        <v>565</v>
       </c>
       <c r="G153" t="s">
         <v>566</v>
       </c>
       <c r="H153" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="I153" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="J153" t="s">
+        <v>338</v>
+      </c>
+      <c r="K153" t="s">
         <v>569</v>
-      </c>
-      <c r="K153" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -8669,25 +8669,25 @@
         <v>14</v>
       </c>
       <c r="E154" t="s">
+        <v>564</v>
+      </c>
+      <c r="F154" t="s">
         <v>589</v>
-      </c>
-      <c r="F154" t="s">
-        <v>565</v>
       </c>
       <c r="G154" t="s">
         <v>566</v>
       </c>
       <c r="H154" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="I154" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="J154" t="s">
+        <v>338</v>
+      </c>
+      <c r="K154" t="s">
         <v>569</v>
-      </c>
-      <c r="K154" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -8704,25 +8704,25 @@
         <v>14</v>
       </c>
       <c r="E155" t="s">
+        <v>564</v>
+      </c>
+      <c r="F155" t="s">
         <v>589</v>
-      </c>
-      <c r="F155" t="s">
-        <v>565</v>
       </c>
       <c r="G155" t="s">
         <v>566</v>
       </c>
       <c r="H155" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="I155" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="J155" t="s">
+        <v>338</v>
+      </c>
+      <c r="K155" t="s">
         <v>569</v>
-      </c>
-      <c r="K155" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -8739,25 +8739,25 @@
         <v>14</v>
       </c>
       <c r="E156" t="s">
+        <v>564</v>
+      </c>
+      <c r="F156" t="s">
         <v>618</v>
-      </c>
-      <c r="F156" t="s">
-        <v>565</v>
       </c>
       <c r="G156" t="s">
         <v>566</v>
       </c>
       <c r="H156" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="I156" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="J156" t="s">
+        <v>338</v>
+      </c>
+      <c r="K156" t="s">
         <v>569</v>
-      </c>
-      <c r="K156" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -8774,25 +8774,25 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
+        <v>564</v>
+      </c>
+      <c r="F157" t="s">
         <v>618</v>
-      </c>
-      <c r="F157" t="s">
-        <v>565</v>
       </c>
       <c r="G157" t="s">
         <v>566</v>
       </c>
       <c r="H157" t="s">
+        <v>619</v>
+      </c>
+      <c r="I157" t="s">
+        <v>568</v>
+      </c>
+      <c r="J157" t="s">
+        <v>338</v>
+      </c>
+      <c r="K157" t="s">
         <v>623</v>
-      </c>
-      <c r="I157" t="s">
-        <v>619</v>
-      </c>
-      <c r="J157" t="s">
-        <v>569</v>
-      </c>
-      <c r="K157" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -8809,25 +8809,25 @@
         <v>14</v>
       </c>
       <c r="E158" t="s">
+        <v>564</v>
+      </c>
+      <c r="F158" t="s">
         <v>618</v>
-      </c>
-      <c r="F158" t="s">
-        <v>565</v>
       </c>
       <c r="G158" t="s">
         <v>566</v>
       </c>
       <c r="H158" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="I158" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="J158" t="s">
+        <v>338</v>
+      </c>
+      <c r="K158" t="s">
         <v>569</v>
-      </c>
-      <c r="K158" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -8844,25 +8844,25 @@
         <v>14</v>
       </c>
       <c r="E159" t="s">
+        <v>564</v>
+      </c>
+      <c r="F159" t="s">
         <v>618</v>
-      </c>
-      <c r="F159" t="s">
-        <v>565</v>
       </c>
       <c r="G159" t="s">
         <v>566</v>
       </c>
       <c r="H159" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="I159" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="J159" t="s">
+        <v>338</v>
+      </c>
+      <c r="K159" t="s">
         <v>569</v>
-      </c>
-      <c r="K159" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -8879,25 +8879,25 @@
         <v>14</v>
       </c>
       <c r="E160" t="s">
+        <v>564</v>
+      </c>
+      <c r="F160" t="s">
         <v>618</v>
-      </c>
-      <c r="F160" t="s">
-        <v>565</v>
       </c>
       <c r="G160" t="s">
         <v>566</v>
       </c>
       <c r="H160" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="I160" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="J160" t="s">
+        <v>338</v>
+      </c>
+      <c r="K160" t="s">
         <v>569</v>
-      </c>
-      <c r="K160" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -8914,25 +8914,25 @@
         <v>14</v>
       </c>
       <c r="E161" t="s">
+        <v>564</v>
+      </c>
+      <c r="F161" t="s">
         <v>618</v>
-      </c>
-      <c r="F161" t="s">
-        <v>565</v>
       </c>
       <c r="G161" t="s">
         <v>566</v>
       </c>
       <c r="H161" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="I161" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="J161" t="s">
+        <v>338</v>
+      </c>
+      <c r="K161" t="s">
         <v>569</v>
-      </c>
-      <c r="K161" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -8949,25 +8949,25 @@
         <v>14</v>
       </c>
       <c r="E162" t="s">
+        <v>564</v>
+      </c>
+      <c r="F162" t="s">
         <v>639</v>
-      </c>
-      <c r="F162" t="s">
-        <v>565</v>
       </c>
       <c r="G162" t="s">
         <v>566</v>
       </c>
       <c r="H162" t="s">
-        <v>567</v>
+        <v>640</v>
       </c>
       <c r="I162" t="s">
-        <v>640</v>
+        <v>568</v>
       </c>
       <c r="J162" t="s">
+        <v>338</v>
+      </c>
+      <c r="K162" t="s">
         <v>569</v>
-      </c>
-      <c r="K162" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -8984,25 +8984,25 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>644</v>
+        <v>564</v>
       </c>
       <c r="F163" t="s">
-        <v>565</v>
+        <v>642</v>
       </c>
       <c r="G163" t="s">
         <v>566</v>
       </c>
       <c r="H163" t="s">
+        <v>644</v>
+      </c>
+      <c r="I163" t="s">
+        <v>568</v>
+      </c>
+      <c r="J163" t="s">
+        <v>338</v>
+      </c>
+      <c r="K163" t="s">
         <v>645</v>
-      </c>
-      <c r="I163" t="s">
-        <v>642</v>
-      </c>
-      <c r="J163" t="s">
-        <v>569</v>
-      </c>
-      <c r="K163" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -9019,25 +9019,25 @@
         <v>14</v>
       </c>
       <c r="E164" t="s">
+        <v>564</v>
+      </c>
+      <c r="F164" t="s">
         <v>649</v>
-      </c>
-      <c r="F164" t="s">
-        <v>565</v>
       </c>
       <c r="G164" t="s">
         <v>566</v>
       </c>
       <c r="H164" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="I164" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="J164" t="s">
+        <v>338</v>
+      </c>
+      <c r="K164" t="s">
         <v>569</v>
-      </c>
-      <c r="K164" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -9054,25 +9054,25 @@
         <v>14</v>
       </c>
       <c r="E165" t="s">
+        <v>564</v>
+      </c>
+      <c r="F165" t="s">
         <v>649</v>
-      </c>
-      <c r="F165" t="s">
-        <v>565</v>
       </c>
       <c r="G165" t="s">
         <v>566</v>
       </c>
       <c r="H165" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="I165" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="J165" t="s">
+        <v>338</v>
+      </c>
+      <c r="K165" t="s">
         <v>569</v>
-      </c>
-      <c r="K165" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -9089,25 +9089,25 @@
         <v>14</v>
       </c>
       <c r="E166" t="s">
+        <v>564</v>
+      </c>
+      <c r="F166" t="s">
         <v>649</v>
-      </c>
-      <c r="F166" t="s">
-        <v>565</v>
       </c>
       <c r="G166" t="s">
         <v>566</v>
       </c>
       <c r="H166" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="I166" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="J166" t="s">
+        <v>338</v>
+      </c>
+      <c r="K166" t="s">
         <v>569</v>
-      </c>
-      <c r="K166" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -9124,25 +9124,25 @@
         <v>14</v>
       </c>
       <c r="E167" t="s">
+        <v>564</v>
+      </c>
+      <c r="F167" t="s">
         <v>649</v>
-      </c>
-      <c r="F167" t="s">
-        <v>565</v>
       </c>
       <c r="G167" t="s">
         <v>566</v>
       </c>
       <c r="H167" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="I167" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="J167" t="s">
+        <v>338</v>
+      </c>
+      <c r="K167" t="s">
         <v>569</v>
-      </c>
-      <c r="K167" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -9159,25 +9159,25 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
+        <v>564</v>
+      </c>
+      <c r="F168" t="s">
         <v>649</v>
-      </c>
-      <c r="F168" t="s">
-        <v>565</v>
       </c>
       <c r="G168" t="s">
         <v>566</v>
       </c>
       <c r="H168" t="s">
+        <v>650</v>
+      </c>
+      <c r="I168" t="s">
+        <v>568</v>
+      </c>
+      <c r="J168" t="s">
+        <v>338</v>
+      </c>
+      <c r="K168" t="s">
         <v>663</v>
-      </c>
-      <c r="I168" t="s">
-        <v>650</v>
-      </c>
-      <c r="J168" t="s">
-        <v>569</v>
-      </c>
-      <c r="K168" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -9191,25 +9191,25 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
+        <v>564</v>
+      </c>
+      <c r="F169" t="s">
         <v>649</v>
-      </c>
-      <c r="F169" t="s">
-        <v>565</v>
       </c>
       <c r="G169" t="s">
         <v>566</v>
       </c>
       <c r="H169" t="s">
+        <v>650</v>
+      </c>
+      <c r="I169" t="s">
+        <v>568</v>
+      </c>
+      <c r="J169" t="s">
+        <v>338</v>
+      </c>
+      <c r="K169" t="s">
         <v>663</v>
-      </c>
-      <c r="I169" t="s">
-        <v>650</v>
-      </c>
-      <c r="J169" t="s">
-        <v>569</v>
-      </c>
-      <c r="K169" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -9226,25 +9226,25 @@
         <v>14</v>
       </c>
       <c r="E170" t="s">
+        <v>564</v>
+      </c>
+      <c r="F170" t="s">
         <v>649</v>
-      </c>
-      <c r="F170" t="s">
-        <v>565</v>
       </c>
       <c r="G170" t="s">
         <v>566</v>
       </c>
       <c r="H170" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="I170" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="J170" t="s">
+        <v>338</v>
+      </c>
+      <c r="K170" t="s">
         <v>569</v>
-      </c>
-      <c r="K170" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -9260,14 +9260,14 @@
       <c r="D171" t="s">
         <v>14</v>
       </c>
-      <c r="F171" t="s">
+      <c r="E171" t="s">
         <v>672</v>
       </c>
       <c r="G171" t="s">
+        <v>337</v>
+      </c>
+      <c r="I171" t="s">
         <v>673</v>
-      </c>
-      <c r="H171" t="s">
-        <v>337</v>
       </c>
       <c r="J171" t="s">
         <v>338</v>
@@ -9289,20 +9289,20 @@
       <c r="D172" t="s">
         <v>14</v>
       </c>
-      <c r="F172" t="s">
+      <c r="E172" t="s">
         <v>672</v>
       </c>
       <c r="G172" t="s">
+        <v>243</v>
+      </c>
+      <c r="I172" t="s">
         <v>673</v>
       </c>
-      <c r="H172" t="s">
-        <v>243</v>
-      </c>
       <c r="J172" t="s">
+        <v>238</v>
+      </c>
+      <c r="K172" t="s">
         <v>244</v>
-      </c>
-      <c r="K172" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -9318,14 +9318,14 @@
       <c r="D173" t="s">
         <v>14</v>
       </c>
-      <c r="F173" t="s">
+      <c r="E173" t="s">
         <v>672</v>
       </c>
       <c r="G173" t="s">
+        <v>337</v>
+      </c>
+      <c r="I173" t="s">
         <v>673</v>
-      </c>
-      <c r="H173" t="s">
-        <v>337</v>
       </c>
       <c r="J173" t="s">
         <v>338</v>
@@ -9347,14 +9347,14 @@
       <c r="D174" t="s">
         <v>14</v>
       </c>
-      <c r="F174" t="s">
+      <c r="E174" t="s">
         <v>672</v>
       </c>
       <c r="G174" t="s">
+        <v>337</v>
+      </c>
+      <c r="I174" t="s">
         <v>673</v>
-      </c>
-      <c r="H174" t="s">
-        <v>337</v>
       </c>
       <c r="J174" t="s">
         <v>338</v>
@@ -9376,14 +9376,14 @@
       <c r="D175" t="s">
         <v>14</v>
       </c>
-      <c r="F175" t="s">
+      <c r="E175" t="s">
         <v>672</v>
       </c>
       <c r="G175" t="s">
+        <v>337</v>
+      </c>
+      <c r="I175" t="s">
         <v>673</v>
-      </c>
-      <c r="H175" t="s">
-        <v>337</v>
       </c>
       <c r="J175" t="s">
         <v>338</v>
@@ -9402,14 +9402,14 @@
       <c r="D176" t="s">
         <v>14</v>
       </c>
-      <c r="F176" t="s">
+      <c r="E176" t="s">
         <v>672</v>
       </c>
       <c r="G176" t="s">
+        <v>337</v>
+      </c>
+      <c r="I176" t="s">
         <v>673</v>
-      </c>
-      <c r="H176" t="s">
-        <v>337</v>
       </c>
       <c r="J176" t="s">
         <v>338</v>
@@ -9431,14 +9431,14 @@
       <c r="D177" t="s">
         <v>14</v>
       </c>
-      <c r="F177" t="s">
+      <c r="E177" t="s">
         <v>691</v>
       </c>
       <c r="G177" t="s">
+        <v>337</v>
+      </c>
+      <c r="I177" t="s">
         <v>692</v>
-      </c>
-      <c r="H177" t="s">
-        <v>337</v>
       </c>
       <c r="J177" t="s">
         <v>338</v>
@@ -9460,14 +9460,14 @@
       <c r="D178" t="s">
         <v>14</v>
       </c>
-      <c r="F178" t="s">
+      <c r="E178" t="s">
         <v>691</v>
       </c>
       <c r="G178" t="s">
+        <v>337</v>
+      </c>
+      <c r="I178" t="s">
         <v>692</v>
-      </c>
-      <c r="H178" t="s">
-        <v>337</v>
       </c>
       <c r="J178" t="s">
         <v>338</v>
@@ -9489,14 +9489,14 @@
       <c r="D179" t="s">
         <v>14</v>
       </c>
-      <c r="F179" t="s">
+      <c r="E179" t="s">
         <v>691</v>
       </c>
       <c r="G179" t="s">
+        <v>337</v>
+      </c>
+      <c r="I179" t="s">
         <v>692</v>
-      </c>
-      <c r="H179" t="s">
-        <v>337</v>
       </c>
       <c r="J179" t="s">
         <v>338</v>
@@ -9518,14 +9518,14 @@
       <c r="D180" t="s">
         <v>14</v>
       </c>
-      <c r="F180" t="s">
+      <c r="E180" t="s">
         <v>691</v>
       </c>
       <c r="G180" t="s">
+        <v>337</v>
+      </c>
+      <c r="I180" t="s">
         <v>692</v>
-      </c>
-      <c r="H180" t="s">
-        <v>337</v>
       </c>
       <c r="J180" t="s">
         <v>338</v>
@@ -9563,10 +9563,10 @@
         <v>709</v>
       </c>
       <c r="J181" t="s">
+        <v>338</v>
+      </c>
+      <c r="K181" t="s">
         <v>710</v>
-      </c>
-      <c r="K181" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -9598,10 +9598,10 @@
         <v>709</v>
       </c>
       <c r="J182" t="s">
+        <v>338</v>
+      </c>
+      <c r="K182" t="s">
         <v>710</v>
-      </c>
-      <c r="K182" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -9633,10 +9633,10 @@
         <v>709</v>
       </c>
       <c r="J183" t="s">
+        <v>338</v>
+      </c>
+      <c r="K183" t="s">
         <v>710</v>
-      </c>
-      <c r="K183" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -9668,10 +9668,10 @@
         <v>709</v>
       </c>
       <c r="J184" t="s">
+        <v>338</v>
+      </c>
+      <c r="K184" t="s">
         <v>710</v>
-      </c>
-      <c r="K184" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -9703,10 +9703,10 @@
         <v>709</v>
       </c>
       <c r="J185" t="s">
+        <v>338</v>
+      </c>
+      <c r="K185" t="s">
         <v>710</v>
-      </c>
-      <c r="K185" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -9738,10 +9738,10 @@
         <v>709</v>
       </c>
       <c r="J186" t="s">
+        <v>338</v>
+      </c>
+      <c r="K186" t="s">
         <v>710</v>
-      </c>
-      <c r="K186" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -9773,10 +9773,10 @@
         <v>709</v>
       </c>
       <c r="J187" t="s">
+        <v>338</v>
+      </c>
+      <c r="K187" t="s">
         <v>710</v>
-      </c>
-      <c r="K187" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -9808,10 +9808,10 @@
         <v>709</v>
       </c>
       <c r="J188" t="s">
+        <v>338</v>
+      </c>
+      <c r="K188" t="s">
         <v>710</v>
-      </c>
-      <c r="K188" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -9843,10 +9843,10 @@
         <v>709</v>
       </c>
       <c r="J189" t="s">
+        <v>338</v>
+      </c>
+      <c r="K189" t="s">
         <v>710</v>
-      </c>
-      <c r="K189" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -9878,10 +9878,10 @@
         <v>709</v>
       </c>
       <c r="J190" t="s">
+        <v>338</v>
+      </c>
+      <c r="K190" t="s">
         <v>710</v>
-      </c>
-      <c r="K190" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -9913,10 +9913,10 @@
         <v>709</v>
       </c>
       <c r="J191" t="s">
+        <v>338</v>
+      </c>
+      <c r="K191" t="s">
         <v>710</v>
-      </c>
-      <c r="K191" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -9945,10 +9945,10 @@
         <v>709</v>
       </c>
       <c r="J192" t="s">
+        <v>338</v>
+      </c>
+      <c r="K192" t="s">
         <v>710</v>
-      </c>
-      <c r="K192" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -9971,19 +9971,19 @@
         <v>706</v>
       </c>
       <c r="G193" t="s">
-        <v>707</v>
+        <v>575</v>
       </c>
       <c r="H193" t="s">
-        <v>746</v>
+        <v>708</v>
       </c>
       <c r="I193" t="s">
         <v>709</v>
       </c>
       <c r="J193" t="s">
-        <v>576</v>
+        <v>338</v>
       </c>
       <c r="K193" t="s">
-        <v>339</v>
+        <v>746</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -10015,10 +10015,10 @@
         <v>709</v>
       </c>
       <c r="J194" t="s">
+        <v>338</v>
+      </c>
+      <c r="K194" t="s">
         <v>710</v>
-      </c>
-      <c r="K194" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -10050,10 +10050,10 @@
         <v>709</v>
       </c>
       <c r="J195" t="s">
+        <v>338</v>
+      </c>
+      <c r="K195" t="s">
         <v>710</v>
-      </c>
-      <c r="K195" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -10085,10 +10085,10 @@
         <v>709</v>
       </c>
       <c r="J196" t="s">
+        <v>338</v>
+      </c>
+      <c r="K196" t="s">
         <v>710</v>
-      </c>
-      <c r="K196" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -10120,10 +10120,10 @@
         <v>709</v>
       </c>
       <c r="J197" t="s">
+        <v>338</v>
+      </c>
+      <c r="K197" t="s">
         <v>710</v>
-      </c>
-      <c r="K197" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -10155,10 +10155,10 @@
         <v>709</v>
       </c>
       <c r="J198" t="s">
+        <v>338</v>
+      </c>
+      <c r="K198" t="s">
         <v>710</v>
-      </c>
-      <c r="K198" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -10175,10 +10175,10 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
+        <v>705</v>
+      </c>
+      <c r="F199" t="s">
         <v>765</v>
-      </c>
-      <c r="F199" t="s">
-        <v>706</v>
       </c>
       <c r="G199" t="s">
         <v>707</v>
@@ -10187,13 +10187,13 @@
         <v>766</v>
       </c>
       <c r="I199" t="s">
+        <v>709</v>
+      </c>
+      <c r="J199" t="s">
+        <v>338</v>
+      </c>
+      <c r="K199" t="s">
         <v>767</v>
-      </c>
-      <c r="J199" t="s">
-        <v>710</v>
-      </c>
-      <c r="K199" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -10210,10 +10210,10 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
+        <v>705</v>
+      </c>
+      <c r="F200" t="s">
         <v>765</v>
-      </c>
-      <c r="F200" t="s">
-        <v>706</v>
       </c>
       <c r="G200" t="s">
         <v>707</v>
@@ -10222,13 +10222,13 @@
         <v>766</v>
       </c>
       <c r="I200" t="s">
+        <v>709</v>
+      </c>
+      <c r="J200" t="s">
+        <v>338</v>
+      </c>
+      <c r="K200" t="s">
         <v>767</v>
-      </c>
-      <c r="J200" t="s">
-        <v>710</v>
-      </c>
-      <c r="K200" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -10245,10 +10245,10 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
+        <v>705</v>
+      </c>
+      <c r="F201" t="s">
         <v>765</v>
-      </c>
-      <c r="F201" t="s">
-        <v>706</v>
       </c>
       <c r="G201" t="s">
         <v>707</v>
@@ -10257,13 +10257,13 @@
         <v>766</v>
       </c>
       <c r="I201" t="s">
+        <v>709</v>
+      </c>
+      <c r="J201" t="s">
+        <v>338</v>
+      </c>
+      <c r="K201" t="s">
         <v>767</v>
-      </c>
-      <c r="J201" t="s">
-        <v>710</v>
-      </c>
-      <c r="K201" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -10277,10 +10277,10 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
+        <v>705</v>
+      </c>
+      <c r="F202" t="s">
         <v>765</v>
-      </c>
-      <c r="F202" t="s">
-        <v>706</v>
       </c>
       <c r="G202" t="s">
         <v>707</v>
@@ -10289,13 +10289,13 @@
         <v>766</v>
       </c>
       <c r="I202" t="s">
+        <v>709</v>
+      </c>
+      <c r="J202" t="s">
+        <v>338</v>
+      </c>
+      <c r="K202" t="s">
         <v>767</v>
-      </c>
-      <c r="J202" t="s">
-        <v>710</v>
-      </c>
-      <c r="K202" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -10312,25 +10312,25 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
+        <v>705</v>
+      </c>
+      <c r="F203" t="s">
         <v>765</v>
       </c>
-      <c r="F203" t="s">
-        <v>706</v>
-      </c>
       <c r="G203" t="s">
-        <v>707</v>
+        <v>575</v>
       </c>
       <c r="H203" t="s">
+        <v>766</v>
+      </c>
+      <c r="I203" t="s">
+        <v>709</v>
+      </c>
+      <c r="J203" t="s">
+        <v>338</v>
+      </c>
+      <c r="K203" t="s">
         <v>746</v>
-      </c>
-      <c r="I203" t="s">
-        <v>767</v>
-      </c>
-      <c r="J203" t="s">
-        <v>576</v>
-      </c>
-      <c r="K203" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10344,10 +10344,10 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
+        <v>705</v>
+      </c>
+      <c r="F204" t="s">
         <v>765</v>
-      </c>
-      <c r="F204" t="s">
-        <v>706</v>
       </c>
       <c r="G204" t="s">
         <v>707</v>
@@ -10356,13 +10356,13 @@
         <v>766</v>
       </c>
       <c r="I204" t="s">
+        <v>709</v>
+      </c>
+      <c r="J204" t="s">
+        <v>338</v>
+      </c>
+      <c r="K204" t="s">
         <v>767</v>
-      </c>
-      <c r="J204" t="s">
-        <v>710</v>
-      </c>
-      <c r="K204" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -10379,10 +10379,10 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
+        <v>705</v>
+      </c>
+      <c r="F205" t="s">
         <v>784</v>
-      </c>
-      <c r="F205" t="s">
-        <v>706</v>
       </c>
       <c r="G205" t="s">
         <v>707</v>
@@ -10391,13 +10391,13 @@
         <v>785</v>
       </c>
       <c r="I205" t="s">
+        <v>709</v>
+      </c>
+      <c r="J205" t="s">
+        <v>338</v>
+      </c>
+      <c r="K205" t="s">
         <v>786</v>
-      </c>
-      <c r="J205" t="s">
-        <v>710</v>
-      </c>
-      <c r="K205" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -10414,10 +10414,10 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
+        <v>705</v>
+      </c>
+      <c r="F206" t="s">
         <v>784</v>
-      </c>
-      <c r="F206" t="s">
-        <v>706</v>
       </c>
       <c r="G206" t="s">
         <v>707</v>
@@ -10426,13 +10426,13 @@
         <v>785</v>
       </c>
       <c r="I206" t="s">
+        <v>709</v>
+      </c>
+      <c r="J206" t="s">
+        <v>338</v>
+      </c>
+      <c r="K206" t="s">
         <v>786</v>
-      </c>
-      <c r="J206" t="s">
-        <v>710</v>
-      </c>
-      <c r="K206" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -10446,10 +10446,10 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
+        <v>705</v>
+      </c>
+      <c r="F207" t="s">
         <v>784</v>
-      </c>
-      <c r="F207" t="s">
-        <v>706</v>
       </c>
       <c r="G207" t="s">
         <v>707</v>
@@ -10458,13 +10458,13 @@
         <v>785</v>
       </c>
       <c r="I207" t="s">
+        <v>709</v>
+      </c>
+      <c r="J207" t="s">
+        <v>338</v>
+      </c>
+      <c r="K207" t="s">
         <v>786</v>
-      </c>
-      <c r="J207" t="s">
-        <v>710</v>
-      </c>
-      <c r="K207" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -10481,25 +10481,25 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
+        <v>705</v>
+      </c>
+      <c r="F208" t="s">
         <v>784</v>
       </c>
-      <c r="F208" t="s">
-        <v>706</v>
-      </c>
       <c r="G208" t="s">
-        <v>707</v>
+        <v>575</v>
       </c>
       <c r="H208" t="s">
+        <v>785</v>
+      </c>
+      <c r="I208" t="s">
+        <v>709</v>
+      </c>
+      <c r="J208" t="s">
+        <v>338</v>
+      </c>
+      <c r="K208" t="s">
         <v>746</v>
-      </c>
-      <c r="I208" t="s">
-        <v>786</v>
-      </c>
-      <c r="J208" t="s">
-        <v>576</v>
-      </c>
-      <c r="K208" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10516,10 +10516,10 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
+        <v>705</v>
+      </c>
+      <c r="F209" t="s">
         <v>784</v>
-      </c>
-      <c r="F209" t="s">
-        <v>706</v>
       </c>
       <c r="G209" t="s">
         <v>707</v>
@@ -10528,13 +10528,13 @@
         <v>785</v>
       </c>
       <c r="I209" t="s">
+        <v>709</v>
+      </c>
+      <c r="J209" t="s">
+        <v>338</v>
+      </c>
+      <c r="K209" t="s">
         <v>786</v>
-      </c>
-      <c r="J209" t="s">
-        <v>710</v>
-      </c>
-      <c r="K209" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -10566,10 +10566,10 @@
         <v>805</v>
       </c>
       <c r="J210" t="s">
+        <v>338</v>
+      </c>
+      <c r="K210" t="s">
         <v>806</v>
-      </c>
-      <c r="K210" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="211" spans="1:11">
@@ -10598,10 +10598,10 @@
         <v>805</v>
       </c>
       <c r="J211" t="s">
+        <v>338</v>
+      </c>
+      <c r="K211" t="s">
         <v>806</v>
-      </c>
-      <c r="K211" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -10633,10 +10633,10 @@
         <v>805</v>
       </c>
       <c r="J212" t="s">
+        <v>338</v>
+      </c>
+      <c r="K212" t="s">
         <v>806</v>
-      </c>
-      <c r="K212" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="213" spans="1:11">
@@ -10665,10 +10665,10 @@
         <v>805</v>
       </c>
       <c r="J213" t="s">
+        <v>338</v>
+      </c>
+      <c r="K213" t="s">
         <v>806</v>
-      </c>
-      <c r="K213" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -10700,10 +10700,10 @@
         <v>805</v>
       </c>
       <c r="J214" t="s">
+        <v>338</v>
+      </c>
+      <c r="K214" t="s">
         <v>806</v>
-      </c>
-      <c r="K214" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="215" spans="1:11">
@@ -10726,19 +10726,19 @@
         <v>802</v>
       </c>
       <c r="G215" t="s">
-        <v>803</v>
+        <v>707</v>
       </c>
       <c r="H215" t="s">
-        <v>766</v>
+        <v>804</v>
       </c>
       <c r="I215" t="s">
         <v>805</v>
       </c>
       <c r="J215" t="s">
-        <v>710</v>
+        <v>338</v>
       </c>
       <c r="K215" t="s">
-        <v>339</v>
+        <v>767</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -10770,10 +10770,10 @@
         <v>805</v>
       </c>
       <c r="J216" t="s">
+        <v>338</v>
+      </c>
+      <c r="K216" t="s">
         <v>806</v>
-      </c>
-      <c r="K216" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -10805,10 +10805,10 @@
         <v>805</v>
       </c>
       <c r="J217" t="s">
+        <v>338</v>
+      </c>
+      <c r="K217" t="s">
         <v>806</v>
-      </c>
-      <c r="K217" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="218" spans="1:11">
@@ -10837,10 +10837,10 @@
         <v>805</v>
       </c>
       <c r="J218" t="s">
+        <v>338</v>
+      </c>
+      <c r="K218" t="s">
         <v>806</v>
-      </c>
-      <c r="K218" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="219" spans="1:11">
@@ -10869,10 +10869,10 @@
         <v>805</v>
       </c>
       <c r="J219" t="s">
+        <v>338</v>
+      </c>
+      <c r="K219" t="s">
         <v>806</v>
-      </c>
-      <c r="K219" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="220" spans="1:11">
@@ -10895,19 +10895,19 @@
         <v>802</v>
       </c>
       <c r="G220" t="s">
-        <v>803</v>
+        <v>566</v>
       </c>
       <c r="H220" t="s">
-        <v>663</v>
+        <v>804</v>
       </c>
       <c r="I220" t="s">
         <v>805</v>
       </c>
       <c r="J220" t="s">
-        <v>569</v>
+        <v>338</v>
       </c>
       <c r="K220" t="s">
-        <v>339</v>
+        <v>663</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -10939,10 +10939,10 @@
         <v>805</v>
       </c>
       <c r="J221" t="s">
+        <v>338</v>
+      </c>
+      <c r="K221" t="s">
         <v>806</v>
-      </c>
-      <c r="K221" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -10974,10 +10974,10 @@
         <v>805</v>
       </c>
       <c r="J222" t="s">
+        <v>338</v>
+      </c>
+      <c r="K222" t="s">
         <v>806</v>
-      </c>
-      <c r="K222" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="223" spans="1:11">
@@ -11006,10 +11006,10 @@
         <v>805</v>
       </c>
       <c r="J223" t="s">
+        <v>338</v>
+      </c>
+      <c r="K223" t="s">
         <v>806</v>
-      </c>
-      <c r="K223" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="224" spans="1:11">
@@ -11041,10 +11041,10 @@
         <v>805</v>
       </c>
       <c r="J224" t="s">
+        <v>338</v>
+      </c>
+      <c r="K224" t="s">
         <v>806</v>
-      </c>
-      <c r="K224" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="225" spans="1:11">
@@ -11076,10 +11076,10 @@
         <v>805</v>
       </c>
       <c r="J225" t="s">
+        <v>338</v>
+      </c>
+      <c r="K225" t="s">
         <v>806</v>
-      </c>
-      <c r="K225" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -11102,19 +11102,19 @@
         <v>802</v>
       </c>
       <c r="G226" t="s">
-        <v>803</v>
+        <v>575</v>
       </c>
       <c r="H226" t="s">
-        <v>575</v>
+        <v>804</v>
       </c>
       <c r="I226" t="s">
         <v>805</v>
       </c>
       <c r="J226" t="s">
+        <v>338</v>
+      </c>
+      <c r="K226" t="s">
         <v>576</v>
-      </c>
-      <c r="K226" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -11146,10 +11146,10 @@
         <v>805</v>
       </c>
       <c r="J227" t="s">
+        <v>338</v>
+      </c>
+      <c r="K227" t="s">
         <v>806</v>
-      </c>
-      <c r="K227" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="228" spans="1:11">
@@ -11172,10 +11172,10 @@
         <v>802</v>
       </c>
       <c r="G228" t="s">
-        <v>803</v>
+        <v>337</v>
       </c>
       <c r="H228" t="s">
-        <v>337</v>
+        <v>804</v>
       </c>
       <c r="I228" t="s">
         <v>805</v>
@@ -11201,10 +11201,10 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
+        <v>801</v>
+      </c>
+      <c r="F229" t="s">
         <v>859</v>
-      </c>
-      <c r="F229" t="s">
-        <v>802</v>
       </c>
       <c r="G229" t="s">
         <v>803</v>
@@ -11213,13 +11213,13 @@
         <v>860</v>
       </c>
       <c r="I229" t="s">
+        <v>805</v>
+      </c>
+      <c r="J229" t="s">
+        <v>338</v>
+      </c>
+      <c r="K229" t="s">
         <v>861</v>
-      </c>
-      <c r="J229" t="s">
-        <v>806</v>
-      </c>
-      <c r="K229" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -11236,10 +11236,10 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
+        <v>801</v>
+      </c>
+      <c r="F230" t="s">
         <v>859</v>
-      </c>
-      <c r="F230" t="s">
-        <v>802</v>
       </c>
       <c r="G230" t="s">
         <v>803</v>
@@ -11248,13 +11248,13 @@
         <v>860</v>
       </c>
       <c r="I230" t="s">
+        <v>805</v>
+      </c>
+      <c r="J230" t="s">
+        <v>338</v>
+      </c>
+      <c r="K230" t="s">
         <v>861</v>
-      </c>
-      <c r="J230" t="s">
-        <v>806</v>
-      </c>
-      <c r="K230" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -11271,25 +11271,25 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
+        <v>801</v>
+      </c>
+      <c r="F231" t="s">
         <v>859</v>
       </c>
-      <c r="F231" t="s">
-        <v>802</v>
-      </c>
       <c r="G231" t="s">
-        <v>803</v>
+        <v>566</v>
       </c>
       <c r="H231" t="s">
+        <v>860</v>
+      </c>
+      <c r="I231" t="s">
+        <v>805</v>
+      </c>
+      <c r="J231" t="s">
+        <v>338</v>
+      </c>
+      <c r="K231" t="s">
         <v>623</v>
-      </c>
-      <c r="I231" t="s">
-        <v>861</v>
-      </c>
-      <c r="J231" t="s">
-        <v>569</v>
-      </c>
-      <c r="K231" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11306,25 +11306,25 @@
         <v>14</v>
       </c>
       <c r="E232" t="s">
+        <v>801</v>
+      </c>
+      <c r="F232" t="s">
         <v>859</v>
       </c>
-      <c r="F232" t="s">
-        <v>802</v>
-      </c>
       <c r="G232" t="s">
-        <v>803</v>
+        <v>566</v>
       </c>
       <c r="H232" t="s">
+        <v>860</v>
+      </c>
+      <c r="I232" t="s">
+        <v>805</v>
+      </c>
+      <c r="J232" t="s">
+        <v>338</v>
+      </c>
+      <c r="K232" t="s">
         <v>663</v>
-      </c>
-      <c r="I232" t="s">
-        <v>861</v>
-      </c>
-      <c r="J232" t="s">
-        <v>569</v>
-      </c>
-      <c r="K232" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11341,10 +11341,10 @@
         <v>14</v>
       </c>
       <c r="E233" t="s">
+        <v>801</v>
+      </c>
+      <c r="F233" t="s">
         <v>859</v>
-      </c>
-      <c r="F233" t="s">
-        <v>802</v>
       </c>
       <c r="G233" t="s">
         <v>803</v>
@@ -11353,13 +11353,13 @@
         <v>860</v>
       </c>
       <c r="I233" t="s">
+        <v>805</v>
+      </c>
+      <c r="J233" t="s">
+        <v>338</v>
+      </c>
+      <c r="K233" t="s">
         <v>861</v>
-      </c>
-      <c r="J233" t="s">
-        <v>806</v>
-      </c>
-      <c r="K233" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -11376,10 +11376,10 @@
         <v>14</v>
       </c>
       <c r="E234" t="s">
+        <v>801</v>
+      </c>
+      <c r="F234" t="s">
         <v>859</v>
-      </c>
-      <c r="F234" t="s">
-        <v>802</v>
       </c>
       <c r="G234" t="s">
         <v>803</v>
@@ -11388,13 +11388,13 @@
         <v>860</v>
       </c>
       <c r="I234" t="s">
+        <v>805</v>
+      </c>
+      <c r="J234" t="s">
+        <v>338</v>
+      </c>
+      <c r="K234" t="s">
         <v>861</v>
-      </c>
-      <c r="J234" t="s">
-        <v>806</v>
-      </c>
-      <c r="K234" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -11411,10 +11411,10 @@
         <v>14</v>
       </c>
       <c r="E235" t="s">
+        <v>801</v>
+      </c>
+      <c r="F235" t="s">
         <v>859</v>
-      </c>
-      <c r="F235" t="s">
-        <v>802</v>
       </c>
       <c r="G235" t="s">
         <v>803</v>
@@ -11423,13 +11423,13 @@
         <v>860</v>
       </c>
       <c r="I235" t="s">
+        <v>805</v>
+      </c>
+      <c r="J235" t="s">
+        <v>338</v>
+      </c>
+      <c r="K235" t="s">
         <v>861</v>
-      </c>
-      <c r="J235" t="s">
-        <v>806</v>
-      </c>
-      <c r="K235" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -11446,10 +11446,10 @@
         <v>14</v>
       </c>
       <c r="E236" t="s">
+        <v>801</v>
+      </c>
+      <c r="F236" t="s">
         <v>859</v>
-      </c>
-      <c r="F236" t="s">
-        <v>802</v>
       </c>
       <c r="G236" t="s">
         <v>803</v>
@@ -11458,13 +11458,13 @@
         <v>860</v>
       </c>
       <c r="I236" t="s">
+        <v>805</v>
+      </c>
+      <c r="J236" t="s">
+        <v>338</v>
+      </c>
+      <c r="K236" t="s">
         <v>861</v>
-      </c>
-      <c r="J236" t="s">
-        <v>806</v>
-      </c>
-      <c r="K236" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -11481,10 +11481,10 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
+        <v>801</v>
+      </c>
+      <c r="F237" t="s">
         <v>859</v>
-      </c>
-      <c r="F237" t="s">
-        <v>802</v>
       </c>
       <c r="G237" t="s">
         <v>803</v>
@@ -11493,13 +11493,13 @@
         <v>860</v>
       </c>
       <c r="I237" t="s">
+        <v>805</v>
+      </c>
+      <c r="J237" t="s">
+        <v>338</v>
+      </c>
+      <c r="K237" t="s">
         <v>861</v>
-      </c>
-      <c r="J237" t="s">
-        <v>806</v>
-      </c>
-      <c r="K237" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -11516,10 +11516,10 @@
         <v>14</v>
       </c>
       <c r="E238" t="s">
+        <v>801</v>
+      </c>
+      <c r="F238" t="s">
         <v>859</v>
-      </c>
-      <c r="F238" t="s">
-        <v>802</v>
       </c>
       <c r="G238" t="s">
         <v>803</v>
@@ -11528,13 +11528,13 @@
         <v>860</v>
       </c>
       <c r="I238" t="s">
+        <v>805</v>
+      </c>
+      <c r="J238" t="s">
+        <v>338</v>
+      </c>
+      <c r="K238" t="s">
         <v>861</v>
-      </c>
-      <c r="J238" t="s">
-        <v>806</v>
-      </c>
-      <c r="K238" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -11551,10 +11551,10 @@
         <v>14</v>
       </c>
       <c r="E239" t="s">
+        <v>801</v>
+      </c>
+      <c r="F239" t="s">
         <v>892</v>
-      </c>
-      <c r="F239" t="s">
-        <v>802</v>
       </c>
       <c r="G239" t="s">
         <v>803</v>
@@ -11563,13 +11563,13 @@
         <v>893</v>
       </c>
       <c r="I239" t="s">
+        <v>805</v>
+      </c>
+      <c r="J239" t="s">
+        <v>338</v>
+      </c>
+      <c r="K239" t="s">
         <v>894</v>
-      </c>
-      <c r="J239" t="s">
-        <v>806</v>
-      </c>
-      <c r="K239" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -11592,13 +11592,13 @@
         <v>899</v>
       </c>
       <c r="G240" t="s">
+        <v>337</v>
+      </c>
+      <c r="H240" t="s">
         <v>900</v>
       </c>
-      <c r="H240" t="s">
-        <v>337</v>
-      </c>
       <c r="I240" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J240" t="s">
         <v>338</v>
@@ -11627,13 +11627,13 @@
         <v>899</v>
       </c>
       <c r="G241" t="s">
+        <v>337</v>
+      </c>
+      <c r="H241" t="s">
         <v>900</v>
       </c>
-      <c r="H241" t="s">
-        <v>337</v>
-      </c>
       <c r="I241" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J241" t="s">
         <v>338</v>
@@ -11662,13 +11662,13 @@
         <v>899</v>
       </c>
       <c r="G242" t="s">
+        <v>337</v>
+      </c>
+      <c r="H242" t="s">
         <v>900</v>
       </c>
-      <c r="H242" t="s">
-        <v>337</v>
-      </c>
       <c r="I242" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J242" t="s">
         <v>338</v>
@@ -11697,13 +11697,13 @@
         <v>899</v>
       </c>
       <c r="G243" t="s">
+        <v>337</v>
+      </c>
+      <c r="H243" t="s">
         <v>900</v>
       </c>
-      <c r="H243" t="s">
-        <v>337</v>
-      </c>
       <c r="I243" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J243" t="s">
         <v>338</v>
@@ -11732,13 +11732,13 @@
         <v>899</v>
       </c>
       <c r="G244" t="s">
+        <v>337</v>
+      </c>
+      <c r="H244" t="s">
         <v>900</v>
       </c>
-      <c r="H244" t="s">
-        <v>337</v>
-      </c>
       <c r="I244" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J244" t="s">
         <v>338</v>
@@ -11767,13 +11767,13 @@
         <v>899</v>
       </c>
       <c r="G245" t="s">
+        <v>337</v>
+      </c>
+      <c r="H245" t="s">
         <v>900</v>
       </c>
-      <c r="H245" t="s">
-        <v>337</v>
-      </c>
       <c r="I245" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J245" t="s">
         <v>338</v>
@@ -11793,25 +11793,25 @@
         <v>14</v>
       </c>
       <c r="E246" t="s">
+        <v>898</v>
+      </c>
+      <c r="F246" t="s">
         <v>918</v>
       </c>
-      <c r="F246" t="s">
-        <v>899</v>
-      </c>
       <c r="G246" t="s">
-        <v>900</v>
+        <v>533</v>
       </c>
       <c r="H246" t="s">
         <v>919</v>
       </c>
       <c r="I246" t="s">
+        <v>899</v>
+      </c>
+      <c r="J246" t="s">
+        <v>338</v>
+      </c>
+      <c r="K246" t="s">
         <v>920</v>
-      </c>
-      <c r="J246" t="s">
-        <v>534</v>
-      </c>
-      <c r="K246" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11827,14 +11827,14 @@
       <c r="D247" t="s">
         <v>14</v>
       </c>
-      <c r="F247" t="s">
+      <c r="E247" t="s">
         <v>924</v>
       </c>
       <c r="G247" t="s">
+        <v>196</v>
+      </c>
+      <c r="I247" t="s">
         <v>925</v>
-      </c>
-      <c r="H247" t="s">
-        <v>196</v>
       </c>
       <c r="J247" t="s">
         <v>197</v>
@@ -11856,14 +11856,14 @@
       <c r="D248" t="s">
         <v>14</v>
       </c>
-      <c r="F248" t="s">
+      <c r="E248" t="s">
         <v>924</v>
       </c>
       <c r="G248" t="s">
+        <v>196</v>
+      </c>
+      <c r="I248" t="s">
         <v>925</v>
-      </c>
-      <c r="H248" t="s">
-        <v>196</v>
       </c>
       <c r="J248" t="s">
         <v>197</v>
@@ -11885,20 +11885,20 @@
       <c r="D249" t="s">
         <v>14</v>
       </c>
-      <c r="F249" t="s">
+      <c r="E249" t="s">
         <v>924</v>
       </c>
       <c r="G249" t="s">
+        <v>932</v>
+      </c>
+      <c r="I249" t="s">
         <v>925</v>
       </c>
-      <c r="H249" t="s">
-        <v>932</v>
-      </c>
       <c r="J249" t="s">
+        <v>197</v>
+      </c>
+      <c r="K249" t="s">
         <v>933</v>
-      </c>
-      <c r="K249" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -11914,14 +11914,14 @@
       <c r="D250" t="s">
         <v>14</v>
       </c>
-      <c r="F250" t="s">
+      <c r="E250" t="s">
         <v>924</v>
       </c>
       <c r="G250" t="s">
+        <v>196</v>
+      </c>
+      <c r="I250" t="s">
         <v>925</v>
-      </c>
-      <c r="H250" t="s">
-        <v>196</v>
       </c>
       <c r="J250" t="s">
         <v>197</v>
@@ -11940,14 +11940,14 @@
       <c r="D251" t="s">
         <v>14</v>
       </c>
-      <c r="F251" t="s">
+      <c r="E251" t="s">
         <v>924</v>
       </c>
       <c r="G251" t="s">
+        <v>196</v>
+      </c>
+      <c r="I251" t="s">
         <v>925</v>
-      </c>
-      <c r="H251" t="s">
-        <v>196</v>
       </c>
       <c r="J251" t="s">
         <v>197</v>
@@ -11969,14 +11969,14 @@
       <c r="D252" t="s">
         <v>14</v>
       </c>
-      <c r="F252" t="s">
+      <c r="E252" t="s">
         <v>924</v>
       </c>
       <c r="G252" t="s">
+        <v>196</v>
+      </c>
+      <c r="I252" t="s">
         <v>925</v>
-      </c>
-      <c r="H252" t="s">
-        <v>196</v>
       </c>
       <c r="J252" t="s">
         <v>197</v>
@@ -11995,20 +11995,20 @@
       <c r="D253" t="s">
         <v>14</v>
       </c>
-      <c r="F253" t="s">
+      <c r="E253" t="s">
         <v>944</v>
       </c>
       <c r="G253" t="s">
         <v>945</v>
       </c>
-      <c r="H253" t="s">
+      <c r="I253" t="s">
         <v>946</v>
       </c>
       <c r="J253" t="s">
+        <v>338</v>
+      </c>
+      <c r="K253" t="s">
         <v>947</v>
-      </c>
-      <c r="K253" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="254" spans="1:11">
@@ -12024,20 +12024,20 @@
       <c r="D254" t="s">
         <v>14</v>
       </c>
-      <c r="F254" t="s">
+      <c r="E254" t="s">
         <v>944</v>
       </c>
       <c r="G254" t="s">
-        <v>945</v>
-      </c>
-      <c r="H254" t="s">
         <v>454</v>
       </c>
+      <c r="I254" t="s">
+        <v>946</v>
+      </c>
       <c r="J254" t="s">
+        <v>191</v>
+      </c>
+      <c r="K254" t="s">
         <v>455</v>
-      </c>
-      <c r="K254" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -12053,20 +12053,20 @@
       <c r="D255" t="s">
         <v>14</v>
       </c>
-      <c r="F255" t="s">
+      <c r="E255" t="s">
         <v>944</v>
       </c>
       <c r="G255" t="s">
-        <v>945</v>
-      </c>
-      <c r="H255" t="s">
         <v>954</v>
       </c>
+      <c r="I255" t="s">
+        <v>946</v>
+      </c>
       <c r="J255" t="s">
+        <v>191</v>
+      </c>
+      <c r="K255" t="s">
         <v>955</v>
-      </c>
-      <c r="K255" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -12082,20 +12082,20 @@
       <c r="D256" t="s">
         <v>14</v>
       </c>
-      <c r="F256" t="s">
+      <c r="E256" t="s">
         <v>944</v>
       </c>
       <c r="G256" t="s">
-        <v>945</v>
-      </c>
-      <c r="H256" t="s">
         <v>954</v>
       </c>
+      <c r="I256" t="s">
+        <v>946</v>
+      </c>
       <c r="J256" t="s">
+        <v>191</v>
+      </c>
+      <c r="K256" t="s">
         <v>955</v>
-      </c>
-      <c r="K256" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -12111,20 +12111,20 @@
       <c r="D257" t="s">
         <v>14</v>
       </c>
-      <c r="F257" t="s">
+      <c r="E257" t="s">
         <v>944</v>
       </c>
       <c r="G257" t="s">
-        <v>945</v>
-      </c>
-      <c r="H257" t="s">
         <v>954</v>
       </c>
+      <c r="I257" t="s">
+        <v>946</v>
+      </c>
       <c r="J257" t="s">
+        <v>191</v>
+      </c>
+      <c r="K257" t="s">
         <v>955</v>
-      </c>
-      <c r="K257" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -12140,20 +12140,20 @@
       <c r="D258" t="s">
         <v>14</v>
       </c>
-      <c r="F258" t="s">
+      <c r="E258" t="s">
         <v>944</v>
       </c>
       <c r="G258" t="s">
-        <v>945</v>
-      </c>
-      <c r="H258" t="s">
-        <v>708</v>
+        <v>707</v>
+      </c>
+      <c r="I258" t="s">
+        <v>946</v>
       </c>
       <c r="J258" t="s">
+        <v>338</v>
+      </c>
+      <c r="K258" t="s">
         <v>710</v>
-      </c>
-      <c r="K258" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -12169,20 +12169,20 @@
       <c r="D259" t="s">
         <v>14</v>
       </c>
-      <c r="F259" t="s">
+      <c r="E259" t="s">
         <v>944</v>
       </c>
       <c r="G259" t="s">
-        <v>945</v>
-      </c>
-      <c r="H259" t="s">
         <v>954</v>
       </c>
+      <c r="I259" t="s">
+        <v>946</v>
+      </c>
       <c r="J259" t="s">
+        <v>191</v>
+      </c>
+      <c r="K259" t="s">
         <v>955</v>
-      </c>
-      <c r="K259" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -12198,14 +12198,14 @@
       <c r="D260" t="s">
         <v>14</v>
       </c>
-      <c r="F260" t="s">
+      <c r="E260" t="s">
         <v>944</v>
       </c>
       <c r="G260" t="s">
-        <v>945</v>
-      </c>
-      <c r="H260" t="s">
         <v>337</v>
+      </c>
+      <c r="I260" t="s">
+        <v>946</v>
       </c>
       <c r="J260" t="s">
         <v>338</v>
@@ -12227,20 +12227,20 @@
       <c r="D261" t="s">
         <v>14</v>
       </c>
-      <c r="F261" t="s">
+      <c r="E261" t="s">
         <v>944</v>
       </c>
       <c r="G261" t="s">
-        <v>945</v>
-      </c>
-      <c r="H261" t="s">
         <v>973</v>
       </c>
+      <c r="I261" t="s">
+        <v>946</v>
+      </c>
       <c r="J261" t="s">
+        <v>406</v>
+      </c>
+      <c r="K261" t="s">
         <v>974</v>
-      </c>
-      <c r="K261" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -12256,14 +12256,14 @@
       <c r="D262" t="s">
         <v>14</v>
       </c>
-      <c r="F262" t="s">
+      <c r="E262" t="s">
         <v>944</v>
       </c>
       <c r="G262" t="s">
-        <v>945</v>
-      </c>
-      <c r="H262" t="s">
         <v>337</v>
+      </c>
+      <c r="I262" t="s">
+        <v>946</v>
       </c>
       <c r="J262" t="s">
         <v>338</v>
@@ -12285,20 +12285,20 @@
       <c r="D263" t="s">
         <v>14</v>
       </c>
-      <c r="F263" t="s">
+      <c r="E263" t="s">
         <v>944</v>
       </c>
       <c r="G263" t="s">
-        <v>945</v>
-      </c>
-      <c r="H263" t="s">
         <v>981</v>
       </c>
+      <c r="I263" t="s">
+        <v>946</v>
+      </c>
       <c r="J263" t="s">
+        <v>378</v>
+      </c>
+      <c r="K263" t="s">
         <v>982</v>
-      </c>
-      <c r="K263" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="264" spans="1:11">
@@ -12314,14 +12314,14 @@
       <c r="D264" t="s">
         <v>14</v>
       </c>
-      <c r="F264" t="s">
+      <c r="E264" t="s">
         <v>944</v>
       </c>
       <c r="G264" t="s">
-        <v>945</v>
-      </c>
-      <c r="H264" t="s">
         <v>58</v>
+      </c>
+      <c r="I264" t="s">
+        <v>946</v>
       </c>
       <c r="J264" t="s">
         <v>59</v>
@@ -12343,14 +12343,14 @@
       <c r="D265" t="s">
         <v>14</v>
       </c>
-      <c r="F265" t="s">
+      <c r="E265" t="s">
         <v>944</v>
       </c>
       <c r="G265" t="s">
-        <v>945</v>
-      </c>
-      <c r="H265" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="I265" t="s">
+        <v>946</v>
       </c>
       <c r="J265" t="s">
         <v>20</v>
@@ -12372,20 +12372,20 @@
       <c r="D266" t="s">
         <v>14</v>
       </c>
-      <c r="F266" t="s">
+      <c r="E266" t="s">
         <v>944</v>
       </c>
       <c r="G266" t="s">
-        <v>945</v>
-      </c>
-      <c r="H266" t="s">
         <v>992</v>
       </c>
+      <c r="I266" t="s">
+        <v>946</v>
+      </c>
       <c r="J266" t="s">
+        <v>238</v>
+      </c>
+      <c r="K266" t="s">
         <v>993</v>
-      </c>
-      <c r="K266" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="267" spans="1:11">
@@ -12401,20 +12401,20 @@
       <c r="D267" t="s">
         <v>14</v>
       </c>
-      <c r="F267" t="s">
+      <c r="E267" t="s">
         <v>997</v>
       </c>
       <c r="G267" t="s">
+        <v>243</v>
+      </c>
+      <c r="I267" t="s">
         <v>998</v>
       </c>
-      <c r="H267" t="s">
-        <v>243</v>
-      </c>
       <c r="J267" t="s">
+        <v>238</v>
+      </c>
+      <c r="K267" t="s">
         <v>244</v>
-      </c>
-      <c r="K267" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -12430,20 +12430,20 @@
       <c r="D268" t="s">
         <v>14</v>
       </c>
-      <c r="F268" t="s">
+      <c r="E268" t="s">
         <v>1002</v>
       </c>
       <c r="G268" t="s">
+        <v>421</v>
+      </c>
+      <c r="I268" t="s">
         <v>1003</v>
       </c>
-      <c r="H268" t="s">
-        <v>422</v>
-      </c>
       <c r="J268" t="s">
+        <v>378</v>
+      </c>
+      <c r="K268" t="s">
         <v>423</v>
-      </c>
-      <c r="K268" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -12459,20 +12459,20 @@
       <c r="D269" t="s">
         <v>14</v>
       </c>
-      <c r="F269" t="s">
+      <c r="E269" t="s">
         <v>1007</v>
       </c>
       <c r="G269" t="s">
+        <v>243</v>
+      </c>
+      <c r="I269" t="s">
         <v>1008</v>
       </c>
-      <c r="H269" t="s">
-        <v>243</v>
-      </c>
       <c r="J269" t="s">
+        <v>238</v>
+      </c>
+      <c r="K269" t="s">
         <v>244</v>
-      </c>
-      <c r="K269" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -12488,20 +12488,20 @@
       <c r="D270" t="s">
         <v>14</v>
       </c>
-      <c r="F270" t="s">
+      <c r="E270" t="s">
         <v>1007</v>
       </c>
       <c r="G270" t="s">
+        <v>243</v>
+      </c>
+      <c r="I270" t="s">
         <v>1008</v>
       </c>
-      <c r="H270" t="s">
-        <v>243</v>
-      </c>
       <c r="J270" t="s">
+        <v>238</v>
+      </c>
+      <c r="K270" t="s">
         <v>244</v>
-      </c>
-      <c r="K270" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -12517,20 +12517,20 @@
       <c r="D271" t="s">
         <v>14</v>
       </c>
-      <c r="F271" t="s">
+      <c r="E271" t="s">
         <v>1015</v>
       </c>
       <c r="G271" t="s">
         <v>1016</v>
       </c>
-      <c r="H271" t="s">
+      <c r="I271" t="s">
         <v>1017</v>
       </c>
       <c r="J271" t="s">
+        <v>238</v>
+      </c>
+      <c r="K271" t="s">
         <v>1018</v>
-      </c>
-      <c r="K271" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="272" spans="1:11">
@@ -12543,20 +12543,20 @@
       <c r="D272" t="s">
         <v>14</v>
       </c>
-      <c r="F272" t="s">
+      <c r="E272" t="s">
         <v>1015</v>
       </c>
       <c r="G272" t="s">
         <v>1016</v>
       </c>
-      <c r="H272" t="s">
+      <c r="I272" t="s">
         <v>1017</v>
       </c>
       <c r="J272" t="s">
+        <v>238</v>
+      </c>
+      <c r="K272" t="s">
         <v>1018</v>
-      </c>
-      <c r="K272" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="273" spans="1:11">
@@ -12572,20 +12572,20 @@
       <c r="D273" t="s">
         <v>14</v>
       </c>
-      <c r="F273" t="s">
+      <c r="E273" t="s">
         <v>1015</v>
       </c>
       <c r="G273" t="s">
         <v>1016</v>
       </c>
-      <c r="H273" t="s">
+      <c r="I273" t="s">
         <v>1017</v>
       </c>
       <c r="J273" t="s">
+        <v>238</v>
+      </c>
+      <c r="K273" t="s">
         <v>1018</v>
-      </c>
-      <c r="K273" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="274" spans="1:11">
@@ -12598,20 +12598,20 @@
       <c r="D274" t="s">
         <v>14</v>
       </c>
-      <c r="F274" t="s">
+      <c r="E274" t="s">
         <v>1015</v>
       </c>
       <c r="G274" t="s">
         <v>1016</v>
       </c>
-      <c r="H274" t="s">
+      <c r="I274" t="s">
         <v>1017</v>
       </c>
       <c r="J274" t="s">
+        <v>238</v>
+      </c>
+      <c r="K274" t="s">
         <v>1018</v>
-      </c>
-      <c r="K274" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="275" spans="1:11">
@@ -12627,20 +12627,20 @@
       <c r="D275" t="s">
         <v>14</v>
       </c>
-      <c r="F275" t="s">
+      <c r="E275" t="s">
         <v>1015</v>
       </c>
       <c r="G275" t="s">
         <v>1016</v>
       </c>
-      <c r="H275" t="s">
+      <c r="I275" t="s">
         <v>1017</v>
       </c>
       <c r="J275" t="s">
+        <v>238</v>
+      </c>
+      <c r="K275" t="s">
         <v>1018</v>
-      </c>
-      <c r="K275" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="276" spans="1:11">
@@ -12656,20 +12656,20 @@
       <c r="D276" t="s">
         <v>14</v>
       </c>
-      <c r="F276" t="s">
+      <c r="E276" t="s">
         <v>1015</v>
       </c>
       <c r="G276" t="s">
         <v>1016</v>
       </c>
-      <c r="H276" t="s">
+      <c r="I276" t="s">
         <v>1017</v>
       </c>
       <c r="J276" t="s">
+        <v>238</v>
+      </c>
+      <c r="K276" t="s">
         <v>1018</v>
-      </c>
-      <c r="K276" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="277" spans="1:11">
@@ -12685,20 +12685,20 @@
       <c r="D277" t="s">
         <v>14</v>
       </c>
-      <c r="F277" t="s">
+      <c r="E277" t="s">
         <v>1015</v>
       </c>
       <c r="G277" t="s">
         <v>1016</v>
       </c>
-      <c r="H277" t="s">
+      <c r="I277" t="s">
         <v>1017</v>
       </c>
       <c r="J277" t="s">
+        <v>238</v>
+      </c>
+      <c r="K277" t="s">
         <v>1018</v>
-      </c>
-      <c r="K277" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="278" spans="1:11">
@@ -12714,20 +12714,20 @@
       <c r="D278" t="s">
         <v>14</v>
       </c>
-      <c r="F278" t="s">
+      <c r="E278" t="s">
         <v>1038</v>
       </c>
       <c r="G278" t="s">
+        <v>421</v>
+      </c>
+      <c r="I278" t="s">
         <v>1039</v>
       </c>
-      <c r="H278" t="s">
-        <v>422</v>
-      </c>
       <c r="J278" t="s">
+        <v>378</v>
+      </c>
+      <c r="K278" t="s">
         <v>423</v>
-      </c>
-      <c r="K278" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -12743,20 +12743,20 @@
       <c r="D279" t="s">
         <v>14</v>
       </c>
-      <c r="F279" t="s">
+      <c r="E279" t="s">
         <v>1038</v>
       </c>
       <c r="G279" t="s">
+        <v>94</v>
+      </c>
+      <c r="I279" t="s">
         <v>1039</v>
       </c>
-      <c r="H279" t="s">
-        <v>95</v>
-      </c>
       <c r="J279" t="s">
+        <v>59</v>
+      </c>
+      <c r="K279" t="s">
         <v>97</v>
-      </c>
-      <c r="K279" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -12772,14 +12772,14 @@
       <c r="D280" t="s">
         <v>14</v>
       </c>
-      <c r="F280" t="s">
+      <c r="E280" t="s">
         <v>1038</v>
       </c>
       <c r="G280" t="s">
+        <v>17</v>
+      </c>
+      <c r="I280" t="s">
         <v>1039</v>
-      </c>
-      <c r="H280" t="s">
-        <v>18</v>
       </c>
       <c r="J280" t="s">
         <v>20</v>
@@ -12801,20 +12801,20 @@
       <c r="D281" t="s">
         <v>14</v>
       </c>
-      <c r="F281" t="s">
+      <c r="E281" t="s">
         <v>1038</v>
       </c>
       <c r="G281" t="s">
+        <v>352</v>
+      </c>
+      <c r="I281" t="s">
         <v>1039</v>
       </c>
-      <c r="H281" t="s">
-        <v>352</v>
-      </c>
       <c r="J281" t="s">
+        <v>238</v>
+      </c>
+      <c r="K281" t="s">
         <v>353</v>
-      </c>
-      <c r="K281" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -12830,14 +12830,14 @@
       <c r="D282" t="s">
         <v>14</v>
       </c>
-      <c r="F282" t="s">
+      <c r="E282" t="s">
         <v>1038</v>
       </c>
       <c r="G282" t="s">
+        <v>253</v>
+      </c>
+      <c r="I282" t="s">
         <v>1039</v>
-      </c>
-      <c r="H282" t="s">
-        <v>253</v>
       </c>
       <c r="J282" t="s">
         <v>254</v>
@@ -12859,20 +12859,20 @@
       <c r="D283" t="s">
         <v>14</v>
       </c>
-      <c r="F283" t="s">
+      <c r="E283" t="s">
         <v>1055</v>
       </c>
       <c r="G283" t="s">
+        <v>803</v>
+      </c>
+      <c r="I283" t="s">
         <v>1056</v>
       </c>
-      <c r="H283" t="s">
-        <v>893</v>
-      </c>
       <c r="J283" t="s">
-        <v>806</v>
+        <v>338</v>
       </c>
       <c r="K283" t="s">
-        <v>339</v>
+        <v>894</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -12888,14 +12888,14 @@
       <c r="D284" t="s">
         <v>14</v>
       </c>
-      <c r="F284" t="s">
+      <c r="E284" t="s">
         <v>1060</v>
       </c>
       <c r="G284" t="s">
+        <v>253</v>
+      </c>
+      <c r="I284" t="s">
         <v>1061</v>
-      </c>
-      <c r="H284" t="s">
-        <v>253</v>
       </c>
       <c r="J284" t="s">
         <v>254</v>
@@ -12914,20 +12914,20 @@
       <c r="D285" t="s">
         <v>14</v>
       </c>
-      <c r="F285" t="s">
+      <c r="E285" t="s">
         <v>1064</v>
       </c>
       <c r="G285" t="s">
+        <v>352</v>
+      </c>
+      <c r="I285" t="s">
         <v>1065</v>
       </c>
-      <c r="H285" t="s">
-        <v>352</v>
-      </c>
       <c r="J285" t="s">
+        <v>238</v>
+      </c>
+      <c r="K285" t="s">
         <v>353</v>
-      </c>
-      <c r="K285" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -12943,20 +12943,20 @@
       <c r="D286" t="s">
         <v>14</v>
       </c>
-      <c r="F286" t="s">
+      <c r="E286" t="s">
         <v>1069</v>
       </c>
       <c r="G286" t="s">
+        <v>981</v>
+      </c>
+      <c r="I286" t="s">
         <v>1070</v>
       </c>
-      <c r="H286" t="s">
-        <v>981</v>
-      </c>
       <c r="J286" t="s">
+        <v>378</v>
+      </c>
+      <c r="K286" t="s">
         <v>982</v>
-      </c>
-      <c r="K286" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -12972,20 +12972,20 @@
       <c r="D287" t="s">
         <v>14</v>
       </c>
-      <c r="F287" t="s">
+      <c r="E287" t="s">
         <v>1069</v>
       </c>
       <c r="G287" t="s">
+        <v>981</v>
+      </c>
+      <c r="I287" t="s">
         <v>1070</v>
       </c>
-      <c r="H287" t="s">
-        <v>981</v>
-      </c>
       <c r="J287" t="s">
+        <v>378</v>
+      </c>
+      <c r="K287" t="s">
         <v>982</v>
-      </c>
-      <c r="K287" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -13001,20 +13001,20 @@
       <c r="D288" t="s">
         <v>14</v>
       </c>
-      <c r="F288" t="s">
+      <c r="E288" t="s">
         <v>1069</v>
       </c>
       <c r="G288" t="s">
+        <v>75</v>
+      </c>
+      <c r="I288" t="s">
         <v>1070</v>
       </c>
-      <c r="H288" t="s">
-        <v>75</v>
-      </c>
       <c r="J288" t="s">
+        <v>20</v>
+      </c>
+      <c r="K288" t="s">
         <v>76</v>
-      </c>
-      <c r="K288" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -13030,14 +13030,14 @@
       <c r="D289" t="s">
         <v>14</v>
       </c>
-      <c r="F289" t="s">
+      <c r="E289" t="s">
         <v>1069</v>
       </c>
       <c r="G289" t="s">
+        <v>58</v>
+      </c>
+      <c r="I289" t="s">
         <v>1070</v>
-      </c>
-      <c r="H289" t="s">
-        <v>58</v>
       </c>
       <c r="J289" t="s">
         <v>59</v>
@@ -13059,14 +13059,14 @@
       <c r="D290" t="s">
         <v>14</v>
       </c>
-      <c r="F290" t="s">
+      <c r="E290" t="s">
         <v>1069</v>
       </c>
       <c r="G290" t="s">
+        <v>58</v>
+      </c>
+      <c r="I290" t="s">
         <v>1070</v>
-      </c>
-      <c r="H290" t="s">
-        <v>58</v>
       </c>
       <c r="J290" t="s">
         <v>59</v>
@@ -13088,20 +13088,20 @@
       <c r="D291" t="s">
         <v>14</v>
       </c>
-      <c r="F291" t="s">
+      <c r="E291" t="s">
         <v>1069</v>
       </c>
       <c r="G291" t="s">
+        <v>352</v>
+      </c>
+      <c r="I291" t="s">
         <v>1070</v>
       </c>
-      <c r="H291" t="s">
-        <v>352</v>
-      </c>
       <c r="J291" t="s">
+        <v>238</v>
+      </c>
+      <c r="K291" t="s">
         <v>353</v>
-      </c>
-      <c r="K291" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -13117,20 +13117,20 @@
       <c r="D292" t="s">
         <v>14</v>
       </c>
-      <c r="F292" t="s">
+      <c r="E292" t="s">
         <v>1069</v>
       </c>
       <c r="G292" t="s">
+        <v>352</v>
+      </c>
+      <c r="I292" t="s">
         <v>1070</v>
       </c>
-      <c r="H292" t="s">
-        <v>352</v>
-      </c>
       <c r="J292" t="s">
+        <v>238</v>
+      </c>
+      <c r="K292" t="s">
         <v>353</v>
-      </c>
-      <c r="K292" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -13146,20 +13146,20 @@
       <c r="D293" t="s">
         <v>14</v>
       </c>
-      <c r="F293" t="s">
+      <c r="E293" t="s">
         <v>1069</v>
       </c>
       <c r="G293" t="s">
+        <v>352</v>
+      </c>
+      <c r="I293" t="s">
         <v>1070</v>
       </c>
-      <c r="H293" t="s">
-        <v>352</v>
-      </c>
       <c r="J293" t="s">
+        <v>238</v>
+      </c>
+      <c r="K293" t="s">
         <v>353</v>
-      </c>
-      <c r="K293" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -13175,20 +13175,20 @@
       <c r="D294" t="s">
         <v>14</v>
       </c>
-      <c r="F294" t="s">
+      <c r="E294" t="s">
         <v>1069</v>
       </c>
       <c r="G294" t="s">
+        <v>352</v>
+      </c>
+      <c r="I294" t="s">
         <v>1070</v>
       </c>
-      <c r="H294" t="s">
-        <v>352</v>
-      </c>
       <c r="J294" t="s">
+        <v>238</v>
+      </c>
+      <c r="K294" t="s">
         <v>353</v>
-      </c>
-      <c r="K294" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -13204,20 +13204,20 @@
       <c r="D295" t="s">
         <v>14</v>
       </c>
-      <c r="F295" t="s">
+      <c r="E295" t="s">
         <v>1098</v>
       </c>
       <c r="G295" t="s">
+        <v>352</v>
+      </c>
+      <c r="I295" t="s">
         <v>1099</v>
       </c>
-      <c r="H295" t="s">
-        <v>352</v>
-      </c>
       <c r="J295" t="s">
+        <v>238</v>
+      </c>
+      <c r="K295" t="s">
         <v>353</v>
-      </c>
-      <c r="K295" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="296" spans="1:11">
@@ -13233,20 +13233,20 @@
       <c r="D296" t="s">
         <v>14</v>
       </c>
-      <c r="F296" t="s">
+      <c r="E296" t="s">
         <v>1098</v>
       </c>
       <c r="G296" t="s">
+        <v>352</v>
+      </c>
+      <c r="I296" t="s">
         <v>1099</v>
       </c>
-      <c r="H296" t="s">
-        <v>352</v>
-      </c>
       <c r="J296" t="s">
+        <v>238</v>
+      </c>
+      <c r="K296" t="s">
         <v>353</v>
-      </c>
-      <c r="K296" t="s">
-        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -28,27 +28,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:group-name</t>
   </si>
   <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -61,27 +61,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -91,12 +91,12 @@
     <t>Educational buildings, equipment, materials; subsidiary services to education (boarding facilities, staff housing); language training; colloquia, seminars, lectures, etc.</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Research and studies on education effectiveness, relevance and quality; systematic evaluation and monitoring.</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
@@ -130,18 +130,18 @@
     <t>Formal and non-formal primary education for children; all elementary and first cycle systematic instruction; provision of learning materials.</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>Second cycle systematic instruction at junior level.</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -223,15 +223,15 @@
     <t>Second cycle systematic instruction at senior levels.</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>Secondary Education</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Elementary vocational training and secondary level technical education; on-the job training; apprenticeships; including informal vocational training.</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
@@ -256,18 +256,18 @@
     <t>Degree and diploma programmes at universities, colleges and polytechnics; scholarships.</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -277,12 +277,12 @@
     <t>Professional-level vocational training programmes and in-service training.</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
@@ -292,24 +292,24 @@
     <t>Health sector policy, planning and programmes; aid to health ministries, public health administration; institution capacity building and advice; medical insurance programmes; including health system strengthening and health governance; unspecified health activities.</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>Health</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -328,12 +328,12 @@
     <t>General medical research (excluding basic health research and research for prevention and control of NCDs (12382)).</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>Laboratories, specialised clinics and hospitals (including equipment and supplies); ambulances; dental services; medical rehabilitation. Excludes noncommunicable diseases (123xx).</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -367,12 +367,12 @@
     <t>Basic and primary health care programmes; paramedical and nursing care programmes; supply of drugs, medicines and vaccines related to basic health care; activities aimed at achieving universal health coverage.</t>
   </si>
   <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>Basic Health</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -382,12 +382,12 @@
     <t>District-level hospitals, clinics and dispensaries and related medical equipment; excluding specialised hospitals and clinics (12191).</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -460,12 +460,12 @@
     <t>Programmes for the prevention and control of NCDs which cannot be broken down into the codes below.</t>
   </si>
   <si>
+    <t>123</t>
+  </si>
+  <si>
     <t>Non-communicable diseases (NCDs)</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -580,21 +580,21 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -604,15 +604,15 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>Large scale sewerage including trunk sewers and sewage pumping stations; domestic and industrial waste water treatment plants.</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>Municipal and industrial solid waste management, including hazardous and toxic waste; collection, disposal and treatment; landfill areas; composting and reuse.</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -715,27 +715,27 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Fiscal policy and planning; support to ministries of finance; strengthening financial and managerial accountability; public expenditure management; improving financial management systems; budget drafting; inter-governmental fiscal relations, public audit, public debt. (Use code 15114 for domestic revenue mobilisation and code 33120 for customs).</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
@@ -760,12 +760,12 @@
     <t>Decentralisation processes (including political, administrative and fiscal dimensions); intergovernmental relations and federalism; strengthening departments of regional and local government, regional and local authorities and their national associations. (Use specific sector codes for decentralisation of sector management and services.)</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
@@ -775,15 +775,15 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -859,12 +859,12 @@
     <t>Support to administration of developing countries' foreign aid (including triangular and south-south cooperation).</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -943,12 +943,12 @@
     <t>Judicial law and order sectors; policy development within ministries of justice or equivalents.</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
@@ -958,12 +958,12 @@
     <t>Police affairs and services.</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Fire-prevention and fire-fighting affairs and services.</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>Prisons</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
@@ -1027,15 +1027,15 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -1072,12 +1072,12 @@
     <t>Electoral management bodies and processes, election observation, voters' education. (Use code 15230 when in the context of an international peacekeeping operation.)</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -1099,12 +1099,12 @@
     <t>Activities that support free and uncensored flow of information on public issues; activities that increase the editorial and technical skills and the integrity of the print and broadcast media, e.g. training of journalists. (Use codes 22010-22040 for provision of equipment and capital assistance to media.)</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -1147,15 +1147,15 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -1192,12 +1192,12 @@
     <t>Collection, production, management and dissemination of statistics and data related to Government &amp; Civil Society. Includes macroeconomic statistics, government finance, fiscal and public sector statistics, support to development of administrative data infrastructure, civil society surveys.</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -1207,12 +1207,12 @@
     <t>Technical co-operation provided to parliament, government ministries, law enforcement agencies and the judiciary to assist review and reform of the security system to improve democratic governance and civilian control; technical co-operation provided to government to improve civilian oversight and democratic control of budgeting, management, accountability and auditing of security expenditure, including military budgets, as part of a public expenditure management programme; assistance to civil society to enhance its competence and capacity to scrutinise the security system so that it is managed in accordance with democratic norms and principles of accountability, transparency and good governance. [Other than in the context of an international peacekeeping operation (15230)].</t>
   </si>
   <si>
+    <t>152</t>
+  </si>
+  <si>
     <t>Conflict, Peace &amp; Security</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -1231,15 +1231,15 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -1276,18 +1276,18 @@
     <t>Social protection or social security strategies, legislation and administration; institution capacity building and advice; social security and other social schemes; support programmes, cash benefits, pensions and special programmes for older persons, orphans, persons with disabilities, children, mothers with newborns, those living in poverty, without jobs and other vulnerable groups; social dimensions of structural adjustment.</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Social protection schemes in the form of cash or in-kind benefits, including pensions, against the risks linked to old age.</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -1348,12 +1348,12 @@
     <t>Employment policy and planning; institution capacity building and advice; employment creation and income generation programmes; including activities specifically designed for the needs of vulnerable groups.</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
@@ -1363,12 +1363,12 @@
     <t>Housing sector policy, planning and programmes; excluding low-cost housing and slum clearance (16040).</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
@@ -1378,12 +1378,12 @@
     <t>Including slum clearance.</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -1402,15 +1402,15 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -1444,12 +1444,12 @@
     <t>Recreation and sport</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -1528,12 +1528,12 @@
     <t>Road infrastructure, road vehicles; passenger road transport, motor passenger cars.</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -1615,12 +1615,12 @@
     <t>Whether or not related to transportation. Whenever possible, report storage projects under the sector of the resource being stored.</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -1684,12 +1684,12 @@
     <t>Radio and TV links, equipment; newspapers; printing and publishing.</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -1708,24 +1708,24 @@
     <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -1741,12 +1741,12 @@
     <t>Regulation of the energy sector, including wholesale and retail electricity provision.</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>Renewable energy generation programmes that cannot be attributed to one single technology (codes 23220 through 23280 below). Fuelwood/charcoal production should be included under forestry 31261.</t>
   </si>
   <si>
+    <t>232</t>
+  </si>
+  <si>
     <t>Energy generation, renewable sources</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -1870,12 +1870,12 @@
     <t>Thermal power plants including when energy source cannot be determined; combined gas-coal power plants.</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
     <t>Energy generation, non-renewable sources</t>
   </si>
   <si>
-    <t>233</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -1933,12 +1933,12 @@
     <t>Electric power plants that make use of both non-renewable and renewable energy sources.</t>
   </si>
   <si>
+    <t>234</t>
+  </si>
+  <si>
     <t>Hybrid energy plants</t>
   </si>
   <si>
-    <t>234</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
@@ -1948,12 +1948,12 @@
     <t>See note regarding ODA eligibility of nuclear energy.</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -1963,12 +1963,12 @@
     <t>Power plants which are designed to produce heat only.</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
     <t>Energy distribution</t>
   </si>
   <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -2131,24 +2131,24 @@
     <t>Agricultural sector policy, planning and programmes; aid to agricultural ministries; institution capacity building and advice; unspecified agriculture.</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2311,15 +2311,15 @@
     <t>Forestry sector policy, planning and programmes; institution capacity building and advice; forest surveys; unspecified forestry and agro-forestry activities.</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>Forestry</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -2368,15 +2368,15 @@
     <t>Fishing sector policy, planning and programmes; institution capacity building and advice; ocean and coastal fishing; marine and freshwater fish surveys and prospecting; fishing boats/equipment; unspecified fishing activities.</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>Fishing</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -2419,24 +2419,24 @@
     <t>Industrial sector policy, planning and programmes; institution capacity building and advice; unspecified industrial activities; manufacturing of goods not specified below.</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
     <t>Industry</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2593,15 +2593,15 @@
     <t>Mineral and mining sector policy, planning and programmes; mining legislation, mining cadastre, mineral resources inventory, information systems, institution capacity building and advice; unspecified mineral resources exploitation.</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -2692,15 +2692,15 @@
     <t>Construction sector policy and planning; excluding construction activities within specific sectors (e.g., hospital or school construction).</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -2710,15 +2710,15 @@
     <t>Trade policy and planning; support to ministries and departments responsible for trade policy; trade-related legislation and regulatory reforms; policy analysis and implementation of multilateral trade agreements e.g. technical barriers to trade and sanitary and phytosanitary measures (TBT/SPS) except at regional level (see 33130); mainstreaming trade in national development strategies (e.g. poverty reduction strategy papers); wholesale/retail trade; unspecified trade and trade promotion activities.</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -2770,15 +2770,15 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>Tourism</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
-    <t>04.7.3 - Tourism (CS)</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -2812,12 +2812,12 @@
     <t>Including natural reserves and actions in the surrounding areas; other measures to protect endangered or vulnerable species and their habitats (e.g. wetlands preservation).</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -2848,18 +2848,18 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>Other Multisector</t>
   </si>
   <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -2878,12 +2878,12 @@
     <t>Urban development and planning; urban management, land information systems.</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -2935,12 +2935,12 @@
     <t>Disaster risk reduction activities if not sector specific. Comprises risk assessments, structural prevention measures (e.g. flood prevention infrastructure), preparedness measures (e.g. early warning systems) normative prevention measures (e.g. building codes, land-use planning), and risk transfer systems (e.g. insurance schemes, risk funds). Also includes building local and national capacities and supporting the establishment of efficient and sustainable national structures able to promote disaster risk reduction.</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
@@ -2959,12 +2959,12 @@
     <t>Short or longer term household food security programmes and activities that improve the access of households to nutritionally adequate diets (excluding any cash transfers within broader social welfare programmes that do not have a specific food security, food acquisition or nutrition focus which should be reported under code 16010).</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -2992,12 +2992,12 @@
     <t>When sector cannot be identified.</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -3061,16 +3061,16 @@
     <t>Actions falling outside the code headings below.</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
     <t>Action Relating to Debt</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>60020</t>
@@ -3741,16 +3741,16 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
@@ -3759,7 +3759,7 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3811,16 +3811,16 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
@@ -3829,7 +3829,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3846,13 +3846,13 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
         <v>40</v>
@@ -3861,10 +3861,10 @@
         <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3884,19 +3884,19 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
         <v>19</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -3916,13 +3916,13 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
         <v>40</v>
@@ -3931,10 +3931,10 @@
         <v>19</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3951,13 +3951,13 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
         <v>40</v>
@@ -3966,10 +3966,10 @@
         <v>19</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3986,13 +3986,13 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
         <v>40</v>
@@ -4001,10 +4001,10 @@
         <v>19</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K10" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4021,25 +4021,25 @@
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="K11" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4056,25 +4056,25 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K12" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4091,25 +4091,25 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I13" t="s">
         <v>19</v>
       </c>
       <c r="J13" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="K13" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4126,25 +4126,25 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I14" t="s">
         <v>19</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="K14" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4161,13 +4161,13 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
         <v>82</v>
@@ -4176,10 +4176,10 @@
         <v>19</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="K15" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4196,25 +4196,25 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s">
         <v>19</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4237,16 +4237,16 @@
         <v>93</v>
       </c>
       <c r="G17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" t="s">
         <v>94</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>95</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>96</v>
-      </c>
-      <c r="J17" t="s">
-        <v>59</v>
       </c>
       <c r="K17" t="s">
         <v>97</v>
@@ -4272,16 +4272,16 @@
         <v>93</v>
       </c>
       <c r="G18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" t="s">
         <v>94</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>95</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>96</v>
-      </c>
-      <c r="J18" t="s">
-        <v>59</v>
       </c>
       <c r="K18" t="s">
         <v>97</v>
@@ -4301,25 +4301,25 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
         <v>93</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="H19" t="s">
+        <v>105</v>
+      </c>
+      <c r="I19" t="s">
         <v>95</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>96</v>
       </c>
-      <c r="J19" t="s">
-        <v>59</v>
-      </c>
       <c r="K19" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4336,25 +4336,25 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F20" t="s">
         <v>93</v>
       </c>
       <c r="G20" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="H20" t="s">
+        <v>110</v>
+      </c>
+      <c r="I20" t="s">
         <v>95</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>96</v>
       </c>
-      <c r="J20" t="s">
-        <v>59</v>
-      </c>
       <c r="K20" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4377,16 +4377,16 @@
         <v>93</v>
       </c>
       <c r="G21" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" t="s">
         <v>94</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>95</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>96</v>
-      </c>
-      <c r="J21" t="s">
-        <v>59</v>
       </c>
       <c r="K21" t="s">
         <v>97</v>
@@ -4406,25 +4406,25 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F22" t="s">
         <v>117</v>
       </c>
       <c r="G22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H22" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" t="s">
+        <v>95</v>
+      </c>
+      <c r="J22" t="s">
         <v>118</v>
       </c>
-      <c r="I22" t="s">
-        <v>96</v>
-      </c>
-      <c r="J22" t="s">
-        <v>59</v>
-      </c>
       <c r="K22" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4441,25 +4441,25 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
         <v>117</v>
       </c>
       <c r="G23" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="H23" t="s">
+        <v>123</v>
+      </c>
+      <c r="I23" t="s">
+        <v>95</v>
+      </c>
+      <c r="J23" t="s">
         <v>118</v>
       </c>
-      <c r="I23" t="s">
-        <v>96</v>
-      </c>
-      <c r="J23" t="s">
-        <v>59</v>
-      </c>
       <c r="K23" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4476,25 +4476,25 @@
         <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F24" t="s">
         <v>117</v>
       </c>
       <c r="G24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" t="s">
+        <v>95</v>
+      </c>
+      <c r="J24" t="s">
         <v>118</v>
       </c>
-      <c r="I24" t="s">
-        <v>96</v>
-      </c>
-      <c r="J24" t="s">
-        <v>59</v>
-      </c>
       <c r="K24" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4511,25 +4511,25 @@
         <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F25" t="s">
         <v>117</v>
       </c>
       <c r="G25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" t="s">
+        <v>95</v>
+      </c>
+      <c r="J25" t="s">
         <v>118</v>
       </c>
-      <c r="I25" t="s">
-        <v>96</v>
-      </c>
-      <c r="J25" t="s">
-        <v>59</v>
-      </c>
       <c r="K25" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4546,25 +4546,25 @@
         <v>14</v>
       </c>
       <c r="E26" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F26" t="s">
         <v>117</v>
       </c>
       <c r="G26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H26" t="s">
+        <v>60</v>
+      </c>
+      <c r="I26" t="s">
+        <v>95</v>
+      </c>
+      <c r="J26" t="s">
         <v>118</v>
       </c>
-      <c r="I26" t="s">
-        <v>96</v>
-      </c>
-      <c r="J26" t="s">
-        <v>59</v>
-      </c>
       <c r="K26" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4581,25 +4581,25 @@
         <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F27" t="s">
         <v>117</v>
       </c>
       <c r="G27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H27" t="s">
+        <v>60</v>
+      </c>
+      <c r="I27" t="s">
+        <v>95</v>
+      </c>
+      <c r="J27" t="s">
         <v>118</v>
       </c>
-      <c r="I27" t="s">
-        <v>96</v>
-      </c>
-      <c r="J27" t="s">
-        <v>59</v>
-      </c>
       <c r="K27" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4616,25 +4616,25 @@
         <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s">
         <v>117</v>
       </c>
       <c r="G28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I28" t="s">
+        <v>95</v>
+      </c>
+      <c r="J28" t="s">
         <v>118</v>
       </c>
-      <c r="I28" t="s">
-        <v>96</v>
-      </c>
-      <c r="J28" t="s">
-        <v>59</v>
-      </c>
       <c r="K28" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4651,25 +4651,25 @@
         <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F29" t="s">
         <v>117</v>
       </c>
       <c r="G29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H29" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" t="s">
+        <v>95</v>
+      </c>
+      <c r="J29" t="s">
         <v>118</v>
       </c>
-      <c r="I29" t="s">
-        <v>96</v>
-      </c>
-      <c r="J29" t="s">
-        <v>59</v>
-      </c>
       <c r="K29" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4692,16 +4692,16 @@
         <v>117</v>
       </c>
       <c r="G30" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" t="s">
         <v>94</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J30" t="s">
         <v>118</v>
-      </c>
-      <c r="I30" t="s">
-        <v>96</v>
-      </c>
-      <c r="J30" t="s">
-        <v>59</v>
       </c>
       <c r="K30" t="s">
         <v>97</v>
@@ -4721,25 +4721,25 @@
         <v>14</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
         <v>148</v>
       </c>
       <c r="G31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H31" t="s">
+        <v>60</v>
+      </c>
+      <c r="I31" t="s">
+        <v>95</v>
+      </c>
+      <c r="J31" t="s">
         <v>149</v>
       </c>
-      <c r="I31" t="s">
-        <v>96</v>
-      </c>
-      <c r="J31" t="s">
-        <v>59</v>
-      </c>
       <c r="K31" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4756,25 +4756,25 @@
         <v>14</v>
       </c>
       <c r="E32" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F32" t="s">
         <v>148</v>
       </c>
       <c r="G32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H32" t="s">
+        <v>60</v>
+      </c>
+      <c r="I32" t="s">
+        <v>95</v>
+      </c>
+      <c r="J32" t="s">
         <v>149</v>
       </c>
-      <c r="I32" t="s">
-        <v>96</v>
-      </c>
-      <c r="J32" t="s">
-        <v>59</v>
-      </c>
       <c r="K32" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4791,25 +4791,25 @@
         <v>14</v>
       </c>
       <c r="E33" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F33" t="s">
         <v>148</v>
       </c>
       <c r="G33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H33" t="s">
+        <v>60</v>
+      </c>
+      <c r="I33" t="s">
+        <v>95</v>
+      </c>
+      <c r="J33" t="s">
         <v>149</v>
       </c>
-      <c r="I33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J33" t="s">
-        <v>59</v>
-      </c>
       <c r="K33" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4826,25 +4826,25 @@
         <v>14</v>
       </c>
       <c r="E34" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F34" t="s">
         <v>148</v>
       </c>
       <c r="G34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H34" t="s">
+        <v>60</v>
+      </c>
+      <c r="I34" t="s">
+        <v>95</v>
+      </c>
+      <c r="J34" t="s">
         <v>149</v>
       </c>
-      <c r="I34" t="s">
-        <v>96</v>
-      </c>
-      <c r="J34" t="s">
-        <v>59</v>
-      </c>
       <c r="K34" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4861,25 +4861,25 @@
         <v>14</v>
       </c>
       <c r="E35" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="F35" t="s">
         <v>148</v>
       </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H35" t="s">
+        <v>60</v>
+      </c>
+      <c r="I35" t="s">
+        <v>95</v>
+      </c>
+      <c r="J35" t="s">
         <v>149</v>
       </c>
-      <c r="I35" t="s">
-        <v>96</v>
-      </c>
-      <c r="J35" t="s">
-        <v>59</v>
-      </c>
       <c r="K35" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4896,25 +4896,25 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F36" t="s">
         <v>148</v>
       </c>
       <c r="G36" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="H36" t="s">
+        <v>105</v>
+      </c>
+      <c r="I36" t="s">
+        <v>95</v>
+      </c>
+      <c r="J36" t="s">
         <v>149</v>
       </c>
-      <c r="I36" t="s">
-        <v>96</v>
-      </c>
-      <c r="J36" t="s">
-        <v>59</v>
-      </c>
       <c r="K36" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4931,19 +4931,19 @@
         <v>14</v>
       </c>
       <c r="E37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37" t="s">
+        <v>59</v>
+      </c>
+      <c r="H37" t="s">
+        <v>60</v>
+      </c>
+      <c r="I37" t="s">
         <v>168</v>
       </c>
-      <c r="G37" t="s">
-        <v>58</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="K37" t="s">
         <v>169</v>
-      </c>
-      <c r="J37" t="s">
-        <v>59</v>
-      </c>
-      <c r="K37" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4960,19 +4960,19 @@
         <v>14</v>
       </c>
       <c r="E38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38" t="s">
+        <v>59</v>
+      </c>
+      <c r="H38" t="s">
+        <v>60</v>
+      </c>
+      <c r="I38" t="s">
         <v>168</v>
       </c>
-      <c r="G38" t="s">
-        <v>58</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="K38" t="s">
         <v>169</v>
-      </c>
-      <c r="J38" t="s">
-        <v>59</v>
-      </c>
-      <c r="K38" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4989,19 +4989,19 @@
         <v>14</v>
       </c>
       <c r="E39" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" t="s">
+        <v>59</v>
+      </c>
+      <c r="H39" t="s">
+        <v>60</v>
+      </c>
+      <c r="I39" t="s">
         <v>168</v>
       </c>
-      <c r="G39" t="s">
-        <v>58</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="K39" t="s">
         <v>169</v>
-      </c>
-      <c r="J39" t="s">
-        <v>59</v>
-      </c>
-      <c r="K39" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5018,19 +5018,19 @@
         <v>14</v>
       </c>
       <c r="E40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40" t="s">
+        <v>59</v>
+      </c>
+      <c r="H40" t="s">
+        <v>60</v>
+      </c>
+      <c r="I40" t="s">
         <v>168</v>
       </c>
-      <c r="G40" t="s">
-        <v>58</v>
-      </c>
-      <c r="I40" t="s">
+      <c r="K40" t="s">
         <v>169</v>
-      </c>
-      <c r="J40" t="s">
-        <v>59</v>
-      </c>
-      <c r="K40" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5047,19 +5047,19 @@
         <v>14</v>
       </c>
       <c r="E41" t="s">
+        <v>92</v>
+      </c>
+      <c r="G41" t="s">
+        <v>59</v>
+      </c>
+      <c r="H41" t="s">
+        <v>94</v>
+      </c>
+      <c r="I41" t="s">
         <v>168</v>
       </c>
-      <c r="G41" t="s">
-        <v>94</v>
-      </c>
-      <c r="I41" t="s">
+      <c r="K41" t="s">
         <v>169</v>
-      </c>
-      <c r="J41" t="s">
-        <v>59</v>
-      </c>
-      <c r="K41" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5076,19 +5076,19 @@
         <v>14</v>
       </c>
       <c r="E42" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42" t="s">
+        <v>59</v>
+      </c>
+      <c r="H42" t="s">
+        <v>105</v>
+      </c>
+      <c r="I42" t="s">
         <v>168</v>
       </c>
-      <c r="G42" t="s">
-        <v>104</v>
-      </c>
-      <c r="I42" t="s">
+      <c r="K42" t="s">
         <v>169</v>
-      </c>
-      <c r="J42" t="s">
-        <v>59</v>
-      </c>
-      <c r="K42" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5110,10 +5110,10 @@
       <c r="G43" t="s">
         <v>189</v>
       </c>
+      <c r="H43" t="s">
+        <v>190</v>
+      </c>
       <c r="I43" t="s">
-        <v>190</v>
-      </c>
-      <c r="J43" t="s">
         <v>191</v>
       </c>
       <c r="K43" t="s">
@@ -5134,19 +5134,19 @@
         <v>14</v>
       </c>
       <c r="E44" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G44" t="s">
-        <v>196</v>
+        <v>197</v>
+      </c>
+      <c r="H44" t="s">
+        <v>198</v>
       </c>
       <c r="I44" t="s">
-        <v>190</v>
-      </c>
-      <c r="J44" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K44" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5168,10 +5168,10 @@
       <c r="G45" t="s">
         <v>189</v>
       </c>
+      <c r="H45" t="s">
+        <v>190</v>
+      </c>
       <c r="I45" t="s">
-        <v>190</v>
-      </c>
-      <c r="J45" t="s">
         <v>191</v>
       </c>
       <c r="K45" t="s">
@@ -5197,10 +5197,10 @@
       <c r="G46" t="s">
         <v>189</v>
       </c>
+      <c r="H46" t="s">
+        <v>190</v>
+      </c>
       <c r="I46" t="s">
-        <v>190</v>
-      </c>
-      <c r="J46" t="s">
         <v>191</v>
       </c>
       <c r="K46" t="s">
@@ -5221,19 +5221,19 @@
         <v>14</v>
       </c>
       <c r="E47" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="G47" t="s">
-        <v>208</v>
+        <v>197</v>
+      </c>
+      <c r="H47" t="s">
+        <v>209</v>
       </c>
       <c r="I47" t="s">
-        <v>190</v>
-      </c>
-      <c r="J47" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K47" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5255,10 +5255,10 @@
       <c r="G48" t="s">
         <v>189</v>
       </c>
+      <c r="H48" t="s">
+        <v>190</v>
+      </c>
       <c r="I48" t="s">
-        <v>190</v>
-      </c>
-      <c r="J48" t="s">
         <v>191</v>
       </c>
       <c r="K48" t="s">
@@ -5284,10 +5284,10 @@
       <c r="G49" t="s">
         <v>189</v>
       </c>
+      <c r="H49" t="s">
+        <v>190</v>
+      </c>
       <c r="I49" t="s">
-        <v>190</v>
-      </c>
-      <c r="J49" t="s">
         <v>191</v>
       </c>
       <c r="K49" t="s">
@@ -5308,19 +5308,19 @@
         <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="G50" t="s">
-        <v>208</v>
+        <v>197</v>
+      </c>
+      <c r="H50" t="s">
+        <v>209</v>
       </c>
       <c r="I50" t="s">
-        <v>190</v>
-      </c>
-      <c r="J50" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K50" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5342,10 +5342,10 @@
       <c r="G51" t="s">
         <v>189</v>
       </c>
+      <c r="H51" t="s">
+        <v>190</v>
+      </c>
       <c r="I51" t="s">
-        <v>190</v>
-      </c>
-      <c r="J51" t="s">
         <v>191</v>
       </c>
       <c r="K51" t="s">
@@ -5366,19 +5366,19 @@
         <v>14</v>
       </c>
       <c r="E52" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="G52" t="s">
-        <v>225</v>
+        <v>197</v>
+      </c>
+      <c r="H52" t="s">
+        <v>226</v>
       </c>
       <c r="I52" t="s">
-        <v>190</v>
-      </c>
-      <c r="J52" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K52" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5395,19 +5395,19 @@
         <v>14</v>
       </c>
       <c r="E53" t="s">
-        <v>188</v>
+        <v>15</v>
       </c>
       <c r="G53" t="s">
         <v>17</v>
       </c>
+      <c r="H53" t="s">
+        <v>18</v>
+      </c>
       <c r="I53" t="s">
-        <v>190</v>
-      </c>
-      <c r="J53" t="s">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="K53" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5459,16 +5459,16 @@
         <v>14</v>
       </c>
       <c r="E55" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F55" t="s">
         <v>234</v>
       </c>
       <c r="G55" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H55" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I55" t="s">
         <v>237</v>
@@ -5477,7 +5477,7 @@
         <v>238</v>
       </c>
       <c r="K55" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -5494,16 +5494,16 @@
         <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F56" t="s">
         <v>234</v>
       </c>
       <c r="G56" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="H56" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="I56" t="s">
         <v>237</v>
@@ -5512,7 +5512,7 @@
         <v>238</v>
       </c>
       <c r="K56" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -5529,25 +5529,25 @@
         <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F57" t="s">
         <v>234</v>
       </c>
       <c r="G57" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H57" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I57" t="s">
         <v>237</v>
       </c>
       <c r="J57" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K57" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5564,16 +5564,16 @@
         <v>14</v>
       </c>
       <c r="E58" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F58" t="s">
         <v>234</v>
       </c>
       <c r="G58" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H58" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I58" t="s">
         <v>237</v>
@@ -5582,7 +5582,7 @@
         <v>238</v>
       </c>
       <c r="K58" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5599,16 +5599,16 @@
         <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F59" t="s">
         <v>234</v>
       </c>
       <c r="G59" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H59" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I59" t="s">
         <v>237</v>
@@ -5617,7 +5617,7 @@
         <v>238</v>
       </c>
       <c r="K59" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5634,16 +5634,16 @@
         <v>14</v>
       </c>
       <c r="E60" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F60" t="s">
         <v>234</v>
       </c>
       <c r="G60" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H60" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I60" t="s">
         <v>237</v>
@@ -5652,7 +5652,7 @@
         <v>238</v>
       </c>
       <c r="K60" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -5669,16 +5669,16 @@
         <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F61" t="s">
         <v>234</v>
       </c>
       <c r="G61" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H61" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I61" t="s">
         <v>237</v>
@@ -5687,7 +5687,7 @@
         <v>238</v>
       </c>
       <c r="K61" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -5704,16 +5704,16 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F62" t="s">
         <v>234</v>
       </c>
       <c r="G62" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H62" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I62" t="s">
         <v>237</v>
@@ -5722,7 +5722,7 @@
         <v>238</v>
       </c>
       <c r="K62" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -5739,16 +5739,16 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="F63" t="s">
         <v>234</v>
       </c>
       <c r="G63" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H63" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I63" t="s">
         <v>237</v>
@@ -5757,7 +5757,7 @@
         <v>238</v>
       </c>
       <c r="K63" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -5774,16 +5774,16 @@
         <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="F64" t="s">
         <v>234</v>
       </c>
       <c r="G64" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H64" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I64" t="s">
         <v>237</v>
@@ -5792,7 +5792,7 @@
         <v>238</v>
       </c>
       <c r="K64" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -5809,16 +5809,16 @@
         <v>14</v>
       </c>
       <c r="E65" t="s">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="F65" t="s">
         <v>234</v>
       </c>
       <c r="G65" t="s">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="H65" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="I65" t="s">
         <v>237</v>
@@ -5827,7 +5827,7 @@
         <v>238</v>
       </c>
       <c r="K65" t="s">
-        <v>282</v>
+        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5879,16 +5879,16 @@
         <v>14</v>
       </c>
       <c r="E67" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F67" t="s">
         <v>234</v>
       </c>
       <c r="G67" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H67" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I67" t="s">
         <v>237</v>
@@ -5897,7 +5897,7 @@
         <v>238</v>
       </c>
       <c r="K67" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5914,7 +5914,7 @@
         <v>14</v>
       </c>
       <c r="E68" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="F68" t="s">
         <v>234</v>
@@ -5932,7 +5932,7 @@
         <v>238</v>
       </c>
       <c r="K68" t="s">
-        <v>292</v>
+        <v>239</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -5949,7 +5949,7 @@
         <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="F69" t="s">
         <v>234</v>
@@ -5967,7 +5967,7 @@
         <v>238</v>
       </c>
       <c r="K69" t="s">
-        <v>296</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -5984,16 +5984,16 @@
         <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F70" t="s">
         <v>234</v>
       </c>
       <c r="G70" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="H70" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="I70" t="s">
         <v>237</v>
@@ -6002,7 +6002,7 @@
         <v>238</v>
       </c>
       <c r="K70" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -6019,16 +6019,16 @@
         <v>14</v>
       </c>
       <c r="E71" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F71" t="s">
         <v>234</v>
       </c>
       <c r="G71" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="H71" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="I71" t="s">
         <v>237</v>
@@ -6037,7 +6037,7 @@
         <v>238</v>
       </c>
       <c r="K71" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6089,25 +6089,25 @@
         <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="F73" t="s">
         <v>234</v>
       </c>
       <c r="G73" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="H73" t="s">
-        <v>236</v>
+        <v>310</v>
       </c>
       <c r="I73" t="s">
         <v>237</v>
       </c>
       <c r="J73" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K73" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6124,25 +6124,25 @@
         <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>233</v>
+        <v>314</v>
       </c>
       <c r="F74" t="s">
         <v>234</v>
       </c>
       <c r="G74" t="s">
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="H74" t="s">
-        <v>236</v>
+        <v>315</v>
       </c>
       <c r="I74" t="s">
         <v>237</v>
       </c>
       <c r="J74" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K74" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6159,25 +6159,25 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="F75" t="s">
         <v>234</v>
       </c>
       <c r="G75" t="s">
-        <v>319</v>
+        <v>254</v>
       </c>
       <c r="H75" t="s">
-        <v>236</v>
+        <v>320</v>
       </c>
       <c r="I75" t="s">
         <v>237</v>
       </c>
       <c r="J75" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K75" t="s">
-        <v>320</v>
+        <v>239</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6194,25 +6194,25 @@
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="F76" t="s">
         <v>234</v>
       </c>
       <c r="G76" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="H76" t="s">
-        <v>236</v>
+        <v>310</v>
       </c>
       <c r="I76" t="s">
         <v>237</v>
       </c>
       <c r="J76" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K76" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -6229,25 +6229,25 @@
         <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="F77" t="s">
         <v>234</v>
       </c>
       <c r="G77" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="H77" t="s">
-        <v>236</v>
+        <v>310</v>
       </c>
       <c r="I77" t="s">
         <v>237</v>
       </c>
       <c r="J77" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K77" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -6264,25 +6264,25 @@
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>233</v>
+        <v>314</v>
       </c>
       <c r="F78" t="s">
         <v>234</v>
       </c>
       <c r="G78" t="s">
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="H78" t="s">
-        <v>236</v>
+        <v>315</v>
       </c>
       <c r="I78" t="s">
         <v>237</v>
       </c>
       <c r="J78" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K78" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -6296,25 +6296,25 @@
         <v>14</v>
       </c>
       <c r="E79" t="s">
-        <v>233</v>
+        <v>332</v>
       </c>
       <c r="F79" t="s">
         <v>234</v>
       </c>
       <c r="G79" t="s">
-        <v>332</v>
+        <v>254</v>
       </c>
       <c r="H79" t="s">
-        <v>236</v>
+        <v>333</v>
       </c>
       <c r="I79" t="s">
         <v>237</v>
       </c>
       <c r="J79" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K79" t="s">
-        <v>333</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -6331,25 +6331,25 @@
         <v>14</v>
       </c>
       <c r="E80" t="s">
-        <v>233</v>
+        <v>337</v>
       </c>
       <c r="F80" t="s">
         <v>234</v>
       </c>
       <c r="G80" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H80" t="s">
-        <v>236</v>
+        <v>339</v>
       </c>
       <c r="I80" t="s">
         <v>237</v>
       </c>
       <c r="J80" t="s">
-        <v>338</v>
+        <v>238</v>
       </c>
       <c r="K80" t="s">
-        <v>339</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -6366,25 +6366,25 @@
         <v>14</v>
       </c>
       <c r="E81" t="s">
-        <v>233</v>
+        <v>337</v>
       </c>
       <c r="F81" t="s">
         <v>234</v>
       </c>
       <c r="G81" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H81" t="s">
-        <v>236</v>
+        <v>339</v>
       </c>
       <c r="I81" t="s">
         <v>237</v>
       </c>
       <c r="J81" t="s">
-        <v>338</v>
+        <v>238</v>
       </c>
       <c r="K81" t="s">
-        <v>339</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -6401,25 +6401,25 @@
         <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>233</v>
+        <v>337</v>
       </c>
       <c r="F82" t="s">
         <v>234</v>
       </c>
       <c r="G82" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H82" t="s">
-        <v>236</v>
+        <v>339</v>
       </c>
       <c r="I82" t="s">
         <v>237</v>
       </c>
       <c r="J82" t="s">
-        <v>338</v>
+        <v>238</v>
       </c>
       <c r="K82" t="s">
-        <v>339</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -6436,7 +6436,7 @@
         <v>14</v>
       </c>
       <c r="E83" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="F83" t="s">
         <v>234</v>
@@ -6454,7 +6454,7 @@
         <v>238</v>
       </c>
       <c r="K83" t="s">
-        <v>296</v>
+        <v>239</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -6471,16 +6471,16 @@
         <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="F84" t="s">
         <v>234</v>
       </c>
       <c r="G84" t="s">
-        <v>352</v>
+        <v>235</v>
       </c>
       <c r="H84" t="s">
-        <v>236</v>
+        <v>353</v>
       </c>
       <c r="I84" t="s">
         <v>237</v>
@@ -6489,7 +6489,7 @@
         <v>238</v>
       </c>
       <c r="K84" t="s">
-        <v>353</v>
+        <v>239</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -6506,16 +6506,16 @@
         <v>14</v>
       </c>
       <c r="E85" t="s">
-        <v>233</v>
+        <v>357</v>
       </c>
       <c r="F85" t="s">
         <v>234</v>
       </c>
       <c r="G85" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H85" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I85" t="s">
         <v>237</v>
@@ -6524,7 +6524,7 @@
         <v>238</v>
       </c>
       <c r="K85" t="s">
-        <v>357</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -6541,25 +6541,25 @@
         <v>14</v>
       </c>
       <c r="E86" t="s">
-        <v>233</v>
+        <v>361</v>
       </c>
       <c r="F86" t="s">
         <v>234</v>
       </c>
       <c r="G86" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="H86" t="s">
-        <v>236</v>
+        <v>362</v>
       </c>
       <c r="I86" t="s">
         <v>237</v>
       </c>
       <c r="J86" t="s">
-        <v>338</v>
+        <v>238</v>
       </c>
       <c r="K86" t="s">
-        <v>362</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -6576,16 +6576,16 @@
         <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>233</v>
+        <v>357</v>
       </c>
       <c r="F87" t="s">
         <v>234</v>
       </c>
       <c r="G87" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H87" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I87" t="s">
         <v>237</v>
@@ -6594,7 +6594,7 @@
         <v>238</v>
       </c>
       <c r="K87" t="s">
-        <v>357</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -6608,16 +6608,16 @@
         <v>14</v>
       </c>
       <c r="E88" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F88" t="s">
         <v>234</v>
       </c>
       <c r="G88" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H88" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I88" t="s">
         <v>237</v>
@@ -6626,7 +6626,7 @@
         <v>238</v>
       </c>
       <c r="K88" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -6643,16 +6643,16 @@
         <v>14</v>
       </c>
       <c r="E89" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F89" t="s">
         <v>234</v>
       </c>
       <c r="G89" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H89" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I89" t="s">
         <v>237</v>
@@ -6661,7 +6661,7 @@
         <v>238</v>
       </c>
       <c r="K89" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -6678,25 +6678,25 @@
         <v>14</v>
       </c>
       <c r="E90" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F90" t="s">
         <v>234</v>
       </c>
       <c r="G90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H90" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I90" t="s">
         <v>237</v>
       </c>
       <c r="J90" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K90" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -6713,25 +6713,25 @@
         <v>14</v>
       </c>
       <c r="E91" t="s">
-        <v>233</v>
+        <v>377</v>
       </c>
       <c r="F91" t="s">
         <v>234</v>
       </c>
       <c r="G91" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H91" t="s">
-        <v>236</v>
+        <v>379</v>
       </c>
       <c r="I91" t="s">
         <v>237</v>
       </c>
       <c r="J91" t="s">
-        <v>378</v>
+        <v>238</v>
       </c>
       <c r="K91" t="s">
-        <v>379</v>
+        <v>239</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -6748,25 +6748,25 @@
         <v>14</v>
       </c>
       <c r="E92" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F92" t="s">
         <v>234</v>
       </c>
       <c r="G92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H92" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I92" t="s">
         <v>237</v>
       </c>
       <c r="J92" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K92" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -6783,16 +6783,16 @@
         <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F93" t="s">
         <v>234</v>
       </c>
       <c r="G93" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="H93" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="I93" t="s">
         <v>237</v>
@@ -6801,7 +6801,7 @@
         <v>238</v>
       </c>
       <c r="K93" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -6818,25 +6818,25 @@
         <v>14</v>
       </c>
       <c r="E94" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F94" t="s">
         <v>234</v>
       </c>
       <c r="G94" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H94" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I94" t="s">
         <v>237</v>
       </c>
       <c r="J94" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K94" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -6853,16 +6853,16 @@
         <v>14</v>
       </c>
       <c r="E95" t="s">
-        <v>233</v>
+        <v>392</v>
       </c>
       <c r="F95" t="s">
         <v>234</v>
       </c>
       <c r="G95" t="s">
-        <v>392</v>
+        <v>235</v>
       </c>
       <c r="H95" t="s">
-        <v>236</v>
+        <v>393</v>
       </c>
       <c r="I95" t="s">
         <v>237</v>
@@ -6871,7 +6871,7 @@
         <v>238</v>
       </c>
       <c r="K95" t="s">
-        <v>393</v>
+        <v>239</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -6888,25 +6888,25 @@
         <v>14</v>
       </c>
       <c r="E96" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F96" t="s">
         <v>397</v>
       </c>
       <c r="G96" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H96" t="s">
-        <v>398</v>
+        <v>255</v>
       </c>
       <c r="I96" t="s">
         <v>237</v>
       </c>
       <c r="J96" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="K96" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -6923,25 +6923,25 @@
         <v>14</v>
       </c>
       <c r="E97" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F97" t="s">
         <v>397</v>
       </c>
       <c r="G97" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H97" t="s">
-        <v>398</v>
+        <v>255</v>
       </c>
       <c r="I97" t="s">
         <v>237</v>
       </c>
       <c r="J97" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="K97" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -6958,25 +6958,25 @@
         <v>14</v>
       </c>
       <c r="E98" t="s">
-        <v>233</v>
+        <v>405</v>
       </c>
       <c r="F98" t="s">
         <v>397</v>
       </c>
       <c r="G98" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H98" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="I98" t="s">
         <v>237</v>
       </c>
       <c r="J98" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="K98" t="s">
-        <v>407</v>
+        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -6993,25 +6993,25 @@
         <v>14</v>
       </c>
       <c r="E99" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F99" t="s">
         <v>397</v>
       </c>
       <c r="G99" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H99" t="s">
-        <v>398</v>
+        <v>255</v>
       </c>
       <c r="I99" t="s">
         <v>237</v>
       </c>
       <c r="J99" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="K99" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -7028,25 +7028,25 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="F100" t="s">
         <v>397</v>
       </c>
       <c r="G100" t="s">
-        <v>319</v>
+        <v>254</v>
       </c>
       <c r="H100" t="s">
-        <v>398</v>
+        <v>320</v>
       </c>
       <c r="I100" t="s">
         <v>237</v>
       </c>
       <c r="J100" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="K100" t="s">
-        <v>320</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -7063,25 +7063,25 @@
         <v>14</v>
       </c>
       <c r="E101" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F101" t="s">
         <v>397</v>
       </c>
       <c r="G101" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H101" t="s">
-        <v>398</v>
+        <v>255</v>
       </c>
       <c r="I101" t="s">
         <v>237</v>
       </c>
       <c r="J101" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="K101" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -7101,13 +7101,13 @@
         <v>420</v>
       </c>
       <c r="G102" t="s">
+        <v>378</v>
+      </c>
+      <c r="H102" t="s">
         <v>421</v>
       </c>
       <c r="I102" t="s">
         <v>422</v>
-      </c>
-      <c r="J102" t="s">
-        <v>378</v>
       </c>
       <c r="K102" t="s">
         <v>423</v>
@@ -7130,13 +7130,13 @@
         <v>420</v>
       </c>
       <c r="G103" t="s">
+        <v>378</v>
+      </c>
+      <c r="H103" t="s">
         <v>421</v>
       </c>
       <c r="I103" t="s">
         <v>422</v>
-      </c>
-      <c r="J103" t="s">
-        <v>378</v>
       </c>
       <c r="K103" t="s">
         <v>423</v>
@@ -7159,13 +7159,13 @@
         <v>420</v>
       </c>
       <c r="G104" t="s">
+        <v>378</v>
+      </c>
+      <c r="H104" t="s">
         <v>421</v>
       </c>
       <c r="I104" t="s">
         <v>422</v>
-      </c>
-      <c r="J104" t="s">
-        <v>378</v>
       </c>
       <c r="K104" t="s">
         <v>423</v>
@@ -7185,19 +7185,19 @@
         <v>14</v>
       </c>
       <c r="E105" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="G105" t="s">
-        <v>433</v>
+        <v>378</v>
+      </c>
+      <c r="H105" t="s">
+        <v>434</v>
       </c>
       <c r="I105" t="s">
         <v>422</v>
       </c>
-      <c r="J105" t="s">
-        <v>378</v>
-      </c>
       <c r="K105" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7217,13 +7217,13 @@
         <v>420</v>
       </c>
       <c r="G106" t="s">
+        <v>378</v>
+      </c>
+      <c r="H106" t="s">
         <v>421</v>
       </c>
       <c r="I106" t="s">
         <v>422</v>
-      </c>
-      <c r="J106" t="s">
-        <v>378</v>
       </c>
       <c r="K106" t="s">
         <v>423</v>
@@ -7243,19 +7243,19 @@
         <v>14</v>
       </c>
       <c r="E107" t="s">
-        <v>420</v>
+        <v>377</v>
       </c>
       <c r="G107" t="s">
-        <v>377</v>
+        <v>378</v>
+      </c>
+      <c r="H107" t="s">
+        <v>379</v>
       </c>
       <c r="I107" t="s">
         <v>422</v>
       </c>
-      <c r="J107" t="s">
-        <v>378</v>
-      </c>
       <c r="K107" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -7272,19 +7272,19 @@
         <v>14</v>
       </c>
       <c r="E108" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="G108" t="s">
-        <v>444</v>
+        <v>378</v>
+      </c>
+      <c r="H108" t="s">
+        <v>445</v>
       </c>
       <c r="I108" t="s">
         <v>422</v>
       </c>
-      <c r="J108" t="s">
-        <v>378</v>
-      </c>
       <c r="K108" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7301,19 +7301,19 @@
         <v>14</v>
       </c>
       <c r="E109" t="s">
-        <v>420</v>
+        <v>449</v>
       </c>
       <c r="G109" t="s">
-        <v>449</v>
+        <v>189</v>
+      </c>
+      <c r="H109" t="s">
+        <v>450</v>
       </c>
       <c r="I109" t="s">
         <v>422</v>
       </c>
-      <c r="J109" t="s">
-        <v>191</v>
-      </c>
       <c r="K109" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -7330,19 +7330,19 @@
         <v>14</v>
       </c>
       <c r="E110" t="s">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="G110" t="s">
-        <v>454</v>
+        <v>189</v>
+      </c>
+      <c r="H110" t="s">
+        <v>455</v>
       </c>
       <c r="I110" t="s">
         <v>422</v>
       </c>
-      <c r="J110" t="s">
-        <v>191</v>
-      </c>
       <c r="K110" t="s">
-        <v>455</v>
+        <v>423</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -7362,13 +7362,13 @@
         <v>420</v>
       </c>
       <c r="G111" t="s">
+        <v>378</v>
+      </c>
+      <c r="H111" t="s">
         <v>421</v>
       </c>
       <c r="I111" t="s">
         <v>422</v>
-      </c>
-      <c r="J111" t="s">
-        <v>378</v>
       </c>
       <c r="K111" t="s">
         <v>423</v>
@@ -7388,19 +7388,19 @@
         <v>14</v>
       </c>
       <c r="E112" t="s">
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="G112" t="s">
-        <v>462</v>
+        <v>463</v>
+      </c>
+      <c r="H112" t="s">
+        <v>464</v>
       </c>
       <c r="I112" t="s">
         <v>422</v>
       </c>
-      <c r="J112" t="s">
-        <v>463</v>
-      </c>
       <c r="K112" t="s">
-        <v>464</v>
+        <v>423</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -7417,19 +7417,19 @@
         <v>14</v>
       </c>
       <c r="E113" t="s">
-        <v>420</v>
+        <v>296</v>
       </c>
       <c r="G113" t="s">
         <v>235</v>
       </c>
+      <c r="H113" t="s">
+        <v>236</v>
+      </c>
       <c r="I113" t="s">
         <v>422</v>
       </c>
-      <c r="J113" t="s">
-        <v>238</v>
-      </c>
       <c r="K113" t="s">
-        <v>296</v>
+        <v>423</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -7446,19 +7446,19 @@
         <v>14</v>
       </c>
       <c r="E114" t="s">
-        <v>420</v>
+        <v>314</v>
       </c>
       <c r="G114" t="s">
-        <v>314</v>
+        <v>254</v>
+      </c>
+      <c r="H114" t="s">
+        <v>315</v>
       </c>
       <c r="I114" t="s">
         <v>422</v>
       </c>
-      <c r="J114" t="s">
-        <v>254</v>
-      </c>
       <c r="K114" t="s">
-        <v>315</v>
+        <v>423</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -7475,19 +7475,19 @@
         <v>14</v>
       </c>
       <c r="E115" t="s">
-        <v>420</v>
+        <v>377</v>
       </c>
       <c r="G115" t="s">
-        <v>377</v>
+        <v>378</v>
+      </c>
+      <c r="H115" t="s">
+        <v>379</v>
       </c>
       <c r="I115" t="s">
         <v>422</v>
       </c>
-      <c r="J115" t="s">
-        <v>378</v>
-      </c>
       <c r="K115" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -7501,19 +7501,19 @@
         <v>14</v>
       </c>
       <c r="E116" t="s">
-        <v>420</v>
+        <v>476</v>
       </c>
       <c r="G116" t="s">
-        <v>476</v>
+        <v>463</v>
+      </c>
+      <c r="H116" t="s">
+        <v>477</v>
       </c>
       <c r="I116" t="s">
         <v>422</v>
       </c>
-      <c r="J116" t="s">
-        <v>463</v>
-      </c>
       <c r="K116" t="s">
-        <v>477</v>
+        <v>423</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -7527,19 +7527,19 @@
         <v>14</v>
       </c>
       <c r="E117" t="s">
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="G117" t="s">
-        <v>462</v>
+        <v>463</v>
+      </c>
+      <c r="H117" t="s">
+        <v>464</v>
       </c>
       <c r="I117" t="s">
         <v>422</v>
       </c>
-      <c r="J117" t="s">
-        <v>463</v>
-      </c>
       <c r="K117" t="s">
-        <v>464</v>
+        <v>423</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -7556,19 +7556,19 @@
         <v>14</v>
       </c>
       <c r="E118" t="s">
-        <v>420</v>
+        <v>483</v>
       </c>
       <c r="G118" t="s">
-        <v>337</v>
+        <v>338</v>
+      </c>
+      <c r="H118" t="s">
+        <v>339</v>
       </c>
       <c r="I118" t="s">
         <v>422</v>
       </c>
-      <c r="J118" t="s">
-        <v>338</v>
-      </c>
       <c r="K118" t="s">
-        <v>483</v>
+        <v>423</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -7585,19 +7585,19 @@
         <v>14</v>
       </c>
       <c r="E119" t="s">
-        <v>420</v>
+        <v>377</v>
       </c>
       <c r="G119" t="s">
-        <v>377</v>
+        <v>378</v>
+      </c>
+      <c r="H119" t="s">
+        <v>379</v>
       </c>
       <c r="I119" t="s">
         <v>422</v>
       </c>
-      <c r="J119" t="s">
-        <v>378</v>
-      </c>
       <c r="K119" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -7614,19 +7614,19 @@
         <v>14</v>
       </c>
       <c r="E120" t="s">
+        <v>352</v>
+      </c>
+      <c r="G120" t="s">
+        <v>235</v>
+      </c>
+      <c r="H120" t="s">
+        <v>353</v>
+      </c>
+      <c r="I120" t="s">
         <v>490</v>
       </c>
-      <c r="G120" t="s">
-        <v>352</v>
-      </c>
-      <c r="I120" t="s">
+      <c r="K120" t="s">
         <v>491</v>
-      </c>
-      <c r="J120" t="s">
-        <v>238</v>
-      </c>
-      <c r="K120" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -7643,19 +7643,19 @@
         <v>14</v>
       </c>
       <c r="E121" t="s">
-        <v>490</v>
+        <v>296</v>
       </c>
       <c r="G121" t="s">
         <v>235</v>
       </c>
+      <c r="H121" t="s">
+        <v>236</v>
+      </c>
       <c r="I121" t="s">
+        <v>490</v>
+      </c>
+      <c r="K121" t="s">
         <v>491</v>
-      </c>
-      <c r="J121" t="s">
-        <v>238</v>
-      </c>
-      <c r="K121" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -7672,19 +7672,19 @@
         <v>14</v>
       </c>
       <c r="E122" t="s">
+        <v>352</v>
+      </c>
+      <c r="G122" t="s">
+        <v>235</v>
+      </c>
+      <c r="H122" t="s">
+        <v>353</v>
+      </c>
+      <c r="I122" t="s">
         <v>490</v>
       </c>
-      <c r="G122" t="s">
-        <v>352</v>
-      </c>
-      <c r="I122" t="s">
+      <c r="K122" t="s">
         <v>491</v>
-      </c>
-      <c r="J122" t="s">
-        <v>238</v>
-      </c>
-      <c r="K122" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -7701,19 +7701,19 @@
         <v>14</v>
       </c>
       <c r="E123" t="s">
+        <v>352</v>
+      </c>
+      <c r="G123" t="s">
+        <v>235</v>
+      </c>
+      <c r="H123" t="s">
+        <v>353</v>
+      </c>
+      <c r="I123" t="s">
         <v>490</v>
       </c>
-      <c r="G123" t="s">
-        <v>352</v>
-      </c>
-      <c r="I123" t="s">
+      <c r="K123" t="s">
         <v>491</v>
-      </c>
-      <c r="J123" t="s">
-        <v>238</v>
-      </c>
-      <c r="K123" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -7730,19 +7730,19 @@
         <v>14</v>
       </c>
       <c r="E124" t="s">
+        <v>504</v>
+      </c>
+      <c r="G124" t="s">
+        <v>338</v>
+      </c>
+      <c r="H124" t="s">
+        <v>505</v>
+      </c>
+      <c r="I124" t="s">
         <v>490</v>
       </c>
-      <c r="G124" t="s">
-        <v>504</v>
-      </c>
-      <c r="I124" t="s">
+      <c r="K124" t="s">
         <v>491</v>
-      </c>
-      <c r="J124" t="s">
-        <v>338</v>
-      </c>
-      <c r="K124" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -7759,19 +7759,19 @@
         <v>14</v>
       </c>
       <c r="E125" t="s">
+        <v>504</v>
+      </c>
+      <c r="G125" t="s">
+        <v>338</v>
+      </c>
+      <c r="H125" t="s">
+        <v>505</v>
+      </c>
+      <c r="I125" t="s">
         <v>490</v>
       </c>
-      <c r="G125" t="s">
-        <v>504</v>
-      </c>
-      <c r="I125" t="s">
+      <c r="K125" t="s">
         <v>491</v>
-      </c>
-      <c r="J125" t="s">
-        <v>338</v>
-      </c>
-      <c r="K125" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -7788,19 +7788,19 @@
         <v>14</v>
       </c>
       <c r="E126" t="s">
+        <v>504</v>
+      </c>
+      <c r="G126" t="s">
+        <v>338</v>
+      </c>
+      <c r="H126" t="s">
+        <v>505</v>
+      </c>
+      <c r="I126" t="s">
         <v>490</v>
       </c>
-      <c r="G126" t="s">
-        <v>504</v>
-      </c>
-      <c r="I126" t="s">
+      <c r="K126" t="s">
         <v>491</v>
-      </c>
-      <c r="J126" t="s">
-        <v>338</v>
-      </c>
-      <c r="K126" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -7817,19 +7817,19 @@
         <v>14</v>
       </c>
       <c r="E127" t="s">
+        <v>504</v>
+      </c>
+      <c r="G127" t="s">
+        <v>338</v>
+      </c>
+      <c r="H127" t="s">
+        <v>505</v>
+      </c>
+      <c r="I127" t="s">
         <v>490</v>
       </c>
-      <c r="G127" t="s">
-        <v>504</v>
-      </c>
-      <c r="I127" t="s">
+      <c r="K127" t="s">
         <v>491</v>
-      </c>
-      <c r="J127" t="s">
-        <v>338</v>
-      </c>
-      <c r="K127" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -7846,19 +7846,19 @@
         <v>14</v>
       </c>
       <c r="E128" t="s">
+        <v>504</v>
+      </c>
+      <c r="G128" t="s">
+        <v>338</v>
+      </c>
+      <c r="H128" t="s">
+        <v>505</v>
+      </c>
+      <c r="I128" t="s">
         <v>490</v>
       </c>
-      <c r="G128" t="s">
-        <v>504</v>
-      </c>
-      <c r="I128" t="s">
+      <c r="K128" t="s">
         <v>491</v>
-      </c>
-      <c r="J128" t="s">
-        <v>338</v>
-      </c>
-      <c r="K128" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -7875,19 +7875,19 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
+        <v>521</v>
+      </c>
+      <c r="G129" t="s">
+        <v>338</v>
+      </c>
+      <c r="H129" t="s">
+        <v>505</v>
+      </c>
+      <c r="I129" t="s">
         <v>490</v>
       </c>
-      <c r="G129" t="s">
-        <v>504</v>
-      </c>
-      <c r="I129" t="s">
+      <c r="K129" t="s">
         <v>491</v>
-      </c>
-      <c r="J129" t="s">
-        <v>338</v>
-      </c>
-      <c r="K129" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7904,19 +7904,19 @@
         <v>14</v>
       </c>
       <c r="E130" t="s">
+        <v>525</v>
+      </c>
+      <c r="G130" t="s">
+        <v>338</v>
+      </c>
+      <c r="H130" t="s">
+        <v>505</v>
+      </c>
+      <c r="I130" t="s">
         <v>490</v>
       </c>
-      <c r="G130" t="s">
-        <v>504</v>
-      </c>
-      <c r="I130" t="s">
+      <c r="K130" t="s">
         <v>491</v>
-      </c>
-      <c r="J130" t="s">
-        <v>338</v>
-      </c>
-      <c r="K130" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7933,19 +7933,19 @@
         <v>14</v>
       </c>
       <c r="E131" t="s">
+        <v>529</v>
+      </c>
+      <c r="G131" t="s">
+        <v>338</v>
+      </c>
+      <c r="H131" t="s">
+        <v>505</v>
+      </c>
+      <c r="I131" t="s">
         <v>490</v>
       </c>
-      <c r="G131" t="s">
-        <v>504</v>
-      </c>
-      <c r="I131" t="s">
+      <c r="K131" t="s">
         <v>491</v>
-      </c>
-      <c r="J131" t="s">
-        <v>338</v>
-      </c>
-      <c r="K131" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7962,19 +7962,19 @@
         <v>14</v>
       </c>
       <c r="E132" t="s">
+        <v>533</v>
+      </c>
+      <c r="G132" t="s">
+        <v>338</v>
+      </c>
+      <c r="H132" t="s">
+        <v>534</v>
+      </c>
+      <c r="I132" t="s">
         <v>490</v>
       </c>
-      <c r="G132" t="s">
-        <v>533</v>
-      </c>
-      <c r="I132" t="s">
+      <c r="K132" t="s">
         <v>491</v>
-      </c>
-      <c r="J132" t="s">
-        <v>338</v>
-      </c>
-      <c r="K132" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -7988,19 +7988,19 @@
         <v>14</v>
       </c>
       <c r="E133" t="s">
+        <v>392</v>
+      </c>
+      <c r="G133" t="s">
+        <v>235</v>
+      </c>
+      <c r="H133" t="s">
+        <v>393</v>
+      </c>
+      <c r="I133" t="s">
         <v>490</v>
       </c>
-      <c r="G133" t="s">
-        <v>392</v>
-      </c>
-      <c r="I133" t="s">
+      <c r="K133" t="s">
         <v>491</v>
-      </c>
-      <c r="J133" t="s">
-        <v>238</v>
-      </c>
-      <c r="K133" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -8017,19 +8017,19 @@
         <v>14</v>
       </c>
       <c r="E134" t="s">
+        <v>361</v>
+      </c>
+      <c r="G134" t="s">
+        <v>338</v>
+      </c>
+      <c r="H134" t="s">
+        <v>362</v>
+      </c>
+      <c r="I134" t="s">
         <v>540</v>
       </c>
-      <c r="G134" t="s">
-        <v>361</v>
-      </c>
-      <c r="I134" t="s">
+      <c r="K134" t="s">
         <v>541</v>
-      </c>
-      <c r="J134" t="s">
-        <v>338</v>
-      </c>
-      <c r="K134" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -8043,19 +8043,19 @@
         <v>14</v>
       </c>
       <c r="E135" t="s">
+        <v>361</v>
+      </c>
+      <c r="G135" t="s">
+        <v>338</v>
+      </c>
+      <c r="H135" t="s">
+        <v>362</v>
+      </c>
+      <c r="I135" t="s">
         <v>540</v>
       </c>
-      <c r="G135" t="s">
-        <v>361</v>
-      </c>
-      <c r="I135" t="s">
+      <c r="K135" t="s">
         <v>541</v>
-      </c>
-      <c r="J135" t="s">
-        <v>338</v>
-      </c>
-      <c r="K135" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -8072,19 +8072,19 @@
         <v>14</v>
       </c>
       <c r="E136" t="s">
+        <v>361</v>
+      </c>
+      <c r="G136" t="s">
+        <v>338</v>
+      </c>
+      <c r="H136" t="s">
+        <v>362</v>
+      </c>
+      <c r="I136" t="s">
         <v>540</v>
       </c>
-      <c r="G136" t="s">
-        <v>361</v>
-      </c>
-      <c r="I136" t="s">
+      <c r="K136" t="s">
         <v>541</v>
-      </c>
-      <c r="J136" t="s">
-        <v>338</v>
-      </c>
-      <c r="K136" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -8101,19 +8101,19 @@
         <v>14</v>
       </c>
       <c r="E137" t="s">
+        <v>361</v>
+      </c>
+      <c r="G137" t="s">
+        <v>338</v>
+      </c>
+      <c r="H137" t="s">
+        <v>362</v>
+      </c>
+      <c r="I137" t="s">
         <v>540</v>
       </c>
-      <c r="G137" t="s">
-        <v>361</v>
-      </c>
-      <c r="I137" t="s">
+      <c r="K137" t="s">
         <v>541</v>
-      </c>
-      <c r="J137" t="s">
-        <v>338</v>
-      </c>
-      <c r="K137" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -8130,19 +8130,19 @@
         <v>14</v>
       </c>
       <c r="E138" t="s">
+        <v>361</v>
+      </c>
+      <c r="G138" t="s">
+        <v>338</v>
+      </c>
+      <c r="H138" t="s">
+        <v>362</v>
+      </c>
+      <c r="I138" t="s">
         <v>540</v>
       </c>
-      <c r="G138" t="s">
-        <v>361</v>
-      </c>
-      <c r="I138" t="s">
+      <c r="K138" t="s">
         <v>541</v>
-      </c>
-      <c r="J138" t="s">
-        <v>338</v>
-      </c>
-      <c r="K138" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -8159,19 +8159,19 @@
         <v>14</v>
       </c>
       <c r="E139" t="s">
+        <v>556</v>
+      </c>
+      <c r="G139" t="s">
+        <v>463</v>
+      </c>
+      <c r="H139" t="s">
+        <v>557</v>
+      </c>
+      <c r="I139" t="s">
         <v>540</v>
       </c>
-      <c r="G139" t="s">
-        <v>556</v>
-      </c>
-      <c r="I139" t="s">
+      <c r="K139" t="s">
         <v>541</v>
-      </c>
-      <c r="J139" t="s">
-        <v>463</v>
-      </c>
-      <c r="K139" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -8188,19 +8188,19 @@
         <v>14</v>
       </c>
       <c r="E140" t="s">
+        <v>361</v>
+      </c>
+      <c r="G140" t="s">
+        <v>338</v>
+      </c>
+      <c r="H140" t="s">
+        <v>362</v>
+      </c>
+      <c r="I140" t="s">
         <v>540</v>
       </c>
-      <c r="G140" t="s">
-        <v>361</v>
-      </c>
-      <c r="I140" t="s">
+      <c r="K140" t="s">
         <v>541</v>
-      </c>
-      <c r="J140" t="s">
-        <v>338</v>
-      </c>
-      <c r="K140" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -8223,16 +8223,16 @@
         <v>565</v>
       </c>
       <c r="G141" t="s">
+        <v>338</v>
+      </c>
+      <c r="H141" t="s">
         <v>566</v>
       </c>
-      <c r="H141" t="s">
+      <c r="I141" t="s">
         <v>567</v>
       </c>
-      <c r="I141" t="s">
+      <c r="J141" t="s">
         <v>568</v>
-      </c>
-      <c r="J141" t="s">
-        <v>338</v>
       </c>
       <c r="K141" t="s">
         <v>569</v>
@@ -8255,16 +8255,16 @@
         <v>565</v>
       </c>
       <c r="G142" t="s">
+        <v>338</v>
+      </c>
+      <c r="H142" t="s">
         <v>566</v>
       </c>
-      <c r="H142" t="s">
+      <c r="I142" t="s">
         <v>567</v>
       </c>
-      <c r="I142" t="s">
+      <c r="J142" t="s">
         <v>568</v>
-      </c>
-      <c r="J142" t="s">
-        <v>338</v>
       </c>
       <c r="K142" t="s">
         <v>569</v>
@@ -8284,25 +8284,25 @@
         <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="F143" t="s">
         <v>565</v>
       </c>
       <c r="G143" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="H143" t="s">
+        <v>576</v>
+      </c>
+      <c r="I143" t="s">
         <v>567</v>
       </c>
-      <c r="I143" t="s">
+      <c r="J143" t="s">
         <v>568</v>
       </c>
-      <c r="J143" t="s">
-        <v>338</v>
-      </c>
       <c r="K143" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -8319,25 +8319,25 @@
         <v>14</v>
       </c>
       <c r="E144" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="F144" t="s">
         <v>565</v>
       </c>
       <c r="G144" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="H144" t="s">
+        <v>576</v>
+      </c>
+      <c r="I144" t="s">
         <v>567</v>
       </c>
-      <c r="I144" t="s">
+      <c r="J144" t="s">
         <v>568</v>
       </c>
-      <c r="J144" t="s">
-        <v>338</v>
-      </c>
       <c r="K144" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -8354,25 +8354,25 @@
         <v>14</v>
       </c>
       <c r="E145" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="F145" t="s">
         <v>565</v>
       </c>
       <c r="G145" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="H145" t="s">
+        <v>576</v>
+      </c>
+      <c r="I145" t="s">
         <v>567</v>
       </c>
-      <c r="I145" t="s">
+      <c r="J145" t="s">
         <v>568</v>
       </c>
-      <c r="J145" t="s">
-        <v>338</v>
-      </c>
       <c r="K145" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -8395,16 +8395,16 @@
         <v>565</v>
       </c>
       <c r="G146" t="s">
+        <v>338</v>
+      </c>
+      <c r="H146" t="s">
         <v>566</v>
       </c>
-      <c r="H146" t="s">
+      <c r="I146" t="s">
         <v>567</v>
       </c>
-      <c r="I146" t="s">
+      <c r="J146" t="s">
         <v>568</v>
-      </c>
-      <c r="J146" t="s">
-        <v>338</v>
       </c>
       <c r="K146" t="s">
         <v>569</v>
@@ -8430,16 +8430,16 @@
         <v>589</v>
       </c>
       <c r="G147" t="s">
+        <v>338</v>
+      </c>
+      <c r="H147" t="s">
         <v>566</v>
       </c>
-      <c r="H147" t="s">
+      <c r="I147" t="s">
+        <v>567</v>
+      </c>
+      <c r="J147" t="s">
         <v>590</v>
-      </c>
-      <c r="I147" t="s">
-        <v>568</v>
-      </c>
-      <c r="J147" t="s">
-        <v>338</v>
       </c>
       <c r="K147" t="s">
         <v>569</v>
@@ -8465,16 +8465,16 @@
         <v>589</v>
       </c>
       <c r="G148" t="s">
+        <v>338</v>
+      </c>
+      <c r="H148" t="s">
         <v>566</v>
       </c>
-      <c r="H148" t="s">
+      <c r="I148" t="s">
+        <v>567</v>
+      </c>
+      <c r="J148" t="s">
         <v>590</v>
-      </c>
-      <c r="I148" t="s">
-        <v>568</v>
-      </c>
-      <c r="J148" t="s">
-        <v>338</v>
       </c>
       <c r="K148" t="s">
         <v>569</v>
@@ -8500,16 +8500,16 @@
         <v>589</v>
       </c>
       <c r="G149" t="s">
+        <v>338</v>
+      </c>
+      <c r="H149" t="s">
         <v>566</v>
       </c>
-      <c r="H149" t="s">
+      <c r="I149" t="s">
+        <v>567</v>
+      </c>
+      <c r="J149" t="s">
         <v>590</v>
-      </c>
-      <c r="I149" t="s">
-        <v>568</v>
-      </c>
-      <c r="J149" t="s">
-        <v>338</v>
       </c>
       <c r="K149" t="s">
         <v>569</v>
@@ -8535,16 +8535,16 @@
         <v>589</v>
       </c>
       <c r="G150" t="s">
+        <v>338</v>
+      </c>
+      <c r="H150" t="s">
         <v>566</v>
       </c>
-      <c r="H150" t="s">
+      <c r="I150" t="s">
+        <v>567</v>
+      </c>
+      <c r="J150" t="s">
         <v>590</v>
-      </c>
-      <c r="I150" t="s">
-        <v>568</v>
-      </c>
-      <c r="J150" t="s">
-        <v>338</v>
       </c>
       <c r="K150" t="s">
         <v>569</v>
@@ -8570,16 +8570,16 @@
         <v>589</v>
       </c>
       <c r="G151" t="s">
+        <v>338</v>
+      </c>
+      <c r="H151" t="s">
         <v>566</v>
       </c>
-      <c r="H151" t="s">
+      <c r="I151" t="s">
+        <v>567</v>
+      </c>
+      <c r="J151" t="s">
         <v>590</v>
-      </c>
-      <c r="I151" t="s">
-        <v>568</v>
-      </c>
-      <c r="J151" t="s">
-        <v>338</v>
       </c>
       <c r="K151" t="s">
         <v>569</v>
@@ -8605,16 +8605,16 @@
         <v>589</v>
       </c>
       <c r="G152" t="s">
+        <v>338</v>
+      </c>
+      <c r="H152" t="s">
         <v>566</v>
       </c>
-      <c r="H152" t="s">
+      <c r="I152" t="s">
+        <v>567</v>
+      </c>
+      <c r="J152" t="s">
         <v>590</v>
-      </c>
-      <c r="I152" t="s">
-        <v>568</v>
-      </c>
-      <c r="J152" t="s">
-        <v>338</v>
       </c>
       <c r="K152" t="s">
         <v>569</v>
@@ -8640,16 +8640,16 @@
         <v>589</v>
       </c>
       <c r="G153" t="s">
+        <v>338</v>
+      </c>
+      <c r="H153" t="s">
         <v>566</v>
       </c>
-      <c r="H153" t="s">
+      <c r="I153" t="s">
+        <v>567</v>
+      </c>
+      <c r="J153" t="s">
         <v>590</v>
-      </c>
-      <c r="I153" t="s">
-        <v>568</v>
-      </c>
-      <c r="J153" t="s">
-        <v>338</v>
       </c>
       <c r="K153" t="s">
         <v>569</v>
@@ -8675,16 +8675,16 @@
         <v>589</v>
       </c>
       <c r="G154" t="s">
+        <v>338</v>
+      </c>
+      <c r="H154" t="s">
         <v>566</v>
       </c>
-      <c r="H154" t="s">
+      <c r="I154" t="s">
+        <v>567</v>
+      </c>
+      <c r="J154" t="s">
         <v>590</v>
-      </c>
-      <c r="I154" t="s">
-        <v>568</v>
-      </c>
-      <c r="J154" t="s">
-        <v>338</v>
       </c>
       <c r="K154" t="s">
         <v>569</v>
@@ -8710,16 +8710,16 @@
         <v>589</v>
       </c>
       <c r="G155" t="s">
+        <v>338</v>
+      </c>
+      <c r="H155" t="s">
         <v>566</v>
       </c>
-      <c r="H155" t="s">
+      <c r="I155" t="s">
+        <v>567</v>
+      </c>
+      <c r="J155" t="s">
         <v>590</v>
-      </c>
-      <c r="I155" t="s">
-        <v>568</v>
-      </c>
-      <c r="J155" t="s">
-        <v>338</v>
       </c>
       <c r="K155" t="s">
         <v>569</v>
@@ -8745,16 +8745,16 @@
         <v>618</v>
       </c>
       <c r="G156" t="s">
+        <v>338</v>
+      </c>
+      <c r="H156" t="s">
         <v>566</v>
       </c>
-      <c r="H156" t="s">
+      <c r="I156" t="s">
+        <v>567</v>
+      </c>
+      <c r="J156" t="s">
         <v>619</v>
-      </c>
-      <c r="I156" t="s">
-        <v>568</v>
-      </c>
-      <c r="J156" t="s">
-        <v>338</v>
       </c>
       <c r="K156" t="s">
         <v>569</v>
@@ -8774,25 +8774,25 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>564</v>
+        <v>623</v>
       </c>
       <c r="F157" t="s">
         <v>618</v>
       </c>
       <c r="G157" t="s">
+        <v>338</v>
+      </c>
+      <c r="H157" t="s">
         <v>566</v>
       </c>
-      <c r="H157" t="s">
+      <c r="I157" t="s">
+        <v>567</v>
+      </c>
+      <c r="J157" t="s">
         <v>619</v>
       </c>
-      <c r="I157" t="s">
-        <v>568</v>
-      </c>
-      <c r="J157" t="s">
-        <v>338</v>
-      </c>
       <c r="K157" t="s">
-        <v>623</v>
+        <v>569</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -8815,16 +8815,16 @@
         <v>618</v>
       </c>
       <c r="G158" t="s">
+        <v>338</v>
+      </c>
+      <c r="H158" t="s">
         <v>566</v>
       </c>
-      <c r="H158" t="s">
+      <c r="I158" t="s">
+        <v>567</v>
+      </c>
+      <c r="J158" t="s">
         <v>619</v>
-      </c>
-      <c r="I158" t="s">
-        <v>568</v>
-      </c>
-      <c r="J158" t="s">
-        <v>338</v>
       </c>
       <c r="K158" t="s">
         <v>569</v>
@@ -8850,16 +8850,16 @@
         <v>618</v>
       </c>
       <c r="G159" t="s">
+        <v>338</v>
+      </c>
+      <c r="H159" t="s">
         <v>566</v>
       </c>
-      <c r="H159" t="s">
+      <c r="I159" t="s">
+        <v>567</v>
+      </c>
+      <c r="J159" t="s">
         <v>619</v>
-      </c>
-      <c r="I159" t="s">
-        <v>568</v>
-      </c>
-      <c r="J159" t="s">
-        <v>338</v>
       </c>
       <c r="K159" t="s">
         <v>569</v>
@@ -8885,16 +8885,16 @@
         <v>618</v>
       </c>
       <c r="G160" t="s">
+        <v>338</v>
+      </c>
+      <c r="H160" t="s">
         <v>566</v>
       </c>
-      <c r="H160" t="s">
+      <c r="I160" t="s">
+        <v>567</v>
+      </c>
+      <c r="J160" t="s">
         <v>619</v>
-      </c>
-      <c r="I160" t="s">
-        <v>568</v>
-      </c>
-      <c r="J160" t="s">
-        <v>338</v>
       </c>
       <c r="K160" t="s">
         <v>569</v>
@@ -8920,16 +8920,16 @@
         <v>618</v>
       </c>
       <c r="G161" t="s">
+        <v>338</v>
+      </c>
+      <c r="H161" t="s">
         <v>566</v>
       </c>
-      <c r="H161" t="s">
+      <c r="I161" t="s">
+        <v>567</v>
+      </c>
+      <c r="J161" t="s">
         <v>619</v>
-      </c>
-      <c r="I161" t="s">
-        <v>568</v>
-      </c>
-      <c r="J161" t="s">
-        <v>338</v>
       </c>
       <c r="K161" t="s">
         <v>569</v>
@@ -8955,16 +8955,16 @@
         <v>639</v>
       </c>
       <c r="G162" t="s">
+        <v>338</v>
+      </c>
+      <c r="H162" t="s">
         <v>566</v>
       </c>
-      <c r="H162" t="s">
+      <c r="I162" t="s">
+        <v>567</v>
+      </c>
+      <c r="J162" t="s">
         <v>640</v>
-      </c>
-      <c r="I162" t="s">
-        <v>568</v>
-      </c>
-      <c r="J162" t="s">
-        <v>338</v>
       </c>
       <c r="K162" t="s">
         <v>569</v>
@@ -8984,25 +8984,25 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>564</v>
+        <v>644</v>
       </c>
       <c r="F163" t="s">
+        <v>645</v>
+      </c>
+      <c r="G163" t="s">
+        <v>338</v>
+      </c>
+      <c r="H163" t="s">
+        <v>566</v>
+      </c>
+      <c r="I163" t="s">
+        <v>567</v>
+      </c>
+      <c r="J163" t="s">
         <v>642</v>
       </c>
-      <c r="G163" t="s">
-        <v>566</v>
-      </c>
-      <c r="H163" t="s">
-        <v>644</v>
-      </c>
-      <c r="I163" t="s">
-        <v>568</v>
-      </c>
-      <c r="J163" t="s">
-        <v>338</v>
-      </c>
       <c r="K163" t="s">
-        <v>645</v>
+        <v>569</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -9025,16 +9025,16 @@
         <v>649</v>
       </c>
       <c r="G164" t="s">
+        <v>338</v>
+      </c>
+      <c r="H164" t="s">
         <v>566</v>
       </c>
-      <c r="H164" t="s">
+      <c r="I164" t="s">
+        <v>567</v>
+      </c>
+      <c r="J164" t="s">
         <v>650</v>
-      </c>
-      <c r="I164" t="s">
-        <v>568</v>
-      </c>
-      <c r="J164" t="s">
-        <v>338</v>
       </c>
       <c r="K164" t="s">
         <v>569</v>
@@ -9060,16 +9060,16 @@
         <v>649</v>
       </c>
       <c r="G165" t="s">
+        <v>338</v>
+      </c>
+      <c r="H165" t="s">
         <v>566</v>
       </c>
-      <c r="H165" t="s">
+      <c r="I165" t="s">
+        <v>567</v>
+      </c>
+      <c r="J165" t="s">
         <v>650</v>
-      </c>
-      <c r="I165" t="s">
-        <v>568</v>
-      </c>
-      <c r="J165" t="s">
-        <v>338</v>
       </c>
       <c r="K165" t="s">
         <v>569</v>
@@ -9095,16 +9095,16 @@
         <v>649</v>
       </c>
       <c r="G166" t="s">
+        <v>338</v>
+      </c>
+      <c r="H166" t="s">
         <v>566</v>
       </c>
-      <c r="H166" t="s">
+      <c r="I166" t="s">
+        <v>567</v>
+      </c>
+      <c r="J166" t="s">
         <v>650</v>
-      </c>
-      <c r="I166" t="s">
-        <v>568</v>
-      </c>
-      <c r="J166" t="s">
-        <v>338</v>
       </c>
       <c r="K166" t="s">
         <v>569</v>
@@ -9130,16 +9130,16 @@
         <v>649</v>
       </c>
       <c r="G167" t="s">
+        <v>338</v>
+      </c>
+      <c r="H167" t="s">
         <v>566</v>
       </c>
-      <c r="H167" t="s">
+      <c r="I167" t="s">
+        <v>567</v>
+      </c>
+      <c r="J167" t="s">
         <v>650</v>
-      </c>
-      <c r="I167" t="s">
-        <v>568</v>
-      </c>
-      <c r="J167" t="s">
-        <v>338</v>
       </c>
       <c r="K167" t="s">
         <v>569</v>
@@ -9159,25 +9159,25 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>564</v>
+        <v>663</v>
       </c>
       <c r="F168" t="s">
         <v>649</v>
       </c>
       <c r="G168" t="s">
+        <v>338</v>
+      </c>
+      <c r="H168" t="s">
         <v>566</v>
       </c>
-      <c r="H168" t="s">
+      <c r="I168" t="s">
+        <v>567</v>
+      </c>
+      <c r="J168" t="s">
         <v>650</v>
       </c>
-      <c r="I168" t="s">
-        <v>568</v>
-      </c>
-      <c r="J168" t="s">
-        <v>338</v>
-      </c>
       <c r="K168" t="s">
-        <v>663</v>
+        <v>569</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -9191,25 +9191,25 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>564</v>
+        <v>663</v>
       </c>
       <c r="F169" t="s">
         <v>649</v>
       </c>
       <c r="G169" t="s">
+        <v>338</v>
+      </c>
+      <c r="H169" t="s">
         <v>566</v>
       </c>
-      <c r="H169" t="s">
+      <c r="I169" t="s">
+        <v>567</v>
+      </c>
+      <c r="J169" t="s">
         <v>650</v>
       </c>
-      <c r="I169" t="s">
-        <v>568</v>
-      </c>
-      <c r="J169" t="s">
-        <v>338</v>
-      </c>
       <c r="K169" t="s">
-        <v>663</v>
+        <v>569</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -9232,16 +9232,16 @@
         <v>649</v>
       </c>
       <c r="G170" t="s">
+        <v>338</v>
+      </c>
+      <c r="H170" t="s">
         <v>566</v>
       </c>
-      <c r="H170" t="s">
+      <c r="I170" t="s">
+        <v>567</v>
+      </c>
+      <c r="J170" t="s">
         <v>650</v>
-      </c>
-      <c r="I170" t="s">
-        <v>568</v>
-      </c>
-      <c r="J170" t="s">
-        <v>338</v>
       </c>
       <c r="K170" t="s">
         <v>569</v>
@@ -9261,19 +9261,19 @@
         <v>14</v>
       </c>
       <c r="E171" t="s">
+        <v>337</v>
+      </c>
+      <c r="G171" t="s">
+        <v>338</v>
+      </c>
+      <c r="H171" t="s">
+        <v>339</v>
+      </c>
+      <c r="I171" t="s">
         <v>672</v>
       </c>
-      <c r="G171" t="s">
-        <v>337</v>
-      </c>
-      <c r="I171" t="s">
+      <c r="K171" t="s">
         <v>673</v>
-      </c>
-      <c r="J171" t="s">
-        <v>338</v>
-      </c>
-      <c r="K171" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -9290,19 +9290,19 @@
         <v>14</v>
       </c>
       <c r="E172" t="s">
+        <v>243</v>
+      </c>
+      <c r="G172" t="s">
+        <v>235</v>
+      </c>
+      <c r="H172" t="s">
+        <v>244</v>
+      </c>
+      <c r="I172" t="s">
         <v>672</v>
       </c>
-      <c r="G172" t="s">
-        <v>243</v>
-      </c>
-      <c r="I172" t="s">
+      <c r="K172" t="s">
         <v>673</v>
-      </c>
-      <c r="J172" t="s">
-        <v>238</v>
-      </c>
-      <c r="K172" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -9319,19 +9319,19 @@
         <v>14</v>
       </c>
       <c r="E173" t="s">
+        <v>337</v>
+      </c>
+      <c r="G173" t="s">
+        <v>338</v>
+      </c>
+      <c r="H173" t="s">
+        <v>339</v>
+      </c>
+      <c r="I173" t="s">
         <v>672</v>
       </c>
-      <c r="G173" t="s">
-        <v>337</v>
-      </c>
-      <c r="I173" t="s">
+      <c r="K173" t="s">
         <v>673</v>
-      </c>
-      <c r="J173" t="s">
-        <v>338</v>
-      </c>
-      <c r="K173" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -9348,19 +9348,19 @@
         <v>14</v>
       </c>
       <c r="E174" t="s">
+        <v>337</v>
+      </c>
+      <c r="G174" t="s">
+        <v>338</v>
+      </c>
+      <c r="H174" t="s">
+        <v>339</v>
+      </c>
+      <c r="I174" t="s">
         <v>672</v>
       </c>
-      <c r="G174" t="s">
-        <v>337</v>
-      </c>
-      <c r="I174" t="s">
+      <c r="K174" t="s">
         <v>673</v>
-      </c>
-      <c r="J174" t="s">
-        <v>338</v>
-      </c>
-      <c r="K174" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -9377,19 +9377,19 @@
         <v>14</v>
       </c>
       <c r="E175" t="s">
+        <v>337</v>
+      </c>
+      <c r="G175" t="s">
+        <v>338</v>
+      </c>
+      <c r="H175" t="s">
+        <v>339</v>
+      </c>
+      <c r="I175" t="s">
         <v>672</v>
       </c>
-      <c r="G175" t="s">
-        <v>337</v>
-      </c>
-      <c r="I175" t="s">
+      <c r="K175" t="s">
         <v>673</v>
-      </c>
-      <c r="J175" t="s">
-        <v>338</v>
-      </c>
-      <c r="K175" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -9403,19 +9403,19 @@
         <v>14</v>
       </c>
       <c r="E176" t="s">
+        <v>337</v>
+      </c>
+      <c r="G176" t="s">
+        <v>338</v>
+      </c>
+      <c r="H176" t="s">
+        <v>339</v>
+      </c>
+      <c r="I176" t="s">
         <v>672</v>
       </c>
-      <c r="G176" t="s">
-        <v>337</v>
-      </c>
-      <c r="I176" t="s">
+      <c r="K176" t="s">
         <v>673</v>
-      </c>
-      <c r="J176" t="s">
-        <v>338</v>
-      </c>
-      <c r="K176" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -9432,19 +9432,19 @@
         <v>14</v>
       </c>
       <c r="E177" t="s">
+        <v>337</v>
+      </c>
+      <c r="G177" t="s">
+        <v>338</v>
+      </c>
+      <c r="H177" t="s">
+        <v>339</v>
+      </c>
+      <c r="I177" t="s">
         <v>691</v>
       </c>
-      <c r="G177" t="s">
-        <v>337</v>
-      </c>
-      <c r="I177" t="s">
+      <c r="K177" t="s">
         <v>692</v>
-      </c>
-      <c r="J177" t="s">
-        <v>338</v>
-      </c>
-      <c r="K177" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -9461,19 +9461,19 @@
         <v>14</v>
       </c>
       <c r="E178" t="s">
+        <v>337</v>
+      </c>
+      <c r="G178" t="s">
+        <v>338</v>
+      </c>
+      <c r="H178" t="s">
+        <v>339</v>
+      </c>
+      <c r="I178" t="s">
         <v>691</v>
       </c>
-      <c r="G178" t="s">
-        <v>337</v>
-      </c>
-      <c r="I178" t="s">
+      <c r="K178" t="s">
         <v>692</v>
-      </c>
-      <c r="J178" t="s">
-        <v>338</v>
-      </c>
-      <c r="K178" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -9490,19 +9490,19 @@
         <v>14</v>
       </c>
       <c r="E179" t="s">
+        <v>337</v>
+      </c>
+      <c r="G179" t="s">
+        <v>338</v>
+      </c>
+      <c r="H179" t="s">
+        <v>339</v>
+      </c>
+      <c r="I179" t="s">
         <v>691</v>
       </c>
-      <c r="G179" t="s">
-        <v>337</v>
-      </c>
-      <c r="I179" t="s">
+      <c r="K179" t="s">
         <v>692</v>
-      </c>
-      <c r="J179" t="s">
-        <v>338</v>
-      </c>
-      <c r="K179" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -9519,19 +9519,19 @@
         <v>14</v>
       </c>
       <c r="E180" t="s">
+        <v>337</v>
+      </c>
+      <c r="G180" t="s">
+        <v>338</v>
+      </c>
+      <c r="H180" t="s">
+        <v>339</v>
+      </c>
+      <c r="I180" t="s">
         <v>691</v>
       </c>
-      <c r="G180" t="s">
-        <v>337</v>
-      </c>
-      <c r="I180" t="s">
+      <c r="K180" t="s">
         <v>692</v>
-      </c>
-      <c r="J180" t="s">
-        <v>338</v>
-      </c>
-      <c r="K180" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -9554,16 +9554,16 @@
         <v>706</v>
       </c>
       <c r="G181" t="s">
+        <v>338</v>
+      </c>
+      <c r="H181" t="s">
         <v>707</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>708</v>
       </c>
-      <c r="I181" t="s">
+      <c r="J181" t="s">
         <v>709</v>
-      </c>
-      <c r="J181" t="s">
-        <v>338</v>
       </c>
       <c r="K181" t="s">
         <v>710</v>
@@ -9589,16 +9589,16 @@
         <v>706</v>
       </c>
       <c r="G182" t="s">
+        <v>338</v>
+      </c>
+      <c r="H182" t="s">
         <v>707</v>
       </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>708</v>
       </c>
-      <c r="I182" t="s">
+      <c r="J182" t="s">
         <v>709</v>
-      </c>
-      <c r="J182" t="s">
-        <v>338</v>
       </c>
       <c r="K182" t="s">
         <v>710</v>
@@ -9624,16 +9624,16 @@
         <v>706</v>
       </c>
       <c r="G183" t="s">
+        <v>338</v>
+      </c>
+      <c r="H183" t="s">
         <v>707</v>
       </c>
-      <c r="H183" t="s">
+      <c r="I183" t="s">
         <v>708</v>
       </c>
-      <c r="I183" t="s">
+      <c r="J183" t="s">
         <v>709</v>
-      </c>
-      <c r="J183" t="s">
-        <v>338</v>
       </c>
       <c r="K183" t="s">
         <v>710</v>
@@ -9659,16 +9659,16 @@
         <v>706</v>
       </c>
       <c r="G184" t="s">
+        <v>338</v>
+      </c>
+      <c r="H184" t="s">
         <v>707</v>
       </c>
-      <c r="H184" t="s">
+      <c r="I184" t="s">
         <v>708</v>
       </c>
-      <c r="I184" t="s">
+      <c r="J184" t="s">
         <v>709</v>
-      </c>
-      <c r="J184" t="s">
-        <v>338</v>
       </c>
       <c r="K184" t="s">
         <v>710</v>
@@ -9694,16 +9694,16 @@
         <v>706</v>
       </c>
       <c r="G185" t="s">
+        <v>338</v>
+      </c>
+      <c r="H185" t="s">
         <v>707</v>
       </c>
-      <c r="H185" t="s">
+      <c r="I185" t="s">
         <v>708</v>
       </c>
-      <c r="I185" t="s">
+      <c r="J185" t="s">
         <v>709</v>
-      </c>
-      <c r="J185" t="s">
-        <v>338</v>
       </c>
       <c r="K185" t="s">
         <v>710</v>
@@ -9729,16 +9729,16 @@
         <v>706</v>
       </c>
       <c r="G186" t="s">
+        <v>338</v>
+      </c>
+      <c r="H186" t="s">
         <v>707</v>
       </c>
-      <c r="H186" t="s">
+      <c r="I186" t="s">
         <v>708</v>
       </c>
-      <c r="I186" t="s">
+      <c r="J186" t="s">
         <v>709</v>
-      </c>
-      <c r="J186" t="s">
-        <v>338</v>
       </c>
       <c r="K186" t="s">
         <v>710</v>
@@ -9764,16 +9764,16 @@
         <v>706</v>
       </c>
       <c r="G187" t="s">
+        <v>338</v>
+      </c>
+      <c r="H187" t="s">
         <v>707</v>
       </c>
-      <c r="H187" t="s">
+      <c r="I187" t="s">
         <v>708</v>
       </c>
-      <c r="I187" t="s">
+      <c r="J187" t="s">
         <v>709</v>
-      </c>
-      <c r="J187" t="s">
-        <v>338</v>
       </c>
       <c r="K187" t="s">
         <v>710</v>
@@ -9799,16 +9799,16 @@
         <v>706</v>
       </c>
       <c r="G188" t="s">
+        <v>338</v>
+      </c>
+      <c r="H188" t="s">
         <v>707</v>
       </c>
-      <c r="H188" t="s">
+      <c r="I188" t="s">
         <v>708</v>
       </c>
-      <c r="I188" t="s">
+      <c r="J188" t="s">
         <v>709</v>
-      </c>
-      <c r="J188" t="s">
-        <v>338</v>
       </c>
       <c r="K188" t="s">
         <v>710</v>
@@ -9834,16 +9834,16 @@
         <v>706</v>
       </c>
       <c r="G189" t="s">
+        <v>338</v>
+      </c>
+      <c r="H189" t="s">
         <v>707</v>
       </c>
-      <c r="H189" t="s">
+      <c r="I189" t="s">
         <v>708</v>
       </c>
-      <c r="I189" t="s">
+      <c r="J189" t="s">
         <v>709</v>
-      </c>
-      <c r="J189" t="s">
-        <v>338</v>
       </c>
       <c r="K189" t="s">
         <v>710</v>
@@ -9869,16 +9869,16 @@
         <v>706</v>
       </c>
       <c r="G190" t="s">
+        <v>338</v>
+      </c>
+      <c r="H190" t="s">
         <v>707</v>
       </c>
-      <c r="H190" t="s">
+      <c r="I190" t="s">
         <v>708</v>
       </c>
-      <c r="I190" t="s">
+      <c r="J190" t="s">
         <v>709</v>
-      </c>
-      <c r="J190" t="s">
-        <v>338</v>
       </c>
       <c r="K190" t="s">
         <v>710</v>
@@ -9904,16 +9904,16 @@
         <v>706</v>
       </c>
       <c r="G191" t="s">
+        <v>338</v>
+      </c>
+      <c r="H191" t="s">
         <v>707</v>
       </c>
-      <c r="H191" t="s">
+      <c r="I191" t="s">
         <v>708</v>
       </c>
-      <c r="I191" t="s">
+      <c r="J191" t="s">
         <v>709</v>
-      </c>
-      <c r="J191" t="s">
-        <v>338</v>
       </c>
       <c r="K191" t="s">
         <v>710</v>
@@ -9936,16 +9936,16 @@
         <v>706</v>
       </c>
       <c r="G192" t="s">
+        <v>338</v>
+      </c>
+      <c r="H192" t="s">
         <v>707</v>
       </c>
-      <c r="H192" t="s">
+      <c r="I192" t="s">
         <v>708</v>
       </c>
-      <c r="I192" t="s">
+      <c r="J192" t="s">
         <v>709</v>
-      </c>
-      <c r="J192" t="s">
-        <v>338</v>
       </c>
       <c r="K192" t="s">
         <v>710</v>
@@ -9965,25 +9965,25 @@
         <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>705</v>
+        <v>746</v>
       </c>
       <c r="F193" t="s">
         <v>706</v>
       </c>
       <c r="G193" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="H193" t="s">
+        <v>576</v>
+      </c>
+      <c r="I193" t="s">
         <v>708</v>
       </c>
-      <c r="I193" t="s">
+      <c r="J193" t="s">
         <v>709</v>
       </c>
-      <c r="J193" t="s">
-        <v>338</v>
-      </c>
       <c r="K193" t="s">
-        <v>746</v>
+        <v>710</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -10006,16 +10006,16 @@
         <v>706</v>
       </c>
       <c r="G194" t="s">
+        <v>338</v>
+      </c>
+      <c r="H194" t="s">
         <v>707</v>
       </c>
-      <c r="H194" t="s">
+      <c r="I194" t="s">
         <v>708</v>
       </c>
-      <c r="I194" t="s">
+      <c r="J194" t="s">
         <v>709</v>
-      </c>
-      <c r="J194" t="s">
-        <v>338</v>
       </c>
       <c r="K194" t="s">
         <v>710</v>
@@ -10041,16 +10041,16 @@
         <v>706</v>
       </c>
       <c r="G195" t="s">
+        <v>338</v>
+      </c>
+      <c r="H195" t="s">
         <v>707</v>
       </c>
-      <c r="H195" t="s">
+      <c r="I195" t="s">
         <v>708</v>
       </c>
-      <c r="I195" t="s">
+      <c r="J195" t="s">
         <v>709</v>
-      </c>
-      <c r="J195" t="s">
-        <v>338</v>
       </c>
       <c r="K195" t="s">
         <v>710</v>
@@ -10076,16 +10076,16 @@
         <v>706</v>
       </c>
       <c r="G196" t="s">
+        <v>338</v>
+      </c>
+      <c r="H196" t="s">
         <v>707</v>
       </c>
-      <c r="H196" t="s">
+      <c r="I196" t="s">
         <v>708</v>
       </c>
-      <c r="I196" t="s">
+      <c r="J196" t="s">
         <v>709</v>
-      </c>
-      <c r="J196" t="s">
-        <v>338</v>
       </c>
       <c r="K196" t="s">
         <v>710</v>
@@ -10111,16 +10111,16 @@
         <v>706</v>
       </c>
       <c r="G197" t="s">
+        <v>338</v>
+      </c>
+      <c r="H197" t="s">
         <v>707</v>
       </c>
-      <c r="H197" t="s">
+      <c r="I197" t="s">
         <v>708</v>
       </c>
-      <c r="I197" t="s">
+      <c r="J197" t="s">
         <v>709</v>
-      </c>
-      <c r="J197" t="s">
-        <v>338</v>
       </c>
       <c r="K197" t="s">
         <v>710</v>
@@ -10146,16 +10146,16 @@
         <v>706</v>
       </c>
       <c r="G198" t="s">
+        <v>338</v>
+      </c>
+      <c r="H198" t="s">
         <v>707</v>
       </c>
-      <c r="H198" t="s">
+      <c r="I198" t="s">
         <v>708</v>
       </c>
-      <c r="I198" t="s">
+      <c r="J198" t="s">
         <v>709</v>
-      </c>
-      <c r="J198" t="s">
-        <v>338</v>
       </c>
       <c r="K198" t="s">
         <v>710</v>
@@ -10175,25 +10175,25 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F199" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G199" t="s">
+        <v>338</v>
+      </c>
+      <c r="H199" t="s">
         <v>707</v>
       </c>
-      <c r="H199" t="s">
-        <v>766</v>
-      </c>
       <c r="I199" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J199" t="s">
-        <v>338</v>
+        <v>767</v>
       </c>
       <c r="K199" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -10210,25 +10210,25 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F200" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G200" t="s">
+        <v>338</v>
+      </c>
+      <c r="H200" t="s">
         <v>707</v>
       </c>
-      <c r="H200" t="s">
-        <v>766</v>
-      </c>
       <c r="I200" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J200" t="s">
-        <v>338</v>
+        <v>767</v>
       </c>
       <c r="K200" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -10245,25 +10245,25 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F201" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G201" t="s">
+        <v>338</v>
+      </c>
+      <c r="H201" t="s">
         <v>707</v>
       </c>
-      <c r="H201" t="s">
-        <v>766</v>
-      </c>
       <c r="I201" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J201" t="s">
-        <v>338</v>
+        <v>767</v>
       </c>
       <c r="K201" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -10277,25 +10277,25 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F202" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G202" t="s">
+        <v>338</v>
+      </c>
+      <c r="H202" t="s">
         <v>707</v>
       </c>
-      <c r="H202" t="s">
-        <v>766</v>
-      </c>
       <c r="I202" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J202" t="s">
-        <v>338</v>
+        <v>767</v>
       </c>
       <c r="K202" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -10312,25 +10312,25 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
-        <v>705</v>
+        <v>746</v>
       </c>
       <c r="F203" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G203" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="H203" t="s">
-        <v>766</v>
+        <v>576</v>
       </c>
       <c r="I203" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J203" t="s">
-        <v>338</v>
+        <v>767</v>
       </c>
       <c r="K203" t="s">
-        <v>746</v>
+        <v>710</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10344,25 +10344,25 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F204" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G204" t="s">
+        <v>338</v>
+      </c>
+      <c r="H204" t="s">
         <v>707</v>
       </c>
-      <c r="H204" t="s">
-        <v>766</v>
-      </c>
       <c r="I204" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J204" t="s">
-        <v>338</v>
+        <v>767</v>
       </c>
       <c r="K204" t="s">
-        <v>767</v>
+        <v>710</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -10379,25 +10379,25 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F205" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G205" t="s">
+        <v>338</v>
+      </c>
+      <c r="H205" t="s">
         <v>707</v>
       </c>
-      <c r="H205" t="s">
-        <v>785</v>
-      </c>
       <c r="I205" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J205" t="s">
-        <v>338</v>
+        <v>786</v>
       </c>
       <c r="K205" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -10414,25 +10414,25 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F206" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G206" t="s">
+        <v>338</v>
+      </c>
+      <c r="H206" t="s">
         <v>707</v>
       </c>
-      <c r="H206" t="s">
-        <v>785</v>
-      </c>
       <c r="I206" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J206" t="s">
-        <v>338</v>
+        <v>786</v>
       </c>
       <c r="K206" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -10446,25 +10446,25 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F207" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G207" t="s">
+        <v>338</v>
+      </c>
+      <c r="H207" t="s">
         <v>707</v>
       </c>
-      <c r="H207" t="s">
-        <v>785</v>
-      </c>
       <c r="I207" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J207" t="s">
-        <v>338</v>
+        <v>786</v>
       </c>
       <c r="K207" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -10481,25 +10481,25 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
-        <v>705</v>
+        <v>746</v>
       </c>
       <c r="F208" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G208" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="H208" t="s">
-        <v>785</v>
+        <v>576</v>
       </c>
       <c r="I208" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J208" t="s">
-        <v>338</v>
+        <v>786</v>
       </c>
       <c r="K208" t="s">
-        <v>746</v>
+        <v>710</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10516,25 +10516,25 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F209" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G209" t="s">
+        <v>338</v>
+      </c>
+      <c r="H209" t="s">
         <v>707</v>
       </c>
-      <c r="H209" t="s">
-        <v>785</v>
-      </c>
       <c r="I209" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J209" t="s">
-        <v>338</v>
+        <v>786</v>
       </c>
       <c r="K209" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -10557,16 +10557,16 @@
         <v>802</v>
       </c>
       <c r="G210" t="s">
+        <v>338</v>
+      </c>
+      <c r="H210" t="s">
         <v>803</v>
       </c>
-      <c r="H210" t="s">
+      <c r="I210" t="s">
         <v>804</v>
       </c>
-      <c r="I210" t="s">
+      <c r="J210" t="s">
         <v>805</v>
-      </c>
-      <c r="J210" t="s">
-        <v>338</v>
       </c>
       <c r="K210" t="s">
         <v>806</v>
@@ -10589,16 +10589,16 @@
         <v>802</v>
       </c>
       <c r="G211" t="s">
+        <v>338</v>
+      </c>
+      <c r="H211" t="s">
         <v>803</v>
       </c>
-      <c r="H211" t="s">
+      <c r="I211" t="s">
         <v>804</v>
       </c>
-      <c r="I211" t="s">
+      <c r="J211" t="s">
         <v>805</v>
-      </c>
-      <c r="J211" t="s">
-        <v>338</v>
       </c>
       <c r="K211" t="s">
         <v>806</v>
@@ -10624,16 +10624,16 @@
         <v>802</v>
       </c>
       <c r="G212" t="s">
+        <v>338</v>
+      </c>
+      <c r="H212" t="s">
         <v>803</v>
       </c>
-      <c r="H212" t="s">
+      <c r="I212" t="s">
         <v>804</v>
       </c>
-      <c r="I212" t="s">
+      <c r="J212" t="s">
         <v>805</v>
-      </c>
-      <c r="J212" t="s">
-        <v>338</v>
       </c>
       <c r="K212" t="s">
         <v>806</v>
@@ -10656,16 +10656,16 @@
         <v>802</v>
       </c>
       <c r="G213" t="s">
+        <v>338</v>
+      </c>
+      <c r="H213" t="s">
         <v>803</v>
       </c>
-      <c r="H213" t="s">
+      <c r="I213" t="s">
         <v>804</v>
       </c>
-      <c r="I213" t="s">
+      <c r="J213" t="s">
         <v>805</v>
-      </c>
-      <c r="J213" t="s">
-        <v>338</v>
       </c>
       <c r="K213" t="s">
         <v>806</v>
@@ -10691,16 +10691,16 @@
         <v>802</v>
       </c>
       <c r="G214" t="s">
+        <v>338</v>
+      </c>
+      <c r="H214" t="s">
         <v>803</v>
       </c>
-      <c r="H214" t="s">
+      <c r="I214" t="s">
         <v>804</v>
       </c>
-      <c r="I214" t="s">
+      <c r="J214" t="s">
         <v>805</v>
-      </c>
-      <c r="J214" t="s">
-        <v>338</v>
       </c>
       <c r="K214" t="s">
         <v>806</v>
@@ -10720,25 +10720,25 @@
         <v>14</v>
       </c>
       <c r="E215" t="s">
-        <v>801</v>
+        <v>765</v>
       </c>
       <c r="F215" t="s">
         <v>802</v>
       </c>
       <c r="G215" t="s">
+        <v>338</v>
+      </c>
+      <c r="H215" t="s">
         <v>707</v>
       </c>
-      <c r="H215" t="s">
+      <c r="I215" t="s">
         <v>804</v>
       </c>
-      <c r="I215" t="s">
+      <c r="J215" t="s">
         <v>805</v>
       </c>
-      <c r="J215" t="s">
-        <v>338</v>
-      </c>
       <c r="K215" t="s">
-        <v>767</v>
+        <v>806</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -10761,16 +10761,16 @@
         <v>802</v>
       </c>
       <c r="G216" t="s">
+        <v>338</v>
+      </c>
+      <c r="H216" t="s">
         <v>803</v>
       </c>
-      <c r="H216" t="s">
+      <c r="I216" t="s">
         <v>804</v>
       </c>
-      <c r="I216" t="s">
+      <c r="J216" t="s">
         <v>805</v>
-      </c>
-      <c r="J216" t="s">
-        <v>338</v>
       </c>
       <c r="K216" t="s">
         <v>806</v>
@@ -10796,16 +10796,16 @@
         <v>802</v>
       </c>
       <c r="G217" t="s">
+        <v>338</v>
+      </c>
+      <c r="H217" t="s">
         <v>803</v>
       </c>
-      <c r="H217" t="s">
+      <c r="I217" t="s">
         <v>804</v>
       </c>
-      <c r="I217" t="s">
+      <c r="J217" t="s">
         <v>805</v>
-      </c>
-      <c r="J217" t="s">
-        <v>338</v>
       </c>
       <c r="K217" t="s">
         <v>806</v>
@@ -10828,16 +10828,16 @@
         <v>802</v>
       </c>
       <c r="G218" t="s">
+        <v>338</v>
+      </c>
+      <c r="H218" t="s">
         <v>803</v>
       </c>
-      <c r="H218" t="s">
+      <c r="I218" t="s">
         <v>804</v>
       </c>
-      <c r="I218" t="s">
+      <c r="J218" t="s">
         <v>805</v>
-      </c>
-      <c r="J218" t="s">
-        <v>338</v>
       </c>
       <c r="K218" t="s">
         <v>806</v>
@@ -10860,16 +10860,16 @@
         <v>802</v>
       </c>
       <c r="G219" t="s">
+        <v>338</v>
+      </c>
+      <c r="H219" t="s">
         <v>803</v>
       </c>
-      <c r="H219" t="s">
+      <c r="I219" t="s">
         <v>804</v>
       </c>
-      <c r="I219" t="s">
+      <c r="J219" t="s">
         <v>805</v>
-      </c>
-      <c r="J219" t="s">
-        <v>338</v>
       </c>
       <c r="K219" t="s">
         <v>806</v>
@@ -10889,25 +10889,25 @@
         <v>14</v>
       </c>
       <c r="E220" t="s">
-        <v>801</v>
+        <v>663</v>
       </c>
       <c r="F220" t="s">
         <v>802</v>
       </c>
       <c r="G220" t="s">
+        <v>338</v>
+      </c>
+      <c r="H220" t="s">
         <v>566</v>
       </c>
-      <c r="H220" t="s">
+      <c r="I220" t="s">
         <v>804</v>
       </c>
-      <c r="I220" t="s">
+      <c r="J220" t="s">
         <v>805</v>
       </c>
-      <c r="J220" t="s">
-        <v>338</v>
-      </c>
       <c r="K220" t="s">
-        <v>663</v>
+        <v>806</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -10930,16 +10930,16 @@
         <v>802</v>
       </c>
       <c r="G221" t="s">
+        <v>338</v>
+      </c>
+      <c r="H221" t="s">
         <v>803</v>
       </c>
-      <c r="H221" t="s">
+      <c r="I221" t="s">
         <v>804</v>
       </c>
-      <c r="I221" t="s">
+      <c r="J221" t="s">
         <v>805</v>
-      </c>
-      <c r="J221" t="s">
-        <v>338</v>
       </c>
       <c r="K221" t="s">
         <v>806</v>
@@ -10965,16 +10965,16 @@
         <v>802</v>
       </c>
       <c r="G222" t="s">
+        <v>338</v>
+      </c>
+      <c r="H222" t="s">
         <v>803</v>
       </c>
-      <c r="H222" t="s">
+      <c r="I222" t="s">
         <v>804</v>
       </c>
-      <c r="I222" t="s">
+      <c r="J222" t="s">
         <v>805</v>
-      </c>
-      <c r="J222" t="s">
-        <v>338</v>
       </c>
       <c r="K222" t="s">
         <v>806</v>
@@ -10997,16 +10997,16 @@
         <v>802</v>
       </c>
       <c r="G223" t="s">
+        <v>338</v>
+      </c>
+      <c r="H223" t="s">
         <v>803</v>
       </c>
-      <c r="H223" t="s">
+      <c r="I223" t="s">
         <v>804</v>
       </c>
-      <c r="I223" t="s">
+      <c r="J223" t="s">
         <v>805</v>
-      </c>
-      <c r="J223" t="s">
-        <v>338</v>
       </c>
       <c r="K223" t="s">
         <v>806</v>
@@ -11032,16 +11032,16 @@
         <v>802</v>
       </c>
       <c r="G224" t="s">
+        <v>338</v>
+      </c>
+      <c r="H224" t="s">
         <v>803</v>
       </c>
-      <c r="H224" t="s">
+      <c r="I224" t="s">
         <v>804</v>
       </c>
-      <c r="I224" t="s">
+      <c r="J224" t="s">
         <v>805</v>
-      </c>
-      <c r="J224" t="s">
-        <v>338</v>
       </c>
       <c r="K224" t="s">
         <v>806</v>
@@ -11067,16 +11067,16 @@
         <v>802</v>
       </c>
       <c r="G225" t="s">
+        <v>338</v>
+      </c>
+      <c r="H225" t="s">
         <v>803</v>
       </c>
-      <c r="H225" t="s">
+      <c r="I225" t="s">
         <v>804</v>
       </c>
-      <c r="I225" t="s">
+      <c r="J225" t="s">
         <v>805</v>
-      </c>
-      <c r="J225" t="s">
-        <v>338</v>
       </c>
       <c r="K225" t="s">
         <v>806</v>
@@ -11096,25 +11096,25 @@
         <v>14</v>
       </c>
       <c r="E226" t="s">
-        <v>801</v>
+        <v>575</v>
       </c>
       <c r="F226" t="s">
         <v>802</v>
       </c>
       <c r="G226" t="s">
-        <v>575</v>
+        <v>338</v>
       </c>
       <c r="H226" t="s">
+        <v>576</v>
+      </c>
+      <c r="I226" t="s">
         <v>804</v>
       </c>
-      <c r="I226" t="s">
+      <c r="J226" t="s">
         <v>805</v>
       </c>
-      <c r="J226" t="s">
-        <v>338</v>
-      </c>
       <c r="K226" t="s">
-        <v>576</v>
+        <v>806</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -11137,16 +11137,16 @@
         <v>802</v>
       </c>
       <c r="G227" t="s">
+        <v>338</v>
+      </c>
+      <c r="H227" t="s">
         <v>803</v>
       </c>
-      <c r="H227" t="s">
+      <c r="I227" t="s">
         <v>804</v>
       </c>
-      <c r="I227" t="s">
+      <c r="J227" t="s">
         <v>805</v>
-      </c>
-      <c r="J227" t="s">
-        <v>338</v>
       </c>
       <c r="K227" t="s">
         <v>806</v>
@@ -11166,25 +11166,25 @@
         <v>14</v>
       </c>
       <c r="E228" t="s">
-        <v>801</v>
+        <v>337</v>
       </c>
       <c r="F228" t="s">
         <v>802</v>
       </c>
       <c r="G228" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H228" t="s">
+        <v>339</v>
+      </c>
+      <c r="I228" t="s">
         <v>804</v>
       </c>
-      <c r="I228" t="s">
+      <c r="J228" t="s">
         <v>805</v>
       </c>
-      <c r="J228" t="s">
-        <v>338</v>
-      </c>
       <c r="K228" t="s">
-        <v>339</v>
+        <v>806</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -11201,25 +11201,25 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F229" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G229" t="s">
+        <v>338</v>
+      </c>
+      <c r="H229" t="s">
         <v>803</v>
       </c>
-      <c r="H229" t="s">
-        <v>860</v>
-      </c>
       <c r="I229" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J229" t="s">
-        <v>338</v>
+        <v>861</v>
       </c>
       <c r="K229" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -11236,25 +11236,25 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F230" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G230" t="s">
+        <v>338</v>
+      </c>
+      <c r="H230" t="s">
         <v>803</v>
       </c>
-      <c r="H230" t="s">
-        <v>860</v>
-      </c>
       <c r="I230" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J230" t="s">
-        <v>338</v>
+        <v>861</v>
       </c>
       <c r="K230" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -11271,25 +11271,25 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
-        <v>801</v>
+        <v>623</v>
       </c>
       <c r="F231" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G231" t="s">
+        <v>338</v>
+      </c>
+      <c r="H231" t="s">
         <v>566</v>
       </c>
-      <c r="H231" t="s">
-        <v>860</v>
-      </c>
       <c r="I231" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J231" t="s">
-        <v>338</v>
+        <v>861</v>
       </c>
       <c r="K231" t="s">
-        <v>623</v>
+        <v>806</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11306,25 +11306,25 @@
         <v>14</v>
       </c>
       <c r="E232" t="s">
-        <v>801</v>
+        <v>663</v>
       </c>
       <c r="F232" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G232" t="s">
+        <v>338</v>
+      </c>
+      <c r="H232" t="s">
         <v>566</v>
       </c>
-      <c r="H232" t="s">
-        <v>860</v>
-      </c>
       <c r="I232" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J232" t="s">
-        <v>338</v>
+        <v>861</v>
       </c>
       <c r="K232" t="s">
-        <v>663</v>
+        <v>806</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11341,25 +11341,25 @@
         <v>14</v>
       </c>
       <c r="E233" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F233" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G233" t="s">
+        <v>338</v>
+      </c>
+      <c r="H233" t="s">
         <v>803</v>
       </c>
-      <c r="H233" t="s">
-        <v>860</v>
-      </c>
       <c r="I233" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J233" t="s">
-        <v>338</v>
+        <v>861</v>
       </c>
       <c r="K233" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -11376,25 +11376,25 @@
         <v>14</v>
       </c>
       <c r="E234" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F234" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G234" t="s">
+        <v>338</v>
+      </c>
+      <c r="H234" t="s">
         <v>803</v>
       </c>
-      <c r="H234" t="s">
-        <v>860</v>
-      </c>
       <c r="I234" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J234" t="s">
-        <v>338</v>
+        <v>861</v>
       </c>
       <c r="K234" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -11411,25 +11411,25 @@
         <v>14</v>
       </c>
       <c r="E235" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F235" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G235" t="s">
+        <v>338</v>
+      </c>
+      <c r="H235" t="s">
         <v>803</v>
       </c>
-      <c r="H235" t="s">
-        <v>860</v>
-      </c>
       <c r="I235" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J235" t="s">
-        <v>338</v>
+        <v>861</v>
       </c>
       <c r="K235" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -11446,25 +11446,25 @@
         <v>14</v>
       </c>
       <c r="E236" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F236" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G236" t="s">
+        <v>338</v>
+      </c>
+      <c r="H236" t="s">
         <v>803</v>
       </c>
-      <c r="H236" t="s">
-        <v>860</v>
-      </c>
       <c r="I236" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J236" t="s">
-        <v>338</v>
+        <v>861</v>
       </c>
       <c r="K236" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -11481,25 +11481,25 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F237" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G237" t="s">
+        <v>338</v>
+      </c>
+      <c r="H237" t="s">
         <v>803</v>
       </c>
-      <c r="H237" t="s">
-        <v>860</v>
-      </c>
       <c r="I237" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J237" t="s">
-        <v>338</v>
+        <v>861</v>
       </c>
       <c r="K237" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -11516,25 +11516,25 @@
         <v>14</v>
       </c>
       <c r="E238" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F238" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G238" t="s">
+        <v>338</v>
+      </c>
+      <c r="H238" t="s">
         <v>803</v>
       </c>
-      <c r="H238" t="s">
-        <v>860</v>
-      </c>
       <c r="I238" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J238" t="s">
-        <v>338</v>
+        <v>861</v>
       </c>
       <c r="K238" t="s">
-        <v>861</v>
+        <v>806</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -11551,25 +11551,25 @@
         <v>14</v>
       </c>
       <c r="E239" t="s">
-        <v>801</v>
+        <v>892</v>
       </c>
       <c r="F239" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="G239" t="s">
+        <v>338</v>
+      </c>
+      <c r="H239" t="s">
         <v>803</v>
       </c>
-      <c r="H239" t="s">
-        <v>893</v>
-      </c>
       <c r="I239" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J239" t="s">
-        <v>338</v>
+        <v>894</v>
       </c>
       <c r="K239" t="s">
-        <v>894</v>
+        <v>806</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -11586,25 +11586,25 @@
         <v>14</v>
       </c>
       <c r="E240" t="s">
+        <v>337</v>
+      </c>
+      <c r="F240" t="s">
         <v>898</v>
       </c>
-      <c r="F240" t="s">
-        <v>899</v>
-      </c>
       <c r="G240" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H240" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
       <c r="I240" t="s">
         <v>899</v>
       </c>
       <c r="J240" t="s">
-        <v>338</v>
+        <v>900</v>
       </c>
       <c r="K240" t="s">
-        <v>339</v>
+        <v>900</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -11621,25 +11621,25 @@
         <v>14</v>
       </c>
       <c r="E241" t="s">
+        <v>337</v>
+      </c>
+      <c r="F241" t="s">
         <v>898</v>
       </c>
-      <c r="F241" t="s">
-        <v>899</v>
-      </c>
       <c r="G241" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H241" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
       <c r="I241" t="s">
         <v>899</v>
       </c>
       <c r="J241" t="s">
-        <v>338</v>
+        <v>900</v>
       </c>
       <c r="K241" t="s">
-        <v>339</v>
+        <v>900</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -11656,25 +11656,25 @@
         <v>14</v>
       </c>
       <c r="E242" t="s">
+        <v>337</v>
+      </c>
+      <c r="F242" t="s">
         <v>898</v>
       </c>
-      <c r="F242" t="s">
-        <v>899</v>
-      </c>
       <c r="G242" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H242" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
       <c r="I242" t="s">
         <v>899</v>
       </c>
       <c r="J242" t="s">
-        <v>338</v>
+        <v>900</v>
       </c>
       <c r="K242" t="s">
-        <v>339</v>
+        <v>900</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -11691,25 +11691,25 @@
         <v>14</v>
       </c>
       <c r="E243" t="s">
+        <v>337</v>
+      </c>
+      <c r="F243" t="s">
         <v>898</v>
       </c>
-      <c r="F243" t="s">
-        <v>899</v>
-      </c>
       <c r="G243" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H243" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
       <c r="I243" t="s">
         <v>899</v>
       </c>
       <c r="J243" t="s">
-        <v>338</v>
+        <v>900</v>
       </c>
       <c r="K243" t="s">
-        <v>339</v>
+        <v>900</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -11726,25 +11726,25 @@
         <v>14</v>
       </c>
       <c r="E244" t="s">
+        <v>337</v>
+      </c>
+      <c r="F244" t="s">
         <v>898</v>
       </c>
-      <c r="F244" t="s">
-        <v>899</v>
-      </c>
       <c r="G244" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H244" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
       <c r="I244" t="s">
         <v>899</v>
       </c>
       <c r="J244" t="s">
-        <v>338</v>
+        <v>900</v>
       </c>
       <c r="K244" t="s">
-        <v>339</v>
+        <v>900</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -11761,25 +11761,25 @@
         <v>14</v>
       </c>
       <c r="E245" t="s">
+        <v>337</v>
+      </c>
+      <c r="F245" t="s">
         <v>898</v>
       </c>
-      <c r="F245" t="s">
-        <v>899</v>
-      </c>
       <c r="G245" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H245" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
       <c r="I245" t="s">
         <v>899</v>
       </c>
       <c r="J245" t="s">
-        <v>338</v>
+        <v>900</v>
       </c>
       <c r="K245" t="s">
-        <v>339</v>
+        <v>900</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -11793,25 +11793,25 @@
         <v>14</v>
       </c>
       <c r="E246" t="s">
-        <v>898</v>
+        <v>918</v>
       </c>
       <c r="F246" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="G246" t="s">
-        <v>533</v>
+        <v>338</v>
       </c>
       <c r="H246" t="s">
-        <v>919</v>
+        <v>534</v>
       </c>
       <c r="I246" t="s">
         <v>899</v>
       </c>
       <c r="J246" t="s">
-        <v>338</v>
+        <v>920</v>
       </c>
       <c r="K246" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11828,19 +11828,19 @@
         <v>14</v>
       </c>
       <c r="E247" t="s">
+        <v>196</v>
+      </c>
+      <c r="G247" t="s">
+        <v>197</v>
+      </c>
+      <c r="H247" t="s">
+        <v>198</v>
+      </c>
+      <c r="I247" t="s">
         <v>924</v>
       </c>
-      <c r="G247" t="s">
-        <v>196</v>
-      </c>
-      <c r="I247" t="s">
+      <c r="K247" t="s">
         <v>925</v>
-      </c>
-      <c r="J247" t="s">
-        <v>197</v>
-      </c>
-      <c r="K247" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -11857,19 +11857,19 @@
         <v>14</v>
       </c>
       <c r="E248" t="s">
+        <v>196</v>
+      </c>
+      <c r="G248" t="s">
+        <v>197</v>
+      </c>
+      <c r="H248" t="s">
+        <v>198</v>
+      </c>
+      <c r="I248" t="s">
         <v>924</v>
       </c>
-      <c r="G248" t="s">
-        <v>196</v>
-      </c>
-      <c r="I248" t="s">
+      <c r="K248" t="s">
         <v>925</v>
-      </c>
-      <c r="J248" t="s">
-        <v>197</v>
-      </c>
-      <c r="K248" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -11886,19 +11886,19 @@
         <v>14</v>
       </c>
       <c r="E249" t="s">
+        <v>932</v>
+      </c>
+      <c r="G249" t="s">
+        <v>197</v>
+      </c>
+      <c r="H249" t="s">
+        <v>933</v>
+      </c>
+      <c r="I249" t="s">
         <v>924</v>
       </c>
-      <c r="G249" t="s">
-        <v>932</v>
-      </c>
-      <c r="I249" t="s">
+      <c r="K249" t="s">
         <v>925</v>
-      </c>
-      <c r="J249" t="s">
-        <v>197</v>
-      </c>
-      <c r="K249" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -11915,19 +11915,19 @@
         <v>14</v>
       </c>
       <c r="E250" t="s">
+        <v>196</v>
+      </c>
+      <c r="G250" t="s">
+        <v>197</v>
+      </c>
+      <c r="H250" t="s">
+        <v>198</v>
+      </c>
+      <c r="I250" t="s">
         <v>924</v>
       </c>
-      <c r="G250" t="s">
-        <v>196</v>
-      </c>
-      <c r="I250" t="s">
+      <c r="K250" t="s">
         <v>925</v>
-      </c>
-      <c r="J250" t="s">
-        <v>197</v>
-      </c>
-      <c r="K250" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -11941,19 +11941,19 @@
         <v>14</v>
       </c>
       <c r="E251" t="s">
+        <v>196</v>
+      </c>
+      <c r="G251" t="s">
+        <v>197</v>
+      </c>
+      <c r="H251" t="s">
+        <v>198</v>
+      </c>
+      <c r="I251" t="s">
         <v>924</v>
       </c>
-      <c r="G251" t="s">
-        <v>196</v>
-      </c>
-      <c r="I251" t="s">
+      <c r="K251" t="s">
         <v>925</v>
-      </c>
-      <c r="J251" t="s">
-        <v>197</v>
-      </c>
-      <c r="K251" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -11970,19 +11970,19 @@
         <v>14</v>
       </c>
       <c r="E252" t="s">
+        <v>196</v>
+      </c>
+      <c r="G252" t="s">
+        <v>197</v>
+      </c>
+      <c r="H252" t="s">
+        <v>198</v>
+      </c>
+      <c r="I252" t="s">
         <v>924</v>
       </c>
-      <c r="G252" t="s">
-        <v>196</v>
-      </c>
-      <c r="I252" t="s">
+      <c r="K252" t="s">
         <v>925</v>
-      </c>
-      <c r="J252" t="s">
-        <v>197</v>
-      </c>
-      <c r="K252" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -11999,13 +11999,13 @@
         <v>944</v>
       </c>
       <c r="G253" t="s">
+        <v>338</v>
+      </c>
+      <c r="H253" t="s">
         <v>945</v>
       </c>
       <c r="I253" t="s">
         <v>946</v>
-      </c>
-      <c r="J253" t="s">
-        <v>338</v>
       </c>
       <c r="K253" t="s">
         <v>947</v>
@@ -12025,19 +12025,19 @@
         <v>14</v>
       </c>
       <c r="E254" t="s">
-        <v>944</v>
+        <v>454</v>
       </c>
       <c r="G254" t="s">
-        <v>454</v>
+        <v>189</v>
+      </c>
+      <c r="H254" t="s">
+        <v>455</v>
       </c>
       <c r="I254" t="s">
         <v>946</v>
       </c>
-      <c r="J254" t="s">
-        <v>191</v>
-      </c>
       <c r="K254" t="s">
-        <v>455</v>
+        <v>947</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -12054,19 +12054,19 @@
         <v>14</v>
       </c>
       <c r="E255" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="G255" t="s">
-        <v>954</v>
+        <v>189</v>
+      </c>
+      <c r="H255" t="s">
+        <v>955</v>
       </c>
       <c r="I255" t="s">
         <v>946</v>
       </c>
-      <c r="J255" t="s">
-        <v>191</v>
-      </c>
       <c r="K255" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -12083,19 +12083,19 @@
         <v>14</v>
       </c>
       <c r="E256" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="G256" t="s">
-        <v>954</v>
+        <v>189</v>
+      </c>
+      <c r="H256" t="s">
+        <v>955</v>
       </c>
       <c r="I256" t="s">
         <v>946</v>
       </c>
-      <c r="J256" t="s">
-        <v>191</v>
-      </c>
       <c r="K256" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -12112,19 +12112,19 @@
         <v>14</v>
       </c>
       <c r="E257" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="G257" t="s">
-        <v>954</v>
+        <v>189</v>
+      </c>
+      <c r="H257" t="s">
+        <v>955</v>
       </c>
       <c r="I257" t="s">
         <v>946</v>
       </c>
-      <c r="J257" t="s">
-        <v>191</v>
-      </c>
       <c r="K257" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -12141,19 +12141,19 @@
         <v>14</v>
       </c>
       <c r="E258" t="s">
-        <v>944</v>
+        <v>705</v>
       </c>
       <c r="G258" t="s">
+        <v>338</v>
+      </c>
+      <c r="H258" t="s">
         <v>707</v>
       </c>
       <c r="I258" t="s">
         <v>946</v>
       </c>
-      <c r="J258" t="s">
-        <v>338</v>
-      </c>
       <c r="K258" t="s">
-        <v>710</v>
+        <v>947</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -12170,19 +12170,19 @@
         <v>14</v>
       </c>
       <c r="E259" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="G259" t="s">
-        <v>954</v>
+        <v>189</v>
+      </c>
+      <c r="H259" t="s">
+        <v>955</v>
       </c>
       <c r="I259" t="s">
         <v>946</v>
       </c>
-      <c r="J259" t="s">
-        <v>191</v>
-      </c>
       <c r="K259" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -12199,19 +12199,19 @@
         <v>14</v>
       </c>
       <c r="E260" t="s">
-        <v>944</v>
+        <v>337</v>
       </c>
       <c r="G260" t="s">
-        <v>337</v>
+        <v>338</v>
+      </c>
+      <c r="H260" t="s">
+        <v>339</v>
       </c>
       <c r="I260" t="s">
         <v>946</v>
       </c>
-      <c r="J260" t="s">
-        <v>338</v>
-      </c>
       <c r="K260" t="s">
-        <v>339</v>
+        <v>947</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -12228,19 +12228,19 @@
         <v>14</v>
       </c>
       <c r="E261" t="s">
-        <v>944</v>
+        <v>973</v>
       </c>
       <c r="G261" t="s">
-        <v>973</v>
+        <v>406</v>
+      </c>
+      <c r="H261" t="s">
+        <v>974</v>
       </c>
       <c r="I261" t="s">
         <v>946</v>
       </c>
-      <c r="J261" t="s">
-        <v>406</v>
-      </c>
       <c r="K261" t="s">
-        <v>974</v>
+        <v>947</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -12257,19 +12257,19 @@
         <v>14</v>
       </c>
       <c r="E262" t="s">
-        <v>944</v>
+        <v>337</v>
       </c>
       <c r="G262" t="s">
-        <v>337</v>
+        <v>338</v>
+      </c>
+      <c r="H262" t="s">
+        <v>339</v>
       </c>
       <c r="I262" t="s">
         <v>946</v>
       </c>
-      <c r="J262" t="s">
-        <v>338</v>
-      </c>
       <c r="K262" t="s">
-        <v>339</v>
+        <v>947</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -12286,19 +12286,19 @@
         <v>14</v>
       </c>
       <c r="E263" t="s">
-        <v>944</v>
+        <v>981</v>
       </c>
       <c r="G263" t="s">
-        <v>981</v>
+        <v>378</v>
+      </c>
+      <c r="H263" t="s">
+        <v>982</v>
       </c>
       <c r="I263" t="s">
         <v>946</v>
       </c>
-      <c r="J263" t="s">
-        <v>378</v>
-      </c>
       <c r="K263" t="s">
-        <v>982</v>
+        <v>947</v>
       </c>
     </row>
     <row r="264" spans="1:11">
@@ -12315,19 +12315,19 @@
         <v>14</v>
       </c>
       <c r="E264" t="s">
-        <v>944</v>
+        <v>58</v>
       </c>
       <c r="G264" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="H264" t="s">
+        <v>60</v>
       </c>
       <c r="I264" t="s">
         <v>946</v>
       </c>
-      <c r="J264" t="s">
-        <v>59</v>
-      </c>
       <c r="K264" t="s">
-        <v>60</v>
+        <v>947</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -12344,19 +12344,19 @@
         <v>14</v>
       </c>
       <c r="E265" t="s">
-        <v>944</v>
+        <v>15</v>
       </c>
       <c r="G265" t="s">
         <v>17</v>
       </c>
+      <c r="H265" t="s">
+        <v>18</v>
+      </c>
       <c r="I265" t="s">
         <v>946</v>
       </c>
-      <c r="J265" t="s">
-        <v>20</v>
-      </c>
       <c r="K265" t="s">
-        <v>21</v>
+        <v>947</v>
       </c>
     </row>
     <row r="266" spans="1:11">
@@ -12373,19 +12373,19 @@
         <v>14</v>
       </c>
       <c r="E266" t="s">
-        <v>944</v>
+        <v>992</v>
       </c>
       <c r="G266" t="s">
-        <v>992</v>
+        <v>235</v>
+      </c>
+      <c r="H266" t="s">
+        <v>993</v>
       </c>
       <c r="I266" t="s">
         <v>946</v>
       </c>
-      <c r="J266" t="s">
-        <v>238</v>
-      </c>
       <c r="K266" t="s">
-        <v>993</v>
+        <v>947</v>
       </c>
     </row>
     <row r="267" spans="1:11">
@@ -12402,19 +12402,19 @@
         <v>14</v>
       </c>
       <c r="E267" t="s">
+        <v>243</v>
+      </c>
+      <c r="G267" t="s">
+        <v>235</v>
+      </c>
+      <c r="H267" t="s">
+        <v>244</v>
+      </c>
+      <c r="I267" t="s">
         <v>997</v>
       </c>
-      <c r="G267" t="s">
-        <v>243</v>
-      </c>
-      <c r="I267" t="s">
+      <c r="K267" t="s">
         <v>998</v>
-      </c>
-      <c r="J267" t="s">
-        <v>238</v>
-      </c>
-      <c r="K267" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -12431,19 +12431,19 @@
         <v>14</v>
       </c>
       <c r="E268" t="s">
+        <v>420</v>
+      </c>
+      <c r="G268" t="s">
+        <v>378</v>
+      </c>
+      <c r="H268" t="s">
+        <v>421</v>
+      </c>
+      <c r="I268" t="s">
         <v>1002</v>
       </c>
-      <c r="G268" t="s">
-        <v>421</v>
-      </c>
-      <c r="I268" t="s">
+      <c r="K268" t="s">
         <v>1003</v>
-      </c>
-      <c r="J268" t="s">
-        <v>378</v>
-      </c>
-      <c r="K268" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -12460,19 +12460,19 @@
         <v>14</v>
       </c>
       <c r="E269" t="s">
+        <v>243</v>
+      </c>
+      <c r="G269" t="s">
+        <v>235</v>
+      </c>
+      <c r="H269" t="s">
+        <v>244</v>
+      </c>
+      <c r="I269" t="s">
         <v>1007</v>
       </c>
-      <c r="G269" t="s">
-        <v>243</v>
-      </c>
-      <c r="I269" t="s">
+      <c r="K269" t="s">
         <v>1008</v>
-      </c>
-      <c r="J269" t="s">
-        <v>238</v>
-      </c>
-      <c r="K269" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -12489,19 +12489,19 @@
         <v>14</v>
       </c>
       <c r="E270" t="s">
+        <v>243</v>
+      </c>
+      <c r="G270" t="s">
+        <v>235</v>
+      </c>
+      <c r="H270" t="s">
+        <v>244</v>
+      </c>
+      <c r="I270" t="s">
         <v>1007</v>
       </c>
-      <c r="G270" t="s">
-        <v>243</v>
-      </c>
-      <c r="I270" t="s">
+      <c r="K270" t="s">
         <v>1008</v>
-      </c>
-      <c r="J270" t="s">
-        <v>238</v>
-      </c>
-      <c r="K270" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -12521,13 +12521,13 @@
         <v>1015</v>
       </c>
       <c r="G271" t="s">
+        <v>235</v>
+      </c>
+      <c r="H271" t="s">
         <v>1016</v>
       </c>
       <c r="I271" t="s">
         <v>1017</v>
-      </c>
-      <c r="J271" t="s">
-        <v>238</v>
       </c>
       <c r="K271" t="s">
         <v>1018</v>
@@ -12547,13 +12547,13 @@
         <v>1015</v>
       </c>
       <c r="G272" t="s">
+        <v>235</v>
+      </c>
+      <c r="H272" t="s">
         <v>1016</v>
       </c>
       <c r="I272" t="s">
         <v>1017</v>
-      </c>
-      <c r="J272" t="s">
-        <v>238</v>
       </c>
       <c r="K272" t="s">
         <v>1018</v>
@@ -12576,13 +12576,13 @@
         <v>1015</v>
       </c>
       <c r="G273" t="s">
+        <v>235</v>
+      </c>
+      <c r="H273" t="s">
         <v>1016</v>
       </c>
       <c r="I273" t="s">
         <v>1017</v>
-      </c>
-      <c r="J273" t="s">
-        <v>238</v>
       </c>
       <c r="K273" t="s">
         <v>1018</v>
@@ -12602,13 +12602,13 @@
         <v>1015</v>
       </c>
       <c r="G274" t="s">
+        <v>235</v>
+      </c>
+      <c r="H274" t="s">
         <v>1016</v>
       </c>
       <c r="I274" t="s">
         <v>1017</v>
-      </c>
-      <c r="J274" t="s">
-        <v>238</v>
       </c>
       <c r="K274" t="s">
         <v>1018</v>
@@ -12631,13 +12631,13 @@
         <v>1015</v>
       </c>
       <c r="G275" t="s">
+        <v>235</v>
+      </c>
+      <c r="H275" t="s">
         <v>1016</v>
       </c>
       <c r="I275" t="s">
         <v>1017</v>
-      </c>
-      <c r="J275" t="s">
-        <v>238</v>
       </c>
       <c r="K275" t="s">
         <v>1018</v>
@@ -12660,13 +12660,13 @@
         <v>1015</v>
       </c>
       <c r="G276" t="s">
+        <v>235</v>
+      </c>
+      <c r="H276" t="s">
         <v>1016</v>
       </c>
       <c r="I276" t="s">
         <v>1017</v>
-      </c>
-      <c r="J276" t="s">
-        <v>238</v>
       </c>
       <c r="K276" t="s">
         <v>1018</v>
@@ -12689,13 +12689,13 @@
         <v>1015</v>
       </c>
       <c r="G277" t="s">
+        <v>235</v>
+      </c>
+      <c r="H277" t="s">
         <v>1016</v>
       </c>
       <c r="I277" t="s">
         <v>1017</v>
-      </c>
-      <c r="J277" t="s">
-        <v>238</v>
       </c>
       <c r="K277" t="s">
         <v>1018</v>
@@ -12715,19 +12715,19 @@
         <v>14</v>
       </c>
       <c r="E278" t="s">
+        <v>420</v>
+      </c>
+      <c r="G278" t="s">
+        <v>378</v>
+      </c>
+      <c r="H278" t="s">
+        <v>421</v>
+      </c>
+      <c r="I278" t="s">
         <v>1038</v>
       </c>
-      <c r="G278" t="s">
-        <v>421</v>
-      </c>
-      <c r="I278" t="s">
+      <c r="K278" t="s">
         <v>1039</v>
-      </c>
-      <c r="J278" t="s">
-        <v>378</v>
-      </c>
-      <c r="K278" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -12744,19 +12744,19 @@
         <v>14</v>
       </c>
       <c r="E279" t="s">
+        <v>92</v>
+      </c>
+      <c r="G279" t="s">
+        <v>59</v>
+      </c>
+      <c r="H279" t="s">
+        <v>94</v>
+      </c>
+      <c r="I279" t="s">
         <v>1038</v>
       </c>
-      <c r="G279" t="s">
-        <v>94</v>
-      </c>
-      <c r="I279" t="s">
+      <c r="K279" t="s">
         <v>1039</v>
-      </c>
-      <c r="J279" t="s">
-        <v>59</v>
-      </c>
-      <c r="K279" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -12773,19 +12773,19 @@
         <v>14</v>
       </c>
       <c r="E280" t="s">
-        <v>1038</v>
+        <v>15</v>
       </c>
       <c r="G280" t="s">
         <v>17</v>
       </c>
+      <c r="H280" t="s">
+        <v>18</v>
+      </c>
       <c r="I280" t="s">
+        <v>1038</v>
+      </c>
+      <c r="K280" t="s">
         <v>1039</v>
-      </c>
-      <c r="J280" t="s">
-        <v>20</v>
-      </c>
-      <c r="K280" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="281" spans="1:11">
@@ -12802,19 +12802,19 @@
         <v>14</v>
       </c>
       <c r="E281" t="s">
+        <v>352</v>
+      </c>
+      <c r="G281" t="s">
+        <v>235</v>
+      </c>
+      <c r="H281" t="s">
+        <v>353</v>
+      </c>
+      <c r="I281" t="s">
         <v>1038</v>
       </c>
-      <c r="G281" t="s">
-        <v>352</v>
-      </c>
-      <c r="I281" t="s">
+      <c r="K281" t="s">
         <v>1039</v>
-      </c>
-      <c r="J281" t="s">
-        <v>238</v>
-      </c>
-      <c r="K281" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -12831,19 +12831,19 @@
         <v>14</v>
       </c>
       <c r="E282" t="s">
+        <v>253</v>
+      </c>
+      <c r="G282" t="s">
+        <v>254</v>
+      </c>
+      <c r="H282" t="s">
+        <v>255</v>
+      </c>
+      <c r="I282" t="s">
         <v>1038</v>
       </c>
-      <c r="G282" t="s">
-        <v>253</v>
-      </c>
-      <c r="I282" t="s">
+      <c r="K282" t="s">
         <v>1039</v>
-      </c>
-      <c r="J282" t="s">
-        <v>254</v>
-      </c>
-      <c r="K282" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -12860,19 +12860,19 @@
         <v>14</v>
       </c>
       <c r="E283" t="s">
+        <v>892</v>
+      </c>
+      <c r="G283" t="s">
+        <v>338</v>
+      </c>
+      <c r="H283" t="s">
+        <v>803</v>
+      </c>
+      <c r="I283" t="s">
         <v>1055</v>
       </c>
-      <c r="G283" t="s">
-        <v>803</v>
-      </c>
-      <c r="I283" t="s">
+      <c r="K283" t="s">
         <v>1056</v>
-      </c>
-      <c r="J283" t="s">
-        <v>338</v>
-      </c>
-      <c r="K283" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -12889,19 +12889,19 @@
         <v>14</v>
       </c>
       <c r="E284" t="s">
+        <v>253</v>
+      </c>
+      <c r="G284" t="s">
+        <v>254</v>
+      </c>
+      <c r="H284" t="s">
+        <v>255</v>
+      </c>
+      <c r="I284" t="s">
         <v>1060</v>
       </c>
-      <c r="G284" t="s">
-        <v>253</v>
-      </c>
-      <c r="I284" t="s">
+      <c r="K284" t="s">
         <v>1061</v>
-      </c>
-      <c r="J284" t="s">
-        <v>254</v>
-      </c>
-      <c r="K284" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -12915,19 +12915,19 @@
         <v>14</v>
       </c>
       <c r="E285" t="s">
+        <v>352</v>
+      </c>
+      <c r="G285" t="s">
+        <v>235</v>
+      </c>
+      <c r="H285" t="s">
+        <v>353</v>
+      </c>
+      <c r="I285" t="s">
         <v>1064</v>
       </c>
-      <c r="G285" t="s">
-        <v>352</v>
-      </c>
-      <c r="I285" t="s">
+      <c r="K285" t="s">
         <v>1065</v>
-      </c>
-      <c r="J285" t="s">
-        <v>238</v>
-      </c>
-      <c r="K285" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -12944,19 +12944,19 @@
         <v>14</v>
       </c>
       <c r="E286" t="s">
+        <v>981</v>
+      </c>
+      <c r="G286" t="s">
+        <v>378</v>
+      </c>
+      <c r="H286" t="s">
+        <v>982</v>
+      </c>
+      <c r="I286" t="s">
         <v>1069</v>
       </c>
-      <c r="G286" t="s">
-        <v>981</v>
-      </c>
-      <c r="I286" t="s">
+      <c r="K286" t="s">
         <v>1070</v>
-      </c>
-      <c r="J286" t="s">
-        <v>378</v>
-      </c>
-      <c r="K286" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -12973,19 +12973,19 @@
         <v>14</v>
       </c>
       <c r="E287" t="s">
+        <v>981</v>
+      </c>
+      <c r="G287" t="s">
+        <v>378</v>
+      </c>
+      <c r="H287" t="s">
+        <v>982</v>
+      </c>
+      <c r="I287" t="s">
         <v>1069</v>
       </c>
-      <c r="G287" t="s">
-        <v>981</v>
-      </c>
-      <c r="I287" t="s">
+      <c r="K287" t="s">
         <v>1070</v>
-      </c>
-      <c r="J287" t="s">
-        <v>378</v>
-      </c>
-      <c r="K287" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -13002,19 +13002,19 @@
         <v>14</v>
       </c>
       <c r="E288" t="s">
+        <v>75</v>
+      </c>
+      <c r="G288" t="s">
+        <v>17</v>
+      </c>
+      <c r="H288" t="s">
+        <v>76</v>
+      </c>
+      <c r="I288" t="s">
         <v>1069</v>
       </c>
-      <c r="G288" t="s">
-        <v>75</v>
-      </c>
-      <c r="I288" t="s">
+      <c r="K288" t="s">
         <v>1070</v>
-      </c>
-      <c r="J288" t="s">
-        <v>20</v>
-      </c>
-      <c r="K288" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -13031,19 +13031,19 @@
         <v>14</v>
       </c>
       <c r="E289" t="s">
+        <v>58</v>
+      </c>
+      <c r="G289" t="s">
+        <v>59</v>
+      </c>
+      <c r="H289" t="s">
+        <v>60</v>
+      </c>
+      <c r="I289" t="s">
         <v>1069</v>
       </c>
-      <c r="G289" t="s">
-        <v>58</v>
-      </c>
-      <c r="I289" t="s">
+      <c r="K289" t="s">
         <v>1070</v>
-      </c>
-      <c r="J289" t="s">
-        <v>59</v>
-      </c>
-      <c r="K289" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="290" spans="1:11">
@@ -13060,19 +13060,19 @@
         <v>14</v>
       </c>
       <c r="E290" t="s">
+        <v>58</v>
+      </c>
+      <c r="G290" t="s">
+        <v>59</v>
+      </c>
+      <c r="H290" t="s">
+        <v>60</v>
+      </c>
+      <c r="I290" t="s">
         <v>1069</v>
       </c>
-      <c r="G290" t="s">
-        <v>58</v>
-      </c>
-      <c r="I290" t="s">
+      <c r="K290" t="s">
         <v>1070</v>
-      </c>
-      <c r="J290" t="s">
-        <v>59</v>
-      </c>
-      <c r="K290" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -13089,19 +13089,19 @@
         <v>14</v>
       </c>
       <c r="E291" t="s">
+        <v>352</v>
+      </c>
+      <c r="G291" t="s">
+        <v>235</v>
+      </c>
+      <c r="H291" t="s">
+        <v>353</v>
+      </c>
+      <c r="I291" t="s">
         <v>1069</v>
       </c>
-      <c r="G291" t="s">
-        <v>352</v>
-      </c>
-      <c r="I291" t="s">
+      <c r="K291" t="s">
         <v>1070</v>
-      </c>
-      <c r="J291" t="s">
-        <v>238</v>
-      </c>
-      <c r="K291" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -13118,19 +13118,19 @@
         <v>14</v>
       </c>
       <c r="E292" t="s">
+        <v>352</v>
+      </c>
+      <c r="G292" t="s">
+        <v>235</v>
+      </c>
+      <c r="H292" t="s">
+        <v>353</v>
+      </c>
+      <c r="I292" t="s">
         <v>1069</v>
       </c>
-      <c r="G292" t="s">
-        <v>352</v>
-      </c>
-      <c r="I292" t="s">
+      <c r="K292" t="s">
         <v>1070</v>
-      </c>
-      <c r="J292" t="s">
-        <v>238</v>
-      </c>
-      <c r="K292" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -13147,19 +13147,19 @@
         <v>14</v>
       </c>
       <c r="E293" t="s">
+        <v>352</v>
+      </c>
+      <c r="G293" t="s">
+        <v>235</v>
+      </c>
+      <c r="H293" t="s">
+        <v>353</v>
+      </c>
+      <c r="I293" t="s">
         <v>1069</v>
       </c>
-      <c r="G293" t="s">
-        <v>352</v>
-      </c>
-      <c r="I293" t="s">
+      <c r="K293" t="s">
         <v>1070</v>
-      </c>
-      <c r="J293" t="s">
-        <v>238</v>
-      </c>
-      <c r="K293" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -13176,19 +13176,19 @@
         <v>14</v>
       </c>
       <c r="E294" t="s">
+        <v>352</v>
+      </c>
+      <c r="G294" t="s">
+        <v>235</v>
+      </c>
+      <c r="H294" t="s">
+        <v>353</v>
+      </c>
+      <c r="I294" t="s">
         <v>1069</v>
       </c>
-      <c r="G294" t="s">
-        <v>352</v>
-      </c>
-      <c r="I294" t="s">
+      <c r="K294" t="s">
         <v>1070</v>
-      </c>
-      <c r="J294" t="s">
-        <v>238</v>
-      </c>
-      <c r="K294" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -13205,19 +13205,19 @@
         <v>14</v>
       </c>
       <c r="E295" t="s">
+        <v>352</v>
+      </c>
+      <c r="G295" t="s">
+        <v>235</v>
+      </c>
+      <c r="H295" t="s">
+        <v>353</v>
+      </c>
+      <c r="I295" t="s">
         <v>1098</v>
       </c>
-      <c r="G295" t="s">
-        <v>352</v>
-      </c>
-      <c r="I295" t="s">
+      <c r="K295" t="s">
         <v>1099</v>
-      </c>
-      <c r="J295" t="s">
-        <v>238</v>
-      </c>
-      <c r="K295" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="296" spans="1:11">
@@ -13234,19 +13234,19 @@
         <v>14</v>
       </c>
       <c r="E296" t="s">
+        <v>352</v>
+      </c>
+      <c r="G296" t="s">
+        <v>235</v>
+      </c>
+      <c r="H296" t="s">
+        <v>353</v>
+      </c>
+      <c r="I296" t="s">
         <v>1098</v>
       </c>
-      <c r="G296" t="s">
-        <v>352</v>
-      </c>
-      <c r="I296" t="s">
+      <c r="K296" t="s">
         <v>1099</v>
-      </c>
-      <c r="J296" t="s">
-        <v>238</v>
-      </c>
-      <c r="K296" t="s">
-        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -28,27 +28,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -61,27 +61,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>09 - Education</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -130,18 +130,18 @@
     <t>Formal and non-formal primary education for children; all elementary and first cycle systematic instruction; provision of learning materials.</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>112</t>
+    <t>Basic Education</t>
   </si>
   <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>Second cycle systematic instruction at senior levels.</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>09.2.2 - Upper‐secondary education (IS)</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>Secondary Education</t>
   </si>
   <si>
@@ -256,18 +256,18 @@
     <t>Degree and diploma programmes at universities, colleges and polytechnics; scholarships.</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>Post-Secondary Education</t>
   </si>
   <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -292,24 +292,24 @@
     <t>Health sector policy, planning and programmes; aid to health ministries, public health administration; institution capacity building and advice; medical insurance programmes; including health system strengthening and health governance; unspecified health activities.</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>121</t>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>120</t>
   </si>
   <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -520,12 +520,12 @@
     <t>Population/development policies; demographic research/analysis; reproductive health research; unspecified population activities. (Use purpose code 15190 for data on migration and refugees. Use code 13096 for census work, vital registration and migration data collection.)</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -580,21 +580,21 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -715,27 +715,27 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>01 - General public services</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -1276,18 +1276,18 @@
     <t>Social protection or social security strategies, legislation and administration; institution capacity building and advice; social security and other social schemes; support programmes, cash benefits, pensions and special programmes for older persons, orphans, persons with disabilities, children, mothers with newborns, those living in poverty, without jobs and other vulnerable groups; social dimensions of structural adjustment.</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1486,12 +1486,12 @@
     <t>Transport sector policy, planning and programmes; aid to transport ministries; institution capacity building and advice; unspecified transport; activities that combine road, rail, water and/or air transport. Includes prevention of road accidents. Whenever possible, report transport of goods under the sector of the good being transported.</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21011</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>Communications sector policy, planning and programmes; institution capacity building and advice; including postal services development; unspecified communications activities.</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22011</t>
   </si>
   <si>
@@ -1708,24 +1708,24 @@
     <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>231</t>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>230</t>
   </si>
   <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -1948,12 +1948,12 @@
     <t>See note regarding ODA eligibility of nuclear energy.</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>04.3.3 - Nuclear fuel (CS)</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -2032,12 +2032,12 @@
     <t>Finance sector policy, planning and programmes; institution capacity building and advice; financial markets and systems.</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -2089,12 +2089,12 @@
     <t>Public sector policies and institution support to the business environment and investment climate, including business regulations, property rights, non-discrimination, investment promotion, competition policy, enterprises law, private-public partnerships.</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -2131,24 +2131,24 @@
     <t>Agricultural sector policy, planning and programmes; aid to agricultural ministries; institution capacity building and advice; unspecified agriculture.</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>311</t>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>310</t>
   </si>
   <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2311,12 +2311,12 @@
     <t>Forestry sector policy, planning and programmes; institution capacity building and advice; forest surveys; unspecified forestry and agro-forestry activities.</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>04.2.2 - Forestry (CS)</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>Forestry</t>
   </si>
   <si>
@@ -2368,12 +2368,12 @@
     <t>Fishing sector policy, planning and programmes; institution capacity building and advice; ocean and coastal fishing; marine and freshwater fish surveys and prospecting; fishing boats/equipment; unspecified fishing activities.</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>04.2.3 - Fishing and hunting (CS)</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>Fishing</t>
   </si>
   <si>
@@ -2419,24 +2419,24 @@
     <t>Industrial sector policy, planning and programmes; institution capacity building and advice; unspecified industrial activities; manufacturing of goods not specified below.</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>321</t>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>320</t>
   </si>
   <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2593,12 +2593,12 @@
     <t>Mineral and mining sector policy, planning and programmes; mining legislation, mining cadastre, mineral resources inventory, information systems, institution capacity building and advice; unspecified mineral resources exploitation.</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
@@ -2692,12 +2692,12 @@
     <t>Construction sector policy and planning; excluding construction activities within specific sectors (e.g., hospital or school construction).</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>04.4.3 - Construction (CS)</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>Construction</t>
   </si>
   <si>
@@ -2710,15 +2710,15 @@
     <t>Trade policy and planning; support to ministries and departments responsible for trade policy; trade-related legislation and regulatory reforms; policy analysis and implementation of multilateral trade agreements e.g. technical barriers to trade and sanitary and phytosanitary measures (TBT/SPS) except at regional level (see 33130); mainstreaming trade in national development strategies (e.g. poverty reduction strategy papers); wholesale/retail trade; unspecified trade and trade promotion activities.</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
     <t>330</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -2770,12 +2770,12 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>Tourism</t>
   </si>
   <si>
@@ -2788,12 +2788,12 @@
     <t>Environmental policy, laws, regulations and economic instruments; administrational institutions and practices; environmental and land use planning and decision-making procedures; seminars, meetings; miscellaneous conservation and protection measures not specified below.</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -2848,18 +2848,18 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -3007,12 +3007,12 @@
     <t>Unearmarked contributions to the government budget; support for the implementation of macroeconomic reforms (structural adjustment programmes, poverty reduction strategies); general programme assistance (when not allocable by sector).</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
@@ -3022,12 +3022,12 @@
     <t>Supply of edible human food under national or international programmes including transport costs, cash payments made for food supplies; project food assistance aid and food assistance aid for market sales when benefiting sector not specified. Excludes food security policy and administrative management (43071), household food security programmes (43072) and emergency food assistance aid (72040). Report as multilateral: i) food assistance aid by EU financed out of its budget and allocated pro rata to EU member countries; and ii) core contributions to the World Food Programme.</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
@@ -3037,12 +3037,12 @@
     <t>Capital goods and services; lines of credit.</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -3061,18 +3061,18 @@
     <t>Actions falling outside the code headings below.</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -3130,12 +3130,12 @@
     <t>Shelter, water, sanitation, education, health services including supply of medicines and malnutrition management, including medical nutrition management; supply of other nonfood relief items (including cash and voucher delivery modalities) for the benefit of crisisaffected people, including refugees and internally displaced people in developing countries, Includes assistance delivered by or coordinated by international civil protection units in the immediate aftermath of a disaster (in-kind assistance, deployment of specially-equipped teams, logistics and transportation, or assessment and coordination by experts sent to the field). Also includes measures to promote and protect the safety, well-being, dignity and integrity of crisis-affected people including refugees and internally displaced persons in developing countries. (Activities designed to protect the security of persons or properties through the use or display of force are not reportable as ODA.)</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72011</t>
   </si>
   <si>
@@ -3181,12 +3181,12 @@
     <t>Social and economic rehabilitation in the aftermath of emergencies to facilitate recovery and resilience building and enable populations to restore their livelihoods in the wake of an emergency situation (e.g. trauma counselling and treatment, employment programmes). Includes infrastructure necessary for the delivery of humanitarian aid; restoring pre-existing essential infrastructure and facilities (e.g. water and sanitation, shelter, health care services, education); rehabilitation of basic agricultural inputs and livestock. Excludes longer-term reconstruction ('build back better') which is reportable against relevant sectors.</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
@@ -3196,24 +3196,24 @@
     <t>Building the responsiveness, capability and capacity of international, regional and national humanitarian actors to disasters. Support to the institutional capacities of national and local government, specialised humanitarian bodies, and civil society organisations to anticipate, respond and recover from the impact of potential, imminent and current hazardous events and emergency situations that pose humanitarian threats and could call for a humanitarian response. This includes risk analysis and assessment, mitigation, preparedness, such as stockpiling of emergency items and training and capacity building aimed to increase the speed and effectiveness of lifesaving assistance delivered in the occurrence of crisis.</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
@@ -3223,12 +3223,12 @@
     <t>Costs incurred in donor countries for basic assistance to asylum seekers and refugees from developing countries, up to 12 months, when costs cannot be disaggregated. See section II.6 and Annex 17.</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>93011</t>
   </si>
   <si>
@@ -3310,10 +3310,10 @@
     <t>Contributions to general development of the recipient should be included under programme assistance (51010).</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>
@@ -3741,16 +3741,16 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
@@ -3759,7 +3759,7 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3811,16 +3811,16 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
@@ -3829,7 +3829,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3846,25 +3846,25 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>39</v>
       </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
       <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
         <v>40</v>
       </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
       <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
         <v>41</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3884,7 +3884,7 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
@@ -3893,10 +3893,10 @@
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J7" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -3916,25 +3916,25 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>39</v>
       </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
       <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
         <v>40</v>
       </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
       <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
         <v>41</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3951,25 +3951,25 @@
         <v>14</v>
       </c>
       <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
         <v>38</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>39</v>
       </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
       <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
         <v>40</v>
       </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
       <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s">
         <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3986,25 +3986,25 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
         <v>54</v>
       </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
       <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
         <v>40</v>
       </c>
-      <c r="I10" t="s">
-        <v>19</v>
-      </c>
       <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s">
         <v>41</v>
-      </c>
-      <c r="K10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4021,25 +4021,25 @@
         <v>14</v>
       </c>
       <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" t="s">
         <v>58</v>
       </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>59</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" t="s">
         <v>60</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4056,25 +4056,25 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
         <v>64</v>
       </c>
-      <c r="F12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
       <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
         <v>65</v>
-      </c>
-      <c r="I12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4091,25 +4091,25 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
         <v>69</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>70</v>
       </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
       <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" t="s">
         <v>65</v>
-      </c>
-      <c r="I13" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" t="s">
-        <v>71</v>
-      </c>
-      <c r="K13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4126,25 +4126,25 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" t="s">
         <v>75</v>
       </c>
-      <c r="F14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" t="s">
-        <v>17</v>
-      </c>
       <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" t="s">
         <v>76</v>
-      </c>
-      <c r="I14" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" t="s">
-        <v>71</v>
-      </c>
-      <c r="K14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4161,25 +4161,25 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
         <v>80</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>81</v>
       </c>
-      <c r="G15" t="s">
-        <v>17</v>
-      </c>
       <c r="H15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" t="s">
         <v>82</v>
       </c>
-      <c r="I15" t="s">
-        <v>19</v>
-      </c>
       <c r="J15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" t="s">
         <v>83</v>
-      </c>
-      <c r="K15" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4196,25 +4196,25 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s">
         <v>87</v>
       </c>
-      <c r="F16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" t="s">
-        <v>17</v>
-      </c>
       <c r="H16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" t="s">
         <v>88</v>
-      </c>
-      <c r="I16" t="s">
-        <v>19</v>
-      </c>
-      <c r="J16" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4237,10 +4237,10 @@
         <v>93</v>
       </c>
       <c r="G17" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" t="s">
         <v>59</v>
-      </c>
-      <c r="H17" t="s">
-        <v>94</v>
       </c>
       <c r="I17" t="s">
         <v>95</v>
@@ -4272,10 +4272,10 @@
         <v>93</v>
       </c>
       <c r="G18" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18" t="s">
         <v>59</v>
-      </c>
-      <c r="H18" t="s">
-        <v>94</v>
       </c>
       <c r="I18" t="s">
         <v>95</v>
@@ -4301,16 +4301,16 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F19" t="s">
         <v>93</v>
       </c>
       <c r="G19" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" t="s">
         <v>59</v>
-      </c>
-      <c r="H19" t="s">
-        <v>105</v>
       </c>
       <c r="I19" t="s">
         <v>95</v>
@@ -4319,7 +4319,7 @@
         <v>96</v>
       </c>
       <c r="K19" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4336,16 +4336,16 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s">
         <v>93</v>
       </c>
       <c r="G20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" t="s">
         <v>59</v>
-      </c>
-      <c r="H20" t="s">
-        <v>110</v>
       </c>
       <c r="I20" t="s">
         <v>95</v>
@@ -4354,7 +4354,7 @@
         <v>96</v>
       </c>
       <c r="K20" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4377,10 +4377,10 @@
         <v>93</v>
       </c>
       <c r="G21" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" t="s">
         <v>59</v>
-      </c>
-      <c r="H21" t="s">
-        <v>94</v>
       </c>
       <c r="I21" t="s">
         <v>95</v>
@@ -4406,25 +4406,25 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F22" t="s">
         <v>117</v>
       </c>
       <c r="G22" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" t="s">
         <v>59</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
+        <v>118</v>
+      </c>
+      <c r="J22" t="s">
+        <v>96</v>
+      </c>
+      <c r="K22" t="s">
         <v>60</v>
-      </c>
-      <c r="I22" t="s">
-        <v>95</v>
-      </c>
-      <c r="J22" t="s">
-        <v>118</v>
-      </c>
-      <c r="K22" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4441,25 +4441,25 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="F23" t="s">
         <v>117</v>
       </c>
       <c r="G23" t="s">
+        <v>122</v>
+      </c>
+      <c r="H23" t="s">
         <v>59</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
+        <v>118</v>
+      </c>
+      <c r="J23" t="s">
+        <v>96</v>
+      </c>
+      <c r="K23" t="s">
         <v>123</v>
-      </c>
-      <c r="I23" t="s">
-        <v>95</v>
-      </c>
-      <c r="J23" t="s">
-        <v>118</v>
-      </c>
-      <c r="K23" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4476,25 +4476,25 @@
         <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s">
         <v>117</v>
       </c>
       <c r="G24" t="s">
+        <v>58</v>
+      </c>
+      <c r="H24" t="s">
         <v>59</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
+        <v>118</v>
+      </c>
+      <c r="J24" t="s">
+        <v>96</v>
+      </c>
+      <c r="K24" t="s">
         <v>60</v>
-      </c>
-      <c r="I24" t="s">
-        <v>95</v>
-      </c>
-      <c r="J24" t="s">
-        <v>118</v>
-      </c>
-      <c r="K24" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4511,25 +4511,25 @@
         <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s">
         <v>117</v>
       </c>
       <c r="G25" t="s">
+        <v>58</v>
+      </c>
+      <c r="H25" t="s">
         <v>59</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
+        <v>118</v>
+      </c>
+      <c r="J25" t="s">
+        <v>96</v>
+      </c>
+      <c r="K25" t="s">
         <v>60</v>
-      </c>
-      <c r="I25" t="s">
-        <v>95</v>
-      </c>
-      <c r="J25" t="s">
-        <v>118</v>
-      </c>
-      <c r="K25" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4546,25 +4546,25 @@
         <v>14</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F26" t="s">
         <v>117</v>
       </c>
       <c r="G26" t="s">
+        <v>58</v>
+      </c>
+      <c r="H26" t="s">
         <v>59</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
+        <v>118</v>
+      </c>
+      <c r="J26" t="s">
+        <v>96</v>
+      </c>
+      <c r="K26" t="s">
         <v>60</v>
-      </c>
-      <c r="I26" t="s">
-        <v>95</v>
-      </c>
-      <c r="J26" t="s">
-        <v>118</v>
-      </c>
-      <c r="K26" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4581,25 +4581,25 @@
         <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F27" t="s">
         <v>117</v>
       </c>
       <c r="G27" t="s">
+        <v>58</v>
+      </c>
+      <c r="H27" t="s">
         <v>59</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
+        <v>118</v>
+      </c>
+      <c r="J27" t="s">
+        <v>96</v>
+      </c>
+      <c r="K27" t="s">
         <v>60</v>
-      </c>
-      <c r="I27" t="s">
-        <v>95</v>
-      </c>
-      <c r="J27" t="s">
-        <v>118</v>
-      </c>
-      <c r="K27" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4616,25 +4616,25 @@
         <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F28" t="s">
         <v>117</v>
       </c>
       <c r="G28" t="s">
+        <v>58</v>
+      </c>
+      <c r="H28" t="s">
         <v>59</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
+        <v>118</v>
+      </c>
+      <c r="J28" t="s">
+        <v>96</v>
+      </c>
+      <c r="K28" t="s">
         <v>60</v>
-      </c>
-      <c r="I28" t="s">
-        <v>95</v>
-      </c>
-      <c r="J28" t="s">
-        <v>118</v>
-      </c>
-      <c r="K28" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4651,25 +4651,25 @@
         <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s">
         <v>117</v>
       </c>
       <c r="G29" t="s">
+        <v>58</v>
+      </c>
+      <c r="H29" t="s">
         <v>59</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
+        <v>118</v>
+      </c>
+      <c r="J29" t="s">
+        <v>96</v>
+      </c>
+      <c r="K29" t="s">
         <v>60</v>
-      </c>
-      <c r="I29" t="s">
-        <v>95</v>
-      </c>
-      <c r="J29" t="s">
-        <v>118</v>
-      </c>
-      <c r="K29" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4692,16 +4692,16 @@
         <v>117</v>
       </c>
       <c r="G30" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" t="s">
         <v>59</v>
       </c>
-      <c r="H30" t="s">
-        <v>94</v>
-      </c>
       <c r="I30" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="J30" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="K30" t="s">
         <v>97</v>
@@ -4721,25 +4721,25 @@
         <v>14</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
         <v>148</v>
       </c>
       <c r="G31" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" t="s">
         <v>59</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
+        <v>149</v>
+      </c>
+      <c r="J31" t="s">
+        <v>96</v>
+      </c>
+      <c r="K31" t="s">
         <v>60</v>
-      </c>
-      <c r="I31" t="s">
-        <v>95</v>
-      </c>
-      <c r="J31" t="s">
-        <v>149</v>
-      </c>
-      <c r="K31" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4756,25 +4756,25 @@
         <v>14</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F32" t="s">
         <v>148</v>
       </c>
       <c r="G32" t="s">
+        <v>58</v>
+      </c>
+      <c r="H32" t="s">
         <v>59</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
+        <v>149</v>
+      </c>
+      <c r="J32" t="s">
+        <v>96</v>
+      </c>
+      <c r="K32" t="s">
         <v>60</v>
-      </c>
-      <c r="I32" t="s">
-        <v>95</v>
-      </c>
-      <c r="J32" t="s">
-        <v>149</v>
-      </c>
-      <c r="K32" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4791,25 +4791,25 @@
         <v>14</v>
       </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F33" t="s">
         <v>148</v>
       </c>
       <c r="G33" t="s">
+        <v>58</v>
+      </c>
+      <c r="H33" t="s">
         <v>59</v>
       </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
+        <v>149</v>
+      </c>
+      <c r="J33" t="s">
+        <v>96</v>
+      </c>
+      <c r="K33" t="s">
         <v>60</v>
-      </c>
-      <c r="I33" t="s">
-        <v>95</v>
-      </c>
-      <c r="J33" t="s">
-        <v>149</v>
-      </c>
-      <c r="K33" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4826,25 +4826,25 @@
         <v>14</v>
       </c>
       <c r="E34" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F34" t="s">
         <v>148</v>
       </c>
       <c r="G34" t="s">
+        <v>58</v>
+      </c>
+      <c r="H34" t="s">
         <v>59</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
+        <v>149</v>
+      </c>
+      <c r="J34" t="s">
+        <v>96</v>
+      </c>
+      <c r="K34" t="s">
         <v>60</v>
-      </c>
-      <c r="I34" t="s">
-        <v>95</v>
-      </c>
-      <c r="J34" t="s">
-        <v>149</v>
-      </c>
-      <c r="K34" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4861,25 +4861,25 @@
         <v>14</v>
       </c>
       <c r="E35" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="F35" t="s">
         <v>148</v>
       </c>
       <c r="G35" t="s">
+        <v>58</v>
+      </c>
+      <c r="H35" t="s">
         <v>59</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
+        <v>149</v>
+      </c>
+      <c r="J35" t="s">
+        <v>96</v>
+      </c>
+      <c r="K35" t="s">
         <v>60</v>
-      </c>
-      <c r="I35" t="s">
-        <v>95</v>
-      </c>
-      <c r="J35" t="s">
-        <v>149</v>
-      </c>
-      <c r="K35" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4896,25 +4896,25 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F36" t="s">
         <v>148</v>
       </c>
       <c r="G36" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" t="s">
         <v>59</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
+        <v>149</v>
+      </c>
+      <c r="J36" t="s">
+        <v>96</v>
+      </c>
+      <c r="K36" t="s">
         <v>105</v>
-      </c>
-      <c r="I36" t="s">
-        <v>95</v>
-      </c>
-      <c r="J36" t="s">
-        <v>149</v>
-      </c>
-      <c r="K36" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4931,19 +4931,19 @@
         <v>14</v>
       </c>
       <c r="E37" t="s">
+        <v>168</v>
+      </c>
+      <c r="G37" t="s">
         <v>58</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>59</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
+        <v>169</v>
+      </c>
+      <c r="K37" t="s">
         <v>60</v>
-      </c>
-      <c r="I37" t="s">
-        <v>168</v>
-      </c>
-      <c r="K37" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4960,19 +4960,19 @@
         <v>14</v>
       </c>
       <c r="E38" t="s">
+        <v>168</v>
+      </c>
+      <c r="G38" t="s">
         <v>58</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>59</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" t="s">
+        <v>169</v>
+      </c>
+      <c r="K38" t="s">
         <v>60</v>
-      </c>
-      <c r="I38" t="s">
-        <v>168</v>
-      </c>
-      <c r="K38" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4989,19 +4989,19 @@
         <v>14</v>
       </c>
       <c r="E39" t="s">
+        <v>168</v>
+      </c>
+      <c r="G39" t="s">
         <v>58</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>59</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" t="s">
+        <v>169</v>
+      </c>
+      <c r="K39" t="s">
         <v>60</v>
-      </c>
-      <c r="I39" t="s">
-        <v>168</v>
-      </c>
-      <c r="K39" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5018,19 +5018,19 @@
         <v>14</v>
       </c>
       <c r="E40" t="s">
+        <v>168</v>
+      </c>
+      <c r="G40" t="s">
         <v>58</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>59</v>
       </c>
-      <c r="H40" t="s">
+      <c r="J40" t="s">
+        <v>169</v>
+      </c>
+      <c r="K40" t="s">
         <v>60</v>
-      </c>
-      <c r="I40" t="s">
-        <v>168</v>
-      </c>
-      <c r="K40" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5047,19 +5047,19 @@
         <v>14</v>
       </c>
       <c r="E41" t="s">
-        <v>92</v>
+        <v>168</v>
       </c>
       <c r="G41" t="s">
+        <v>94</v>
+      </c>
+      <c r="H41" t="s">
         <v>59</v>
       </c>
-      <c r="H41" t="s">
-        <v>94</v>
-      </c>
-      <c r="I41" t="s">
-        <v>168</v>
+      <c r="J41" t="s">
+        <v>169</v>
       </c>
       <c r="K41" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5076,19 +5076,19 @@
         <v>14</v>
       </c>
       <c r="E42" t="s">
+        <v>168</v>
+      </c>
+      <c r="G42" t="s">
         <v>104</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>59</v>
       </c>
-      <c r="H42" t="s">
+      <c r="J42" t="s">
+        <v>169</v>
+      </c>
+      <c r="K42" t="s">
         <v>105</v>
-      </c>
-      <c r="I42" t="s">
-        <v>168</v>
-      </c>
-      <c r="K42" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5113,7 +5113,7 @@
       <c r="H43" t="s">
         <v>190</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>191</v>
       </c>
       <c r="K43" t="s">
@@ -5134,19 +5134,19 @@
         <v>14</v>
       </c>
       <c r="E44" t="s">
+        <v>188</v>
+      </c>
+      <c r="G44" t="s">
         <v>196</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>197</v>
       </c>
-      <c r="H44" t="s">
+      <c r="J44" t="s">
+        <v>191</v>
+      </c>
+      <c r="K44" t="s">
         <v>198</v>
-      </c>
-      <c r="I44" t="s">
-        <v>191</v>
-      </c>
-      <c r="K44" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5171,7 +5171,7 @@
       <c r="H45" t="s">
         <v>190</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>191</v>
       </c>
       <c r="K45" t="s">
@@ -5200,7 +5200,7 @@
       <c r="H46" t="s">
         <v>190</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>191</v>
       </c>
       <c r="K46" t="s">
@@ -5221,19 +5221,19 @@
         <v>14</v>
       </c>
       <c r="E47" t="s">
+        <v>188</v>
+      </c>
+      <c r="G47" t="s">
         <v>208</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>197</v>
       </c>
-      <c r="H47" t="s">
+      <c r="J47" t="s">
+        <v>191</v>
+      </c>
+      <c r="K47" t="s">
         <v>209</v>
-      </c>
-      <c r="I47" t="s">
-        <v>191</v>
-      </c>
-      <c r="K47" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5258,7 +5258,7 @@
       <c r="H48" t="s">
         <v>190</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>191</v>
       </c>
       <c r="K48" t="s">
@@ -5287,7 +5287,7 @@
       <c r="H49" t="s">
         <v>190</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>191</v>
       </c>
       <c r="K49" t="s">
@@ -5308,19 +5308,19 @@
         <v>14</v>
       </c>
       <c r="E50" t="s">
+        <v>188</v>
+      </c>
+      <c r="G50" t="s">
         <v>208</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>197</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
+        <v>191</v>
+      </c>
+      <c r="K50" t="s">
         <v>209</v>
-      </c>
-      <c r="I50" t="s">
-        <v>191</v>
-      </c>
-      <c r="K50" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5345,7 +5345,7 @@
       <c r="H51" t="s">
         <v>190</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>191</v>
       </c>
       <c r="K51" t="s">
@@ -5366,19 +5366,19 @@
         <v>14</v>
       </c>
       <c r="E52" t="s">
+        <v>188</v>
+      </c>
+      <c r="G52" t="s">
         <v>225</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>197</v>
       </c>
-      <c r="H52" t="s">
+      <c r="J52" t="s">
+        <v>191</v>
+      </c>
+      <c r="K52" t="s">
         <v>226</v>
-      </c>
-      <c r="I52" t="s">
-        <v>191</v>
-      </c>
-      <c r="K52" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5395,7 +5395,7 @@
         <v>14</v>
       </c>
       <c r="E53" t="s">
-        <v>15</v>
+        <v>188</v>
       </c>
       <c r="G53" t="s">
         <v>17</v>
@@ -5403,11 +5403,11 @@
       <c r="H53" t="s">
         <v>18</v>
       </c>
-      <c r="I53" t="s">
+      <c r="J53" t="s">
         <v>191</v>
       </c>
       <c r="K53" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5459,16 +5459,16 @@
         <v>14</v>
       </c>
       <c r="E55" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F55" t="s">
         <v>234</v>
       </c>
       <c r="G55" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H55" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I55" t="s">
         <v>237</v>
@@ -5477,7 +5477,7 @@
         <v>238</v>
       </c>
       <c r="K55" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -5494,16 +5494,16 @@
         <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="F56" t="s">
         <v>234</v>
       </c>
       <c r="G56" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="H56" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="I56" t="s">
         <v>237</v>
@@ -5512,7 +5512,7 @@
         <v>238</v>
       </c>
       <c r="K56" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -5529,16 +5529,16 @@
         <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F57" t="s">
         <v>234</v>
       </c>
       <c r="G57" t="s">
+        <v>253</v>
+      </c>
+      <c r="H57" t="s">
         <v>254</v>
-      </c>
-      <c r="H57" t="s">
-        <v>255</v>
       </c>
       <c r="I57" t="s">
         <v>237</v>
@@ -5547,7 +5547,7 @@
         <v>238</v>
       </c>
       <c r="K57" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5564,16 +5564,16 @@
         <v>14</v>
       </c>
       <c r="E58" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F58" t="s">
         <v>234</v>
       </c>
       <c r="G58" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H58" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I58" t="s">
         <v>237</v>
@@ -5582,7 +5582,7 @@
         <v>238</v>
       </c>
       <c r="K58" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5599,16 +5599,16 @@
         <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F59" t="s">
         <v>234</v>
       </c>
       <c r="G59" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H59" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I59" t="s">
         <v>237</v>
@@ -5617,7 +5617,7 @@
         <v>238</v>
       </c>
       <c r="K59" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5634,16 +5634,16 @@
         <v>14</v>
       </c>
       <c r="E60" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F60" t="s">
         <v>234</v>
       </c>
       <c r="G60" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H60" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I60" t="s">
         <v>237</v>
@@ -5652,7 +5652,7 @@
         <v>238</v>
       </c>
       <c r="K60" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -5669,16 +5669,16 @@
         <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F61" t="s">
         <v>234</v>
       </c>
       <c r="G61" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H61" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I61" t="s">
         <v>237</v>
@@ -5687,7 +5687,7 @@
         <v>238</v>
       </c>
       <c r="K61" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -5704,16 +5704,16 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F62" t="s">
         <v>234</v>
       </c>
       <c r="G62" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H62" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I62" t="s">
         <v>237</v>
@@ -5722,7 +5722,7 @@
         <v>238</v>
       </c>
       <c r="K62" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -5739,16 +5739,16 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>274</v>
+        <v>233</v>
       </c>
       <c r="F63" t="s">
         <v>234</v>
       </c>
       <c r="G63" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="H63" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I63" t="s">
         <v>237</v>
@@ -5757,7 +5757,7 @@
         <v>238</v>
       </c>
       <c r="K63" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -5774,16 +5774,16 @@
         <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>274</v>
+        <v>233</v>
       </c>
       <c r="F64" t="s">
         <v>234</v>
       </c>
       <c r="G64" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="H64" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I64" t="s">
         <v>237</v>
@@ -5792,7 +5792,7 @@
         <v>238</v>
       </c>
       <c r="K64" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -5809,16 +5809,16 @@
         <v>14</v>
       </c>
       <c r="E65" t="s">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="F65" t="s">
         <v>234</v>
       </c>
       <c r="G65" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="H65" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="I65" t="s">
         <v>237</v>
@@ -5827,7 +5827,7 @@
         <v>238</v>
       </c>
       <c r="K65" t="s">
-        <v>239</v>
+        <v>282</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5879,16 +5879,16 @@
         <v>14</v>
       </c>
       <c r="E67" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F67" t="s">
         <v>234</v>
       </c>
       <c r="G67" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H67" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I67" t="s">
         <v>237</v>
@@ -5897,7 +5897,7 @@
         <v>238</v>
       </c>
       <c r="K67" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5914,13 +5914,13 @@
         <v>14</v>
       </c>
       <c r="E68" t="s">
-        <v>292</v>
+        <v>233</v>
       </c>
       <c r="F68" t="s">
         <v>234</v>
       </c>
       <c r="G68" t="s">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="H68" t="s">
         <v>236</v>
@@ -5949,13 +5949,13 @@
         <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="F69" t="s">
         <v>234</v>
       </c>
       <c r="G69" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="H69" t="s">
         <v>236</v>
@@ -5984,16 +5984,16 @@
         <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="F70" t="s">
         <v>234</v>
       </c>
       <c r="G70" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="H70" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="I70" t="s">
         <v>237</v>
@@ -6002,7 +6002,7 @@
         <v>238</v>
       </c>
       <c r="K70" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -6019,16 +6019,16 @@
         <v>14</v>
       </c>
       <c r="E71" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="F71" t="s">
         <v>234</v>
       </c>
       <c r="G71" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="H71" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="I71" t="s">
         <v>237</v>
@@ -6037,7 +6037,7 @@
         <v>238</v>
       </c>
       <c r="K71" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6089,16 +6089,16 @@
         <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="F73" t="s">
         <v>234</v>
       </c>
       <c r="G73" t="s">
+        <v>309</v>
+      </c>
+      <c r="H73" t="s">
         <v>254</v>
-      </c>
-      <c r="H73" t="s">
-        <v>310</v>
       </c>
       <c r="I73" t="s">
         <v>237</v>
@@ -6107,7 +6107,7 @@
         <v>238</v>
       </c>
       <c r="K73" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6124,16 +6124,16 @@
         <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>314</v>
+        <v>233</v>
       </c>
       <c r="F74" t="s">
         <v>234</v>
       </c>
       <c r="G74" t="s">
+        <v>314</v>
+      </c>
+      <c r="H74" t="s">
         <v>254</v>
-      </c>
-      <c r="H74" t="s">
-        <v>315</v>
       </c>
       <c r="I74" t="s">
         <v>237</v>
@@ -6142,7 +6142,7 @@
         <v>238</v>
       </c>
       <c r="K74" t="s">
-        <v>239</v>
+        <v>315</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6159,16 +6159,16 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>319</v>
+        <v>233</v>
       </c>
       <c r="F75" t="s">
         <v>234</v>
       </c>
       <c r="G75" t="s">
+        <v>319</v>
+      </c>
+      <c r="H75" t="s">
         <v>254</v>
-      </c>
-      <c r="H75" t="s">
-        <v>320</v>
       </c>
       <c r="I75" t="s">
         <v>237</v>
@@ -6177,7 +6177,7 @@
         <v>238</v>
       </c>
       <c r="K75" t="s">
-        <v>239</v>
+        <v>320</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6194,16 +6194,16 @@
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="F76" t="s">
         <v>234</v>
       </c>
       <c r="G76" t="s">
+        <v>309</v>
+      </c>
+      <c r="H76" t="s">
         <v>254</v>
-      </c>
-      <c r="H76" t="s">
-        <v>310</v>
       </c>
       <c r="I76" t="s">
         <v>237</v>
@@ -6212,7 +6212,7 @@
         <v>238</v>
       </c>
       <c r="K76" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -6229,16 +6229,16 @@
         <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="F77" t="s">
         <v>234</v>
       </c>
       <c r="G77" t="s">
+        <v>309</v>
+      </c>
+      <c r="H77" t="s">
         <v>254</v>
-      </c>
-      <c r="H77" t="s">
-        <v>310</v>
       </c>
       <c r="I77" t="s">
         <v>237</v>
@@ -6247,7 +6247,7 @@
         <v>238</v>
       </c>
       <c r="K77" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -6264,16 +6264,16 @@
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>314</v>
+        <v>233</v>
       </c>
       <c r="F78" t="s">
         <v>234</v>
       </c>
       <c r="G78" t="s">
+        <v>314</v>
+      </c>
+      <c r="H78" t="s">
         <v>254</v>
-      </c>
-      <c r="H78" t="s">
-        <v>315</v>
       </c>
       <c r="I78" t="s">
         <v>237</v>
@@ -6282,7 +6282,7 @@
         <v>238</v>
       </c>
       <c r="K78" t="s">
-        <v>239</v>
+        <v>315</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -6296,16 +6296,16 @@
         <v>14</v>
       </c>
       <c r="E79" t="s">
-        <v>332</v>
+        <v>233</v>
       </c>
       <c r="F79" t="s">
         <v>234</v>
       </c>
       <c r="G79" t="s">
+        <v>332</v>
+      </c>
+      <c r="H79" t="s">
         <v>254</v>
-      </c>
-      <c r="H79" t="s">
-        <v>333</v>
       </c>
       <c r="I79" t="s">
         <v>237</v>
@@ -6314,7 +6314,7 @@
         <v>238</v>
       </c>
       <c r="K79" t="s">
-        <v>239</v>
+        <v>333</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -6331,16 +6331,16 @@
         <v>14</v>
       </c>
       <c r="E80" t="s">
-        <v>337</v>
+        <v>233</v>
       </c>
       <c r="F80" t="s">
         <v>234</v>
       </c>
       <c r="G80" t="s">
+        <v>337</v>
+      </c>
+      <c r="H80" t="s">
         <v>338</v>
-      </c>
-      <c r="H80" t="s">
-        <v>339</v>
       </c>
       <c r="I80" t="s">
         <v>237</v>
@@ -6349,7 +6349,7 @@
         <v>238</v>
       </c>
       <c r="K80" t="s">
-        <v>239</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -6366,16 +6366,16 @@
         <v>14</v>
       </c>
       <c r="E81" t="s">
-        <v>337</v>
+        <v>233</v>
       </c>
       <c r="F81" t="s">
         <v>234</v>
       </c>
       <c r="G81" t="s">
+        <v>337</v>
+      </c>
+      <c r="H81" t="s">
         <v>338</v>
-      </c>
-      <c r="H81" t="s">
-        <v>339</v>
       </c>
       <c r="I81" t="s">
         <v>237</v>
@@ -6384,7 +6384,7 @@
         <v>238</v>
       </c>
       <c r="K81" t="s">
-        <v>239</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -6401,16 +6401,16 @@
         <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>337</v>
+        <v>233</v>
       </c>
       <c r="F82" t="s">
         <v>234</v>
       </c>
       <c r="G82" t="s">
+        <v>337</v>
+      </c>
+      <c r="H82" t="s">
         <v>338</v>
-      </c>
-      <c r="H82" t="s">
-        <v>339</v>
       </c>
       <c r="I82" t="s">
         <v>237</v>
@@ -6419,7 +6419,7 @@
         <v>238</v>
       </c>
       <c r="K82" t="s">
-        <v>239</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -6436,13 +6436,13 @@
         <v>14</v>
       </c>
       <c r="E83" t="s">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="F83" t="s">
         <v>234</v>
       </c>
       <c r="G83" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="H83" t="s">
         <v>236</v>
@@ -6471,16 +6471,16 @@
         <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>352</v>
+        <v>233</v>
       </c>
       <c r="F84" t="s">
         <v>234</v>
       </c>
       <c r="G84" t="s">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="H84" t="s">
-        <v>353</v>
+        <v>236</v>
       </c>
       <c r="I84" t="s">
         <v>237</v>
@@ -6489,7 +6489,7 @@
         <v>238</v>
       </c>
       <c r="K84" t="s">
-        <v>239</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -6506,16 +6506,16 @@
         <v>14</v>
       </c>
       <c r="E85" t="s">
-        <v>357</v>
+        <v>233</v>
       </c>
       <c r="F85" t="s">
         <v>234</v>
       </c>
       <c r="G85" t="s">
-        <v>235</v>
+        <v>357</v>
       </c>
       <c r="H85" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I85" t="s">
         <v>237</v>
@@ -6524,7 +6524,7 @@
         <v>238</v>
       </c>
       <c r="K85" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -6541,16 +6541,16 @@
         <v>14</v>
       </c>
       <c r="E86" t="s">
-        <v>361</v>
+        <v>233</v>
       </c>
       <c r="F86" t="s">
         <v>234</v>
       </c>
       <c r="G86" t="s">
+        <v>361</v>
+      </c>
+      <c r="H86" t="s">
         <v>338</v>
-      </c>
-      <c r="H86" t="s">
-        <v>362</v>
       </c>
       <c r="I86" t="s">
         <v>237</v>
@@ -6559,7 +6559,7 @@
         <v>238</v>
       </c>
       <c r="K86" t="s">
-        <v>239</v>
+        <v>362</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -6576,16 +6576,16 @@
         <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>357</v>
+        <v>233</v>
       </c>
       <c r="F87" t="s">
         <v>234</v>
       </c>
       <c r="G87" t="s">
-        <v>235</v>
+        <v>357</v>
       </c>
       <c r="H87" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I87" t="s">
         <v>237</v>
@@ -6594,7 +6594,7 @@
         <v>238</v>
       </c>
       <c r="K87" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -6608,16 +6608,16 @@
         <v>14</v>
       </c>
       <c r="E88" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F88" t="s">
         <v>234</v>
       </c>
       <c r="G88" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H88" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I88" t="s">
         <v>237</v>
@@ -6626,7 +6626,7 @@
         <v>238</v>
       </c>
       <c r="K88" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -6643,16 +6643,16 @@
         <v>14</v>
       </c>
       <c r="E89" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F89" t="s">
         <v>234</v>
       </c>
       <c r="G89" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H89" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I89" t="s">
         <v>237</v>
@@ -6661,7 +6661,7 @@
         <v>238</v>
       </c>
       <c r="K89" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -6678,16 +6678,16 @@
         <v>14</v>
       </c>
       <c r="E90" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F90" t="s">
         <v>234</v>
       </c>
       <c r="G90" t="s">
+        <v>253</v>
+      </c>
+      <c r="H90" t="s">
         <v>254</v>
-      </c>
-      <c r="H90" t="s">
-        <v>255</v>
       </c>
       <c r="I90" t="s">
         <v>237</v>
@@ -6696,7 +6696,7 @@
         <v>238</v>
       </c>
       <c r="K90" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -6713,16 +6713,16 @@
         <v>14</v>
       </c>
       <c r="E91" t="s">
-        <v>377</v>
+        <v>233</v>
       </c>
       <c r="F91" t="s">
         <v>234</v>
       </c>
       <c r="G91" t="s">
+        <v>377</v>
+      </c>
+      <c r="H91" t="s">
         <v>378</v>
-      </c>
-      <c r="H91" t="s">
-        <v>379</v>
       </c>
       <c r="I91" t="s">
         <v>237</v>
@@ -6731,7 +6731,7 @@
         <v>238</v>
       </c>
       <c r="K91" t="s">
-        <v>239</v>
+        <v>379</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -6748,16 +6748,16 @@
         <v>14</v>
       </c>
       <c r="E92" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F92" t="s">
         <v>234</v>
       </c>
       <c r="G92" t="s">
+        <v>253</v>
+      </c>
+      <c r="H92" t="s">
         <v>254</v>
-      </c>
-      <c r="H92" t="s">
-        <v>255</v>
       </c>
       <c r="I92" t="s">
         <v>237</v>
@@ -6766,7 +6766,7 @@
         <v>238</v>
       </c>
       <c r="K92" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -6783,16 +6783,16 @@
         <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="F93" t="s">
         <v>234</v>
       </c>
       <c r="G93" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="H93" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="I93" t="s">
         <v>237</v>
@@ -6801,7 +6801,7 @@
         <v>238</v>
       </c>
       <c r="K93" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -6818,16 +6818,16 @@
         <v>14</v>
       </c>
       <c r="E94" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F94" t="s">
         <v>234</v>
       </c>
       <c r="G94" t="s">
+        <v>253</v>
+      </c>
+      <c r="H94" t="s">
         <v>254</v>
-      </c>
-      <c r="H94" t="s">
-        <v>255</v>
       </c>
       <c r="I94" t="s">
         <v>237</v>
@@ -6836,7 +6836,7 @@
         <v>238</v>
       </c>
       <c r="K94" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -6853,16 +6853,16 @@
         <v>14</v>
       </c>
       <c r="E95" t="s">
-        <v>392</v>
+        <v>233</v>
       </c>
       <c r="F95" t="s">
         <v>234</v>
       </c>
       <c r="G95" t="s">
-        <v>235</v>
+        <v>392</v>
       </c>
       <c r="H95" t="s">
-        <v>393</v>
+        <v>236</v>
       </c>
       <c r="I95" t="s">
         <v>237</v>
@@ -6871,7 +6871,7 @@
         <v>238</v>
       </c>
       <c r="K95" t="s">
-        <v>239</v>
+        <v>393</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -6888,25 +6888,25 @@
         <v>14</v>
       </c>
       <c r="E96" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F96" t="s">
         <v>397</v>
       </c>
       <c r="G96" t="s">
+        <v>253</v>
+      </c>
+      <c r="H96" t="s">
         <v>254</v>
       </c>
-      <c r="H96" t="s">
+      <c r="I96" t="s">
+        <v>398</v>
+      </c>
+      <c r="J96" t="s">
+        <v>238</v>
+      </c>
+      <c r="K96" t="s">
         <v>255</v>
-      </c>
-      <c r="I96" t="s">
-        <v>237</v>
-      </c>
-      <c r="J96" t="s">
-        <v>398</v>
-      </c>
-      <c r="K96" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -6923,25 +6923,25 @@
         <v>14</v>
       </c>
       <c r="E97" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F97" t="s">
         <v>397</v>
       </c>
       <c r="G97" t="s">
+        <v>253</v>
+      </c>
+      <c r="H97" t="s">
         <v>254</v>
       </c>
-      <c r="H97" t="s">
+      <c r="I97" t="s">
+        <v>398</v>
+      </c>
+      <c r="J97" t="s">
+        <v>238</v>
+      </c>
+      <c r="K97" t="s">
         <v>255</v>
-      </c>
-      <c r="I97" t="s">
-        <v>237</v>
-      </c>
-      <c r="J97" t="s">
-        <v>398</v>
-      </c>
-      <c r="K97" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -6958,25 +6958,25 @@
         <v>14</v>
       </c>
       <c r="E98" t="s">
-        <v>405</v>
+        <v>233</v>
       </c>
       <c r="F98" t="s">
         <v>397</v>
       </c>
       <c r="G98" t="s">
+        <v>405</v>
+      </c>
+      <c r="H98" t="s">
         <v>406</v>
       </c>
-      <c r="H98" t="s">
+      <c r="I98" t="s">
+        <v>398</v>
+      </c>
+      <c r="J98" t="s">
+        <v>238</v>
+      </c>
+      <c r="K98" t="s">
         <v>407</v>
-      </c>
-      <c r="I98" t="s">
-        <v>237</v>
-      </c>
-      <c r="J98" t="s">
-        <v>398</v>
-      </c>
-      <c r="K98" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -6993,25 +6993,25 @@
         <v>14</v>
       </c>
       <c r="E99" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F99" t="s">
         <v>397</v>
       </c>
       <c r="G99" t="s">
+        <v>253</v>
+      </c>
+      <c r="H99" t="s">
         <v>254</v>
       </c>
-      <c r="H99" t="s">
+      <c r="I99" t="s">
+        <v>398</v>
+      </c>
+      <c r="J99" t="s">
+        <v>238</v>
+      </c>
+      <c r="K99" t="s">
         <v>255</v>
-      </c>
-      <c r="I99" t="s">
-        <v>237</v>
-      </c>
-      <c r="J99" t="s">
-        <v>398</v>
-      </c>
-      <c r="K99" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -7028,25 +7028,25 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
-        <v>319</v>
+        <v>233</v>
       </c>
       <c r="F100" t="s">
         <v>397</v>
       </c>
       <c r="G100" t="s">
+        <v>319</v>
+      </c>
+      <c r="H100" t="s">
         <v>254</v>
       </c>
-      <c r="H100" t="s">
+      <c r="I100" t="s">
+        <v>398</v>
+      </c>
+      <c r="J100" t="s">
+        <v>238</v>
+      </c>
+      <c r="K100" t="s">
         <v>320</v>
-      </c>
-      <c r="I100" t="s">
-        <v>237</v>
-      </c>
-      <c r="J100" t="s">
-        <v>398</v>
-      </c>
-      <c r="K100" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -7063,25 +7063,25 @@
         <v>14</v>
       </c>
       <c r="E101" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F101" t="s">
         <v>397</v>
       </c>
       <c r="G101" t="s">
+        <v>253</v>
+      </c>
+      <c r="H101" t="s">
         <v>254</v>
       </c>
-      <c r="H101" t="s">
+      <c r="I101" t="s">
+        <v>398</v>
+      </c>
+      <c r="J101" t="s">
+        <v>238</v>
+      </c>
+      <c r="K101" t="s">
         <v>255</v>
-      </c>
-      <c r="I101" t="s">
-        <v>237</v>
-      </c>
-      <c r="J101" t="s">
-        <v>398</v>
-      </c>
-      <c r="K101" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -7101,12 +7101,12 @@
         <v>420</v>
       </c>
       <c r="G102" t="s">
+        <v>421</v>
+      </c>
+      <c r="H102" t="s">
         <v>378</v>
       </c>
-      <c r="H102" t="s">
-        <v>421</v>
-      </c>
-      <c r="I102" t="s">
+      <c r="J102" t="s">
         <v>422</v>
       </c>
       <c r="K102" t="s">
@@ -7130,12 +7130,12 @@
         <v>420</v>
       </c>
       <c r="G103" t="s">
+        <v>421</v>
+      </c>
+      <c r="H103" t="s">
         <v>378</v>
       </c>
-      <c r="H103" t="s">
-        <v>421</v>
-      </c>
-      <c r="I103" t="s">
+      <c r="J103" t="s">
         <v>422</v>
       </c>
       <c r="K103" t="s">
@@ -7159,12 +7159,12 @@
         <v>420</v>
       </c>
       <c r="G104" t="s">
+        <v>421</v>
+      </c>
+      <c r="H104" t="s">
         <v>378</v>
       </c>
-      <c r="H104" t="s">
-        <v>421</v>
-      </c>
-      <c r="I104" t="s">
+      <c r="J104" t="s">
         <v>422</v>
       </c>
       <c r="K104" t="s">
@@ -7185,19 +7185,19 @@
         <v>14</v>
       </c>
       <c r="E105" t="s">
+        <v>420</v>
+      </c>
+      <c r="G105" t="s">
         <v>433</v>
       </c>
-      <c r="G105" t="s">
+      <c r="H105" t="s">
         <v>378</v>
       </c>
-      <c r="H105" t="s">
+      <c r="J105" t="s">
+        <v>422</v>
+      </c>
+      <c r="K105" t="s">
         <v>434</v>
-      </c>
-      <c r="I105" t="s">
-        <v>422</v>
-      </c>
-      <c r="K105" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7217,12 +7217,12 @@
         <v>420</v>
       </c>
       <c r="G106" t="s">
+        <v>421</v>
+      </c>
+      <c r="H106" t="s">
         <v>378</v>
       </c>
-      <c r="H106" t="s">
-        <v>421</v>
-      </c>
-      <c r="I106" t="s">
+      <c r="J106" t="s">
         <v>422</v>
       </c>
       <c r="K106" t="s">
@@ -7243,19 +7243,19 @@
         <v>14</v>
       </c>
       <c r="E107" t="s">
+        <v>420</v>
+      </c>
+      <c r="G107" t="s">
         <v>377</v>
       </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>378</v>
       </c>
-      <c r="H107" t="s">
+      <c r="J107" t="s">
+        <v>422</v>
+      </c>
+      <c r="K107" t="s">
         <v>379</v>
-      </c>
-      <c r="I107" t="s">
-        <v>422</v>
-      </c>
-      <c r="K107" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -7272,19 +7272,19 @@
         <v>14</v>
       </c>
       <c r="E108" t="s">
+        <v>420</v>
+      </c>
+      <c r="G108" t="s">
         <v>444</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" t="s">
         <v>378</v>
       </c>
-      <c r="H108" t="s">
+      <c r="J108" t="s">
+        <v>422</v>
+      </c>
+      <c r="K108" t="s">
         <v>445</v>
-      </c>
-      <c r="I108" t="s">
-        <v>422</v>
-      </c>
-      <c r="K108" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7301,19 +7301,19 @@
         <v>14</v>
       </c>
       <c r="E109" t="s">
+        <v>420</v>
+      </c>
+      <c r="G109" t="s">
         <v>449</v>
       </c>
-      <c r="G109" t="s">
-        <v>189</v>
-      </c>
       <c r="H109" t="s">
+        <v>190</v>
+      </c>
+      <c r="J109" t="s">
+        <v>422</v>
+      </c>
+      <c r="K109" t="s">
         <v>450</v>
-      </c>
-      <c r="I109" t="s">
-        <v>422</v>
-      </c>
-      <c r="K109" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -7330,19 +7330,19 @@
         <v>14</v>
       </c>
       <c r="E110" t="s">
+        <v>420</v>
+      </c>
+      <c r="G110" t="s">
         <v>454</v>
       </c>
-      <c r="G110" t="s">
-        <v>189</v>
-      </c>
       <c r="H110" t="s">
+        <v>190</v>
+      </c>
+      <c r="J110" t="s">
+        <v>422</v>
+      </c>
+      <c r="K110" t="s">
         <v>455</v>
-      </c>
-      <c r="I110" t="s">
-        <v>422</v>
-      </c>
-      <c r="K110" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -7362,12 +7362,12 @@
         <v>420</v>
       </c>
       <c r="G111" t="s">
+        <v>421</v>
+      </c>
+      <c r="H111" t="s">
         <v>378</v>
       </c>
-      <c r="H111" t="s">
-        <v>421</v>
-      </c>
-      <c r="I111" t="s">
+      <c r="J111" t="s">
         <v>422</v>
       </c>
       <c r="K111" t="s">
@@ -7388,19 +7388,19 @@
         <v>14</v>
       </c>
       <c r="E112" t="s">
+        <v>420</v>
+      </c>
+      <c r="G112" t="s">
         <v>462</v>
       </c>
-      <c r="G112" t="s">
+      <c r="H112" t="s">
         <v>463</v>
       </c>
-      <c r="H112" t="s">
+      <c r="J112" t="s">
+        <v>422</v>
+      </c>
+      <c r="K112" t="s">
         <v>464</v>
-      </c>
-      <c r="I112" t="s">
-        <v>422</v>
-      </c>
-      <c r="K112" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -7417,19 +7417,19 @@
         <v>14</v>
       </c>
       <c r="E113" t="s">
+        <v>420</v>
+      </c>
+      <c r="G113" t="s">
         <v>296</v>
-      </c>
-      <c r="G113" t="s">
-        <v>235</v>
       </c>
       <c r="H113" t="s">
         <v>236</v>
       </c>
-      <c r="I113" t="s">
+      <c r="J113" t="s">
         <v>422</v>
       </c>
       <c r="K113" t="s">
-        <v>423</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -7446,19 +7446,19 @@
         <v>14</v>
       </c>
       <c r="E114" t="s">
+        <v>420</v>
+      </c>
+      <c r="G114" t="s">
         <v>314</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>254</v>
       </c>
-      <c r="H114" t="s">
+      <c r="J114" t="s">
+        <v>422</v>
+      </c>
+      <c r="K114" t="s">
         <v>315</v>
-      </c>
-      <c r="I114" t="s">
-        <v>422</v>
-      </c>
-      <c r="K114" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -7475,19 +7475,19 @@
         <v>14</v>
       </c>
       <c r="E115" t="s">
+        <v>420</v>
+      </c>
+      <c r="G115" t="s">
         <v>377</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115" t="s">
         <v>378</v>
       </c>
-      <c r="H115" t="s">
+      <c r="J115" t="s">
+        <v>422</v>
+      </c>
+      <c r="K115" t="s">
         <v>379</v>
-      </c>
-      <c r="I115" t="s">
-        <v>422</v>
-      </c>
-      <c r="K115" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -7501,19 +7501,19 @@
         <v>14</v>
       </c>
       <c r="E116" t="s">
+        <v>420</v>
+      </c>
+      <c r="G116" t="s">
         <v>476</v>
       </c>
-      <c r="G116" t="s">
+      <c r="H116" t="s">
         <v>463</v>
       </c>
-      <c r="H116" t="s">
+      <c r="J116" t="s">
+        <v>422</v>
+      </c>
+      <c r="K116" t="s">
         <v>477</v>
-      </c>
-      <c r="I116" t="s">
-        <v>422</v>
-      </c>
-      <c r="K116" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -7527,19 +7527,19 @@
         <v>14</v>
       </c>
       <c r="E117" t="s">
+        <v>420</v>
+      </c>
+      <c r="G117" t="s">
         <v>462</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" t="s">
         <v>463</v>
       </c>
-      <c r="H117" t="s">
+      <c r="J117" t="s">
+        <v>422</v>
+      </c>
+      <c r="K117" t="s">
         <v>464</v>
-      </c>
-      <c r="I117" t="s">
-        <v>422</v>
-      </c>
-      <c r="K117" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -7556,19 +7556,19 @@
         <v>14</v>
       </c>
       <c r="E118" t="s">
+        <v>420</v>
+      </c>
+      <c r="G118" t="s">
         <v>483</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" t="s">
         <v>338</v>
       </c>
-      <c r="H118" t="s">
+      <c r="J118" t="s">
+        <v>422</v>
+      </c>
+      <c r="K118" t="s">
         <v>339</v>
-      </c>
-      <c r="I118" t="s">
-        <v>422</v>
-      </c>
-      <c r="K118" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -7585,19 +7585,19 @@
         <v>14</v>
       </c>
       <c r="E119" t="s">
+        <v>420</v>
+      </c>
+      <c r="G119" t="s">
         <v>377</v>
       </c>
-      <c r="G119" t="s">
+      <c r="H119" t="s">
         <v>378</v>
       </c>
-      <c r="H119" t="s">
+      <c r="J119" t="s">
+        <v>422</v>
+      </c>
+      <c r="K119" t="s">
         <v>379</v>
-      </c>
-      <c r="I119" t="s">
-        <v>422</v>
-      </c>
-      <c r="K119" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -7614,19 +7614,19 @@
         <v>14</v>
       </c>
       <c r="E120" t="s">
+        <v>490</v>
+      </c>
+      <c r="G120" t="s">
         <v>352</v>
       </c>
-      <c r="G120" t="s">
-        <v>235</v>
-      </c>
       <c r="H120" t="s">
+        <v>236</v>
+      </c>
+      <c r="J120" t="s">
+        <v>491</v>
+      </c>
+      <c r="K120" t="s">
         <v>353</v>
-      </c>
-      <c r="I120" t="s">
-        <v>490</v>
-      </c>
-      <c r="K120" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -7643,19 +7643,19 @@
         <v>14</v>
       </c>
       <c r="E121" t="s">
+        <v>490</v>
+      </c>
+      <c r="G121" t="s">
         <v>296</v>
-      </c>
-      <c r="G121" t="s">
-        <v>235</v>
       </c>
       <c r="H121" t="s">
         <v>236</v>
       </c>
-      <c r="I121" t="s">
-        <v>490</v>
+      <c r="J121" t="s">
+        <v>491</v>
       </c>
       <c r="K121" t="s">
-        <v>491</v>
+        <v>239</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -7672,19 +7672,19 @@
         <v>14</v>
       </c>
       <c r="E122" t="s">
+        <v>490</v>
+      </c>
+      <c r="G122" t="s">
         <v>352</v>
       </c>
-      <c r="G122" t="s">
-        <v>235</v>
-      </c>
       <c r="H122" t="s">
+        <v>236</v>
+      </c>
+      <c r="J122" t="s">
+        <v>491</v>
+      </c>
+      <c r="K122" t="s">
         <v>353</v>
-      </c>
-      <c r="I122" t="s">
-        <v>490</v>
-      </c>
-      <c r="K122" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -7701,19 +7701,19 @@
         <v>14</v>
       </c>
       <c r="E123" t="s">
+        <v>490</v>
+      </c>
+      <c r="G123" t="s">
         <v>352</v>
       </c>
-      <c r="G123" t="s">
-        <v>235</v>
-      </c>
       <c r="H123" t="s">
+        <v>236</v>
+      </c>
+      <c r="J123" t="s">
+        <v>491</v>
+      </c>
+      <c r="K123" t="s">
         <v>353</v>
-      </c>
-      <c r="I123" t="s">
-        <v>490</v>
-      </c>
-      <c r="K123" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -7730,19 +7730,19 @@
         <v>14</v>
       </c>
       <c r="E124" t="s">
+        <v>490</v>
+      </c>
+      <c r="G124" t="s">
         <v>504</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>338</v>
       </c>
-      <c r="H124" t="s">
+      <c r="J124" t="s">
+        <v>491</v>
+      </c>
+      <c r="K124" t="s">
         <v>505</v>
-      </c>
-      <c r="I124" t="s">
-        <v>490</v>
-      </c>
-      <c r="K124" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -7759,19 +7759,19 @@
         <v>14</v>
       </c>
       <c r="E125" t="s">
+        <v>490</v>
+      </c>
+      <c r="G125" t="s">
         <v>504</v>
       </c>
-      <c r="G125" t="s">
+      <c r="H125" t="s">
         <v>338</v>
       </c>
-      <c r="H125" t="s">
+      <c r="J125" t="s">
+        <v>491</v>
+      </c>
+      <c r="K125" t="s">
         <v>505</v>
-      </c>
-      <c r="I125" t="s">
-        <v>490</v>
-      </c>
-      <c r="K125" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -7788,19 +7788,19 @@
         <v>14</v>
       </c>
       <c r="E126" t="s">
+        <v>490</v>
+      </c>
+      <c r="G126" t="s">
         <v>504</v>
       </c>
-      <c r="G126" t="s">
+      <c r="H126" t="s">
         <v>338</v>
       </c>
-      <c r="H126" t="s">
+      <c r="J126" t="s">
+        <v>491</v>
+      </c>
+      <c r="K126" t="s">
         <v>505</v>
-      </c>
-      <c r="I126" t="s">
-        <v>490</v>
-      </c>
-      <c r="K126" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -7817,19 +7817,19 @@
         <v>14</v>
       </c>
       <c r="E127" t="s">
+        <v>490</v>
+      </c>
+      <c r="G127" t="s">
         <v>504</v>
       </c>
-      <c r="G127" t="s">
+      <c r="H127" t="s">
         <v>338</v>
       </c>
-      <c r="H127" t="s">
+      <c r="J127" t="s">
+        <v>491</v>
+      </c>
+      <c r="K127" t="s">
         <v>505</v>
-      </c>
-      <c r="I127" t="s">
-        <v>490</v>
-      </c>
-      <c r="K127" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -7846,19 +7846,19 @@
         <v>14</v>
       </c>
       <c r="E128" t="s">
+        <v>490</v>
+      </c>
+      <c r="G128" t="s">
         <v>504</v>
       </c>
-      <c r="G128" t="s">
+      <c r="H128" t="s">
         <v>338</v>
       </c>
-      <c r="H128" t="s">
+      <c r="J128" t="s">
+        <v>491</v>
+      </c>
+      <c r="K128" t="s">
         <v>505</v>
-      </c>
-      <c r="I128" t="s">
-        <v>490</v>
-      </c>
-      <c r="K128" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -7875,19 +7875,19 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
+        <v>490</v>
+      </c>
+      <c r="G129" t="s">
         <v>521</v>
       </c>
-      <c r="G129" t="s">
+      <c r="H129" t="s">
         <v>338</v>
       </c>
-      <c r="H129" t="s">
+      <c r="J129" t="s">
+        <v>491</v>
+      </c>
+      <c r="K129" t="s">
         <v>505</v>
-      </c>
-      <c r="I129" t="s">
-        <v>490</v>
-      </c>
-      <c r="K129" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7904,19 +7904,19 @@
         <v>14</v>
       </c>
       <c r="E130" t="s">
+        <v>490</v>
+      </c>
+      <c r="G130" t="s">
         <v>525</v>
       </c>
-      <c r="G130" t="s">
+      <c r="H130" t="s">
         <v>338</v>
       </c>
-      <c r="H130" t="s">
+      <c r="J130" t="s">
+        <v>491</v>
+      </c>
+      <c r="K130" t="s">
         <v>505</v>
-      </c>
-      <c r="I130" t="s">
-        <v>490</v>
-      </c>
-      <c r="K130" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7933,19 +7933,19 @@
         <v>14</v>
       </c>
       <c r="E131" t="s">
+        <v>490</v>
+      </c>
+      <c r="G131" t="s">
         <v>529</v>
       </c>
-      <c r="G131" t="s">
+      <c r="H131" t="s">
         <v>338</v>
       </c>
-      <c r="H131" t="s">
+      <c r="J131" t="s">
+        <v>491</v>
+      </c>
+      <c r="K131" t="s">
         <v>505</v>
-      </c>
-      <c r="I131" t="s">
-        <v>490</v>
-      </c>
-      <c r="K131" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7962,19 +7962,19 @@
         <v>14</v>
       </c>
       <c r="E132" t="s">
+        <v>490</v>
+      </c>
+      <c r="G132" t="s">
         <v>533</v>
       </c>
-      <c r="G132" t="s">
+      <c r="H132" t="s">
         <v>338</v>
       </c>
-      <c r="H132" t="s">
+      <c r="J132" t="s">
+        <v>491</v>
+      </c>
+      <c r="K132" t="s">
         <v>534</v>
-      </c>
-      <c r="I132" t="s">
-        <v>490</v>
-      </c>
-      <c r="K132" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -7988,19 +7988,19 @@
         <v>14</v>
       </c>
       <c r="E133" t="s">
+        <v>490</v>
+      </c>
+      <c r="G133" t="s">
         <v>392</v>
       </c>
-      <c r="G133" t="s">
-        <v>235</v>
-      </c>
       <c r="H133" t="s">
+        <v>236</v>
+      </c>
+      <c r="J133" t="s">
+        <v>491</v>
+      </c>
+      <c r="K133" t="s">
         <v>393</v>
-      </c>
-      <c r="I133" t="s">
-        <v>490</v>
-      </c>
-      <c r="K133" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -8017,19 +8017,19 @@
         <v>14</v>
       </c>
       <c r="E134" t="s">
+        <v>540</v>
+      </c>
+      <c r="G134" t="s">
         <v>361</v>
       </c>
-      <c r="G134" t="s">
+      <c r="H134" t="s">
         <v>338</v>
       </c>
-      <c r="H134" t="s">
+      <c r="J134" t="s">
+        <v>541</v>
+      </c>
+      <c r="K134" t="s">
         <v>362</v>
-      </c>
-      <c r="I134" t="s">
-        <v>540</v>
-      </c>
-      <c r="K134" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -8043,19 +8043,19 @@
         <v>14</v>
       </c>
       <c r="E135" t="s">
+        <v>540</v>
+      </c>
+      <c r="G135" t="s">
         <v>361</v>
       </c>
-      <c r="G135" t="s">
+      <c r="H135" t="s">
         <v>338</v>
       </c>
-      <c r="H135" t="s">
+      <c r="J135" t="s">
+        <v>541</v>
+      </c>
+      <c r="K135" t="s">
         <v>362</v>
-      </c>
-      <c r="I135" t="s">
-        <v>540</v>
-      </c>
-      <c r="K135" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -8072,19 +8072,19 @@
         <v>14</v>
       </c>
       <c r="E136" t="s">
+        <v>540</v>
+      </c>
+      <c r="G136" t="s">
         <v>361</v>
       </c>
-      <c r="G136" t="s">
+      <c r="H136" t="s">
         <v>338</v>
       </c>
-      <c r="H136" t="s">
+      <c r="J136" t="s">
+        <v>541</v>
+      </c>
+      <c r="K136" t="s">
         <v>362</v>
-      </c>
-      <c r="I136" t="s">
-        <v>540</v>
-      </c>
-      <c r="K136" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -8101,19 +8101,19 @@
         <v>14</v>
       </c>
       <c r="E137" t="s">
+        <v>540</v>
+      </c>
+      <c r="G137" t="s">
         <v>361</v>
       </c>
-      <c r="G137" t="s">
+      <c r="H137" t="s">
         <v>338</v>
       </c>
-      <c r="H137" t="s">
+      <c r="J137" t="s">
+        <v>541</v>
+      </c>
+      <c r="K137" t="s">
         <v>362</v>
-      </c>
-      <c r="I137" t="s">
-        <v>540</v>
-      </c>
-      <c r="K137" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -8130,19 +8130,19 @@
         <v>14</v>
       </c>
       <c r="E138" t="s">
+        <v>540</v>
+      </c>
+      <c r="G138" t="s">
         <v>361</v>
       </c>
-      <c r="G138" t="s">
+      <c r="H138" t="s">
         <v>338</v>
       </c>
-      <c r="H138" t="s">
+      <c r="J138" t="s">
+        <v>541</v>
+      </c>
+      <c r="K138" t="s">
         <v>362</v>
-      </c>
-      <c r="I138" t="s">
-        <v>540</v>
-      </c>
-      <c r="K138" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -8159,19 +8159,19 @@
         <v>14</v>
       </c>
       <c r="E139" t="s">
+        <v>540</v>
+      </c>
+      <c r="G139" t="s">
         <v>556</v>
       </c>
-      <c r="G139" t="s">
+      <c r="H139" t="s">
         <v>463</v>
       </c>
-      <c r="H139" t="s">
+      <c r="J139" t="s">
+        <v>541</v>
+      </c>
+      <c r="K139" t="s">
         <v>557</v>
-      </c>
-      <c r="I139" t="s">
-        <v>540</v>
-      </c>
-      <c r="K139" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -8188,19 +8188,19 @@
         <v>14</v>
       </c>
       <c r="E140" t="s">
+        <v>540</v>
+      </c>
+      <c r="G140" t="s">
         <v>361</v>
       </c>
-      <c r="G140" t="s">
+      <c r="H140" t="s">
         <v>338</v>
       </c>
-      <c r="H140" t="s">
+      <c r="J140" t="s">
+        <v>541</v>
+      </c>
+      <c r="K140" t="s">
         <v>362</v>
-      </c>
-      <c r="I140" t="s">
-        <v>540</v>
-      </c>
-      <c r="K140" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -8223,10 +8223,10 @@
         <v>565</v>
       </c>
       <c r="G141" t="s">
+        <v>566</v>
+      </c>
+      <c r="H141" t="s">
         <v>338</v>
-      </c>
-      <c r="H141" t="s">
-        <v>566</v>
       </c>
       <c r="I141" t="s">
         <v>567</v>
@@ -8255,10 +8255,10 @@
         <v>565</v>
       </c>
       <c r="G142" t="s">
+        <v>566</v>
+      </c>
+      <c r="H142" t="s">
         <v>338</v>
-      </c>
-      <c r="H142" t="s">
-        <v>566</v>
       </c>
       <c r="I142" t="s">
         <v>567</v>
@@ -8284,16 +8284,16 @@
         <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="F143" t="s">
         <v>565</v>
       </c>
       <c r="G143" t="s">
+        <v>575</v>
+      </c>
+      <c r="H143" t="s">
         <v>338</v>
-      </c>
-      <c r="H143" t="s">
-        <v>576</v>
       </c>
       <c r="I143" t="s">
         <v>567</v>
@@ -8302,7 +8302,7 @@
         <v>568</v>
       </c>
       <c r="K143" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -8319,16 +8319,16 @@
         <v>14</v>
       </c>
       <c r="E144" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="F144" t="s">
         <v>565</v>
       </c>
       <c r="G144" t="s">
+        <v>575</v>
+      </c>
+      <c r="H144" t="s">
         <v>338</v>
-      </c>
-      <c r="H144" t="s">
-        <v>576</v>
       </c>
       <c r="I144" t="s">
         <v>567</v>
@@ -8337,7 +8337,7 @@
         <v>568</v>
       </c>
       <c r="K144" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -8354,16 +8354,16 @@
         <v>14</v>
       </c>
       <c r="E145" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="F145" t="s">
         <v>565</v>
       </c>
       <c r="G145" t="s">
+        <v>575</v>
+      </c>
+      <c r="H145" t="s">
         <v>338</v>
-      </c>
-      <c r="H145" t="s">
-        <v>576</v>
       </c>
       <c r="I145" t="s">
         <v>567</v>
@@ -8372,7 +8372,7 @@
         <v>568</v>
       </c>
       <c r="K145" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -8395,10 +8395,10 @@
         <v>565</v>
       </c>
       <c r="G146" t="s">
+        <v>566</v>
+      </c>
+      <c r="H146" t="s">
         <v>338</v>
-      </c>
-      <c r="H146" t="s">
-        <v>566</v>
       </c>
       <c r="I146" t="s">
         <v>567</v>
@@ -8430,16 +8430,16 @@
         <v>589</v>
       </c>
       <c r="G147" t="s">
+        <v>566</v>
+      </c>
+      <c r="H147" t="s">
         <v>338</v>
       </c>
-      <c r="H147" t="s">
-        <v>566</v>
-      </c>
       <c r="I147" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="J147" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K147" t="s">
         <v>569</v>
@@ -8465,16 +8465,16 @@
         <v>589</v>
       </c>
       <c r="G148" t="s">
+        <v>566</v>
+      </c>
+      <c r="H148" t="s">
         <v>338</v>
       </c>
-      <c r="H148" t="s">
-        <v>566</v>
-      </c>
       <c r="I148" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="J148" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K148" t="s">
         <v>569</v>
@@ -8500,16 +8500,16 @@
         <v>589</v>
       </c>
       <c r="G149" t="s">
+        <v>566</v>
+      </c>
+      <c r="H149" t="s">
         <v>338</v>
       </c>
-      <c r="H149" t="s">
-        <v>566</v>
-      </c>
       <c r="I149" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="J149" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K149" t="s">
         <v>569</v>
@@ -8535,16 +8535,16 @@
         <v>589</v>
       </c>
       <c r="G150" t="s">
+        <v>566</v>
+      </c>
+      <c r="H150" t="s">
         <v>338</v>
       </c>
-      <c r="H150" t="s">
-        <v>566</v>
-      </c>
       <c r="I150" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="J150" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K150" t="s">
         <v>569</v>
@@ -8570,16 +8570,16 @@
         <v>589</v>
       </c>
       <c r="G151" t="s">
+        <v>566</v>
+      </c>
+      <c r="H151" t="s">
         <v>338</v>
       </c>
-      <c r="H151" t="s">
-        <v>566</v>
-      </c>
       <c r="I151" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="J151" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K151" t="s">
         <v>569</v>
@@ -8605,16 +8605,16 @@
         <v>589</v>
       </c>
       <c r="G152" t="s">
+        <v>566</v>
+      </c>
+      <c r="H152" t="s">
         <v>338</v>
       </c>
-      <c r="H152" t="s">
-        <v>566</v>
-      </c>
       <c r="I152" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="J152" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K152" t="s">
         <v>569</v>
@@ -8640,16 +8640,16 @@
         <v>589</v>
       </c>
       <c r="G153" t="s">
+        <v>566</v>
+      </c>
+      <c r="H153" t="s">
         <v>338</v>
       </c>
-      <c r="H153" t="s">
-        <v>566</v>
-      </c>
       <c r="I153" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="J153" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K153" t="s">
         <v>569</v>
@@ -8675,16 +8675,16 @@
         <v>589</v>
       </c>
       <c r="G154" t="s">
+        <v>566</v>
+      </c>
+      <c r="H154" t="s">
         <v>338</v>
       </c>
-      <c r="H154" t="s">
-        <v>566</v>
-      </c>
       <c r="I154" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="J154" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K154" t="s">
         <v>569</v>
@@ -8710,16 +8710,16 @@
         <v>589</v>
       </c>
       <c r="G155" t="s">
+        <v>566</v>
+      </c>
+      <c r="H155" t="s">
         <v>338</v>
       </c>
-      <c r="H155" t="s">
-        <v>566</v>
-      </c>
       <c r="I155" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="J155" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="K155" t="s">
         <v>569</v>
@@ -8745,16 +8745,16 @@
         <v>618</v>
       </c>
       <c r="G156" t="s">
+        <v>566</v>
+      </c>
+      <c r="H156" t="s">
         <v>338</v>
       </c>
-      <c r="H156" t="s">
-        <v>566</v>
-      </c>
       <c r="I156" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="J156" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="K156" t="s">
         <v>569</v>
@@ -8774,22 +8774,22 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>623</v>
+        <v>564</v>
       </c>
       <c r="F157" t="s">
         <v>618</v>
       </c>
       <c r="G157" t="s">
+        <v>623</v>
+      </c>
+      <c r="H157" t="s">
         <v>338</v>
       </c>
-      <c r="H157" t="s">
-        <v>566</v>
-      </c>
       <c r="I157" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="J157" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="K157" t="s">
         <v>569</v>
@@ -8815,16 +8815,16 @@
         <v>618</v>
       </c>
       <c r="G158" t="s">
+        <v>566</v>
+      </c>
+      <c r="H158" t="s">
         <v>338</v>
       </c>
-      <c r="H158" t="s">
-        <v>566</v>
-      </c>
       <c r="I158" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="J158" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="K158" t="s">
         <v>569</v>
@@ -8850,16 +8850,16 @@
         <v>618</v>
       </c>
       <c r="G159" t="s">
+        <v>566</v>
+      </c>
+      <c r="H159" t="s">
         <v>338</v>
       </c>
-      <c r="H159" t="s">
-        <v>566</v>
-      </c>
       <c r="I159" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="J159" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="K159" t="s">
         <v>569</v>
@@ -8885,16 +8885,16 @@
         <v>618</v>
       </c>
       <c r="G160" t="s">
+        <v>566</v>
+      </c>
+      <c r="H160" t="s">
         <v>338</v>
       </c>
-      <c r="H160" t="s">
-        <v>566</v>
-      </c>
       <c r="I160" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="J160" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="K160" t="s">
         <v>569</v>
@@ -8920,16 +8920,16 @@
         <v>618</v>
       </c>
       <c r="G161" t="s">
+        <v>566</v>
+      </c>
+      <c r="H161" t="s">
         <v>338</v>
       </c>
-      <c r="H161" t="s">
-        <v>566</v>
-      </c>
       <c r="I161" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="J161" t="s">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="K161" t="s">
         <v>569</v>
@@ -8955,16 +8955,16 @@
         <v>639</v>
       </c>
       <c r="G162" t="s">
+        <v>566</v>
+      </c>
+      <c r="H162" t="s">
         <v>338</v>
       </c>
-      <c r="H162" t="s">
-        <v>566</v>
-      </c>
       <c r="I162" t="s">
-        <v>567</v>
+        <v>640</v>
       </c>
       <c r="J162" t="s">
-        <v>640</v>
+        <v>568</v>
       </c>
       <c r="K162" t="s">
         <v>569</v>
@@ -8984,22 +8984,22 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
+        <v>564</v>
+      </c>
+      <c r="F163" t="s">
         <v>644</v>
       </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
         <v>645</v>
       </c>
-      <c r="G163" t="s">
+      <c r="H163" t="s">
         <v>338</v>
       </c>
-      <c r="H163" t="s">
-        <v>566</v>
-      </c>
       <c r="I163" t="s">
-        <v>567</v>
+        <v>642</v>
       </c>
       <c r="J163" t="s">
-        <v>642</v>
+        <v>568</v>
       </c>
       <c r="K163" t="s">
         <v>569</v>
@@ -9025,16 +9025,16 @@
         <v>649</v>
       </c>
       <c r="G164" t="s">
+        <v>566</v>
+      </c>
+      <c r="H164" t="s">
         <v>338</v>
       </c>
-      <c r="H164" t="s">
-        <v>566</v>
-      </c>
       <c r="I164" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="J164" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K164" t="s">
         <v>569</v>
@@ -9060,16 +9060,16 @@
         <v>649</v>
       </c>
       <c r="G165" t="s">
+        <v>566</v>
+      </c>
+      <c r="H165" t="s">
         <v>338</v>
       </c>
-      <c r="H165" t="s">
-        <v>566</v>
-      </c>
       <c r="I165" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="J165" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K165" t="s">
         <v>569</v>
@@ -9095,16 +9095,16 @@
         <v>649</v>
       </c>
       <c r="G166" t="s">
+        <v>566</v>
+      </c>
+      <c r="H166" t="s">
         <v>338</v>
       </c>
-      <c r="H166" t="s">
-        <v>566</v>
-      </c>
       <c r="I166" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="J166" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K166" t="s">
         <v>569</v>
@@ -9130,16 +9130,16 @@
         <v>649</v>
       </c>
       <c r="G167" t="s">
+        <v>566</v>
+      </c>
+      <c r="H167" t="s">
         <v>338</v>
       </c>
-      <c r="H167" t="s">
-        <v>566</v>
-      </c>
       <c r="I167" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="J167" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K167" t="s">
         <v>569</v>
@@ -9159,22 +9159,22 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>663</v>
+        <v>564</v>
       </c>
       <c r="F168" t="s">
         <v>649</v>
       </c>
       <c r="G168" t="s">
+        <v>663</v>
+      </c>
+      <c r="H168" t="s">
         <v>338</v>
       </c>
-      <c r="H168" t="s">
-        <v>566</v>
-      </c>
       <c r="I168" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="J168" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K168" t="s">
         <v>569</v>
@@ -9191,22 +9191,22 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>663</v>
+        <v>564</v>
       </c>
       <c r="F169" t="s">
         <v>649</v>
       </c>
       <c r="G169" t="s">
+        <v>663</v>
+      </c>
+      <c r="H169" t="s">
         <v>338</v>
       </c>
-      <c r="H169" t="s">
-        <v>566</v>
-      </c>
       <c r="I169" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="J169" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K169" t="s">
         <v>569</v>
@@ -9232,16 +9232,16 @@
         <v>649</v>
       </c>
       <c r="G170" t="s">
+        <v>566</v>
+      </c>
+      <c r="H170" t="s">
         <v>338</v>
       </c>
-      <c r="H170" t="s">
-        <v>566</v>
-      </c>
       <c r="I170" t="s">
-        <v>567</v>
+        <v>650</v>
       </c>
       <c r="J170" t="s">
-        <v>650</v>
+        <v>568</v>
       </c>
       <c r="K170" t="s">
         <v>569</v>
@@ -9261,19 +9261,19 @@
         <v>14</v>
       </c>
       <c r="E171" t="s">
+        <v>672</v>
+      </c>
+      <c r="G171" t="s">
         <v>337</v>
       </c>
-      <c r="G171" t="s">
+      <c r="H171" t="s">
         <v>338</v>
       </c>
-      <c r="H171" t="s">
+      <c r="J171" t="s">
+        <v>673</v>
+      </c>
+      <c r="K171" t="s">
         <v>339</v>
-      </c>
-      <c r="I171" t="s">
-        <v>672</v>
-      </c>
-      <c r="K171" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -9290,19 +9290,19 @@
         <v>14</v>
       </c>
       <c r="E172" t="s">
+        <v>672</v>
+      </c>
+      <c r="G172" t="s">
         <v>243</v>
       </c>
-      <c r="G172" t="s">
-        <v>235</v>
-      </c>
       <c r="H172" t="s">
+        <v>236</v>
+      </c>
+      <c r="J172" t="s">
+        <v>673</v>
+      </c>
+      <c r="K172" t="s">
         <v>244</v>
-      </c>
-      <c r="I172" t="s">
-        <v>672</v>
-      </c>
-      <c r="K172" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -9319,19 +9319,19 @@
         <v>14</v>
       </c>
       <c r="E173" t="s">
+        <v>672</v>
+      </c>
+      <c r="G173" t="s">
         <v>337</v>
       </c>
-      <c r="G173" t="s">
+      <c r="H173" t="s">
         <v>338</v>
       </c>
-      <c r="H173" t="s">
+      <c r="J173" t="s">
+        <v>673</v>
+      </c>
+      <c r="K173" t="s">
         <v>339</v>
-      </c>
-      <c r="I173" t="s">
-        <v>672</v>
-      </c>
-      <c r="K173" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -9348,19 +9348,19 @@
         <v>14</v>
       </c>
       <c r="E174" t="s">
+        <v>672</v>
+      </c>
+      <c r="G174" t="s">
         <v>337</v>
       </c>
-      <c r="G174" t="s">
+      <c r="H174" t="s">
         <v>338</v>
       </c>
-      <c r="H174" t="s">
+      <c r="J174" t="s">
+        <v>673</v>
+      </c>
+      <c r="K174" t="s">
         <v>339</v>
-      </c>
-      <c r="I174" t="s">
-        <v>672</v>
-      </c>
-      <c r="K174" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -9377,19 +9377,19 @@
         <v>14</v>
       </c>
       <c r="E175" t="s">
+        <v>672</v>
+      </c>
+      <c r="G175" t="s">
         <v>337</v>
       </c>
-      <c r="G175" t="s">
+      <c r="H175" t="s">
         <v>338</v>
       </c>
-      <c r="H175" t="s">
+      <c r="J175" t="s">
+        <v>673</v>
+      </c>
+      <c r="K175" t="s">
         <v>339</v>
-      </c>
-      <c r="I175" t="s">
-        <v>672</v>
-      </c>
-      <c r="K175" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -9403,19 +9403,19 @@
         <v>14</v>
       </c>
       <c r="E176" t="s">
+        <v>672</v>
+      </c>
+      <c r="G176" t="s">
         <v>337</v>
       </c>
-      <c r="G176" t="s">
+      <c r="H176" t="s">
         <v>338</v>
       </c>
-      <c r="H176" t="s">
+      <c r="J176" t="s">
+        <v>673</v>
+      </c>
+      <c r="K176" t="s">
         <v>339</v>
-      </c>
-      <c r="I176" t="s">
-        <v>672</v>
-      </c>
-      <c r="K176" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -9432,19 +9432,19 @@
         <v>14</v>
       </c>
       <c r="E177" t="s">
+        <v>691</v>
+      </c>
+      <c r="G177" t="s">
         <v>337</v>
       </c>
-      <c r="G177" t="s">
+      <c r="H177" t="s">
         <v>338</v>
       </c>
-      <c r="H177" t="s">
+      <c r="J177" t="s">
+        <v>692</v>
+      </c>
+      <c r="K177" t="s">
         <v>339</v>
-      </c>
-      <c r="I177" t="s">
-        <v>691</v>
-      </c>
-      <c r="K177" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -9461,19 +9461,19 @@
         <v>14</v>
       </c>
       <c r="E178" t="s">
+        <v>691</v>
+      </c>
+      <c r="G178" t="s">
         <v>337</v>
       </c>
-      <c r="G178" t="s">
+      <c r="H178" t="s">
         <v>338</v>
       </c>
-      <c r="H178" t="s">
+      <c r="J178" t="s">
+        <v>692</v>
+      </c>
+      <c r="K178" t="s">
         <v>339</v>
-      </c>
-      <c r="I178" t="s">
-        <v>691</v>
-      </c>
-      <c r="K178" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -9490,19 +9490,19 @@
         <v>14</v>
       </c>
       <c r="E179" t="s">
+        <v>691</v>
+      </c>
+      <c r="G179" t="s">
         <v>337</v>
       </c>
-      <c r="G179" t="s">
+      <c r="H179" t="s">
         <v>338</v>
       </c>
-      <c r="H179" t="s">
+      <c r="J179" t="s">
+        <v>692</v>
+      </c>
+      <c r="K179" t="s">
         <v>339</v>
-      </c>
-      <c r="I179" t="s">
-        <v>691</v>
-      </c>
-      <c r="K179" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -9519,19 +9519,19 @@
         <v>14</v>
       </c>
       <c r="E180" t="s">
+        <v>691</v>
+      </c>
+      <c r="G180" t="s">
         <v>337</v>
       </c>
-      <c r="G180" t="s">
+      <c r="H180" t="s">
         <v>338</v>
       </c>
-      <c r="H180" t="s">
+      <c r="J180" t="s">
+        <v>692</v>
+      </c>
+      <c r="K180" t="s">
         <v>339</v>
-      </c>
-      <c r="I180" t="s">
-        <v>691</v>
-      </c>
-      <c r="K180" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -9554,10 +9554,10 @@
         <v>706</v>
       </c>
       <c r="G181" t="s">
+        <v>707</v>
+      </c>
+      <c r="H181" t="s">
         <v>338</v>
-      </c>
-      <c r="H181" t="s">
-        <v>707</v>
       </c>
       <c r="I181" t="s">
         <v>708</v>
@@ -9589,10 +9589,10 @@
         <v>706</v>
       </c>
       <c r="G182" t="s">
+        <v>707</v>
+      </c>
+      <c r="H182" t="s">
         <v>338</v>
-      </c>
-      <c r="H182" t="s">
-        <v>707</v>
       </c>
       <c r="I182" t="s">
         <v>708</v>
@@ -9624,10 +9624,10 @@
         <v>706</v>
       </c>
       <c r="G183" t="s">
+        <v>707</v>
+      </c>
+      <c r="H183" t="s">
         <v>338</v>
-      </c>
-      <c r="H183" t="s">
-        <v>707</v>
       </c>
       <c r="I183" t="s">
         <v>708</v>
@@ -9659,10 +9659,10 @@
         <v>706</v>
       </c>
       <c r="G184" t="s">
+        <v>707</v>
+      </c>
+      <c r="H184" t="s">
         <v>338</v>
-      </c>
-      <c r="H184" t="s">
-        <v>707</v>
       </c>
       <c r="I184" t="s">
         <v>708</v>
@@ -9694,10 +9694,10 @@
         <v>706</v>
       </c>
       <c r="G185" t="s">
+        <v>707</v>
+      </c>
+      <c r="H185" t="s">
         <v>338</v>
-      </c>
-      <c r="H185" t="s">
-        <v>707</v>
       </c>
       <c r="I185" t="s">
         <v>708</v>
@@ -9729,10 +9729,10 @@
         <v>706</v>
       </c>
       <c r="G186" t="s">
+        <v>707</v>
+      </c>
+      <c r="H186" t="s">
         <v>338</v>
-      </c>
-      <c r="H186" t="s">
-        <v>707</v>
       </c>
       <c r="I186" t="s">
         <v>708</v>
@@ -9764,10 +9764,10 @@
         <v>706</v>
       </c>
       <c r="G187" t="s">
+        <v>707</v>
+      </c>
+      <c r="H187" t="s">
         <v>338</v>
-      </c>
-      <c r="H187" t="s">
-        <v>707</v>
       </c>
       <c r="I187" t="s">
         <v>708</v>
@@ -9799,10 +9799,10 @@
         <v>706</v>
       </c>
       <c r="G188" t="s">
+        <v>707</v>
+      </c>
+      <c r="H188" t="s">
         <v>338</v>
-      </c>
-      <c r="H188" t="s">
-        <v>707</v>
       </c>
       <c r="I188" t="s">
         <v>708</v>
@@ -9834,10 +9834,10 @@
         <v>706</v>
       </c>
       <c r="G189" t="s">
+        <v>707</v>
+      </c>
+      <c r="H189" t="s">
         <v>338</v>
-      </c>
-      <c r="H189" t="s">
-        <v>707</v>
       </c>
       <c r="I189" t="s">
         <v>708</v>
@@ -9869,10 +9869,10 @@
         <v>706</v>
       </c>
       <c r="G190" t="s">
+        <v>707</v>
+      </c>
+      <c r="H190" t="s">
         <v>338</v>
-      </c>
-      <c r="H190" t="s">
-        <v>707</v>
       </c>
       <c r="I190" t="s">
         <v>708</v>
@@ -9904,10 +9904,10 @@
         <v>706</v>
       </c>
       <c r="G191" t="s">
+        <v>707</v>
+      </c>
+      <c r="H191" t="s">
         <v>338</v>
-      </c>
-      <c r="H191" t="s">
-        <v>707</v>
       </c>
       <c r="I191" t="s">
         <v>708</v>
@@ -9936,10 +9936,10 @@
         <v>706</v>
       </c>
       <c r="G192" t="s">
+        <v>707</v>
+      </c>
+      <c r="H192" t="s">
         <v>338</v>
-      </c>
-      <c r="H192" t="s">
-        <v>707</v>
       </c>
       <c r="I192" t="s">
         <v>708</v>
@@ -9965,16 +9965,16 @@
         <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>746</v>
+        <v>705</v>
       </c>
       <c r="F193" t="s">
         <v>706</v>
       </c>
       <c r="G193" t="s">
+        <v>746</v>
+      </c>
+      <c r="H193" t="s">
         <v>338</v>
-      </c>
-      <c r="H193" t="s">
-        <v>576</v>
       </c>
       <c r="I193" t="s">
         <v>708</v>
@@ -9983,7 +9983,7 @@
         <v>709</v>
       </c>
       <c r="K193" t="s">
-        <v>710</v>
+        <v>576</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -10006,10 +10006,10 @@
         <v>706</v>
       </c>
       <c r="G194" t="s">
+        <v>707</v>
+      </c>
+      <c r="H194" t="s">
         <v>338</v>
-      </c>
-      <c r="H194" t="s">
-        <v>707</v>
       </c>
       <c r="I194" t="s">
         <v>708</v>
@@ -10041,10 +10041,10 @@
         <v>706</v>
       </c>
       <c r="G195" t="s">
+        <v>707</v>
+      </c>
+      <c r="H195" t="s">
         <v>338</v>
-      </c>
-      <c r="H195" t="s">
-        <v>707</v>
       </c>
       <c r="I195" t="s">
         <v>708</v>
@@ -10076,10 +10076,10 @@
         <v>706</v>
       </c>
       <c r="G196" t="s">
+        <v>707</v>
+      </c>
+      <c r="H196" t="s">
         <v>338</v>
-      </c>
-      <c r="H196" t="s">
-        <v>707</v>
       </c>
       <c r="I196" t="s">
         <v>708</v>
@@ -10111,10 +10111,10 @@
         <v>706</v>
       </c>
       <c r="G197" t="s">
+        <v>707</v>
+      </c>
+      <c r="H197" t="s">
         <v>338</v>
-      </c>
-      <c r="H197" t="s">
-        <v>707</v>
       </c>
       <c r="I197" t="s">
         <v>708</v>
@@ -10146,10 +10146,10 @@
         <v>706</v>
       </c>
       <c r="G198" t="s">
+        <v>707</v>
+      </c>
+      <c r="H198" t="s">
         <v>338</v>
-      </c>
-      <c r="H198" t="s">
-        <v>707</v>
       </c>
       <c r="I198" t="s">
         <v>708</v>
@@ -10175,22 +10175,22 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
+        <v>705</v>
+      </c>
+      <c r="F199" t="s">
         <v>765</v>
       </c>
-      <c r="F199" t="s">
+      <c r="G199" t="s">
         <v>766</v>
       </c>
-      <c r="G199" t="s">
+      <c r="H199" t="s">
         <v>338</v>
       </c>
-      <c r="H199" t="s">
-        <v>707</v>
-      </c>
       <c r="I199" t="s">
-        <v>708</v>
+        <v>767</v>
       </c>
       <c r="J199" t="s">
-        <v>767</v>
+        <v>709</v>
       </c>
       <c r="K199" t="s">
         <v>710</v>
@@ -10210,22 +10210,22 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
+        <v>705</v>
+      </c>
+      <c r="F200" t="s">
         <v>765</v>
       </c>
-      <c r="F200" t="s">
+      <c r="G200" t="s">
         <v>766</v>
       </c>
-      <c r="G200" t="s">
+      <c r="H200" t="s">
         <v>338</v>
       </c>
-      <c r="H200" t="s">
-        <v>707</v>
-      </c>
       <c r="I200" t="s">
-        <v>708</v>
+        <v>767</v>
       </c>
       <c r="J200" t="s">
-        <v>767</v>
+        <v>709</v>
       </c>
       <c r="K200" t="s">
         <v>710</v>
@@ -10245,22 +10245,22 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
+        <v>705</v>
+      </c>
+      <c r="F201" t="s">
         <v>765</v>
       </c>
-      <c r="F201" t="s">
+      <c r="G201" t="s">
         <v>766</v>
       </c>
-      <c r="G201" t="s">
+      <c r="H201" t="s">
         <v>338</v>
       </c>
-      <c r="H201" t="s">
-        <v>707</v>
-      </c>
       <c r="I201" t="s">
-        <v>708</v>
+        <v>767</v>
       </c>
       <c r="J201" t="s">
-        <v>767</v>
+        <v>709</v>
       </c>
       <c r="K201" t="s">
         <v>710</v>
@@ -10277,22 +10277,22 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
+        <v>705</v>
+      </c>
+      <c r="F202" t="s">
         <v>765</v>
       </c>
-      <c r="F202" t="s">
+      <c r="G202" t="s">
         <v>766</v>
       </c>
-      <c r="G202" t="s">
+      <c r="H202" t="s">
         <v>338</v>
       </c>
-      <c r="H202" t="s">
-        <v>707</v>
-      </c>
       <c r="I202" t="s">
-        <v>708</v>
+        <v>767</v>
       </c>
       <c r="J202" t="s">
-        <v>767</v>
+        <v>709</v>
       </c>
       <c r="K202" t="s">
         <v>710</v>
@@ -10312,25 +10312,25 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
+        <v>705</v>
+      </c>
+      <c r="F203" t="s">
+        <v>765</v>
+      </c>
+      <c r="G203" t="s">
         <v>746</v>
       </c>
-      <c r="F203" t="s">
-        <v>766</v>
-      </c>
-      <c r="G203" t="s">
+      <c r="H203" t="s">
         <v>338</v>
       </c>
-      <c r="H203" t="s">
+      <c r="I203" t="s">
+        <v>767</v>
+      </c>
+      <c r="J203" t="s">
+        <v>709</v>
+      </c>
+      <c r="K203" t="s">
         <v>576</v>
-      </c>
-      <c r="I203" t="s">
-        <v>708</v>
-      </c>
-      <c r="J203" t="s">
-        <v>767</v>
-      </c>
-      <c r="K203" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10344,22 +10344,22 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
+        <v>705</v>
+      </c>
+      <c r="F204" t="s">
         <v>765</v>
       </c>
-      <c r="F204" t="s">
+      <c r="G204" t="s">
         <v>766</v>
       </c>
-      <c r="G204" t="s">
+      <c r="H204" t="s">
         <v>338</v>
       </c>
-      <c r="H204" t="s">
-        <v>707</v>
-      </c>
       <c r="I204" t="s">
-        <v>708</v>
+        <v>767</v>
       </c>
       <c r="J204" t="s">
-        <v>767</v>
+        <v>709</v>
       </c>
       <c r="K204" t="s">
         <v>710</v>
@@ -10379,22 +10379,22 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
+        <v>705</v>
+      </c>
+      <c r="F205" t="s">
         <v>784</v>
       </c>
-      <c r="F205" t="s">
+      <c r="G205" t="s">
         <v>785</v>
       </c>
-      <c r="G205" t="s">
+      <c r="H205" t="s">
         <v>338</v>
       </c>
-      <c r="H205" t="s">
-        <v>707</v>
-      </c>
       <c r="I205" t="s">
-        <v>708</v>
+        <v>786</v>
       </c>
       <c r="J205" t="s">
-        <v>786</v>
+        <v>709</v>
       </c>
       <c r="K205" t="s">
         <v>710</v>
@@ -10414,22 +10414,22 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
+        <v>705</v>
+      </c>
+      <c r="F206" t="s">
         <v>784</v>
       </c>
-      <c r="F206" t="s">
+      <c r="G206" t="s">
         <v>785</v>
       </c>
-      <c r="G206" t="s">
+      <c r="H206" t="s">
         <v>338</v>
       </c>
-      <c r="H206" t="s">
-        <v>707</v>
-      </c>
       <c r="I206" t="s">
-        <v>708</v>
+        <v>786</v>
       </c>
       <c r="J206" t="s">
-        <v>786</v>
+        <v>709</v>
       </c>
       <c r="K206" t="s">
         <v>710</v>
@@ -10446,22 +10446,22 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
+        <v>705</v>
+      </c>
+      <c r="F207" t="s">
         <v>784</v>
       </c>
-      <c r="F207" t="s">
+      <c r="G207" t="s">
         <v>785</v>
       </c>
-      <c r="G207" t="s">
+      <c r="H207" t="s">
         <v>338</v>
       </c>
-      <c r="H207" t="s">
-        <v>707</v>
-      </c>
       <c r="I207" t="s">
-        <v>708</v>
+        <v>786</v>
       </c>
       <c r="J207" t="s">
-        <v>786</v>
+        <v>709</v>
       </c>
       <c r="K207" t="s">
         <v>710</v>
@@ -10481,25 +10481,25 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
+        <v>705</v>
+      </c>
+      <c r="F208" t="s">
+        <v>784</v>
+      </c>
+      <c r="G208" t="s">
         <v>746</v>
       </c>
-      <c r="F208" t="s">
-        <v>785</v>
-      </c>
-      <c r="G208" t="s">
+      <c r="H208" t="s">
         <v>338</v>
       </c>
-      <c r="H208" t="s">
+      <c r="I208" t="s">
+        <v>786</v>
+      </c>
+      <c r="J208" t="s">
+        <v>709</v>
+      </c>
+      <c r="K208" t="s">
         <v>576</v>
-      </c>
-      <c r="I208" t="s">
-        <v>708</v>
-      </c>
-      <c r="J208" t="s">
-        <v>786</v>
-      </c>
-      <c r="K208" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10516,22 +10516,22 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
+        <v>705</v>
+      </c>
+      <c r="F209" t="s">
         <v>784</v>
       </c>
-      <c r="F209" t="s">
+      <c r="G209" t="s">
         <v>785</v>
       </c>
-      <c r="G209" t="s">
+      <c r="H209" t="s">
         <v>338</v>
       </c>
-      <c r="H209" t="s">
-        <v>707</v>
-      </c>
       <c r="I209" t="s">
-        <v>708</v>
+        <v>786</v>
       </c>
       <c r="J209" t="s">
-        <v>786</v>
+        <v>709</v>
       </c>
       <c r="K209" t="s">
         <v>710</v>
@@ -10557,10 +10557,10 @@
         <v>802</v>
       </c>
       <c r="G210" t="s">
+        <v>803</v>
+      </c>
+      <c r="H210" t="s">
         <v>338</v>
-      </c>
-      <c r="H210" t="s">
-        <v>803</v>
       </c>
       <c r="I210" t="s">
         <v>804</v>
@@ -10589,10 +10589,10 @@
         <v>802</v>
       </c>
       <c r="G211" t="s">
+        <v>803</v>
+      </c>
+      <c r="H211" t="s">
         <v>338</v>
-      </c>
-      <c r="H211" t="s">
-        <v>803</v>
       </c>
       <c r="I211" t="s">
         <v>804</v>
@@ -10624,10 +10624,10 @@
         <v>802</v>
       </c>
       <c r="G212" t="s">
+        <v>803</v>
+      </c>
+      <c r="H212" t="s">
         <v>338</v>
-      </c>
-      <c r="H212" t="s">
-        <v>803</v>
       </c>
       <c r="I212" t="s">
         <v>804</v>
@@ -10656,10 +10656,10 @@
         <v>802</v>
       </c>
       <c r="G213" t="s">
+        <v>803</v>
+      </c>
+      <c r="H213" t="s">
         <v>338</v>
-      </c>
-      <c r="H213" t="s">
-        <v>803</v>
       </c>
       <c r="I213" t="s">
         <v>804</v>
@@ -10691,10 +10691,10 @@
         <v>802</v>
       </c>
       <c r="G214" t="s">
+        <v>803</v>
+      </c>
+      <c r="H214" t="s">
         <v>338</v>
-      </c>
-      <c r="H214" t="s">
-        <v>803</v>
       </c>
       <c r="I214" t="s">
         <v>804</v>
@@ -10720,16 +10720,16 @@
         <v>14</v>
       </c>
       <c r="E215" t="s">
-        <v>765</v>
+        <v>801</v>
       </c>
       <c r="F215" t="s">
         <v>802</v>
       </c>
       <c r="G215" t="s">
+        <v>766</v>
+      </c>
+      <c r="H215" t="s">
         <v>338</v>
-      </c>
-      <c r="H215" t="s">
-        <v>707</v>
       </c>
       <c r="I215" t="s">
         <v>804</v>
@@ -10738,7 +10738,7 @@
         <v>805</v>
       </c>
       <c r="K215" t="s">
-        <v>806</v>
+        <v>710</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -10761,10 +10761,10 @@
         <v>802</v>
       </c>
       <c r="G216" t="s">
+        <v>803</v>
+      </c>
+      <c r="H216" t="s">
         <v>338</v>
-      </c>
-      <c r="H216" t="s">
-        <v>803</v>
       </c>
       <c r="I216" t="s">
         <v>804</v>
@@ -10796,10 +10796,10 @@
         <v>802</v>
       </c>
       <c r="G217" t="s">
+        <v>803</v>
+      </c>
+      <c r="H217" t="s">
         <v>338</v>
-      </c>
-      <c r="H217" t="s">
-        <v>803</v>
       </c>
       <c r="I217" t="s">
         <v>804</v>
@@ -10828,10 +10828,10 @@
         <v>802</v>
       </c>
       <c r="G218" t="s">
+        <v>803</v>
+      </c>
+      <c r="H218" t="s">
         <v>338</v>
-      </c>
-      <c r="H218" t="s">
-        <v>803</v>
       </c>
       <c r="I218" t="s">
         <v>804</v>
@@ -10860,10 +10860,10 @@
         <v>802</v>
       </c>
       <c r="G219" t="s">
+        <v>803</v>
+      </c>
+      <c r="H219" t="s">
         <v>338</v>
-      </c>
-      <c r="H219" t="s">
-        <v>803</v>
       </c>
       <c r="I219" t="s">
         <v>804</v>
@@ -10889,16 +10889,16 @@
         <v>14</v>
       </c>
       <c r="E220" t="s">
-        <v>663</v>
+        <v>801</v>
       </c>
       <c r="F220" t="s">
         <v>802</v>
       </c>
       <c r="G220" t="s">
+        <v>663</v>
+      </c>
+      <c r="H220" t="s">
         <v>338</v>
-      </c>
-      <c r="H220" t="s">
-        <v>566</v>
       </c>
       <c r="I220" t="s">
         <v>804</v>
@@ -10907,7 +10907,7 @@
         <v>805</v>
       </c>
       <c r="K220" t="s">
-        <v>806</v>
+        <v>569</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -10930,10 +10930,10 @@
         <v>802</v>
       </c>
       <c r="G221" t="s">
+        <v>803</v>
+      </c>
+      <c r="H221" t="s">
         <v>338</v>
-      </c>
-      <c r="H221" t="s">
-        <v>803</v>
       </c>
       <c r="I221" t="s">
         <v>804</v>
@@ -10965,10 +10965,10 @@
         <v>802</v>
       </c>
       <c r="G222" t="s">
+        <v>803</v>
+      </c>
+      <c r="H222" t="s">
         <v>338</v>
-      </c>
-      <c r="H222" t="s">
-        <v>803</v>
       </c>
       <c r="I222" t="s">
         <v>804</v>
@@ -10997,10 +10997,10 @@
         <v>802</v>
       </c>
       <c r="G223" t="s">
+        <v>803</v>
+      </c>
+      <c r="H223" t="s">
         <v>338</v>
-      </c>
-      <c r="H223" t="s">
-        <v>803</v>
       </c>
       <c r="I223" t="s">
         <v>804</v>
@@ -11032,10 +11032,10 @@
         <v>802</v>
       </c>
       <c r="G224" t="s">
+        <v>803</v>
+      </c>
+      <c r="H224" t="s">
         <v>338</v>
-      </c>
-      <c r="H224" t="s">
-        <v>803</v>
       </c>
       <c r="I224" t="s">
         <v>804</v>
@@ -11067,10 +11067,10 @@
         <v>802</v>
       </c>
       <c r="G225" t="s">
+        <v>803</v>
+      </c>
+      <c r="H225" t="s">
         <v>338</v>
-      </c>
-      <c r="H225" t="s">
-        <v>803</v>
       </c>
       <c r="I225" t="s">
         <v>804</v>
@@ -11096,16 +11096,16 @@
         <v>14</v>
       </c>
       <c r="E226" t="s">
-        <v>575</v>
+        <v>801</v>
       </c>
       <c r="F226" t="s">
         <v>802</v>
       </c>
       <c r="G226" t="s">
+        <v>575</v>
+      </c>
+      <c r="H226" t="s">
         <v>338</v>
-      </c>
-      <c r="H226" t="s">
-        <v>576</v>
       </c>
       <c r="I226" t="s">
         <v>804</v>
@@ -11114,7 +11114,7 @@
         <v>805</v>
       </c>
       <c r="K226" t="s">
-        <v>806</v>
+        <v>576</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -11137,10 +11137,10 @@
         <v>802</v>
       </c>
       <c r="G227" t="s">
+        <v>803</v>
+      </c>
+      <c r="H227" t="s">
         <v>338</v>
-      </c>
-      <c r="H227" t="s">
-        <v>803</v>
       </c>
       <c r="I227" t="s">
         <v>804</v>
@@ -11166,16 +11166,16 @@
         <v>14</v>
       </c>
       <c r="E228" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F228" t="s">
         <v>802</v>
       </c>
       <c r="G228" t="s">
+        <v>337</v>
+      </c>
+      <c r="H228" t="s">
         <v>338</v>
-      </c>
-      <c r="H228" t="s">
-        <v>339</v>
       </c>
       <c r="I228" t="s">
         <v>804</v>
@@ -11184,7 +11184,7 @@
         <v>805</v>
       </c>
       <c r="K228" t="s">
-        <v>806</v>
+        <v>339</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -11201,22 +11201,22 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
+        <v>801</v>
+      </c>
+      <c r="F229" t="s">
         <v>859</v>
       </c>
-      <c r="F229" t="s">
+      <c r="G229" t="s">
         <v>860</v>
       </c>
-      <c r="G229" t="s">
+      <c r="H229" t="s">
         <v>338</v>
       </c>
-      <c r="H229" t="s">
-        <v>803</v>
-      </c>
       <c r="I229" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="J229" t="s">
-        <v>861</v>
+        <v>805</v>
       </c>
       <c r="K229" t="s">
         <v>806</v>
@@ -11236,22 +11236,22 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
+        <v>801</v>
+      </c>
+      <c r="F230" t="s">
         <v>859</v>
       </c>
-      <c r="F230" t="s">
+      <c r="G230" t="s">
         <v>860</v>
       </c>
-      <c r="G230" t="s">
+      <c r="H230" t="s">
         <v>338</v>
       </c>
-      <c r="H230" t="s">
-        <v>803</v>
-      </c>
       <c r="I230" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="J230" t="s">
-        <v>861</v>
+        <v>805</v>
       </c>
       <c r="K230" t="s">
         <v>806</v>
@@ -11271,25 +11271,25 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
+        <v>801</v>
+      </c>
+      <c r="F231" t="s">
+        <v>859</v>
+      </c>
+      <c r="G231" t="s">
         <v>623</v>
       </c>
-      <c r="F231" t="s">
-        <v>860</v>
-      </c>
-      <c r="G231" t="s">
+      <c r="H231" t="s">
         <v>338</v>
       </c>
-      <c r="H231" t="s">
-        <v>566</v>
-      </c>
       <c r="I231" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="J231" t="s">
-        <v>861</v>
+        <v>805</v>
       </c>
       <c r="K231" t="s">
-        <v>806</v>
+        <v>569</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11306,25 +11306,25 @@
         <v>14</v>
       </c>
       <c r="E232" t="s">
+        <v>801</v>
+      </c>
+      <c r="F232" t="s">
+        <v>859</v>
+      </c>
+      <c r="G232" t="s">
         <v>663</v>
       </c>
-      <c r="F232" t="s">
-        <v>860</v>
-      </c>
-      <c r="G232" t="s">
+      <c r="H232" t="s">
         <v>338</v>
       </c>
-      <c r="H232" t="s">
-        <v>566</v>
-      </c>
       <c r="I232" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="J232" t="s">
-        <v>861</v>
+        <v>805</v>
       </c>
       <c r="K232" t="s">
-        <v>806</v>
+        <v>569</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11341,22 +11341,22 @@
         <v>14</v>
       </c>
       <c r="E233" t="s">
+        <v>801</v>
+      </c>
+      <c r="F233" t="s">
         <v>859</v>
       </c>
-      <c r="F233" t="s">
+      <c r="G233" t="s">
         <v>860</v>
       </c>
-      <c r="G233" t="s">
+      <c r="H233" t="s">
         <v>338</v>
       </c>
-      <c r="H233" t="s">
-        <v>803</v>
-      </c>
       <c r="I233" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="J233" t="s">
-        <v>861</v>
+        <v>805</v>
       </c>
       <c r="K233" t="s">
         <v>806</v>
@@ -11376,22 +11376,22 @@
         <v>14</v>
       </c>
       <c r="E234" t="s">
+        <v>801</v>
+      </c>
+      <c r="F234" t="s">
         <v>859</v>
       </c>
-      <c r="F234" t="s">
+      <c r="G234" t="s">
         <v>860</v>
       </c>
-      <c r="G234" t="s">
+      <c r="H234" t="s">
         <v>338</v>
       </c>
-      <c r="H234" t="s">
-        <v>803</v>
-      </c>
       <c r="I234" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="J234" t="s">
-        <v>861</v>
+        <v>805</v>
       </c>
       <c r="K234" t="s">
         <v>806</v>
@@ -11411,22 +11411,22 @@
         <v>14</v>
       </c>
       <c r="E235" t="s">
+        <v>801</v>
+      </c>
+      <c r="F235" t="s">
         <v>859</v>
       </c>
-      <c r="F235" t="s">
+      <c r="G235" t="s">
         <v>860</v>
       </c>
-      <c r="G235" t="s">
+      <c r="H235" t="s">
         <v>338</v>
       </c>
-      <c r="H235" t="s">
-        <v>803</v>
-      </c>
       <c r="I235" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="J235" t="s">
-        <v>861</v>
+        <v>805</v>
       </c>
       <c r="K235" t="s">
         <v>806</v>
@@ -11446,22 +11446,22 @@
         <v>14</v>
       </c>
       <c r="E236" t="s">
+        <v>801</v>
+      </c>
+      <c r="F236" t="s">
         <v>859</v>
       </c>
-      <c r="F236" t="s">
+      <c r="G236" t="s">
         <v>860</v>
       </c>
-      <c r="G236" t="s">
+      <c r="H236" t="s">
         <v>338</v>
       </c>
-      <c r="H236" t="s">
-        <v>803</v>
-      </c>
       <c r="I236" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="J236" t="s">
-        <v>861</v>
+        <v>805</v>
       </c>
       <c r="K236" t="s">
         <v>806</v>
@@ -11481,22 +11481,22 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
+        <v>801</v>
+      </c>
+      <c r="F237" t="s">
         <v>859</v>
       </c>
-      <c r="F237" t="s">
+      <c r="G237" t="s">
         <v>860</v>
       </c>
-      <c r="G237" t="s">
+      <c r="H237" t="s">
         <v>338</v>
       </c>
-      <c r="H237" t="s">
-        <v>803</v>
-      </c>
       <c r="I237" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="J237" t="s">
-        <v>861</v>
+        <v>805</v>
       </c>
       <c r="K237" t="s">
         <v>806</v>
@@ -11516,22 +11516,22 @@
         <v>14</v>
       </c>
       <c r="E238" t="s">
+        <v>801</v>
+      </c>
+      <c r="F238" t="s">
         <v>859</v>
       </c>
-      <c r="F238" t="s">
+      <c r="G238" t="s">
         <v>860</v>
       </c>
-      <c r="G238" t="s">
+      <c r="H238" t="s">
         <v>338</v>
       </c>
-      <c r="H238" t="s">
-        <v>803</v>
-      </c>
       <c r="I238" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="J238" t="s">
-        <v>861</v>
+        <v>805</v>
       </c>
       <c r="K238" t="s">
         <v>806</v>
@@ -11551,22 +11551,22 @@
         <v>14</v>
       </c>
       <c r="E239" t="s">
+        <v>801</v>
+      </c>
+      <c r="F239" t="s">
         <v>892</v>
       </c>
-      <c r="F239" t="s">
+      <c r="G239" t="s">
         <v>893</v>
       </c>
-      <c r="G239" t="s">
+      <c r="H239" t="s">
         <v>338</v>
       </c>
-      <c r="H239" t="s">
-        <v>803</v>
-      </c>
       <c r="I239" t="s">
-        <v>804</v>
+        <v>894</v>
       </c>
       <c r="J239" t="s">
-        <v>894</v>
+        <v>805</v>
       </c>
       <c r="K239" t="s">
         <v>806</v>
@@ -11586,25 +11586,25 @@
         <v>14</v>
       </c>
       <c r="E240" t="s">
+        <v>898</v>
+      </c>
+      <c r="F240" t="s">
+        <v>899</v>
+      </c>
+      <c r="G240" t="s">
         <v>337</v>
       </c>
-      <c r="F240" t="s">
+      <c r="H240" t="s">
+        <v>338</v>
+      </c>
+      <c r="I240" t="s">
         <v>898</v>
-      </c>
-      <c r="G240" t="s">
-        <v>338</v>
-      </c>
-      <c r="H240" t="s">
-        <v>339</v>
-      </c>
-      <c r="I240" t="s">
-        <v>899</v>
       </c>
       <c r="J240" t="s">
         <v>900</v>
       </c>
       <c r="K240" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -11621,25 +11621,25 @@
         <v>14</v>
       </c>
       <c r="E241" t="s">
+        <v>898</v>
+      </c>
+      <c r="F241" t="s">
+        <v>899</v>
+      </c>
+      <c r="G241" t="s">
         <v>337</v>
       </c>
-      <c r="F241" t="s">
+      <c r="H241" t="s">
+        <v>338</v>
+      </c>
+      <c r="I241" t="s">
         <v>898</v>
-      </c>
-      <c r="G241" t="s">
-        <v>338</v>
-      </c>
-      <c r="H241" t="s">
-        <v>339</v>
-      </c>
-      <c r="I241" t="s">
-        <v>899</v>
       </c>
       <c r="J241" t="s">
         <v>900</v>
       </c>
       <c r="K241" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -11656,25 +11656,25 @@
         <v>14</v>
       </c>
       <c r="E242" t="s">
+        <v>898</v>
+      </c>
+      <c r="F242" t="s">
+        <v>899</v>
+      </c>
+      <c r="G242" t="s">
         <v>337</v>
       </c>
-      <c r="F242" t="s">
+      <c r="H242" t="s">
+        <v>338</v>
+      </c>
+      <c r="I242" t="s">
         <v>898</v>
-      </c>
-      <c r="G242" t="s">
-        <v>338</v>
-      </c>
-      <c r="H242" t="s">
-        <v>339</v>
-      </c>
-      <c r="I242" t="s">
-        <v>899</v>
       </c>
       <c r="J242" t="s">
         <v>900</v>
       </c>
       <c r="K242" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -11691,25 +11691,25 @@
         <v>14</v>
       </c>
       <c r="E243" t="s">
+        <v>898</v>
+      </c>
+      <c r="F243" t="s">
+        <v>899</v>
+      </c>
+      <c r="G243" t="s">
         <v>337</v>
       </c>
-      <c r="F243" t="s">
+      <c r="H243" t="s">
+        <v>338</v>
+      </c>
+      <c r="I243" t="s">
         <v>898</v>
-      </c>
-      <c r="G243" t="s">
-        <v>338</v>
-      </c>
-      <c r="H243" t="s">
-        <v>339</v>
-      </c>
-      <c r="I243" t="s">
-        <v>899</v>
       </c>
       <c r="J243" t="s">
         <v>900</v>
       </c>
       <c r="K243" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -11726,25 +11726,25 @@
         <v>14</v>
       </c>
       <c r="E244" t="s">
+        <v>898</v>
+      </c>
+      <c r="F244" t="s">
+        <v>899</v>
+      </c>
+      <c r="G244" t="s">
         <v>337</v>
       </c>
-      <c r="F244" t="s">
+      <c r="H244" t="s">
+        <v>338</v>
+      </c>
+      <c r="I244" t="s">
         <v>898</v>
-      </c>
-      <c r="G244" t="s">
-        <v>338</v>
-      </c>
-      <c r="H244" t="s">
-        <v>339</v>
-      </c>
-      <c r="I244" t="s">
-        <v>899</v>
       </c>
       <c r="J244" t="s">
         <v>900</v>
       </c>
       <c r="K244" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -11761,25 +11761,25 @@
         <v>14</v>
       </c>
       <c r="E245" t="s">
+        <v>898</v>
+      </c>
+      <c r="F245" t="s">
+        <v>899</v>
+      </c>
+      <c r="G245" t="s">
         <v>337</v>
       </c>
-      <c r="F245" t="s">
+      <c r="H245" t="s">
+        <v>338</v>
+      </c>
+      <c r="I245" t="s">
         <v>898</v>
-      </c>
-      <c r="G245" t="s">
-        <v>338</v>
-      </c>
-      <c r="H245" t="s">
-        <v>339</v>
-      </c>
-      <c r="I245" t="s">
-        <v>899</v>
       </c>
       <c r="J245" t="s">
         <v>900</v>
       </c>
       <c r="K245" t="s">
-        <v>900</v>
+        <v>339</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -11793,25 +11793,25 @@
         <v>14</v>
       </c>
       <c r="E246" t="s">
+        <v>898</v>
+      </c>
+      <c r="F246" t="s">
         <v>918</v>
       </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
         <v>919</v>
       </c>
-      <c r="G246" t="s">
+      <c r="H246" t="s">
         <v>338</v>
       </c>
-      <c r="H246" t="s">
+      <c r="I246" t="s">
+        <v>920</v>
+      </c>
+      <c r="J246" t="s">
+        <v>900</v>
+      </c>
+      <c r="K246" t="s">
         <v>534</v>
-      </c>
-      <c r="I246" t="s">
-        <v>899</v>
-      </c>
-      <c r="J246" t="s">
-        <v>920</v>
-      </c>
-      <c r="K246" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11828,19 +11828,19 @@
         <v>14</v>
       </c>
       <c r="E247" t="s">
+        <v>924</v>
+      </c>
+      <c r="G247" t="s">
         <v>196</v>
       </c>
-      <c r="G247" t="s">
+      <c r="H247" t="s">
         <v>197</v>
       </c>
-      <c r="H247" t="s">
+      <c r="J247" t="s">
+        <v>925</v>
+      </c>
+      <c r="K247" t="s">
         <v>198</v>
-      </c>
-      <c r="I247" t="s">
-        <v>924</v>
-      </c>
-      <c r="K247" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -11857,19 +11857,19 @@
         <v>14</v>
       </c>
       <c r="E248" t="s">
+        <v>924</v>
+      </c>
+      <c r="G248" t="s">
         <v>196</v>
       </c>
-      <c r="G248" t="s">
+      <c r="H248" t="s">
         <v>197</v>
       </c>
-      <c r="H248" t="s">
+      <c r="J248" t="s">
+        <v>925</v>
+      </c>
+      <c r="K248" t="s">
         <v>198</v>
-      </c>
-      <c r="I248" t="s">
-        <v>924</v>
-      </c>
-      <c r="K248" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -11886,19 +11886,19 @@
         <v>14</v>
       </c>
       <c r="E249" t="s">
+        <v>924</v>
+      </c>
+      <c r="G249" t="s">
         <v>932</v>
       </c>
-      <c r="G249" t="s">
+      <c r="H249" t="s">
         <v>197</v>
       </c>
-      <c r="H249" t="s">
+      <c r="J249" t="s">
+        <v>925</v>
+      </c>
+      <c r="K249" t="s">
         <v>933</v>
-      </c>
-      <c r="I249" t="s">
-        <v>924</v>
-      </c>
-      <c r="K249" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -11915,19 +11915,19 @@
         <v>14</v>
       </c>
       <c r="E250" t="s">
+        <v>924</v>
+      </c>
+      <c r="G250" t="s">
         <v>196</v>
       </c>
-      <c r="G250" t="s">
+      <c r="H250" t="s">
         <v>197</v>
       </c>
-      <c r="H250" t="s">
+      <c r="J250" t="s">
+        <v>925</v>
+      </c>
+      <c r="K250" t="s">
         <v>198</v>
-      </c>
-      <c r="I250" t="s">
-        <v>924</v>
-      </c>
-      <c r="K250" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -11941,19 +11941,19 @@
         <v>14</v>
       </c>
       <c r="E251" t="s">
+        <v>924</v>
+      </c>
+      <c r="G251" t="s">
         <v>196</v>
       </c>
-      <c r="G251" t="s">
+      <c r="H251" t="s">
         <v>197</v>
       </c>
-      <c r="H251" t="s">
+      <c r="J251" t="s">
+        <v>925</v>
+      </c>
+      <c r="K251" t="s">
         <v>198</v>
-      </c>
-      <c r="I251" t="s">
-        <v>924</v>
-      </c>
-      <c r="K251" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -11970,19 +11970,19 @@
         <v>14</v>
       </c>
       <c r="E252" t="s">
+        <v>924</v>
+      </c>
+      <c r="G252" t="s">
         <v>196</v>
       </c>
-      <c r="G252" t="s">
+      <c r="H252" t="s">
         <v>197</v>
       </c>
-      <c r="H252" t="s">
+      <c r="J252" t="s">
+        <v>925</v>
+      </c>
+      <c r="K252" t="s">
         <v>198</v>
-      </c>
-      <c r="I252" t="s">
-        <v>924</v>
-      </c>
-      <c r="K252" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -11999,12 +11999,12 @@
         <v>944</v>
       </c>
       <c r="G253" t="s">
+        <v>945</v>
+      </c>
+      <c r="H253" t="s">
         <v>338</v>
       </c>
-      <c r="H253" t="s">
-        <v>945</v>
-      </c>
-      <c r="I253" t="s">
+      <c r="J253" t="s">
         <v>946</v>
       </c>
       <c r="K253" t="s">
@@ -12025,19 +12025,19 @@
         <v>14</v>
       </c>
       <c r="E254" t="s">
+        <v>944</v>
+      </c>
+      <c r="G254" t="s">
         <v>454</v>
       </c>
-      <c r="G254" t="s">
-        <v>189</v>
-      </c>
       <c r="H254" t="s">
+        <v>190</v>
+      </c>
+      <c r="J254" t="s">
+        <v>946</v>
+      </c>
+      <c r="K254" t="s">
         <v>455</v>
-      </c>
-      <c r="I254" t="s">
-        <v>946</v>
-      </c>
-      <c r="K254" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -12054,19 +12054,19 @@
         <v>14</v>
       </c>
       <c r="E255" t="s">
+        <v>944</v>
+      </c>
+      <c r="G255" t="s">
         <v>954</v>
       </c>
-      <c r="G255" t="s">
-        <v>189</v>
-      </c>
       <c r="H255" t="s">
+        <v>190</v>
+      </c>
+      <c r="J255" t="s">
+        <v>946</v>
+      </c>
+      <c r="K255" t="s">
         <v>955</v>
-      </c>
-      <c r="I255" t="s">
-        <v>946</v>
-      </c>
-      <c r="K255" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -12083,19 +12083,19 @@
         <v>14</v>
       </c>
       <c r="E256" t="s">
+        <v>944</v>
+      </c>
+      <c r="G256" t="s">
         <v>954</v>
       </c>
-      <c r="G256" t="s">
-        <v>189</v>
-      </c>
       <c r="H256" t="s">
+        <v>190</v>
+      </c>
+      <c r="J256" t="s">
+        <v>946</v>
+      </c>
+      <c r="K256" t="s">
         <v>955</v>
-      </c>
-      <c r="I256" t="s">
-        <v>946</v>
-      </c>
-      <c r="K256" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -12112,19 +12112,19 @@
         <v>14</v>
       </c>
       <c r="E257" t="s">
+        <v>944</v>
+      </c>
+      <c r="G257" t="s">
         <v>954</v>
       </c>
-      <c r="G257" t="s">
-        <v>189</v>
-      </c>
       <c r="H257" t="s">
+        <v>190</v>
+      </c>
+      <c r="J257" t="s">
+        <v>946</v>
+      </c>
+      <c r="K257" t="s">
         <v>955</v>
-      </c>
-      <c r="I257" t="s">
-        <v>946</v>
-      </c>
-      <c r="K257" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -12141,19 +12141,19 @@
         <v>14</v>
       </c>
       <c r="E258" t="s">
-        <v>705</v>
+        <v>944</v>
       </c>
       <c r="G258" t="s">
+        <v>707</v>
+      </c>
+      <c r="H258" t="s">
         <v>338</v>
       </c>
-      <c r="H258" t="s">
-        <v>707</v>
-      </c>
-      <c r="I258" t="s">
+      <c r="J258" t="s">
         <v>946</v>
       </c>
       <c r="K258" t="s">
-        <v>947</v>
+        <v>710</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -12170,19 +12170,19 @@
         <v>14</v>
       </c>
       <c r="E259" t="s">
+        <v>944</v>
+      </c>
+      <c r="G259" t="s">
         <v>954</v>
       </c>
-      <c r="G259" t="s">
-        <v>189</v>
-      </c>
       <c r="H259" t="s">
+        <v>190</v>
+      </c>
+      <c r="J259" t="s">
+        <v>946</v>
+      </c>
+      <c r="K259" t="s">
         <v>955</v>
-      </c>
-      <c r="I259" t="s">
-        <v>946</v>
-      </c>
-      <c r="K259" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -12199,19 +12199,19 @@
         <v>14</v>
       </c>
       <c r="E260" t="s">
+        <v>944</v>
+      </c>
+      <c r="G260" t="s">
         <v>337</v>
       </c>
-      <c r="G260" t="s">
+      <c r="H260" t="s">
         <v>338</v>
       </c>
-      <c r="H260" t="s">
+      <c r="J260" t="s">
+        <v>946</v>
+      </c>
+      <c r="K260" t="s">
         <v>339</v>
-      </c>
-      <c r="I260" t="s">
-        <v>946</v>
-      </c>
-      <c r="K260" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -12228,19 +12228,19 @@
         <v>14</v>
       </c>
       <c r="E261" t="s">
+        <v>944</v>
+      </c>
+      <c r="G261" t="s">
         <v>973</v>
       </c>
-      <c r="G261" t="s">
+      <c r="H261" t="s">
         <v>406</v>
       </c>
-      <c r="H261" t="s">
+      <c r="J261" t="s">
+        <v>946</v>
+      </c>
+      <c r="K261" t="s">
         <v>974</v>
-      </c>
-      <c r="I261" t="s">
-        <v>946</v>
-      </c>
-      <c r="K261" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -12257,19 +12257,19 @@
         <v>14</v>
       </c>
       <c r="E262" t="s">
+        <v>944</v>
+      </c>
+      <c r="G262" t="s">
         <v>337</v>
       </c>
-      <c r="G262" t="s">
+      <c r="H262" t="s">
         <v>338</v>
       </c>
-      <c r="H262" t="s">
+      <c r="J262" t="s">
+        <v>946</v>
+      </c>
+      <c r="K262" t="s">
         <v>339</v>
-      </c>
-      <c r="I262" t="s">
-        <v>946</v>
-      </c>
-      <c r="K262" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -12286,19 +12286,19 @@
         <v>14</v>
       </c>
       <c r="E263" t="s">
+        <v>944</v>
+      </c>
+      <c r="G263" t="s">
         <v>981</v>
       </c>
-      <c r="G263" t="s">
+      <c r="H263" t="s">
         <v>378</v>
       </c>
-      <c r="H263" t="s">
+      <c r="J263" t="s">
+        <v>946</v>
+      </c>
+      <c r="K263" t="s">
         <v>982</v>
-      </c>
-      <c r="I263" t="s">
-        <v>946</v>
-      </c>
-      <c r="K263" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="264" spans="1:11">
@@ -12315,19 +12315,19 @@
         <v>14</v>
       </c>
       <c r="E264" t="s">
+        <v>944</v>
+      </c>
+      <c r="G264" t="s">
         <v>58</v>
       </c>
-      <c r="G264" t="s">
+      <c r="H264" t="s">
         <v>59</v>
       </c>
-      <c r="H264" t="s">
+      <c r="J264" t="s">
+        <v>946</v>
+      </c>
+      <c r="K264" t="s">
         <v>60</v>
-      </c>
-      <c r="I264" t="s">
-        <v>946</v>
-      </c>
-      <c r="K264" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -12344,7 +12344,7 @@
         <v>14</v>
       </c>
       <c r="E265" t="s">
-        <v>15</v>
+        <v>944</v>
       </c>
       <c r="G265" t="s">
         <v>17</v>
@@ -12352,11 +12352,11 @@
       <c r="H265" t="s">
         <v>18</v>
       </c>
-      <c r="I265" t="s">
+      <c r="J265" t="s">
         <v>946</v>
       </c>
       <c r="K265" t="s">
-        <v>947</v>
+        <v>21</v>
       </c>
     </row>
     <row r="266" spans="1:11">
@@ -12373,19 +12373,19 @@
         <v>14</v>
       </c>
       <c r="E266" t="s">
+        <v>944</v>
+      </c>
+      <c r="G266" t="s">
         <v>992</v>
       </c>
-      <c r="G266" t="s">
-        <v>235</v>
-      </c>
       <c r="H266" t="s">
+        <v>236</v>
+      </c>
+      <c r="J266" t="s">
+        <v>946</v>
+      </c>
+      <c r="K266" t="s">
         <v>993</v>
-      </c>
-      <c r="I266" t="s">
-        <v>946</v>
-      </c>
-      <c r="K266" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="267" spans="1:11">
@@ -12402,19 +12402,19 @@
         <v>14</v>
       </c>
       <c r="E267" t="s">
+        <v>997</v>
+      </c>
+      <c r="G267" t="s">
         <v>243</v>
       </c>
-      <c r="G267" t="s">
-        <v>235</v>
-      </c>
       <c r="H267" t="s">
+        <v>236</v>
+      </c>
+      <c r="J267" t="s">
+        <v>998</v>
+      </c>
+      <c r="K267" t="s">
         <v>244</v>
-      </c>
-      <c r="I267" t="s">
-        <v>997</v>
-      </c>
-      <c r="K267" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -12431,19 +12431,19 @@
         <v>14</v>
       </c>
       <c r="E268" t="s">
-        <v>420</v>
+        <v>1002</v>
       </c>
       <c r="G268" t="s">
+        <v>421</v>
+      </c>
+      <c r="H268" t="s">
         <v>378</v>
       </c>
-      <c r="H268" t="s">
-        <v>421</v>
-      </c>
-      <c r="I268" t="s">
-        <v>1002</v>
+      <c r="J268" t="s">
+        <v>1003</v>
       </c>
       <c r="K268" t="s">
-        <v>1003</v>
+        <v>423</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -12460,19 +12460,19 @@
         <v>14</v>
       </c>
       <c r="E269" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G269" t="s">
         <v>243</v>
       </c>
-      <c r="G269" t="s">
-        <v>235</v>
-      </c>
       <c r="H269" t="s">
+        <v>236</v>
+      </c>
+      <c r="J269" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K269" t="s">
         <v>244</v>
-      </c>
-      <c r="I269" t="s">
-        <v>1007</v>
-      </c>
-      <c r="K269" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -12489,19 +12489,19 @@
         <v>14</v>
       </c>
       <c r="E270" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G270" t="s">
         <v>243</v>
       </c>
-      <c r="G270" t="s">
-        <v>235</v>
-      </c>
       <c r="H270" t="s">
+        <v>236</v>
+      </c>
+      <c r="J270" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K270" t="s">
         <v>244</v>
-      </c>
-      <c r="I270" t="s">
-        <v>1007</v>
-      </c>
-      <c r="K270" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -12521,12 +12521,12 @@
         <v>1015</v>
       </c>
       <c r="G271" t="s">
-        <v>235</v>
+        <v>1016</v>
       </c>
       <c r="H271" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I271" t="s">
+        <v>236</v>
+      </c>
+      <c r="J271" t="s">
         <v>1017</v>
       </c>
       <c r="K271" t="s">
@@ -12547,12 +12547,12 @@
         <v>1015</v>
       </c>
       <c r="G272" t="s">
-        <v>235</v>
+        <v>1016</v>
       </c>
       <c r="H272" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I272" t="s">
+        <v>236</v>
+      </c>
+      <c r="J272" t="s">
         <v>1017</v>
       </c>
       <c r="K272" t="s">
@@ -12576,12 +12576,12 @@
         <v>1015</v>
       </c>
       <c r="G273" t="s">
-        <v>235</v>
+        <v>1016</v>
       </c>
       <c r="H273" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I273" t="s">
+        <v>236</v>
+      </c>
+      <c r="J273" t="s">
         <v>1017</v>
       </c>
       <c r="K273" t="s">
@@ -12602,12 +12602,12 @@
         <v>1015</v>
       </c>
       <c r="G274" t="s">
-        <v>235</v>
+        <v>1016</v>
       </c>
       <c r="H274" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I274" t="s">
+        <v>236</v>
+      </c>
+      <c r="J274" t="s">
         <v>1017</v>
       </c>
       <c r="K274" t="s">
@@ -12631,12 +12631,12 @@
         <v>1015</v>
       </c>
       <c r="G275" t="s">
-        <v>235</v>
+        <v>1016</v>
       </c>
       <c r="H275" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I275" t="s">
+        <v>236</v>
+      </c>
+      <c r="J275" t="s">
         <v>1017</v>
       </c>
       <c r="K275" t="s">
@@ -12660,12 +12660,12 @@
         <v>1015</v>
       </c>
       <c r="G276" t="s">
-        <v>235</v>
+        <v>1016</v>
       </c>
       <c r="H276" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I276" t="s">
+        <v>236</v>
+      </c>
+      <c r="J276" t="s">
         <v>1017</v>
       </c>
       <c r="K276" t="s">
@@ -12689,12 +12689,12 @@
         <v>1015</v>
       </c>
       <c r="G277" t="s">
-        <v>235</v>
+        <v>1016</v>
       </c>
       <c r="H277" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I277" t="s">
+        <v>236</v>
+      </c>
+      <c r="J277" t="s">
         <v>1017</v>
       </c>
       <c r="K277" t="s">
@@ -12715,19 +12715,19 @@
         <v>14</v>
       </c>
       <c r="E278" t="s">
-        <v>420</v>
+        <v>1038</v>
       </c>
       <c r="G278" t="s">
+        <v>421</v>
+      </c>
+      <c r="H278" t="s">
         <v>378</v>
       </c>
-      <c r="H278" t="s">
-        <v>421</v>
-      </c>
-      <c r="I278" t="s">
-        <v>1038</v>
+      <c r="J278" t="s">
+        <v>1039</v>
       </c>
       <c r="K278" t="s">
-        <v>1039</v>
+        <v>423</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -12744,19 +12744,19 @@
         <v>14</v>
       </c>
       <c r="E279" t="s">
-        <v>92</v>
+        <v>1038</v>
       </c>
       <c r="G279" t="s">
+        <v>94</v>
+      </c>
+      <c r="H279" t="s">
         <v>59</v>
       </c>
-      <c r="H279" t="s">
-        <v>94</v>
-      </c>
-      <c r="I279" t="s">
-        <v>1038</v>
+      <c r="J279" t="s">
+        <v>1039</v>
       </c>
       <c r="K279" t="s">
-        <v>1039</v>
+        <v>97</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -12773,7 +12773,7 @@
         <v>14</v>
       </c>
       <c r="E280" t="s">
-        <v>15</v>
+        <v>1038</v>
       </c>
       <c r="G280" t="s">
         <v>17</v>
@@ -12781,11 +12781,11 @@
       <c r="H280" t="s">
         <v>18</v>
       </c>
-      <c r="I280" t="s">
-        <v>1038</v>
+      <c r="J280" t="s">
+        <v>1039</v>
       </c>
       <c r="K280" t="s">
-        <v>1039</v>
+        <v>21</v>
       </c>
     </row>
     <row r="281" spans="1:11">
@@ -12802,19 +12802,19 @@
         <v>14</v>
       </c>
       <c r="E281" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G281" t="s">
         <v>352</v>
       </c>
-      <c r="G281" t="s">
-        <v>235</v>
-      </c>
       <c r="H281" t="s">
+        <v>236</v>
+      </c>
+      <c r="J281" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K281" t="s">
         <v>353</v>
-      </c>
-      <c r="I281" t="s">
-        <v>1038</v>
-      </c>
-      <c r="K281" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -12831,19 +12831,19 @@
         <v>14</v>
       </c>
       <c r="E282" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G282" t="s">
         <v>253</v>
       </c>
-      <c r="G282" t="s">
+      <c r="H282" t="s">
         <v>254</v>
       </c>
-      <c r="H282" t="s">
+      <c r="J282" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K282" t="s">
         <v>255</v>
-      </c>
-      <c r="I282" t="s">
-        <v>1038</v>
-      </c>
-      <c r="K282" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -12860,19 +12860,19 @@
         <v>14</v>
       </c>
       <c r="E283" t="s">
-        <v>892</v>
+        <v>1055</v>
       </c>
       <c r="G283" t="s">
+        <v>893</v>
+      </c>
+      <c r="H283" t="s">
         <v>338</v>
       </c>
-      <c r="H283" t="s">
-        <v>803</v>
-      </c>
-      <c r="I283" t="s">
-        <v>1055</v>
+      <c r="J283" t="s">
+        <v>1056</v>
       </c>
       <c r="K283" t="s">
-        <v>1056</v>
+        <v>806</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -12889,19 +12889,19 @@
         <v>14</v>
       </c>
       <c r="E284" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G284" t="s">
         <v>253</v>
       </c>
-      <c r="G284" t="s">
+      <c r="H284" t="s">
         <v>254</v>
       </c>
-      <c r="H284" t="s">
+      <c r="J284" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K284" t="s">
         <v>255</v>
-      </c>
-      <c r="I284" t="s">
-        <v>1060</v>
-      </c>
-      <c r="K284" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -12915,19 +12915,19 @@
         <v>14</v>
       </c>
       <c r="E285" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G285" t="s">
         <v>352</v>
       </c>
-      <c r="G285" t="s">
-        <v>235</v>
-      </c>
       <c r="H285" t="s">
+        <v>236</v>
+      </c>
+      <c r="J285" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K285" t="s">
         <v>353</v>
-      </c>
-      <c r="I285" t="s">
-        <v>1064</v>
-      </c>
-      <c r="K285" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -12944,19 +12944,19 @@
         <v>14</v>
       </c>
       <c r="E286" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G286" t="s">
         <v>981</v>
       </c>
-      <c r="G286" t="s">
+      <c r="H286" t="s">
         <v>378</v>
       </c>
-      <c r="H286" t="s">
+      <c r="J286" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K286" t="s">
         <v>982</v>
-      </c>
-      <c r="I286" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K286" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -12973,19 +12973,19 @@
         <v>14</v>
       </c>
       <c r="E287" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G287" t="s">
         <v>981</v>
       </c>
-      <c r="G287" t="s">
+      <c r="H287" t="s">
         <v>378</v>
       </c>
-      <c r="H287" t="s">
+      <c r="J287" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K287" t="s">
         <v>982</v>
-      </c>
-      <c r="I287" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K287" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -13002,19 +13002,19 @@
         <v>14</v>
       </c>
       <c r="E288" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G288" t="s">
         <v>75</v>
       </c>
-      <c r="G288" t="s">
-        <v>17</v>
-      </c>
       <c r="H288" t="s">
+        <v>18</v>
+      </c>
+      <c r="J288" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K288" t="s">
         <v>76</v>
-      </c>
-      <c r="I288" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K288" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -13031,19 +13031,19 @@
         <v>14</v>
       </c>
       <c r="E289" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G289" t="s">
         <v>58</v>
       </c>
-      <c r="G289" t="s">
+      <c r="H289" t="s">
         <v>59</v>
       </c>
-      <c r="H289" t="s">
+      <c r="J289" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K289" t="s">
         <v>60</v>
-      </c>
-      <c r="I289" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K289" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="290" spans="1:11">
@@ -13060,19 +13060,19 @@
         <v>14</v>
       </c>
       <c r="E290" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G290" t="s">
         <v>58</v>
       </c>
-      <c r="G290" t="s">
+      <c r="H290" t="s">
         <v>59</v>
       </c>
-      <c r="H290" t="s">
+      <c r="J290" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K290" t="s">
         <v>60</v>
-      </c>
-      <c r="I290" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K290" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -13089,19 +13089,19 @@
         <v>14</v>
       </c>
       <c r="E291" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G291" t="s">
         <v>352</v>
       </c>
-      <c r="G291" t="s">
-        <v>235</v>
-      </c>
       <c r="H291" t="s">
+        <v>236</v>
+      </c>
+      <c r="J291" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K291" t="s">
         <v>353</v>
-      </c>
-      <c r="I291" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K291" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -13118,19 +13118,19 @@
         <v>14</v>
       </c>
       <c r="E292" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G292" t="s">
         <v>352</v>
       </c>
-      <c r="G292" t="s">
-        <v>235</v>
-      </c>
       <c r="H292" t="s">
+        <v>236</v>
+      </c>
+      <c r="J292" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K292" t="s">
         <v>353</v>
-      </c>
-      <c r="I292" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K292" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -13147,19 +13147,19 @@
         <v>14</v>
       </c>
       <c r="E293" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G293" t="s">
         <v>352</v>
       </c>
-      <c r="G293" t="s">
-        <v>235</v>
-      </c>
       <c r="H293" t="s">
+        <v>236</v>
+      </c>
+      <c r="J293" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K293" t="s">
         <v>353</v>
-      </c>
-      <c r="I293" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K293" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -13176,19 +13176,19 @@
         <v>14</v>
       </c>
       <c r="E294" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G294" t="s">
         <v>352</v>
       </c>
-      <c r="G294" t="s">
-        <v>235</v>
-      </c>
       <c r="H294" t="s">
+        <v>236</v>
+      </c>
+      <c r="J294" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K294" t="s">
         <v>353</v>
-      </c>
-      <c r="I294" t="s">
-        <v>1069</v>
-      </c>
-      <c r="K294" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -13205,19 +13205,19 @@
         <v>14</v>
       </c>
       <c r="E295" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G295" t="s">
         <v>352</v>
       </c>
-      <c r="G295" t="s">
-        <v>235</v>
-      </c>
       <c r="H295" t="s">
+        <v>236</v>
+      </c>
+      <c r="J295" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K295" t="s">
         <v>353</v>
-      </c>
-      <c r="I295" t="s">
-        <v>1098</v>
-      </c>
-      <c r="K295" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="296" spans="1:11">
@@ -13234,19 +13234,19 @@
         <v>14</v>
       </c>
       <c r="E296" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G296" t="s">
         <v>352</v>
       </c>
-      <c r="G296" t="s">
-        <v>235</v>
-      </c>
       <c r="H296" t="s">
+        <v>236</v>
+      </c>
+      <c r="J296" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K296" t="s">
         <v>353</v>
-      </c>
-      <c r="I296" t="s">
-        <v>1098</v>
-      </c>
-      <c r="K296" t="s">
-        <v>1099</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/xlsx/en/SectorCOFOG.xlsx
@@ -31,24 +31,24 @@
     <t>codeforiati:group-name</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -64,24 +64,24 @@
     <t>Education</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -91,12 +91,12 @@
     <t>Educational buildings, equipment, materials; subsidiary services to education (boarding facilities, staff housing); language training; colloquia, seminars, lectures, etc.</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Research and studies on education effectiveness, relevance and quality; systematic evaluation and monitoring.</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
@@ -130,18 +130,18 @@
     <t>Formal and non-formal primary education for children; all elementary and first cycle systematic instruction; provision of learning materials.</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>Basic Education</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>Second cycle systematic instruction at junior level.</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>Second cycle systematic instruction at senior levels.</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>Secondary Education</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Elementary vocational training and secondary level technical education; on-the job training; apprenticeships; including informal vocational training.</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
@@ -256,18 +256,18 @@
     <t>Degree and diploma programmes at universities, colleges and polytechnics; scholarships.</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -277,12 +277,12 @@
     <t>Professional-level vocational training programmes and in-service training.</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
@@ -295,21 +295,21 @@
     <t>Health</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>Health, General</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -328,12 +328,12 @@
     <t>General medical research (excluding basic health research and research for prevention and control of NCDs (12382)).</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>Laboratories, specialised clinics and hospitals (including equipment and supplies); ambulances; dental services; medical rehabilitation. Excludes noncommunicable diseases (123xx).</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -382,12 +382,12 @@
     <t>District-level hospitals, clinics and dispensaries and related medical equipment; excluding specialised hospitals and clinics (12191).</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -583,6 +583,9 @@
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
@@ -592,9 +595,6 @@
     <t>140</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -604,15 +604,15 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>Large scale sewerage including trunk sewers and sewage pumping stations; domestic and industrial waste water treatment plants.</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>Municipal and industrial solid waste management, including hazardous and toxic waste; collection, disposal and treatment; landfill areas; composting and reuse.</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -718,24 +718,24 @@
     <t>Government &amp; Civil Society</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Fiscal policy and planning; support to ministries of finance; strengthening financial and managerial accountability; public expenditure management; improving financial management systems; budget drafting; inter-governmental fiscal relations, public audit, public debt. (Use code 15114 for domestic revenue mobilisation and code 33120 for customs).</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
@@ -760,12 +760,12 @@
     <t>Decentralisation processes (including political, administrative and fiscal dimensions); intergovernmental relations and federalism; strengthening departments of regional and local government, regional and local authorities and their national associations. (Use specific sector codes for decentralisation of sector management and services.)</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
@@ -775,15 +775,15 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -859,12 +859,12 @@
     <t>Support to administration of developing countries' foreign aid (including triangular and south-south cooperation).</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -943,12 +943,12 @@
     <t>Judicial law and order sectors; policy development within ministries of justice or equivalents.</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
@@ -958,12 +958,12 @@
     <t>Police affairs and services.</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Fire-prevention and fire-fighting affairs and services.</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>Prisons</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
@@ -1027,15 +1027,15 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -1072,12 +1072,12 @@
     <t>Electoral management bodies and processes, election observation, voters' education. (Use code 15230 when in the context of an international peacekeeping operation.)</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -1099,12 +1099,12 @@
     <t>Activities that support free and uncensored flow of information on public issues; activities that increase the editorial and technical skills and the integrity of the print and broadcast media, e.g. training of journalists. (Use codes 22010-22040 for provision of equipment and capital assistance to media.)</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -1147,15 +1147,15 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -1192,12 +1192,12 @@
     <t>Collection, production, management and dissemination of statistics and data related to Government &amp; Civil Society. Includes macroeconomic statistics, government finance, fiscal and public sector statistics, support to development of administrative data infrastructure, civil society surveys.</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -1231,15 +1231,15 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -1279,15 +1279,15 @@
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Social protection schemes in the form of cash or in-kind benefits, including pensions, against the risks linked to old age.</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -1348,12 +1348,12 @@
     <t>Employment policy and planning; institution capacity building and advice; employment creation and income generation programmes; including activities specifically designed for the needs of vulnerable groups.</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
@@ -1363,12 +1363,12 @@
     <t>Housing sector policy, planning and programmes; excluding low-cost housing and slum clearance (16040).</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
@@ -1378,12 +1378,12 @@
     <t>Including slum clearance.</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -1402,15 +1402,15 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -1444,12 +1444,12 @@
     <t>Recreation and sport</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -1528,12 +1528,12 @@
     <t>Road infrastructure, road vehicles; passenger road transport, motor passenger cars.</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -1615,12 +1615,12 @@
     <t>Whether or not related to transportation. Whenever possible, report storage projects under the sector of the resource being stored.</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -1684,12 +1684,12 @@
     <t>Radio and TV links, equipment; newspapers; printing and publishing.</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -1711,21 +1711,21 @@
     <t>Energy</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>Energy Policy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -1741,12 +1741,12 @@
     <t>Regulation of the energy sector, including wholesale and retail electricity provision.</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -1948,12 +1948,12 @@
     <t>See note regarding ODA eligibility of nuclear energy.</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -2134,21 +2134,21 @@
     <t>Agriculture, Forestry, Fishing</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2311,12 +2311,12 @@
     <t>Forestry sector policy, planning and programmes; institution capacity building and advice; forest surveys; unspecified forestry and agro-forestry activities.</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
     <t>Forestry</t>
   </si>
   <si>
@@ -2368,12 +2368,12 @@
     <t>Fishing sector policy, planning and programmes; institution capacity building and advice; ocean and coastal fishing; marine and freshwater fish surveys and prospecting; fishing boats/equipment; unspecified fishing activities.</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
     <t>Fishing</t>
   </si>
   <si>
@@ -2422,21 +2422,21 @@
     <t>Industry, Mining, Construction</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>Industry</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2593,12 +2593,12 @@
     <t>Mineral and mining sector policy, planning and programmes; mining legislation, mining cadastre, mineral resources inventory, information systems, institution capacity building and advice; unspecified mineral resources exploitation.</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
     <t>Mineral Resources &amp; Mining</t>
   </si>
   <si>
@@ -2692,12 +2692,12 @@
     <t>Construction sector policy and planning; excluding construction activities within specific sectors (e.g., hospital or school construction).</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
     <t>Construction</t>
   </si>
   <si>
@@ -2713,12 +2713,12 @@
     <t>Trade Policies &amp; Regulations</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -2770,12 +2770,12 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>04.7.3 - Tourism (CS)</t>
-  </si>
-  <si>
     <t>Tourism</t>
   </si>
   <si>
@@ -2812,12 +2812,12 @@
     <t>Including natural reserves and actions in the surrounding areas; other measures to protect endangered or vulnerable species and their habitats (e.g. wetlands preservation).</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -2851,15 +2851,15 @@
     <t>Other Multisector</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -2878,12 +2878,12 @@
     <t>Urban development and planning; urban management, land information systems.</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -2935,12 +2935,12 @@
     <t>Disaster risk reduction activities if not sector specific. Comprises risk assessments, structural prevention measures (e.g. flood prevention infrastructure), preparedness measures (e.g. early warning systems) normative prevention measures (e.g. building codes, land-use planning), and risk transfer systems (e.g. insurance schemes, risk funds). Also includes building local and national capacities and supporting the establishment of efficient and sustainable national structures able to promote disaster risk reduction.</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
@@ -2959,12 +2959,12 @@
     <t>Short or longer term household food security programmes and activities that improve the access of households to nutritionally adequate diets (excluding any cash transfers within broader social welfare programmes that do not have a specific food security, food acquisition or nutrition focus which should be reported under code 16010).</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -2992,12 +2992,12 @@
     <t>When sector cannot be identified.</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -3064,13 +3064,13 @@
     <t>Action Relating to Debt</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -3744,10 +3744,10 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -3759,7 +3759,7 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3814,10 +3814,10 @@
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
@@ -3829,7 +3829,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3858,10 +3858,10 @@
         <v>18</v>
       </c>
       <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s">
         <v>40</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
       </c>
       <c r="K6" t="s">
         <v>41</v>
@@ -3884,7 +3884,7 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
@@ -3893,13 +3893,13 @@
         <v>18</v>
       </c>
       <c r="I7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" t="s">
         <v>40</v>
       </c>
-      <c r="J7" t="s">
-        <v>20</v>
-      </c>
       <c r="K7" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3928,10 +3928,10 @@
         <v>18</v>
       </c>
       <c r="I8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s">
         <v>40</v>
-      </c>
-      <c r="J8" t="s">
-        <v>20</v>
       </c>
       <c r="K8" t="s">
         <v>41</v>
@@ -3963,10 +3963,10 @@
         <v>18</v>
       </c>
       <c r="I9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" t="s">
         <v>40</v>
-      </c>
-      <c r="J9" t="s">
-        <v>20</v>
       </c>
       <c r="K9" t="s">
         <v>41</v>
@@ -3998,10 +3998,10 @@
         <v>18</v>
       </c>
       <c r="I10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" t="s">
         <v>40</v>
-      </c>
-      <c r="J10" t="s">
-        <v>20</v>
       </c>
       <c r="K10" t="s">
         <v>41</v>
@@ -4024,22 +4024,22 @@
         <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" t="s">
         <v>40</v>
       </c>
-      <c r="J11" t="s">
-        <v>20</v>
-      </c>
       <c r="K11" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4059,22 +4059,22 @@
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
       </c>
       <c r="I12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" t="s">
         <v>40</v>
       </c>
-      <c r="J12" t="s">
-        <v>20</v>
-      </c>
       <c r="K12" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4094,22 +4094,22 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" t="s">
         <v>69</v>
-      </c>
-      <c r="G13" t="s">
-        <v>70</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" t="s">
         <v>71</v>
-      </c>
-      <c r="J13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4129,22 +4129,22 @@
         <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
       </c>
       <c r="I14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" t="s">
         <v>71</v>
-      </c>
-      <c r="J14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4173,10 +4173,10 @@
         <v>18</v>
       </c>
       <c r="I15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" t="s">
         <v>82</v>
-      </c>
-      <c r="J15" t="s">
-        <v>20</v>
       </c>
       <c r="K15" t="s">
         <v>83</v>
@@ -4199,22 +4199,22 @@
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" t="s">
         <v>82</v>
       </c>
-      <c r="J16" t="s">
-        <v>20</v>
-      </c>
       <c r="K16" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4240,7 +4240,7 @@
         <v>94</v>
       </c>
       <c r="H17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I17" t="s">
         <v>95</v>
@@ -4275,7 +4275,7 @@
         <v>94</v>
       </c>
       <c r="H18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I18" t="s">
         <v>95</v>
@@ -4304,13 +4304,13 @@
         <v>92</v>
       </c>
       <c r="F19" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I19" t="s">
         <v>95</v>
@@ -4319,7 +4319,7 @@
         <v>96</v>
       </c>
       <c r="K19" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4339,13 +4339,13 @@
         <v>92</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="G20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I20" t="s">
         <v>95</v>
@@ -4354,7 +4354,7 @@
         <v>96</v>
       </c>
       <c r="K20" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4380,7 +4380,7 @@
         <v>94</v>
       </c>
       <c r="H21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I21" t="s">
         <v>95</v>
@@ -4409,22 +4409,22 @@
         <v>92</v>
       </c>
       <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" t="s">
+        <v>95</v>
+      </c>
+      <c r="J22" t="s">
         <v>117</v>
       </c>
-      <c r="G22" t="s">
-        <v>58</v>
-      </c>
-      <c r="H22" t="s">
-        <v>59</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="K22" t="s">
         <v>118</v>
-      </c>
-      <c r="J22" t="s">
-        <v>96</v>
-      </c>
-      <c r="K22" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4444,22 +4444,22 @@
         <v>92</v>
       </c>
       <c r="F23" t="s">
+        <v>122</v>
+      </c>
+      <c r="G23" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" t="s">
+        <v>95</v>
+      </c>
+      <c r="J23" t="s">
         <v>117</v>
       </c>
-      <c r="G23" t="s">
-        <v>122</v>
-      </c>
-      <c r="H23" t="s">
-        <v>59</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
         <v>118</v>
-      </c>
-      <c r="J23" t="s">
-        <v>96</v>
-      </c>
-      <c r="K23" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4479,22 +4479,22 @@
         <v>92</v>
       </c>
       <c r="F24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" t="s">
+        <v>95</v>
+      </c>
+      <c r="J24" t="s">
         <v>117</v>
       </c>
-      <c r="G24" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
         <v>118</v>
-      </c>
-      <c r="J24" t="s">
-        <v>96</v>
-      </c>
-      <c r="K24" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4514,22 +4514,22 @@
         <v>92</v>
       </c>
       <c r="F25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" t="s">
+        <v>95</v>
+      </c>
+      <c r="J25" t="s">
         <v>117</v>
       </c>
-      <c r="G25" t="s">
-        <v>58</v>
-      </c>
-      <c r="H25" t="s">
-        <v>59</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>118</v>
-      </c>
-      <c r="J25" t="s">
-        <v>96</v>
-      </c>
-      <c r="K25" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4549,22 +4549,22 @@
         <v>92</v>
       </c>
       <c r="F26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H26" t="s">
+       